--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bikanervala GGN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="India BV" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="International BV" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haldiram India" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OM Sweets India" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Bikanervala GGN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Competitors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="India BV" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="International BV" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Haldiram India" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="OM Sweets India" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,8 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +41,19 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +64,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -94,6 +131,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,8 +512,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -477,6 +529,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="6" t="n">
+        <v>46300</v>
+      </c>
+      <c r="H1" s="6" t="n">
+        <v>46300</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -507,6 +565,16 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -539,6 +607,12 @@
           <t>https://share.google/JV7XDH4ryWmQNPfVY</t>
         </is>
       </c>
+      <c r="G3" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>4870</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -569,6 +643,12 @@
           <t>https://share.google/AXcgrOXWWfQtoSOkz</t>
         </is>
       </c>
+      <c r="G4" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>15774</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -599,6 +679,12 @@
           <t>https://share.google/Lq1yf4rveBX5BWyts</t>
         </is>
       </c>
+      <c r="G5" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>5513</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -629,6 +715,12 @@
           <t>https://share.google/5iiO04ZTn35j8E5HB</t>
         </is>
       </c>
+      <c r="G6" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>6534</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -659,6 +751,12 @@
           <t>https://share.google/iNagaqHoCbBOIvV0x</t>
         </is>
       </c>
+      <c r="G7" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>2387</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -689,6 +787,12 @@
           <t>https://share.google/S4Kwkg9xEW0S2j7a0</t>
         </is>
       </c>
+      <c r="G8" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>7161</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -719,6 +823,12 @@
           <t>https://share.google/NS8T7gwZSlKSNr3UP</t>
         </is>
       </c>
+      <c r="G9" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>3661</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -749,6 +859,12 @@
           <t>https://share.google/Xmyef4OwQmXyWCFN0</t>
         </is>
       </c>
+      <c r="G10" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>2775</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -779,6 +895,12 @@
           <t>https://share.google/6khAtgqK72w0kjN0Q</t>
         </is>
       </c>
+      <c r="G11" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>1094</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -809,6 +931,12 @@
           <t>https://share.google/CgukSORsdWkszVRvP</t>
         </is>
       </c>
+      <c r="G12" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>1108</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -839,6 +967,12 @@
           <t>https://share.google/BNfINmH1QbNZhf7ox</t>
         </is>
       </c>
+      <c r="G13" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>2211</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -869,6 +1003,12 @@
           <t>https://share.google/LJxUW77APw08Vr9a0</t>
         </is>
       </c>
+      <c r="G14" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>2347</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -899,6 +1039,12 @@
           <t>https://share.google/LAZMqwdryXVTeQkgt</t>
         </is>
       </c>
+      <c r="G15" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>2587</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -929,6 +1075,12 @@
           <t>https://share.google/lkP8lqhdoKZRzyal3</t>
         </is>
       </c>
+      <c r="G16" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>885</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -959,6 +1111,12 @@
           <t>https://share.google/255ZPlPOiTGMhDzy0</t>
         </is>
       </c>
+      <c r="G17" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>1326</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -989,6 +1147,12 @@
           <t>https://share.google/9TqthrgcK6VnEH9Kh</t>
         </is>
       </c>
+      <c r="G18" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>449</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1019,6 +1183,12 @@
           <t>https://share.google/uqXvcL4esuwjgcsRz</t>
         </is>
       </c>
+      <c r="G19" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>926</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1049,6 +1219,12 @@
           <t>https://share.google/E5KGOYYKX6YqD07hf</t>
         </is>
       </c>
+      <c r="G20" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>1091</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1079,6 +1255,12 @@
           <t>https://share.google/ooNGpI4Ewi9Zt5t02</t>
         </is>
       </c>
+      <c r="G21" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>788</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1109,6 +1291,12 @@
           <t>https://share.google/Z2RQtKISxQhQWQSl4</t>
         </is>
       </c>
+      <c r="G22" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>657</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1139,6 +1327,12 @@
           <t>https://share.google/grSJuehxs8v7sVOVt</t>
         </is>
       </c>
+      <c r="G23" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>696</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1169,6 +1363,12 @@
           <t>https://share.google/V1f6JY6CBgPW0eoIg</t>
         </is>
       </c>
+      <c r="G24" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>1430</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1199,6 +1399,12 @@
           <t>https://share.google/r13AfGhfeAFwXti2i</t>
         </is>
       </c>
+      <c r="G25" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>698</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1225,6 +1431,12 @@
           <t>https://share.google/e0rEvKWJDcji81RKF</t>
         </is>
       </c>
+      <c r="G26" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>356</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1251,6 +1463,12 @@
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>1165</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1263,8 +1481,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -1280,6 +1498,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="6" t="n">
+        <v>46300</v>
+      </c>
+      <c r="H1" s="6" t="n">
+        <v>46300</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1310,6 +1534,16 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -1342,6 +1576,12 @@
           <t>https://share.google/vwJnwPNeUQYJeEduL</t>
         </is>
       </c>
+      <c r="G3" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1394,6 +1634,12 @@
           <t>https://share.google/W7otAdG8FtptbWSwl</t>
         </is>
       </c>
+      <c r="G5" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>3862</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1424,6 +1670,12 @@
           <t>https://share.google/W7otAdG8FtptbWSwl</t>
         </is>
       </c>
+      <c r="G6" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>3862</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1454,6 +1706,12 @@
           <t>https://share.google/Z2RQtKISxQhQWQSl4</t>
         </is>
       </c>
+      <c r="G7" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>657</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1484,6 +1742,12 @@
           <t>https://share.google/lP3zeGY3pdczZ13a6</t>
         </is>
       </c>
+      <c r="G8" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1514,6 +1778,12 @@
           <t>https://share.google/lP3zeGY3pdczZ13a6</t>
         </is>
       </c>
+      <c r="G9" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1544,6 +1814,12 @@
           <t>https://share.google/lP3zeGY3pdczZ13a6</t>
         </is>
       </c>
+      <c r="G10" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1574,6 +1850,12 @@
           <t>https://share.google/z92S6uNfId7gh7xXh</t>
         </is>
       </c>
+      <c r="G11" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1604,6 +1886,12 @@
           <t>https://share.google/z92S6uNfId7gh7xXh</t>
         </is>
       </c>
+      <c r="G12" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1634,6 +1922,12 @@
           <t>https://share.google/76FqjGJdw3pWT7Nhm</t>
         </is>
       </c>
+      <c r="G13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>1820</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1664,6 +1958,12 @@
           <t>https://share.google/76FqjGJdw3pWT7Nhm</t>
         </is>
       </c>
+      <c r="G14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>1820</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1694,6 +1994,12 @@
           <t>https://share.google/76FqjGJdw3pWT7Nhm</t>
         </is>
       </c>
+      <c r="G15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>1820</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1746,6 +2052,12 @@
           <t>https://share.google/76FqjGJdw3pWT7Nhm</t>
         </is>
       </c>
+      <c r="G17" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>1820</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1776,6 +2088,12 @@
           <t>https://share.google/tK0HH6YhuhGFtmkpF</t>
         </is>
       </c>
+      <c r="G18" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>4500</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1806,6 +2124,12 @@
           <t>https://share.google/tK0HH6YhuhGFtmkpF</t>
         </is>
       </c>
+      <c r="G19" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>4500</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1836,6 +2160,12 @@
           <t>https://share.google/Xmyef4OwQmXyWCFN0</t>
         </is>
       </c>
+      <c r="G20" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>2775</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1866,6 +2196,12 @@
           <t>https://share.google/0fL448lM3UMCNEVP7</t>
         </is>
       </c>
+      <c r="G21" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>915</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1896,6 +2232,12 @@
           <t>https://share.google/0fL448lM3UMCNEVP7</t>
         </is>
       </c>
+      <c r="G22" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>915</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1926,6 +2268,12 @@
           <t>https://share.google/0fL448lM3UMCNEVP7</t>
         </is>
       </c>
+      <c r="G23" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>915</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1956,6 +2304,12 @@
           <t>https://share.google/0fL448lM3UMCNEVP7</t>
         </is>
       </c>
+      <c r="G24" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>915</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1986,6 +2340,12 @@
           <t>https://share.google/Ofv3RzFrXczsACnpP</t>
         </is>
       </c>
+      <c r="G25" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>847</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -2016,6 +2376,12 @@
           <t>https://share.google/Ofv3RzFrXczsACnpP</t>
         </is>
       </c>
+      <c r="G26" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>847</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -2046,6 +2412,12 @@
           <t>https://share.google/Ofv3RzFrXczsACnpP</t>
         </is>
       </c>
+      <c r="G27" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>847</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -2076,6 +2448,12 @@
           <t>https://share.google/xPXfeD0V5srbLT4eX</t>
         </is>
       </c>
+      <c r="G28" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>3601</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -2106,6 +2484,12 @@
           <t>https://share.google/xPXfeD0V5srbLT4eX</t>
         </is>
       </c>
+      <c r="G29" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>3601</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -2158,6 +2542,12 @@
           <t>https://share.google/BNfINmH1QbNZhf7ox</t>
         </is>
       </c>
+      <c r="G31" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>2211</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -2188,6 +2578,12 @@
           <t>https://share.google/aK8m7Ox6K0FZJ6Xwu</t>
         </is>
       </c>
+      <c r="G32" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>1042</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -2218,6 +2614,12 @@
           <t>https://share.google/aK8m7Ox6K0FZJ6Xwu</t>
         </is>
       </c>
+      <c r="G33" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>1042</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -2270,6 +2672,12 @@
           <t>https://share.google/7DhqfVESQtmCb7UZh</t>
         </is>
       </c>
+      <c r="G35" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>4834</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -2300,6 +2708,12 @@
           <t>https://share.google/7DhqfVESQtmCb7UZh</t>
         </is>
       </c>
+      <c r="G36" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>4834</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2330,6 +2744,12 @@
           <t>https://share.google/i9dx9ixhDINCZ9YbT</t>
         </is>
       </c>
+      <c r="G37" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>282</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -2360,6 +2780,12 @@
           <t>https://share.google/i9dx9ixhDINCZ9YbT</t>
         </is>
       </c>
+      <c r="G38" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>282</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -2390,6 +2816,12 @@
           <t>https://share.google/LAZMqwdryXVTeQkgt</t>
         </is>
       </c>
+      <c r="G39" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>2587</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2420,6 +2852,12 @@
           <t>https://share.google/9TqthrgcK6VnEH9Kh</t>
         </is>
       </c>
+      <c r="G40" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>449</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2450,6 +2888,12 @@
           <t>https://share.google/6khAtgqK72w0kjN0Q</t>
         </is>
       </c>
+      <c r="G41" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>1094</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -2480,6 +2924,12 @@
           <t>https://share.google/Jlgj9CSmiwGBJzq7p</t>
         </is>
       </c>
+      <c r="G42" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>11734</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -2510,6 +2960,12 @@
           <t>https://share.google/Jlgj9CSmiwGBJzq7p</t>
         </is>
       </c>
+      <c r="G43" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>11734</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -2540,6 +2996,12 @@
           <t>https://share.google/EFPYdy3wXu07YRAlK</t>
         </is>
       </c>
+      <c r="G44" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>191</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -2570,6 +3032,12 @@
           <t>https://share.google/EFPYdy3wXu07YRAlK</t>
         </is>
       </c>
+      <c r="G45" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>191</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -2600,6 +3068,12 @@
           <t>https://share.google/aioloSd77eFIRO9Ok</t>
         </is>
       </c>
+      <c r="G46" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -2630,6 +3104,12 @@
           <t>https://share.google/aioloSd77eFIRO9Ok</t>
         </is>
       </c>
+      <c r="G47" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -2660,6 +3140,12 @@
           <t>https://share.google/KaiqyN6GtR2mXupJW</t>
         </is>
       </c>
+      <c r="G48" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>1773</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -2689,6 +3175,12 @@
         <is>
           <t>https://share.google/KaiqyN6GtR2mXupJW</t>
         </is>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>1773</v>
       </c>
     </row>
     <row r="50">
@@ -3120,8 +3612,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F109"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -3137,6 +3629,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="6" t="n">
+        <v>46300</v>
+      </c>
+      <c r="H1" s="6" t="n">
+        <v>46300</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3167,6 +3665,16 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -3199,6 +3707,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Netaji+Subhash+Place+Delhi,+Shop+No.+01+ITL+Twin+Tower,+Netaji+Subhash+Place,+Pitampura,+New+Delhi,+Delhi+110034/@28.6911987,77.1522225,16z/data=!4m6!3m5!1s0x390d03c155555555:0x5b4d4b46cc7ccd4a!8m2!3d28.6911987!4d77.1522225!16s%2Fg%2F1tfldmlm?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
+      <c r="G3" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>2094</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -3229,6 +3743,12 @@
           <t>https://www.google.com/maps/place/Ground+Floor,+Bikanervala+%7C+Sadar+Bazaar,+Devika+Sadar,+Shop+No.+G+12,+G+14-19+7+G+24+-+44,+Qutab+Rd,+Narain+Market,+Sadar+Bazar,+New+Delhi,+Delhi+110006/@28.6558145,77.2162412,16z/data=!4m6!3m5!1s0x390cfde0b0b14249:0xc8e86801bdd1bfd0!8m2!3d28.6558145!4d77.2162412!16s%2Fg%2F11ksks6gbd?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
+      <c r="G4" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>631</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -3259,6 +3779,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Liberty+Cinema+Karol+Bagh/@28.6606284,77.1876003,17z/data=!3m1!4b1!4m6!3m5!1s0x390d03326d19a899:0xd2fef34572239279!8m2!3d28.6606284!4d77.1876003!16s%2Fg%2F11m5qhcscj?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G5" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>1555</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -3289,6 +3815,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Kalkaji+Metro/@28.5494507,77.259104,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce361d13dfecb:0x11d594dba2638f6d!8m2!3d28.5494507!4d77.259104!16s%2Fg%2F11x72l6mq2?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G6" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -3319,6 +3851,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Lajpat+Nagar+Delhi/@28.5708816,77.2390955,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce252e00cf3fb:0xf48521c45d7cd156!8m2!3d28.5708816!4d77.2390955!16s%2Fg%2F1td_wzrz?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>10882</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -3349,6 +3887,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Defence+Colony+Delhi/@28.5748765,77.2381202,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce3d5f019e1e9:0xa3e490839a38e681!8m2!3d28.5748765!4d77.2381202!16s%2Fg%2F11qb4tsxc0?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G8" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>2937</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -3379,6 +3923,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+East+of+Kailash+Delhi/@28.5587762,77.246459,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce39ca675e7c3:0xbe857ad66d22f2bf!8m2!3d28.5587762!4d77.246459!16s%2Fg%2F11s1qvx_74?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G9" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>217</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -3409,6 +3959,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Preet+Vihar+Delhi/@28.6392518,77.2948339,17z/data=!3m1!4b1!4m6!3m5!1s0x390cfb510ec67a93:0xfad0c088f3f91804!8m2!3d28.6392518!4d77.2948339!16s%2Fg%2F1tgnkg53?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G10" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>5139</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -3435,6 +3991,12 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>7302</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -3461,6 +4023,12 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>4869</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -3487,6 +4055,12 @@
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>948</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -3513,6 +4087,12 @@
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>1916</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -3539,6 +4119,12 @@
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>833</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -3565,6 +4151,12 @@
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>3402</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -3591,6 +4183,12 @@
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>5647</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -3617,6 +4215,12 @@
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>4601</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -3643,6 +4247,12 @@
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>5739</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -3669,6 +4279,12 @@
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>8133</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -3695,6 +4311,12 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>6604</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -3721,6 +4343,12 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>6274</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -3751,6 +4379,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Dwarka+Delhi/@28.5966087,77.0417524,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1b72556cb43b:0xdd37fb0751d2b900!8m2!3d28.5966087!4d77.0417524!16s%2Fg%2F11grt4vw5b?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G23" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>6217</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -3777,6 +4411,12 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>4692</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -3803,6 +4443,12 @@
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>6260</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -3829,6 +4475,12 @@
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>1900</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -3855,6 +4507,12 @@
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>8386</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -3881,6 +4539,12 @@
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>233</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -3911,6 +4575,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Chanakyapuri+Delhi/@28.585244,77.19149,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1d7cdedc3389:0x60798b43139c76d3!8m2!3d28.585244!4d77.19149!16s%2Fg%2F1tdvhkdv?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G29" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>8651</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -3937,6 +4607,12 @@
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>2775</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -3967,6 +4643,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+GK-II+Savitri+Cinema+Delhi/@28.5374253,77.2389712,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce22b17e2d781:0x40c5f102209b866c!8m2!3d28.5374253!4d77.2389712!16s%2Fg%2F11cmr0t9q8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G31" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>5575</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -3993,6 +4675,12 @@
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>5513</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -4023,6 +4711,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+57+Gurugram/@28.4161819,77.0849591,17z/data=!3m1!4b1!4m6!3m5!1s0x390d232798684757:0xb380904dacac7eed!8m2!3d28.4161819!4d77.0849591!16s%2Fg%2F11k522rkjz?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G33" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>4870</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -4049,6 +4743,12 @@
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>885</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -4075,6 +4775,12 @@
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>2587</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -4101,6 +4807,12 @@
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>696</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -4131,6 +4843,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+The+Esplanade+Mall+Sector+37+Gurugram/@28.4538074,76.9928507,17z/data=!3m1!4b1!4m6!3m5!1s0x390d171587c41467:0x4070a84c531d04ce!8m2!3d28.4538074!4d76.9928507!16s%2Fg%2F11tggmn3j8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G37" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>1328</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -4157,6 +4875,12 @@
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>1094</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -4183,6 +4907,12 @@
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>510</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -4209,6 +4939,12 @@
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>1091</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -4239,6 +4975,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+62+Gurugram/@28.4014616,77.0852188,17z/data=!3m1!4b1!4m6!3m5!1s0x390d23dcf278418d:0x4d1e11be0af4d661!8m2!3d28.4014616!4d77.0852188!16s%2Fg%2F11h7qrpfv4?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G41" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>449</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -4269,6 +5011,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+15+Gurugram/@28.4578375,77.0443773,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1902973194b5:0x7d02f6d383fb8a58!8m2!3d28.4578375!4d77.0443773!16s%2Fg%2F11trqkrhym?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G42" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>2387</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -4295,6 +5043,12 @@
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>2211</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -4321,6 +5075,12 @@
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>6534</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -4351,6 +5111,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+67+Gurugram/@28.3897015,77.0674498,17z/data=!3m1!4b1!4m6!3m5!1s0x390d23d7d3976715:0xb8dc58e2f64d1b2e!8m2!3d28.3897015!4d77.0674498!16s%2Fg%2F11h7ksct1w?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G45" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>1108</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -4381,6 +5147,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sohna+Road+Gurugram/@28.4253629,77.0390099,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1875d4418c91:0x3b4b144484bee44a!8m2!3d28.4253629!4d77.0390099!16s%2Fg%2F1wj_4f0r?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G46" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>7162</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -4407,6 +5179,12 @@
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>15774</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -4433,6 +5211,12 @@
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>3661</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -4463,6 +5247,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+80+Gurugram/@28.3766192,76.9593435,17z/data=!3m1!4b1!4m6!3m5!1s0x390d3da30c57ee59:0x82d80073b91470fc!8m2!3d28.3766192!4d76.9593435!16s%2Fg%2F11fhh4ykm5?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G49" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>2347</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -4489,6 +5279,12 @@
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>1885</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -4515,6 +5311,12 @@
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>7229</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -4541,6 +5343,12 @@
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>1693</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -4571,6 +5379,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+18+Noida/@28.5715738,77.3246799,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce44edd59cf9b:0x7abd947a6a0578bf!8m2!3d28.5715738!4d77.3246799!16s%2Fg%2F124sxkwj8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G53" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>9641</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -4601,6 +5415,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Gaur+City+Mall+Greater+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G54" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>796</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -4627,6 +5447,12 @@
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>7229</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -4653,6 +5479,12 @@
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>709</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -4683,6 +5515,12 @@
           <t>https://share.google/ROkTSrwbJf84BzhPA</t>
         </is>
       </c>
+      <c r="G57" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>429</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -4713,6 +5551,12 @@
           <t>https://share.google/zdFAyEbaRbQ5k484p</t>
         </is>
       </c>
+      <c r="G58" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>203</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -4743,6 +5587,12 @@
           <t>https://share.google/Lb3nqjJMTsd4B288R</t>
         </is>
       </c>
+      <c r="G59" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>656</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -4773,6 +5623,12 @@
           <t>https://share.google/UhwDLEldKfKeeOvuF</t>
         </is>
       </c>
+      <c r="G60" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -4803,6 +5659,12 @@
           <t>https://share.google/y3qxY9okUtRY9qT5G</t>
         </is>
       </c>
+      <c r="G61" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H61" s="9" t="n">
+        <v>2891</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -4833,6 +5695,12 @@
           <t>https://share.google/6IsINvdHSLIIHkIhQ</t>
         </is>
       </c>
+      <c r="G62" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H62" s="9" t="n">
+        <v>583</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -4863,6 +5731,12 @@
           <t>https://share.google/dyEWjeSFB5bMuBtCr</t>
         </is>
       </c>
+      <c r="G63" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>9251</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -4893,6 +5767,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Gaur+Biz+Park+Gaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G64" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>1005</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -4923,6 +5803,12 @@
           <t>https://www.google.com/maps/place/Plot+No.+12,+Bikanervala+%7C+Rajendra+Nagar,+Sahibabad,,+Rajender+Nagar,+Sector+5,+Rajendra+Nagar,+Sahibabad,+Ghaziabad,+Uttar+Pradesh+201005/@28.6780951,77.3592434,16z/data=!4m6!3m5!1s0x390cfa8b972e5a11:0x42944ce5f6223fbd!8m2!3d28.6780951!4d77.3592434!16s%2Fg%2F11b6gg2nvh?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
+      <c r="G65" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>3846</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -4953,6 +5839,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Choudhary+More+Ghaziabad/@28.656764,77.4343384,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf1cfc180871d:0x5aa84735b213aa6a!8m2!3d28.656764!4d77.4343384!16s%2Fg%2F11clr_s4v9?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G66" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H66" s="9" t="n">
+        <v>4137</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -4979,6 +5871,12 @@
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H67" s="9" t="n">
+        <v>10337</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -5005,6 +5903,12 @@
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H68" s="9" t="n">
+        <v>4287</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -5031,6 +5935,12 @@
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr"/>
+      <c r="G69" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H69" s="9" t="n">
+        <v>2202</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -5061,6 +5971,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+KW+Delhi+6/@28.696452,77.4352816,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf15e12b7409f:0x21ba0dd8e12c1453!8m2!3d28.696452!4d77.4352816!16s%2Fg%2F11jzgk44vp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G70" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H70" s="9" t="n">
+        <v>280</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -5091,6 +6007,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Modinagar/@28.8133765,77.5519765,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf5b71abce455:0xfc2ef5a0bb38f92!8m2!3d28.8133765!4d77.5519765!16s%2Fg%2F11ghftj4c1?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G71" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H71" s="9" t="n">
+        <v>6139</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -5117,6 +6039,12 @@
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H72" s="9" t="n">
+        <v>3743</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -5143,6 +6071,12 @@
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
+      <c r="G73" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H73" s="9" t="n">
+        <v>1100</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -5173,6 +6107,12 @@
           <t>https://www.google.com/maps/place/Bikanervala/@17.4003058,78.4774782,17z/data=!3m1!4b1!4m6!3m5!1s0x3bcb99dde5faac85:0xc52bb5f5f9e7c58a!8m2!3d17.4003058!4d78.4774782!16s%2Fg%2F11bxc61jfn?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G74" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H74" s="9" t="n">
+        <v>9514</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -5199,6 +6139,12 @@
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
+      <c r="G75" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H75" s="9" t="n">
+        <v>16965</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -5229,6 +6175,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Kothaguda+Hyderabad/@17.4580231,78.3731827,17z/data=!3m1!4b1!4m6!3m5!1s0x3bcb93cbab4eb893:0x81f819feba8d556b!8m2!3d17.4580231!4d78.3731827!16s%2Fg%2F11fkvr28k6?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G76" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H76" s="9" t="n">
+        <v>8556</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -5259,6 +6211,12 @@
           <t>https://www.google.com/maps/place/Bikanervala/@26.7851067,80.9918353,17z/data=!3m1!4b1!4m6!3m5!1s0x399be30647fd426d:0xd01584f16db3efe3!8m2!3d26.7851067!4d80.9918353!16s%2Fg%2F11jsr96pd9?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G77" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H77" s="9" t="n">
+        <v>2436</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -5285,6 +6243,12 @@
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" s="9" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -5315,6 +6279,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Emerald+Mall+Lucknow/@26.7879677,80.9106156,17z/data=!3m1!4b1!4m6!3m5!1s0x399bfda33d9b4ed1:0x4bc0f33320d7156b!8m2!3d26.7879677!4d80.9106156!16s%2Fg%2F11vs2f1qpf?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G79" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H79" s="9" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -5341,6 +6311,12 @@
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H80" s="9" t="n">
+        <v>1478</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -5367,6 +6343,16 @@
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -5393,6 +6379,12 @@
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H82" s="9" t="n">
+        <v>1419</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -5419,6 +6411,12 @@
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
+      <c r="G83" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H83" s="9" t="n">
+        <v>209</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -5445,6 +6443,12 @@
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr"/>
+      <c r="G84" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H84" s="9" t="n">
+        <v>287</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -5471,6 +6475,12 @@
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr"/>
+      <c r="G85" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H85" s="9" t="n">
+        <v>3934</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -5497,6 +6507,12 @@
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H86" s="9" t="n">
+        <v>467</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -5523,6 +6539,12 @@
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr"/>
+      <c r="G87" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H87" s="9" t="n">
+        <v>5254</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -5549,6 +6571,12 @@
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H88" s="9" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -5575,6 +6603,12 @@
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr"/>
+      <c r="G89" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H89" s="9" t="n">
+        <v>8385</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -5601,6 +6635,12 @@
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H90" s="9" t="n">
+        <v>3592</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -5627,6 +6667,12 @@
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H91" s="9" t="n">
+        <v>3220</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -5653,6 +6699,12 @@
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H92" s="9" t="n">
+        <v>2878</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -5679,6 +6731,12 @@
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H93" s="9" t="n">
+        <v>3770</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -5705,6 +6763,12 @@
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H94" s="9" t="n">
+        <v>1623</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -5731,6 +6795,12 @@
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr"/>
+      <c r="G95" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H95" s="9" t="n">
+        <v>7493</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -5757,6 +6827,12 @@
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H96" s="9" t="n">
+        <v>2835</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -5783,6 +6859,12 @@
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr"/>
+      <c r="G97" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H97" s="9" t="n">
+        <v>2870</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -5809,6 +6891,12 @@
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H98" s="9" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -5835,6 +6923,12 @@
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr"/>
+      <c r="G99" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H99" s="9" t="n">
+        <v>1689</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -5861,6 +6955,12 @@
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H100" s="9" t="n">
+        <v>2197</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -5887,6 +6987,12 @@
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr"/>
+      <c r="G101" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H101" s="9" t="n">
+        <v>288</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -5913,6 +7019,12 @@
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr"/>
+      <c r="G102" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H102" s="9" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -5939,6 +7051,12 @@
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr"/>
+      <c r="G103" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H103" s="9" t="n">
+        <v>848</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -5965,6 +7083,12 @@
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H104" s="9" t="n">
+        <v>427</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -5991,6 +7115,12 @@
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H105" s="9" t="n">
+        <v>883</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -6017,6 +7147,12 @@
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
+      <c r="G106" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H106" s="9" t="n">
+        <v>454</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -6043,6 +7179,12 @@
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H107" s="9" t="n">
+        <v>1517</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -6069,6 +7211,12 @@
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
+      <c r="G108" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H108" s="9" t="n">
+        <v>1864</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -6095,6 +7243,12 @@
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr"/>
+      <c r="G109" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H109" s="9" t="n">
+        <v>64</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6107,8 +7261,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -6124,6 +7278,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="6" t="n">
+        <v>46300</v>
+      </c>
+      <c r="H1" s="6" t="n">
+        <v>46300</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6154,6 +7314,16 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -6186,6 +7356,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Karama+%7C+Indian+Vegetarian+Restaurant+in+Dubai+-+4B+St+-+Sheikh+Khalifa+Bin+Zayed+St+-+behind+Park+Regis+Kris+Kin+Hotel+-+Al+Karama+-+Dubai+-+United+Arab+Emirates/@25.2487074,55.3022648,16z/data=!4m6!3m5!1s0x3e5f43263a32659d:0x3e7a496c31265a14!8m2!3d25.2487074!4d55.3022648!16s%2Fg%2F11fkl98x2w?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
+      <c r="G3" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>6982</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -6216,6 +7392,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Barsha+Heights+Dubai?hl=en</t>
         </is>
       </c>
+      <c r="G4" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>1718</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -6246,6 +7428,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Barsha+1+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1159702,55.2049553,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6bc01e76ba11:0x4fd1a9f4b2e6f5e3!8m2!3d25.1159702!4d55.2049553!16s%2Fg%2F1hhn4cw5b?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G5" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>3415</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -6276,6 +7464,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Arjan+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.0611644,55.2416108,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6f3d18bbdbdd:0xf394598ae51611cd!8m2!3d25.0611644!4d55.2416108!16s%2Fg%2F11k4t6j5kj?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G6" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>1348</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -6306,6 +7500,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Dubai+Hills+Mall+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1000884,55.2380841,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6ffb10c94323:0xe15233cd12b4c95e!8m2!3d25.1000884!4d55.2380841!16s%2Fg%2F11srb65qdy?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G7" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>1109</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -6336,6 +7536,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Sheikh+Zayed+Road+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2287901,55.2861116,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43aad3d78e71:0xb8b194cb916fd9b0!8m2!3d25.2287901!4d55.2861116!16s%2Fg%2F11spn08t8p?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G8" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>3363</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -6366,6 +7572,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Gold+Souk+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2720383,55.2977013,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43768964654b:0xc11f03b76b0ba714!8m2!3d25.2720383!4d55.2977013!16s%2Fg%2F11sqkp7mp7?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G9" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -6396,6 +7608,12 @@
           <t>https://www.google.com/maps/place/Bikanervala/@25.1971872,55.2793099,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43291308afa5:0xe48b7db44021ad9d!8m2!3d25.1971872!4d55.2793099!16s%2Fg%2F11h_6kxb_4?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G10" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>1195</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -6426,6 +7644,12 @@
           <t>https://www.google.com/maps/place/Bikanervala/@25.0443703,55.2301107,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6fbad2abf81f:0x2b8744ab6a1bf442!8m2!3d25.0443703!4d55.2301107!16s%2Fg%2F11wqdtyl9k?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G11" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>812</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -6452,6 +7676,12 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>3415</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -6482,6 +7712,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Jumeirah+3+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1568314,55.2048822,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6bf2c1bdccc9:0x43c26854ab27ef01!8m2!3d25.1568314!4d55.2048822!16s%2Fg%2F11s5twnr34?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G13" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>406</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -6512,6 +7748,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Furjan+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.0253394,55.1523478,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6d3bc9bcdbdb:0xe6f0ccdcb4b1e8ab!8m2!3d25.0253394!4d55.1523478!16s%2Fg%2F11g8kr7p26?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G14" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>3447</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -6542,6 +7784,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+International+City+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1587461,55.4044494,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6152822cefa7:0x62485254b618ad37!8m2!3d25.1587461!4d55.4044494!16s%2Fg%2F11fy4nt_fh?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G15" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>1986</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -6572,6 +7820,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Ghurair+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.268832,55.3167197,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f432a6356bd7d:0x6e8727a69863a0ea!8m2!3d25.268832!4d55.3167197!16s%2Fg%2F11gj4q5yml?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G16" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -6602,6 +7856,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Business+Bay+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1907081,55.2657305,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f69d43a494553:0xcae55dd8d4af25bc!8m2!3d25.1907081!4d55.2657305!16s%2Fg%2F11cnch2xjh?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G17" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>1329</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -6632,6 +7892,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Abu+Dhabi+%7C+Indian+Vegetarian+Restaurant+in+Abu+Dhabi/@24.4787181,54.3632708,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5e6797000fef8b:0x252e9c63c8d0f687!8m2!3d24.4787181!4d54.3632708!16s%2Fg%2F11j3jt3jck?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G18" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>4495</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -6662,6 +7928,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Qusais+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2779484,55.362064,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f5c5ef14f580b:0x42f37dd66cc3bd09!8m2!3d25.2779484!4d55.362064!16s%2Fg%2F11bbwn_ftp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G19" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>1660</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -6692,6 +7964,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Hounslow/@51.4697256,-0.3575675,17z/data=!3m1!4b1!4m6!3m5!1s0x48760db0ad77af37:0x259004b7a001719e!8m2!3d51.4697256!4d-0.3575675!16s%2Fg%2F11lw2pkxzp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G20" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>4366</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -6718,6 +7996,12 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>3833</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -6744,6 +8028,12 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -6770,6 +8060,12 @@
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>443</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -6796,6 +8092,12 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>1684</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -6822,6 +8124,12 @@
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>3362</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -6848,6 +8156,12 @@
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>1767</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -6874,6 +8188,12 @@
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>530</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -6900,6 +8220,12 @@
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>1325</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -6926,6 +8252,12 @@
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>638</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -6952,6 +8284,12 @@
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -6978,6 +8316,12 @@
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>1323</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -7004,6 +8348,12 @@
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>1427</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -7030,6 +8380,12 @@
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>1334</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -7056,6 +8412,12 @@
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>186</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -7082,6 +8444,12 @@
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -7108,6 +8476,12 @@
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>993</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -7134,6 +8508,12 @@
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>205</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -7160,6 +8540,12 @@
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>211</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -7186,6 +8572,12 @@
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>853</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -7212,6 +8604,12 @@
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>2234</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -7238,6 +8636,12 @@
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -7264,6 +8668,12 @@
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>1581</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -7290,6 +8700,12 @@
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>1165</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -7316,6 +8732,12 @@
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>474</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -7342,6 +8764,12 @@
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>370</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -7368,6 +8796,12 @@
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>937</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -7394,6 +8828,12 @@
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>2566</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -7420,6 +8860,12 @@
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>1429</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -7446,6 +8892,12 @@
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>1417</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -7472,6 +8924,12 @@
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>1549</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -7498,6 +8956,12 @@
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>2807</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -7524,6 +8988,12 @@
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>742</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -7550,6 +9020,12 @@
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>1224</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -7576,6 +9052,12 @@
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>673</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -7602,6 +9084,12 @@
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>420</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -7848,8 +9336,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F113"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H113"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -7865,6 +9353,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="6" t="n">
+        <v>46300</v>
+      </c>
+      <c r="H1" s="6" t="n">
+        <v>46300</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7895,6 +9389,16 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -7923,6 +9427,12 @@
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>4571</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -7949,6 +9459,12 @@
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>1228</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -7975,6 +9491,12 @@
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>460</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -8001,6 +9523,12 @@
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>11588</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -8027,6 +9555,12 @@
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -8053,6 +9587,12 @@
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>917</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -8079,6 +9619,12 @@
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>1604</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -8105,6 +9651,12 @@
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>1994</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -8131,6 +9683,12 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>3082</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -8157,6 +9715,12 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>3624</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -8183,6 +9747,12 @@
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>21261</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -8209,6 +9779,12 @@
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>2945</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -8235,6 +9811,12 @@
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>4200</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -8261,6 +9843,12 @@
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>2387</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -8287,6 +9875,12 @@
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -8313,6 +9907,12 @@
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>12119</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -8339,6 +9939,12 @@
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>3076</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -8365,6 +9971,12 @@
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>9245</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -8391,6 +10003,12 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -8417,6 +10035,12 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>6136</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -8443,6 +10067,12 @@
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>1734</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -8469,6 +10099,12 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>1060</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -8495,6 +10131,12 @@
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>2052</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -8521,6 +10163,12 @@
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>2776</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -8547,6 +10195,12 @@
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>11062</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -8573,6 +10227,12 @@
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>5490</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -8599,6 +10259,12 @@
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>4008</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -8625,6 +10291,12 @@
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>1579</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -8651,6 +10323,12 @@
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>1579</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -8677,6 +10355,12 @@
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>2808</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -8703,6 +10387,12 @@
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>18968</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -8729,6 +10419,12 @@
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>39673</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -8755,6 +10451,12 @@
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>5228</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -8781,6 +10483,12 @@
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>10370</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -8807,6 +10515,12 @@
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>7404</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -8833,6 +10547,12 @@
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>539</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -8859,6 +10579,12 @@
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>1124</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -8885,6 +10611,12 @@
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>539</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -8911,6 +10643,12 @@
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>2615</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -8937,6 +10675,12 @@
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>1441</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -8963,6 +10707,12 @@
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>955</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -8989,6 +10739,12 @@
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>4162</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -9015,6 +10771,12 @@
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>3480</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -9041,6 +10803,12 @@
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>7884</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -9067,6 +10835,12 @@
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>6136</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -9093,6 +10867,12 @@
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>983</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -9119,6 +10899,12 @@
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>3640</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -9145,6 +10931,12 @@
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -9171,6 +10963,12 @@
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>4116</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -9197,6 +10995,12 @@
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>308</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -9223,6 +11027,12 @@
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -9249,6 +11059,12 @@
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>4116</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -9275,6 +11091,12 @@
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -9301,6 +11123,12 @@
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>493</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -9327,6 +11155,12 @@
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>7852</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -9353,6 +11187,12 @@
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>4017</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -9379,6 +11219,12 @@
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>2840</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -9405,6 +11251,12 @@
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>2251</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -9431,6 +11283,12 @@
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H61" s="9" t="n">
+        <v>7819</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -9457,6 +11315,12 @@
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H62" s="9" t="n">
+        <v>3614</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -9483,6 +11347,12 @@
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>4769</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -9509,6 +11379,12 @@
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>2626</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -9535,6 +11411,12 @@
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr"/>
+      <c r="G65" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>2900</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -9561,6 +11443,12 @@
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H66" s="9" t="n">
+        <v>6441</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -9587,6 +11475,12 @@
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H67" s="9" t="n">
+        <v>781</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -9613,6 +11507,12 @@
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H68" s="9" t="n">
+        <v>19100</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -9639,6 +11539,12 @@
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr"/>
+      <c r="G69" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H69" s="9" t="n">
+        <v>2911</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -9665,6 +11571,12 @@
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H70" s="9" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -9691,6 +11603,12 @@
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H71" s="9" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -9717,6 +11635,12 @@
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H72" s="9" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -9743,6 +11667,12 @@
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
+      <c r="G73" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H73" s="9" t="n">
+        <v>3862</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -9769,6 +11699,12 @@
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H74" s="9" t="n">
+        <v>754</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -9795,6 +11731,12 @@
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
+      <c r="G75" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H75" s="9" t="n">
+        <v>4653</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -9821,6 +11763,12 @@
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H76" s="9" t="n">
+        <v>5286</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -9847,6 +11795,12 @@
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H77" s="9" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -9873,6 +11827,12 @@
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H78" s="9" t="n">
+        <v>1130</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -9899,6 +11859,12 @@
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr"/>
+      <c r="G79" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H79" s="9" t="n">
+        <v>634</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -9925,6 +11891,12 @@
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H80" s="9" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -9951,6 +11923,12 @@
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H81" s="9" t="n">
+        <v>1554</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -9977,6 +11955,12 @@
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H82" s="9" t="n">
+        <v>11734</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -10003,6 +11987,12 @@
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
+      <c r="G83" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H83" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -10029,6 +12019,12 @@
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr"/>
+      <c r="G84" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H84" s="9" t="n">
+        <v>5926</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -10055,6 +12051,12 @@
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr"/>
+      <c r="G85" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H85" s="9" t="n">
+        <v>3258</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -10081,6 +12083,12 @@
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H86" s="9" t="n">
+        <v>10418</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -10107,6 +12115,12 @@
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr"/>
+      <c r="G87" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H87" s="9" t="n">
+        <v>4151</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -10133,6 +12147,12 @@
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H88" s="9" t="n">
+        <v>2998</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -10159,6 +12179,12 @@
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr"/>
+      <c r="G89" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H89" s="9" t="n">
+        <v>1296</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -10185,6 +12211,12 @@
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H90" s="9" t="n">
+        <v>2233</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -10211,6 +12243,12 @@
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H91" s="9" t="n">
+        <v>7974</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -10237,6 +12275,12 @@
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H92" s="9" t="n">
+        <v>784</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -10263,6 +12307,12 @@
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H93" s="9" t="n">
+        <v>788</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -10289,6 +12339,12 @@
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H94" s="9" t="n">
+        <v>2595</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -10315,6 +12371,12 @@
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr"/>
+      <c r="G95" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H95" s="9" t="n">
+        <v>1677</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -10341,6 +12403,12 @@
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H96" s="9" t="n">
+        <v>6438</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -10367,6 +12435,12 @@
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr"/>
+      <c r="G97" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H97" s="9" t="n">
+        <v>2315</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -10393,6 +12467,12 @@
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H98" s="9" t="n">
+        <v>1933</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -10419,6 +12499,12 @@
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr"/>
+      <c r="G99" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H99" s="9" t="n">
+        <v>5568</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -10445,6 +12531,12 @@
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H100" s="9" t="n">
+        <v>17772</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -10471,6 +12563,12 @@
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr"/>
+      <c r="G101" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H101" s="9" t="n">
+        <v>6151</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -10497,6 +12595,12 @@
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr"/>
+      <c r="G102" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H102" s="9" t="n">
+        <v>5283</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -10523,6 +12627,12 @@
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr"/>
+      <c r="G103" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H103" s="9" t="n">
+        <v>1172</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -10549,6 +12659,12 @@
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H104" s="9" t="n">
+        <v>4076</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -10575,6 +12691,12 @@
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H105" s="9" t="n">
+        <v>1172</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -10601,6 +12723,12 @@
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
+      <c r="G106" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H106" s="9" t="n">
+        <v>10973</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -10627,6 +12755,12 @@
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H107" s="9" t="n">
+        <v>3159</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -10653,6 +12787,12 @@
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
+      <c r="G108" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H108" s="9" t="n">
+        <v>3052</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -10679,6 +12819,12 @@
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr"/>
+      <c r="G109" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H109" s="9" t="n">
+        <v>2619</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
@@ -10705,6 +12851,12 @@
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr"/>
+      <c r="G110" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H110" s="9" t="n">
+        <v>1879</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
@@ -10731,6 +12883,12 @@
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr"/>
+      <c r="G111" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H111" s="9" t="n">
+        <v>1196</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
@@ -10757,6 +12915,12 @@
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr"/>
+      <c r="G112" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H112" s="9" t="n">
+        <v>2446</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
@@ -10783,6 +12947,12 @@
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H113" s="9" t="n">
+        <v>2629</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10795,8 +12965,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -10812,6 +12982,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="6" t="n">
+        <v>46300</v>
+      </c>
+      <c r="H1" s="6" t="n">
+        <v>46300</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -10842,6 +13018,16 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -10870,6 +13056,12 @@
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>14377</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -10896,6 +13088,12 @@
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>1198</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -10922,6 +13120,12 @@
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -10948,6 +13152,12 @@
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -10974,6 +13184,12 @@
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>4834</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -11000,6 +13216,12 @@
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>2066</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -11026,6 +13248,12 @@
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>5777</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -11052,6 +13280,12 @@
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>6553</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -11078,6 +13312,12 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>10574</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -11104,6 +13344,12 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>12232</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -11130,6 +13376,12 @@
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>10698</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -11156,6 +13408,12 @@
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>6808</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -11182,6 +13440,12 @@
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>3601</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -11208,6 +13472,12 @@
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>4500</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -11234,6 +13504,12 @@
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>876</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -11260,6 +13536,12 @@
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>19719</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -11286,6 +13568,12 @@
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>2017</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -11312,6 +13600,12 @@
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>2015</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -11338,6 +13632,12 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>8779</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -11364,6 +13664,12 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>1118</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -11390,6 +13696,12 @@
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>676</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -11416,6 +13728,12 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>1820</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,12 @@
       <c r="H1" s="6" t="n">
         <v>46300</v>
       </c>
+      <c r="I1" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="J1" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -573,6 +579,16 @@
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -613,6 +629,12 @@
       <c r="H3" s="9" t="n">
         <v>4870</v>
       </c>
+      <c r="I3" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>4882</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -649,6 +671,12 @@
       <c r="H4" s="9" t="n">
         <v>15774</v>
       </c>
+      <c r="I4" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>15770</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -685,6 +713,12 @@
       <c r="H5" s="9" t="n">
         <v>5513</v>
       </c>
+      <c r="I5" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>5520</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -721,6 +755,12 @@
       <c r="H6" s="9" t="n">
         <v>6534</v>
       </c>
+      <c r="I6" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>6538</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -757,6 +797,12 @@
       <c r="H7" s="9" t="n">
         <v>2387</v>
       </c>
+      <c r="I7" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>2383</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -793,6 +839,12 @@
       <c r="H8" s="9" t="n">
         <v>7161</v>
       </c>
+      <c r="I8" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>7147</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -829,6 +881,12 @@
       <c r="H9" s="9" t="n">
         <v>3661</v>
       </c>
+      <c r="I9" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>3657</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -865,6 +923,12 @@
       <c r="H10" s="9" t="n">
         <v>2775</v>
       </c>
+      <c r="I10" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>2777</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -901,6 +965,12 @@
       <c r="H11" s="9" t="n">
         <v>1094</v>
       </c>
+      <c r="I11" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>1097</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -937,6 +1007,12 @@
       <c r="H12" s="9" t="n">
         <v>1108</v>
       </c>
+      <c r="I12" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>1108</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -973,6 +1049,12 @@
       <c r="H13" s="9" t="n">
         <v>2211</v>
       </c>
+      <c r="I13" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>2216</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1009,6 +1091,12 @@
       <c r="H14" s="9" t="n">
         <v>2347</v>
       </c>
+      <c r="I14" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>2347</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1045,6 +1133,12 @@
       <c r="H15" s="9" t="n">
         <v>2587</v>
       </c>
+      <c r="I15" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>2588</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1081,6 +1175,12 @@
       <c r="H16" s="9" t="n">
         <v>885</v>
       </c>
+      <c r="I16" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>885</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1117,6 +1217,12 @@
       <c r="H17" s="9" t="n">
         <v>1326</v>
       </c>
+      <c r="I17" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>1327</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1153,6 +1259,12 @@
       <c r="H18" s="9" t="n">
         <v>449</v>
       </c>
+      <c r="I18" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>449</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1189,6 +1301,12 @@
       <c r="H19" s="9" t="n">
         <v>926</v>
       </c>
+      <c r="I19" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>928</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1225,6 +1343,12 @@
       <c r="H20" s="9" t="n">
         <v>1091</v>
       </c>
+      <c r="I20" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>1093</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1261,6 +1385,12 @@
       <c r="H21" s="9" t="n">
         <v>788</v>
       </c>
+      <c r="I21" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>788</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1297,6 +1427,12 @@
       <c r="H22" s="9" t="n">
         <v>657</v>
       </c>
+      <c r="I22" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>658</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1333,6 +1469,12 @@
       <c r="H23" s="9" t="n">
         <v>696</v>
       </c>
+      <c r="I23" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>697</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1369,6 +1511,12 @@
       <c r="H24" s="9" t="n">
         <v>1430</v>
       </c>
+      <c r="I24" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>1428</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1405,6 +1553,12 @@
       <c r="H25" s="9" t="n">
         <v>698</v>
       </c>
+      <c r="I25" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>698</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1437,6 +1591,12 @@
       <c r="H26" s="9" t="n">
         <v>356</v>
       </c>
+      <c r="I26" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>358</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1468,6 +1628,12 @@
       </c>
       <c r="H27" s="9" t="n">
         <v>1165</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>1323</v>
       </c>
     </row>
   </sheetData>
@@ -1481,7 +1647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1504,6 +1670,12 @@
       <c r="H1" s="6" t="n">
         <v>46300</v>
       </c>
+      <c r="I1" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="J1" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1542,6 +1714,16 @@
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1582,6 +1764,12 @@
       <c r="H3" s="9" t="n">
         <v>81</v>
       </c>
+      <c r="I3" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1640,6 +1828,12 @@
       <c r="H5" s="9" t="n">
         <v>3862</v>
       </c>
+      <c r="I5" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>3862</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1676,6 +1870,12 @@
       <c r="H6" s="9" t="n">
         <v>3862</v>
       </c>
+      <c r="I6" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>3862</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1712,6 +1912,12 @@
       <c r="H7" s="9" t="n">
         <v>657</v>
       </c>
+      <c r="I7" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>658</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1748,6 +1954,12 @@
       <c r="H8" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="I8" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>6808</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1784,6 +1996,12 @@
       <c r="H9" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="I9" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>6808</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1820,6 +2038,12 @@
       <c r="H10" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="I10" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>6808</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1856,6 +2080,12 @@
       <c r="H11" s="9" t="n">
         <v>1193</v>
       </c>
+      <c r="I11" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1892,6 +2122,12 @@
       <c r="H12" s="9" t="n">
         <v>1193</v>
       </c>
+      <c r="I12" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1928,6 +2164,12 @@
       <c r="H13" s="9" t="n">
         <v>1820</v>
       </c>
+      <c r="I13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>1820</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1964,6 +2206,12 @@
       <c r="H14" s="9" t="n">
         <v>1820</v>
       </c>
+      <c r="I14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>1820</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -2000,6 +2248,12 @@
       <c r="H15" s="9" t="n">
         <v>1820</v>
       </c>
+      <c r="I15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>1820</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -2058,6 +2312,12 @@
       <c r="H17" s="9" t="n">
         <v>1820</v>
       </c>
+      <c r="I17" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>1820</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -2094,6 +2354,12 @@
       <c r="H18" s="9" t="n">
         <v>4500</v>
       </c>
+      <c r="I18" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>4500</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -2130,6 +2396,12 @@
       <c r="H19" s="9" t="n">
         <v>4500</v>
       </c>
+      <c r="I19" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>4500</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -2166,6 +2438,12 @@
       <c r="H20" s="9" t="n">
         <v>2775</v>
       </c>
+      <c r="I20" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>2777</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -2202,6 +2480,12 @@
       <c r="H21" s="9" t="n">
         <v>915</v>
       </c>
+      <c r="I21" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -2238,6 +2522,12 @@
       <c r="H22" s="9" t="n">
         <v>915</v>
       </c>
+      <c r="I22" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -2274,6 +2564,12 @@
       <c r="H23" s="9" t="n">
         <v>915</v>
       </c>
+      <c r="I23" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -2310,6 +2606,12 @@
       <c r="H24" s="9" t="n">
         <v>915</v>
       </c>
+      <c r="I24" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -2346,6 +2648,12 @@
       <c r="H25" s="9" t="n">
         <v>847</v>
       </c>
+      <c r="I25" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>847</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -2382,6 +2690,12 @@
       <c r="H26" s="9" t="n">
         <v>847</v>
       </c>
+      <c r="I26" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>847</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -2418,6 +2732,12 @@
       <c r="H27" s="9" t="n">
         <v>847</v>
       </c>
+      <c r="I27" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>847</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -2454,6 +2774,12 @@
       <c r="H28" s="9" t="n">
         <v>3601</v>
       </c>
+      <c r="I28" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>3602</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -2490,6 +2816,12 @@
       <c r="H29" s="9" t="n">
         <v>3601</v>
       </c>
+      <c r="I29" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>3602</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -2548,6 +2880,12 @@
       <c r="H31" s="9" t="n">
         <v>2211</v>
       </c>
+      <c r="I31" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>2216</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -2584,6 +2922,12 @@
       <c r="H32" s="9" t="n">
         <v>1042</v>
       </c>
+      <c r="I32" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>1042</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -2620,6 +2964,12 @@
       <c r="H33" s="9" t="n">
         <v>1042</v>
       </c>
+      <c r="I33" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>1042</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -2678,6 +3028,12 @@
       <c r="H35" s="9" t="n">
         <v>4834</v>
       </c>
+      <c r="I35" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>4836</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -2714,6 +3070,12 @@
       <c r="H36" s="9" t="n">
         <v>4834</v>
       </c>
+      <c r="I36" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>4836</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2750,6 +3112,12 @@
       <c r="H37" s="9" t="n">
         <v>282</v>
       </c>
+      <c r="I37" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>282</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -2786,6 +3154,12 @@
       <c r="H38" s="9" t="n">
         <v>282</v>
       </c>
+      <c r="I38" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>282</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -2822,6 +3196,12 @@
       <c r="H39" s="9" t="n">
         <v>2587</v>
       </c>
+      <c r="I39" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>2588</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2858,6 +3238,12 @@
       <c r="H40" s="9" t="n">
         <v>449</v>
       </c>
+      <c r="I40" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>449</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2894,6 +3280,12 @@
       <c r="H41" s="9" t="n">
         <v>1094</v>
       </c>
+      <c r="I41" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>1097</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -2930,6 +3322,12 @@
       <c r="H42" s="9" t="n">
         <v>11734</v>
       </c>
+      <c r="I42" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>11735</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -2966,6 +3364,12 @@
       <c r="H43" s="9" t="n">
         <v>11734</v>
       </c>
+      <c r="I43" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>11735</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -3002,6 +3406,12 @@
       <c r="H44" s="9" t="n">
         <v>191</v>
       </c>
+      <c r="I44" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -3038,6 +3448,12 @@
       <c r="H45" s="9" t="n">
         <v>191</v>
       </c>
+      <c r="I45" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -3074,6 +3490,12 @@
       <c r="H46" s="9" t="n">
         <v>2000</v>
       </c>
+      <c r="I46" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>2002</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -3110,6 +3532,12 @@
       <c r="H47" s="9" t="n">
         <v>2000</v>
       </c>
+      <c r="I47" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>2002</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -3146,6 +3574,12 @@
       <c r="H48" s="9" t="n">
         <v>1773</v>
       </c>
+      <c r="I48" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>1774</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -3181,6 +3615,12 @@
       </c>
       <c r="H49" s="9" t="n">
         <v>1773</v>
+      </c>
+      <c r="I49" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>1774</v>
       </c>
     </row>
     <row r="50">
@@ -3612,7 +4052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3635,6 +4075,12 @@
       <c r="H1" s="6" t="n">
         <v>46300</v>
       </c>
+      <c r="I1" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="J1" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3673,6 +4119,16 @@
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -3713,6 +4169,12 @@
       <c r="H3" s="9" t="n">
         <v>2094</v>
       </c>
+      <c r="I3" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>2094</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -3749,6 +4211,12 @@
       <c r="H4" s="9" t="n">
         <v>631</v>
       </c>
+      <c r="I4" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>632</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -3785,6 +4253,12 @@
       <c r="H5" s="9" t="n">
         <v>1555</v>
       </c>
+      <c r="I5" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>1555</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -3821,6 +4295,12 @@
       <c r="H6" s="9" t="n">
         <v>126</v>
       </c>
+      <c r="I6" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -3857,6 +4337,12 @@
       <c r="H7" s="9" t="n">
         <v>10882</v>
       </c>
+      <c r="I7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>10884</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -3893,6 +4379,12 @@
       <c r="H8" s="9" t="n">
         <v>2937</v>
       </c>
+      <c r="I8" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>2937</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -3929,6 +4421,12 @@
       <c r="H9" s="9" t="n">
         <v>217</v>
       </c>
+      <c r="I9" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>217</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -3965,6 +4463,12 @@
       <c r="H10" s="9" t="n">
         <v>5139</v>
       </c>
+      <c r="I10" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>5138</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -3997,6 +4501,12 @@
       <c r="H11" s="9" t="n">
         <v>7302</v>
       </c>
+      <c r="I11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>7305</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -4029,6 +4539,12 @@
       <c r="H12" s="9" t="n">
         <v>4869</v>
       </c>
+      <c r="I12" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>4869</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -4061,6 +4577,12 @@
       <c r="H13" s="9" t="n">
         <v>948</v>
       </c>
+      <c r="I13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>948</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -4093,6 +4615,12 @@
       <c r="H14" s="9" t="n">
         <v>1916</v>
       </c>
+      <c r="I14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>1916</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -4125,6 +4653,12 @@
       <c r="H15" s="9" t="n">
         <v>833</v>
       </c>
+      <c r="I15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>834</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -4157,6 +4691,12 @@
       <c r="H16" s="9" t="n">
         <v>3402</v>
       </c>
+      <c r="I16" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>3402</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -4189,6 +4729,12 @@
       <c r="H17" s="9" t="n">
         <v>5647</v>
       </c>
+      <c r="I17" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>5648</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -4221,6 +4767,12 @@
       <c r="H18" s="9" t="n">
         <v>4601</v>
       </c>
+      <c r="I18" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>4601</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -4253,6 +4805,12 @@
       <c r="H19" s="9" t="n">
         <v>5739</v>
       </c>
+      <c r="I19" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>5739</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -4285,6 +4843,12 @@
       <c r="H20" s="9" t="n">
         <v>8133</v>
       </c>
+      <c r="I20" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>8133</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -4317,6 +4881,12 @@
       <c r="H21" s="9" t="n">
         <v>6604</v>
       </c>
+      <c r="I21" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>6604</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -4349,6 +4919,12 @@
       <c r="H22" s="9" t="n">
         <v>6274</v>
       </c>
+      <c r="I22" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>6274</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -4385,6 +4961,12 @@
       <c r="H23" s="9" t="n">
         <v>6217</v>
       </c>
+      <c r="I23" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>6217</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -4417,6 +4999,12 @@
       <c r="H24" s="9" t="n">
         <v>4692</v>
       </c>
+      <c r="I24" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>4693</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -4449,6 +5037,12 @@
       <c r="H25" s="9" t="n">
         <v>6260</v>
       </c>
+      <c r="I25" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>6256</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -4481,6 +5075,12 @@
       <c r="H26" s="9" t="n">
         <v>1900</v>
       </c>
+      <c r="I26" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>1900</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -4513,6 +5113,12 @@
       <c r="H27" s="9" t="n">
         <v>8386</v>
       </c>
+      <c r="I27" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>8386</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -4545,6 +5151,12 @@
       <c r="H28" s="9" t="n">
         <v>233</v>
       </c>
+      <c r="I28" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>233</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -4581,6 +5193,12 @@
       <c r="H29" s="9" t="n">
         <v>8651</v>
       </c>
+      <c r="I29" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>8646</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -4613,6 +5231,12 @@
       <c r="H30" s="9" t="n">
         <v>2775</v>
       </c>
+      <c r="I30" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>2777</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -4649,6 +5273,12 @@
       <c r="H31" s="9" t="n">
         <v>5575</v>
       </c>
+      <c r="I31" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>5575</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -4681,6 +5311,12 @@
       <c r="H32" s="9" t="n">
         <v>5513</v>
       </c>
+      <c r="I32" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>5520</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -4717,6 +5353,12 @@
       <c r="H33" s="9" t="n">
         <v>4870</v>
       </c>
+      <c r="I33" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>4882</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -4749,6 +5391,12 @@
       <c r="H34" s="9" t="n">
         <v>885</v>
       </c>
+      <c r="I34" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>885</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -4781,6 +5429,12 @@
       <c r="H35" s="9" t="n">
         <v>2587</v>
       </c>
+      <c r="I35" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>2588</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -4813,6 +5467,12 @@
       <c r="H36" s="9" t="n">
         <v>696</v>
       </c>
+      <c r="I36" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>697</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -4849,6 +5509,12 @@
       <c r="H37" s="9" t="n">
         <v>1328</v>
       </c>
+      <c r="I37" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>1327</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -4881,6 +5547,12 @@
       <c r="H38" s="9" t="n">
         <v>1094</v>
       </c>
+      <c r="I38" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>1097</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -4913,6 +5585,12 @@
       <c r="H39" s="9" t="n">
         <v>510</v>
       </c>
+      <c r="I39" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>510</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -4945,6 +5623,12 @@
       <c r="H40" s="9" t="n">
         <v>1091</v>
       </c>
+      <c r="I40" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>1093</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -4981,6 +5665,12 @@
       <c r="H41" s="9" t="n">
         <v>449</v>
       </c>
+      <c r="I41" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>449</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -5017,6 +5707,12 @@
       <c r="H42" s="9" t="n">
         <v>2387</v>
       </c>
+      <c r="I42" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>2383</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -5049,6 +5745,12 @@
       <c r="H43" s="9" t="n">
         <v>2211</v>
       </c>
+      <c r="I43" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>2216</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -5081,6 +5783,12 @@
       <c r="H44" s="9" t="n">
         <v>6534</v>
       </c>
+      <c r="I44" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>6538</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -5117,6 +5825,12 @@
       <c r="H45" s="9" t="n">
         <v>1108</v>
       </c>
+      <c r="I45" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>1108</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -5153,6 +5867,12 @@
       <c r="H46" s="9" t="n">
         <v>7162</v>
       </c>
+      <c r="I46" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>7147</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -5185,6 +5905,12 @@
       <c r="H47" s="9" t="n">
         <v>15774</v>
       </c>
+      <c r="I47" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>15770</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -5217,6 +5943,12 @@
       <c r="H48" s="9" t="n">
         <v>3661</v>
       </c>
+      <c r="I48" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>3657</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -5253,6 +5985,12 @@
       <c r="H49" s="9" t="n">
         <v>2347</v>
       </c>
+      <c r="I49" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>2347</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -5285,6 +6023,12 @@
       <c r="H50" s="9" t="n">
         <v>1885</v>
       </c>
+      <c r="I50" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>1885</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -5317,6 +6061,12 @@
       <c r="H51" s="9" t="n">
         <v>7229</v>
       </c>
+      <c r="I51" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>7230</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -5349,6 +6099,12 @@
       <c r="H52" s="9" t="n">
         <v>1693</v>
       </c>
+      <c r="I52" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>1693</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -5385,6 +6141,12 @@
       <c r="H53" s="9" t="n">
         <v>9641</v>
       </c>
+      <c r="I53" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>9642</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -5421,6 +6183,12 @@
       <c r="H54" s="9" t="n">
         <v>796</v>
       </c>
+      <c r="I54" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>796</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -5453,6 +6221,12 @@
       <c r="H55" s="9" t="n">
         <v>7229</v>
       </c>
+      <c r="I55" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>796</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -5485,6 +6259,12 @@
       <c r="H56" s="9" t="n">
         <v>709</v>
       </c>
+      <c r="I56" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>710</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -5521,6 +6301,12 @@
       <c r="H57" s="9" t="n">
         <v>429</v>
       </c>
+      <c r="I57" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>429</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -5557,6 +6343,12 @@
       <c r="H58" s="9" t="n">
         <v>203</v>
       </c>
+      <c r="I58" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>203</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -5593,6 +6385,12 @@
       <c r="H59" s="9" t="n">
         <v>656</v>
       </c>
+      <c r="I59" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>656</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -5629,6 +6427,12 @@
       <c r="H60" s="9" t="n">
         <v>360</v>
       </c>
+      <c r="I60" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>361</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -5665,6 +6469,12 @@
       <c r="H61" s="9" t="n">
         <v>2891</v>
       </c>
+      <c r="I61" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>2891</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -5701,6 +6511,12 @@
       <c r="H62" s="9" t="n">
         <v>583</v>
       </c>
+      <c r="I62" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>583</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -5737,6 +6553,12 @@
       <c r="H63" s="9" t="n">
         <v>9251</v>
       </c>
+      <c r="I63" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>9253</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -5773,6 +6595,12 @@
       <c r="H64" s="9" t="n">
         <v>1005</v>
       </c>
+      <c r="I64" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>1005</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -5809,6 +6637,12 @@
       <c r="H65" s="9" t="n">
         <v>3846</v>
       </c>
+      <c r="I65" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>3846</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -5845,6 +6679,12 @@
       <c r="H66" s="9" t="n">
         <v>4137</v>
       </c>
+      <c r="I66" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>4137</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -5877,6 +6717,12 @@
       <c r="H67" s="9" t="n">
         <v>10337</v>
       </c>
+      <c r="I67" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>10340</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -5909,6 +6755,12 @@
       <c r="H68" s="9" t="n">
         <v>4287</v>
       </c>
+      <c r="I68" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>4288</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -5941,6 +6793,12 @@
       <c r="H69" s="9" t="n">
         <v>2202</v>
       </c>
+      <c r="I69" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>2204</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -5977,6 +6835,12 @@
       <c r="H70" s="9" t="n">
         <v>280</v>
       </c>
+      <c r="I70" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>280</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -6013,6 +6877,12 @@
       <c r="H71" s="9" t="n">
         <v>6139</v>
       </c>
+      <c r="I71" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>6139</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -6045,6 +6915,12 @@
       <c r="H72" s="9" t="n">
         <v>3743</v>
       </c>
+      <c r="I72" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>3744</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -6077,6 +6953,12 @@
       <c r="H73" s="9" t="n">
         <v>1100</v>
       </c>
+      <c r="I73" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>1101</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -6113,6 +6995,12 @@
       <c r="H74" s="9" t="n">
         <v>9514</v>
       </c>
+      <c r="I74" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>9514</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -6145,6 +7033,12 @@
       <c r="H75" s="9" t="n">
         <v>16965</v>
       </c>
+      <c r="I75" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>16965</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -6181,6 +7075,12 @@
       <c r="H76" s="9" t="n">
         <v>8556</v>
       </c>
+      <c r="I76" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>8557</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -6217,6 +7117,12 @@
       <c r="H77" s="9" t="n">
         <v>2436</v>
       </c>
+      <c r="I77" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>2437</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -6249,6 +7155,12 @@
       <c r="H78" s="9" t="n">
         <v>111</v>
       </c>
+      <c r="I78" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -6285,6 +7197,12 @@
       <c r="H79" s="9" t="n">
         <v>175</v>
       </c>
+      <c r="I79" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -6317,6 +7235,12 @@
       <c r="H80" s="9" t="n">
         <v>1478</v>
       </c>
+      <c r="I80" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>1478</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -6353,6 +7277,16 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -6385,6 +7319,12 @@
       <c r="H82" s="9" t="n">
         <v>1419</v>
       </c>
+      <c r="I82" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>1419</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -6417,6 +7357,12 @@
       <c r="H83" s="9" t="n">
         <v>209</v>
       </c>
+      <c r="I83" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>209</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -6449,6 +7395,12 @@
       <c r="H84" s="9" t="n">
         <v>287</v>
       </c>
+      <c r="I84" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>288</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -6481,6 +7433,12 @@
       <c r="H85" s="9" t="n">
         <v>3934</v>
       </c>
+      <c r="I85" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>3935</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -6513,6 +7471,12 @@
       <c r="H86" s="9" t="n">
         <v>467</v>
       </c>
+      <c r="I86" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>469</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -6545,6 +7509,12 @@
       <c r="H87" s="9" t="n">
         <v>5254</v>
       </c>
+      <c r="I87" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>5255</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -6577,6 +7547,12 @@
       <c r="H88" s="9" t="n">
         <v>119</v>
       </c>
+      <c r="I88" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -6609,6 +7585,12 @@
       <c r="H89" s="9" t="n">
         <v>8385</v>
       </c>
+      <c r="I89" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>8385</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -6641,6 +7623,12 @@
       <c r="H90" s="9" t="n">
         <v>3592</v>
       </c>
+      <c r="I90" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>3595</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -6673,6 +7661,12 @@
       <c r="H91" s="9" t="n">
         <v>3220</v>
       </c>
+      <c r="I91" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>3220</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -6705,6 +7699,12 @@
       <c r="H92" s="9" t="n">
         <v>2878</v>
       </c>
+      <c r="I92" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>2878</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -6737,6 +7737,12 @@
       <c r="H93" s="9" t="n">
         <v>3770</v>
       </c>
+      <c r="I93" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>3770</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -6769,6 +7775,12 @@
       <c r="H94" s="9" t="n">
         <v>1623</v>
       </c>
+      <c r="I94" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>1623</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -6801,6 +7813,12 @@
       <c r="H95" s="9" t="n">
         <v>7493</v>
       </c>
+      <c r="I95" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>7494</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -6833,6 +7851,12 @@
       <c r="H96" s="9" t="n">
         <v>2835</v>
       </c>
+      <c r="I96" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>2835</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -6865,6 +7889,12 @@
       <c r="H97" s="9" t="n">
         <v>2870</v>
       </c>
+      <c r="I97" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>2877</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -6897,6 +7927,12 @@
       <c r="H98" s="9" t="n">
         <v>91</v>
       </c>
+      <c r="I98" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -6929,6 +7965,12 @@
       <c r="H99" s="9" t="n">
         <v>1689</v>
       </c>
+      <c r="I99" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>1689</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -6961,6 +8003,12 @@
       <c r="H100" s="9" t="n">
         <v>2197</v>
       </c>
+      <c r="I100" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>2202</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -6993,6 +8041,12 @@
       <c r="H101" s="9" t="n">
         <v>288</v>
       </c>
+      <c r="I101" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>212</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -7025,6 +8079,12 @@
       <c r="H102" s="9" t="n">
         <v>75</v>
       </c>
+      <c r="I102" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>251</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -7057,6 +8117,12 @@
       <c r="H103" s="9" t="n">
         <v>848</v>
       </c>
+      <c r="I103" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>849</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -7089,6 +8155,12 @@
       <c r="H104" s="9" t="n">
         <v>427</v>
       </c>
+      <c r="I104" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>427</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -7121,6 +8193,12 @@
       <c r="H105" s="9" t="n">
         <v>883</v>
       </c>
+      <c r="I105" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>885</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -7153,6 +8231,12 @@
       <c r="H106" s="9" t="n">
         <v>454</v>
       </c>
+      <c r="I106" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>455</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -7185,6 +8269,12 @@
       <c r="H107" s="9" t="n">
         <v>1517</v>
       </c>
+      <c r="I107" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>1517</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -7217,6 +8307,12 @@
       <c r="H108" s="9" t="n">
         <v>1864</v>
       </c>
+      <c r="I108" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>1864</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -7247,6 +8343,12 @@
         <v>3.6</v>
       </c>
       <c r="H109" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="I109" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J109" s="9" t="n">
         <v>64</v>
       </c>
     </row>
@@ -7261,7 +8363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7284,6 +8386,12 @@
       <c r="H1" s="6" t="n">
         <v>46300</v>
       </c>
+      <c r="I1" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="J1" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7322,6 +8430,16 @@
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -7362,6 +8480,12 @@
       <c r="H3" s="9" t="n">
         <v>6982</v>
       </c>
+      <c r="I3" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>6984</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -7398,6 +8522,12 @@
       <c r="H4" s="9" t="n">
         <v>1718</v>
       </c>
+      <c r="I4" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>1720</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -7434,6 +8564,12 @@
       <c r="H5" s="9" t="n">
         <v>3415</v>
       </c>
+      <c r="I5" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>3415</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -7470,6 +8606,12 @@
       <c r="H6" s="9" t="n">
         <v>1348</v>
       </c>
+      <c r="I6" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>1348</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -7506,6 +8648,12 @@
       <c r="H7" s="9" t="n">
         <v>1109</v>
       </c>
+      <c r="I7" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>1109</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -7542,6 +8690,12 @@
       <c r="H8" s="9" t="n">
         <v>3363</v>
       </c>
+      <c r="I8" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>3364</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -7578,6 +8732,12 @@
       <c r="H9" s="9" t="n">
         <v>1970</v>
       </c>
+      <c r="I9" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -7614,6 +8774,12 @@
       <c r="H10" s="9" t="n">
         <v>1195</v>
       </c>
+      <c r="I10" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>1195</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -7650,6 +8816,12 @@
       <c r="H11" s="9" t="n">
         <v>812</v>
       </c>
+      <c r="I11" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>812</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -7682,6 +8854,12 @@
       <c r="H12" s="9" t="n">
         <v>3415</v>
       </c>
+      <c r="I12" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>3415</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -7718,6 +8896,12 @@
       <c r="H13" s="9" t="n">
         <v>406</v>
       </c>
+      <c r="I13" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>406</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -7754,6 +8938,12 @@
       <c r="H14" s="9" t="n">
         <v>3447</v>
       </c>
+      <c r="I14" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>3448</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -7790,6 +8980,12 @@
       <c r="H15" s="9" t="n">
         <v>1986</v>
       </c>
+      <c r="I15" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>1986</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -7826,6 +9022,12 @@
       <c r="H16" s="9" t="n">
         <v>1338</v>
       </c>
+      <c r="I16" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -7862,6 +9064,12 @@
       <c r="H17" s="9" t="n">
         <v>1329</v>
       </c>
+      <c r="I17" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>1331</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -7898,6 +9106,12 @@
       <c r="H18" s="9" t="n">
         <v>4495</v>
       </c>
+      <c r="I18" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>4495</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -7934,6 +9148,12 @@
       <c r="H19" s="9" t="n">
         <v>1660</v>
       </c>
+      <c r="I19" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>1661</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -7970,6 +9190,12 @@
       <c r="H20" s="9" t="n">
         <v>4366</v>
       </c>
+      <c r="I20" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>4369</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -8002,6 +9228,12 @@
       <c r="H21" s="9" t="n">
         <v>3833</v>
       </c>
+      <c r="I21" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>3843</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -8034,6 +9266,12 @@
       <c r="H22" s="9" t="n">
         <v>86</v>
       </c>
+      <c r="I22" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -8066,6 +9304,12 @@
       <c r="H23" s="9" t="n">
         <v>443</v>
       </c>
+      <c r="I23" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>443</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -8098,6 +9342,12 @@
       <c r="H24" s="9" t="n">
         <v>1684</v>
       </c>
+      <c r="I24" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>1684</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -8130,6 +9380,12 @@
       <c r="H25" s="9" t="n">
         <v>3362</v>
       </c>
+      <c r="I25" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>3363</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -8162,6 +9418,12 @@
       <c r="H26" s="9" t="n">
         <v>1767</v>
       </c>
+      <c r="I26" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>1767</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -8194,6 +9456,12 @@
       <c r="H27" s="9" t="n">
         <v>530</v>
       </c>
+      <c r="I27" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>530</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -8226,6 +9494,12 @@
       <c r="H28" s="9" t="n">
         <v>1325</v>
       </c>
+      <c r="I28" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>1325</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -8258,6 +9532,12 @@
       <c r="H29" s="9" t="n">
         <v>638</v>
       </c>
+      <c r="I29" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>640</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -8290,6 +9570,12 @@
       <c r="H30" s="9" t="n">
         <v>35</v>
       </c>
+      <c r="I30" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -8322,6 +9608,12 @@
       <c r="H31" s="9" t="n">
         <v>1323</v>
       </c>
+      <c r="I31" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>1323</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -8354,6 +9646,12 @@
       <c r="H32" s="9" t="n">
         <v>1427</v>
       </c>
+      <c r="I32" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>1427</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -8386,6 +9684,12 @@
       <c r="H33" s="9" t="n">
         <v>1334</v>
       </c>
+      <c r="I33" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>1334</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -8418,6 +9722,12 @@
       <c r="H34" s="9" t="n">
         <v>186</v>
       </c>
+      <c r="I34" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>186</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -8450,6 +9760,12 @@
       <c r="H35" s="9" t="n">
         <v>127</v>
       </c>
+      <c r="I35" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -8482,6 +9798,12 @@
       <c r="H36" s="9" t="n">
         <v>993</v>
       </c>
+      <c r="I36" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>993</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -8514,6 +9836,12 @@
       <c r="H37" s="9" t="n">
         <v>205</v>
       </c>
+      <c r="I37" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>205</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -8546,6 +9874,12 @@
       <c r="H38" s="9" t="n">
         <v>211</v>
       </c>
+      <c r="I38" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>211</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -8578,6 +9912,12 @@
       <c r="H39" s="9" t="n">
         <v>853</v>
       </c>
+      <c r="I39" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>853</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -8610,6 +9950,12 @@
       <c r="H40" s="9" t="n">
         <v>2234</v>
       </c>
+      <c r="I40" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>2234</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -8642,6 +9988,12 @@
       <c r="H41" s="9" t="n">
         <v>450</v>
       </c>
+      <c r="I41" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -8674,6 +10026,12 @@
       <c r="H42" s="9" t="n">
         <v>1581</v>
       </c>
+      <c r="I42" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>1582</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -8706,6 +10064,12 @@
       <c r="H43" s="9" t="n">
         <v>1165</v>
       </c>
+      <c r="I43" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>1165</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -8738,6 +10102,12 @@
       <c r="H44" s="9" t="n">
         <v>474</v>
       </c>
+      <c r="I44" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>474</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -8770,6 +10140,12 @@
       <c r="H45" s="9" t="n">
         <v>370</v>
       </c>
+      <c r="I45" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>369</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -8802,6 +10178,12 @@
       <c r="H46" s="9" t="n">
         <v>937</v>
       </c>
+      <c r="I46" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>1042</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -8834,6 +10216,12 @@
       <c r="H47" s="9" t="n">
         <v>2566</v>
       </c>
+      <c r="I47" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>2566</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -8866,6 +10254,12 @@
       <c r="H48" s="9" t="n">
         <v>1429</v>
       </c>
+      <c r="I48" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>1429</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -8898,6 +10292,12 @@
       <c r="H49" s="9" t="n">
         <v>1417</v>
       </c>
+      <c r="I49" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>1418</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -8930,6 +10330,12 @@
       <c r="H50" s="9" t="n">
         <v>1549</v>
       </c>
+      <c r="I50" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>1549</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -8962,6 +10368,12 @@
       <c r="H51" s="9" t="n">
         <v>2807</v>
       </c>
+      <c r="I51" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>2807</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -8994,6 +10406,12 @@
       <c r="H52" s="9" t="n">
         <v>742</v>
       </c>
+      <c r="I52" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>742</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -9026,6 +10444,12 @@
       <c r="H53" s="9" t="n">
         <v>1224</v>
       </c>
+      <c r="I53" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>1224</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -9058,6 +10482,12 @@
       <c r="H54" s="9" t="n">
         <v>673</v>
       </c>
+      <c r="I54" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>673</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -9088,6 +10518,12 @@
         <v>4.4</v>
       </c>
       <c r="H55" s="9" t="n">
+        <v>420</v>
+      </c>
+      <c r="I55" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J55" s="9" t="n">
         <v>420</v>
       </c>
     </row>
@@ -9336,7 +10772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9359,6 +10795,12 @@
       <c r="H1" s="6" t="n">
         <v>46300</v>
       </c>
+      <c r="I1" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="J1" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -9397,6 +10839,16 @@
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -9433,6 +10885,12 @@
       <c r="H3" s="9" t="n">
         <v>4571</v>
       </c>
+      <c r="I3" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>4571</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -9465,6 +10923,12 @@
       <c r="H4" s="9" t="n">
         <v>1228</v>
       </c>
+      <c r="I4" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>1228</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -9497,6 +10961,12 @@
       <c r="H5" s="9" t="n">
         <v>460</v>
       </c>
+      <c r="I5" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>460</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -9529,6 +10999,12 @@
       <c r="H6" s="9" t="n">
         <v>11588</v>
       </c>
+      <c r="I6" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>11588</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -9561,6 +11037,12 @@
       <c r="H7" s="9" t="n">
         <v>2050</v>
       </c>
+      <c r="I7" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -9593,6 +11075,12 @@
       <c r="H8" s="9" t="n">
         <v>917</v>
       </c>
+      <c r="I8" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>917</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -9625,6 +11113,12 @@
       <c r="H9" s="9" t="n">
         <v>1604</v>
       </c>
+      <c r="I9" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>1604</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -9657,6 +11151,12 @@
       <c r="H10" s="9" t="n">
         <v>1994</v>
       </c>
+      <c r="I10" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>2010</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -9689,6 +11189,12 @@
       <c r="H11" s="9" t="n">
         <v>3082</v>
       </c>
+      <c r="I11" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>3082</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -9721,6 +11227,12 @@
       <c r="H12" s="9" t="n">
         <v>3624</v>
       </c>
+      <c r="I12" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>3624</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -9753,6 +11265,12 @@
       <c r="H13" s="9" t="n">
         <v>21261</v>
       </c>
+      <c r="I13" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>21262</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -9785,6 +11303,12 @@
       <c r="H14" s="9" t="n">
         <v>2945</v>
       </c>
+      <c r="I14" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>2945</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -9817,6 +11341,12 @@
       <c r="H15" s="9" t="n">
         <v>4200</v>
       </c>
+      <c r="I15" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>4202</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -9849,6 +11379,12 @@
       <c r="H16" s="9" t="n">
         <v>2387</v>
       </c>
+      <c r="I16" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>2387</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -9881,6 +11417,12 @@
       <c r="H17" s="9" t="n">
         <v>4</v>
       </c>
+      <c r="I17" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -9913,6 +11455,12 @@
       <c r="H18" s="9" t="n">
         <v>12119</v>
       </c>
+      <c r="I18" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>12118</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -9945,6 +11493,12 @@
       <c r="H19" s="9" t="n">
         <v>3076</v>
       </c>
+      <c r="I19" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>3077</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -9977,6 +11531,12 @@
       <c r="H20" s="9" t="n">
         <v>9245</v>
       </c>
+      <c r="I20" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>9245</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -10009,6 +11569,12 @@
       <c r="H21" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="I21" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -10041,6 +11607,12 @@
       <c r="H22" s="9" t="n">
         <v>6136</v>
       </c>
+      <c r="I22" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>6136</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -10073,6 +11645,12 @@
       <c r="H23" s="9" t="n">
         <v>1734</v>
       </c>
+      <c r="I23" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>1722</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -10105,6 +11683,12 @@
       <c r="H24" s="9" t="n">
         <v>1060</v>
       </c>
+      <c r="I24" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>1060</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -10137,6 +11721,12 @@
       <c r="H25" s="9" t="n">
         <v>2052</v>
       </c>
+      <c r="I25" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>2052</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -10169,6 +11759,12 @@
       <c r="H26" s="9" t="n">
         <v>2776</v>
       </c>
+      <c r="I26" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>2776</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -10201,6 +11797,12 @@
       <c r="H27" s="9" t="n">
         <v>11062</v>
       </c>
+      <c r="I27" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>11064</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -10233,6 +11835,12 @@
       <c r="H28" s="9" t="n">
         <v>5490</v>
       </c>
+      <c r="I28" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>5490</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -10265,6 +11873,12 @@
       <c r="H29" s="9" t="n">
         <v>4008</v>
       </c>
+      <c r="I29" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>4008</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -10297,6 +11911,12 @@
       <c r="H30" s="9" t="n">
         <v>1579</v>
       </c>
+      <c r="I30" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>1579</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -10329,6 +11949,12 @@
       <c r="H31" s="9" t="n">
         <v>1579</v>
       </c>
+      <c r="I31" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>1579</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -10361,6 +11987,12 @@
       <c r="H32" s="9" t="n">
         <v>2808</v>
       </c>
+      <c r="I32" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>2809</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -10393,6 +12025,12 @@
       <c r="H33" s="9" t="n">
         <v>18968</v>
       </c>
+      <c r="I33" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>18967</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -10425,6 +12063,12 @@
       <c r="H34" s="9" t="n">
         <v>39673</v>
       </c>
+      <c r="I34" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>39673</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -10457,6 +12101,12 @@
       <c r="H35" s="9" t="n">
         <v>5228</v>
       </c>
+      <c r="I35" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>5228</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -10489,6 +12139,12 @@
       <c r="H36" s="9" t="n">
         <v>10370</v>
       </c>
+      <c r="I36" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>10372</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -10521,6 +12177,12 @@
       <c r="H37" s="9" t="n">
         <v>7404</v>
       </c>
+      <c r="I37" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>7404</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -10553,6 +12215,12 @@
       <c r="H38" s="9" t="n">
         <v>539</v>
       </c>
+      <c r="I38" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>539</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -10585,6 +12253,12 @@
       <c r="H39" s="9" t="n">
         <v>1124</v>
       </c>
+      <c r="I39" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>1124</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -10617,6 +12291,12 @@
       <c r="H40" s="9" t="n">
         <v>539</v>
       </c>
+      <c r="I40" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>539</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -10649,6 +12329,12 @@
       <c r="H41" s="9" t="n">
         <v>2615</v>
       </c>
+      <c r="I41" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>2615</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -10681,6 +12367,12 @@
       <c r="H42" s="9" t="n">
         <v>1441</v>
       </c>
+      <c r="I42" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>1441</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -10713,6 +12405,12 @@
       <c r="H43" s="9" t="n">
         <v>955</v>
       </c>
+      <c r="I43" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>955</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -10745,6 +12443,12 @@
       <c r="H44" s="9" t="n">
         <v>4162</v>
       </c>
+      <c r="I44" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>4162</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -10777,6 +12481,12 @@
       <c r="H45" s="9" t="n">
         <v>3480</v>
       </c>
+      <c r="I45" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>3481</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -10809,6 +12519,12 @@
       <c r="H46" s="9" t="n">
         <v>7884</v>
       </c>
+      <c r="I46" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>7884</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -10841,6 +12557,12 @@
       <c r="H47" s="9" t="n">
         <v>6136</v>
       </c>
+      <c r="I47" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>6136</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -10873,6 +12595,12 @@
       <c r="H48" s="9" t="n">
         <v>983</v>
       </c>
+      <c r="I48" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>983</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -10905,6 +12633,12 @@
       <c r="H49" s="9" t="n">
         <v>3640</v>
       </c>
+      <c r="I49" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>3640</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -10937,6 +12671,12 @@
       <c r="H50" s="9" t="n">
         <v>147</v>
       </c>
+      <c r="I50" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -10969,6 +12709,12 @@
       <c r="H51" s="9" t="n">
         <v>4116</v>
       </c>
+      <c r="I51" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>4117</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -11001,6 +12747,12 @@
       <c r="H52" s="9" t="n">
         <v>308</v>
       </c>
+      <c r="I52" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>309</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -11033,6 +12785,12 @@
       <c r="H53" s="9" t="n">
         <v>122</v>
       </c>
+      <c r="I53" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -11065,6 +12823,12 @@
       <c r="H54" s="9" t="n">
         <v>4116</v>
       </c>
+      <c r="I54" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>4117</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -11097,6 +12861,12 @@
       <c r="H55" s="9" t="n">
         <v>46</v>
       </c>
+      <c r="I55" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -11129,6 +12899,12 @@
       <c r="H56" s="9" t="n">
         <v>493</v>
       </c>
+      <c r="I56" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>492</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -11161,6 +12937,12 @@
       <c r="H57" s="9" t="n">
         <v>7852</v>
       </c>
+      <c r="I57" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>7852</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -11193,6 +12975,12 @@
       <c r="H58" s="9" t="n">
         <v>4017</v>
       </c>
+      <c r="I58" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>4017</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -11225,6 +13013,12 @@
       <c r="H59" s="9" t="n">
         <v>2840</v>
       </c>
+      <c r="I59" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>2848</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -11257,6 +13051,12 @@
       <c r="H60" s="9" t="n">
         <v>2251</v>
       </c>
+      <c r="I60" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>2251</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -11289,6 +13089,12 @@
       <c r="H61" s="9" t="n">
         <v>7819</v>
       </c>
+      <c r="I61" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>7819</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -11321,6 +13127,12 @@
       <c r="H62" s="9" t="n">
         <v>3614</v>
       </c>
+      <c r="I62" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>3614</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -11353,6 +13165,12 @@
       <c r="H63" s="9" t="n">
         <v>4769</v>
       </c>
+      <c r="I63" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>4769</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -11385,6 +13203,12 @@
       <c r="H64" s="9" t="n">
         <v>2626</v>
       </c>
+      <c r="I64" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>2626</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -11417,6 +13241,12 @@
       <c r="H65" s="9" t="n">
         <v>2900</v>
       </c>
+      <c r="I65" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>2900</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -11449,6 +13279,12 @@
       <c r="H66" s="9" t="n">
         <v>6441</v>
       </c>
+      <c r="I66" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>6443</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -11481,6 +13317,12 @@
       <c r="H67" s="9" t="n">
         <v>781</v>
       </c>
+      <c r="I67" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>781</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -11513,6 +13355,12 @@
       <c r="H68" s="9" t="n">
         <v>19100</v>
       </c>
+      <c r="I68" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>19103</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -11545,6 +13393,12 @@
       <c r="H69" s="9" t="n">
         <v>2911</v>
       </c>
+      <c r="I69" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>2913</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -11577,6 +13431,12 @@
       <c r="H70" s="9" t="n">
         <v>2629</v>
       </c>
+      <c r="I70" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -11609,6 +13469,12 @@
       <c r="H71" s="9" t="n">
         <v>1193</v>
       </c>
+      <c r="I71" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -11641,6 +13507,12 @@
       <c r="H72" s="9" t="n">
         <v>4165</v>
       </c>
+      <c r="I72" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -11673,6 +13545,12 @@
       <c r="H73" s="9" t="n">
         <v>3862</v>
       </c>
+      <c r="I73" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>3862</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -11705,6 +13583,12 @@
       <c r="H74" s="9" t="n">
         <v>754</v>
       </c>
+      <c r="I74" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>754</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -11737,6 +13621,12 @@
       <c r="H75" s="9" t="n">
         <v>4653</v>
       </c>
+      <c r="I75" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>4653</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -11769,6 +13659,12 @@
       <c r="H76" s="9" t="n">
         <v>5286</v>
       </c>
+      <c r="I76" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>5286</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -11801,6 +13697,12 @@
       <c r="H77" s="9" t="n">
         <v>159</v>
       </c>
+      <c r="I77" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -11833,6 +13735,12 @@
       <c r="H78" s="9" t="n">
         <v>1130</v>
       </c>
+      <c r="I78" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>1131</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -11865,6 +13773,12 @@
       <c r="H79" s="9" t="n">
         <v>634</v>
       </c>
+      <c r="I79" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>634</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -11897,6 +13811,12 @@
       <c r="H80" s="9" t="n">
         <v>1187</v>
       </c>
+      <c r="I80" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -11929,6 +13849,12 @@
       <c r="H81" s="9" t="n">
         <v>1554</v>
       </c>
+      <c r="I81" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>1554</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -11961,6 +13887,12 @@
       <c r="H82" s="9" t="n">
         <v>11734</v>
       </c>
+      <c r="I82" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>11735</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -11993,6 +13925,12 @@
       <c r="H83" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="I83" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -12025,6 +13963,12 @@
       <c r="H84" s="9" t="n">
         <v>5926</v>
       </c>
+      <c r="I84" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>5927</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -12057,6 +14001,12 @@
       <c r="H85" s="9" t="n">
         <v>3258</v>
       </c>
+      <c r="I85" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>3258</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -12089,6 +14039,12 @@
       <c r="H86" s="9" t="n">
         <v>10418</v>
       </c>
+      <c r="I86" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>10418</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -12121,6 +14077,12 @@
       <c r="H87" s="9" t="n">
         <v>4151</v>
       </c>
+      <c r="I87" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>4151</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -12153,6 +14115,12 @@
       <c r="H88" s="9" t="n">
         <v>2998</v>
       </c>
+      <c r="I88" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>2998</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -12185,6 +14153,12 @@
       <c r="H89" s="9" t="n">
         <v>1296</v>
       </c>
+      <c r="I89" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>1296</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -12217,6 +14191,12 @@
       <c r="H90" s="9" t="n">
         <v>2233</v>
       </c>
+      <c r="I90" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>2233</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -12249,6 +14229,12 @@
       <c r="H91" s="9" t="n">
         <v>7974</v>
       </c>
+      <c r="I91" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>7974</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -12281,6 +14267,12 @@
       <c r="H92" s="9" t="n">
         <v>784</v>
       </c>
+      <c r="I92" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>784</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -12313,6 +14305,12 @@
       <c r="H93" s="9" t="n">
         <v>788</v>
       </c>
+      <c r="I93" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>788</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -12345,6 +14343,12 @@
       <c r="H94" s="9" t="n">
         <v>2595</v>
       </c>
+      <c r="I94" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>2595</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -12377,6 +14381,12 @@
       <c r="H95" s="9" t="n">
         <v>1677</v>
       </c>
+      <c r="I95" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>1677</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -12409,6 +14419,12 @@
       <c r="H96" s="9" t="n">
         <v>6438</v>
       </c>
+      <c r="I96" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>6438</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -12441,6 +14457,12 @@
       <c r="H97" s="9" t="n">
         <v>2315</v>
       </c>
+      <c r="I97" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>2315</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -12473,6 +14495,12 @@
       <c r="H98" s="9" t="n">
         <v>1933</v>
       </c>
+      <c r="I98" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>1933</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -12505,6 +14533,12 @@
       <c r="H99" s="9" t="n">
         <v>5568</v>
       </c>
+      <c r="I99" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>5568</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -12537,6 +14571,12 @@
       <c r="H100" s="9" t="n">
         <v>17772</v>
       </c>
+      <c r="I100" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>17773</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -12569,6 +14609,12 @@
       <c r="H101" s="9" t="n">
         <v>6151</v>
       </c>
+      <c r="I101" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>6151</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -12601,6 +14647,12 @@
       <c r="H102" s="9" t="n">
         <v>5283</v>
       </c>
+      <c r="I102" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>5283</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -12633,6 +14685,12 @@
       <c r="H103" s="9" t="n">
         <v>1172</v>
       </c>
+      <c r="I103" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>1173</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -12665,6 +14723,12 @@
       <c r="H104" s="9" t="n">
         <v>4076</v>
       </c>
+      <c r="I104" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>4076</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -12697,6 +14761,12 @@
       <c r="H105" s="9" t="n">
         <v>1172</v>
       </c>
+      <c r="I105" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>1173</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -12729,6 +14799,12 @@
       <c r="H106" s="9" t="n">
         <v>10973</v>
       </c>
+      <c r="I106" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>10973</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -12761,6 +14837,12 @@
       <c r="H107" s="9" t="n">
         <v>3159</v>
       </c>
+      <c r="I107" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>3159</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -12793,6 +14875,12 @@
       <c r="H108" s="9" t="n">
         <v>3052</v>
       </c>
+      <c r="I108" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>3052</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -12825,6 +14913,12 @@
       <c r="H109" s="9" t="n">
         <v>2619</v>
       </c>
+      <c r="I109" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>2619</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
@@ -12857,6 +14951,12 @@
       <c r="H110" s="9" t="n">
         <v>1879</v>
       </c>
+      <c r="I110" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>1879</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
@@ -12889,6 +14989,12 @@
       <c r="H111" s="9" t="n">
         <v>1196</v>
       </c>
+      <c r="I111" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>1196</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
@@ -12921,6 +15027,12 @@
       <c r="H112" s="9" t="n">
         <v>2446</v>
       </c>
+      <c r="I112" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>2447</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
@@ -12951,6 +15063,12 @@
         <v>4.6</v>
       </c>
       <c r="H113" s="9" t="n">
+        <v>2629</v>
+      </c>
+      <c r="I113" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J113" s="9" t="n">
         <v>2629</v>
       </c>
     </row>
@@ -12965,7 +15083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12988,6 +15106,12 @@
       <c r="H1" s="6" t="n">
         <v>46300</v>
       </c>
+      <c r="I1" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="J1" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -13026,6 +15150,16 @@
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -13062,6 +15196,12 @@
       <c r="H3" s="9" t="n">
         <v>14377</v>
       </c>
+      <c r="I3" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>14377</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -13094,6 +15234,12 @@
       <c r="H4" s="9" t="n">
         <v>1198</v>
       </c>
+      <c r="I4" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>1198</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -13126,6 +15272,12 @@
       <c r="H5" s="9" t="n">
         <v>14</v>
       </c>
+      <c r="I5" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -13158,6 +15310,12 @@
       <c r="H6" s="9" t="n">
         <v>61</v>
       </c>
+      <c r="I6" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -13190,6 +15348,12 @@
       <c r="H7" s="9" t="n">
         <v>4834</v>
       </c>
+      <c r="I7" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>4836</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -13222,6 +15386,12 @@
       <c r="H8" s="9" t="n">
         <v>2066</v>
       </c>
+      <c r="I8" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>2067</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -13254,6 +15424,12 @@
       <c r="H9" s="9" t="n">
         <v>5777</v>
       </c>
+      <c r="I9" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>5777</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -13286,6 +15462,12 @@
       <c r="H10" s="9" t="n">
         <v>6553</v>
       </c>
+      <c r="I10" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>6554</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -13318,6 +15500,12 @@
       <c r="H11" s="9" t="n">
         <v>10574</v>
       </c>
+      <c r="I11" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>10574</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -13350,6 +15538,12 @@
       <c r="H12" s="9" t="n">
         <v>12232</v>
       </c>
+      <c r="I12" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>12233</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -13382,6 +15576,12 @@
       <c r="H13" s="9" t="n">
         <v>10698</v>
       </c>
+      <c r="I13" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>10698</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -13414,6 +15614,12 @@
       <c r="H14" s="9" t="n">
         <v>6808</v>
       </c>
+      <c r="I14" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>6808</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -13446,6 +15652,12 @@
       <c r="H15" s="9" t="n">
         <v>3601</v>
       </c>
+      <c r="I15" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>3602</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -13478,6 +15690,12 @@
       <c r="H16" s="9" t="n">
         <v>4500</v>
       </c>
+      <c r="I16" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>4500</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -13510,6 +15728,12 @@
       <c r="H17" s="9" t="n">
         <v>876</v>
       </c>
+      <c r="I17" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>876</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -13542,6 +15766,12 @@
       <c r="H18" s="9" t="n">
         <v>19719</v>
       </c>
+      <c r="I18" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>19720</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -13574,6 +15804,12 @@
       <c r="H19" s="9" t="n">
         <v>2017</v>
       </c>
+      <c r="I19" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>2017</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -13606,6 +15842,12 @@
       <c r="H20" s="9" t="n">
         <v>2015</v>
       </c>
+      <c r="I20" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>2023</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -13638,6 +15880,12 @@
       <c r="H21" s="9" t="n">
         <v>8779</v>
       </c>
+      <c r="I21" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>8780</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -13670,6 +15918,12 @@
       <c r="H22" s="9" t="n">
         <v>1118</v>
       </c>
+      <c r="I22" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>1118</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -13702,6 +15956,12 @@
       <c r="H23" s="9" t="n">
         <v>676</v>
       </c>
+      <c r="I23" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>676</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -13732,6 +15992,12 @@
         <v>4</v>
       </c>
       <c r="H24" s="9" t="n">
+        <v>1820</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" s="9" t="n">
         <v>1820</v>
       </c>
     </row>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -633,7 +633,7 @@
         <v>4.4</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>4882</v>
+        <v>4874</v>
       </c>
     </row>
     <row r="4">
@@ -675,7 +675,7 @@
         <v>4.3</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>15770</v>
+        <v>15769</v>
       </c>
     </row>
     <row r="5">
@@ -717,7 +717,7 @@
         <v>4.5</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>5520</v>
+        <v>5526</v>
       </c>
     </row>
     <row r="6">
@@ -759,7 +759,7 @@
         <v>4.3</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>6538</v>
+        <v>6534</v>
       </c>
     </row>
     <row r="7">
@@ -801,7 +801,7 @@
         <v>4.5</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2383</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="8">
@@ -843,7 +843,7 @@
         <v>4.4</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>7147</v>
+        <v>7145</v>
       </c>
     </row>
     <row r="9">
@@ -885,7 +885,7 @@
         <v>4.4</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>3657</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="10">
@@ -927,7 +927,7 @@
         <v>4.4</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2777</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="11">
@@ -969,7 +969,7 @@
         <v>4.7</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="12">
@@ -1053,7 +1053,7 @@
         <v>4.7</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>2216</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="14">
@@ -1179,7 +1179,7 @@
         <v>4.5</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>885</v>
+        <v>888</v>
       </c>
     </row>
     <row r="17">
@@ -1263,7 +1263,7 @@
         <v>4.4</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="19">
@@ -1347,7 +1347,7 @@
         <v>4.6</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="21">
@@ -1431,7 +1431,7 @@
         <v>4.7</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="23">
@@ -1473,7 +1473,7 @@
         <v>4.7</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="24">
@@ -1557,7 +1557,7 @@
         <v>4.8</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="26">
@@ -1630,10 +1630,10 @@
         <v>1165</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1323</v>
+        <v>2234</v>
       </c>
     </row>
   </sheetData>
@@ -1916,7 +1916,7 @@
         <v>4.7</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -1955,10 +1955,10 @@
         <v>8</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>6808</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9">
@@ -1997,10 +1997,10 @@
         <v>8</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>6808</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
@@ -2039,10 +2039,10 @@
         <v>8</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>6808</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -2442,7 +2442,7 @@
         <v>4.4</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>2777</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="21">
@@ -2481,10 +2481,10 @@
         <v>915</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
@@ -2523,10 +2523,10 @@
         <v>915</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -2565,10 +2565,10 @@
         <v>915</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
@@ -2607,10 +2607,10 @@
         <v>915</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25">
@@ -2778,7 +2778,7 @@
         <v>4.2</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>3602</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="29">
@@ -2820,7 +2820,7 @@
         <v>4.2</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>3602</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="30">
@@ -2884,7 +2884,7 @@
         <v>4.7</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>2216</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="32">
@@ -2923,10 +2923,10 @@
         <v>1042</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>1042</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33">
@@ -2965,10 +2965,10 @@
         <v>1042</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>1042</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34">
@@ -3242,7 +3242,7 @@
         <v>4.4</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="41">
@@ -3284,7 +3284,7 @@
         <v>4.7</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="42">
@@ -3326,7 +3326,7 @@
         <v>4.3</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>11735</v>
+        <v>11737</v>
       </c>
     </row>
     <row r="43">
@@ -3368,7 +3368,7 @@
         <v>4.3</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>11735</v>
+        <v>11737</v>
       </c>
     </row>
     <row r="44">
@@ -4173,7 +4173,7 @@
         <v>4.3</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>2094</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="4">
@@ -4467,7 +4467,7 @@
         <v>4.3</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>5138</v>
+        <v>5139</v>
       </c>
     </row>
     <row r="11">
@@ -4543,7 +4543,7 @@
         <v>4.5</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>4869</v>
+        <v>4871</v>
       </c>
     </row>
     <row r="13">
@@ -4581,7 +4581,7 @@
         <v>4</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="14">
@@ -4771,7 +4771,7 @@
         <v>4.4</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>4601</v>
+        <v>4603</v>
       </c>
     </row>
     <row r="19">
@@ -4809,7 +4809,7 @@
         <v>4.3</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>5739</v>
+        <v>5743</v>
       </c>
     </row>
     <row r="20">
@@ -4847,7 +4847,7 @@
         <v>4.6</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>8133</v>
+        <v>8144</v>
       </c>
     </row>
     <row r="21">
@@ -4923,7 +4923,7 @@
         <v>4.4</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>6274</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="23">
@@ -5041,7 +5041,7 @@
         <v>4.5</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>6256</v>
+        <v>6254</v>
       </c>
     </row>
     <row r="26">
@@ -5079,7 +5079,7 @@
         <v>4.6</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="27">
@@ -5197,7 +5197,7 @@
         <v>4.3</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>8646</v>
+        <v>8649</v>
       </c>
     </row>
     <row r="30">
@@ -5235,7 +5235,7 @@
         <v>4.4</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>2777</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="31">
@@ -5315,7 +5315,7 @@
         <v>4.5</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>5520</v>
+        <v>5526</v>
       </c>
     </row>
     <row r="33">
@@ -5357,7 +5357,7 @@
         <v>4.4</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>4882</v>
+        <v>4874</v>
       </c>
     </row>
     <row r="34">
@@ -5395,7 +5395,7 @@
         <v>4.5</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>885</v>
+        <v>888</v>
       </c>
     </row>
     <row r="35">
@@ -5471,7 +5471,7 @@
         <v>4.7</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="37">
@@ -5551,7 +5551,7 @@
         <v>4.7</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1097</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="39">
@@ -5627,7 +5627,7 @@
         <v>4.6</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="41">
@@ -5669,7 +5669,7 @@
         <v>4.4</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="42">
@@ -5711,7 +5711,7 @@
         <v>4.5</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2383</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="43">
@@ -5749,7 +5749,7 @@
         <v>4.7</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2216</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="44">
@@ -5787,7 +5787,7 @@
         <v>4.3</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>6538</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="45">
@@ -5871,7 +5871,7 @@
         <v>4.4</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>7147</v>
+        <v>7144</v>
       </c>
     </row>
     <row r="47">
@@ -5909,7 +5909,7 @@
         <v>4.3</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>15770</v>
+        <v>15769</v>
       </c>
     </row>
     <row r="48">
@@ -5947,7 +5947,7 @@
         <v>4.4</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>3657</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="49">
@@ -6103,7 +6103,7 @@
         <v>4</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="53">
@@ -6222,10 +6222,10 @@
         <v>7229</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>796</v>
+        <v>7230</v>
       </c>
     </row>
     <row r="56">
@@ -6389,7 +6389,7 @@
         <v>4.5</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="60">
@@ -6473,7 +6473,7 @@
         <v>4.4</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>2891</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="62">
@@ -6721,7 +6721,7 @@
         <v>4.2</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>10340</v>
+        <v>10341</v>
       </c>
     </row>
     <row r="68">
@@ -6759,7 +6759,7 @@
         <v>4.5</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>4288</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="69">
@@ -6881,7 +6881,7 @@
         <v>4.3</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>6139</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="72">
@@ -7037,7 +7037,7 @@
         <v>4.2</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>16965</v>
+        <v>16966</v>
       </c>
     </row>
     <row r="76">
@@ -7121,7 +7121,7 @@
         <v>4.7</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2437</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="78">
@@ -7239,7 +7239,7 @@
         <v>4.8</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>1478</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="81">
@@ -7323,7 +7323,7 @@
         <v>4.4</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="83">
@@ -7399,7 +7399,7 @@
         <v>4</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="85">
@@ -7437,7 +7437,7 @@
         <v>4.6</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>3935</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="86">
@@ -7513,7 +7513,7 @@
         <v>4.2</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>5255</v>
+        <v>5256</v>
       </c>
     </row>
     <row r="88">
@@ -7627,7 +7627,7 @@
         <v>4.6</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>3595</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="91">
@@ -7665,7 +7665,7 @@
         <v>4.5</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>3220</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="92">
@@ -7893,7 +7893,7 @@
         <v>4.2</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>2877</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="98">
@@ -8042,10 +8042,10 @@
         <v>288</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>212</v>
+        <v>288</v>
       </c>
     </row>
     <row r="102">
@@ -8080,10 +8080,10 @@
         <v>75</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>251</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103">
@@ -8121,7 +8121,7 @@
         <v>4.4</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="104">
@@ -8235,7 +8235,7 @@
         <v>4.5</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="107">
@@ -8526,7 +8526,7 @@
         <v>4.6</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>1720</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="5">
@@ -8568,7 +8568,7 @@
         <v>4.3</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>3415</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="6">
@@ -8652,7 +8652,7 @@
         <v>4.7</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="8">
@@ -8694,7 +8694,7 @@
         <v>4.8</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>3364</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="9">
@@ -8858,7 +8858,7 @@
         <v>4.3</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>3415</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="13">
@@ -8942,7 +8942,7 @@
         <v>4.7</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>3448</v>
+        <v>3449</v>
       </c>
     </row>
     <row r="15">
@@ -9068,7 +9068,7 @@
         <v>4.6</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="18">
@@ -9232,7 +9232,7 @@
         <v>4.4</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>3843</v>
+        <v>3847</v>
       </c>
     </row>
     <row r="22">
@@ -9536,7 +9536,7 @@
         <v>4.6</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="30">
@@ -9802,7 +9802,7 @@
         <v>3.9</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="37">
@@ -9916,7 +9916,7 @@
         <v>4.2</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="40">
@@ -10141,7 +10141,7 @@
         <v>370</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J45" s="9" t="n">
         <v>369</v>
@@ -10220,7 +10220,7 @@
         <v>3.7</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>2566</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="48">
@@ -10296,7 +10296,7 @@
         <v>3.5</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>1418</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="50">
@@ -10334,7 +10334,7 @@
         <v>4.1</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="51">
@@ -10372,7 +10372,7 @@
         <v>4.1</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>2807</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="52">
@@ -10448,7 +10448,7 @@
         <v>4.1</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>1224</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="54">
@@ -10889,7 +10889,7 @@
         <v>4.3</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>4571</v>
+        <v>4576</v>
       </c>
     </row>
     <row r="4">
@@ -10927,7 +10927,7 @@
         <v>4.4</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="5">
@@ -11079,7 +11079,7 @@
         <v>4.4</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="9">
@@ -11155,7 +11155,7 @@
         <v>4.3</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2010</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="11">
@@ -11459,7 +11459,7 @@
         <v>4.3</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>12118</v>
+        <v>12119</v>
       </c>
     </row>
     <row r="19">
@@ -11649,7 +11649,7 @@
         <v>4.5</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1722</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="24">
@@ -11725,7 +11725,7 @@
         <v>4.7</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>2052</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="26">
@@ -11801,7 +11801,7 @@
         <v>4.2</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>11064</v>
+        <v>11065</v>
       </c>
     </row>
     <row r="28">
@@ -12067,7 +12067,7 @@
         <v>4.1</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>39673</v>
+        <v>39675</v>
       </c>
     </row>
     <row r="35">
@@ -12371,7 +12371,7 @@
         <v>4.1</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="43">
@@ -12523,7 +12523,7 @@
         <v>4.2</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>7884</v>
+        <v>7885</v>
       </c>
     </row>
     <row r="47">
@@ -12637,7 +12637,7 @@
         <v>4.5</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>3640</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="50">
@@ -12675,7 +12675,7 @@
         <v>4.9</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51">
@@ -12713,7 +12713,7 @@
         <v>4.2</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>4117</v>
+        <v>4119</v>
       </c>
     </row>
     <row r="52">
@@ -12751,7 +12751,7 @@
         <v>4.7</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53">
@@ -12789,7 +12789,7 @@
         <v>4.8</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54">
@@ -12827,7 +12827,7 @@
         <v>4.2</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>4117</v>
+        <v>4119</v>
       </c>
     </row>
     <row r="55">
@@ -12865,7 +12865,7 @@
         <v>4.7</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56">
@@ -13131,7 +13131,7 @@
         <v>4.1</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>3614</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="63">
@@ -13283,7 +13283,7 @@
         <v>4.1</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>6443</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="67">
@@ -13397,7 +13397,7 @@
         <v>4.5</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>2913</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="70">
@@ -13625,7 +13625,7 @@
         <v>4.3</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>4653</v>
+        <v>4654</v>
       </c>
     </row>
     <row r="76">
@@ -13891,7 +13891,7 @@
         <v>4.3</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>11735</v>
+        <v>11737</v>
       </c>
     </row>
     <row r="83">
@@ -14195,7 +14195,7 @@
         <v>4.3</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>2233</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="91">
@@ -14233,7 +14233,7 @@
         <v>4.2</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>7974</v>
+        <v>7976</v>
       </c>
     </row>
     <row r="92">
@@ -14423,7 +14423,7 @@
         <v>4.2</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>6438</v>
+        <v>6439</v>
       </c>
     </row>
     <row r="97">
@@ -14499,7 +14499,7 @@
         <v>4.1</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1933</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="99">
@@ -14537,7 +14537,7 @@
         <v>4.5</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>5568</v>
+        <v>5570</v>
       </c>
     </row>
     <row r="100">
@@ -14613,7 +14613,7 @@
         <v>4.5</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>6151</v>
+        <v>6158</v>
       </c>
     </row>
     <row r="102">
@@ -14803,7 +14803,7 @@
         <v>4.1</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>10973</v>
+        <v>10974</v>
       </c>
     </row>
     <row r="107">
@@ -14879,7 +14879,7 @@
         <v>4.5</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>3052</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="109">
@@ -14917,7 +14917,7 @@
         <v>4.3</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>2619</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="110">
@@ -15031,7 +15031,7 @@
         <v>4.4</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>2447</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="113">
@@ -15238,7 +15238,7 @@
         <v>4.3</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="5">
@@ -15314,7 +15314,7 @@
         <v>4.3</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -15618,7 +15618,7 @@
         <v>4.2</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>6808</v>
+        <v>6809</v>
       </c>
     </row>
     <row r="15">
@@ -15656,7 +15656,7 @@
         <v>4.2</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>3602</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="16">
@@ -15770,7 +15770,7 @@
         <v>4.2</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>19720</v>
+        <v>19723</v>
       </c>
     </row>
     <row r="19">
@@ -15884,7 +15884,7 @@
         <v>4.2</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>8780</v>
+        <v>8781</v>
       </c>
     </row>
     <row r="22">

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -675,7 +675,7 @@
         <v>4.3</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>15769</v>
+        <v>15771</v>
       </c>
     </row>
     <row r="5">
@@ -717,7 +717,7 @@
         <v>4.5</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>5526</v>
+        <v>5531</v>
       </c>
     </row>
     <row r="6">
@@ -759,7 +759,7 @@
         <v>4.3</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>6534</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="7">
@@ -801,7 +801,7 @@
         <v>4.5</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2389</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="8">
@@ -843,7 +843,7 @@
         <v>4.4</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>7145</v>
+        <v>7147</v>
       </c>
     </row>
     <row r="9">
@@ -969,7 +969,7 @@
         <v>4.7</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1100</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="12">
@@ -1053,7 +1053,7 @@
         <v>4.7</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>2210</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="14">
@@ -1095,7 +1095,7 @@
         <v>4.4</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>2347</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="15">
@@ -1221,7 +1221,7 @@
         <v>4.7</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1327</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="18">
@@ -1347,7 +1347,7 @@
         <v>4.6</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="21">
@@ -1557,7 +1557,7 @@
         <v>4.8</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="26">
@@ -1630,10 +1630,10 @@
         <v>1165</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>2234</v>
+        <v>1165</v>
       </c>
     </row>
   </sheetData>
@@ -1958,7 +1958,7 @@
         <v>4.3</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>168</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -2000,7 +2000,7 @@
         <v>4.3</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>168</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -2042,7 +2042,7 @@
         <v>4.3</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>168</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -2481,10 +2481,10 @@
         <v>915</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>28</v>
+        <v>915</v>
       </c>
     </row>
     <row r="22">
@@ -2523,10 +2523,10 @@
         <v>915</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>28</v>
+        <v>915</v>
       </c>
     </row>
     <row r="23">
@@ -2565,10 +2565,10 @@
         <v>915</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>28</v>
+        <v>915</v>
       </c>
     </row>
     <row r="24">
@@ -2607,10 +2607,10 @@
         <v>915</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>28</v>
+        <v>915</v>
       </c>
     </row>
     <row r="25">
@@ -2884,7 +2884,7 @@
         <v>4.7</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>2210</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="32">
@@ -2923,10 +2923,10 @@
         <v>1042</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>168</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="33">
@@ -2965,10 +2965,10 @@
         <v>1042</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>168</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="34">
@@ -3284,7 +3284,7 @@
         <v>4.7</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>1100</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="42">
@@ -4173,7 +4173,7 @@
         <v>4.3</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>2098</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="4">
@@ -4422,10 +4422,10 @@
         <v>217</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10">
@@ -4543,7 +4543,7 @@
         <v>4.5</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>4871</v>
+        <v>4872</v>
       </c>
     </row>
     <row r="13">
@@ -4695,7 +4695,7 @@
         <v>4.2</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>3402</v>
+        <v>3403</v>
       </c>
     </row>
     <row r="17">
@@ -4847,7 +4847,7 @@
         <v>4.6</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>8144</v>
+        <v>8145</v>
       </c>
     </row>
     <row r="21">
@@ -4885,7 +4885,7 @@
         <v>4.4</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>6604</v>
+        <v>6608</v>
       </c>
     </row>
     <row r="22">
@@ -4923,7 +4923,7 @@
         <v>4.4</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>6252</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="23">
@@ -5003,7 +5003,7 @@
         <v>4.8</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>4693</v>
+        <v>4694</v>
       </c>
     </row>
     <row r="25">
@@ -5041,7 +5041,7 @@
         <v>4.5</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>6254</v>
+        <v>6257</v>
       </c>
     </row>
     <row r="26">
@@ -5197,7 +5197,7 @@
         <v>4.3</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>8649</v>
+        <v>8650</v>
       </c>
     </row>
     <row r="30">
@@ -5315,7 +5315,7 @@
         <v>4.5</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>5526</v>
+        <v>5531</v>
       </c>
     </row>
     <row r="33">
@@ -5513,7 +5513,7 @@
         <v>4.7</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1327</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="38">
@@ -5551,7 +5551,7 @@
         <v>4.7</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1100</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="39">
@@ -5627,7 +5627,7 @@
         <v>4.6</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="41">
@@ -5711,7 +5711,7 @@
         <v>4.5</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2390</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="43">
@@ -5749,7 +5749,7 @@
         <v>4.7</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2210</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="44">
@@ -5871,7 +5871,7 @@
         <v>4.4</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>7144</v>
+        <v>7147</v>
       </c>
     </row>
     <row r="47">
@@ -5909,7 +5909,7 @@
         <v>4.3</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>15769</v>
+        <v>15771</v>
       </c>
     </row>
     <row r="48">
@@ -5989,7 +5989,7 @@
         <v>4.4</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>2347</v>
+        <v>2348</v>
       </c>
     </row>
     <row r="50">
@@ -6599,7 +6599,7 @@
         <v>3.9</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="65">
@@ -6721,7 +6721,7 @@
         <v>4.2</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>10341</v>
+        <v>10342</v>
       </c>
     </row>
     <row r="68">
@@ -6759,7 +6759,7 @@
         <v>4.5</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>4289</v>
+        <v>4292</v>
       </c>
     </row>
     <row r="69">
@@ -6881,7 +6881,7 @@
         <v>4.3</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>6140</v>
+        <v>6141</v>
       </c>
     </row>
     <row r="72">
@@ -7121,7 +7121,7 @@
         <v>4.7</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2440</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="78">
@@ -7239,7 +7239,7 @@
         <v>4.8</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="81">
@@ -7437,7 +7437,7 @@
         <v>4.6</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>3942</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="86">
@@ -7513,7 +7513,7 @@
         <v>4.2</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>5256</v>
+        <v>5257</v>
       </c>
     </row>
     <row r="88">
@@ -7627,7 +7627,7 @@
         <v>4.6</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>3599</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="91">
@@ -7665,7 +7665,7 @@
         <v>4.5</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>3226</v>
+        <v>3227</v>
       </c>
     </row>
     <row r="92">
@@ -7893,7 +7893,7 @@
         <v>4.2</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>2886</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="98">
@@ -8121,7 +8121,7 @@
         <v>4.4</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="104">
@@ -8778,7 +8778,7 @@
         <v>4.6</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="11">
@@ -9152,7 +9152,7 @@
         <v>4.5</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1661</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="20">
@@ -10144,7 +10144,7 @@
         <v>4.2</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="46">
@@ -10524,7 +10524,7 @@
         <v>4.4</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="56">
@@ -11155,7 +11155,7 @@
         <v>4.3</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="11">
@@ -11269,7 +11269,7 @@
         <v>4.2</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>21262</v>
+        <v>21263</v>
       </c>
     </row>
     <row r="14">
@@ -11497,7 +11497,7 @@
         <v>4.2</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>3077</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="20">
@@ -11649,7 +11649,7 @@
         <v>4.5</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1721</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="24">
@@ -11801,7 +11801,7 @@
         <v>4.2</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>11065</v>
+        <v>11066</v>
       </c>
     </row>
     <row r="28">
@@ -12067,7 +12067,7 @@
         <v>4.1</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>39675</v>
+        <v>39676</v>
       </c>
     </row>
     <row r="35">
@@ -12143,7 +12143,7 @@
         <v>4.3</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>10372</v>
+        <v>10373</v>
       </c>
     </row>
     <row r="37">
@@ -12333,7 +12333,7 @@
         <v>4.2</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>2615</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="42">
@@ -12523,7 +12523,7 @@
         <v>4.2</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>7885</v>
+        <v>7886</v>
       </c>
     </row>
     <row r="47">
@@ -12675,7 +12675,7 @@
         <v>4.9</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="51">
@@ -13093,7 +13093,7 @@
         <v>4.2</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>7819</v>
+        <v>7820</v>
       </c>
     </row>
     <row r="62">
@@ -13625,7 +13625,7 @@
         <v>4.3</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>4654</v>
+        <v>4655</v>
       </c>
     </row>
     <row r="76">
@@ -13663,7 +13663,7 @@
         <v>4.3</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>5286</v>
+        <v>5287</v>
       </c>
     </row>
     <row r="77">
@@ -14005,7 +14005,7 @@
         <v>4.4</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>3258</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="86">
@@ -14233,7 +14233,7 @@
         <v>4.2</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>7976</v>
+        <v>7975</v>
       </c>
     </row>
     <row r="92">
@@ -14575,7 +14575,7 @@
         <v>4.4</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>17773</v>
+        <v>17774</v>
       </c>
     </row>
     <row r="101">
@@ -14613,7 +14613,7 @@
         <v>4.5</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>6158</v>
+        <v>6160</v>
       </c>
     </row>
     <row r="102">
@@ -15031,7 +15031,7 @@
         <v>4.4</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>2448</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="113">
@@ -15352,7 +15352,7 @@
         <v>4.2</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>4836</v>
+        <v>4835</v>
       </c>
     </row>
     <row r="8">
@@ -15846,7 +15846,7 @@
         <v>4.1</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="21">

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Bikanervala GGN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Competitors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="India BV" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="International BV" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Haldiram India" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="OM Sweets India" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bikanervala GGN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="India BV" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="International BV" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haldiram India" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OM Sweets India" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,10 +21,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
-  <fonts count="5">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,19 +39,8 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -64,30 +51,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -131,21 +94,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,8 +460,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -529,18 +477,6 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="G1" s="6" t="n">
-        <v>46300</v>
-      </c>
-      <c r="H1" s="6" t="n">
-        <v>46300</v>
-      </c>
-      <c r="I1" s="6" t="n">
-        <v>46301</v>
-      </c>
-      <c r="J1" s="6" t="n">
-        <v>46301</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -571,26 +507,6 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>Review Count</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -623,18 +539,6 @@
           <t>https://share.google/JV7XDH4ryWmQNPfVY</t>
         </is>
       </c>
-      <c r="G3" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>4870</v>
-      </c>
-      <c r="I3" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>4874</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -665,18 +569,6 @@
           <t>https://share.google/AXcgrOXWWfQtoSOkz</t>
         </is>
       </c>
-      <c r="G4" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>15774</v>
-      </c>
-      <c r="I4" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>15771</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -707,18 +599,6 @@
           <t>https://share.google/Lq1yf4rveBX5BWyts</t>
         </is>
       </c>
-      <c r="G5" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>5513</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>5531</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -749,18 +629,6 @@
           <t>https://share.google/5iiO04ZTn35j8E5HB</t>
         </is>
       </c>
-      <c r="G6" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>6534</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>6533</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -791,18 +659,6 @@
           <t>https://share.google/iNagaqHoCbBOIvV0x</t>
         </is>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>2387</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>2397</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -833,18 +689,6 @@
           <t>https://share.google/S4Kwkg9xEW0S2j7a0</t>
         </is>
       </c>
-      <c r="G8" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>7161</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>7147</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -875,18 +719,6 @@
           <t>https://share.google/NS8T7gwZSlKSNr3UP</t>
         </is>
       </c>
-      <c r="G9" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>3661</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>3667</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -917,18 +749,6 @@
           <t>https://share.google/Xmyef4OwQmXyWCFN0</t>
         </is>
       </c>
-      <c r="G10" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>2775</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>2781</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -959,18 +779,6 @@
           <t>https://share.google/6khAtgqK72w0kjN0Q</t>
         </is>
       </c>
-      <c r="G11" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>1094</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>1103</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1001,18 +809,6 @@
           <t>https://share.google/CgukSORsdWkszVRvP</t>
         </is>
       </c>
-      <c r="G12" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>1108</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>1108</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1043,18 +839,6 @@
           <t>https://share.google/BNfINmH1QbNZhf7ox</t>
         </is>
       </c>
-      <c r="G13" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>2211</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>2213</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1085,18 +869,6 @@
           <t>https://share.google/LJxUW77APw08Vr9a0</t>
         </is>
       </c>
-      <c r="G14" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>2347</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>2348</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1127,18 +899,6 @@
           <t>https://share.google/LAZMqwdryXVTeQkgt</t>
         </is>
       </c>
-      <c r="G15" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <v>2587</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>2588</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1169,18 +929,6 @@
           <t>https://share.google/lkP8lqhdoKZRzyal3</t>
         </is>
       </c>
-      <c r="G16" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>885</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>888</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1211,18 +959,6 @@
           <t>https://share.google/255ZPlPOiTGMhDzy0</t>
         </is>
       </c>
-      <c r="G17" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>1326</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>1329</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1253,18 +989,6 @@
           <t>https://share.google/9TqthrgcK6VnEH9Kh</t>
         </is>
       </c>
-      <c r="G18" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>449</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>450</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1295,18 +1019,6 @@
           <t>https://share.google/uqXvcL4esuwjgcsRz</t>
         </is>
       </c>
-      <c r="G19" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>926</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>928</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1337,18 +1049,6 @@
           <t>https://share.google/E5KGOYYKX6YqD07hf</t>
         </is>
       </c>
-      <c r="G20" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>1091</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>1097</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1379,18 +1079,6 @@
           <t>https://share.google/ooNGpI4Ewi9Zt5t02</t>
         </is>
       </c>
-      <c r="G21" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>788</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>788</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1421,18 +1109,6 @@
           <t>https://share.google/Z2RQtKISxQhQWQSl4</t>
         </is>
       </c>
-      <c r="G22" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>657</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>659</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1463,18 +1139,6 @@
           <t>https://share.google/grSJuehxs8v7sVOVt</t>
         </is>
       </c>
-      <c r="G23" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>696</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>699</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1505,18 +1169,6 @@
           <t>https://share.google/V1f6JY6CBgPW0eoIg</t>
         </is>
       </c>
-      <c r="G24" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>1430</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>1428</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1547,18 +1199,6 @@
           <t>https://share.google/r13AfGhfeAFwXti2i</t>
         </is>
       </c>
-      <c r="G25" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H25" s="9" t="n">
-        <v>698</v>
-      </c>
-      <c r="I25" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J25" s="9" t="n">
-        <v>703</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1584,56 +1224,6 @@
         <is>
           <t>https://share.google/e0rEvKWJDcji81RKF</t>
         </is>
-      </c>
-      <c r="G26" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H26" s="9" t="n">
-        <v>356</v>
-      </c>
-      <c r="I26" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J26" s="9" t="n">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Bikanervala</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>1165</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>1165</v>
       </c>
     </row>
   </sheetData>
@@ -1647,8 +1237,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:F68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -1664,18 +1254,6 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="G1" s="6" t="n">
-        <v>46300</v>
-      </c>
-      <c r="H1" s="6" t="n">
-        <v>46300</v>
-      </c>
-      <c r="I1" s="6" t="n">
-        <v>46301</v>
-      </c>
-      <c r="J1" s="6" t="n">
-        <v>46301</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1685,47 +1263,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>Pairs</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>Store Code</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Store Address</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Outlet Name</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>Review Count</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -1758,18 +1316,6 @@
           <t>https://share.google/vwJnwPNeUQYJeEduL</t>
         </is>
       </c>
-      <c r="G3" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>81</v>
-      </c>
-      <c r="I3" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>81</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1822,18 +1368,6 @@
           <t>https://share.google/W7otAdG8FtptbWSwl</t>
         </is>
       </c>
-      <c r="G5" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>3862</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>3862</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1864,18 +1398,6 @@
           <t>https://share.google/W7otAdG8FtptbWSwl</t>
         </is>
       </c>
-      <c r="G6" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>3862</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>3862</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1906,18 +1428,6 @@
           <t>https://share.google/Z2RQtKISxQhQWQSl4</t>
         </is>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>657</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>659</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1948,18 +1458,6 @@
           <t>https://share.google/lP3zeGY3pdczZ13a6</t>
         </is>
       </c>
-      <c r="G8" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1990,18 +1488,6 @@
           <t>https://share.google/lP3zeGY3pdczZ13a6</t>
         </is>
       </c>
-      <c r="G9" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -2032,18 +1518,6 @@
           <t>https://share.google/lP3zeGY3pdczZ13a6</t>
         </is>
       </c>
-      <c r="G10" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -2074,18 +1548,6 @@
           <t>https://share.google/z92S6uNfId7gh7xXh</t>
         </is>
       </c>
-      <c r="G11" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>1193</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>1193</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -2116,18 +1578,6 @@
           <t>https://share.google/z92S6uNfId7gh7xXh</t>
         </is>
       </c>
-      <c r="G12" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>1193</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>1193</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -2158,18 +1608,6 @@
           <t>https://share.google/76FqjGJdw3pWT7Nhm</t>
         </is>
       </c>
-      <c r="G13" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>1820</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>1820</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -2200,18 +1638,6 @@
           <t>https://share.google/76FqjGJdw3pWT7Nhm</t>
         </is>
       </c>
-      <c r="G14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>1820</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>1820</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -2242,18 +1668,6 @@
           <t>https://share.google/76FqjGJdw3pWT7Nhm</t>
         </is>
       </c>
-      <c r="G15" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <v>1820</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>1820</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -2306,18 +1720,6 @@
           <t>https://share.google/76FqjGJdw3pWT7Nhm</t>
         </is>
       </c>
-      <c r="G17" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>1820</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>1820</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -2348,18 +1750,6 @@
           <t>https://share.google/tK0HH6YhuhGFtmkpF</t>
         </is>
       </c>
-      <c r="G18" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>4500</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>4500</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -2390,18 +1780,6 @@
           <t>https://share.google/tK0HH6YhuhGFtmkpF</t>
         </is>
       </c>
-      <c r="G19" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>4500</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>4500</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -2432,18 +1810,6 @@
           <t>https://share.google/Xmyef4OwQmXyWCFN0</t>
         </is>
       </c>
-      <c r="G20" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>2775</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>2781</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -2471,20 +1837,8 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>https://share.google/0fL448lM3UMCNEVP7</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>915</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>915</v>
+          <t>https://share.google/AXcgrOXWWfQtoSOkz</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -2513,20 +1867,8 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>https://share.google/0fL448lM3UMCNEVP7</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>915</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>915</v>
+          <t>https://share.google/PJ8dwnAbtWjau9ZuQ</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2555,20 +1897,8 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>https://share.google/0fL448lM3UMCNEVP7</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>915</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>915</v>
+          <t>https://www.google.com/maps/search/Om+Sweets+Sector+23+Gurgaon?hl=en</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -2597,20 +1927,8 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>https://share.google/0fL448lM3UMCNEVP7</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>915</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>915</v>
+          <t>https://www.google.com/maps/search/Om+Sweets+Sector+31+Gurgaon?hl=en</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -2642,18 +1960,6 @@
           <t>https://share.google/Ofv3RzFrXczsACnpP</t>
         </is>
       </c>
-      <c r="G25" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H25" s="9" t="n">
-        <v>847</v>
-      </c>
-      <c r="I25" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J25" s="9" t="n">
-        <v>847</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -2684,18 +1990,6 @@
           <t>https://share.google/Ofv3RzFrXczsACnpP</t>
         </is>
       </c>
-      <c r="G26" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H26" s="9" t="n">
-        <v>847</v>
-      </c>
-      <c r="I26" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J26" s="9" t="n">
-        <v>847</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -2726,18 +2020,6 @@
           <t>https://share.google/Ofv3RzFrXczsACnpP</t>
         </is>
       </c>
-      <c r="G27" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>847</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>847</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -2768,18 +2050,6 @@
           <t>https://share.google/xPXfeD0V5srbLT4eX</t>
         </is>
       </c>
-      <c r="G28" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H28" s="9" t="n">
-        <v>3601</v>
-      </c>
-      <c r="I28" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J28" s="9" t="n">
-        <v>3604</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -2810,18 +2080,6 @@
           <t>https://share.google/xPXfeD0V5srbLT4eX</t>
         </is>
       </c>
-      <c r="G29" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>3601</v>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J29" s="9" t="n">
-        <v>3604</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -2874,18 +2132,6 @@
           <t>https://share.google/BNfINmH1QbNZhf7ox</t>
         </is>
       </c>
-      <c r="G31" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H31" s="9" t="n">
-        <v>2211</v>
-      </c>
-      <c r="I31" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>2213</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -2916,18 +2162,6 @@
           <t>https://share.google/aK8m7Ox6K0FZJ6Xwu</t>
         </is>
       </c>
-      <c r="G32" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>1042</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>1043</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -2958,18 +2192,6 @@
           <t>https://share.google/aK8m7Ox6K0FZJ6Xwu</t>
         </is>
       </c>
-      <c r="G33" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>1042</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>1043</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -3022,18 +2244,6 @@
           <t>https://share.google/7DhqfVESQtmCb7UZh</t>
         </is>
       </c>
-      <c r="G35" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>4834</v>
-      </c>
-      <c r="I35" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J35" s="9" t="n">
-        <v>4836</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -3064,18 +2274,6 @@
           <t>https://share.google/7DhqfVESQtmCb7UZh</t>
         </is>
       </c>
-      <c r="G36" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H36" s="9" t="n">
-        <v>4834</v>
-      </c>
-      <c r="I36" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>4836</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -3106,18 +2304,6 @@
           <t>https://share.google/i9dx9ixhDINCZ9YbT</t>
         </is>
       </c>
-      <c r="G37" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H37" s="9" t="n">
-        <v>282</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>282</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -3148,18 +2334,6 @@
           <t>https://share.google/i9dx9ixhDINCZ9YbT</t>
         </is>
       </c>
-      <c r="G38" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H38" s="9" t="n">
-        <v>282</v>
-      </c>
-      <c r="I38" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>282</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -3190,18 +2364,6 @@
           <t>https://share.google/LAZMqwdryXVTeQkgt</t>
         </is>
       </c>
-      <c r="G39" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>2587</v>
-      </c>
-      <c r="I39" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J39" s="9" t="n">
-        <v>2588</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -3232,18 +2394,6 @@
           <t>https://share.google/9TqthrgcK6VnEH9Kh</t>
         </is>
       </c>
-      <c r="G40" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H40" s="9" t="n">
-        <v>449</v>
-      </c>
-      <c r="I40" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J40" s="9" t="n">
-        <v>450</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -3274,18 +2424,6 @@
           <t>https://share.google/6khAtgqK72w0kjN0Q</t>
         </is>
       </c>
-      <c r="G41" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H41" s="9" t="n">
-        <v>1094</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J41" s="9" t="n">
-        <v>1103</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -3316,18 +2454,6 @@
           <t>https://share.google/Jlgj9CSmiwGBJzq7p</t>
         </is>
       </c>
-      <c r="G42" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H42" s="9" t="n">
-        <v>11734</v>
-      </c>
-      <c r="I42" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J42" s="9" t="n">
-        <v>11737</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -3358,18 +2484,6 @@
           <t>https://share.google/Jlgj9CSmiwGBJzq7p</t>
         </is>
       </c>
-      <c r="G43" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H43" s="9" t="n">
-        <v>11734</v>
-      </c>
-      <c r="I43" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J43" s="9" t="n">
-        <v>11737</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -3400,18 +2514,6 @@
           <t>https://share.google/EFPYdy3wXu07YRAlK</t>
         </is>
       </c>
-      <c r="G44" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H44" s="9" t="n">
-        <v>191</v>
-      </c>
-      <c r="I44" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>192</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -3442,18 +2544,6 @@
           <t>https://share.google/EFPYdy3wXu07YRAlK</t>
         </is>
       </c>
-      <c r="G45" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H45" s="9" t="n">
-        <v>191</v>
-      </c>
-      <c r="I45" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J45" s="9" t="n">
-        <v>192</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -3484,18 +2574,6 @@
           <t>https://share.google/aioloSd77eFIRO9Ok</t>
         </is>
       </c>
-      <c r="G46" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H46" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I46" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J46" s="9" t="n">
-        <v>2002</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -3526,18 +2604,6 @@
           <t>https://share.google/aioloSd77eFIRO9Ok</t>
         </is>
       </c>
-      <c r="G47" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H47" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I47" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J47" s="9" t="n">
-        <v>2002</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -3568,18 +2634,6 @@
           <t>https://share.google/KaiqyN6GtR2mXupJW</t>
         </is>
       </c>
-      <c r="G48" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H48" s="9" t="n">
-        <v>1773</v>
-      </c>
-      <c r="I48" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J48" s="9" t="n">
-        <v>1774</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -3609,18 +2663,6 @@
         <is>
           <t>https://share.google/KaiqyN6GtR2mXupJW</t>
         </is>
-      </c>
-      <c r="G49" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H49" s="9" t="n">
-        <v>1773</v>
-      </c>
-      <c r="I49" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J49" s="9" t="n">
-        <v>1774</v>
       </c>
     </row>
     <row r="50">
@@ -4052,8 +3094,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J109"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:F109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -4069,18 +3111,6 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="G1" s="6" t="n">
-        <v>46300</v>
-      </c>
-      <c r="H1" s="6" t="n">
-        <v>46300</v>
-      </c>
-      <c r="I1" s="6" t="n">
-        <v>46301</v>
-      </c>
-      <c r="J1" s="6" t="n">
-        <v>46301</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -4111,26 +3141,6 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>Review Count</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -4163,18 +3173,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Netaji+Subhash+Place+Delhi,+Shop+No.+01+ITL+Twin+Tower,+Netaji+Subhash+Place,+Pitampura,+New+Delhi,+Delhi+110034/@28.6911987,77.1522225,16z/data=!4m6!3m5!1s0x390d03c155555555:0x5b4d4b46cc7ccd4a!8m2!3d28.6911987!4d77.1522225!16s%2Fg%2F1tfldmlm?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
-      <c r="G3" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>2094</v>
-      </c>
-      <c r="I3" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>2099</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -4205,18 +3203,6 @@
           <t>https://www.google.com/maps/place/Ground+Floor,+Bikanervala+%7C+Sadar+Bazaar,+Devika+Sadar,+Shop+No.+G+12,+G+14-19+7+G+24+-+44,+Qutab+Rd,+Narain+Market,+Sadar+Bazar,+New+Delhi,+Delhi+110006/@28.6558145,77.2162412,16z/data=!4m6!3m5!1s0x390cfde0b0b14249:0xc8e86801bdd1bfd0!8m2!3d28.6558145!4d77.2162412!16s%2Fg%2F11ksks6gbd?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
-      <c r="G4" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>631</v>
-      </c>
-      <c r="I4" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>632</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -4247,18 +3233,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Liberty+Cinema+Karol+Bagh/@28.6606284,77.1876003,17z/data=!3m1!4b1!4m6!3m5!1s0x390d03326d19a899:0xd2fef34572239279!8m2!3d28.6606284!4d77.1876003!16s%2Fg%2F11m5qhcscj?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G5" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>1555</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>1555</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -4289,18 +3263,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Kalkaji+Metro/@28.5494507,77.259104,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce361d13dfecb:0x11d594dba2638f6d!8m2!3d28.5494507!4d77.259104!16s%2Fg%2F11x72l6mq2?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G6" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>126</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>126</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -4331,18 +3293,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Lajpat+Nagar+Delhi/@28.5708816,77.2390955,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce252e00cf3fb:0xf48521c45d7cd156!8m2!3d28.5708816!4d77.2390955!16s%2Fg%2F1td_wzrz?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>10882</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>10884</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -4373,18 +3323,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Defence+Colony+Delhi/@28.5748765,77.2381202,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce3d5f019e1e9:0xa3e490839a38e681!8m2!3d28.5748765!4d77.2381202!16s%2Fg%2F11qb4tsxc0?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G8" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>2937</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>2937</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -4415,18 +3353,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+East+of+Kailash+Delhi/@28.5587762,77.246459,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce39ca675e7c3:0xbe857ad66d22f2bf!8m2!3d28.5587762!4d77.246459!16s%2Fg%2F11s1qvx_74?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G9" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>217</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>218</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -4457,18 +3383,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Preet+Vihar+Delhi/@28.6392518,77.2948339,17z/data=!3m1!4b1!4m6!3m5!1s0x390cfb510ec67a93:0xfad0c088f3f91804!8m2!3d28.6392518!4d77.2948339!16s%2Fg%2F1tgnkg53?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G10" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>5139</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>5139</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -4495,18 +3409,6 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>7302</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>7305</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -4533,18 +3435,6 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>4869</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>4872</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -4571,18 +3461,6 @@
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>948</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>949</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -4609,18 +3487,6 @@
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>1916</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>1916</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -4647,18 +3513,6 @@
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <v>833</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>834</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -4685,18 +3539,6 @@
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>3402</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>3403</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -4723,18 +3565,6 @@
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>5647</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>5648</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -4761,18 +3591,6 @@
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>4601</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>4603</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -4799,18 +3617,6 @@
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>5739</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>5743</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -4837,18 +3643,6 @@
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>8133</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>8145</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -4875,18 +3669,6 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>6604</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>6608</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -4913,18 +3695,6 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>6274</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>6258</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -4955,18 +3725,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Dwarka+Delhi/@28.5966087,77.0417524,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1b72556cb43b:0xdd37fb0751d2b900!8m2!3d28.5966087!4d77.0417524!16s%2Fg%2F11grt4vw5b?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G23" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>6217</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>6217</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -4993,18 +3751,6 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>4692</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>4694</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -5031,18 +3777,6 @@
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H25" s="9" t="n">
-        <v>6260</v>
-      </c>
-      <c r="I25" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J25" s="9" t="n">
-        <v>6257</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -5069,18 +3803,6 @@
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H26" s="9" t="n">
-        <v>1900</v>
-      </c>
-      <c r="I26" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J26" s="9" t="n">
-        <v>1901</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -5107,18 +3829,6 @@
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>8386</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>8386</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -5145,18 +3855,6 @@
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H28" s="9" t="n">
-        <v>233</v>
-      </c>
-      <c r="I28" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="9" t="n">
-        <v>233</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -5187,18 +3885,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Chanakyapuri+Delhi/@28.585244,77.19149,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1d7cdedc3389:0x60798b43139c76d3!8m2!3d28.585244!4d77.19149!16s%2Fg%2F1tdvhkdv?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G29" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>8651</v>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J29" s="9" t="n">
-        <v>8650</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -5225,18 +3911,6 @@
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H30" s="9" t="n">
-        <v>2775</v>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J30" s="9" t="n">
-        <v>2781</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -5267,18 +3941,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+GK-II+Savitri+Cinema+Delhi/@28.5374253,77.2389712,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce22b17e2d781:0x40c5f102209b866c!8m2!3d28.5374253!4d77.2389712!16s%2Fg%2F11cmr0t9q8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G31" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H31" s="9" t="n">
-        <v>5575</v>
-      </c>
-      <c r="I31" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>5575</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -5305,18 +3967,6 @@
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>5513</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>5531</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -5347,18 +3997,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+57+Gurugram/@28.4161819,77.0849591,17z/data=!3m1!4b1!4m6!3m5!1s0x390d232798684757:0xb380904dacac7eed!8m2!3d28.4161819!4d77.0849591!16s%2Fg%2F11k522rkjz?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G33" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>4870</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>4874</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -5385,18 +4023,6 @@
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H34" s="9" t="n">
-        <v>885</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>888</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -5423,18 +4049,6 @@
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>2587</v>
-      </c>
-      <c r="I35" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J35" s="9" t="n">
-        <v>2588</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -5461,18 +4075,6 @@
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H36" s="9" t="n">
-        <v>696</v>
-      </c>
-      <c r="I36" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>699</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -5503,18 +4105,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+The+Esplanade+Mall+Sector+37+Gurugram/@28.4538074,76.9928507,17z/data=!3m1!4b1!4m6!3m5!1s0x390d171587c41467:0x4070a84c531d04ce!8m2!3d28.4538074!4d76.9928507!16s%2Fg%2F11tggmn3j8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G37" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H37" s="9" t="n">
-        <v>1328</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>1329</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -5541,18 +4131,6 @@
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H38" s="9" t="n">
-        <v>1094</v>
-      </c>
-      <c r="I38" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>1103</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -5579,18 +4157,6 @@
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>510</v>
-      </c>
-      <c r="I39" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J39" s="9" t="n">
-        <v>510</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -5617,18 +4183,6 @@
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H40" s="9" t="n">
-        <v>1091</v>
-      </c>
-      <c r="I40" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J40" s="9" t="n">
-        <v>1097</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -5659,18 +4213,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+62+Gurugram/@28.4014616,77.0852188,17z/data=!3m1!4b1!4m6!3m5!1s0x390d23dcf278418d:0x4d1e11be0af4d661!8m2!3d28.4014616!4d77.0852188!16s%2Fg%2F11h7qrpfv4?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G41" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H41" s="9" t="n">
-        <v>449</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J41" s="9" t="n">
-        <v>450</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -5701,18 +4243,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+15+Gurugram/@28.4578375,77.0443773,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1902973194b5:0x7d02f6d383fb8a58!8m2!3d28.4578375!4d77.0443773!16s%2Fg%2F11trqkrhym?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G42" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H42" s="9" t="n">
-        <v>2387</v>
-      </c>
-      <c r="I42" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J42" s="9" t="n">
-        <v>2397</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -5739,18 +4269,6 @@
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
-      <c r="G43" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H43" s="9" t="n">
-        <v>2211</v>
-      </c>
-      <c r="I43" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J43" s="9" t="n">
-        <v>2213</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -5777,18 +4295,6 @@
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H44" s="9" t="n">
-        <v>6534</v>
-      </c>
-      <c r="I44" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>6533</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -5819,18 +4325,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+67+Gurugram/@28.3897015,77.0674498,17z/data=!3m1!4b1!4m6!3m5!1s0x390d23d7d3976715:0xb8dc58e2f64d1b2e!8m2!3d28.3897015!4d77.0674498!16s%2Fg%2F11h7ksct1w?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G45" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H45" s="9" t="n">
-        <v>1108</v>
-      </c>
-      <c r="I45" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J45" s="9" t="n">
-        <v>1108</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -5861,18 +4355,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sohna+Road+Gurugram/@28.4253629,77.0390099,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1875d4418c91:0x3b4b144484bee44a!8m2!3d28.4253629!4d77.0390099!16s%2Fg%2F1wj_4f0r?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G46" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H46" s="9" t="n">
-        <v>7162</v>
-      </c>
-      <c r="I46" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J46" s="9" t="n">
-        <v>7147</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -5899,18 +4381,6 @@
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H47" s="9" t="n">
-        <v>15774</v>
-      </c>
-      <c r="I47" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J47" s="9" t="n">
-        <v>15771</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -5937,18 +4407,6 @@
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H48" s="9" t="n">
-        <v>3661</v>
-      </c>
-      <c r="I48" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J48" s="9" t="n">
-        <v>3667</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -5979,18 +4437,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+80+Gurugram/@28.3766192,76.9593435,17z/data=!3m1!4b1!4m6!3m5!1s0x390d3da30c57ee59:0x82d80073b91470fc!8m2!3d28.3766192!4d76.9593435!16s%2Fg%2F11fhh4ykm5?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G49" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H49" s="9" t="n">
-        <v>2347</v>
-      </c>
-      <c r="I49" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J49" s="9" t="n">
-        <v>2348</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -6017,18 +4463,6 @@
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H50" s="9" t="n">
-        <v>1885</v>
-      </c>
-      <c r="I50" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J50" s="9" t="n">
-        <v>1885</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -6055,18 +4489,6 @@
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H51" s="9" t="n">
-        <v>7229</v>
-      </c>
-      <c r="I51" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J51" s="9" t="n">
-        <v>7230</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -6093,18 +4515,6 @@
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
-      <c r="G52" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H52" s="9" t="n">
-        <v>1693</v>
-      </c>
-      <c r="I52" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J52" s="9" t="n">
-        <v>1694</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -6135,18 +4545,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+18+Noida/@28.5715738,77.3246799,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce44edd59cf9b:0x7abd947a6a0578bf!8m2!3d28.5715738!4d77.3246799!16s%2Fg%2F124sxkwj8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G53" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H53" s="9" t="n">
-        <v>9641</v>
-      </c>
-      <c r="I53" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J53" s="9" t="n">
-        <v>9642</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -6177,18 +4575,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Gaur+City+Mall+Greater+Noida?hl=en</t>
         </is>
       </c>
-      <c r="G54" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H54" s="9" t="n">
-        <v>796</v>
-      </c>
-      <c r="I54" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J54" s="9" t="n">
-        <v>796</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -6215,18 +4601,6 @@
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr"/>
-      <c r="G55" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H55" s="9" t="n">
-        <v>7229</v>
-      </c>
-      <c r="I55" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J55" s="9" t="n">
-        <v>7230</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -6253,18 +4627,6 @@
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H56" s="9" t="n">
-        <v>709</v>
-      </c>
-      <c r="I56" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J56" s="9" t="n">
-        <v>710</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -6295,18 +4657,6 @@
           <t>https://share.google/ROkTSrwbJf84BzhPA</t>
         </is>
       </c>
-      <c r="G57" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H57" s="9" t="n">
-        <v>429</v>
-      </c>
-      <c r="I57" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J57" s="9" t="n">
-        <v>429</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -6337,18 +4687,6 @@
           <t>https://share.google/zdFAyEbaRbQ5k484p</t>
         </is>
       </c>
-      <c r="G58" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H58" s="9" t="n">
-        <v>203</v>
-      </c>
-      <c r="I58" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J58" s="9" t="n">
-        <v>203</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -6379,18 +4717,6 @@
           <t>https://share.google/Lb3nqjJMTsd4B288R</t>
         </is>
       </c>
-      <c r="G59" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H59" s="9" t="n">
-        <v>656</v>
-      </c>
-      <c r="I59" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J59" s="9" t="n">
-        <v>657</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -6421,18 +4747,6 @@
           <t>https://share.google/UhwDLEldKfKeeOvuF</t>
         </is>
       </c>
-      <c r="G60" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H60" s="9" t="n">
-        <v>360</v>
-      </c>
-      <c r="I60" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J60" s="9" t="n">
-        <v>361</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -6463,18 +4777,6 @@
           <t>https://share.google/y3qxY9okUtRY9qT5G</t>
         </is>
       </c>
-      <c r="G61" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H61" s="9" t="n">
-        <v>2891</v>
-      </c>
-      <c r="I61" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J61" s="9" t="n">
-        <v>2892</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -6505,18 +4807,6 @@
           <t>https://share.google/6IsINvdHSLIIHkIhQ</t>
         </is>
       </c>
-      <c r="G62" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H62" s="9" t="n">
-        <v>583</v>
-      </c>
-      <c r="I62" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J62" s="9" t="n">
-        <v>583</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -6547,18 +4837,6 @@
           <t>https://share.google/dyEWjeSFB5bMuBtCr</t>
         </is>
       </c>
-      <c r="G63" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H63" s="9" t="n">
-        <v>9251</v>
-      </c>
-      <c r="I63" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J63" s="9" t="n">
-        <v>9253</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -6589,18 +4867,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Gaur+Biz+Park+Gaziabad?hl=en</t>
         </is>
       </c>
-      <c r="G64" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H64" s="9" t="n">
-        <v>1005</v>
-      </c>
-      <c r="I64" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J64" s="9" t="n">
-        <v>1006</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -6631,18 +4897,6 @@
           <t>https://www.google.com/maps/place/Plot+No.+12,+Bikanervala+%7C+Rajendra+Nagar,+Sahibabad,,+Rajender+Nagar,+Sector+5,+Rajendra+Nagar,+Sahibabad,+Ghaziabad,+Uttar+Pradesh+201005/@28.6780951,77.3592434,16z/data=!4m6!3m5!1s0x390cfa8b972e5a11:0x42944ce5f6223fbd!8m2!3d28.6780951!4d77.3592434!16s%2Fg%2F11b6gg2nvh?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
-      <c r="G65" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H65" s="9" t="n">
-        <v>3846</v>
-      </c>
-      <c r="I65" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J65" s="9" t="n">
-        <v>3846</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -6673,18 +4927,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Choudhary+More+Ghaziabad/@28.656764,77.4343384,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf1cfc180871d:0x5aa84735b213aa6a!8m2!3d28.656764!4d77.4343384!16s%2Fg%2F11clr_s4v9?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G66" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H66" s="9" t="n">
-        <v>4137</v>
-      </c>
-      <c r="I66" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J66" s="9" t="n">
-        <v>4137</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -6711,18 +4953,6 @@
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
-      <c r="G67" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H67" s="9" t="n">
-        <v>10337</v>
-      </c>
-      <c r="I67" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J67" s="9" t="n">
-        <v>10342</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -6749,18 +4979,6 @@
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
-      <c r="G68" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H68" s="9" t="n">
-        <v>4287</v>
-      </c>
-      <c r="I68" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J68" s="9" t="n">
-        <v>4292</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -6787,18 +5005,6 @@
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr"/>
-      <c r="G69" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H69" s="9" t="n">
-        <v>2202</v>
-      </c>
-      <c r="I69" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J69" s="9" t="n">
-        <v>2204</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -6829,18 +5035,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+KW+Delhi+6/@28.696452,77.4352816,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf15e12b7409f:0x21ba0dd8e12c1453!8m2!3d28.696452!4d77.4352816!16s%2Fg%2F11jzgk44vp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G70" s="9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H70" s="9" t="n">
-        <v>280</v>
-      </c>
-      <c r="I70" s="9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J70" s="9" t="n">
-        <v>280</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -6871,18 +5065,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Modinagar/@28.8133765,77.5519765,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf5b71abce455:0xfc2ef5a0bb38f92!8m2!3d28.8133765!4d77.5519765!16s%2Fg%2F11ghftj4c1?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G71" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H71" s="9" t="n">
-        <v>6139</v>
-      </c>
-      <c r="I71" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J71" s="9" t="n">
-        <v>6141</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -6909,18 +5091,6 @@
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr"/>
-      <c r="G72" s="9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H72" s="9" t="n">
-        <v>3743</v>
-      </c>
-      <c r="I72" s="9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J72" s="9" t="n">
-        <v>3744</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -6947,18 +5117,6 @@
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
-      <c r="G73" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H73" s="9" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I73" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J73" s="9" t="n">
-        <v>1101</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -6989,18 +5147,6 @@
           <t>https://www.google.com/maps/place/Bikanervala/@17.4003058,78.4774782,17z/data=!3m1!4b1!4m6!3m5!1s0x3bcb99dde5faac85:0xc52bb5f5f9e7c58a!8m2!3d17.4003058!4d78.4774782!16s%2Fg%2F11bxc61jfn?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G74" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H74" s="9" t="n">
-        <v>9514</v>
-      </c>
-      <c r="I74" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J74" s="9" t="n">
-        <v>9514</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -7027,18 +5173,6 @@
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
-      <c r="G75" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H75" s="9" t="n">
-        <v>16965</v>
-      </c>
-      <c r="I75" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J75" s="9" t="n">
-        <v>16966</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -7069,18 +5203,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Kothaguda+Hyderabad/@17.4580231,78.3731827,17z/data=!3m1!4b1!4m6!3m5!1s0x3bcb93cbab4eb893:0x81f819feba8d556b!8m2!3d17.4580231!4d78.3731827!16s%2Fg%2F11fkvr28k6?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G76" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H76" s="9" t="n">
-        <v>8556</v>
-      </c>
-      <c r="I76" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J76" s="9" t="n">
-        <v>8557</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -7111,18 +5233,6 @@
           <t>https://www.google.com/maps/place/Bikanervala/@26.7851067,80.9918353,17z/data=!3m1!4b1!4m6!3m5!1s0x399be30647fd426d:0xd01584f16db3efe3!8m2!3d26.7851067!4d80.9918353!16s%2Fg%2F11jsr96pd9?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G77" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H77" s="9" t="n">
-        <v>2436</v>
-      </c>
-      <c r="I77" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J77" s="9" t="n">
-        <v>2441</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -7149,18 +5259,6 @@
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr"/>
-      <c r="G78" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H78" s="9" t="n">
-        <v>111</v>
-      </c>
-      <c r="I78" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J78" s="9" t="n">
-        <v>111</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -7191,18 +5289,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Emerald+Mall+Lucknow/@26.7879677,80.9106156,17z/data=!3m1!4b1!4m6!3m5!1s0x399bfda33d9b4ed1:0x4bc0f33320d7156b!8m2!3d26.7879677!4d80.9106156!16s%2Fg%2F11vs2f1qpf?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G79" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H79" s="9" t="n">
-        <v>175</v>
-      </c>
-      <c r="I79" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J79" s="9" t="n">
-        <v>175</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -7229,18 +5315,6 @@
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr"/>
-      <c r="G80" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H80" s="9" t="n">
-        <v>1478</v>
-      </c>
-      <c r="I80" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J80" s="9" t="n">
-        <v>1483</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -7267,26 +5341,6 @@
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr"/>
-      <c r="G81" s="10" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="J81" s="10" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -7313,18 +5367,6 @@
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
-      <c r="G82" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H82" s="9" t="n">
-        <v>1419</v>
-      </c>
-      <c r="I82" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J82" s="9" t="n">
-        <v>1420</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -7351,18 +5393,6 @@
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
-      <c r="G83" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H83" s="9" t="n">
-        <v>209</v>
-      </c>
-      <c r="I83" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J83" s="9" t="n">
-        <v>209</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -7389,18 +5419,6 @@
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr"/>
-      <c r="G84" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H84" s="9" t="n">
-        <v>287</v>
-      </c>
-      <c r="I84" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J84" s="9" t="n">
-        <v>289</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -7427,18 +5445,6 @@
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr"/>
-      <c r="G85" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H85" s="9" t="n">
-        <v>3934</v>
-      </c>
-      <c r="I85" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J85" s="9" t="n">
-        <v>3941</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -7465,18 +5471,6 @@
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr"/>
-      <c r="G86" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H86" s="9" t="n">
-        <v>467</v>
-      </c>
-      <c r="I86" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J86" s="9" t="n">
-        <v>469</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -7503,18 +5497,6 @@
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr"/>
-      <c r="G87" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H87" s="9" t="n">
-        <v>5254</v>
-      </c>
-      <c r="I87" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J87" s="9" t="n">
-        <v>5257</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -7541,18 +5523,6 @@
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr"/>
-      <c r="G88" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H88" s="9" t="n">
-        <v>119</v>
-      </c>
-      <c r="I88" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J88" s="9" t="n">
-        <v>119</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -7579,18 +5549,6 @@
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr"/>
-      <c r="G89" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H89" s="9" t="n">
-        <v>8385</v>
-      </c>
-      <c r="I89" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J89" s="9" t="n">
-        <v>8385</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -7617,18 +5575,6 @@
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr"/>
-      <c r="G90" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H90" s="9" t="n">
-        <v>3592</v>
-      </c>
-      <c r="I90" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J90" s="9" t="n">
-        <v>3604</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -7655,18 +5601,6 @@
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr"/>
-      <c r="G91" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H91" s="9" t="n">
-        <v>3220</v>
-      </c>
-      <c r="I91" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J91" s="9" t="n">
-        <v>3227</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -7693,18 +5627,6 @@
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr"/>
-      <c r="G92" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H92" s="9" t="n">
-        <v>2878</v>
-      </c>
-      <c r="I92" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J92" s="9" t="n">
-        <v>2878</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -7731,18 +5653,6 @@
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr"/>
-      <c r="G93" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H93" s="9" t="n">
-        <v>3770</v>
-      </c>
-      <c r="I93" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J93" s="9" t="n">
-        <v>3770</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -7769,18 +5679,6 @@
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr"/>
-      <c r="G94" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H94" s="9" t="n">
-        <v>1623</v>
-      </c>
-      <c r="I94" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J94" s="9" t="n">
-        <v>1623</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -7807,18 +5705,6 @@
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr"/>
-      <c r="G95" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H95" s="9" t="n">
-        <v>7493</v>
-      </c>
-      <c r="I95" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J95" s="9" t="n">
-        <v>7494</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -7845,18 +5731,6 @@
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr"/>
-      <c r="G96" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H96" s="9" t="n">
-        <v>2835</v>
-      </c>
-      <c r="I96" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J96" s="9" t="n">
-        <v>2835</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -7883,18 +5757,6 @@
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr"/>
-      <c r="G97" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H97" s="9" t="n">
-        <v>2870</v>
-      </c>
-      <c r="I97" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J97" s="9" t="n">
-        <v>2887</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -7921,18 +5783,6 @@
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr"/>
-      <c r="G98" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H98" s="9" t="n">
-        <v>91</v>
-      </c>
-      <c r="I98" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J98" s="9" t="n">
-        <v>91</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -7959,18 +5809,6 @@
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr"/>
-      <c r="G99" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H99" s="9" t="n">
-        <v>1689</v>
-      </c>
-      <c r="I99" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J99" s="9" t="n">
-        <v>1689</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -7997,18 +5835,6 @@
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr"/>
-      <c r="G100" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H100" s="9" t="n">
-        <v>2197</v>
-      </c>
-      <c r="I100" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J100" s="9" t="n">
-        <v>2202</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -8035,18 +5861,6 @@
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr"/>
-      <c r="G101" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H101" s="9" t="n">
-        <v>288</v>
-      </c>
-      <c r="I101" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J101" s="9" t="n">
-        <v>288</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -8073,18 +5887,6 @@
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr"/>
-      <c r="G102" s="9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H102" s="9" t="n">
-        <v>75</v>
-      </c>
-      <c r="I102" s="9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J102" s="9" t="n">
-        <v>75</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -8111,18 +5913,6 @@
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr"/>
-      <c r="G103" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H103" s="9" t="n">
-        <v>848</v>
-      </c>
-      <c r="I103" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J103" s="9" t="n">
-        <v>853</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -8149,18 +5939,6 @@
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr"/>
-      <c r="G104" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H104" s="9" t="n">
-        <v>427</v>
-      </c>
-      <c r="I104" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J104" s="9" t="n">
-        <v>427</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -8187,18 +5965,6 @@
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr"/>
-      <c r="G105" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H105" s="9" t="n">
-        <v>883</v>
-      </c>
-      <c r="I105" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J105" s="9" t="n">
-        <v>885</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -8225,18 +5991,6 @@
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
-      <c r="G106" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H106" s="9" t="n">
-        <v>454</v>
-      </c>
-      <c r="I106" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J106" s="9" t="n">
-        <v>456</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -8263,18 +6017,6 @@
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr"/>
-      <c r="G107" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H107" s="9" t="n">
-        <v>1517</v>
-      </c>
-      <c r="I107" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J107" s="9" t="n">
-        <v>1517</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -8301,18 +6043,6 @@
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
-      <c r="G108" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H108" s="9" t="n">
-        <v>1864</v>
-      </c>
-      <c r="I108" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J108" s="9" t="n">
-        <v>1864</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -8339,18 +6069,6 @@
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr"/>
-      <c r="G109" s="9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H109" s="9" t="n">
-        <v>64</v>
-      </c>
-      <c r="I109" s="9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J109" s="9" t="n">
-        <v>64</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8363,8 +6081,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:F68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -8380,18 +6098,6 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="G1" s="6" t="n">
-        <v>46300</v>
-      </c>
-      <c r="H1" s="6" t="n">
-        <v>46300</v>
-      </c>
-      <c r="I1" s="6" t="n">
-        <v>46301</v>
-      </c>
-      <c r="J1" s="6" t="n">
-        <v>46301</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -8422,26 +6128,6 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>Review Count</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -8474,18 +6160,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Karama+%7C+Indian+Vegetarian+Restaurant+in+Dubai+-+4B+St+-+Sheikh+Khalifa+Bin+Zayed+St+-+behind+Park+Regis+Kris+Kin+Hotel+-+Al+Karama+-+Dubai+-+United+Arab+Emirates/@25.2487074,55.3022648,16z/data=!4m6!3m5!1s0x3e5f43263a32659d:0x3e7a496c31265a14!8m2!3d25.2487074!4d55.3022648!16s%2Fg%2F11fkl98x2w?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
-      <c r="G3" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>6982</v>
-      </c>
-      <c r="I3" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>6984</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -8516,18 +6190,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Barsha+Heights+Dubai?hl=en</t>
         </is>
       </c>
-      <c r="G4" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>1718</v>
-      </c>
-      <c r="I4" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>1722</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -8558,18 +6220,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Barsha+1+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1159702,55.2049553,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6bc01e76ba11:0x4fd1a9f4b2e6f5e3!8m2!3d25.1159702!4d55.2049553!16s%2Fg%2F1hhn4cw5b?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G5" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>3415</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>3416</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -8600,18 +6250,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Arjan+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.0611644,55.2416108,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6f3d18bbdbdd:0xf394598ae51611cd!8m2!3d25.0611644!4d55.2416108!16s%2Fg%2F11k4t6j5kj?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G6" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>1348</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>1348</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -8642,18 +6280,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Dubai+Hills+Mall+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1000884,55.2380841,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6ffb10c94323:0xe15233cd12b4c95e!8m2!3d25.1000884!4d55.2380841!16s%2Fg%2F11srb65qdy?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>1109</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>1110</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -8684,18 +6310,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Sheikh+Zayed+Road+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2287901,55.2861116,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43aad3d78e71:0xb8b194cb916fd9b0!8m2!3d25.2287901!4d55.2861116!16s%2Fg%2F11spn08t8p?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G8" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>3363</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>3365</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -8726,18 +6340,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Gold+Souk+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2720383,55.2977013,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43768964654b:0xc11f03b76b0ba714!8m2!3d25.2720383!4d55.2977013!16s%2Fg%2F11sqkp7mp7?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G9" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>1970</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>1970</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -8768,18 +6370,6 @@
           <t>https://www.google.com/maps/place/Bikanervala/@25.1971872,55.2793099,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43291308afa5:0xe48b7db44021ad9d!8m2!3d25.1971872!4d55.2793099!16s%2Fg%2F11h_6kxb_4?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G10" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>1195</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>1196</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -8810,18 +6400,6 @@
           <t>https://www.google.com/maps/place/Bikanervala/@25.0443703,55.2301107,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6fbad2abf81f:0x2b8744ab6a1bf442!8m2!3d25.0443703!4d55.2301107!16s%2Fg%2F11wqdtyl9k?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G11" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>812</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>812</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -8848,18 +6426,6 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>3415</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>3416</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -8890,18 +6456,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Jumeirah+3+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1568314,55.2048822,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6bf2c1bdccc9:0x43c26854ab27ef01!8m2!3d25.1568314!4d55.2048822!16s%2Fg%2F11s5twnr34?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G13" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>406</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>406</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -8932,18 +6486,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Furjan+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.0253394,55.1523478,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6d3bc9bcdbdb:0xe6f0ccdcb4b1e8ab!8m2!3d25.0253394!4d55.1523478!16s%2Fg%2F11g8kr7p26?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G14" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>3447</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>3449</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -8974,18 +6516,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+International+City+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1587461,55.4044494,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6152822cefa7:0x62485254b618ad37!8m2!3d25.1587461!4d55.4044494!16s%2Fg%2F11fy4nt_fh?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G15" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <v>1986</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>1986</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -9016,18 +6546,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Ghurair+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.268832,55.3167197,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f432a6356bd7d:0x6e8727a69863a0ea!8m2!3d25.268832!4d55.3167197!16s%2Fg%2F11gj4q5yml?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G16" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>1338</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>1338</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -9058,18 +6576,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Business+Bay+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1907081,55.2657305,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f69d43a494553:0xcae55dd8d4af25bc!8m2!3d25.1907081!4d55.2657305!16s%2Fg%2F11cnch2xjh?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G17" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>1329</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>1332</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -9100,18 +6606,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Abu+Dhabi+%7C+Indian+Vegetarian+Restaurant+in+Abu+Dhabi/@24.4787181,54.3632708,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5e6797000fef8b:0x252e9c63c8d0f687!8m2!3d24.4787181!4d54.3632708!16s%2Fg%2F11j3jt3jck?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G18" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>4495</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>4495</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -9142,18 +6636,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Qusais+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2779484,55.362064,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f5c5ef14f580b:0x42f37dd66cc3bd09!8m2!3d25.2779484!4d55.362064!16s%2Fg%2F11bbwn_ftp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G19" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>1660</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>1663</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -9184,18 +6666,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Hounslow/@51.4697256,-0.3575675,17z/data=!3m1!4b1!4m6!3m5!1s0x48760db0ad77af37:0x259004b7a001719e!8m2!3d51.4697256!4d-0.3575675!16s%2Fg%2F11lw2pkxzp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G20" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>4366</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>4369</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -9222,18 +6692,6 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>3833</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>3847</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -9260,18 +6718,6 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>86</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>86</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -9298,18 +6744,6 @@
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>443</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>443</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -9336,18 +6770,6 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>1684</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>1684</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -9374,18 +6796,6 @@
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H25" s="9" t="n">
-        <v>3362</v>
-      </c>
-      <c r="I25" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J25" s="9" t="n">
-        <v>3363</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -9412,18 +6822,6 @@
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H26" s="9" t="n">
-        <v>1767</v>
-      </c>
-      <c r="I26" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J26" s="9" t="n">
-        <v>1767</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -9450,18 +6848,6 @@
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>530</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>530</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -9488,18 +6874,6 @@
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H28" s="9" t="n">
-        <v>1325</v>
-      </c>
-      <c r="I28" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J28" s="9" t="n">
-        <v>1325</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -9526,18 +6900,6 @@
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>638</v>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J29" s="9" t="n">
-        <v>641</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -9564,18 +6926,6 @@
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H30" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J30" s="9" t="n">
-        <v>35</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -9602,18 +6952,6 @@
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H31" s="9" t="n">
-        <v>1323</v>
-      </c>
-      <c r="I31" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>1323</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -9640,18 +6978,6 @@
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>1427</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>1427</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -9678,18 +7004,6 @@
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr"/>
-      <c r="G33" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>1334</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>1334</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -9716,18 +7030,6 @@
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H34" s="9" t="n">
-        <v>186</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>186</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -9754,18 +7056,6 @@
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>127</v>
-      </c>
-      <c r="I35" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J35" s="9" t="n">
-        <v>127</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -9792,18 +7082,6 @@
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H36" s="9" t="n">
-        <v>993</v>
-      </c>
-      <c r="I36" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>994</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -9830,18 +7108,6 @@
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr"/>
-      <c r="G37" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H37" s="9" t="n">
-        <v>205</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>205</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -9868,18 +7134,6 @@
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H38" s="9" t="n">
-        <v>211</v>
-      </c>
-      <c r="I38" s="9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>211</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -9906,18 +7160,6 @@
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>853</v>
-      </c>
-      <c r="I39" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J39" s="9" t="n">
-        <v>854</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -9944,18 +7186,6 @@
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H40" s="9" t="n">
-        <v>2234</v>
-      </c>
-      <c r="I40" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J40" s="9" t="n">
-        <v>2234</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -9982,18 +7212,6 @@
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H41" s="9" t="n">
-        <v>450</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J41" s="9" t="n">
-        <v>450</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -10020,18 +7238,6 @@
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H42" s="9" t="n">
-        <v>1581</v>
-      </c>
-      <c r="I42" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J42" s="9" t="n">
-        <v>1582</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -10058,18 +7264,6 @@
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
-      <c r="G43" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H43" s="9" t="n">
-        <v>1165</v>
-      </c>
-      <c r="I43" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J43" s="9" t="n">
-        <v>1165</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -10096,18 +7290,6 @@
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H44" s="9" t="n">
-        <v>474</v>
-      </c>
-      <c r="I44" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>474</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -10134,18 +7316,6 @@
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H45" s="9" t="n">
-        <v>370</v>
-      </c>
-      <c r="I45" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J45" s="9" t="n">
-        <v>370</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -10172,18 +7342,6 @@
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H46" s="9" t="n">
-        <v>937</v>
-      </c>
-      <c r="I46" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J46" s="9" t="n">
-        <v>1042</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -10210,18 +7368,6 @@
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H47" s="9" t="n">
-        <v>2566</v>
-      </c>
-      <c r="I47" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J47" s="9" t="n">
-        <v>2567</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -10248,18 +7394,6 @@
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H48" s="9" t="n">
-        <v>1429</v>
-      </c>
-      <c r="I48" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J48" s="9" t="n">
-        <v>1429</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -10286,18 +7420,6 @@
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H49" s="9" t="n">
-        <v>1417</v>
-      </c>
-      <c r="I49" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J49" s="9" t="n">
-        <v>1420</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -10324,18 +7446,6 @@
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H50" s="9" t="n">
-        <v>1549</v>
-      </c>
-      <c r="I50" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J50" s="9" t="n">
-        <v>1550</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -10362,18 +7472,6 @@
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H51" s="9" t="n">
-        <v>2807</v>
-      </c>
-      <c r="I51" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J51" s="9" t="n">
-        <v>2806</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -10400,18 +7498,6 @@
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
-      <c r="G52" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H52" s="9" t="n">
-        <v>742</v>
-      </c>
-      <c r="I52" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J52" s="9" t="n">
-        <v>742</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -10438,18 +7524,6 @@
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr"/>
-      <c r="G53" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H53" s="9" t="n">
-        <v>1224</v>
-      </c>
-      <c r="I53" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J53" s="9" t="n">
-        <v>1226</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -10476,18 +7550,6 @@
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H54" s="9" t="n">
-        <v>673</v>
-      </c>
-      <c r="I54" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J54" s="9" t="n">
-        <v>673</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -10514,18 +7576,6 @@
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr"/>
-      <c r="G55" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H55" s="9" t="n">
-        <v>420</v>
-      </c>
-      <c r="I55" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J55" s="9" t="n">
-        <v>422</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -10772,8 +7822,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:F113"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -10789,18 +7839,6 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="G1" s="6" t="n">
-        <v>46300</v>
-      </c>
-      <c r="H1" s="6" t="n">
-        <v>46300</v>
-      </c>
-      <c r="I1" s="6" t="n">
-        <v>46301</v>
-      </c>
-      <c r="J1" s="6" t="n">
-        <v>46301</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -10831,26 +7869,6 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>Review Count</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -10879,18 +7897,6 @@
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>4571</v>
-      </c>
-      <c r="I3" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>4576</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -10917,18 +7923,6 @@
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>1228</v>
-      </c>
-      <c r="I4" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>1229</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -10955,18 +7949,6 @@
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>460</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>460</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -10993,18 +7975,6 @@
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>11588</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>11588</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -11031,18 +8001,6 @@
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>2050</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>2050</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -11069,18 +8027,6 @@
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>917</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>918</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -11107,18 +8053,6 @@
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>1604</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>1604</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -11145,18 +8079,6 @@
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>1994</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>2023</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -11183,18 +8105,6 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>3082</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>3082</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -11221,18 +8131,6 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>3624</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>3624</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -11259,18 +8157,6 @@
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>21261</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>21263</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -11297,18 +8183,6 @@
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>2945</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>2945</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -11335,18 +8209,6 @@
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <v>4200</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>4202</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -11373,18 +8235,6 @@
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>2387</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>2387</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -11411,18 +8261,6 @@
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -11449,18 +8287,6 @@
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>12119</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>12119</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -11487,18 +8313,6 @@
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>3076</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>3076</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -11525,18 +8339,6 @@
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>9245</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>9245</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -11563,18 +8365,6 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -11601,18 +8391,6 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>6136</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>6136</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -11639,18 +8417,6 @@
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>1734</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>1729</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -11677,18 +8443,6 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>1060</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>1060</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -11715,18 +8469,6 @@
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H25" s="9" t="n">
-        <v>2052</v>
-      </c>
-      <c r="I25" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J25" s="9" t="n">
-        <v>2053</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -11753,18 +8495,6 @@
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H26" s="9" t="n">
-        <v>2776</v>
-      </c>
-      <c r="I26" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J26" s="9" t="n">
-        <v>2776</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -11791,18 +8521,6 @@
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>11062</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>11066</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -11829,18 +8547,6 @@
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H28" s="9" t="n">
-        <v>5490</v>
-      </c>
-      <c r="I28" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J28" s="9" t="n">
-        <v>5490</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -11867,18 +8573,6 @@
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>4008</v>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J29" s="9" t="n">
-        <v>4008</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -11905,18 +8599,6 @@
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H30" s="9" t="n">
-        <v>1579</v>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J30" s="9" t="n">
-        <v>1579</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -11943,18 +8625,6 @@
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H31" s="9" t="n">
-        <v>1579</v>
-      </c>
-      <c r="I31" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>1579</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -11981,18 +8651,6 @@
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>2808</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>2809</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -12019,18 +8677,6 @@
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr"/>
-      <c r="G33" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>18968</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>18967</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -12057,18 +8703,6 @@
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H34" s="9" t="n">
-        <v>39673</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>39676</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -12095,18 +8729,6 @@
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>5228</v>
-      </c>
-      <c r="I35" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J35" s="9" t="n">
-        <v>5228</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -12133,18 +8755,6 @@
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H36" s="9" t="n">
-        <v>10370</v>
-      </c>
-      <c r="I36" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>10373</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -12171,18 +8781,6 @@
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr"/>
-      <c r="G37" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H37" s="9" t="n">
-        <v>7404</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>7404</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -12209,18 +8807,6 @@
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
-      <c r="G38" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H38" s="9" t="n">
-        <v>539</v>
-      </c>
-      <c r="I38" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>539</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -12247,18 +8833,6 @@
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>1124</v>
-      </c>
-      <c r="I39" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J39" s="9" t="n">
-        <v>1124</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -12285,18 +8859,6 @@
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
-      <c r="G40" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H40" s="9" t="n">
-        <v>539</v>
-      </c>
-      <c r="I40" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J40" s="9" t="n">
-        <v>539</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -12323,18 +8885,6 @@
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
-      <c r="G41" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H41" s="9" t="n">
-        <v>2615</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J41" s="9" t="n">
-        <v>2617</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -12361,18 +8911,6 @@
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H42" s="9" t="n">
-        <v>1441</v>
-      </c>
-      <c r="I42" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J42" s="9" t="n">
-        <v>1442</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -12399,18 +8937,6 @@
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
-      <c r="G43" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H43" s="9" t="n">
-        <v>955</v>
-      </c>
-      <c r="I43" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J43" s="9" t="n">
-        <v>955</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -12437,18 +8963,6 @@
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H44" s="9" t="n">
-        <v>4162</v>
-      </c>
-      <c r="I44" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>4162</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -12475,18 +8989,6 @@
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H45" s="9" t="n">
-        <v>3480</v>
-      </c>
-      <c r="I45" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J45" s="9" t="n">
-        <v>3481</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -12513,18 +9015,6 @@
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H46" s="9" t="n">
-        <v>7884</v>
-      </c>
-      <c r="I46" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J46" s="9" t="n">
-        <v>7886</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -12551,18 +9041,6 @@
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H47" s="9" t="n">
-        <v>6136</v>
-      </c>
-      <c r="I47" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J47" s="9" t="n">
-        <v>6136</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -12589,18 +9067,6 @@
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H48" s="9" t="n">
-        <v>983</v>
-      </c>
-      <c r="I48" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J48" s="9" t="n">
-        <v>983</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -12627,18 +9093,6 @@
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H49" s="9" t="n">
-        <v>3640</v>
-      </c>
-      <c r="I49" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J49" s="9" t="n">
-        <v>3643</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -12665,18 +9119,6 @@
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H50" s="9" t="n">
-        <v>147</v>
-      </c>
-      <c r="I50" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J50" s="9" t="n">
-        <v>168</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -12703,18 +9145,6 @@
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
-      <c r="G51" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H51" s="9" t="n">
-        <v>4116</v>
-      </c>
-      <c r="I51" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J51" s="9" t="n">
-        <v>4119</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -12741,18 +9171,6 @@
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
-      <c r="G52" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H52" s="9" t="n">
-        <v>308</v>
-      </c>
-      <c r="I52" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J52" s="9" t="n">
-        <v>314</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -12779,18 +9197,6 @@
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr"/>
-      <c r="G53" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H53" s="9" t="n">
-        <v>122</v>
-      </c>
-      <c r="I53" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J53" s="9" t="n">
-        <v>135</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -12817,18 +9223,6 @@
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H54" s="9" t="n">
-        <v>4116</v>
-      </c>
-      <c r="I54" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J54" s="9" t="n">
-        <v>4119</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -12855,18 +9249,6 @@
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr"/>
-      <c r="G55" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H55" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="I55" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J55" s="9" t="n">
-        <v>55</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -12893,18 +9275,6 @@
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H56" s="9" t="n">
-        <v>493</v>
-      </c>
-      <c r="I56" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J56" s="9" t="n">
-        <v>492</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -12931,18 +9301,6 @@
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr"/>
-      <c r="G57" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H57" s="9" t="n">
-        <v>7852</v>
-      </c>
-      <c r="I57" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J57" s="9" t="n">
-        <v>7852</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -12969,18 +9327,6 @@
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
-      <c r="G58" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H58" s="9" t="n">
-        <v>4017</v>
-      </c>
-      <c r="I58" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J58" s="9" t="n">
-        <v>4017</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -13007,18 +9353,6 @@
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr"/>
-      <c r="G59" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H59" s="9" t="n">
-        <v>2840</v>
-      </c>
-      <c r="I59" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J59" s="9" t="n">
-        <v>2848</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -13045,18 +9379,6 @@
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr"/>
-      <c r="G60" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H60" s="9" t="n">
-        <v>2251</v>
-      </c>
-      <c r="I60" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J60" s="9" t="n">
-        <v>2251</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -13083,18 +9405,6 @@
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr"/>
-      <c r="G61" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H61" s="9" t="n">
-        <v>7819</v>
-      </c>
-      <c r="I61" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J61" s="9" t="n">
-        <v>7820</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -13121,18 +9431,6 @@
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
-      <c r="G62" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H62" s="9" t="n">
-        <v>3614</v>
-      </c>
-      <c r="I62" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J62" s="9" t="n">
-        <v>3615</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -13159,18 +9457,6 @@
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
-      <c r="G63" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H63" s="9" t="n">
-        <v>4769</v>
-      </c>
-      <c r="I63" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J63" s="9" t="n">
-        <v>4769</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -13197,18 +9483,6 @@
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
-      <c r="G64" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H64" s="9" t="n">
-        <v>2626</v>
-      </c>
-      <c r="I64" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J64" s="9" t="n">
-        <v>2626</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -13235,18 +9509,6 @@
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr"/>
-      <c r="G65" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H65" s="9" t="n">
-        <v>2900</v>
-      </c>
-      <c r="I65" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J65" s="9" t="n">
-        <v>2900</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -13273,18 +9535,6 @@
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr"/>
-      <c r="G66" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H66" s="9" t="n">
-        <v>6441</v>
-      </c>
-      <c r="I66" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J66" s="9" t="n">
-        <v>6444</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -13311,18 +9561,6 @@
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
-      <c r="G67" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H67" s="9" t="n">
-        <v>781</v>
-      </c>
-      <c r="I67" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J67" s="9" t="n">
-        <v>781</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -13349,18 +9587,6 @@
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
-      <c r="G68" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H68" s="9" t="n">
-        <v>19100</v>
-      </c>
-      <c r="I68" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J68" s="9" t="n">
-        <v>19103</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -13387,18 +9613,6 @@
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr"/>
-      <c r="G69" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H69" s="9" t="n">
-        <v>2911</v>
-      </c>
-      <c r="I69" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J69" s="9" t="n">
-        <v>2915</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -13425,18 +9639,6 @@
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr"/>
-      <c r="G70" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H70" s="9" t="n">
-        <v>2629</v>
-      </c>
-      <c r="I70" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J70" s="9" t="n">
-        <v>2629</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -13463,18 +9665,6 @@
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr"/>
-      <c r="G71" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H71" s="9" t="n">
-        <v>1193</v>
-      </c>
-      <c r="I71" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J71" s="9" t="n">
-        <v>1193</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -13501,18 +9691,6 @@
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr"/>
-      <c r="G72" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H72" s="9" t="n">
-        <v>4165</v>
-      </c>
-      <c r="I72" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J72" s="9" t="n">
-        <v>4165</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -13539,18 +9717,6 @@
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
-      <c r="G73" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H73" s="9" t="n">
-        <v>3862</v>
-      </c>
-      <c r="I73" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J73" s="9" t="n">
-        <v>3862</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -13577,18 +9743,6 @@
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr"/>
-      <c r="G74" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H74" s="9" t="n">
-        <v>754</v>
-      </c>
-      <c r="I74" s="9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J74" s="9" t="n">
-        <v>754</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -13615,18 +9769,6 @@
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
-      <c r="G75" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H75" s="9" t="n">
-        <v>4653</v>
-      </c>
-      <c r="I75" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J75" s="9" t="n">
-        <v>4655</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -13653,18 +9795,6 @@
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
-      <c r="G76" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H76" s="9" t="n">
-        <v>5286</v>
-      </c>
-      <c r="I76" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J76" s="9" t="n">
-        <v>5287</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -13691,18 +9821,6 @@
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr"/>
-      <c r="G77" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H77" s="9" t="n">
-        <v>159</v>
-      </c>
-      <c r="I77" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J77" s="9" t="n">
-        <v>159</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -13729,18 +9847,6 @@
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr"/>
-      <c r="G78" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H78" s="9" t="n">
-        <v>1130</v>
-      </c>
-      <c r="I78" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J78" s="9" t="n">
-        <v>1131</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -13767,18 +9873,6 @@
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr"/>
-      <c r="G79" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H79" s="9" t="n">
-        <v>634</v>
-      </c>
-      <c r="I79" s="9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J79" s="9" t="n">
-        <v>634</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -13805,18 +9899,6 @@
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr"/>
-      <c r="G80" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H80" s="9" t="n">
-        <v>1187</v>
-      </c>
-      <c r="I80" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J80" s="9" t="n">
-        <v>1187</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -13843,18 +9925,6 @@
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr"/>
-      <c r="G81" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H81" s="9" t="n">
-        <v>1554</v>
-      </c>
-      <c r="I81" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J81" s="9" t="n">
-        <v>1554</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -13881,18 +9951,6 @@
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
-      <c r="G82" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H82" s="9" t="n">
-        <v>11734</v>
-      </c>
-      <c r="I82" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J82" s="9" t="n">
-        <v>11737</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -13919,18 +9977,6 @@
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
-      <c r="G83" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H83" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="I83" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J83" s="9" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -13957,18 +10003,6 @@
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr"/>
-      <c r="G84" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H84" s="9" t="n">
-        <v>5926</v>
-      </c>
-      <c r="I84" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J84" s="9" t="n">
-        <v>5927</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -13995,18 +10029,6 @@
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr"/>
-      <c r="G85" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H85" s="9" t="n">
-        <v>3258</v>
-      </c>
-      <c r="I85" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J85" s="9" t="n">
-        <v>3259</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -14033,18 +10055,6 @@
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr"/>
-      <c r="G86" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H86" s="9" t="n">
-        <v>10418</v>
-      </c>
-      <c r="I86" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J86" s="9" t="n">
-        <v>10418</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -14071,18 +10081,6 @@
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr"/>
-      <c r="G87" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H87" s="9" t="n">
-        <v>4151</v>
-      </c>
-      <c r="I87" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J87" s="9" t="n">
-        <v>4151</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -14109,18 +10107,6 @@
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr"/>
-      <c r="G88" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H88" s="9" t="n">
-        <v>2998</v>
-      </c>
-      <c r="I88" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J88" s="9" t="n">
-        <v>2998</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -14147,18 +10133,6 @@
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr"/>
-      <c r="G89" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H89" s="9" t="n">
-        <v>1296</v>
-      </c>
-      <c r="I89" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J89" s="9" t="n">
-        <v>1296</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -14185,18 +10159,6 @@
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr"/>
-      <c r="G90" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H90" s="9" t="n">
-        <v>2233</v>
-      </c>
-      <c r="I90" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J90" s="9" t="n">
-        <v>2234</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -14223,18 +10185,6 @@
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr"/>
-      <c r="G91" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H91" s="9" t="n">
-        <v>7974</v>
-      </c>
-      <c r="I91" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J91" s="9" t="n">
-        <v>7975</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -14261,18 +10211,6 @@
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr"/>
-      <c r="G92" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H92" s="9" t="n">
-        <v>784</v>
-      </c>
-      <c r="I92" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J92" s="9" t="n">
-        <v>784</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -14299,18 +10237,6 @@
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr"/>
-      <c r="G93" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H93" s="9" t="n">
-        <v>788</v>
-      </c>
-      <c r="I93" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J93" s="9" t="n">
-        <v>788</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -14337,18 +10263,6 @@
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr"/>
-      <c r="G94" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H94" s="9" t="n">
-        <v>2595</v>
-      </c>
-      <c r="I94" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J94" s="9" t="n">
-        <v>2595</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -14375,18 +10289,6 @@
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr"/>
-      <c r="G95" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H95" s="9" t="n">
-        <v>1677</v>
-      </c>
-      <c r="I95" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J95" s="9" t="n">
-        <v>1677</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -14413,18 +10315,6 @@
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr"/>
-      <c r="G96" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H96" s="9" t="n">
-        <v>6438</v>
-      </c>
-      <c r="I96" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J96" s="9" t="n">
-        <v>6439</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -14451,18 +10341,6 @@
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr"/>
-      <c r="G97" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H97" s="9" t="n">
-        <v>2315</v>
-      </c>
-      <c r="I97" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J97" s="9" t="n">
-        <v>2315</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -14489,18 +10367,6 @@
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr"/>
-      <c r="G98" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H98" s="9" t="n">
-        <v>1933</v>
-      </c>
-      <c r="I98" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J98" s="9" t="n">
-        <v>1937</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -14527,18 +10393,6 @@
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr"/>
-      <c r="G99" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H99" s="9" t="n">
-        <v>5568</v>
-      </c>
-      <c r="I99" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J99" s="9" t="n">
-        <v>5570</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -14565,18 +10419,6 @@
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr"/>
-      <c r="G100" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H100" s="9" t="n">
-        <v>17772</v>
-      </c>
-      <c r="I100" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J100" s="9" t="n">
-        <v>17774</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -14603,18 +10445,6 @@
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr"/>
-      <c r="G101" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H101" s="9" t="n">
-        <v>6151</v>
-      </c>
-      <c r="I101" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J101" s="9" t="n">
-        <v>6160</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -14641,18 +10471,6 @@
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr"/>
-      <c r="G102" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H102" s="9" t="n">
-        <v>5283</v>
-      </c>
-      <c r="I102" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J102" s="9" t="n">
-        <v>5283</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -14679,18 +10497,6 @@
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr"/>
-      <c r="G103" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H103" s="9" t="n">
-        <v>1172</v>
-      </c>
-      <c r="I103" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J103" s="9" t="n">
-        <v>1173</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -14717,18 +10523,6 @@
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr"/>
-      <c r="G104" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H104" s="9" t="n">
-        <v>4076</v>
-      </c>
-      <c r="I104" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J104" s="9" t="n">
-        <v>4076</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -14755,18 +10549,6 @@
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr"/>
-      <c r="G105" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H105" s="9" t="n">
-        <v>1172</v>
-      </c>
-      <c r="I105" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J105" s="9" t="n">
-        <v>1173</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -14793,18 +10575,6 @@
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
-      <c r="G106" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H106" s="9" t="n">
-        <v>10973</v>
-      </c>
-      <c r="I106" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J106" s="9" t="n">
-        <v>10974</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -14831,18 +10601,6 @@
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr"/>
-      <c r="G107" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H107" s="9" t="n">
-        <v>3159</v>
-      </c>
-      <c r="I107" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J107" s="9" t="n">
-        <v>3159</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -14869,18 +10627,6 @@
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
-      <c r="G108" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H108" s="9" t="n">
-        <v>3052</v>
-      </c>
-      <c r="I108" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J108" s="9" t="n">
-        <v>3054</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -14907,18 +10653,6 @@
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr"/>
-      <c r="G109" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H109" s="9" t="n">
-        <v>2619</v>
-      </c>
-      <c r="I109" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J109" s="9" t="n">
-        <v>2620</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
@@ -14945,18 +10679,6 @@
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr"/>
-      <c r="G110" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H110" s="9" t="n">
-        <v>1879</v>
-      </c>
-      <c r="I110" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J110" s="9" t="n">
-        <v>1879</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
@@ -14983,18 +10705,6 @@
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr"/>
-      <c r="G111" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H111" s="9" t="n">
-        <v>1196</v>
-      </c>
-      <c r="I111" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J111" s="9" t="n">
-        <v>1196</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
@@ -15021,18 +10731,6 @@
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr"/>
-      <c r="G112" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H112" s="9" t="n">
-        <v>2446</v>
-      </c>
-      <c r="I112" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J112" s="9" t="n">
-        <v>2449</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
@@ -15059,18 +10757,6 @@
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr"/>
-      <c r="G113" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H113" s="9" t="n">
-        <v>2629</v>
-      </c>
-      <c r="I113" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J113" s="9" t="n">
-        <v>2629</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15083,8 +10769,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -15100,18 +10786,6 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="G1" s="6" t="n">
-        <v>46300</v>
-      </c>
-      <c r="H1" s="6" t="n">
-        <v>46300</v>
-      </c>
-      <c r="I1" s="6" t="n">
-        <v>46301</v>
-      </c>
-      <c r="J1" s="6" t="n">
-        <v>46301</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -15142,26 +10816,6 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>Review Count</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -15190,18 +10844,6 @@
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>14377</v>
-      </c>
-      <c r="I3" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>14377</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -15228,18 +10870,6 @@
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>1198</v>
-      </c>
-      <c r="I4" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>1199</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -15266,18 +10896,6 @@
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="I5" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -15304,18 +10922,6 @@
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>61</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>62</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -15342,18 +10948,6 @@
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>4834</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>4835</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -15380,18 +10974,6 @@
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>2066</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>2067</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -15418,18 +11000,6 @@
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H9" s="9" t="n">
-        <v>5777</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>5777</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -15456,18 +11026,6 @@
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>6553</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>6554</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -15494,18 +11052,6 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>10574</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>10574</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -15532,18 +11078,6 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>12232</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>12233</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -15570,18 +11104,6 @@
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H13" s="9" t="n">
-        <v>10698</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>10698</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -15608,18 +11130,6 @@
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>6808</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>6809</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -15646,18 +11156,6 @@
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H15" s="9" t="n">
-        <v>3601</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>3604</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -15684,18 +11182,6 @@
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>4500</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>4500</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -15722,18 +11208,6 @@
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>876</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>876</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -15760,18 +11234,6 @@
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>19719</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>19723</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -15798,18 +11260,6 @@
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>2017</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>2017</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -15836,18 +11286,6 @@
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H20" s="9" t="n">
-        <v>2015</v>
-      </c>
-      <c r="I20" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>2024</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -15874,18 +11312,6 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H21" s="9" t="n">
-        <v>8779</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>8781</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -15912,18 +11338,6 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>1118</v>
-      </c>
-      <c r="I22" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>1118</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -15950,18 +11364,6 @@
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>676</v>
-      </c>
-      <c r="I23" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>676</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -15988,18 +11390,6 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>1820</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>1820</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bikanervala GGN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="India BV" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="International BV" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haldiram India" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OM Sweets India" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Bikanervala GGN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Competitors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="India BV" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="International BV" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Haldiram India" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="OM Sweets India" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,8 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +41,19 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +64,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -94,6 +131,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,8 +512,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -477,6 +529,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="H1" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -507,6 +565,16 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -539,6 +607,12 @@
           <t>https://share.google/JV7XDH4ryWmQNPfVY</t>
         </is>
       </c>
+      <c r="G3" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>4873</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -569,6 +643,12 @@
           <t>https://share.google/AXcgrOXWWfQtoSOkz</t>
         </is>
       </c>
+      <c r="G4" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>15772</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -599,6 +679,12 @@
           <t>https://share.google/Lq1yf4rveBX5BWyts</t>
         </is>
       </c>
+      <c r="G5" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>5536</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -629,6 +715,12 @@
           <t>https://share.google/5iiO04ZTn35j8E5HB</t>
         </is>
       </c>
+      <c r="G6" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>6534</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -659,6 +751,12 @@
           <t>https://share.google/iNagaqHoCbBOIvV0x</t>
         </is>
       </c>
+      <c r="G7" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>2397</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -689,6 +787,12 @@
           <t>https://share.google/S4Kwkg9xEW0S2j7a0</t>
         </is>
       </c>
+      <c r="G8" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>7147</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -719,6 +823,12 @@
           <t>https://share.google/NS8T7gwZSlKSNr3UP</t>
         </is>
       </c>
+      <c r="G9" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>3664</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -749,6 +859,12 @@
           <t>https://share.google/Xmyef4OwQmXyWCFN0</t>
         </is>
       </c>
+      <c r="G10" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>2781</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -779,6 +895,12 @@
           <t>https://share.google/6khAtgqK72w0kjN0Q</t>
         </is>
       </c>
+      <c r="G11" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>1103</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -809,6 +931,12 @@
           <t>https://share.google/CgukSORsdWkszVRvP</t>
         </is>
       </c>
+      <c r="G12" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>1108</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -839,6 +967,12 @@
           <t>https://share.google/BNfINmH1QbNZhf7ox</t>
         </is>
       </c>
+      <c r="G13" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>2217</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -869,6 +1003,12 @@
           <t>https://share.google/LJxUW77APw08Vr9a0</t>
         </is>
       </c>
+      <c r="G14" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>2348</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -899,6 +1039,12 @@
           <t>https://share.google/LAZMqwdryXVTeQkgt</t>
         </is>
       </c>
+      <c r="G15" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>2588</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -929,6 +1075,12 @@
           <t>https://share.google/lkP8lqhdoKZRzyal3</t>
         </is>
       </c>
+      <c r="G16" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>888</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -959,6 +1111,12 @@
           <t>https://share.google/255ZPlPOiTGMhDzy0</t>
         </is>
       </c>
+      <c r="G17" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>1328</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -989,6 +1147,12 @@
           <t>https://share.google/9TqthrgcK6VnEH9Kh</t>
         </is>
       </c>
+      <c r="G18" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1019,6 +1183,12 @@
           <t>https://share.google/uqXvcL4esuwjgcsRz</t>
         </is>
       </c>
+      <c r="G19" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>928</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1049,6 +1219,12 @@
           <t>https://share.google/E5KGOYYKX6YqD07hf</t>
         </is>
       </c>
+      <c r="G20" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>1097</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1079,6 +1255,12 @@
           <t>https://share.google/ooNGpI4Ewi9Zt5t02</t>
         </is>
       </c>
+      <c r="G21" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>788</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1109,6 +1291,12 @@
           <t>https://share.google/Z2RQtKISxQhQWQSl4</t>
         </is>
       </c>
+      <c r="G22" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>659</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1139,6 +1327,12 @@
           <t>https://share.google/grSJuehxs8v7sVOVt</t>
         </is>
       </c>
+      <c r="G23" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>699</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1169,6 +1363,12 @@
           <t>https://share.google/V1f6JY6CBgPW0eoIg</t>
         </is>
       </c>
+      <c r="G24" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>1428</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1199,6 +1399,12 @@
           <t>https://share.google/r13AfGhfeAFwXti2i</t>
         </is>
       </c>
+      <c r="G25" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>704</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1224,6 +1430,12 @@
         <is>
           <t>https://share.google/e0rEvKWJDcji81RKF</t>
         </is>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -1237,8 +1449,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -1254,6 +1466,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="H1" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1284,6 +1502,16 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -1316,6 +1544,12 @@
           <t>https://share.google/vwJnwPNeUQYJeEduL</t>
         </is>
       </c>
+      <c r="G3" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1338,6 +1572,12 @@
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1368,6 +1608,12 @@
           <t>https://share.google/W7otAdG8FtptbWSwl</t>
         </is>
       </c>
+      <c r="G5" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>3862</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1398,6 +1644,12 @@
           <t>https://share.google/W7otAdG8FtptbWSwl</t>
         </is>
       </c>
+      <c r="G6" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>3862</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1428,6 +1680,12 @@
           <t>https://share.google/Z2RQtKISxQhQWQSl4</t>
         </is>
       </c>
+      <c r="G7" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>659</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1458,6 +1716,12 @@
           <t>https://share.google/lP3zeGY3pdczZ13a6</t>
         </is>
       </c>
+      <c r="G8" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>19723</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1488,6 +1752,12 @@
           <t>https://share.google/lP3zeGY3pdczZ13a6</t>
         </is>
       </c>
+      <c r="G9" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>19723</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1518,6 +1788,12 @@
           <t>https://share.google/lP3zeGY3pdczZ13a6</t>
         </is>
       </c>
+      <c r="G10" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>19723</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1548,6 +1824,12 @@
           <t>https://share.google/z92S6uNfId7gh7xXh</t>
         </is>
       </c>
+      <c r="G11" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1578,6 +1860,12 @@
           <t>https://share.google/z92S6uNfId7gh7xXh</t>
         </is>
       </c>
+      <c r="G12" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1608,6 +1896,12 @@
           <t>https://share.google/76FqjGJdw3pWT7Nhm</t>
         </is>
       </c>
+      <c r="G13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>1820</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1638,6 +1932,12 @@
           <t>https://share.google/76FqjGJdw3pWT7Nhm</t>
         </is>
       </c>
+      <c r="G14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>1820</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1668,6 +1968,12 @@
           <t>https://share.google/76FqjGJdw3pWT7Nhm</t>
         </is>
       </c>
+      <c r="G15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>1820</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1690,6 +1996,12 @@
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1720,6 +2032,12 @@
           <t>https://share.google/76FqjGJdw3pWT7Nhm</t>
         </is>
       </c>
+      <c r="G17" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>1820</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1750,6 +2068,12 @@
           <t>https://share.google/tK0HH6YhuhGFtmkpF</t>
         </is>
       </c>
+      <c r="G18" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>4500</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1780,6 +2104,12 @@
           <t>https://share.google/tK0HH6YhuhGFtmkpF</t>
         </is>
       </c>
+      <c r="G19" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>4500</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1810,6 +2140,12 @@
           <t>https://share.google/Xmyef4OwQmXyWCFN0</t>
         </is>
       </c>
+      <c r="G20" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>2781</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1840,6 +2176,12 @@
           <t>https://share.google/AXcgrOXWWfQtoSOkz</t>
         </is>
       </c>
+      <c r="G21" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>15772</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1870,6 +2212,12 @@
           <t>https://share.google/PJ8dwnAbtWjau9ZuQ</t>
         </is>
       </c>
+      <c r="G22" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>5927</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1900,6 +2248,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+23+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G23" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>10574</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1930,6 +2284,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+31+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G24" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>12233</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1960,6 +2320,12 @@
           <t>https://share.google/Ofv3RzFrXczsACnpP</t>
         </is>
       </c>
+      <c r="G25" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>847</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1990,6 +2356,12 @@
           <t>https://share.google/Ofv3RzFrXczsACnpP</t>
         </is>
       </c>
+      <c r="G26" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>847</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -2020,6 +2392,12 @@
           <t>https://share.google/Ofv3RzFrXczsACnpP</t>
         </is>
       </c>
+      <c r="G27" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>847</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -2050,6 +2428,12 @@
           <t>https://share.google/xPXfeD0V5srbLT4eX</t>
         </is>
       </c>
+      <c r="G28" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>3604</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -2080,6 +2464,12 @@
           <t>https://share.google/xPXfeD0V5srbLT4eX</t>
         </is>
       </c>
+      <c r="G29" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>3604</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -2102,6 +2492,12 @@
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>1156</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -2132,6 +2528,12 @@
           <t>https://share.google/BNfINmH1QbNZhf7ox</t>
         </is>
       </c>
+      <c r="G31" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>2216</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -2162,6 +2564,12 @@
           <t>https://share.google/aK8m7Ox6K0FZJ6Xwu</t>
         </is>
       </c>
+      <c r="G32" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>1043</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -2192,6 +2600,12 @@
           <t>https://share.google/aK8m7Ox6K0FZJ6Xwu</t>
         </is>
       </c>
+      <c r="G33" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>1043</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -2214,6 +2628,12 @@
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>1131</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -2244,6 +2664,12 @@
           <t>https://share.google/7DhqfVESQtmCb7UZh</t>
         </is>
       </c>
+      <c r="G35" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>4836</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -2274,6 +2700,12 @@
           <t>https://share.google/7DhqfVESQtmCb7UZh</t>
         </is>
       </c>
+      <c r="G36" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>4836</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2304,6 +2736,12 @@
           <t>https://share.google/i9dx9ixhDINCZ9YbT</t>
         </is>
       </c>
+      <c r="G37" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>282</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -2334,6 +2772,12 @@
           <t>https://share.google/i9dx9ixhDINCZ9YbT</t>
         </is>
       </c>
+      <c r="G38" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>282</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -2364,6 +2808,12 @@
           <t>https://share.google/LAZMqwdryXVTeQkgt</t>
         </is>
       </c>
+      <c r="G39" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>2588</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2394,6 +2844,12 @@
           <t>https://share.google/9TqthrgcK6VnEH9Kh</t>
         </is>
       </c>
+      <c r="G40" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2424,6 +2880,12 @@
           <t>https://share.google/6khAtgqK72w0kjN0Q</t>
         </is>
       </c>
+      <c r="G41" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>1103</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -2454,6 +2916,12 @@
           <t>https://share.google/Jlgj9CSmiwGBJzq7p</t>
         </is>
       </c>
+      <c r="G42" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>11737</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -2484,6 +2952,12 @@
           <t>https://share.google/Jlgj9CSmiwGBJzq7p</t>
         </is>
       </c>
+      <c r="G43" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>11737</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -2514,6 +2988,12 @@
           <t>https://share.google/EFPYdy3wXu07YRAlK</t>
         </is>
       </c>
+      <c r="G44" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -2544,6 +3024,12 @@
           <t>https://share.google/EFPYdy3wXu07YRAlK</t>
         </is>
       </c>
+      <c r="G45" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -2574,6 +3060,12 @@
           <t>https://share.google/aioloSd77eFIRO9Ok</t>
         </is>
       </c>
+      <c r="G46" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>2002</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -2604,6 +3096,12 @@
           <t>https://share.google/aioloSd77eFIRO9Ok</t>
         </is>
       </c>
+      <c r="G47" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>2002</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -2634,6 +3132,12 @@
           <t>https://share.google/KaiqyN6GtR2mXupJW</t>
         </is>
       </c>
+      <c r="G48" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>1774</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -2664,6 +3168,12 @@
           <t>https://share.google/KaiqyN6GtR2mXupJW</t>
         </is>
       </c>
+      <c r="G49" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>1774</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -2686,6 +3196,12 @@
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -2708,6 +3224,12 @@
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>5927</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -2730,6 +3252,12 @@
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>1554</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -2752,6 +3280,12 @@
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>4655</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -2774,6 +3308,12 @@
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>5287</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -2796,6 +3336,12 @@
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -2818,6 +3364,12 @@
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -2840,6 +3392,12 @@
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>1844</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -2862,6 +3420,12 @@
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>4655</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -2884,6 +3448,12 @@
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>5777</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -2906,6 +3476,12 @@
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>6554</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -2928,6 +3504,12 @@
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H61" s="9" t="n">
+        <v>10698</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -2950,6 +3532,8 @@
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="9" t="n"/>
+      <c r="H62" s="9" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -2972,6 +3556,12 @@
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>876</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -2994,6 +3584,12 @@
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>1199</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -3016,6 +3612,12 @@
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr"/>
+      <c r="G65" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -3038,6 +3640,12 @@
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H66" s="9" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -3060,6 +3668,12 @@
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H67" s="9" t="n">
+        <v>885</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -3082,6 +3696,12 @@
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H68" s="9" t="n">
+        <v>14377</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3094,8 +3714,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F109"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -3111,6 +3731,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="H1" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3141,6 +3767,16 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -3173,6 +3809,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Netaji+Subhash+Place+Delhi,+Shop+No.+01+ITL+Twin+Tower,+Netaji+Subhash+Place,+Pitampura,+New+Delhi,+Delhi+110034/@28.6911987,77.1522225,16z/data=!4m6!3m5!1s0x390d03c155555555:0x5b4d4b46cc7ccd4a!8m2!3d28.6911987!4d77.1522225!16s%2Fg%2F1tfldmlm?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
+      <c r="G3" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>2101</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -3203,6 +3845,12 @@
           <t>https://www.google.com/maps/place/Ground+Floor,+Bikanervala+%7C+Sadar+Bazaar,+Devika+Sadar,+Shop+No.+G+12,+G+14-19+7+G+24+-+44,+Qutab+Rd,+Narain+Market,+Sadar+Bazar,+New+Delhi,+Delhi+110006/@28.6558145,77.2162412,16z/data=!4m6!3m5!1s0x390cfde0b0b14249:0xc8e86801bdd1bfd0!8m2!3d28.6558145!4d77.2162412!16s%2Fg%2F11ksks6gbd?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
+      <c r="G4" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>632</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -3233,6 +3881,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Liberty+Cinema+Karol+Bagh/@28.6606284,77.1876003,17z/data=!3m1!4b1!4m6!3m5!1s0x390d03326d19a899:0xd2fef34572239279!8m2!3d28.6606284!4d77.1876003!16s%2Fg%2F11m5qhcscj?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G5" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>1555</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -3263,6 +3917,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Kalkaji+Metro/@28.5494507,77.259104,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce361d13dfecb:0x11d594dba2638f6d!8m2!3d28.5494507!4d77.259104!16s%2Fg%2F11x72l6mq2?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G6" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -3293,6 +3953,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Lajpat+Nagar+Delhi/@28.5708816,77.2390955,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce252e00cf3fb:0xf48521c45d7cd156!8m2!3d28.5708816!4d77.2390955!16s%2Fg%2F1td_wzrz?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>10884</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -3323,6 +3989,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Defence+Colony+Delhi/@28.5748765,77.2381202,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce3d5f019e1e9:0xa3e490839a38e681!8m2!3d28.5748765!4d77.2381202!16s%2Fg%2F11qb4tsxc0?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G8" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>2937</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -3353,6 +4025,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+East+of+Kailash+Delhi/@28.5587762,77.246459,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce39ca675e7c3:0xbe857ad66d22f2bf!8m2!3d28.5587762!4d77.246459!16s%2Fg%2F11s1qvx_74?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>218</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -3383,6 +4061,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Preet+Vihar+Delhi/@28.6392518,77.2948339,17z/data=!3m1!4b1!4m6!3m5!1s0x390cfb510ec67a93:0xfad0c088f3f91804!8m2!3d28.6392518!4d77.2948339!16s%2Fg%2F1tgnkg53?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G10" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>5139</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -3409,6 +4093,12 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>7305</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -3435,6 +4125,12 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>4873</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -3461,6 +4157,12 @@
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>949</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -3487,6 +4189,12 @@
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>1916</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -3513,6 +4221,12 @@
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>834</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -3539,6 +4253,12 @@
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>3403</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -3565,6 +4285,12 @@
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>5648</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -3591,6 +4317,12 @@
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>4603</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -3617,6 +4349,12 @@
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>5750</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -3643,6 +4381,12 @@
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>8147</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -3669,6 +4413,12 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>6608</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -3695,6 +4445,12 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>6260</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -3725,6 +4481,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Dwarka+Delhi/@28.5966087,77.0417524,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1b72556cb43b:0xdd37fb0751d2b900!8m2!3d28.5966087!4d77.0417524!16s%2Fg%2F11grt4vw5b?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G23" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>6217</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -3751,6 +4513,12 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>4694</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -3777,6 +4545,12 @@
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>6256</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -3803,6 +4577,12 @@
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>1901</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -3829,6 +4609,12 @@
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>8386</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -3855,6 +4641,12 @@
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>233</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -3885,6 +4677,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Chanakyapuri+Delhi/@28.585244,77.19149,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1d7cdedc3389:0x60798b43139c76d3!8m2!3d28.585244!4d77.19149!16s%2Fg%2F1tdvhkdv?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G29" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>8650</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -3911,6 +4709,12 @@
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>2782</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -3941,6 +4745,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+GK-II+Savitri+Cinema+Delhi/@28.5374253,77.2389712,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce22b17e2d781:0x40c5f102209b866c!8m2!3d28.5374253!4d77.2389712!16s%2Fg%2F11cmr0t9q8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G31" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>5575</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -3967,6 +4777,12 @@
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>5537</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -3997,6 +4813,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+57+Gurugram/@28.4161819,77.0849591,17z/data=!3m1!4b1!4m6!3m5!1s0x390d232798684757:0xb380904dacac7eed!8m2!3d28.4161819!4d77.0849591!16s%2Fg%2F11k522rkjz?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G33" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>4873</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -4023,6 +4845,12 @@
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>888</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -4049,6 +4877,12 @@
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>2588</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -4075,6 +4909,12 @@
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>699</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -4105,6 +4945,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+The+Esplanade+Mall+Sector+37+Gurugram/@28.4538074,76.9928507,17z/data=!3m1!4b1!4m6!3m5!1s0x390d171587c41467:0x4070a84c531d04ce!8m2!3d28.4538074!4d76.9928507!16s%2Fg%2F11tggmn3j8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G37" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>1328</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -4131,6 +4977,12 @@
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>1103</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -4157,6 +5009,12 @@
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>510</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -4183,6 +5041,12 @@
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>1097</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -4213,6 +5077,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+62+Gurugram/@28.4014616,77.0852188,17z/data=!3m1!4b1!4m6!3m5!1s0x390d23dcf278418d:0x4d1e11be0af4d661!8m2!3d28.4014616!4d77.0852188!16s%2Fg%2F11h7qrpfv4?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G41" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -4243,6 +5113,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+15+Gurugram/@28.4578375,77.0443773,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1902973194b5:0x7d02f6d383fb8a58!8m2!3d28.4578375!4d77.0443773!16s%2Fg%2F11trqkrhym?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G42" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>2397</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -4269,6 +5145,12 @@
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>2216</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -4295,6 +5177,12 @@
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>6533</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -4325,6 +5213,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+67+Gurugram/@28.3897015,77.0674498,17z/data=!3m1!4b1!4m6!3m5!1s0x390d23d7d3976715:0xb8dc58e2f64d1b2e!8m2!3d28.3897015!4d77.0674498!16s%2Fg%2F11h7ksct1w?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G45" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>1108</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -4355,6 +5249,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sohna+Road+Gurugram/@28.4253629,77.0390099,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1875d4418c91:0x3b4b144484bee44a!8m2!3d28.4253629!4d77.0390099!16s%2Fg%2F1wj_4f0r?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G46" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>7146</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -4381,6 +5281,12 @@
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>15772</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -4407,6 +5313,12 @@
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>3664</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -4437,6 +5349,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+80+Gurugram/@28.3766192,76.9593435,17z/data=!3m1!4b1!4m6!3m5!1s0x390d3da30c57ee59:0x82d80073b91470fc!8m2!3d28.3766192!4d76.9593435!16s%2Fg%2F11fhh4ykm5?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G49" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>2348</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -4463,6 +5381,12 @@
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>1885</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -4489,6 +5413,12 @@
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>7230</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -4515,6 +5445,12 @@
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>1694</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -4545,6 +5481,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+18+Noida/@28.5715738,77.3246799,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce44edd59cf9b:0x7abd947a6a0578bf!8m2!3d28.5715738!4d77.3246799!16s%2Fg%2F124sxkwj8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G53" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>9642</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -4575,6 +5517,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Gaur+City+Mall+Greater+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G54" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>796</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -4601,6 +5549,12 @@
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>7230</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -4627,6 +5581,12 @@
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>710</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -4657,6 +5617,12 @@
           <t>https://share.google/ROkTSrwbJf84BzhPA</t>
         </is>
       </c>
+      <c r="G57" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>429</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -4687,6 +5653,12 @@
           <t>https://share.google/zdFAyEbaRbQ5k484p</t>
         </is>
       </c>
+      <c r="G58" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>203</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -4717,6 +5689,12 @@
           <t>https://share.google/Lb3nqjJMTsd4B288R</t>
         </is>
       </c>
+      <c r="G59" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>657</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -4747,6 +5725,12 @@
           <t>https://share.google/UhwDLEldKfKeeOvuF</t>
         </is>
       </c>
+      <c r="G60" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>361</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -4777,6 +5761,12 @@
           <t>https://share.google/y3qxY9okUtRY9qT5G</t>
         </is>
       </c>
+      <c r="G61" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H61" s="9" t="n">
+        <v>2894</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -4807,6 +5797,12 @@
           <t>https://share.google/6IsINvdHSLIIHkIhQ</t>
         </is>
       </c>
+      <c r="G62" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H62" s="9" t="n">
+        <v>583</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -4837,6 +5833,12 @@
           <t>https://share.google/dyEWjeSFB5bMuBtCr</t>
         </is>
       </c>
+      <c r="G63" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>9253</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -4867,6 +5869,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Gaur+Biz+Park+Gaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G64" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>1006</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -4897,6 +5905,12 @@
           <t>https://www.google.com/maps/place/Plot+No.+12,+Bikanervala+%7C+Rajendra+Nagar,+Sahibabad,,+Rajender+Nagar,+Sector+5,+Rajendra+Nagar,+Sahibabad,+Ghaziabad,+Uttar+Pradesh+201005/@28.6780951,77.3592434,16z/data=!4m6!3m5!1s0x390cfa8b972e5a11:0x42944ce5f6223fbd!8m2!3d28.6780951!4d77.3592434!16s%2Fg%2F11b6gg2nvh?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
+      <c r="G65" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>3846</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -4927,6 +5941,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Choudhary+More+Ghaziabad/@28.656764,77.4343384,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf1cfc180871d:0x5aa84735b213aa6a!8m2!3d28.656764!4d77.4343384!16s%2Fg%2F11clr_s4v9?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G66" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H66" s="9" t="n">
+        <v>4137</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -4953,6 +5973,12 @@
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H67" s="9" t="n">
+        <v>10344</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -4979,6 +6005,12 @@
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H68" s="9" t="n">
+        <v>4292</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -5005,6 +6037,12 @@
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr"/>
+      <c r="G69" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H69" s="9" t="n">
+        <v>2204</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -5035,6 +6073,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+KW+Delhi+6/@28.696452,77.4352816,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf15e12b7409f:0x21ba0dd8e12c1453!8m2!3d28.696452!4d77.4352816!16s%2Fg%2F11jzgk44vp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G70" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H70" s="9" t="n">
+        <v>280</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -5065,6 +6109,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Modinagar/@28.8133765,77.5519765,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf5b71abce455:0xfc2ef5a0bb38f92!8m2!3d28.8133765!4d77.5519765!16s%2Fg%2F11ghftj4c1?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G71" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H71" s="9" t="n">
+        <v>6141</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -5091,6 +6141,12 @@
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H72" s="9" t="n">
+        <v>3744</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -5117,6 +6173,12 @@
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
+      <c r="G73" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H73" s="9" t="n">
+        <v>1101</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -5147,6 +6209,12 @@
           <t>https://www.google.com/maps/place/Bikanervala/@17.4003058,78.4774782,17z/data=!3m1!4b1!4m6!3m5!1s0x3bcb99dde5faac85:0xc52bb5f5f9e7c58a!8m2!3d17.4003058!4d78.4774782!16s%2Fg%2F11bxc61jfn?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G74" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H74" s="9" t="n">
+        <v>9514</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -5173,6 +6241,12 @@
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
+      <c r="G75" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H75" s="9" t="n">
+        <v>16966</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -5203,6 +6277,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Kothaguda+Hyderabad/@17.4580231,78.3731827,17z/data=!3m1!4b1!4m6!3m5!1s0x3bcb93cbab4eb893:0x81f819feba8d556b!8m2!3d17.4580231!4d78.3731827!16s%2Fg%2F11fkvr28k6?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G76" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H76" s="9" t="n">
+        <v>8557</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -5233,6 +6313,12 @@
           <t>https://www.google.com/maps/place/Bikanervala/@26.7851067,80.9918353,17z/data=!3m1!4b1!4m6!3m5!1s0x399be30647fd426d:0xd01584f16db3efe3!8m2!3d26.7851067!4d80.9918353!16s%2Fg%2F11jsr96pd9?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G77" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H77" s="9" t="n">
+        <v>2442</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -5259,6 +6345,12 @@
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" s="9" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -5289,6 +6381,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Emerald+Mall+Lucknow/@26.7879677,80.9106156,17z/data=!3m1!4b1!4m6!3m5!1s0x399bfda33d9b4ed1:0x4bc0f33320d7156b!8m2!3d26.7879677!4d80.9106156!16s%2Fg%2F11vs2f1qpf?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G79" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H79" s="9" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -5315,6 +6413,12 @@
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H80" s="9" t="n">
+        <v>1484</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -5341,6 +6445,16 @@
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -5367,6 +6481,12 @@
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H82" s="9" t="n">
+        <v>1422</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -5393,6 +6513,12 @@
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
+      <c r="G83" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H83" s="9" t="n">
+        <v>209</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -5419,6 +6545,12 @@
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr"/>
+      <c r="G84" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H84" s="9" t="n">
+        <v>289</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -5445,6 +6577,12 @@
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr"/>
+      <c r="G85" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H85" s="9" t="n">
+        <v>3941</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -5471,6 +6609,12 @@
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H86" s="9" t="n">
+        <v>469</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -5497,6 +6641,12 @@
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr"/>
+      <c r="G87" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H87" s="9" t="n">
+        <v>5257</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -5523,6 +6673,12 @@
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H88" s="9" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -5549,6 +6705,12 @@
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr"/>
+      <c r="G89" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H89" s="9" t="n">
+        <v>8385</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -5575,6 +6737,12 @@
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H90" s="9" t="n">
+        <v>3604</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -5601,6 +6769,12 @@
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H91" s="9" t="n">
+        <v>3228</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -5627,6 +6801,12 @@
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H92" s="9" t="n">
+        <v>2878</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -5653,6 +6833,12 @@
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H93" s="9" t="n">
+        <v>3770</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -5679,6 +6865,12 @@
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H94" s="9" t="n">
+        <v>1624</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -5705,6 +6897,12 @@
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr"/>
+      <c r="G95" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H95" s="9" t="n">
+        <v>7495</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -5731,6 +6929,12 @@
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H96" s="9" t="n">
+        <v>2835</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -5757,6 +6961,12 @@
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr"/>
+      <c r="G97" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H97" s="9" t="n">
+        <v>2887</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -5783,6 +6993,12 @@
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H98" s="9" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -5809,6 +7025,12 @@
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr"/>
+      <c r="G99" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H99" s="9" t="n">
+        <v>1690</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -5835,6 +7057,12 @@
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H100" s="9" t="n">
+        <v>2202</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -5861,6 +7089,12 @@
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr"/>
+      <c r="G101" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H101" s="9" t="n">
+        <v>288</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -5887,6 +7121,12 @@
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr"/>
+      <c r="G102" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H102" s="9" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -5913,6 +7153,12 @@
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr"/>
+      <c r="G103" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H103" s="9" t="n">
+        <v>853</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -5939,6 +7185,12 @@
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H104" s="9" t="n">
+        <v>427</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -5965,6 +7217,12 @@
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H105" s="9" t="n">
+        <v>885</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -5991,6 +7249,12 @@
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
+      <c r="G106" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H106" s="9" t="n">
+        <v>456</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -6017,6 +7281,12 @@
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H107" s="9" t="n">
+        <v>1517</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -6043,6 +7313,12 @@
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
+      <c r="G108" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H108" s="9" t="n">
+        <v>1864</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -6069,6 +7345,12 @@
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr"/>
+      <c r="G109" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H109" s="9" t="n">
+        <v>64</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6081,8 +7363,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -6098,6 +7380,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="H1" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6128,6 +7416,16 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -6160,6 +7458,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Karama+%7C+Indian+Vegetarian+Restaurant+in+Dubai+-+4B+St+-+Sheikh+Khalifa+Bin+Zayed+St+-+behind+Park+Regis+Kris+Kin+Hotel+-+Al+Karama+-+Dubai+-+United+Arab+Emirates/@25.2487074,55.3022648,16z/data=!4m6!3m5!1s0x3e5f43263a32659d:0x3e7a496c31265a14!8m2!3d25.2487074!4d55.3022648!16s%2Fg%2F11fkl98x2w?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
+      <c r="G3" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>6985</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -6190,6 +7494,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Barsha+Heights+Dubai?hl=en</t>
         </is>
       </c>
+      <c r="G4" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>1722</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -6220,6 +7530,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Barsha+1+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1159702,55.2049553,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6bc01e76ba11:0x4fd1a9f4b2e6f5e3!8m2!3d25.1159702!4d55.2049553!16s%2Fg%2F1hhn4cw5b?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G5" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>3416</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -6250,6 +7566,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Arjan+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.0611644,55.2416108,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6f3d18bbdbdd:0xf394598ae51611cd!8m2!3d25.0611644!4d55.2416108!16s%2Fg%2F11k4t6j5kj?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G6" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>1350</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -6280,6 +7602,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Dubai+Hills+Mall+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1000884,55.2380841,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6ffb10c94323:0xe15233cd12b4c95e!8m2!3d25.1000884!4d55.2380841!16s%2Fg%2F11srb65qdy?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G7" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>1110</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -6310,6 +7638,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Sheikh+Zayed+Road+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2287901,55.2861116,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43aad3d78e71:0xb8b194cb916fd9b0!8m2!3d25.2287901!4d55.2861116!16s%2Fg%2F11spn08t8p?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G8" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>3365</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -6340,6 +7674,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Gold+Souk+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2720383,55.2977013,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43768964654b:0xc11f03b76b0ba714!8m2!3d25.2720383!4d55.2977013!16s%2Fg%2F11sqkp7mp7?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G9" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -6370,6 +7710,12 @@
           <t>https://www.google.com/maps/place/Bikanervala/@25.1971872,55.2793099,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43291308afa5:0xe48b7db44021ad9d!8m2!3d25.1971872!4d55.2793099!16s%2Fg%2F11h_6kxb_4?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G10" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>1197</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -6400,6 +7746,12 @@
           <t>https://www.google.com/maps/place/Bikanervala/@25.0443703,55.2301107,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6fbad2abf81f:0x2b8744ab6a1bf442!8m2!3d25.0443703!4d55.2301107!16s%2Fg%2F11wqdtyl9k?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G11" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>812</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -6426,6 +7778,12 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>3416</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -6456,6 +7814,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Jumeirah+3+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1568314,55.2048822,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6bf2c1bdccc9:0x43c26854ab27ef01!8m2!3d25.1568314!4d55.2048822!16s%2Fg%2F11s5twnr34?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G13" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>406</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -6486,6 +7850,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Furjan+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.0253394,55.1523478,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6d3bc9bcdbdb:0xe6f0ccdcb4b1e8ab!8m2!3d25.0253394!4d55.1523478!16s%2Fg%2F11g8kr7p26?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G14" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>3449</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -6516,6 +7886,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+International+City+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1587461,55.4044494,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6152822cefa7:0x62485254b618ad37!8m2!3d25.1587461!4d55.4044494!16s%2Fg%2F11fy4nt_fh?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G15" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>1986</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -6546,6 +7922,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Ghurair+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.268832,55.3167197,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f432a6356bd7d:0x6e8727a69863a0ea!8m2!3d25.268832!4d55.3167197!16s%2Fg%2F11gj4q5yml?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G16" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -6576,6 +7958,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Business+Bay+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1907081,55.2657305,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f69d43a494553:0xcae55dd8d4af25bc!8m2!3d25.1907081!4d55.2657305!16s%2Fg%2F11cnch2xjh?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G17" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>1332</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -6606,6 +7994,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Abu+Dhabi+%7C+Indian+Vegetarian+Restaurant+in+Abu+Dhabi/@24.4787181,54.3632708,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5e6797000fef8b:0x252e9c63c8d0f687!8m2!3d24.4787181!4d54.3632708!16s%2Fg%2F11j3jt3jck?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G18" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>4495</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -6636,6 +8030,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Qusais+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2779484,55.362064,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f5c5ef14f580b:0x42f37dd66cc3bd09!8m2!3d25.2779484!4d55.362064!16s%2Fg%2F11bbwn_ftp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G19" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>1663</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -6666,6 +8066,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Hounslow/@51.4697256,-0.3575675,17z/data=!3m1!4b1!4m6!3m5!1s0x48760db0ad77af37:0x259004b7a001719e!8m2!3d51.4697256!4d-0.3575675!16s%2Fg%2F11lw2pkxzp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G20" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>4369</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -6692,6 +8098,12 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>3847</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -6718,6 +8130,12 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -6744,6 +8162,12 @@
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>443</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -6770,6 +8194,12 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>1684</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -6796,6 +8226,12 @@
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>3363</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -6822,6 +8258,12 @@
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>1767</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -6848,6 +8290,12 @@
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>530</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -6874,6 +8322,12 @@
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>1325</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -6900,6 +8354,12 @@
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>641</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -6926,6 +8386,12 @@
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -6952,6 +8418,12 @@
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>1323</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -6978,6 +8450,12 @@
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>1427</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -7004,6 +8482,12 @@
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>1334</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -7030,6 +8514,12 @@
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>186</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -7056,6 +8546,12 @@
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -7082,6 +8578,12 @@
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>994</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -7108,6 +8610,12 @@
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>205</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -7134,6 +8642,12 @@
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>211</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -7160,6 +8674,12 @@
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>854</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -7186,6 +8706,12 @@
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>2234</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -7212,6 +8738,12 @@
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -7238,6 +8770,12 @@
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>1582</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -7264,6 +8802,12 @@
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>1165</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -7290,6 +8834,12 @@
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>474</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -7316,6 +8866,12 @@
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>371</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -7342,6 +8898,12 @@
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>1042</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -7368,6 +8930,12 @@
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>2567</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -7394,6 +8962,12 @@
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>1429</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -7420,6 +8994,12 @@
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>1420</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -7446,6 +9026,12 @@
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>1550</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -7472,6 +9058,12 @@
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>2806</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -7498,6 +9090,12 @@
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>742</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -7524,6 +9122,12 @@
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>1226</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -7550,6 +9154,12 @@
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>673</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -7576,6 +9186,12 @@
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>422</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -7822,8 +9438,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F113"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H113"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -7839,6 +9455,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="H1" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7869,6 +9491,16 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -7897,6 +9529,12 @@
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>4576</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -7923,6 +9561,12 @@
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>1229</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -7949,6 +9593,12 @@
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>460</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -7975,6 +9625,12 @@
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>11588</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -8001,6 +9657,12 @@
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -8027,6 +9689,12 @@
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>918</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -8053,6 +9721,12 @@
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>1604</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -8079,6 +9753,12 @@
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>2023</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -8105,6 +9785,12 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>3082</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -8131,6 +9817,12 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>3624</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -8157,6 +9849,12 @@
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>21263</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -8183,6 +9881,12 @@
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>2946</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -8209,6 +9913,12 @@
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>4203</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -8235,6 +9945,12 @@
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>2387</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -8261,6 +9977,12 @@
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -8287,6 +10009,12 @@
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>12119</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -8313,6 +10041,12 @@
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>3076</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -8339,6 +10073,12 @@
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>9245</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -8365,6 +10105,12 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -8391,6 +10137,12 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>6136</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -8417,6 +10169,12 @@
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>1729</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -8443,6 +10201,12 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>1060</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -8469,6 +10233,12 @@
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>2053</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -8495,6 +10265,12 @@
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>2776</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -8521,6 +10297,12 @@
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>11068</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -8547,6 +10329,12 @@
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>5490</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -8573,6 +10361,12 @@
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>4008</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -8599,6 +10393,12 @@
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>1579</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -8625,6 +10425,12 @@
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>1579</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -8651,6 +10457,12 @@
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>2810</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -8677,6 +10489,12 @@
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>18967</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -8703,6 +10521,12 @@
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>39676</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -8729,6 +10553,12 @@
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>5228</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -8755,6 +10585,12 @@
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>10373</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -8781,6 +10617,12 @@
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>7404</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -8807,6 +10649,12 @@
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>539</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -8833,6 +10681,12 @@
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>1124</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -8859,6 +10713,12 @@
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>539</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -8885,6 +10745,12 @@
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>2617</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -8911,6 +10777,12 @@
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>1442</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -8937,6 +10809,12 @@
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>955</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -8963,6 +10841,12 @@
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>4162</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -8989,6 +10873,12 @@
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr"/>
+      <c r="G45" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>3482</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -9015,6 +10905,12 @@
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>7886</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -9041,6 +10937,12 @@
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr"/>
+      <c r="G47" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>6136</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -9067,6 +10969,12 @@
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr"/>
+      <c r="G48" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>983</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -9093,6 +11001,12 @@
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
+      <c r="G49" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>3643</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -9119,6 +11033,12 @@
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr"/>
+      <c r="G50" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>168</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -9145,6 +11065,12 @@
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>4119</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -9171,6 +11097,12 @@
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr"/>
+      <c r="G52" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>314</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -9197,6 +11129,12 @@
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>135</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -9223,6 +11161,12 @@
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr"/>
+      <c r="G54" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>4119</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -9249,6 +11193,12 @@
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -9275,6 +11225,12 @@
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr"/>
+      <c r="G56" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>492</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -9301,6 +11257,12 @@
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>7852</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -9327,6 +11289,12 @@
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr"/>
+      <c r="G58" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>4017</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -9353,6 +11321,12 @@
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr"/>
+      <c r="G59" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>2848</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -9379,6 +11353,12 @@
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr"/>
+      <c r="G60" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>2251</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -9405,6 +11385,12 @@
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr"/>
+      <c r="G61" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H61" s="9" t="n">
+        <v>7820</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -9431,6 +11417,12 @@
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H62" s="9" t="n">
+        <v>3615</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -9457,6 +11449,12 @@
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr"/>
+      <c r="G63" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>4769</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -9483,6 +11481,12 @@
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr"/>
+      <c r="G64" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>2626</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -9509,6 +11513,12 @@
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr"/>
+      <c r="G65" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>2900</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -9535,6 +11545,12 @@
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr"/>
+      <c r="G66" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H66" s="9" t="n">
+        <v>6444</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -9561,6 +11577,12 @@
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr"/>
+      <c r="G67" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H67" s="9" t="n">
+        <v>781</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -9587,6 +11609,12 @@
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr"/>
+      <c r="G68" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H68" s="9" t="n">
+        <v>19103</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -9613,6 +11641,12 @@
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr"/>
+      <c r="G69" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H69" s="9" t="n">
+        <v>2915</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -9639,6 +11673,12 @@
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr"/>
+      <c r="G70" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H70" s="9" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -9665,6 +11705,12 @@
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr"/>
+      <c r="G71" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H71" s="9" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -9691,6 +11737,12 @@
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr"/>
+      <c r="G72" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H72" s="9" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -9717,6 +11769,12 @@
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr"/>
+      <c r="G73" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H73" s="9" t="n">
+        <v>3862</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -9743,6 +11801,12 @@
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H74" s="9" t="n">
+        <v>754</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -9769,6 +11833,12 @@
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr"/>
+      <c r="G75" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H75" s="9" t="n">
+        <v>4655</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -9795,6 +11865,12 @@
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H76" s="9" t="n">
+        <v>5287</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -9821,6 +11897,12 @@
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr"/>
+      <c r="G77" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H77" s="9" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -9847,6 +11929,12 @@
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr"/>
+      <c r="G78" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H78" s="9" t="n">
+        <v>1131</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -9873,6 +11961,12 @@
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr"/>
+      <c r="G79" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H79" s="9" t="n">
+        <v>634</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -9899,6 +11993,12 @@
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr"/>
+      <c r="G80" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H80" s="9" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -9925,6 +12025,12 @@
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr"/>
+      <c r="G81" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H81" s="9" t="n">
+        <v>1554</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -9951,6 +12057,12 @@
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr"/>
+      <c r="G82" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H82" s="9" t="n">
+        <v>11737</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -9977,6 +12089,12 @@
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr"/>
+      <c r="G83" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H83" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -10003,6 +12121,12 @@
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr"/>
+      <c r="G84" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H84" s="9" t="n">
+        <v>5927</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -10029,6 +12153,12 @@
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr"/>
+      <c r="G85" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H85" s="9" t="n">
+        <v>3259</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -10055,6 +12185,12 @@
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H86" s="9" t="n">
+        <v>10418</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -10081,6 +12217,12 @@
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr"/>
+      <c r="G87" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H87" s="9" t="n">
+        <v>4151</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -10107,6 +12249,12 @@
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr"/>
+      <c r="G88" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H88" s="9" t="n">
+        <v>2998</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -10133,6 +12281,12 @@
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr"/>
+      <c r="G89" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H89" s="9" t="n">
+        <v>1296</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -10159,6 +12313,12 @@
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr"/>
+      <c r="G90" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H90" s="9" t="n">
+        <v>2234</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -10185,6 +12345,12 @@
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr"/>
+      <c r="G91" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H91" s="9" t="n">
+        <v>7975</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -10211,6 +12377,12 @@
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr"/>
+      <c r="G92" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H92" s="9" t="n">
+        <v>784</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -10237,6 +12409,12 @@
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr"/>
+      <c r="G93" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H93" s="9" t="n">
+        <v>788</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -10263,6 +12441,12 @@
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr"/>
+      <c r="G94" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H94" s="9" t="n">
+        <v>2595</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -10289,6 +12473,12 @@
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr"/>
+      <c r="G95" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H95" s="9" t="n">
+        <v>1677</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -10315,6 +12505,12 @@
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr"/>
+      <c r="G96" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H96" s="9" t="n">
+        <v>6439</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -10341,6 +12537,12 @@
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr"/>
+      <c r="G97" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H97" s="9" t="n">
+        <v>2315</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -10367,6 +12569,12 @@
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr"/>
+      <c r="G98" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H98" s="9" t="n">
+        <v>1937</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -10393,6 +12601,12 @@
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr"/>
+      <c r="G99" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H99" s="9" t="n">
+        <v>5570</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -10419,6 +12633,12 @@
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H100" s="9" t="n">
+        <v>17774</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -10445,6 +12665,12 @@
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr"/>
+      <c r="G101" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H101" s="9" t="n">
+        <v>6160</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -10471,6 +12697,12 @@
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr"/>
+      <c r="G102" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H102" s="9" t="n">
+        <v>5283</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -10497,6 +12729,12 @@
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr"/>
+      <c r="G103" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H103" s="9" t="n">
+        <v>1173</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -10523,6 +12761,12 @@
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr"/>
+      <c r="G104" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H104" s="9" t="n">
+        <v>4076</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -10549,6 +12793,12 @@
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr"/>
+      <c r="G105" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H105" s="9" t="n">
+        <v>1173</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -10575,6 +12825,12 @@
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
+      <c r="G106" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H106" s="9" t="n">
+        <v>10974</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -10601,6 +12857,12 @@
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr"/>
+      <c r="G107" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H107" s="9" t="n">
+        <v>3159</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -10627,6 +12889,12 @@
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr"/>
+      <c r="G108" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H108" s="9" t="n">
+        <v>3055</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -10653,6 +12921,12 @@
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr"/>
+      <c r="G109" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H109" s="9" t="n">
+        <v>2620</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
@@ -10679,6 +12953,12 @@
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr"/>
+      <c r="G110" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H110" s="9" t="n">
+        <v>1879</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
@@ -10705,6 +12985,12 @@
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr"/>
+      <c r="G111" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H111" s="9" t="n">
+        <v>1196</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
@@ -10731,6 +13017,12 @@
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr"/>
+      <c r="G112" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H112" s="9" t="n">
+        <v>2449</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
@@ -10757,6 +13049,12 @@
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr"/>
+      <c r="G113" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H113" s="9" t="n">
+        <v>2629</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10769,8 +13067,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -10786,6 +13084,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="6" t="n">
+        <v>46301</v>
+      </c>
+      <c r="H1" s="6" t="n">
+        <v>46301</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -10816,6 +13120,16 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -10844,6 +13158,12 @@
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>14377</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -10870,6 +13190,12 @@
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>1199</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -10896,6 +13222,12 @@
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -10922,6 +13254,12 @@
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -10948,6 +13286,12 @@
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>4836</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -10974,6 +13318,12 @@
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>2067</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -11000,6 +13350,12 @@
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>5777</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -11026,6 +13382,12 @@
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>6554</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -11052,6 +13414,12 @@
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>10574</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -11078,6 +13446,12 @@
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>12233</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -11104,6 +13478,12 @@
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>10698</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -11130,6 +13510,12 @@
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>6809</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -11156,6 +13542,12 @@
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>3605</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -11182,6 +13574,12 @@
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>4500</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -11208,6 +13606,12 @@
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>876</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -11234,6 +13638,12 @@
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>19723</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -11260,6 +13670,12 @@
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>2017</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -11286,6 +13702,12 @@
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>2024</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -11312,6 +13734,12 @@
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>8781</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -11338,6 +13766,12 @@
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>1118</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -11364,6 +13798,12 @@
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>676</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -11390,6 +13830,12 @@
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>1820</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -611,7 +611,7 @@
         <v>4.4</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>4873</v>
+        <v>4872</v>
       </c>
     </row>
     <row r="4">
@@ -683,7 +683,7 @@
         <v>4.5</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>5536</v>
+        <v>5539</v>
       </c>
     </row>
     <row r="6">
@@ -719,7 +719,7 @@
         <v>4.3</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>6534</v>
+        <v>6531</v>
       </c>
     </row>
     <row r="7">
@@ -755,7 +755,7 @@
         <v>4.5</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>2397</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="8">
@@ -791,7 +791,7 @@
         <v>4.4</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>7147</v>
+        <v>7152</v>
       </c>
     </row>
     <row r="9">
@@ -827,7 +827,7 @@
         <v>4.4</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>3664</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="10">
@@ -863,7 +863,7 @@
         <v>4.4</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>2781</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="11">
@@ -1007,7 +1007,7 @@
         <v>4.4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>2348</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="15">
@@ -1043,7 +1043,7 @@
         <v>4.4</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>2588</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="16">
@@ -1115,7 +1115,7 @@
         <v>4.7</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="18">
@@ -1187,7 +1187,7 @@
         <v>4.7</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="20">
@@ -1259,7 +1259,7 @@
         <v>4.6</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="22">
@@ -1435,7 +1435,7 @@
         <v>4.9</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -1612,7 +1612,7 @@
         <v>4.3</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>3862</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="6">
@@ -1648,7 +1648,7 @@
         <v>4.3</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>3862</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="7">
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="G8" s="9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>19723</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9">
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="G9" s="9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>19723</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="G10" s="9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>19723</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -2072,7 +2072,7 @@
         <v>4.1</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>4500</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="19">
@@ -2108,7 +2108,7 @@
         <v>4.1</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>4500</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="20">
@@ -2144,7 +2144,7 @@
         <v>4.4</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>2781</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="21">
@@ -2216,7 +2216,7 @@
         <v>4.2</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>5927</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="23">
@@ -2432,7 +2432,7 @@
         <v>4.2</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>3604</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="29">
@@ -2468,7 +2468,7 @@
         <v>4.2</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>3604</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="30">
@@ -2496,7 +2496,7 @@
         <v>4.5</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="31">
@@ -2532,7 +2532,7 @@
         <v>4.7</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>2216</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="32">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="G32" s="9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>1043</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="G33" s="9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>1043</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34">
@@ -2668,7 +2668,7 @@
         <v>4.2</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>4836</v>
+        <v>4837</v>
       </c>
     </row>
     <row r="36">
@@ -2704,7 +2704,7 @@
         <v>4.2</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>4836</v>
+        <v>4837</v>
       </c>
     </row>
     <row r="37">
@@ -2740,7 +2740,7 @@
         <v>4.3</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="38">
@@ -2776,7 +2776,7 @@
         <v>4.3</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39">
@@ -2812,7 +2812,7 @@
         <v>4.4</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>2588</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="40">
@@ -2920,7 +2920,7 @@
         <v>4.3</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>11737</v>
+        <v>11739</v>
       </c>
     </row>
     <row r="43">
@@ -2956,7 +2956,7 @@
         <v>4.3</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>11737</v>
+        <v>11739</v>
       </c>
     </row>
     <row r="44">
@@ -3064,7 +3064,7 @@
         <v>4.3</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>2002</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="47">
@@ -3100,7 +3100,7 @@
         <v>4.3</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>2002</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="48">
@@ -3228,7 +3228,7 @@
         <v>4.2</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>5927</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="52">
@@ -3284,7 +3284,7 @@
         <v>4.3</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>4655</v>
+        <v>4656</v>
       </c>
     </row>
     <row r="54">
@@ -3396,7 +3396,7 @@
         <v>4.6</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>1844</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="58">
@@ -3424,7 +3424,7 @@
         <v>4.3</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>4655</v>
+        <v>4656</v>
       </c>
     </row>
     <row r="59">
@@ -3452,7 +3452,7 @@
         <v>4.2</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>5777</v>
+        <v>5779</v>
       </c>
     </row>
     <row r="60">
@@ -3532,8 +3532,12 @@
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr"/>
-      <c r="G62" s="9" t="n"/>
-      <c r="H62" s="9" t="n"/>
+      <c r="G62" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H62" s="9" t="n">
+        <v>2067</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -3560,7 +3564,7 @@
         <v>4.2</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="64">
@@ -3672,7 +3676,7 @@
         <v>4.1</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="68">
@@ -3700,7 +3704,7 @@
         <v>4.2</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>14377</v>
+        <v>14379</v>
       </c>
     </row>
   </sheetData>
@@ -3813,7 +3817,7 @@
         <v>4.3</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="4">
@@ -3957,7 +3961,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>10884</v>
+        <v>10886</v>
       </c>
     </row>
     <row r="8">
@@ -3993,7 +3997,7 @@
         <v>4.2</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>2937</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="9">
@@ -4065,7 +4069,7 @@
         <v>4.3</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>5139</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="11">
@@ -4097,7 +4101,7 @@
         <v>4</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>7305</v>
+        <v>7306</v>
       </c>
     </row>
     <row r="12">
@@ -4129,7 +4133,7 @@
         <v>4.5</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>4873</v>
+        <v>4879</v>
       </c>
     </row>
     <row r="13">
@@ -4193,7 +4197,7 @@
         <v>4</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>1916</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="15">
@@ -4257,7 +4261,7 @@
         <v>4.2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>3403</v>
+        <v>3413</v>
       </c>
     </row>
     <row r="17">
@@ -4353,7 +4357,7 @@
         <v>4.3</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>5750</v>
+        <v>5751</v>
       </c>
     </row>
     <row r="20">
@@ -4385,7 +4389,7 @@
         <v>4.6</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>8147</v>
+        <v>8150</v>
       </c>
     </row>
     <row r="21">
@@ -4417,7 +4421,7 @@
         <v>4.4</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6608</v>
+        <v>6611</v>
       </c>
     </row>
     <row r="22">
@@ -4449,7 +4453,7 @@
         <v>4.4</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>6260</v>
+        <v>6261</v>
       </c>
     </row>
     <row r="23">
@@ -4517,7 +4521,7 @@
         <v>4.8</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>4694</v>
+        <v>4696</v>
       </c>
     </row>
     <row r="25">
@@ -4549,7 +4553,7 @@
         <v>4.5</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>6256</v>
+        <v>6258</v>
       </c>
     </row>
     <row r="26">
@@ -4581,7 +4585,7 @@
         <v>4.6</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>1901</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="27">
@@ -4681,7 +4685,7 @@
         <v>4.3</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>8650</v>
+        <v>8652</v>
       </c>
     </row>
     <row r="30">
@@ -4713,7 +4717,7 @@
         <v>4.4</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>2782</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="31">
@@ -4749,7 +4753,7 @@
         <v>4.1</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>5575</v>
+        <v>5576</v>
       </c>
     </row>
     <row r="32">
@@ -4781,7 +4785,7 @@
         <v>4.5</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>5537</v>
+        <v>5539</v>
       </c>
     </row>
     <row r="33">
@@ -4817,7 +4821,7 @@
         <v>4.4</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>4873</v>
+        <v>4872</v>
       </c>
     </row>
     <row r="34">
@@ -4881,7 +4885,7 @@
         <v>4.4</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>2588</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="36">
@@ -4949,7 +4953,7 @@
         <v>4.7</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="38">
@@ -5117,7 +5121,7 @@
         <v>4.5</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>2397</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="43">
@@ -5149,7 +5153,7 @@
         <v>4.7</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>2216</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="44">
@@ -5181,7 +5185,7 @@
         <v>4.3</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>6533</v>
+        <v>6531</v>
       </c>
     </row>
     <row r="45">
@@ -5253,7 +5257,7 @@
         <v>4.4</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>7146</v>
+        <v>7152</v>
       </c>
     </row>
     <row r="47">
@@ -5317,7 +5321,7 @@
         <v>4.4</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>3664</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="49">
@@ -5353,7 +5357,7 @@
         <v>4.4</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>2348</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="50">
@@ -5485,7 +5489,7 @@
         <v>4</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>9642</v>
+        <v>9645</v>
       </c>
     </row>
     <row r="54">
@@ -5550,10 +5554,10 @@
       </c>
       <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="9" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>7230</v>
+        <v>796</v>
       </c>
     </row>
     <row r="56">
@@ -5621,7 +5625,7 @@
         <v>4</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="58">
@@ -5765,7 +5769,7 @@
         <v>4.4</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>2894</v>
+        <v>2896</v>
       </c>
     </row>
     <row r="62">
@@ -5945,7 +5949,7 @@
         <v>3.9</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>4137</v>
+        <v>4138</v>
       </c>
     </row>
     <row r="67">
@@ -5977,7 +5981,7 @@
         <v>4.2</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>10344</v>
+        <v>10349</v>
       </c>
     </row>
     <row r="68">
@@ -6009,7 +6013,7 @@
         <v>4.5</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>4292</v>
+        <v>4294</v>
       </c>
     </row>
     <row r="69">
@@ -6177,7 +6181,7 @@
         <v>4.3</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>1101</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="74">
@@ -6213,7 +6217,7 @@
         <v>4.1</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>9514</v>
+        <v>9515</v>
       </c>
     </row>
     <row r="75">
@@ -6245,7 +6249,7 @@
         <v>4.2</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>16966</v>
+        <v>16967</v>
       </c>
     </row>
     <row r="76">
@@ -6317,7 +6321,7 @@
         <v>4.7</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>2442</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="78">
@@ -6417,7 +6421,7 @@
         <v>4.8</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>1484</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="81">
@@ -6485,7 +6489,7 @@
         <v>4.4</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>1422</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="83">
@@ -6581,7 +6585,7 @@
         <v>4.6</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>3941</v>
+        <v>3940</v>
       </c>
     </row>
     <row r="86">
@@ -6613,7 +6617,7 @@
         <v>4.7</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="87">
@@ -6645,7 +6649,7 @@
         <v>4.2</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>5257</v>
+        <v>5259</v>
       </c>
     </row>
     <row r="88">
@@ -6709,7 +6713,7 @@
         <v>4</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>8385</v>
+        <v>8386</v>
       </c>
     </row>
     <row r="90">
@@ -6741,7 +6745,7 @@
         <v>4.6</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>3604</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="91">
@@ -6773,7 +6777,7 @@
         <v>4.5</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>3228</v>
+        <v>3229</v>
       </c>
     </row>
     <row r="92">
@@ -6901,7 +6905,7 @@
         <v>3.9</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>7495</v>
+        <v>7496</v>
       </c>
     </row>
     <row r="96">
@@ -6965,7 +6969,7 @@
         <v>4.2</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>2887</v>
+        <v>2888</v>
       </c>
     </row>
     <row r="98">
@@ -7029,7 +7033,7 @@
         <v>4.1</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="100">
@@ -7061,7 +7065,7 @@
         <v>4.5</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>2202</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="101">
@@ -7157,7 +7161,7 @@
         <v>4.4</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="104">
@@ -7221,7 +7225,7 @@
         <v>4.2</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
     <row r="106">
@@ -7317,7 +7321,7 @@
         <v>4.7</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>1864</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="109">
@@ -7462,7 +7466,7 @@
         <v>4.5</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>6985</v>
+        <v>6991</v>
       </c>
     </row>
     <row r="4">
@@ -7498,7 +7502,7 @@
         <v>4.6</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>1722</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="5">
@@ -7534,7 +7538,7 @@
         <v>4.3</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>3416</v>
+        <v>3417</v>
       </c>
     </row>
     <row r="6">
@@ -7570,7 +7574,7 @@
         <v>4.6</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="7">
@@ -7642,7 +7646,7 @@
         <v>4.8</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>3365</v>
+        <v>3369</v>
       </c>
     </row>
     <row r="9">
@@ -7678,7 +7682,7 @@
         <v>4.7</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="10">
@@ -7782,7 +7786,7 @@
         <v>4.3</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>3416</v>
+        <v>3417</v>
       </c>
     </row>
     <row r="13">
@@ -7854,7 +7858,7 @@
         <v>4.7</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>3449</v>
+        <v>3457</v>
       </c>
     </row>
     <row r="15">
@@ -7890,7 +7894,7 @@
         <v>4.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="16">
@@ -7926,7 +7930,7 @@
         <v>4.6</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="17">
@@ -8034,7 +8038,7 @@
         <v>4.5</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1663</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="20">
@@ -8070,7 +8074,7 @@
         <v>4.6</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>4369</v>
+        <v>4371</v>
       </c>
     </row>
     <row r="21">
@@ -8102,7 +8106,7 @@
         <v>4.4</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>3847</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="22">
@@ -8358,7 +8362,7 @@
         <v>4.6</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="30">
@@ -8486,7 +8490,7 @@
         <v>3.7</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="34">
@@ -8518,7 +8522,7 @@
         <v>3.9</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35">
@@ -8678,7 +8682,7 @@
         <v>4.2</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="40">
@@ -8774,7 +8778,7 @@
         <v>4.7</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>1582</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="43">
@@ -9190,7 +9194,7 @@
         <v>4.4</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="56">
@@ -9853,7 +9857,7 @@
         <v>4.2</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>21263</v>
+        <v>21264</v>
       </c>
     </row>
     <row r="14">
@@ -9917,7 +9921,7 @@
         <v>4.4</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>4203</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="16">
@@ -10173,7 +10177,7 @@
         <v>4.5</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1729</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="24">
@@ -10301,7 +10305,7 @@
         <v>4.2</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>11068</v>
+        <v>11070</v>
       </c>
     </row>
     <row r="28">
@@ -10525,7 +10529,7 @@
         <v>4.1</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>39676</v>
+        <v>39678</v>
       </c>
     </row>
     <row r="35">
@@ -10621,7 +10625,7 @@
         <v>4.2</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>7404</v>
+        <v>7405</v>
       </c>
     </row>
     <row r="38">
@@ -10845,7 +10849,7 @@
         <v>4.5</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>4162</v>
+        <v>4166</v>
       </c>
     </row>
     <row r="45">
@@ -10877,7 +10881,7 @@
         <v>4.4</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>3482</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="46">
@@ -11101,7 +11105,7 @@
         <v>4.7</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53">
@@ -11133,7 +11137,7 @@
         <v>4.8</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="54">
@@ -11229,7 +11233,7 @@
         <v>4.8</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="57">
@@ -11325,7 +11329,7 @@
         <v>4.5</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>2848</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="60">
@@ -11389,7 +11393,7 @@
         <v>4.2</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>7820</v>
+        <v>7822</v>
       </c>
     </row>
     <row r="62">
@@ -11549,7 +11553,7 @@
         <v>4.1</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>6444</v>
+        <v>6445</v>
       </c>
     </row>
     <row r="67">
@@ -11613,7 +11617,7 @@
         <v>4.3</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>19103</v>
+        <v>19105</v>
       </c>
     </row>
     <row r="69">
@@ -11645,7 +11649,7 @@
         <v>4.5</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>2915</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="70">
@@ -11773,7 +11777,7 @@
         <v>4.3</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>3862</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="74">
@@ -11837,7 +11841,7 @@
         <v>4.3</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4655</v>
+        <v>4656</v>
       </c>
     </row>
     <row r="76">
@@ -12061,7 +12065,7 @@
         <v>4.3</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>11737</v>
+        <v>11739</v>
       </c>
     </row>
     <row r="83">
@@ -12125,7 +12129,7 @@
         <v>4.2</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>5927</v>
+        <v>5930</v>
       </c>
     </row>
     <row r="85">
@@ -12157,7 +12161,7 @@
         <v>4.4</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>3259</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="86">
@@ -12605,7 +12609,7 @@
         <v>4.5</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>5570</v>
+        <v>5578</v>
       </c>
     </row>
     <row r="100">
@@ -12637,7 +12641,7 @@
         <v>4.4</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>17774</v>
+        <v>17781</v>
       </c>
     </row>
     <row r="101">
@@ -12669,7 +12673,7 @@
         <v>4.5</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>6160</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="102">
@@ -12733,7 +12737,7 @@
         <v>4.4</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="104">
@@ -12797,7 +12801,7 @@
         <v>4.4</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="106">
@@ -12893,7 +12897,7 @@
         <v>4.5</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>3055</v>
+        <v>3056</v>
       </c>
     </row>
     <row r="109">
@@ -13021,7 +13025,7 @@
         <v>4.4</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>2449</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="113">
@@ -13053,7 +13057,7 @@
         <v>4.6</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>2629</v>
+        <v>2630</v>
       </c>
     </row>
   </sheetData>
@@ -13162,7 +13166,7 @@
         <v>4.2</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>14377</v>
+        <v>14379</v>
       </c>
     </row>
     <row r="4">
@@ -13290,7 +13294,7 @@
         <v>4.2</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>4836</v>
+        <v>4837</v>
       </c>
     </row>
     <row r="8">
@@ -13354,7 +13358,7 @@
         <v>4.2</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>5777</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="10">
@@ -13514,7 +13518,7 @@
         <v>4.2</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>6809</v>
+        <v>6810</v>
       </c>
     </row>
     <row r="15">
@@ -13546,7 +13550,7 @@
         <v>4.2</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>3605</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="16">
@@ -13578,7 +13582,7 @@
         <v>4.1</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>4500</v>
+        <v>4502</v>
       </c>
     </row>
     <row r="17">
@@ -13610,7 +13614,7 @@
         <v>4.2</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="18">
@@ -13674,7 +13678,7 @@
         <v>4.2</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="20">
@@ -13706,7 +13710,7 @@
         <v>4.1</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="21">
@@ -13738,7 +13742,7 @@
         <v>4.2</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>8781</v>
+        <v>8782</v>
       </c>
     </row>
     <row r="22">
@@ -13802,7 +13806,7 @@
         <v>4</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="24">

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,12 @@
       <c r="H1" s="6" t="n">
         <v>46301</v>
       </c>
+      <c r="I1" s="6" t="n">
+        <v>46302</v>
+      </c>
+      <c r="J1" s="6" t="n">
+        <v>46302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -573,6 +579,16 @@
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -613,6 +629,12 @@
       <c r="H3" s="9" t="n">
         <v>4872</v>
       </c>
+      <c r="I3" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>4869</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -649,6 +671,12 @@
       <c r="H4" s="9" t="n">
         <v>15772</v>
       </c>
+      <c r="I4" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>15773</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -685,6 +713,12 @@
       <c r="H5" s="9" t="n">
         <v>5539</v>
       </c>
+      <c r="I5" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>5544</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -721,6 +755,12 @@
       <c r="H6" s="9" t="n">
         <v>6531</v>
       </c>
+      <c r="I6" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>6542</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -757,6 +797,12 @@
       <c r="H7" s="9" t="n">
         <v>2400</v>
       </c>
+      <c r="I7" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>2406</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -793,6 +839,12 @@
       <c r="H8" s="9" t="n">
         <v>7152</v>
       </c>
+      <c r="I8" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>7170</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -829,6 +881,12 @@
       <c r="H9" s="9" t="n">
         <v>3652</v>
       </c>
+      <c r="I9" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>3659</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -865,6 +923,12 @@
       <c r="H10" s="9" t="n">
         <v>2783</v>
       </c>
+      <c r="I10" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>2781</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -901,6 +965,12 @@
       <c r="H11" s="9" t="n">
         <v>1103</v>
       </c>
+      <c r="I11" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>1110</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -937,6 +1007,12 @@
       <c r="H12" s="9" t="n">
         <v>1108</v>
       </c>
+      <c r="I12" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>1108</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -973,6 +1049,12 @@
       <c r="H13" s="9" t="n">
         <v>2217</v>
       </c>
+      <c r="I13" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>2225</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1009,6 +1091,12 @@
       <c r="H14" s="9" t="n">
         <v>2349</v>
       </c>
+      <c r="I14" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>2379</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1045,6 +1133,12 @@
       <c r="H15" s="9" t="n">
         <v>2591</v>
       </c>
+      <c r="I15" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>2601</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1081,6 +1175,12 @@
       <c r="H16" s="9" t="n">
         <v>888</v>
       </c>
+      <c r="I16" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>890</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1117,6 +1217,12 @@
       <c r="H17" s="9" t="n">
         <v>1327</v>
       </c>
+      <c r="I17" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>1327</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1153,6 +1259,12 @@
       <c r="H18" s="9" t="n">
         <v>450</v>
       </c>
+      <c r="I18" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>452</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1189,6 +1301,12 @@
       <c r="H19" s="9" t="n">
         <v>929</v>
       </c>
+      <c r="I19" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>920</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1225,6 +1343,12 @@
       <c r="H20" s="9" t="n">
         <v>1097</v>
       </c>
+      <c r="I20" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>1099</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1261,6 +1385,12 @@
       <c r="H21" s="9" t="n">
         <v>789</v>
       </c>
+      <c r="I21" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>789</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1297,6 +1427,12 @@
       <c r="H22" s="9" t="n">
         <v>659</v>
       </c>
+      <c r="I22" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>660</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1333,6 +1469,12 @@
       <c r="H23" s="9" t="n">
         <v>699</v>
       </c>
+      <c r="I23" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>698</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1369,6 +1511,12 @@
       <c r="H24" s="9" t="n">
         <v>1428</v>
       </c>
+      <c r="I24" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>1425</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1405,6 +1553,12 @@
       <c r="H25" s="9" t="n">
         <v>704</v>
       </c>
+      <c r="I25" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>707</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1436,6 +1590,12 @@
       </c>
       <c r="H26" s="9" t="n">
         <v>360</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -1449,7 +1609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1472,6 +1632,12 @@
       <c r="H1" s="6" t="n">
         <v>46301</v>
       </c>
+      <c r="I1" s="6" t="n">
+        <v>46302</v>
+      </c>
+      <c r="J1" s="6" t="n">
+        <v>46302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1510,6 +1676,16 @@
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1550,6 +1726,12 @@
       <c r="H3" s="9" t="n">
         <v>81</v>
       </c>
+      <c r="I3" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1578,6 +1760,12 @@
       <c r="H4" s="9" t="n">
         <v>81</v>
       </c>
+      <c r="I4" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1614,6 +1802,12 @@
       <c r="H5" s="9" t="n">
         <v>3863</v>
       </c>
+      <c r="I5" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>3864</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1650,6 +1844,12 @@
       <c r="H6" s="9" t="n">
         <v>3863</v>
       </c>
+      <c r="I6" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>3864</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1686,6 +1886,12 @@
       <c r="H7" s="9" t="n">
         <v>659</v>
       </c>
+      <c r="I7" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>660</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1722,6 +1928,12 @@
       <c r="H8" s="9" t="n">
         <v>168</v>
       </c>
+      <c r="I8" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>6811</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1758,6 +1970,12 @@
       <c r="H9" s="9" t="n">
         <v>168</v>
       </c>
+      <c r="I9" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>6811</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1794,6 +2012,12 @@
       <c r="H10" s="9" t="n">
         <v>168</v>
       </c>
+      <c r="I10" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>6811</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1830,6 +2054,12 @@
       <c r="H11" s="9" t="n">
         <v>1193</v>
       </c>
+      <c r="I11" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1866,6 +2096,12 @@
       <c r="H12" s="9" t="n">
         <v>1193</v>
       </c>
+      <c r="I12" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1902,6 +2138,12 @@
       <c r="H13" s="9" t="n">
         <v>1820</v>
       </c>
+      <c r="I13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>1821</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1938,6 +2180,12 @@
       <c r="H14" s="9" t="n">
         <v>1820</v>
       </c>
+      <c r="I14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>1821</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1974,6 +2222,12 @@
       <c r="H15" s="9" t="n">
         <v>1820</v>
       </c>
+      <c r="I15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>1821</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -2002,6 +2256,12 @@
       <c r="H16" s="9" t="n">
         <v>2629</v>
       </c>
+      <c r="I16" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -2038,6 +2298,12 @@
       <c r="H17" s="9" t="n">
         <v>1820</v>
       </c>
+      <c r="I17" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>1821</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -2074,6 +2340,12 @@
       <c r="H18" s="9" t="n">
         <v>4502</v>
       </c>
+      <c r="I18" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>4502</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -2110,6 +2382,12 @@
       <c r="H19" s="9" t="n">
         <v>4502</v>
       </c>
+      <c r="I19" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>4502</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -2146,6 +2424,12 @@
       <c r="H20" s="9" t="n">
         <v>2783</v>
       </c>
+      <c r="I20" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>2781</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -2182,6 +2466,12 @@
       <c r="H21" s="9" t="n">
         <v>15772</v>
       </c>
+      <c r="I21" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>15773</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -2218,6 +2508,12 @@
       <c r="H22" s="9" t="n">
         <v>5930</v>
       </c>
+      <c r="I22" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>5931</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -2254,6 +2550,12 @@
       <c r="H23" s="9" t="n">
         <v>10574</v>
       </c>
+      <c r="I23" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>10575</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -2290,6 +2592,12 @@
       <c r="H24" s="9" t="n">
         <v>12233</v>
       </c>
+      <c r="I24" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>12234</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -2326,6 +2634,12 @@
       <c r="H25" s="9" t="n">
         <v>847</v>
       </c>
+      <c r="I25" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>847</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -2362,6 +2676,12 @@
       <c r="H26" s="9" t="n">
         <v>847</v>
       </c>
+      <c r="I26" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>847</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -2398,6 +2718,12 @@
       <c r="H27" s="9" t="n">
         <v>847</v>
       </c>
+      <c r="I27" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>847</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -2434,6 +2760,12 @@
       <c r="H28" s="9" t="n">
         <v>3607</v>
       </c>
+      <c r="I28" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>3606</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -2470,6 +2802,12 @@
       <c r="H29" s="9" t="n">
         <v>3607</v>
       </c>
+      <c r="I29" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>3606</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -2498,6 +2836,12 @@
       <c r="H30" s="9" t="n">
         <v>1157</v>
       </c>
+      <c r="I30" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>1160</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -2534,6 +2878,12 @@
       <c r="H31" s="9" t="n">
         <v>2217</v>
       </c>
+      <c r="I31" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>2225</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -2570,6 +2920,12 @@
       <c r="H32" s="9" t="n">
         <v>168</v>
       </c>
+      <c r="I32" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>1043</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -2606,6 +2962,12 @@
       <c r="H33" s="9" t="n">
         <v>168</v>
       </c>
+      <c r="I33" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>1043</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -2634,6 +2996,12 @@
       <c r="H34" s="9" t="n">
         <v>1131</v>
       </c>
+      <c r="I34" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>1131</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -2670,6 +3038,12 @@
       <c r="H35" s="9" t="n">
         <v>4837</v>
       </c>
+      <c r="I35" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>4837</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -2706,6 +3080,12 @@
       <c r="H36" s="9" t="n">
         <v>4837</v>
       </c>
+      <c r="I36" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>4837</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2742,6 +3122,12 @@
       <c r="H37" s="9" t="n">
         <v>283</v>
       </c>
+      <c r="I37" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>283</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -2778,6 +3164,12 @@
       <c r="H38" s="9" t="n">
         <v>283</v>
       </c>
+      <c r="I38" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>283</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -2814,6 +3206,12 @@
       <c r="H39" s="9" t="n">
         <v>2591</v>
       </c>
+      <c r="I39" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>2601</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2850,6 +3248,12 @@
       <c r="H40" s="9" t="n">
         <v>450</v>
       </c>
+      <c r="I40" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>452</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2886,6 +3290,12 @@
       <c r="H41" s="9" t="n">
         <v>1103</v>
       </c>
+      <c r="I41" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>1110</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -2922,6 +3332,12 @@
       <c r="H42" s="9" t="n">
         <v>11739</v>
       </c>
+      <c r="I42" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>11741</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -2958,6 +3374,12 @@
       <c r="H43" s="9" t="n">
         <v>11739</v>
       </c>
+      <c r="I43" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>11741</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -2994,6 +3416,12 @@
       <c r="H44" s="9" t="n">
         <v>192</v>
       </c>
+      <c r="I44" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -3030,6 +3458,12 @@
       <c r="H45" s="9" t="n">
         <v>192</v>
       </c>
+      <c r="I45" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -3066,6 +3500,12 @@
       <c r="H46" s="9" t="n">
         <v>2004</v>
       </c>
+      <c r="I46" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>2005</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -3102,6 +3542,12 @@
       <c r="H47" s="9" t="n">
         <v>2004</v>
       </c>
+      <c r="I47" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>2005</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -3138,6 +3584,12 @@
       <c r="H48" s="9" t="n">
         <v>1774</v>
       </c>
+      <c r="I48" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>1774</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -3174,6 +3626,12 @@
       <c r="H49" s="9" t="n">
         <v>1774</v>
       </c>
+      <c r="I49" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>1774</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -3202,6 +3660,12 @@
       <c r="H50" s="9" t="n">
         <v>2629</v>
       </c>
+      <c r="I50" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -3230,6 +3694,12 @@
       <c r="H51" s="9" t="n">
         <v>5930</v>
       </c>
+      <c r="I51" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>5931</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -3258,6 +3728,12 @@
       <c r="H52" s="9" t="n">
         <v>1554</v>
       </c>
+      <c r="I52" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>1561</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -3286,6 +3762,12 @@
       <c r="H53" s="9" t="n">
         <v>4656</v>
       </c>
+      <c r="I53" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>4656</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -3314,6 +3796,12 @@
       <c r="H54" s="9" t="n">
         <v>5287</v>
       </c>
+      <c r="I54" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>5287</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -3342,6 +3830,12 @@
       <c r="H55" s="9" t="n">
         <v>170</v>
       </c>
+      <c r="I55" s="9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -3370,6 +3864,12 @@
       <c r="H56" s="9" t="n">
         <v>4165</v>
       </c>
+      <c r="I56" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>4166</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -3398,6 +3898,12 @@
       <c r="H57" s="9" t="n">
         <v>1847</v>
       </c>
+      <c r="I57" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>1847</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -3426,6 +3932,12 @@
       <c r="H58" s="9" t="n">
         <v>4656</v>
       </c>
+      <c r="I58" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>4656</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -3454,6 +3966,12 @@
       <c r="H59" s="9" t="n">
         <v>5779</v>
       </c>
+      <c r="I59" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>5781</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -3482,6 +4000,12 @@
       <c r="H60" s="9" t="n">
         <v>6554</v>
       </c>
+      <c r="I60" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>6557</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -3510,6 +4034,12 @@
       <c r="H61" s="9" t="n">
         <v>10698</v>
       </c>
+      <c r="I61" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>10700</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -3538,6 +4068,12 @@
       <c r="H62" s="9" t="n">
         <v>2067</v>
       </c>
+      <c r="I62" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>2067</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -3566,6 +4102,12 @@
       <c r="H63" s="9" t="n">
         <v>878</v>
       </c>
+      <c r="I63" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>878</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -3594,6 +4136,12 @@
       <c r="H64" s="9" t="n">
         <v>1199</v>
       </c>
+      <c r="I64" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>1201</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -3622,6 +4170,12 @@
       <c r="H65" s="9" t="n">
         <v>28</v>
       </c>
+      <c r="I65" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -3650,6 +4204,12 @@
       <c r="H66" s="9" t="n">
         <v>73</v>
       </c>
+      <c r="I66" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -3678,6 +4238,12 @@
       <c r="H67" s="9" t="n">
         <v>886</v>
       </c>
+      <c r="I67" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>886</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -3704,6 +4270,12 @@
         <v>4.2</v>
       </c>
       <c r="H68" s="9" t="n">
+        <v>14379</v>
+      </c>
+      <c r="I68" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J68" s="9" t="n">
         <v>14379</v>
       </c>
     </row>
@@ -3718,7 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3741,6 +4313,12 @@
       <c r="H1" s="6" t="n">
         <v>46301</v>
       </c>
+      <c r="I1" s="6" t="n">
+        <v>46302</v>
+      </c>
+      <c r="J1" s="6" t="n">
+        <v>46302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3779,6 +4357,16 @@
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -3819,6 +4407,12 @@
       <c r="H3" s="9" t="n">
         <v>2102</v>
       </c>
+      <c r="I3" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>2109</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -3855,6 +4449,12 @@
       <c r="H4" s="9" t="n">
         <v>632</v>
       </c>
+      <c r="I4" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>632</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -3891,6 +4491,12 @@
       <c r="H5" s="9" t="n">
         <v>1555</v>
       </c>
+      <c r="I5" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>1555</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -3927,6 +4533,12 @@
       <c r="H6" s="9" t="n">
         <v>126</v>
       </c>
+      <c r="I6" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -3963,6 +4575,12 @@
       <c r="H7" s="9" t="n">
         <v>10886</v>
       </c>
+      <c r="I7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>10887</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -3999,6 +4617,12 @@
       <c r="H8" s="9" t="n">
         <v>2940</v>
       </c>
+      <c r="I8" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>2940</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -4035,6 +4659,12 @@
       <c r="H9" s="9" t="n">
         <v>218</v>
       </c>
+      <c r="I9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>218</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -4071,6 +4701,12 @@
       <c r="H10" s="9" t="n">
         <v>5140</v>
       </c>
+      <c r="I10" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>5139</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -4103,6 +4739,12 @@
       <c r="H11" s="9" t="n">
         <v>7306</v>
       </c>
+      <c r="I11" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>7317</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -4135,6 +4777,12 @@
       <c r="H12" s="9" t="n">
         <v>4879</v>
       </c>
+      <c r="I12" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>4887</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -4167,6 +4815,12 @@
       <c r="H13" s="9" t="n">
         <v>949</v>
       </c>
+      <c r="I13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>949</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -4199,6 +4853,12 @@
       <c r="H14" s="9" t="n">
         <v>1918</v>
       </c>
+      <c r="I14" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>1918</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -4231,6 +4891,12 @@
       <c r="H15" s="9" t="n">
         <v>834</v>
       </c>
+      <c r="I15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>834</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -4263,6 +4929,12 @@
       <c r="H16" s="9" t="n">
         <v>3413</v>
       </c>
+      <c r="I16" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>3423</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -4295,6 +4967,12 @@
       <c r="H17" s="9" t="n">
         <v>5648</v>
       </c>
+      <c r="I17" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>5651</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -4327,6 +5005,12 @@
       <c r="H18" s="9" t="n">
         <v>4603</v>
       </c>
+      <c r="I18" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>4608</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -4359,6 +5043,12 @@
       <c r="H19" s="9" t="n">
         <v>5751</v>
       </c>
+      <c r="I19" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>5749</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -4391,6 +5081,12 @@
       <c r="H20" s="9" t="n">
         <v>8150</v>
       </c>
+      <c r="I20" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>8150</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -4423,6 +5119,12 @@
       <c r="H21" s="9" t="n">
         <v>6611</v>
       </c>
+      <c r="I21" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>6610</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -4455,6 +5157,12 @@
       <c r="H22" s="9" t="n">
         <v>6261</v>
       </c>
+      <c r="I22" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>6274</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -4491,6 +5199,12 @@
       <c r="H23" s="9" t="n">
         <v>6217</v>
       </c>
+      <c r="I23" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>6214</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -4523,6 +5237,12 @@
       <c r="H24" s="9" t="n">
         <v>4696</v>
       </c>
+      <c r="I24" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>4695</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -4555,6 +5275,12 @@
       <c r="H25" s="9" t="n">
         <v>6258</v>
       </c>
+      <c r="I25" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>6269</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -4587,6 +5313,12 @@
       <c r="H26" s="9" t="n">
         <v>1904</v>
       </c>
+      <c r="I26" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>1905</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -4619,6 +5351,12 @@
       <c r="H27" s="9" t="n">
         <v>8386</v>
       </c>
+      <c r="I27" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>8387</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -4651,6 +5389,12 @@
       <c r="H28" s="9" t="n">
         <v>233</v>
       </c>
+      <c r="I28" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>233</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -4687,6 +5431,12 @@
       <c r="H29" s="9" t="n">
         <v>8652</v>
       </c>
+      <c r="I29" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>8662</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -4719,6 +5469,12 @@
       <c r="H30" s="9" t="n">
         <v>2783</v>
       </c>
+      <c r="I30" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>2781</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -4755,6 +5511,12 @@
       <c r="H31" s="9" t="n">
         <v>5576</v>
       </c>
+      <c r="I31" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>5576</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -4787,6 +5549,12 @@
       <c r="H32" s="9" t="n">
         <v>5539</v>
       </c>
+      <c r="I32" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>5544</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -4823,6 +5591,12 @@
       <c r="H33" s="9" t="n">
         <v>4872</v>
       </c>
+      <c r="I33" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>4869</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -4855,6 +5629,12 @@
       <c r="H34" s="9" t="n">
         <v>888</v>
       </c>
+      <c r="I34" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>890</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -4887,6 +5667,12 @@
       <c r="H35" s="9" t="n">
         <v>2591</v>
       </c>
+      <c r="I35" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>2601</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -4919,6 +5705,12 @@
       <c r="H36" s="9" t="n">
         <v>699</v>
       </c>
+      <c r="I36" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>698</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -4955,6 +5747,12 @@
       <c r="H37" s="9" t="n">
         <v>1327</v>
       </c>
+      <c r="I37" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>1327</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -4987,6 +5785,12 @@
       <c r="H38" s="9" t="n">
         <v>1103</v>
       </c>
+      <c r="I38" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>1110</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -5019,6 +5823,12 @@
       <c r="H39" s="9" t="n">
         <v>510</v>
       </c>
+      <c r="I39" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>510</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -5051,6 +5861,12 @@
       <c r="H40" s="9" t="n">
         <v>1097</v>
       </c>
+      <c r="I40" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>1099</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -5087,6 +5903,12 @@
       <c r="H41" s="9" t="n">
         <v>450</v>
       </c>
+      <c r="I41" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>452</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -5123,6 +5945,12 @@
       <c r="H42" s="9" t="n">
         <v>2400</v>
       </c>
+      <c r="I42" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>2406</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -5155,6 +5983,12 @@
       <c r="H43" s="9" t="n">
         <v>2217</v>
       </c>
+      <c r="I43" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>2225</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -5187,6 +6021,12 @@
       <c r="H44" s="9" t="n">
         <v>6531</v>
       </c>
+      <c r="I44" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>6542</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -5223,6 +6063,12 @@
       <c r="H45" s="9" t="n">
         <v>1108</v>
       </c>
+      <c r="I45" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>1108</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -5259,6 +6105,12 @@
       <c r="H46" s="9" t="n">
         <v>7152</v>
       </c>
+      <c r="I46" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>7170</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -5291,6 +6143,12 @@
       <c r="H47" s="9" t="n">
         <v>15772</v>
       </c>
+      <c r="I47" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>15773</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -5323,6 +6181,12 @@
       <c r="H48" s="9" t="n">
         <v>3652</v>
       </c>
+      <c r="I48" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>3659</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -5359,6 +6223,12 @@
       <c r="H49" s="9" t="n">
         <v>2349</v>
       </c>
+      <c r="I49" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>2379</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -5391,6 +6261,12 @@
       <c r="H50" s="9" t="n">
         <v>1885</v>
       </c>
+      <c r="I50" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>1885</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -5423,6 +6299,12 @@
       <c r="H51" s="9" t="n">
         <v>7230</v>
       </c>
+      <c r="I51" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>7231</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -5455,6 +6337,12 @@
       <c r="H52" s="9" t="n">
         <v>1694</v>
       </c>
+      <c r="I52" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>1693</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -5491,6 +6379,12 @@
       <c r="H53" s="9" t="n">
         <v>9645</v>
       </c>
+      <c r="I53" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>9646</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -5527,6 +6421,12 @@
       <c r="H54" s="9" t="n">
         <v>796</v>
       </c>
+      <c r="I54" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>796</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -5559,6 +6459,12 @@
       <c r="H55" s="9" t="n">
         <v>796</v>
       </c>
+      <c r="I55" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>796</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -5591,6 +6497,12 @@
       <c r="H56" s="9" t="n">
         <v>710</v>
       </c>
+      <c r="I56" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>710</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -5627,6 +6539,12 @@
       <c r="H57" s="9" t="n">
         <v>433</v>
       </c>
+      <c r="I57" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>436</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -5663,6 +6581,12 @@
       <c r="H58" s="9" t="n">
         <v>203</v>
       </c>
+      <c r="I58" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>203</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -5699,6 +6623,12 @@
       <c r="H59" s="9" t="n">
         <v>657</v>
       </c>
+      <c r="I59" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>657</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -5735,6 +6665,12 @@
       <c r="H60" s="9" t="n">
         <v>361</v>
       </c>
+      <c r="I60" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>361</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -5771,6 +6707,12 @@
       <c r="H61" s="9" t="n">
         <v>2896</v>
       </c>
+      <c r="I61" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>2901</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -5807,6 +6749,12 @@
       <c r="H62" s="9" t="n">
         <v>583</v>
       </c>
+      <c r="I62" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>583</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -5843,6 +6791,12 @@
       <c r="H63" s="9" t="n">
         <v>9253</v>
       </c>
+      <c r="I63" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>9257</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -5879,6 +6833,12 @@
       <c r="H64" s="9" t="n">
         <v>1006</v>
       </c>
+      <c r="I64" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>1007</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -5915,6 +6875,12 @@
       <c r="H65" s="9" t="n">
         <v>3846</v>
       </c>
+      <c r="I65" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>3846</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -5951,6 +6917,12 @@
       <c r="H66" s="9" t="n">
         <v>4138</v>
       </c>
+      <c r="I66" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>4138</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -5983,6 +6955,12 @@
       <c r="H67" s="9" t="n">
         <v>10349</v>
       </c>
+      <c r="I67" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>10356</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -6015,6 +6993,12 @@
       <c r="H68" s="9" t="n">
         <v>4294</v>
       </c>
+      <c r="I68" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>4296</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -6047,6 +7031,12 @@
       <c r="H69" s="9" t="n">
         <v>2204</v>
       </c>
+      <c r="I69" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>2208</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -6083,6 +7073,12 @@
       <c r="H70" s="9" t="n">
         <v>280</v>
       </c>
+      <c r="I70" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>280</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -6119,6 +7115,12 @@
       <c r="H71" s="9" t="n">
         <v>6141</v>
       </c>
+      <c r="I71" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>6141</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -6151,6 +7153,12 @@
       <c r="H72" s="9" t="n">
         <v>3744</v>
       </c>
+      <c r="I72" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>3745</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -6183,6 +7191,12 @@
       <c r="H73" s="9" t="n">
         <v>1103</v>
       </c>
+      <c r="I73" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>1107</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -6219,6 +7233,12 @@
       <c r="H74" s="9" t="n">
         <v>9515</v>
       </c>
+      <c r="I74" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>9515</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -6251,6 +7271,12 @@
       <c r="H75" s="9" t="n">
         <v>16967</v>
       </c>
+      <c r="I75" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>16967</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -6287,6 +7313,12 @@
       <c r="H76" s="9" t="n">
         <v>8557</v>
       </c>
+      <c r="I76" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>8557</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -6323,6 +7355,12 @@
       <c r="H77" s="9" t="n">
         <v>2446</v>
       </c>
+      <c r="I77" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>2459</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -6355,6 +7393,12 @@
       <c r="H78" s="9" t="n">
         <v>111</v>
       </c>
+      <c r="I78" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>111</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -6391,6 +7435,12 @@
       <c r="H79" s="9" t="n">
         <v>175</v>
       </c>
+      <c r="I79" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -6423,6 +7473,12 @@
       <c r="H80" s="9" t="n">
         <v>1488</v>
       </c>
+      <c r="I80" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>1499</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -6459,6 +7515,16 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -6491,6 +7557,12 @@
       <c r="H82" s="9" t="n">
         <v>1428</v>
       </c>
+      <c r="I82" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>1436</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -6523,6 +7595,12 @@
       <c r="H83" s="9" t="n">
         <v>209</v>
       </c>
+      <c r="I83" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>209</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -6555,6 +7633,12 @@
       <c r="H84" s="9" t="n">
         <v>289</v>
       </c>
+      <c r="I84" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>290</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -6587,6 +7671,12 @@
       <c r="H85" s="9" t="n">
         <v>3940</v>
       </c>
+      <c r="I85" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>3945</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -6619,6 +7709,12 @@
       <c r="H86" s="9" t="n">
         <v>470</v>
       </c>
+      <c r="I86" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>475</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -6651,6 +7747,12 @@
       <c r="H87" s="9" t="n">
         <v>5259</v>
       </c>
+      <c r="I87" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>5267</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -6683,6 +7785,12 @@
       <c r="H88" s="9" t="n">
         <v>119</v>
       </c>
+      <c r="I88" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -6715,6 +7823,12 @@
       <c r="H89" s="9" t="n">
         <v>8386</v>
       </c>
+      <c r="I89" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>8387</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -6747,6 +7861,12 @@
       <c r="H90" s="9" t="n">
         <v>3607</v>
       </c>
+      <c r="I90" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>3621</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -6779,6 +7899,12 @@
       <c r="H91" s="9" t="n">
         <v>3229</v>
       </c>
+      <c r="I91" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>3229</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -6811,6 +7937,12 @@
       <c r="H92" s="9" t="n">
         <v>2878</v>
       </c>
+      <c r="I92" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>2881</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -6843,6 +7975,12 @@
       <c r="H93" s="9" t="n">
         <v>3770</v>
       </c>
+      <c r="I93" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>3770</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -6875,6 +8013,12 @@
       <c r="H94" s="9" t="n">
         <v>1624</v>
       </c>
+      <c r="I94" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>1624</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -6907,6 +8051,12 @@
       <c r="H95" s="9" t="n">
         <v>7496</v>
       </c>
+      <c r="I95" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>7497</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -6939,6 +8089,12 @@
       <c r="H96" s="9" t="n">
         <v>2835</v>
       </c>
+      <c r="I96" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>2835</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -6971,6 +8127,12 @@
       <c r="H97" s="9" t="n">
         <v>2888</v>
       </c>
+      <c r="I97" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>2876</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -7003,6 +8165,12 @@
       <c r="H98" s="9" t="n">
         <v>91</v>
       </c>
+      <c r="I98" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -7035,6 +8203,12 @@
       <c r="H99" s="9" t="n">
         <v>1691</v>
       </c>
+      <c r="I99" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>1691</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -7067,6 +8241,12 @@
       <c r="H100" s="9" t="n">
         <v>2203</v>
       </c>
+      <c r="I100" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>2203</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -7099,6 +8279,12 @@
       <c r="H101" s="9" t="n">
         <v>288</v>
       </c>
+      <c r="I101" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>288</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -7131,6 +8317,12 @@
       <c r="H102" s="9" t="n">
         <v>75</v>
       </c>
+      <c r="I102" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -7163,6 +8355,12 @@
       <c r="H103" s="9" t="n">
         <v>854</v>
       </c>
+      <c r="I103" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>856</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -7195,6 +8393,12 @@
       <c r="H104" s="9" t="n">
         <v>427</v>
       </c>
+      <c r="I104" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>427</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -7227,6 +8431,12 @@
       <c r="H105" s="9" t="n">
         <v>887</v>
       </c>
+      <c r="I105" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>888</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -7259,6 +8469,12 @@
       <c r="H106" s="9" t="n">
         <v>456</v>
       </c>
+      <c r="I106" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>456</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -7291,6 +8507,12 @@
       <c r="H107" s="9" t="n">
         <v>1517</v>
       </c>
+      <c r="I107" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>1518</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -7323,6 +8545,12 @@
       <c r="H108" s="9" t="n">
         <v>1866</v>
       </c>
+      <c r="I108" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>1868</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -7353,6 +8581,12 @@
         <v>3.6</v>
       </c>
       <c r="H109" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="I109" s="9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J109" s="9" t="n">
         <v>64</v>
       </c>
     </row>
@@ -7367,7 +8601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7390,6 +8624,12 @@
       <c r="H1" s="6" t="n">
         <v>46301</v>
       </c>
+      <c r="I1" s="6" t="n">
+        <v>46302</v>
+      </c>
+      <c r="J1" s="6" t="n">
+        <v>46302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -7428,6 +8668,16 @@
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -7468,6 +8718,12 @@
       <c r="H3" s="9" t="n">
         <v>6991</v>
       </c>
+      <c r="I3" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>6996</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -7504,6 +8760,12 @@
       <c r="H4" s="9" t="n">
         <v>1725</v>
       </c>
+      <c r="I4" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>1718</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -7540,6 +8802,12 @@
       <c r="H5" s="9" t="n">
         <v>3417</v>
       </c>
+      <c r="I5" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>3417</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -7576,6 +8844,12 @@
       <c r="H6" s="9" t="n">
         <v>1351</v>
       </c>
+      <c r="I6" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>1351</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -7612,6 +8886,12 @@
       <c r="H7" s="9" t="n">
         <v>1110</v>
       </c>
+      <c r="I7" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>1110</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -7648,6 +8928,12 @@
       <c r="H8" s="9" t="n">
         <v>3369</v>
       </c>
+      <c r="I8" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>3371</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -7684,6 +8970,12 @@
       <c r="H9" s="9" t="n">
         <v>1971</v>
       </c>
+      <c r="I9" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>1971</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -7720,6 +9012,12 @@
       <c r="H10" s="9" t="n">
         <v>1197</v>
       </c>
+      <c r="I10" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>1199</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -7756,6 +9054,12 @@
       <c r="H11" s="9" t="n">
         <v>812</v>
       </c>
+      <c r="I11" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>812</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -7788,6 +9092,12 @@
       <c r="H12" s="9" t="n">
         <v>3417</v>
       </c>
+      <c r="I12" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>3417</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -7824,6 +9134,12 @@
       <c r="H13" s="9" t="n">
         <v>406</v>
       </c>
+      <c r="I13" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>406</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -7860,6 +9176,12 @@
       <c r="H14" s="9" t="n">
         <v>3457</v>
       </c>
+      <c r="I14" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>3461</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -7896,6 +9218,12 @@
       <c r="H15" s="9" t="n">
         <v>1985</v>
       </c>
+      <c r="I15" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>1987</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -7932,6 +9260,12 @@
       <c r="H16" s="9" t="n">
         <v>1337</v>
       </c>
+      <c r="I16" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>1337</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -7968,6 +9302,12 @@
       <c r="H17" s="9" t="n">
         <v>1332</v>
       </c>
+      <c r="I17" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>1334</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -8004,6 +9344,12 @@
       <c r="H18" s="9" t="n">
         <v>4495</v>
       </c>
+      <c r="I18" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>4493</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -8040,6 +9386,12 @@
       <c r="H19" s="9" t="n">
         <v>1665</v>
       </c>
+      <c r="I19" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>1667</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -8076,6 +9428,12 @@
       <c r="H20" s="9" t="n">
         <v>4371</v>
       </c>
+      <c r="I20" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>4374</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -8108,6 +9466,12 @@
       <c r="H21" s="9" t="n">
         <v>3849</v>
       </c>
+      <c r="I21" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>3855</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -8140,6 +9504,12 @@
       <c r="H22" s="9" t="n">
         <v>86</v>
       </c>
+      <c r="I22" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -8172,6 +9542,12 @@
       <c r="H23" s="9" t="n">
         <v>443</v>
       </c>
+      <c r="I23" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>443</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -8204,6 +9580,12 @@
       <c r="H24" s="9" t="n">
         <v>1684</v>
       </c>
+      <c r="I24" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>1684</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -8236,6 +9618,12 @@
       <c r="H25" s="9" t="n">
         <v>3363</v>
       </c>
+      <c r="I25" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>3364</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -8268,6 +9656,12 @@
       <c r="H26" s="9" t="n">
         <v>1767</v>
       </c>
+      <c r="I26" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>1767</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -8300,6 +9694,12 @@
       <c r="H27" s="9" t="n">
         <v>530</v>
       </c>
+      <c r="I27" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>530</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -8332,6 +9732,12 @@
       <c r="H28" s="9" t="n">
         <v>1325</v>
       </c>
+      <c r="I28" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>1325</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -8364,6 +9770,12 @@
       <c r="H29" s="9" t="n">
         <v>642</v>
       </c>
+      <c r="I29" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>642</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -8396,6 +9808,12 @@
       <c r="H30" s="9" t="n">
         <v>35</v>
       </c>
+      <c r="I30" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -8428,6 +9846,12 @@
       <c r="H31" s="9" t="n">
         <v>1323</v>
       </c>
+      <c r="I31" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>1323</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -8460,6 +9884,12 @@
       <c r="H32" s="9" t="n">
         <v>1427</v>
       </c>
+      <c r="I32" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>1427</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -8492,6 +9922,12 @@
       <c r="H33" s="9" t="n">
         <v>1335</v>
       </c>
+      <c r="I33" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>1335</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -8524,6 +9960,12 @@
       <c r="H34" s="9" t="n">
         <v>190</v>
       </c>
+      <c r="I34" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -8556,6 +9998,12 @@
       <c r="H35" s="9" t="n">
         <v>127</v>
       </c>
+      <c r="I35" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -8588,6 +10036,12 @@
       <c r="H36" s="9" t="n">
         <v>994</v>
       </c>
+      <c r="I36" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>994</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -8620,6 +10074,12 @@
       <c r="H37" s="9" t="n">
         <v>205</v>
       </c>
+      <c r="I37" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>205</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -8652,6 +10112,12 @@
       <c r="H38" s="9" t="n">
         <v>211</v>
       </c>
+      <c r="I38" s="9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>212</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -8684,6 +10150,12 @@
       <c r="H39" s="9" t="n">
         <v>855</v>
       </c>
+      <c r="I39" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>857</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -8716,6 +10188,12 @@
       <c r="H40" s="9" t="n">
         <v>2234</v>
       </c>
+      <c r="I40" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>2233</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -8748,6 +10226,12 @@
       <c r="H41" s="9" t="n">
         <v>450</v>
       </c>
+      <c r="I41" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -8780,6 +10264,12 @@
       <c r="H42" s="9" t="n">
         <v>1584</v>
       </c>
+      <c r="I42" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>1585</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -8812,6 +10302,12 @@
       <c r="H43" s="9" t="n">
         <v>1165</v>
       </c>
+      <c r="I43" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>1165</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -8844,6 +10340,12 @@
       <c r="H44" s="9" t="n">
         <v>474</v>
       </c>
+      <c r="I44" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>474</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -8876,6 +10378,12 @@
       <c r="H45" s="9" t="n">
         <v>371</v>
       </c>
+      <c r="I45" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>394</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -8908,6 +10416,12 @@
       <c r="H46" s="9" t="n">
         <v>1042</v>
       </c>
+      <c r="I46" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>1043</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -8940,6 +10454,12 @@
       <c r="H47" s="9" t="n">
         <v>2567</v>
       </c>
+      <c r="I47" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>2568</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -8972,6 +10492,12 @@
       <c r="H48" s="9" t="n">
         <v>1429</v>
       </c>
+      <c r="I48" s="9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>1429</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -9004,6 +10530,12 @@
       <c r="H49" s="9" t="n">
         <v>1420</v>
       </c>
+      <c r="I49" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>1420</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -9036,6 +10568,12 @@
       <c r="H50" s="9" t="n">
         <v>1550</v>
       </c>
+      <c r="I50" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>1550</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -9068,6 +10606,12 @@
       <c r="H51" s="9" t="n">
         <v>2806</v>
       </c>
+      <c r="I51" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>2806</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -9100,6 +10644,12 @@
       <c r="H52" s="9" t="n">
         <v>742</v>
       </c>
+      <c r="I52" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>744</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -9132,6 +10682,12 @@
       <c r="H53" s="9" t="n">
         <v>1226</v>
       </c>
+      <c r="I53" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>1229</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -9164,6 +10720,12 @@
       <c r="H54" s="9" t="n">
         <v>673</v>
       </c>
+      <c r="I54" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>673</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -9195,6 +10757,12 @@
       </c>
       <c r="H55" s="9" t="n">
         <v>423</v>
+      </c>
+      <c r="I55" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>424</v>
       </c>
     </row>
     <row r="56">
@@ -9442,7 +11010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9465,6 +11033,12 @@
       <c r="H1" s="6" t="n">
         <v>46301</v>
       </c>
+      <c r="I1" s="6" t="n">
+        <v>46302</v>
+      </c>
+      <c r="J1" s="6" t="n">
+        <v>46302</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -9503,6 +11077,16 @@
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -9539,6 +11123,12 @@
       <c r="H3" s="9" t="n">
         <v>4576</v>
       </c>
+      <c r="I3" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>4573</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -9571,6 +11161,12 @@
       <c r="H4" s="9" t="n">
         <v>1229</v>
       </c>
+      <c r="I4" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>1230</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -9603,6 +11199,12 @@
       <c r="H5" s="9" t="n">
         <v>460</v>
       </c>
+      <c r="I5" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>460</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -9635,6 +11237,12 @@
       <c r="H6" s="9" t="n">
         <v>11588</v>
       </c>
+      <c r="I6" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>11587</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -9667,6 +11275,12 @@
       <c r="H7" s="9" t="n">
         <v>2050</v>
       </c>
+      <c r="I7" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -9699,6 +11313,12 @@
       <c r="H8" s="9" t="n">
         <v>918</v>
       </c>
+      <c r="I8" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>918</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -9731,6 +11351,12 @@
       <c r="H9" s="9" t="n">
         <v>1604</v>
       </c>
+      <c r="I9" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>1604</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -9763,6 +11389,12 @@
       <c r="H10" s="9" t="n">
         <v>2023</v>
       </c>
+      <c r="I10" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>2040</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -9795,6 +11427,12 @@
       <c r="H11" s="9" t="n">
         <v>3082</v>
       </c>
+      <c r="I11" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>3082</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -9827,6 +11465,12 @@
       <c r="H12" s="9" t="n">
         <v>3624</v>
       </c>
+      <c r="I12" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>3625</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -9859,6 +11503,12 @@
       <c r="H13" s="9" t="n">
         <v>21264</v>
       </c>
+      <c r="I13" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>21267</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -9891,6 +11541,12 @@
       <c r="H14" s="9" t="n">
         <v>2946</v>
       </c>
+      <c r="I14" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>2947</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -9923,6 +11579,12 @@
       <c r="H15" s="9" t="n">
         <v>4204</v>
       </c>
+      <c r="I15" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>4204</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -9955,6 +11617,12 @@
       <c r="H16" s="9" t="n">
         <v>2387</v>
       </c>
+      <c r="I16" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>2387</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -9987,6 +11655,12 @@
       <c r="H17" s="9" t="n">
         <v>4</v>
       </c>
+      <c r="I17" s="9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -10019,6 +11693,12 @@
       <c r="H18" s="9" t="n">
         <v>12119</v>
       </c>
+      <c r="I18" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>12127</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -10051,6 +11731,12 @@
       <c r="H19" s="9" t="n">
         <v>3076</v>
       </c>
+      <c r="I19" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>3079</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -10083,6 +11769,12 @@
       <c r="H20" s="9" t="n">
         <v>9245</v>
       </c>
+      <c r="I20" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>9246</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -10115,6 +11807,12 @@
       <c r="H21" s="9" t="n">
         <v>8</v>
       </c>
+      <c r="I21" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -10147,6 +11845,12 @@
       <c r="H22" s="9" t="n">
         <v>6136</v>
       </c>
+      <c r="I22" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>6136</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -10179,6 +11883,12 @@
       <c r="H23" s="9" t="n">
         <v>1728</v>
       </c>
+      <c r="I23" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>1745</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -10211,6 +11921,12 @@
       <c r="H24" s="9" t="n">
         <v>1060</v>
       </c>
+      <c r="I24" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>1060</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -10243,6 +11959,12 @@
       <c r="H25" s="9" t="n">
         <v>2053</v>
       </c>
+      <c r="I25" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>2053</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -10275,6 +11997,12 @@
       <c r="H26" s="9" t="n">
         <v>2776</v>
       </c>
+      <c r="I26" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>2776</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -10307,6 +12035,12 @@
       <c r="H27" s="9" t="n">
         <v>11070</v>
       </c>
+      <c r="I27" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>11079</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -10339,6 +12073,12 @@
       <c r="H28" s="9" t="n">
         <v>5490</v>
       </c>
+      <c r="I28" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>5490</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -10371,6 +12111,12 @@
       <c r="H29" s="9" t="n">
         <v>4008</v>
       </c>
+      <c r="I29" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>4012</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -10403,6 +12149,12 @@
       <c r="H30" s="9" t="n">
         <v>1579</v>
       </c>
+      <c r="I30" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>1579</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -10435,6 +12187,12 @@
       <c r="H31" s="9" t="n">
         <v>1579</v>
       </c>
+      <c r="I31" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>1579</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -10467,6 +12225,12 @@
       <c r="H32" s="9" t="n">
         <v>2810</v>
       </c>
+      <c r="I32" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>2810</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -10499,6 +12263,12 @@
       <c r="H33" s="9" t="n">
         <v>18967</v>
       </c>
+      <c r="I33" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>18970</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -10531,6 +12301,12 @@
       <c r="H34" s="9" t="n">
         <v>39678</v>
       </c>
+      <c r="I34" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>39685</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -10563,6 +12339,12 @@
       <c r="H35" s="9" t="n">
         <v>5228</v>
       </c>
+      <c r="I35" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>5228</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -10595,6 +12377,12 @@
       <c r="H36" s="9" t="n">
         <v>10373</v>
       </c>
+      <c r="I36" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>10379</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -10627,6 +12415,12 @@
       <c r="H37" s="9" t="n">
         <v>7405</v>
       </c>
+      <c r="I37" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>7404</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -10659,6 +12453,12 @@
       <c r="H38" s="9" t="n">
         <v>539</v>
       </c>
+      <c r="I38" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>539</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -10691,6 +12491,12 @@
       <c r="H39" s="9" t="n">
         <v>1124</v>
       </c>
+      <c r="I39" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>1124</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -10723,6 +12529,12 @@
       <c r="H40" s="9" t="n">
         <v>539</v>
       </c>
+      <c r="I40" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>539</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -10755,6 +12567,12 @@
       <c r="H41" s="9" t="n">
         <v>2617</v>
       </c>
+      <c r="I41" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>2619</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -10787,6 +12605,12 @@
       <c r="H42" s="9" t="n">
         <v>1442</v>
       </c>
+      <c r="I42" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>1443</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -10819,6 +12643,12 @@
       <c r="H43" s="9" t="n">
         <v>955</v>
       </c>
+      <c r="I43" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>955</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -10851,6 +12681,12 @@
       <c r="H44" s="9" t="n">
         <v>4166</v>
       </c>
+      <c r="I44" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>4177</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -10883,6 +12719,12 @@
       <c r="H45" s="9" t="n">
         <v>3484</v>
       </c>
+      <c r="I45" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>3485</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -10915,6 +12757,12 @@
       <c r="H46" s="9" t="n">
         <v>7886</v>
       </c>
+      <c r="I46" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>7886</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -10947,6 +12795,12 @@
       <c r="H47" s="9" t="n">
         <v>6136</v>
       </c>
+      <c r="I47" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>6136</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -10979,6 +12833,12 @@
       <c r="H48" s="9" t="n">
         <v>983</v>
       </c>
+      <c r="I48" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>983</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -11011,6 +12871,12 @@
       <c r="H49" s="9" t="n">
         <v>3643</v>
       </c>
+      <c r="I49" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>3645</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -11043,6 +12909,12 @@
       <c r="H50" s="9" t="n">
         <v>168</v>
       </c>
+      <c r="I50" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>171</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -11075,6 +12947,12 @@
       <c r="H51" s="9" t="n">
         <v>4119</v>
       </c>
+      <c r="I51" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>4120</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -11107,6 +12985,12 @@
       <c r="H52" s="9" t="n">
         <v>315</v>
       </c>
+      <c r="I52" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>298</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -11139,6 +13023,12 @@
       <c r="H53" s="9" t="n">
         <v>139</v>
       </c>
+      <c r="I53" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -11171,6 +13061,12 @@
       <c r="H54" s="9" t="n">
         <v>4119</v>
       </c>
+      <c r="I54" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>4120</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -11203,6 +13099,12 @@
       <c r="H55" s="9" t="n">
         <v>55</v>
       </c>
+      <c r="I55" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -11235,6 +13137,12 @@
       <c r="H56" s="9" t="n">
         <v>493</v>
       </c>
+      <c r="I56" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>493</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -11267,6 +13175,12 @@
       <c r="H57" s="9" t="n">
         <v>7852</v>
       </c>
+      <c r="I57" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>7852</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -11299,6 +13213,12 @@
       <c r="H58" s="9" t="n">
         <v>4017</v>
       </c>
+      <c r="I58" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>4017</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -11331,6 +13251,12 @@
       <c r="H59" s="9" t="n">
         <v>2857</v>
       </c>
+      <c r="I59" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>2870</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -11363,6 +13289,12 @@
       <c r="H60" s="9" t="n">
         <v>2251</v>
       </c>
+      <c r="I60" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>2251</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -11395,6 +13327,12 @@
       <c r="H61" s="9" t="n">
         <v>7822</v>
       </c>
+      <c r="I61" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>7824</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -11427,6 +13365,12 @@
       <c r="H62" s="9" t="n">
         <v>3615</v>
       </c>
+      <c r="I62" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>3616</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -11459,6 +13403,12 @@
       <c r="H63" s="9" t="n">
         <v>4769</v>
       </c>
+      <c r="I63" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>4769</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -11491,6 +13441,12 @@
       <c r="H64" s="9" t="n">
         <v>2626</v>
       </c>
+      <c r="I64" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>2626</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -11523,6 +13479,12 @@
       <c r="H65" s="9" t="n">
         <v>2900</v>
       </c>
+      <c r="I65" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>2901</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -11555,6 +13517,12 @@
       <c r="H66" s="9" t="n">
         <v>6445</v>
       </c>
+      <c r="I66" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>6445</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -11587,6 +13555,12 @@
       <c r="H67" s="9" t="n">
         <v>781</v>
       </c>
+      <c r="I67" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>781</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -11619,6 +13593,12 @@
       <c r="H68" s="9" t="n">
         <v>19105</v>
       </c>
+      <c r="I68" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>19107</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -11651,6 +13631,12 @@
       <c r="H69" s="9" t="n">
         <v>2916</v>
       </c>
+      <c r="I69" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>2918</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -11683,6 +13669,12 @@
       <c r="H70" s="9" t="n">
         <v>2629</v>
       </c>
+      <c r="I70" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -11715,6 +13707,12 @@
       <c r="H71" s="9" t="n">
         <v>1193</v>
       </c>
+      <c r="I71" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -11747,6 +13745,12 @@
       <c r="H72" s="9" t="n">
         <v>4165</v>
       </c>
+      <c r="I72" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>4166</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -11779,6 +13783,12 @@
       <c r="H73" s="9" t="n">
         <v>3863</v>
       </c>
+      <c r="I73" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>3864</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -11811,6 +13821,12 @@
       <c r="H74" s="9" t="n">
         <v>754</v>
       </c>
+      <c r="I74" s="9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>754</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -11843,6 +13859,12 @@
       <c r="H75" s="9" t="n">
         <v>4656</v>
       </c>
+      <c r="I75" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>4656</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -11875,6 +13897,12 @@
       <c r="H76" s="9" t="n">
         <v>5287</v>
       </c>
+      <c r="I76" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>5287</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -11907,6 +13935,12 @@
       <c r="H77" s="9" t="n">
         <v>159</v>
       </c>
+      <c r="I77" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -11939,6 +13973,12 @@
       <c r="H78" s="9" t="n">
         <v>1131</v>
       </c>
+      <c r="I78" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>1131</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -11971,6 +14011,12 @@
       <c r="H79" s="9" t="n">
         <v>634</v>
       </c>
+      <c r="I79" s="9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>634</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -12003,6 +14049,12 @@
       <c r="H80" s="9" t="n">
         <v>1187</v>
       </c>
+      <c r="I80" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -12035,6 +14087,12 @@
       <c r="H81" s="9" t="n">
         <v>1554</v>
       </c>
+      <c r="I81" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>1561</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -12067,6 +14125,12 @@
       <c r="H82" s="9" t="n">
         <v>11739</v>
       </c>
+      <c r="I82" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>11741</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -12099,6 +14163,12 @@
       <c r="H83" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="I83" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -12131,6 +14201,12 @@
       <c r="H84" s="9" t="n">
         <v>5930</v>
       </c>
+      <c r="I84" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>5931</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -12163,6 +14239,12 @@
       <c r="H85" s="9" t="n">
         <v>3263</v>
       </c>
+      <c r="I85" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>3263</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -12195,6 +14277,12 @@
       <c r="H86" s="9" t="n">
         <v>10418</v>
       </c>
+      <c r="I86" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>10429</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -12227,6 +14315,12 @@
       <c r="H87" s="9" t="n">
         <v>4151</v>
       </c>
+      <c r="I87" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>4152</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -12259,6 +14353,12 @@
       <c r="H88" s="9" t="n">
         <v>2998</v>
       </c>
+      <c r="I88" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>2998</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -12291,6 +14391,12 @@
       <c r="H89" s="9" t="n">
         <v>1296</v>
       </c>
+      <c r="I89" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>1296</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -12323,6 +14429,12 @@
       <c r="H90" s="9" t="n">
         <v>2234</v>
       </c>
+      <c r="I90" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>2235</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -12355,6 +14467,12 @@
       <c r="H91" s="9" t="n">
         <v>7975</v>
       </c>
+      <c r="I91" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>7976</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -12387,6 +14505,12 @@
       <c r="H92" s="9" t="n">
         <v>784</v>
       </c>
+      <c r="I92" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>783</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -12419,6 +14543,12 @@
       <c r="H93" s="9" t="n">
         <v>788</v>
       </c>
+      <c r="I93" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>789</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -12451,6 +14581,12 @@
       <c r="H94" s="9" t="n">
         <v>2595</v>
       </c>
+      <c r="I94" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>2595</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -12483,6 +14619,12 @@
       <c r="H95" s="9" t="n">
         <v>1677</v>
       </c>
+      <c r="I95" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>1678</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -12515,6 +14657,12 @@
       <c r="H96" s="9" t="n">
         <v>6439</v>
       </c>
+      <c r="I96" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>6439</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -12547,6 +14695,12 @@
       <c r="H97" s="9" t="n">
         <v>2315</v>
       </c>
+      <c r="I97" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>2315</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -12579,6 +14733,12 @@
       <c r="H98" s="9" t="n">
         <v>1937</v>
       </c>
+      <c r="I98" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>1938</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -12611,6 +14771,12 @@
       <c r="H99" s="9" t="n">
         <v>5578</v>
       </c>
+      <c r="I99" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>5579</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -12643,6 +14809,12 @@
       <c r="H100" s="9" t="n">
         <v>17781</v>
       </c>
+      <c r="I100" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>17788</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -12675,6 +14847,12 @@
       <c r="H101" s="9" t="n">
         <v>6159</v>
       </c>
+      <c r="I101" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>6170</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -12707,6 +14885,12 @@
       <c r="H102" s="9" t="n">
         <v>5283</v>
       </c>
+      <c r="I102" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>5283</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
@@ -12739,6 +14923,12 @@
       <c r="H103" s="9" t="n">
         <v>1174</v>
       </c>
+      <c r="I103" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>1175</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n">
@@ -12771,6 +14961,12 @@
       <c r="H104" s="9" t="n">
         <v>4076</v>
       </c>
+      <c r="I104" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>4077</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n">
@@ -12803,6 +14999,12 @@
       <c r="H105" s="9" t="n">
         <v>1174</v>
       </c>
+      <c r="I105" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>1175</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n">
@@ -12835,6 +15037,12 @@
       <c r="H106" s="9" t="n">
         <v>10974</v>
       </c>
+      <c r="I106" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>10975</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n">
@@ -12867,6 +15075,12 @@
       <c r="H107" s="9" t="n">
         <v>3159</v>
       </c>
+      <c r="I107" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>3159</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n">
@@ -12899,6 +15113,12 @@
       <c r="H108" s="9" t="n">
         <v>3056</v>
       </c>
+      <c r="I108" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>3058</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="n">
@@ -12931,6 +15151,12 @@
       <c r="H109" s="9" t="n">
         <v>2620</v>
       </c>
+      <c r="I109" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>2623</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="n">
@@ -12963,6 +15189,12 @@
       <c r="H110" s="9" t="n">
         <v>1879</v>
       </c>
+      <c r="I110" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>1879</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n">
@@ -12995,6 +15227,12 @@
       <c r="H111" s="9" t="n">
         <v>1196</v>
       </c>
+      <c r="I111" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>1196</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n">
@@ -13027,6 +15265,12 @@
       <c r="H112" s="9" t="n">
         <v>2450</v>
       </c>
+      <c r="I112" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>2452</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n">
@@ -13058,6 +15302,12 @@
       </c>
       <c r="H113" s="9" t="n">
         <v>2630</v>
+      </c>
+      <c r="I113" s="9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>2640</v>
       </c>
     </row>
   </sheetData>
@@ -13071,7 +15321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13094,6 +15344,12 @@
       <c r="H1" s="6" t="n">
         <v>46301</v>
       </c>
+      <c r="I1" s="6" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J1" s="6" t="n">
+        <v>46303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -13132,6 +15388,16 @@
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -13168,6 +15434,12 @@
       <c r="H3" s="9" t="n">
         <v>14379</v>
       </c>
+      <c r="I3" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>14379</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -13200,6 +15472,12 @@
       <c r="H4" s="9" t="n">
         <v>1199</v>
       </c>
+      <c r="I4" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>1201</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -13232,6 +15510,12 @@
       <c r="H5" s="9" t="n">
         <v>15</v>
       </c>
+      <c r="I5" s="9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -13264,6 +15548,12 @@
       <c r="H6" s="9" t="n">
         <v>62</v>
       </c>
+      <c r="I6" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -13296,6 +15586,12 @@
       <c r="H7" s="9" t="n">
         <v>4837</v>
       </c>
+      <c r="I7" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>4837</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -13328,6 +15624,12 @@
       <c r="H8" s="9" t="n">
         <v>2067</v>
       </c>
+      <c r="I8" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>2067</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -13360,6 +15662,12 @@
       <c r="H9" s="9" t="n">
         <v>5780</v>
       </c>
+      <c r="I9" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>5781</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -13392,6 +15700,12 @@
       <c r="H10" s="9" t="n">
         <v>6554</v>
       </c>
+      <c r="I10" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>6557</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -13424,6 +15738,12 @@
       <c r="H11" s="9" t="n">
         <v>10574</v>
       </c>
+      <c r="I11" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>10575</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -13456,6 +15776,12 @@
       <c r="H12" s="9" t="n">
         <v>12233</v>
       </c>
+      <c r="I12" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>12235</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -13488,6 +15814,12 @@
       <c r="H13" s="9" t="n">
         <v>10698</v>
       </c>
+      <c r="I13" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>10700</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -13520,6 +15852,12 @@
       <c r="H14" s="9" t="n">
         <v>6810</v>
       </c>
+      <c r="I14" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>6811</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -13552,6 +15890,12 @@
       <c r="H15" s="9" t="n">
         <v>3607</v>
       </c>
+      <c r="I15" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>3606</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -13584,6 +15928,12 @@
       <c r="H16" s="9" t="n">
         <v>4502</v>
       </c>
+      <c r="I16" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>4502</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -13616,6 +15966,12 @@
       <c r="H17" s="9" t="n">
         <v>878</v>
       </c>
+      <c r="I17" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>878</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -13648,6 +16004,12 @@
       <c r="H18" s="9" t="n">
         <v>19723</v>
       </c>
+      <c r="I18" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>19722</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -13680,6 +16042,12 @@
       <c r="H19" s="9" t="n">
         <v>2019</v>
       </c>
+      <c r="I19" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>2019</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -13712,6 +16080,12 @@
       <c r="H20" s="9" t="n">
         <v>2023</v>
       </c>
+      <c r="I20" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>2032</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -13744,6 +16118,12 @@
       <c r="H21" s="9" t="n">
         <v>8782</v>
       </c>
+      <c r="I21" s="9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>8782</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -13776,6 +16156,12 @@
       <c r="H22" s="9" t="n">
         <v>1118</v>
       </c>
+      <c r="I22" s="9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>1118</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -13808,6 +16194,12 @@
       <c r="H23" s="9" t="n">
         <v>677</v>
       </c>
+      <c r="I23" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>677</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -13839,6 +16231,12 @@
       </c>
       <c r="H24" s="9" t="n">
         <v>1820</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>1821</v>
       </c>
     </row>
   </sheetData>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bikanervala GGN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="India BV" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="International BV" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haldiram India" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OM Sweets India" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Other Outlets" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Bikanervala GGN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Competitors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="India BV" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="International BV" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Haldiram India" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="OM Sweets India" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Other Outlets" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,8 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +47,19 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +70,30 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -115,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -143,6 +180,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -508,8 +560,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -525,6 +577,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="11" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H1" s="11" t="n">
+        <v>46303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -555,6 +613,16 @@
       <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -587,6 +655,12 @@
           <t>https://share.google/JV7XDH4ryWmQNPfVY</t>
         </is>
       </c>
+      <c r="G3" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>4871</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -617,6 +691,12 @@
           <t>https://share.google/AXcgrOXWWfQtoSOkz</t>
         </is>
       </c>
+      <c r="G4" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>15768</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -647,6 +727,12 @@
           <t>https://share.google/Lq1yf4rveBX5BWyts</t>
         </is>
       </c>
+      <c r="G5" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>5546</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -677,6 +763,12 @@
           <t>https://share.google/5iiO04ZTn35j8E5HB</t>
         </is>
       </c>
+      <c r="G6" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>6544</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -707,6 +799,12 @@
           <t>https://share.google/iNagaqHoCbBOIvV0x</t>
         </is>
       </c>
+      <c r="G7" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>2414</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -737,6 +835,12 @@
           <t>https://share.google/S4Kwkg9xEW0S2j7a0</t>
         </is>
       </c>
+      <c r="G8" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>7187</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -767,6 +871,12 @@
           <t>https://share.google/NS8T7gwZSlKSNr3UP</t>
         </is>
       </c>
+      <c r="G9" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>3666</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -797,6 +907,12 @@
           <t>https://share.google/Xmyef4OwQmXyWCFN0</t>
         </is>
       </c>
+      <c r="G10" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>2768</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -827,6 +943,12 @@
           <t>https://share.google/6khAtgqK72w0kjN0Q</t>
         </is>
       </c>
+      <c r="G11" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>1115</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -857,6 +979,12 @@
           <t>https://share.google/CgukSORsdWkszVRvP</t>
         </is>
       </c>
+      <c r="G12" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>1107</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -887,6 +1015,12 @@
           <t>https://share.google/BNfINmH1QbNZhf7ox</t>
         </is>
       </c>
+      <c r="G13" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>2222</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -917,6 +1051,12 @@
           <t>https://share.google/LJxUW77APw08Vr9a0</t>
         </is>
       </c>
+      <c r="G14" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>2379</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -947,6 +1087,12 @@
           <t>https://share.google/LAZMqwdryXVTeQkgt</t>
         </is>
       </c>
+      <c r="G15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>2598</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -977,6 +1123,12 @@
           <t>https://share.google/lkP8lqhdoKZRzyal3</t>
         </is>
       </c>
+      <c r="G16" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>893</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -1007,6 +1159,12 @@
           <t>https://share.google/255ZPlPOiTGMhDzy0</t>
         </is>
       </c>
+      <c r="G17" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>1332</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -1037,6 +1195,12 @@
           <t>https://share.google/9TqthrgcK6VnEH9Kh</t>
         </is>
       </c>
+      <c r="G18" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>455</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -1067,6 +1231,12 @@
           <t>https://share.google/uqXvcL4esuwjgcsRz</t>
         </is>
       </c>
+      <c r="G19" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>914</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -1097,6 +1267,12 @@
           <t>https://share.google/E5KGOYYKX6YqD07hf</t>
         </is>
       </c>
+      <c r="G20" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>1099</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -1127,6 +1303,12 @@
           <t>https://share.google/ooNGpI4Ewi9Zt5t02</t>
         </is>
       </c>
+      <c r="G21" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>787</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -1157,6 +1339,12 @@
           <t>https://share.google/Z2RQtKISxQhQWQSl4</t>
         </is>
       </c>
+      <c r="G22" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>659</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -1187,6 +1375,12 @@
           <t>https://share.google/grSJuehxs8v7sVOVt</t>
         </is>
       </c>
+      <c r="G23" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>695</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -1217,6 +1411,12 @@
           <t>https://share.google/V1f6JY6CBgPW0eoIg</t>
         </is>
       </c>
+      <c r="G24" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>1424</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -1247,6 +1447,12 @@
           <t>https://share.google/r13AfGhfeAFwXti2i</t>
         </is>
       </c>
+      <c r="G25" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>706</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1272,6 +1478,12 @@
         <is>
           <t>https://share.google/e0rEvKWJDcji81RKF</t>
         </is>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -1285,8 +1497,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -1303,6 +1515,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="H1" s="11" t="n">
+        <v>46303</v>
+      </c>
+      <c r="I1" s="11" t="n">
+        <v>46303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -1338,6 +1556,16 @@
       <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Pairs</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -1375,6 +1603,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H3" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>695</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -1410,6 +1644,12 @@
           <t>#2</t>
         </is>
       </c>
+      <c r="H4" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -1445,6 +1685,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H5" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>787</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1480,6 +1726,12 @@
           <t>#4</t>
         </is>
       </c>
+      <c r="H6" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>3864</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1515,6 +1767,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H7" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>659</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1550,6 +1808,12 @@
           <t>Pair 3</t>
         </is>
       </c>
+      <c r="H8" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>893</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1585,6 +1849,12 @@
           <t>#7</t>
         </is>
       </c>
+      <c r="H9" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>3265</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1620,6 +1890,12 @@
           <t>#8</t>
         </is>
       </c>
+      <c r="H10" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>19721</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1655,6 +1931,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H11" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>1424</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1690,6 +1972,12 @@
           <t>#10</t>
         </is>
       </c>
+      <c r="H12" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -1725,6 +2013,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H13" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>755</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -1760,6 +2054,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H14" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>6811</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1795,6 +2095,12 @@
           <t>Pair 3</t>
         </is>
       </c>
+      <c r="H15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>7187</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1830,6 +2136,12 @@
           <t>#14</t>
         </is>
       </c>
+      <c r="H16" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>535</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -1865,6 +2177,12 @@
           <t>#15</t>
         </is>
       </c>
+      <c r="H17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>1822</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -1900,6 +2218,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H18" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>4504</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -1935,6 +2259,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>6544</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -1970,6 +2300,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H20" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>2768</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -2005,6 +2341,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H21" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>15768</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2040,6 +2382,12 @@
           <t>#20</t>
         </is>
       </c>
+      <c r="H22" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>5933</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -2075,6 +2423,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H23" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>10577</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -2110,6 +2464,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H24" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>12236</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -2145,6 +2505,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H25" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>2006</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -2180,6 +2546,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H26" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -2215,6 +2587,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H27" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>3666</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -2250,6 +2628,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H28" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>3606</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -2285,6 +2669,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H29" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>4871</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -2320,6 +2710,12 @@
           <t>#28</t>
         </is>
       </c>
+      <c r="H30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>1160</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -2355,6 +2751,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H31" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>2222</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -2390,6 +2792,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H32" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>1043</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -2425,6 +2833,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H33" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>5546</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -2460,6 +2874,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H34" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>1131</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -2495,6 +2915,12 @@
           <t>#33</t>
         </is>
       </c>
+      <c r="H35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>4837</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -2530,6 +2956,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H36" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>1107</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -2565,6 +2997,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H37" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>2414</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -2600,6 +3038,12 @@
           <t>#36</t>
         </is>
       </c>
+      <c r="H38" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>281</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -2635,6 +3079,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H39" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>2598</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -2670,6 +3120,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H40" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>455</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -2705,6 +3161,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H41" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>1115</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -2740,6 +3202,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H42" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I42" s="14" t="n">
+        <v>11744</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -2775,6 +3243,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H43" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>1099</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -2810,6 +3284,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H44" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>1332</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -2845,6 +3325,12 @@
           <t>#43</t>
         </is>
       </c>
+      <c r="H45" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -2880,6 +3366,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H46" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I46" s="14" t="n">
+        <v>2006</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -2915,6 +3407,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H47" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>2379</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -2950,6 +3448,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H48" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I48" s="14" t="n">
+        <v>914</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -2985,6 +3489,12 @@
           <t>#47</t>
         </is>
       </c>
+      <c r="H49" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>1774</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -3020,6 +3530,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H50" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I50" s="14" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -3055,6 +3571,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H51" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I51" s="14" t="n">
+        <v>1566</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -3090,6 +3612,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H52" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I52" s="14" t="n">
+        <v>1566</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -3125,6 +3653,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H53" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I53" s="14" t="n">
+        <v>3265</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -3160,6 +3694,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H54" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I54" s="14" t="n">
+        <v>5288</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -3195,6 +3735,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H55" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I55" s="14" t="n">
+        <v>5547</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -3230,6 +3776,12 @@
           <t>#54</t>
         </is>
       </c>
+      <c r="H56" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I56" s="14" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -3265,6 +3817,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H57" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I57" s="14" t="n">
+        <v>1846</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -3300,6 +3858,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H58" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I58" s="14" t="n">
+        <v>4658</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -3335,6 +3899,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H59" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I59" s="14" t="n">
+        <v>5780</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -3370,6 +3940,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I60" s="14" t="n">
+        <v>6559</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -3405,6 +3981,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H61" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I61" s="14" t="n">
+        <v>10701</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -3440,6 +4022,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H62" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I62" s="14" t="n">
+        <v>2067</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -3475,6 +4063,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H63" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I63" s="14" t="n">
+        <v>878</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -3510,6 +4104,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H64" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I64" s="14" t="n">
+        <v>1201</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -3545,6 +4145,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H65" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I65" s="14" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -3580,6 +4186,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H66" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I66" s="14" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -3615,6 +4227,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H67" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I67" s="14" t="n">
+        <v>886</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -3649,6 +4267,12 @@
         <is>
           <t>Pair 1</t>
         </is>
+      </c>
+      <c r="H68" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I68" s="14" t="n">
+        <v>14377</v>
       </c>
     </row>
   </sheetData>
@@ -3662,8 +4286,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G206"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I206"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -3679,6 +4303,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="H1" s="11" t="n">
+        <v>46303</v>
+      </c>
+      <c r="I1" s="11" t="n">
+        <v>46303</v>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
@@ -3714,6 +4344,16 @@
       <c r="G2" s="9" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -3751,6 +4391,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Netaji+Subhash+Place+Delhi,+Shop+No.+01+ITL+Twin+Tower,+Netaji+Subhash+Place,+Pitampura,+New+Delhi,+Delhi+110034/@28.6911987,77.1522225,16z/data=!4m6!3m5!1s0x390d03c155555555:0x5b4d4b46cc7ccd4a!8m2!3d28.6911987!4d77.1522225!16s%2Fg%2F1tfldmlm?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
+      <c r="H3" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>2115</v>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="7" t="n">
@@ -3786,6 +4432,12 @@
           <t>https://www.google.com/maps/place/Ground+Floor,+Bikanervala+%7C+Sadar+Bazaar,+Devika+Sadar,+Shop+No.+G+12,+G+14-19+7+G+24+-+44,+Qutab+Rd,+Narain+Market,+Sadar+Bazar,+New+Delhi,+Delhi+110006/@28.6558145,77.2162412,16z/data=!4m6!3m5!1s0x390cfde0b0b14249:0xc8e86801bdd1bfd0!8m2!3d28.6558145!4d77.2162412!16s%2Fg%2F11ksks6gbd?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
+      <c r="H4" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>632</v>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="7" t="n">
@@ -3821,6 +4473,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Liberty+Cinema+Karol+Bagh/@28.6606284,77.1876003,17z/data=!3m1!4b1!4m6!3m5!1s0x390d03326d19a899:0xd2fef34572239279!8m2!3d28.6606284!4d77.1876003!16s%2Fg%2F11m5qhcscj?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H5" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>1555</v>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="7" t="n">
@@ -3856,6 +4514,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Kalkaji+Metro/@28.5494507,77.259104,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce361d13dfecb:0x11d594dba2638f6d!8m2!3d28.5494507!4d77.259104!16s%2Fg%2F11x72l6mq2?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H6" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="n">
@@ -3891,6 +4555,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Lajpat+Nagar+Delhi/@28.5708816,77.2390955,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce252e00cf3fb:0xf48521c45d7cd156!8m2!3d28.5708816!4d77.2390955!16s%2Fg%2F1td_wzrz?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>10888</v>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="7" t="n">
@@ -3926,6 +4596,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Defence+Colony+Delhi/@28.5748765,77.2381202,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce3d5f019e1e9:0xa3e490839a38e681!8m2!3d28.5748765!4d77.2381202!16s%2Fg%2F11qb4tsxc0?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H8" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>2940</v>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="7" t="n">
@@ -3961,6 +4637,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+East+of+Kailash+Delhi/@28.5587762,77.246459,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce39ca675e7c3:0xbe857ad66d22f2bf!8m2!3d28.5587762!4d77.246459!16s%2Fg%2F11s1qvx_74?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>218</v>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="7" t="n">
@@ -3996,6 +4678,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Preet+Vihar+Delhi/@28.6392518,77.2948339,17z/data=!3m1!4b1!4m6!3m5!1s0x390cfb510ec67a93:0xfad0c088f3f91804!8m2!3d28.6392518!4d77.2948339!16s%2Fg%2F1tgnkg53?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H10" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>5138</v>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="7" t="n">
@@ -4031,6 +4719,12 @@
           <t>https://www.google.com/maps/search/BV+Connaught+Place+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H11" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="7" t="n">
@@ -4066,6 +4760,12 @@
           <t>https://www.google.com/maps/search/BV+RRM+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H12" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>656</v>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="7" t="n">
@@ -4101,6 +4801,12 @@
           <t>https://www.google.com/maps/search/BV+Mayur+Vihar+Phase+1+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H13" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>2494</v>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="7" t="n">
@@ -4136,6 +4842,12 @@
           <t>https://www.google.com/maps/search/BV+Chandni+Chowk+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H14" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="n">
@@ -4171,6 +4883,12 @@
           <t>https://www.google.com/maps/search/BV+Okhla+Industrial+Area+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H15" s="14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="7" t="n">
@@ -4206,6 +4924,12 @@
           <t>https://www.google.com/maps/search/BV+GTK+Road+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H16" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>3431</v>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="n">
@@ -4241,6 +4965,12 @@
           <t>https://www.google.com/maps/search/BV+Punjabi+Bagh+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H17" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="7" t="n">
@@ -4276,6 +5006,12 @@
           <t>https://www.google.com/maps/search/BV+Kamla+Nagar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H18" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>1865</v>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="7" t="n">
@@ -4311,6 +5047,12 @@
           <t>https://www.google.com/maps/search/BV+Rohini+West+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>606</v>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="7" t="n">
@@ -4346,6 +5088,12 @@
           <t>https://www.google.com/maps/search/BV+Kirti+Nagar+Industrial+Area+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H20" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="7" t="n">
@@ -4381,6 +5129,12 @@
           <t>https://www.google.com/maps/search/BV+Dilshad+Garden+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H21" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="7" t="n">
@@ -4416,6 +5170,12 @@
           <t>https://www.google.com/maps/search/BV+Malviya+Nagar+Extension+Saket?hl=en</t>
         </is>
       </c>
+      <c r="H22" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>6280</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="7" t="n">
@@ -4451,6 +5211,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Dwarka+Delhi/@28.5966087,77.0417524,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1b72556cb43b:0xdd37fb0751d2b900!8m2!3d28.5966087!4d77.0417524!16s%2Fg%2F11grt4vw5b?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H23" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>6218</v>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="7" t="n">
@@ -4486,6 +5252,12 @@
           <t>https://www.google.com/maps/search/BV+Rani+Bagh+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H24" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>13126</v>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="7" t="n">
@@ -4521,6 +5293,12 @@
           <t>https://www.google.com/maps/search/BV+Janakpuri+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H25" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="7" t="n">
@@ -4556,6 +5334,12 @@
           <t>https://www.google.com/maps/search/BV+Jyoti+Nagar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H26" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>1908</v>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="7" t="n">
@@ -4591,6 +5375,12 @@
           <t>https://www.google.com/maps/search/BV+Raja+Garden+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H27" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="7" t="n">
@@ -4626,6 +5416,12 @@
           <t>https://www.google.com/maps/search/BV+Nehru+Place+Metro+Station+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H28" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>10034</v>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="7" t="n">
@@ -4661,6 +5457,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Chanakyapuri+Delhi/@28.585244,77.19149,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1d7cdedc3389:0x60798b43139c76d3!8m2!3d28.585244!4d77.19149!16s%2Fg%2F1tdvhkdv?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H29" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>8671</v>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="n">
@@ -4696,6 +5498,12 @@
           <t>https://www.google.com/maps/search/BV+Aerocity+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H30" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>21970</v>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="7" t="n">
@@ -4731,6 +5539,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+GK-II+Savitri+Cinema+Delhi/@28.5374253,77.2389712,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce22b17e2d781:0x40c5f102209b866c!8m2!3d28.5374253!4d77.2389712!16s%2Fg%2F11cmr0t9q8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H31" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>5576</v>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="7" t="n">
@@ -4756,11 +5570,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Sec+-+109+Gurgaon?hl=en</t>
         </is>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -4787,11 +5606,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+57+Gurugram/@28.4161819,77.0849591,17z/data=!3m1!4b1!4m6!3m5!1s0x390d232798684757:0xb380904dacac7eed!8m2!3d28.4161819!4d77.0849591!16s%2Fg%2F11k522rkjz?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>4871</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -4818,11 +5642,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Sec+-+14+Gurgaon?hl=en</t>
         </is>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>893</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -4849,11 +5678,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Sec+-+99+Gurgaon?hl=en</t>
         </is>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -4880,11 +5714,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Sec+-+24+Gurgaon?hl=en</t>
         </is>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>695</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -4911,11 +5750,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Bikanervala+%7C+The+Esplanade+Mall+Sector+37+Gurugram/@28.4538074,76.9928507,17z/data=!3m1!4b1!4m6!3m5!1s0x390d171587c41467:0x4070a84c531d04ce!8m2!3d28.4538074!4d76.9928507!16s%2Fg%2F11tggmn3j8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>1332</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -4942,11 +5786,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Cyber+Park+Udhyog+Vihar+Gurgaon?hl=en</t>
         </is>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>2687</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -4973,11 +5822,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Foodcourt+Opulent+Mall+Gurgaon?hl=en</t>
         </is>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>23003</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -5004,11 +5858,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+JMD+Empire+Square+Gurgaon?hl=en</t>
         </is>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>571</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -5035,11 +5894,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+62+Gurugram/@28.4014616,77.0852188,17z/data=!3m1!4b1!4m6!3m5!1s0x390d23dcf278418d:0x4d1e11be0af4d661!8m2!3d28.4014616!4d77.0852188!16s%2Fg%2F11h7qrpfv4?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>455</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -5066,11 +5930,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+15+Gurugram/@28.4578375,77.0443773,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1902973194b5:0x7d02f6d383fb8a58!8m2!3d28.4578375!4d77.0443773!16s%2Fg%2F11trqkrhym?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I42" s="14" t="n">
+        <v>2414</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -5097,11 +5966,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Sec+-+95+Gurgaon?hl=en</t>
         </is>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>2222</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -5128,11 +6002,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Sec+-+54+Gurgaon?hl=en</t>
         </is>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>1358</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -5159,11 +6038,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+67+Gurugram/@28.3897015,77.0674498,17z/data=!3m1!4b1!4m6!3m5!1s0x390d23d7d3976715:0xb8dc58e2f64d1b2e!8m2!3d28.3897015!4d77.0674498!16s%2Fg%2F11h7ksct1w?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>1107</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -5190,11 +6074,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sohna+Road+Gurugram/@28.4253629,77.0390099,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1875d4418c91:0x3b4b144484bee44a!8m2!3d28.4253629!4d77.0390099!16s%2Fg%2F1wj_4f0r?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I46" s="14" t="n">
+        <v>7190</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -5221,11 +6110,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Sec+-+29+Gurgaon?hl=en</t>
         </is>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -5252,11 +6146,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Sec+-+86+Gurgaon?hl=en</t>
         </is>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I48" s="14" t="n">
+        <v>3666</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -5283,11 +6182,16 @@
           <t>Gurgaon</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+80+Gurugram/@28.3766192,76.9593435,17z/data=!3m1!4b1!4m6!3m5!1s0x390d3da30c57ee59:0x82d80073b91470fc!8m2!3d28.3766192!4d76.9593435!16s%2Fg%2F11fhh4ykm5?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>2379</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -5314,11 +6218,16 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Sec+-+62+Noida?hl=en</t>
         </is>
+      </c>
+      <c r="H50" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I50" s="14" t="n">
+        <v>5591</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -5345,11 +6254,16 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Omaxe+NRI+Greater+Noida?hl=en</t>
         </is>
+      </c>
+      <c r="H51" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I51" s="14" t="n">
+        <v>1007</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -5376,11 +6290,16 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Knowledge+Park+3+Greater+Noida?hl=en</t>
         </is>
+      </c>
+      <c r="H52" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I52" s="14" t="n">
+        <v>772</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -5407,11 +6326,16 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+18+Noida/@28.5715738,77.3246799,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce44edd59cf9b:0x7abd947a6a0578bf!8m2!3d28.5715738!4d77.3246799!16s%2Fg%2F124sxkwj8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
+      </c>
+      <c r="H53" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I53" s="14" t="n">
+        <v>9648</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -5438,11 +6362,16 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Bikanervala+Gaur+City+Mall+Greater+Noida?hl=en</t>
         </is>
+      </c>
+      <c r="H54" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I54" s="14" t="n">
+        <v>796</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -5469,11 +6398,16 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Krishna+Apsara+Plaza+Noida?hl=en</t>
         </is>
+      </c>
+      <c r="H55" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I55" s="14" t="n">
+        <v>298</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -5500,11 +6434,16 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+URBTCH+Sec+-+153+Noida?hl=en</t>
         </is>
+      </c>
+      <c r="H56" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I56" s="14" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -5531,11 +6470,16 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" s="8" t="inlineStr">
         <is>
           <t>https://share.google/ROkTSrwbJf84BzhPA</t>
         </is>
+      </c>
+      <c r="H57" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I57" s="14" t="n">
+        <v>437</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -5562,11 +6506,16 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" s="8" t="inlineStr">
         <is>
           <t>https://share.google/zdFAyEbaRbQ5k484p</t>
         </is>
+      </c>
+      <c r="H58" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I58" s="14" t="n">
+        <v>203</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -5593,11 +6542,16 @@
           <t>Gaziabad</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" s="8" t="inlineStr">
         <is>
           <t>https://share.google/Lb3nqjJMTsd4B288R</t>
         </is>
+      </c>
+      <c r="H59" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I59" s="14" t="n">
+        <v>658</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -5624,11 +6578,16 @@
           <t>Gaziabad</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" s="8" t="inlineStr">
         <is>
           <t>https://share.google/UhwDLEldKfKeeOvuF</t>
         </is>
+      </c>
+      <c r="H60" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I60" s="14" t="n">
+        <v>361</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -5655,11 +6614,16 @@
           <t>Gaziabad</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" s="8" t="inlineStr">
         <is>
           <t>https://share.google/y3qxY9okUtRY9qT5G</t>
         </is>
+      </c>
+      <c r="H61" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I61" s="14" t="n">
+        <v>2914</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -5686,11 +6650,16 @@
           <t>Gaziabad</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" s="8" t="inlineStr">
         <is>
           <t>https://share.google/6IsINvdHSLIIHkIhQ</t>
         </is>
+      </c>
+      <c r="H62" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I62" s="14" t="n">
+        <v>585</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -5717,11 +6686,16 @@
           <t>Gaziabad</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
           <t>https://share.google/dyEWjeSFB5bMuBtCr</t>
         </is>
+      </c>
+      <c r="H63" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I63" s="14" t="n">
+        <v>9258</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -5748,11 +6722,16 @@
           <t>Gaziabad</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Bikanervala+Gaur+Biz+Park+Gaziabad?hl=en</t>
         </is>
+      </c>
+      <c r="H64" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I64" s="14" t="n">
+        <v>1007</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -5779,11 +6758,16 @@
           <t>Gaziabad</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Plot+No.+12,+Bikanervala+%7C+Rajendra+Nagar,+Sahibabad,,+Rajender+Nagar,+Sector+5,+Rajendra+Nagar,+Sahibabad,+Ghaziabad,+Uttar+Pradesh+201005/@28.6780951,77.3592434,16z/data=!4m6!3m5!1s0x390cfa8b972e5a11:0x42944ce5f6223fbd!8m2!3d28.6780951!4d77.3592434!16s%2Fg%2F11b6gg2nvh?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
+      </c>
+      <c r="H65" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I65" s="14" t="n">
+        <v>3845</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -5810,11 +6794,16 @@
           <t>Gaziabad</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Choudhary+More+Ghaziabad/@28.656764,77.4343384,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf1cfc180871d:0x5aa84735b213aa6a!8m2!3d28.656764!4d77.4343384!16s%2Fg%2F11clr_s4v9?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
+      </c>
+      <c r="H66" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I66" s="14" t="n">
+        <v>4137</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -5841,11 +6830,16 @@
           <t>Gaziabad</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Indirapuram+Gaziabad?hl=en</t>
         </is>
+      </c>
+      <c r="H67" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I67" s="14" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -5872,11 +6866,16 @@
           <t>Gaziabad</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Raj+Nagar+Extension+Gaziabad?hl=en</t>
         </is>
+      </c>
+      <c r="H68" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I68" s="14" t="n">
+        <v>4300</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -5903,11 +6902,16 @@
           <t>Gaziabad</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Vasundhara+Gaziabad?hl=en</t>
         </is>
+      </c>
+      <c r="H69" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I69" s="14" t="n">
+        <v>2213</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -5934,11 +6938,16 @@
           <t>Gaziabad</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Bikanervala+%7C+KW+Delhi+6/@28.696452,77.4352816,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf15e12b7409f:0x21ba0dd8e12c1453!8m2!3d28.696452!4d77.4352816!16s%2Fg%2F11jzgk44vp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
+      </c>
+      <c r="H70" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I70" s="14" t="n">
+        <v>280</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -5965,11 +6974,16 @@
           <t>Gaziabad</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Modinagar/@28.8133765,77.5519765,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf5b71abce455:0xfc2ef5a0bb38f92!8m2!3d28.8133765!4d77.5519765!16s%2Fg%2F11ghftj4c1?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
+      </c>
+      <c r="H71" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I71" s="14" t="n">
+        <v>6142</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -5996,11 +7010,16 @@
           <t>Gaziabad</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Lal+Kuan+Gaziabad?hl=en</t>
         </is>
+      </c>
+      <c r="H72" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I72" s="14" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -6027,11 +7046,16 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/KegUZzVNtBCzn3zC9</t>
         </is>
+      </c>
+      <c r="H73" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I73" s="14" t="n">
+        <v>1108</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -6058,11 +7082,16 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/uzteMjzzkSa3PjHcA</t>
         </is>
+      </c>
+      <c r="H74" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I74" s="14" t="n">
+        <v>9514</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -6089,11 +7118,16 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/o8aMcy4bzjEiMSc88</t>
         </is>
+      </c>
+      <c r="H75" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I75" s="14" t="n">
+        <v>16969</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -6120,11 +7154,16 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/LeLGBiAqApZipLR2A</t>
         </is>
+      </c>
+      <c r="H76" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I76" s="14" t="n">
+        <v>8560</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -6151,11 +7190,16 @@
           <t>Lucknow</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Bikanervala/@26.7851067,80.9918353,17z/data=!3m1!4b1!4m6!3m5!1s0x399be30647fd426d:0xd01584f16db3efe3!8m2!3d26.7851067!4d80.9918353!16s%2Fg%2F11jsr96pd9?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
+      </c>
+      <c r="H77" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I77" s="14" t="n">
+        <v>2468</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -6182,11 +7226,16 @@
           <t>Lucknow</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Fun+Republik+Lucknow?hl=en</t>
         </is>
+      </c>
+      <c r="H78" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I78" s="14" t="n">
+        <v>10943</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -6213,11 +7262,16 @@
           <t>Lucknow</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Emerald+Mall+Lucknow/@26.7879677,80.9106156,17z/data=!3m1!4b1!4m6!3m5!1s0x399bfda33d9b4ed1:0x4bc0f33320d7156b!8m2!3d26.7879677!4d80.9106156!16s%2Fg%2F11vs2f1qpf?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
+      </c>
+      <c r="H79" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I79" s="14" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -6244,11 +7298,16 @@
           <t>Lucknow</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Vijay+Tower+Lucknow?hl=en</t>
         </is>
+      </c>
+      <c r="H80" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I80" s="14" t="n">
+        <v>148</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -6275,10 +7334,19 @@
           <t>Lucknow</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Indira+Nagar+Lucknow+%28Closed%29?hl=en</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -6306,11 +7374,16 @@
           <t>Lucknow</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Vibhuti+Khand+Gomti+Nagar+Lucknow?hl=en</t>
         </is>
+      </c>
+      <c r="H82" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I82" s="14" t="n">
+        <v>1437</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -6337,11 +7410,16 @@
           <t>Faridabad</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Sec+-+12+Faridabad?hl=en</t>
         </is>
+      </c>
+      <c r="H83" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I83" s="14" t="n">
+        <v>1739</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -6368,11 +7446,16 @@
           <t>Faridabad</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Mansha+Vega+Street+Faridabad?hl=en</t>
         </is>
+      </c>
+      <c r="H84" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I84" s="14" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -6399,11 +7482,16 @@
           <t>Bhatinda</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Mandi+Dabwali+Road+Bhatinda?hl=en</t>
         </is>
+      </c>
+      <c r="H85" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I85" s="14" t="n">
+        <v>3949</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -6430,11 +7518,16 @@
           <t>Bhatinda</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Park+Penorama+Colony+Bhatinda?hl=en</t>
         </is>
+      </c>
+      <c r="H86" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I86" s="14" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -6461,11 +7554,16 @@
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Nungabakkam+Chennai?hl=en</t>
         </is>
+      </c>
+      <c r="H87" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I87" s="14" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -6492,11 +7590,16 @@
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Chennai+Kilpauk?hl=en</t>
         </is>
+      </c>
+      <c r="H88" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I88" s="14" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -6523,11 +7626,16 @@
           <t>Meerut</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Modipuram+Meerut?hl=en</t>
         </is>
+      </c>
+      <c r="H89" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I89" s="14" t="n">
+        <v>834</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -6554,11 +7662,16 @@
           <t>Meerut</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Harsh+Commercial+Park+Meerut?hl=en</t>
         </is>
+      </c>
+      <c r="H90" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I90" s="14" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -6585,11 +7698,16 @@
           <t>Sonipat</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Kundli+Sonipat?hl=en</t>
         </is>
+      </c>
+      <c r="H91" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I91" s="14" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -6616,11 +7734,16 @@
           <t>Varanasi</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Bhelupura+Varanasi?hl=en</t>
         </is>
+      </c>
+      <c r="H92" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I92" s="14" t="n">
+        <v>27258</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -6647,11 +7770,16 @@
           <t>Zirakpur</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Global+Business+Park+Zirakpur?hl=en</t>
         </is>
+      </c>
+      <c r="H93" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I93" s="14" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -6678,11 +7806,16 @@
           <t>Ludhiana</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Pakhowal+Road+Ludhiana?hl=en</t>
         </is>
+      </c>
+      <c r="H94" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I94" s="14" t="n">
+        <v>1624</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -6709,11 +7842,16 @@
           <t>Jaipur</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Tonk+Road+Jaipur?hl=en</t>
         </is>
+      </c>
+      <c r="H95" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I95" s="14" t="n">
+        <v>7498</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -6740,11 +7878,16 @@
           <t>Jalandhar</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Model+Town+Jalandhar?hl=en</t>
         </is>
+      </c>
+      <c r="H96" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I96" s="14" t="n">
+        <v>2835</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -6771,11 +7914,16 @@
           <t>Mohali</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+C+Plaza+Mohali?hl=en</t>
         </is>
+      </c>
+      <c r="H97" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I97" s="14" t="n">
+        <v>43968</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -6802,11 +7950,16 @@
           <t>Dehradun</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Pacific+Mall+Rajpur+Road+Dehradun?hl=en</t>
         </is>
+      </c>
+      <c r="H98" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I98" s="14" t="n">
+        <v>42232</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -6833,11 +7986,16 @@
           <t>Gwalier</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Lashkar+Gwalier?hl=en</t>
         </is>
+      </c>
+      <c r="H99" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I99" s="14" t="n">
+        <v>12477</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -6864,11 +8022,16 @@
           <t>Bahadurgharh</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Avenue+37+Bahadurgarh?hl=en</t>
         </is>
+      </c>
+      <c r="H100" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I100" s="14" t="n">
+        <v>344</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -6895,11 +8058,16 @@
           <t>Saharanpur</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Tehsil+Deoband+Saharanpur?hl=en</t>
         </is>
+      </c>
+      <c r="H101" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I101" s="14" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -6926,11 +8094,16 @@
           <t>Ambala</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Barara+Ambala?hl=en</t>
         </is>
+      </c>
+      <c r="H102" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I102" s="14" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -6957,11 +8130,16 @@
           <t>Sri Ganganagar</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Hanuman+Garh+Road+Sri+GnagaNagar?hl=en</t>
         </is>
+      </c>
+      <c r="H103" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I103" s="14" t="n">
+        <v>857</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -6988,11 +8166,16 @@
           <t>Sangrur</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Nabha+Gate+Road+Sangrur?hl=en</t>
         </is>
+      </c>
+      <c r="H104" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I104" s="14" t="n">
+        <v>428</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -7019,11 +8202,16 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Jayanagar+Bengaluru?hl=en</t>
         </is>
+      </c>
+      <c r="H105" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I105" s="14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -7050,11 +8238,16 @@
           <t>Hisar</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Village+Quatabpur+Hisar?hl=en</t>
         </is>
+      </c>
+      <c r="H106" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I106" s="14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -7081,11 +8274,16 @@
           <t>Jammu</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Akhnoor+Jammu?hl=en</t>
         </is>
+      </c>
+      <c r="H107" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I107" s="14" t="n">
+        <v>4253</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -7112,11 +8310,16 @@
           <t>Rohtak</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+Model+Town+Rohtak?hl=en</t>
         </is>
+      </c>
+      <c r="H108" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I108" s="14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
@@ -7143,11 +8346,16 @@
           <t>Rajasthan</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/BV+NH+27+Abu+Road+Rajasthan?hl=en</t>
         </is>
+      </c>
+      <c r="H109" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I109" s="14" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -7174,11 +8382,16 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/X2g2z7mRg9ZU92F2A</t>
         </is>
+      </c>
+      <c r="H110" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I110" s="14" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -7205,11 +8418,16 @@
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/37R2ESFo5oS8p2em7</t>
         </is>
+      </c>
+      <c r="H111" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I111" s="14" t="n">
+        <v>866</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -7246,6 +8464,12 @@
           <t>https://goo.gl/maps/iMtbXqwaWUDYu8xf6</t>
         </is>
       </c>
+      <c r="H112" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I112" s="14" t="n">
+        <v>8390</v>
+      </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="7" t="n">
@@ -7281,6 +8505,12 @@
           <t>https://goo.gl/maps/CxUCASbc6Zf2TocB8</t>
         </is>
       </c>
+      <c r="H113" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I113" s="14" t="n">
+        <v>4894</v>
+      </c>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="7" t="n">
@@ -7316,6 +8546,12 @@
           <t>https://goo.gl/maps/ATskvznck1gui7f6A</t>
         </is>
       </c>
+      <c r="H114" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I114" s="14" t="n">
+        <v>3365</v>
+      </c>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="7" t="n">
@@ -7351,6 +8587,12 @@
           <t>https://goo.gl/maps/KbVjkRcx6jMVdGQW7</t>
         </is>
       </c>
+      <c r="H115" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I115" s="14" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="7" t="n">
@@ -7386,6 +8628,12 @@
           <t>https://goo.gl/maps/AmjQDTZCHpP9PfrB6</t>
         </is>
       </c>
+      <c r="H116" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I116" s="14" t="n">
+        <v>8671</v>
+      </c>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="7" t="n">
@@ -7421,6 +8669,12 @@
           <t>https://maps.app.goo.gl/zcrubnk5RZ3jKg5A8</t>
         </is>
       </c>
+      <c r="H117" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I117" s="14" t="n">
+        <v>11852</v>
+      </c>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="7" t="n">
@@ -7456,6 +8710,12 @@
           <t>https://goo.gl/maps/dqHX14AbaKcSsV5i7</t>
         </is>
       </c>
+      <c r="H118" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I118" s="14" t="n">
+        <v>2769</v>
+      </c>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="7" t="n">
@@ -7491,6 +8751,12 @@
           <t>https://maps.app.goo.gl/NbSW2GgWBiTTWokQ6</t>
         </is>
       </c>
+      <c r="H119" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I119" s="14" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="7" t="n">
@@ -7526,6 +8792,12 @@
           <t>https://maps.app.goo.gl/x8i3gr7m9LKKvijw9</t>
         </is>
       </c>
+      <c r="H120" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I120" s="14" t="n">
+        <v>464</v>
+      </c>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="7" t="n">
@@ -7561,6 +8833,12 @@
           <t>https://maps.app.goo.gl/pNH5r5yxdP3DTRfj9</t>
         </is>
       </c>
+      <c r="H121" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I121" s="14" t="n">
+        <v>776</v>
+      </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="7" t="n">
@@ -7596,6 +8874,12 @@
           <t>https://maps.app.goo.gl/Lt1LVynLWcuu8eXy5</t>
         </is>
       </c>
+      <c r="H122" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I122" s="14" t="n">
+        <v>169</v>
+      </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="7" t="n">
@@ -7631,6 +8915,12 @@
           <t>https://maps.app.goo.gl/G7HFA2zCPT3Co2BU9</t>
         </is>
       </c>
+      <c r="H123" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I123" s="14" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="7" t="n">
@@ -7666,6 +8956,12 @@
           <t>https://maps.app.goo.gl/9LmyBZrg48UVmmmM7</t>
         </is>
       </c>
+      <c r="H124" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I124" s="14" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="7" t="n">
@@ -7701,6 +8997,12 @@
           <t>https://maps.app.goo.gl/mnuCcmi4TeeNHkNv7</t>
         </is>
       </c>
+      <c r="H125" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I125" s="14" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="7" t="n">
@@ -7736,6 +9038,12 @@
           <t>https://maps.app.goo.gl/hWXz3RWjo8iBq8vC6</t>
         </is>
       </c>
+      <c r="H126" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I126" s="14" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="7" t="n">
@@ -7771,6 +9079,12 @@
           <t>https://goo.gl/maps/EXwmxHqPpSwBfAn9A</t>
         </is>
       </c>
+      <c r="H127" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I127" s="14" t="n">
+        <v>4191</v>
+      </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="7" t="n">
@@ -7806,6 +9120,12 @@
           <t>https://maps.app.goo.gl/Qr7ipPaWf38VtzRZA</t>
         </is>
       </c>
+      <c r="H128" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I128" s="14" t="n">
+        <v>288</v>
+      </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="7" t="n">
@@ -7831,11 +9151,16 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
       <c r="G129" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/xV9F7hCGssGURhmZ9</t>
         </is>
+      </c>
+      <c r="H129" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I129" s="14" t="n">
+        <v>4227</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -7862,11 +9187,16 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/je2V2Z8h1Pu8a2Vz8</t>
         </is>
+      </c>
+      <c r="H130" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I130" s="14" t="n">
+        <v>659</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -7893,11 +9223,16 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
       <c r="G131" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/12vCQuxEBD9PWE8F8</t>
         </is>
+      </c>
+      <c r="H131" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I131" s="14" t="n">
+        <v>787</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -7924,11 +9259,16 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
       <c r="G132" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/ucnkKCkPLq9GUTEL8</t>
         </is>
+      </c>
+      <c r="H132" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I132" s="14" t="n">
+        <v>706</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -7955,11 +9295,16 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Bikanervala+Elan+Epic+Sec-70+Gurguram+Gurugram?hl=en</t>
         </is>
+      </c>
+      <c r="H133" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I133" s="14" t="n">
+        <v>1424</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -7986,11 +9331,16 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
       <c r="G134" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/CWNkDPq7wK3DihFMA</t>
         </is>
+      </c>
+      <c r="H134" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I134" s="14" t="n">
+        <v>695</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -8017,11 +9367,16 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/uYECDKn6odyrrTA96</t>
         </is>
+      </c>
+      <c r="H135" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I135" s="14" t="n">
+        <v>372</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -8048,11 +9403,16 @@
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
       <c r="G136" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/uYECDKn6odyrrTA96</t>
         </is>
+      </c>
+      <c r="H136" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I136" s="14" t="n">
+        <v>372</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -8079,11 +9439,16 @@
           <t>Chennai</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/KTGuqx8wJFbQL3V48</t>
         </is>
+      </c>
+      <c r="H137" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I137" s="14" t="n">
+        <v>5273</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -8110,11 +9475,16 @@
           <t>Ahmedabad</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Bikanervala+Prahalad+Nagar%2C+Ahmedabad%2C+Gujarat+380051+Ahmedabad?hl=en</t>
         </is>
+      </c>
+      <c r="H138" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I138" s="14" t="n">
+        <v>2545</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -8141,11 +9511,16 @@
           <t>Ahmedabad</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Bikanervala+Nehru+Nagar%2C+Ahmedabad%2C+Gujarat+380015+Ahmedabad?hl=en</t>
         </is>
+      </c>
+      <c r="H139" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I139" s="14" t="n">
+        <v>3196</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -8172,11 +9547,16 @@
           <t>Lucknow</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/32mqLYxSNUxQfjDy5</t>
         </is>
+      </c>
+      <c r="H140" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I140" s="14" t="n">
+        <v>1437</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -8203,11 +9583,16 @@
           <t>Lucknow</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/723xYbZvfAGXSj5g7</t>
         </is>
+      </c>
+      <c r="H141" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I141" s="14" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -8234,11 +9619,16 @@
           <t>Noida</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
       <c r="G142" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/3WvgLWd5QSehGjEH6</t>
         </is>
+      </c>
+      <c r="H142" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I142" s="14" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -8265,11 +9655,16 @@
           <t>Agra</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
       <c r="G143" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Bikanervala+Fatehabad+Rd%2C+opposite+Hotel+ITC+Mughal%2C+Tajganj%2C+Agra%2C+Uttar+Pradesh+282001+Agra?hl=en</t>
         </is>
+      </c>
+      <c r="H143" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I143" s="14" t="n">
+        <v>4189</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -8296,11 +9691,16 @@
           <t>Agra</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
       <c r="G144" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Bikanervala+Near+tulsi+cinema%2C+Kripal+colony%2C+Sanjay+nagar%2C+pashupati+colony%2C+khandari%2C+Agra%2C+Agra?hl=en</t>
         </is>
+      </c>
+      <c r="H144" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I144" s="14" t="n">
+        <v>4586</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -8327,11 +9727,16 @@
           <t>Allahabad</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
       <c r="G145" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/uYKxT37zNmYp3MU78</t>
         </is>
+      </c>
+      <c r="H145" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I145" s="14" t="n">
+        <v>1530</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -8358,11 +9763,16 @@
           <t>Bathinda</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
       <c r="G146" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/q1cas4PoB2wq7y218</t>
         </is>
+      </c>
+      <c r="H146" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I146" s="14" t="n">
+        <v>3949</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -8389,11 +9799,16 @@
           <t>Dehradun</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
       <c r="G147" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/9korfoaVEuCnsttx9</t>
         </is>
+      </c>
+      <c r="H147" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I147" s="14" t="n">
+        <v>2953</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -8420,11 +9835,16 @@
           <t>Faridabad</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
       <c r="G148" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/wyFeTmbGR45kCHRJ8</t>
         </is>
+      </c>
+      <c r="H148" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I148" s="14" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -8451,11 +9871,16 @@
           <t>Faridkot</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/NuHBsab6Z71CqfnJ7</t>
         </is>
+      </c>
+      <c r="H149" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I149" s="14" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -8482,11 +9907,16 @@
           <t>Garh Mukteshwar</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
       <c r="G150" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/szumsxsq2FSh8P7h7</t>
         </is>
+      </c>
+      <c r="H150" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I150" s="14" t="n">
+        <v>2594</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -8513,11 +9943,16 @@
           <t>Ghaziabad</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
       <c r="G151" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/B4CK1TxcuJf2gwGV8</t>
         </is>
+      </c>
+      <c r="H151" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I151" s="14" t="n">
+        <v>3845</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -8544,11 +9979,16 @@
           <t>Ghaziabad</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
       <c r="G152" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/4pJwnbEcxGBVBWZi6</t>
         </is>
+      </c>
+      <c r="H152" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I152" s="14" t="n">
+        <v>510</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -8575,11 +10015,16 @@
           <t>Ghaziabad</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
       <c r="G153" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/gYRQUULU5t9wi18S8</t>
         </is>
+      </c>
+      <c r="H153" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I153" s="14" t="n">
+        <v>9258</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -8606,11 +10051,16 @@
           <t>Ghaziabad</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
       <c r="G154" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/arsjABkMQUNEYFgF6</t>
         </is>
+      </c>
+      <c r="H154" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I154" s="14" t="n">
+        <v>9244</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -8637,11 +10087,16 @@
           <t>Ghaziabad</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
       <c r="G155" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/N7a66uNDkDcDgctb6</t>
         </is>
+      </c>
+      <c r="H155" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I155" s="14" t="n">
+        <v>4300</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -8668,11 +10123,16 @@
           <t>Ghaziabad</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
       <c r="G156" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/LkRXmhWrNkmb4bfQ9</t>
         </is>
+      </c>
+      <c r="H156" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I156" s="14" t="n">
+        <v>198</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -8699,11 +10159,16 @@
           <t>Ghaziabad</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
       <c r="G157" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/fdpmtgiFnnmBpBhZ6</t>
         </is>
+      </c>
+      <c r="H157" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I157" s="14" t="n">
+        <v>585</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -8730,11 +10195,16 @@
           <t>Ghaziabad</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
       <c r="G158" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/LJVSZyoMxAU6wMvDA</t>
         </is>
+      </c>
+      <c r="H158" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I158" s="14" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -8761,11 +10231,16 @@
           <t>Ghaziabad</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr"/>
       <c r="G159" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/AjzLtZx8muxVP8NEA</t>
         </is>
+      </c>
+      <c r="H159" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I159" s="14" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -8792,11 +10267,16 @@
           <t>Goa</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
       <c r="G160" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/6HL3Gohkz7u4cYQa7</t>
         </is>
+      </c>
+      <c r="H160" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I160" s="14" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -8823,11 +10303,16 @@
           <t>Goa</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr"/>
       <c r="G161" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/oWmDoNJLbdvENyak7</t>
         </is>
+      </c>
+      <c r="H161" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I161" s="14" t="n">
+        <v>133</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -8854,11 +10339,16 @@
           <t>Gorakhpur</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr"/>
       <c r="G162" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/FHgqWFsLmanWmdpD7</t>
         </is>
+      </c>
+      <c r="H162" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I162" s="14" t="n">
+        <v>1937</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -8885,11 +10375,16 @@
           <t>Gwalior</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr"/>
       <c r="G163" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/xJrmieBbKX6bUuSV7</t>
         </is>
+      </c>
+      <c r="H163" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I163" s="14" t="n">
+        <v>1697</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -8916,11 +10411,16 @@
           <t>Gajraula</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr"/>
       <c r="G164" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/aNahaC7CwDFV5kyi9</t>
         </is>
+      </c>
+      <c r="H164" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I164" s="14" t="n">
+        <v>9349</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -8947,11 +10447,16 @@
           <t>Hapur</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
       <c r="G165" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/jWbbnvbERR8sWwr67</t>
         </is>
+      </c>
+      <c r="H165" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I165" s="14" t="n">
+        <v>1091</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -8978,11 +10483,16 @@
           <t>Haridwar</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
       <c r="G166" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/fHakJ7u4WEXt3Ck36</t>
         </is>
+      </c>
+      <c r="H166" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I166" s="14" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -9009,11 +10519,16 @@
           <t>Haldwani</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
       <c r="G167" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/apShSYj546Yn2Sb77</t>
         </is>
+      </c>
+      <c r="H167" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I167" s="14" t="n">
+        <v>3360</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -9040,11 +10555,16 @@
           <t>Indore</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
       <c r="G168" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/V9dCfncbjgbxiVmu8</t>
         </is>
+      </c>
+      <c r="H168" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I168" s="14" t="n">
+        <v>848</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -9071,11 +10591,16 @@
           <t>Jalandhar</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
       <c r="G169" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Bikanervala+BX-143%2C+Royal+Plaza%2C+Plot+No.+224%2C+Model+House+Rd%2C+Tej+Mohan+Nagar%2C+Basti+Sheikh%2C+Dashmesh+Nagar%2C+Jalandhar%2C+Punjab+144002+Jalandhar?hl=en</t>
         </is>
+      </c>
+      <c r="H169" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I169" s="14" t="n">
+        <v>112</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -9102,11 +10627,16 @@
           <t>Jammu</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr"/>
       <c r="G170" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/HLAivSgrHkcp4qnaA</t>
         </is>
+      </c>
+      <c r="H170" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I170" s="14" t="n">
+        <v>142</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -9133,11 +10663,16 @@
           <t>Jammu</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr"/>
       <c r="G171" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/Vz5yNZTUumTKdLSd8</t>
         </is>
+      </c>
+      <c r="H171" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I171" s="14" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -9164,11 +10699,16 @@
           <t>Jammu</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr"/>
       <c r="G172" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/zYmsiM2GuUKTfVeD6</t>
         </is>
+      </c>
+      <c r="H172" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I172" s="14" t="n">
+        <v>190</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -9195,11 +10735,16 @@
           <t>Jammu</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr"/>
       <c r="G173" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/LBtyvdAnk8e5m1578</t>
         </is>
+      </c>
+      <c r="H173" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I173" s="14" t="n">
+        <v>406</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -9226,11 +10771,16 @@
           <t>Jammu</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
       <c r="G174" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/UStZQsyjFuie2zcQA</t>
         </is>
+      </c>
+      <c r="H174" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I174" s="14" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -9257,11 +10807,16 @@
           <t>Jammu</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
       <c r="G175" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/u7fUEMutEveKTJfaA</t>
         </is>
+      </c>
+      <c r="H175" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I175" s="14" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -9288,11 +10843,16 @@
           <t>Jhansi</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr"/>
       <c r="G176" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/Y1coLwehTfUaHJgQ9</t>
         </is>
+      </c>
+      <c r="H176" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I176" s="14" t="n">
+        <v>2052</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -9319,11 +10879,16 @@
           <t>Jabalpur</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr"/>
       <c r="G177" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/nCMGxjXNMPSkpduXA</t>
         </is>
+      </c>
+      <c r="H177" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I177" s="14" t="n">
+        <v>566</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -9350,11 +10915,16 @@
           <t>Kanpur</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
       <c r="G178" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/Yd2kU1mEc8tyWvnJ8</t>
         </is>
+      </c>
+      <c r="H178" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I178" s="14" t="n">
+        <v>4078</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -9381,11 +10951,16 @@
           <t>Kanpur</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
       <c r="G179" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/b1DPwmk5pLaEaMkAA</t>
         </is>
+      </c>
+      <c r="H179" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I179" s="14" t="n">
+        <v>3196</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -9412,11 +10987,16 @@
           <t>Kanpur</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr"/>
       <c r="G180" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/9shVkw5NVcCaEc2f7</t>
         </is>
+      </c>
+      <c r="H180" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I180" s="14" t="n">
+        <v>492</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -9443,11 +11023,16 @@
           <t>Kanpur</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
       <c r="G181" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/KD7iMcgQd1KqrwuX6</t>
         </is>
+      </c>
+      <c r="H181" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I181" s="14" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
@@ -9474,11 +11059,16 @@
           <t>Kanpur</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr"/>
       <c r="G182" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/Yd2kU1mEc8tyWvnJ8</t>
         </is>
+      </c>
+      <c r="H182" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I182" s="14" t="n">
+        <v>4078</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -9505,11 +11095,16 @@
           <t>Kashipur</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr"/>
       <c r="G183" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/ZCFFUjrMcfzQt27h8</t>
         </is>
+      </c>
+      <c r="H183" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I183" s="14" t="n">
+        <v>219</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
@@ -9536,11 +11131,16 @@
           <t>Ludhiana</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr"/>
       <c r="G184" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/wyjWtNYLyFV8wGLo6</t>
         </is>
+      </c>
+      <c r="H184" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I184" s="14" t="n">
+        <v>372</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
@@ -9567,11 +11167,16 @@
           <t>Moradabad</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr"/>
       <c r="G185" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/Mdwf9WhXGqgWpP1s8</t>
         </is>
+      </c>
+      <c r="H185" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I185" s="14" t="n">
+        <v>727</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -9598,11 +11203,16 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr"/>
       <c r="G186" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/qYiG7AWurb3kpPT57</t>
         </is>
+      </c>
+      <c r="H186" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I186" s="14" t="n">
+        <v>434</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
@@ -9629,11 +11239,16 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr"/>
       <c r="G187" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/8CvxLW27EUBgXm287</t>
         </is>
+      </c>
+      <c r="H187" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I187" s="14" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
@@ -9660,11 +11275,16 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr"/>
       <c r="G188" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/XA4qoyenHaBCULJR9</t>
         </is>
+      </c>
+      <c r="H188" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I188" s="14" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
@@ -9691,11 +11311,16 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr"/>
       <c r="G189" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/jF1fPUaWD5TR8wZn6</t>
         </is>
+      </c>
+      <c r="H189" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I189" s="14" t="n">
+        <v>196</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
@@ -9722,11 +11347,16 @@
           <t>Mumbai</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr"/>
       <c r="G190" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/6pZshenjLsstWLWy5</t>
         </is>
+      </c>
+      <c r="H190" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I190" s="14" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -9753,11 +11383,16 @@
           <t>Muzaffarnagar</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr"/>
       <c r="G191" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/YwNxSsrKnhA3Fzae8</t>
         </is>
+      </c>
+      <c r="H191" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I191" s="14" t="n">
+        <v>7436</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
@@ -9784,11 +11419,16 @@
           <t>Nuh</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr"/>
       <c r="G192" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/W21VqyaGAhgWLW1Z7</t>
         </is>
+      </c>
+      <c r="H192" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I192" s="14" t="n">
+        <v>2939</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -9815,11 +11455,16 @@
           <t>Patna</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr"/>
       <c r="G193" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/SofrRQ31CC1sKfiq9</t>
         </is>
+      </c>
+      <c r="H193" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I193" s="14" t="n">
+        <v>488</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
@@ -9846,11 +11491,16 @@
           <t>Rajasthan</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr"/>
       <c r="G194" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/UnxqTGRsvK65sSta7</t>
         </is>
+      </c>
+      <c r="H194" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I194" s="14" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
@@ -9877,11 +11527,16 @@
           <t>Rajasthan</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr"/>
       <c r="G195" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/F8jPscSQ2V93c6vi8</t>
         </is>
+      </c>
+      <c r="H195" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I195" s="14" t="n">
+        <v>2228</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
@@ -9908,11 +11563,16 @@
           <t>Rajasthan</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr"/>
       <c r="G196" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/Zh4ebnPqcXvPMZNG9</t>
         </is>
+      </c>
+      <c r="H196" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I196" s="14" t="n">
+        <v>2665</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -9939,11 +11599,16 @@
           <t>Rampur</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr"/>
       <c r="G197" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/kuVZMKKgf5DubNtN8</t>
         </is>
+      </c>
+      <c r="H197" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" s="14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
@@ -9970,11 +11635,16 @@
           <t>Sonipat</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
       <c r="G198" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/EFUzibDLaLXcxkTd8</t>
         </is>
+      </c>
+      <c r="H198" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I198" s="14" t="n">
+        <v>8998</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -10001,11 +11671,16 @@
           <t>Sonipat</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr"/>
       <c r="G199" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/6W1ZNqLiW1QG7swx5</t>
         </is>
+      </c>
+      <c r="H199" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I199" s="14" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
@@ -10032,11 +11707,16 @@
           <t>Sirsa</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr"/>
       <c r="G200" s="8" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/Bikanervala+Sirsa%2C+Haryana%2C+Sirsa+Sirsa?hl=en</t>
         </is>
+      </c>
+      <c r="H200" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I200" s="14" t="n">
+        <v>190</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
@@ -10063,11 +11743,16 @@
           <t>UNA</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr"/>
       <c r="G201" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/ifJQ68YEKMTaET63A</t>
         </is>
+      </c>
+      <c r="H201" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I201" s="14" t="n">
+        <v>143</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
@@ -10094,11 +11779,16 @@
           <t>Varanasi</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr"/>
       <c r="G202" s="8" t="inlineStr">
         <is>
           <t>https://goo.gl/maps/gt6giRYsgV7Jfsmp8</t>
         </is>
+      </c>
+      <c r="H202" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I202" s="14" t="n">
+        <v>2882</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -10125,11 +11815,16 @@
           <t>Vrindavan</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr"/>
       <c r="G203" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/k8nPnXCjPNR1Fw26A</t>
         </is>
+      </c>
+      <c r="H203" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I203" s="14" t="n">
+        <v>16993</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -10156,11 +11851,16 @@
           <t>Vadodara</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr"/>
       <c r="G204" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/zD7nJnVUnKHTBbTc7</t>
         </is>
+      </c>
+      <c r="H204" s="14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I204" s="14" t="n">
+        <v>152</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
@@ -10187,11 +11887,16 @@
           <t>Waknaghat</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr"/>
       <c r="G205" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/rTKgS8LFdLXcgLgG8</t>
         </is>
+      </c>
+      <c r="H205" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I205" s="14" t="n">
+        <v>337</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -10218,11 +11923,16 @@
           <t>Zirakpur</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr"/>
       <c r="G206" s="8" t="inlineStr">
         <is>
           <t>https://maps.app.goo.gl/F4A61XtKBQZhzMRC7</t>
         </is>
+      </c>
+      <c r="H206" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I206" s="14" t="n">
+        <v>161</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1"/>
@@ -10237,8 +11947,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -10254,6 +11964,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="11" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H1" s="11" t="n">
+        <v>46303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -10284,6 +12000,16 @@
       <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -10316,6 +12042,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Karama+%7C+Indian+Vegetarian+Restaurant+in+Dubai+-+4B+St+-+Sheikh+Khalifa+Bin+Zayed+St+-+behind+Park+Regis+Kris+Kin+Hotel+-+Al+Karama+-+Dubai+-+United+Arab+Emirates/@25.2487074,55.3022648,16z/data=!4m6!3m5!1s0x3e5f43263a32659d:0x3e7a496c31265a14!8m2!3d25.2487074!4d55.3022648!16s%2Fg%2F11fkl98x2w?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
+      <c r="G3" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>6999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -10346,6 +12078,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Barsha+Heights+Dubai?hl=en</t>
         </is>
       </c>
+      <c r="G4" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>1720</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -10376,6 +12114,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Barsha+1+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1159702,55.2049553,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6bc01e76ba11:0x4fd1a9f4b2e6f5e3!8m2!3d25.1159702!4d55.2049553!16s%2Fg%2F1hhn4cw5b?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G5" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>3414</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -10406,6 +12150,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Arjan+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.0611644,55.2416108,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6f3d18bbdbdd:0xf394598ae51611cd!8m2!3d25.0611644!4d55.2416108!16s%2Fg%2F11k4t6j5kj?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G6" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>1351</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -10436,6 +12186,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Dubai+Hills+Mall+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1000884,55.2380841,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6ffb10c94323:0xe15233cd12b4c95e!8m2!3d25.1000884!4d55.2380841!16s%2Fg%2F11srb65qdy?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G7" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>1108</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -10466,6 +12222,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Sheikh+Zayed+Road+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2287901,55.2861116,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43aad3d78e71:0xb8b194cb916fd9b0!8m2!3d25.2287901!4d55.2861116!16s%2Fg%2F11spn08t8p?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G8" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>3371</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -10496,6 +12258,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Gold+Souk+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2720383,55.2977013,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43768964654b:0xc11f03b76b0ba714!8m2!3d25.2720383!4d55.2977013!16s%2Fg%2F11sqkp7mp7?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G9" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -10526,6 +12294,12 @@
           <t>https://www.google.com/maps/place/Bikanervala/@25.1971872,55.2793099,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43291308afa5:0xe48b7db44021ad9d!8m2!3d25.1971872!4d55.2793099!16s%2Fg%2F11h_6kxb_4?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G10" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>1200</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -10556,6 +12330,12 @@
           <t>https://www.google.com/maps/place/Bikanervala/@25.0443703,55.2301107,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6fbad2abf81f:0x2b8744ab6a1bf442!8m2!3d25.0443703!4d55.2301107!16s%2Fg%2F11wqdtyl9k?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G11" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>812</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -10586,6 +12366,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Jumeirah+Village+Circle?hl=en</t>
         </is>
       </c>
+      <c r="G12" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>3414</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -10616,6 +12402,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Jumeirah+3+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1568314,55.2048822,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6bf2c1bdccc9:0x43c26854ab27ef01!8m2!3d25.1568314!4d55.2048822!16s%2Fg%2F11s5twnr34?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G13" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>406</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -10646,6 +12438,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Furjan+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.0253394,55.1523478,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6d3bc9bcdbdb:0xe6f0ccdcb4b1e8ab!8m2!3d25.0253394!4d55.1523478!16s%2Fg%2F11g8kr7p26?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G14" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>3465</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -10676,6 +12474,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+International+City+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1587461,55.4044494,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6152822cefa7:0x62485254b618ad37!8m2!3d25.1587461!4d55.4044494!16s%2Fg%2F11fy4nt_fh?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G15" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>1986</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -10706,6 +12510,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Ghurair+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.268832,55.3167197,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f432a6356bd7d:0x6e8727a69863a0ea!8m2!3d25.268832!4d55.3167197!16s%2Fg%2F11gj4q5yml?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G16" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>1337</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -10736,6 +12546,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Business+Bay+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1907081,55.2657305,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f69d43a494553:0xcae55dd8d4af25bc!8m2!3d25.1907081!4d55.2657305!16s%2Fg%2F11cnch2xjh?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G17" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>1337</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -10766,6 +12582,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Abu+Dhabi+%7C+Indian+Vegetarian+Restaurant+in+Abu+Dhabi/@24.4787181,54.3632708,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5e6797000fef8b:0x252e9c63c8d0f687!8m2!3d24.4787181!4d54.3632708!16s%2Fg%2F11j3jt3jck?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G18" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>4492</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -10796,6 +12618,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Qusais+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2779484,55.362064,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f5c5ef14f580b:0x42f37dd66cc3bd09!8m2!3d25.2779484!4d55.362064!16s%2Fg%2F11bbwn_ftp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G19" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>1672</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -10826,6 +12654,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Hounslow/@51.4697256,-0.3575675,17z/data=!3m1!4b1!4m6!3m5!1s0x48760db0ad77af37:0x259004b7a001719e!8m2!3d51.4697256!4d-0.3575675!16s%2Fg%2F11lw2pkxzp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G20" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>4374</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -10856,6 +12690,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Doha+Qatar?hl=en</t>
         </is>
       </c>
+      <c r="G21" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>3854</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -10886,6 +12726,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Investment+Park+Dubai+%28Dubai%29?hl=en</t>
         </is>
       </c>
+      <c r="G22" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -10916,6 +12762,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Jumeirah+%28The+Point%2C+Palm%29+Dubai+%28Dubai%29?hl=en</t>
         </is>
       </c>
+      <c r="G23" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>443</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -10946,6 +12798,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Lynx+Tower+%28Silicon+Oasis%29+Dubai+%28Dubai%29?hl=en</t>
         </is>
       </c>
+      <c r="G24" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>1684</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -10976,6 +12834,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+JLT+Dubai+%28Dubai%29?hl=en</t>
         </is>
       </c>
+      <c r="G25" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>3364</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -11006,6 +12870,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Al+Wahda+Street+Sharjah+%28Sharjah%29?hl=en</t>
         </is>
       </c>
+      <c r="G26" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>1766</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -11036,6 +12906,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Muweillah+Sharjah+%28Sharjah%29?hl=en</t>
         </is>
       </c>
+      <c r="G27" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>531</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -11066,6 +12942,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Southall+London+%28UK%29?hl=en</t>
         </is>
       </c>
+      <c r="G28" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>1325</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -11096,6 +12978,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Ilford+London+%28UK%29?hl=en</t>
         </is>
       </c>
+      <c r="G29" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>642</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -11126,6 +13014,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Express+City+Centre+Mall+Doha+%28Qatar%29?hl=en</t>
         </is>
       </c>
+      <c r="G30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -11156,6 +13050,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Jersey+City+NJ+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G31" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>1323</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -11186,6 +13086,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Iselin+NJ+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G32" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>1427</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -11216,6 +13122,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Kendall+Park+NJ+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G33" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>1335</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -11246,6 +13158,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Rochelle+Park+NJ+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G34" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -11276,6 +13194,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Westlake+Village+CA+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -11306,6 +13230,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Fremont+CA+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G36" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>994</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -11336,6 +13266,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Diamond+Bar+CA+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G37" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>205</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -11366,6 +13302,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Sunnyvale+CA+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G38" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>212</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -11396,6 +13338,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Overland+Park+KS+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G39" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>841</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -11426,6 +13374,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Irving+TX+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G40" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>2233</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -11456,6 +13410,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Dublin+OH+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G41" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -11486,6 +13446,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Hicksville+NY+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G42" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>1586</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -11516,6 +13482,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Schaumburg+IL+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G43" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>1164</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -11546,6 +13518,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Chandler+AZ+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G44" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>474</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -11576,6 +13554,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Campbelltown+Adelaide+%28Australia%29?hl=en</t>
         </is>
       </c>
+      <c r="G45" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>411</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -11606,6 +13590,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Rouse+Hill+Sydney+%28Australia%29?hl=en</t>
         </is>
       </c>
+      <c r="G46" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>1045</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -11636,6 +13626,8 @@
           <t>https://www.google.com/maps/search/Bikanervala+Truganina+Melbourne+%28Australia%29?hl=en</t>
         </is>
       </c>
+      <c r="G47" s="14" t="n"/>
+      <c r="H47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -11666,6 +13658,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Henderson+Auckland+%28New+Zealand%29?hl=en</t>
         </is>
       </c>
+      <c r="G48" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>1429</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -11696,6 +13694,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Mount+Roskill+Auckland+%28New+Zealand%29?hl=en</t>
         </is>
       </c>
+      <c r="G49" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>1420</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -11726,6 +13730,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Sydenham+Christchurch+%28New+Zealand%29?hl=en</t>
         </is>
       </c>
+      <c r="G50" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H50" s="14" t="n">
+        <v>1550</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -11756,6 +13766,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Brampton+%28Canada%29?hl=en</t>
         </is>
       </c>
+      <c r="G51" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H51" s="14" t="n">
+        <v>2806</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -11786,6 +13802,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Markham+%28Canada%29?hl=en</t>
         </is>
       </c>
+      <c r="G52" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" s="14" t="n">
+        <v>744</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -11816,6 +13838,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Changi+Airport+T3+%28Singapore%29?hl=en</t>
         </is>
       </c>
+      <c r="G53" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H53" s="14" t="n">
+        <v>1229</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -11846,6 +13874,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Katong+%28Singapore%29?hl=en</t>
         </is>
       </c>
+      <c r="G54" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" s="14" t="n">
+        <v>674</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -11875,6 +13909,12 @@
         <is>
           <t>https://www.google.com/maps/search/Bikanervala+Manama+%28Bahrain%29?hl=en</t>
         </is>
+      </c>
+      <c r="G55" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H55" s="14" t="n">
+        <v>424</v>
       </c>
     </row>
     <row r="56">
@@ -12122,8 +14162,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F113"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H113"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -12139,6 +14179,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="11" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H1" s="11" t="n">
+        <v>46303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -12169,6 +14215,16 @@
       <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -12201,6 +14257,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Cross+River+Mall+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G3" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>4571</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -12231,6 +14293,12 @@
           <t>https://www.google.com/maps/search/Haldiram+CBD+Shahdara+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G4" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>1230</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -12261,6 +14329,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Vikas+Marg+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G5" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>460</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -12291,6 +14365,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Akshardham+Parsvnath+Mall+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G6" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>11587</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -12321,6 +14401,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Dilshad+Garden+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G7" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -12351,6 +14437,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Krishna+Nagar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G8" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>918</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -12381,6 +14473,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Indraprastha+Apollo+Hospital+Sarita+Vihar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G9" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>1604</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -12411,6 +14509,12 @@
           <t>https://www.google.com/maps/search/Haldiram+DLF+Promenade+Vasant+Kunj+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G10" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>2049</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -12441,6 +14545,12 @@
           <t>https://www.google.com/maps/search/Haldiram+DLF+Saket+District+Centre+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G11" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>3082</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -12471,6 +14581,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Kalkaji+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G12" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>3628</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -12501,6 +14617,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Lajpat+Nagar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G13" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>21269</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -12531,6 +14653,12 @@
           <t>https://www.google.com/maps/search/Haldiram+New+Friends+Colony+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G14" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>2947</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -12561,6 +14689,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Green+Park+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>4205</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -12591,6 +14725,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Nehru+Place+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G16" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>2389</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -12621,6 +14761,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Kailash+Colony+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G17" s="14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -12651,6 +14797,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Mathura+Road+Mohan+Co-operative+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G18" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>12127</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -12681,6 +14833,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Sarojini+Nagar+DLF+South+Square+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G19" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>3092</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -12711,6 +14869,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Malviya+Nagar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G20" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>9247</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -12741,6 +14905,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Lok+Vihar+Pitampura+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G21" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -12771,6 +14941,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Paschim+Vihar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G22" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>6137</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -12801,6 +14977,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Katwaria+Sarai+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G23" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>1766</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -12831,6 +15013,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Anupam+Saket+PVR+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G24" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>1060</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -12861,6 +15049,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Jungpura+Extension+Eros+One+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G25" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>2054</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -12891,6 +15085,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Jasola+DLF+Tower+A+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G26" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>2780</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -12921,6 +15121,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Moti+Nagar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G27" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>11084</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -12951,6 +15157,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pitampura+D+Mall+Netaji+Subhash+Place+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G28" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>5490</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -12981,6 +15193,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Janpath+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G29" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>4018</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -13011,6 +15229,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Netaji+Subhash+Place+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>1579</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -13041,6 +15265,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Netaji+Subhash+Place+2+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G31" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>1579</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -13071,6 +15301,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Bikaner+House+Pandara+Road+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G32" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>2810</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -13101,6 +15337,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Chandni+Chowk+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G33" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>18971</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -13131,6 +15373,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Connaught+Place+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G34" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>39691</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -13161,6 +15409,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Model+Town+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>5229</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -13191,6 +15445,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pusa+Road+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G36" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>10387</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -13221,6 +15481,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Dwarka+City+Centre+Sector+12+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G37" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>7404</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -13251,6 +15517,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Vegas+Mall+Food+Court+Dwarka+Sector+14+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G38" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>538</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -13281,6 +15553,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Dwarka+Sector+21+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G39" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>1124</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -13311,6 +15589,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Vegas+Mall+Showroom+Dwarka+Sector+14+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G40" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>538</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -13341,6 +15625,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Tilak+Nagar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G41" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>2621</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -13371,6 +15661,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Janakpuri+Unity+One+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G42" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>1445</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -13401,6 +15697,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Janak+Cinema+Janakpuri+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G43" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>955</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -13431,6 +15733,12 @@
           <t>https://www.google.com/maps/search/Haldiram+New+Delhi+Railway+Station?hl=en</t>
         </is>
       </c>
+      <c r="G44" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>4181</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -13461,6 +15769,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Rajouri+Garden+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G45" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>3486</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -13491,6 +15805,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Rohini+D+Mall+Sector+10+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G46" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>7886</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -13521,6 +15841,12 @@
           <t>https://www.google.com/maps/search/Haldiram+ARSS+Mall+Paschim+Vihar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G47" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>6137</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -13551,6 +15877,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Vaishali+Enclave+Pitampura+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G48" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>983</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -13581,6 +15913,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Dwarka+Sector+11+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G49" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>3645</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -13611,6 +15949,12 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T1+Domestic+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G50" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H50" s="14" t="n">
+        <v>171</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -13641,6 +15985,12 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+D-04+Domestic+Departure+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G51" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H51" s="14" t="n">
+        <v>4120</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -13671,6 +16021,12 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T3+International+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G52" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H52" s="14" t="n">
+        <v>294</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -13701,6 +16057,12 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T3+International+Departure+Gate+17B+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G53" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H53" s="14" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -13731,6 +16093,12 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T3A+Baggage+Reclaim+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G54" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H54" s="14" t="n">
+        <v>4120</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -13761,6 +16129,12 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T2+Arrival+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G55" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H55" s="14" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -13791,6 +16165,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Okhla+Jasola+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G56" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H56" s="14" t="n">
+        <v>493</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -13821,6 +16201,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Spice+Mall+Sector+25A+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G57" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H57" s="14" t="n">
+        <v>7853</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -13851,6 +16237,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Logix+City+Centre+Sector+32+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G58" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H58" s="14" t="n">
+        <v>4018</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -13881,6 +16273,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Skymark+One+Sector+98+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G59" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H59" s="14" t="n">
+        <v>2876</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -13911,6 +16309,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Paras+One33+Sector+133+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H60" s="14" t="n">
+        <v>2251</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -13941,6 +16345,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Sector+18+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G61" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H61" s="14" t="n">
+        <v>7832</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -13971,6 +16381,12 @@
           <t>https://www.google.com/maps/search/Haldiram+DLF+Mall+of+India+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G62" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H62" s="14" t="n">
+        <v>3616</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -14001,6 +16417,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Youth+Plaza+Sector+63+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G63" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" s="14" t="n">
+        <v>4769</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -14031,6 +16453,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Hush+Life+Sector+63+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G64" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H64" s="14" t="n">
+        <v>2626</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -14061,6 +16489,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Advant+IT+Park+Noida+Expressway?hl=en</t>
         </is>
       </c>
+      <c r="G65" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H65" s="14" t="n">
+        <v>2903</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -14091,6 +16525,12 @@
           <t>https://www.google.com/maps/search/Haldiram+MSX+Mall+Greater+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G66" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H66" s="14" t="n">
+        <v>6446</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -14121,6 +16561,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Grand+Venice+Mall+Greater+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G67" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H67" s="14" t="n">
+        <v>781</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -14151,6 +16597,12 @@
           <t>https://www.google.com/maps/search/Haldiram+NH8+Kherki+Daula+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G68" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H68" s="14" t="n">
+        <v>19109</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -14181,6 +16633,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Iris+Broadway+Sector+85-86+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G69" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H69" s="14" t="n">
+        <v>2918</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -14211,6 +16669,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Vatika+Business+Park+Sector+49+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G70" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H70" s="14" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
@@ -14241,6 +16705,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Three+Roads+Sector+70+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G71" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H71" s="14" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -14271,6 +16741,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Ambience+Mall+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G72" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H72" s="14" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -14301,6 +16777,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Cyber+Hub+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G73" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H73" s="14" t="n">
+        <v>3864</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -14331,6 +16813,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Fortis+Hospital+Huda+City+Centre+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G74" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H74" s="14" t="n">
+        <v>755</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -14361,6 +16849,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Palam+Vihar+Global+Foyer+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G75" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H75" s="14" t="n">
+        <v>4658</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -14391,6 +16885,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Element+One+Sector+47-49+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G76" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H76" s="14" t="n">
+        <v>5288</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -14421,6 +16921,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Eros+City+Square+Sector+49-50+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G77" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H77" s="14" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -14451,6 +16957,12 @@
           <t>https://www.google.com/maps/search/Haldiram+AIPL+Joy+Street+Sector+66+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G78" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H78" s="14" t="n">
+        <v>1131</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -14481,6 +16993,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Worldmark+3+Sector+65+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G79" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H79" s="14" t="n">
+        <v>634</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -14511,6 +17029,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Ardee+Mall+Sector+52+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G80" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H80" s="14" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -14541,6 +17065,12 @@
           <t>https://www.google.com/maps/search/Haldiram+MGF+Metropolitan+Mall+MG+Road+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G81" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H81" s="14" t="n">
+        <v>1566</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -14571,6 +17101,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Sahara+Mall+MG+Road+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G82" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H82" s="14" t="n">
+        <v>11744</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -14601,6 +17137,12 @@
           <t>https://www.google.com/maps/search/Haldiram+City+Centre+MG+Road+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G83" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H83" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
@@ -14631,6 +17173,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Sector+29+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G84" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H84" s="14" t="n">
+        <v>5933</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -14661,6 +17209,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Sector+14+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G85" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H85" s="14" t="n">
+        <v>3265</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -14691,6 +17245,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Parsvnath+City+Mall+Sector+12+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G86" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H86" s="14" t="n">
+        <v>10433</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
@@ -14721,6 +17281,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Crown+Interiorz+Sector+35+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G87" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H87" s="14" t="n">
+        <v>4152</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
@@ -14751,6 +17317,12 @@
           <t>https://www.google.com/maps/search/Haldiram+NIT+Metropolis+Mall+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G88" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H88" s="14" t="n">
+        <v>2998</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
@@ -14781,6 +17353,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Sector+15+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G89" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H89" s="14" t="n">
+        <v>1295</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -14811,6 +17389,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Angel+Mega+Mall+Kaushambi+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G90" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H90" s="14" t="n">
+        <v>2235</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
@@ -14841,6 +17425,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Ajnara+Orbit+Plaza+Crossing+Republic+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G91" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H91" s="14" t="n">
+        <v>7974</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
@@ -14871,6 +17461,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Sahibabad+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G92" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H92" s="14" t="n">
+        <v>783</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
@@ -14901,6 +17497,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Signature+Global+Mall+Vaishali+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G93" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H93" s="14" t="n">
+        <v>790</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
@@ -14931,6 +17533,12 @@
           <t>https://www.google.com/maps/search/Haldiram+RDC+Raj+Nagar+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G94" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H94" s="14" t="n">
+        <v>2595</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
@@ -14961,6 +17569,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Nehru+Nagar+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G95" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H95" s="14" t="n">
+        <v>1678</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
@@ -14991,6 +17605,12 @@
           <t>https://www.google.com/maps/search/Haldiram+World+Square+Mall+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G96" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H96" s="14" t="n">
+        <v>6440</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
@@ -15021,6 +17641,12 @@
           <t>https://www.google.com/maps/search/Haldiram+East+Delhi+Mall+Kaushambi+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G97" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H97" s="14" t="n">
+        <v>2315</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -15051,6 +17677,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Vasundhara+Sector+11+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G98" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H98" s="14" t="n">
+        <v>1937</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
@@ -15081,6 +17713,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Gajraula+NH-24?hl=en</t>
         </is>
       </c>
+      <c r="G99" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H99" s="14" t="n">
+        <v>5580</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -15111,6 +17749,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Khatauli?hl=en</t>
         </is>
       </c>
+      <c r="G100" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H100" s="14" t="n">
+        <v>17789</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -15141,6 +17785,12 @@
           <t>https://www.google.com/maps/search/Haldiram+SRK+Mall+Agra?hl=en</t>
         </is>
       </c>
+      <c r="G101" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H101" s="14" t="n">
+        <v>6173</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -15171,6 +17821,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Rewari?hl=en</t>
         </is>
       </c>
+      <c r="G102" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H102" s="14" t="n">
+        <v>5282</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
@@ -15201,6 +17857,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Jaipur+135+NH-8+Behror?hl=en</t>
         </is>
       </c>
+      <c r="G103" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H103" s="14" t="n">
+        <v>1176</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -15231,6 +17893,12 @@
           <t>https://www.google.com/maps/search/Haldiram+V+Square+Mall+Bhiwadi?hl=en</t>
         </is>
       </c>
+      <c r="G104" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H104" s="14" t="n">
+        <v>4077</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
@@ -15261,6 +17929,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Delhi+135+NH-8+Behror?hl=en</t>
         </is>
       </c>
+      <c r="G105" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H105" s="14" t="n">
+        <v>1176</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
@@ -15291,6 +17965,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Zirakpur?hl=en</t>
         </is>
       </c>
+      <c r="G106" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H106" s="14" t="n">
+        <v>10977</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -15321,6 +18001,12 @@
           <t>https://www.google.com/maps/search/Haldiram+VR+Punjab+Mall+Mohali?hl=en</t>
         </is>
       </c>
+      <c r="G107" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H107" s="14" t="n">
+        <v>3159</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -15351,6 +18037,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Ambala?hl=en</t>
         </is>
       </c>
+      <c r="G108" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H108" s="14" t="n">
+        <v>3059</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
@@ -15381,6 +18073,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Amritsar?hl=en</t>
         </is>
       </c>
+      <c r="G109" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H109" s="14" t="n">
+        <v>2622</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
@@ -15411,6 +18109,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Barnala?hl=en</t>
         </is>
       </c>
+      <c r="G110" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H110" s="14" t="n">
+        <v>1881</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
@@ -15441,6 +18145,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Sonipat?hl=en</t>
         </is>
       </c>
+      <c r="G111" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H111" s="14" t="n">
+        <v>1196</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -15471,6 +18181,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pathankot?hl=en</t>
         </is>
       </c>
+      <c r="G112" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H112" s="14" t="n">
+        <v>2454</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
@@ -15500,6 +18216,12 @@
         <is>
           <t>https://www.google.com/maps/search/Haldiram+Kosi+Kalan?hl=en</t>
         </is>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H113" s="14" t="n">
+        <v>2645</v>
       </c>
     </row>
   </sheetData>
@@ -15513,8 +18235,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -15530,6 +18252,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="11" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H1" s="11" t="n">
+        <v>46303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -15560,6 +18288,16 @@
       <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -15592,6 +18330,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Jail+Road+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G3" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>14378</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -15622,6 +18366,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Arjun+Nagar+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G4" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>1201</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -15652,6 +18402,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Elan+Town+Centre+Sector+67+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G5" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -15682,6 +18438,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Huda+Market+Sector+57+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G6" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -15712,6 +18474,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+M3M+Cosmopolitan+Sector+66+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G7" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>4837</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -15742,6 +18510,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+New+Colony+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G8" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>2067</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -15772,6 +18546,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Palam+Vihar+Road+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G9" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>5780</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -15802,6 +18582,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+10A+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G10" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>6559</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -15832,6 +18618,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+23+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G11" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>10577</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -15862,6 +18654,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+31+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G12" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>12236</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -15892,6 +18690,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+4+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G13" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>10701</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -15922,6 +18726,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+46+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G14" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>6811</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -15952,6 +18762,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+50+Good+Earth+City+Centre+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G15" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>3606</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -15982,6 +18798,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+57+Hong+Kong+Bazaar+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G16" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>4504</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -16012,6 +18834,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+7+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G17" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>878</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -16042,6 +18870,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+14+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G18" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>19721</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -16072,6 +18906,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+NIT+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G19" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>2022</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -16102,6 +18942,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Omaxe+World+Street+Sector+79+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G20" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>2045</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -16132,6 +18978,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+16+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G21" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>8784</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -16162,6 +19014,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+31+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G22" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>1119</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -16192,6 +19050,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Palwal?hl=en</t>
         </is>
       </c>
+      <c r="G23" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>677</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -16221,6 +19085,12 @@
         <is>
           <t>https://www.google.com/maps/search/Om+Sweets+Sohna?hl=en</t>
         </is>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>1822</v>
       </c>
     </row>
   </sheetData>
@@ -16234,8 +19104,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -16251,6 +19121,12 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="G1" s="11" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H1" s="11" t="n">
+        <v>46303</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -16281,6 +19157,16 @@
       <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Store Google Link</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
         </is>
       </c>
     </row>
@@ -16313,6 +19199,12 @@
           <t>https://www.google.com/maps/place/Chhappan+Bhog,+Al+Karama/@25.2479856,55.3006626,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f432656ecfa05:0x5176630a2b823f84!8m2!3d25.2479856!4d55.3006626!16s%2Fg%2F1hf18zyrs?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MTAwNS4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G3" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -16343,6 +19235,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Vegetarian+Restaurant/data=!4m7!3m6!1s0x3e5f433f29d3305d:0xca1c139baf67d16f!8m2!3d25.2620463!4d55.2972863!16s%2Fg%2F11_pspnn0!19sChIJXTDTKT9DXz4Rb9Fnr5sTHMo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G4" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>1041</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -16373,6 +19271,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Sweets+and+Restaurant/data=!4m7!3m6!1s0x3e5f42d80a18fbdb:0x9f86aefc091ecb9!8m2!3d25.2486238!4d55.3024612!16s%2Fg%2F11bbwx1fbb!19sChIJ2_sYCthCXz4RueyRwO9q-Ak?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G5" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>1981</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -16403,6 +19307,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Restaurant/data=!4m7!3m6!1s0x3e5f729cb45eefab:0xac26aaf47bcb314!8m2!3d24.9992282!4d55.170383!16s%2Fg%2F11f3hf2kqp!19sChIJq-9etJxyXz4RFLO8R69qwgo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -16433,6 +19343,12 @@
           <t>https://www.google.com/maps/place/Puranmal/data=!4m7!3m6!1s0x3e5f133176ad688d:0x3383f49dba4666ef!8m2!3d25.0476057!4d55.1311601!16s%2Fg%2F1hhgjxrxn!19sChIJjWitdjETXz4R72ZGup30gzM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G7" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>1412</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -16463,6 +19379,12 @@
           <t>https://www.google.com/maps/place/Puranmal+sweets+and+restaurant/data=!4m7!3m6!1s0x3e5f6fca777c80b7:0xd9fcbfdd4343072d!8m2!3d25.0590927!4d55.2412228!16s%2Fg%2F11y_gyll3p!19sChIJt4B8d8pvXz4RLQdDQ92__Nk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G8" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -16493,6 +19415,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Sweets+%26+Restaurant/data=!4m7!3m6!1s0x3e5f646e13b36049:0xb69ac7e875aba115!8m2!3d25.1180318!4d55.3910236!16s%2Fg%2F11bbwqz2c0!19sChIJSWCzE25kXz4RFaGrdejHmrY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G9" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>1133</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -16523,6 +19451,12 @@
           <t>https://www.google.com/maps/place/Vega+by+Puranmal/data=!4m7!3m6!1s0x3e5f4251eda72f51:0x1b6293d48301a31c!8m2!3d25.2284641!4d55.2604103!16s%2Fg%2F11bc7tvmsh!19sChIJUS-n7VFCXz4RHKMBg9STYhs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G10" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>722</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -16553,6 +19487,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Restaurants+DMCC/data=!4m7!3m6!1s0x3e5f6d48eaaed9f7:0x791c0ba6c372ae26!8m2!3d25.0690597!4d55.138396!16s%2Fg%2F11ms89fkjx!19sChIJ99mu6khtXz4RJq5yw6YLHHk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G11" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -16583,6 +19523,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Authentic+Indian+Delicacies/data=!4m7!3m6!1s0x3e5f436690ce24a1:0x7980cd991fdc9e15!8m2!3d25.2218502!4d55.2814127!16s%2Fg%2F11s_fz4c8s!19sChIJoSTOkGZDXz4RFZ7cH5nNgHk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G12" s="14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -16613,6 +19559,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Meadows+%28Enoc%29/data=!4m7!3m6!1s0x3e5f6d258d8a3247:0x6cbc17e16920e393!8m2!3d25.0642063!4d55.1549915!16s%2Fg%2F11j3phbw8b!19sChIJRzKKjSVtXz4Rk-MgaeEXvGw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G13" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -16643,6 +19595,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Greens/data=!4m7!3m6!1s0x3e5f6b50f32318cf:0xc102df0e0c359348!8m2!3d25.094062!4d55.1678865!16s%2Fg%2F11hjkgs3kq!19sChIJzxgj81BrXz4RSJM1DA7fAsE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G14" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -16673,6 +19631,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Resturant/data=!4m7!3m6!1s0x3e5f5c77eab52041:0x9bf086c3c54484d0!8m2!3d25.303719!4d55.3708944!16s%2Fg%2F11c1ptxkdb!19sChIJQSC16ndcXz4R0IRExcOG8Js?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G15" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>562</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -16703,6 +19667,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Warehouse/data=!4m7!3m6!1s0x3e5f7268095ac931:0x1bebae7a986abcaf!8m2!3d24.9894399!4d55.192723!16s%2Fg%2F11bx1gykmp!19sChIJMclaCWhyXz4Rr7xqmHqu6xs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G16" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -16733,6 +19703,12 @@
           <t>https://www.google.com/maps/place/Haldiram%E2%80%99s+Al+Mankhool-+Vegetarian+Restaurant+in+Dubai/data=!4m7!3m6!1s0x3e5f43ffefd64bdf:0xd55fd4634f47f83f!8m2!3d25.2550953!4d55.2935363!16s%2Fg%2F11yc82939p!19sChIJ30vW7_9DXz4RP_hHT2PUX9U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G17" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>5835</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -16763,6 +19739,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s-+Sheikh+Zayed+Road/data=!4m7!3m6!1s0x3e5f430026f8137d:0xbc533bf410617740!8m2!3d25.2226875!4d55.2820625!16s%2Fg%2F11z3v_0z7p!19sChIJfRP4JgBDXz4RQHdhEPQ7U7w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G18" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>1120</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -16793,6 +19775,12 @@
           <t>https://www.google.com/maps/place/Shree+Haldiram+restaurant/data=!4m7!3m6!1s0x3e5f43208d06a43d:0xa95a2f625d380979!8m2!3d25.2370936!4d55.3075144!16s%2Fg%2F11rvdtdbqf!19sChIJPaQGjSBDXz4ReQk4XWIvWqk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -16823,6 +19811,12 @@
           <t>https://www.google.com/maps/place/Kailash+Parbat/data=!4m7!3m6!1s0x3e5f4339607918bb:0xb6fb2afaf133c371!8m2!3d25.25816!4d55.3108109!16s%2Fg%2F11gtb6v4m3!19sChIJuxh5YDlDXz4RccMz8foq-7Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G20" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>2471</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -16853,6 +19847,12 @@
           <t>https://www.google.com/maps/place/Kailash+Parbat,+Pure+Veg+Restaurant+Oud+Metha,+Dubai/data=!4m7!3m6!1s0x3e5f4354d534364f:0x7e15b26dd9861a0b!8m2!3d25.236946!4d55.3066909!16s%2Fg%2F11rjttcfky!19sChIJTzY01VRDXz4RCxqG2W2yFX4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G21" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>341</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -16883,6 +19883,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb913407f2d1b5:0x3249a9e465711151!8m2!3d17.429486!4d78.4098711!16s%2Fg%2F12629gjp0!19sChIJtdHyBzSRyzsRURFxZeSpSTI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G22" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>4357</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -16913,6 +19919,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb99dd2703988d:0xef045befa5f3726e!8m2!3d17.4011091!4d78.4858873!16s%2Fg%2F1tj48yhg!19sChIJjZgDJ92ZyzsRbnLzpe9bBO8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G23" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>11258</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -16943,6 +19955,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb918eafb67403:0x509ba3d059027dd0!8m2!3d17.4859258!4d78.3903757!16s%2Fg%2F11fy9ssrk3!19sChIJA3S2r46RyzsR0H0CWdCjm1A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G24" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>13829</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -16973,6 +19991,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9b23a1136449:0xeaa3a261dda1ba18!8m2!3d17.4432886!4d78.4781068!16s%2Fg%2F11h_11dbss!19sChIJSWQToSObyzsRGLqh3WGio-o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G25" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>5024</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -17003,6 +20027,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb972c621e321f:0x39d6c04e3a800c16!8m2!3d17.4269497!4d78.4433936!16s%2Fg%2F1w110n5q!19sChIJHzIeYiyXyzsRFgyAOk7A1jk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G26" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>8083</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -17033,6 +20063,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9bdb0fd94b33:0x2cf8f2cc691ea5b4!8m2!3d17.4408497!4d78.5032582!16s%2Fg%2F11h4tnmqw2!19sChIJM0vZD9ubyzsRtKUeaczy-Cw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G27" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>7816</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -17063,6 +20099,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb93a010c47de3:0x2a6d183afbe9aea9!8m2!3d17.4495681!4d78.3634623!16s%2Fg%2F11fqqbr4t3!19sChIJ433EEKCTyzsRqa7p-zoYbSo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G28" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>6651</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -17093,6 +20135,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb95404cdeed5f:0x368b5c59f9072840!8m2!3d17.3855295!4d78.3303451!16s%2Fg%2F11xt9dz54t!19sChIJX-3eTECVyzsRQCgH-VlcizY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G29" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>1155</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -17123,6 +20171,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9727c96cf2cb:0xed10d003e11e198d!8m2!3d17.4126667!4d78.4303883!16s%2Fg%2F1ptxy0rc8!19sChIJy_JsySeXyzsRjRke4QPQEO0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G30" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>4943</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -17153,6 +20207,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9b76029a6381:0xfbe255b51a1975d8!8m2!3d17.5137477!4d78.479297!16s%2Fg%2F11svfkn0lv!19sChIJgWOaAnabyzsR2HUZGrVV4vs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G31" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>8065</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -17183,6 +20243,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcbbb81d4c3e721:0x6cfdcb31d373fc39!8m2!3d17.2352717!4d78.4306917!16s%2Fg%2F11c5t04l3c!19sChIJIefD1IG7yzsROfxz0zHL_Ww?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G32" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>8436</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -17213,6 +20279,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9b1732f66e7b:0xf311299cd0febcba!8m2!3d17.4837097!4d78.5426156!16s%2Fg%2F11y3npb6zt!19sChIJe272MhebyzsRurz-0JwpEfM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G33" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>4182</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -17243,6 +20315,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb95633e613e13:0x5de8794d037bb3ee!8m2!3d17.4203322!4d78.3797772!16s%2Fg%2F11ntl7h69x!19sChIJEz5hPmOVyzsR7rN7A0156F0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G34" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -17273,6 +20351,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Jubilee+Hills/data=!4m7!3m6!1s0x3bcb9136402aa371:0xf6b91a349382b790!8m2!3d17.4313965!4d78.407714!16s%2Fg%2F1pp2x6w4s!19sChIJcaMqQDaRyzsRkLeCkzQaufY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>4429</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -17303,6 +20387,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Himayathnagar/data=!4m7!3m6!1s0x3bcb99e0f3ba40ad:0x95ec754fd3ed92!8m2!3d17.4056989!4d78.4791329!16s%2Fg%2F1hc5k1hm9!19sChIJrUC68-CZyzsRku3TT3XslQA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G36" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>5551</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -17333,6 +20423,12 @@
           <t>https://www.google.com/maps/place/Dadu%E2%80%99s+Gachibowli/data=!4m7!3m6!1s0x3bcb93c86eaff663:0xe881fab9e954d25b!8m2!3d17.446841!4d78.3639362!16s%2Fg%2F11fn5sfyl9!19sChIJY_avbsiTyzsRW9JU6bn6geg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G37" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>4185</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -17363,6 +20459,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Banjara+Hills/data=!4m7!3m6!1s0x3bcb973c9c5873a1:0x2940a491f0de08bf!8m2!3d17.4134194!4d78.4276568!16s%2Fg%2F11by_dbs5h!19sChIJoXNYnDyXyzsRvwje8JGkQCk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G38" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>2506</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -17393,6 +20495,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Secunderabad/data=!4m7!3m6!1s0x3bcb9a101536a157:0x4fbfcbf25b9c1602!8m2!3d17.4414333!4d78.4880539!16s%2Fg%2F1td46f3y!19sChIJV6E2FRCayzsRAhacW_LLv08?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G39" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>6421</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -17423,6 +20531,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Kukatpally/data=!4m7!3m6!1s0x3bcb91f9fa95f95d:0xf3471b49fd532f93!8m2!3d17.495512!4d78.3994334!16s%2Fg%2F11h6m7_vqw!19sChIJXfmV-vmRyzsRky9T_UkbR_M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G40" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>2544</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -17453,6 +20567,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Chaitanyapuri/data=!4m7!3m6!1s0x3bcb99a4d81ed5f7:0xc4937f510b885941!8m2!3d17.3687084!4d78.5325781!16s%2Fg%2F11kbl95gd1!19sChIJ99Ue2KSZyzsRQVmIC1F_k8Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G41" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>1059</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -17483,6 +20603,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+A.s+Rao+Nagar/data=!4m7!3m6!1s0x3bcb9b47f0228861:0x9970f2f0f46294c9!8m2!3d17.4767773!4d78.5647402!16s%2Fg%2F11l1fnp8hs!19sChIJYYgi8EebyzsRyZRi9PDycJk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G42" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>799</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -17513,6 +20639,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Kompally/data=!4m7!3m6!1s0x3bcb8547f232405d:0xe1b5a93b4c962020!8m2!3d17.5239986!4d78.4830535!16s%2Fg%2F11vzgjlgsk!19sChIJXUAy8keFyzsRICCWTDupteE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G43" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>547</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -17543,6 +20675,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s/data=!4m7!3m6!1s0x3bcbbb64da0fd53d:0xd3947265d1327d51!8m2!3d17.2351596!4d78.4313221!16s%2Fg%2F11rx1gt4d5!19sChIJPdUP2mS7yzsRUX0y0WVylNM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G44" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -17573,6 +20711,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9344d3dd34e5:0x701ec19a3d8373e1!8m2!3d17.4472944!4d78.3784477!16s%2Fg%2F11ng76x8kt!19sChIJ5TTd00STyzsR4XODPZrBHnA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G45" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>5063</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -17603,6 +20747,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb97a0091cc689:0x5f7ee7f4961d390c!8m2!3d17.4191704!4d78.4486398!16s%2Fg%2F11n5wdprb_!19sChIJicYcCaCXyzsRDDkdlvTnfl8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G46" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>647</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -17633,6 +20783,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s+-+Aero+Plaza,+Hyderabad/data=!4m7!3m6!1s0x3bcbbbff55e0cb19:0x4268c454a214c7a3!8m2!3d17.237544!4d78.4295774!16s%2Fg%2F11ptph2_n0!19sChIJGcvgVf-7yzsRo8cUolTEaEI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G47" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>2581</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -17663,6 +20819,12 @@
           <t>https://www.google.com/maps/place/Haldirams+-+International+Airport,+Hyderabad/data=!4m7!3m6!1s0x3bcbbbc5450a64d5:0x66e9f016f5a1788a!8m2!3d17.2356242!4d78.4297872!16s%2Fg%2F11y37rf_81!19sChIJ1WQKRcW7yzsRinih9Rbw6WY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G48" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -17693,6 +20855,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb99d3156ad8a7:0x1f634101e38f8bf1!8m2!3d17.3719005!4d78.5112991!16s%2Fg%2F11sbh9wfj7!19sChIJp9hqFdOZyzsR8YuP4wFBYx8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G49" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>4615</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -17723,6 +20891,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s+-+Begumpet/data=!4m7!3m6!1s0x3bcb9b2fb6226879:0x792f95f1fa86db53!8m2!3d17.4433059!4d78.4779833!16s%2Fg%2F11y1vfjg9x!19sChIJeWgiti-byzsRU9uG-vGVL3k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G50" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H50" s="14" t="n">
+        <v>3299</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -17753,6 +20927,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9193207c307b:0x21e95c3d44bbc116!8m2!3d17.434484!4d78.386676!16s%2Fg%2F11mngj1_p3!19sChIJezB8IJORyzsRFsG7RD1c6SE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G51" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H51" s="14" t="n">
+        <v>783</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -17783,6 +20963,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb93ac007ef313:0x5752fbf292af5ebc!8m2!3d17.457948!4d78.3636007!16s%2Fg%2F11h8y9pk4d!19sChIJE_N-AKyTyzsRvF6vkvL7Ulc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G52" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H52" s="14" t="n">
+        <v>1497</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -17813,6 +20999,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcbbb42526f5f6f:0xc737ba21de493937!8m2!3d17.2365531!4d78.4294807!16s%2Fg%2F11rv6lmby8!19sChIJb19vUkK7yzsRNzlJ3iG6N8c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G53" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H53" s="14" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -17843,6 +21035,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb992d5300c2dd:0x78bb7b7bb178e2a5!8m2!3d17.4004116!4d78.5549239!16s%2Fg%2F11sk8g8pt2!19sChIJ3cIAUy2ZyzsRpeJ4sXt7u3g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G54" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H54" s="14" t="n">
+        <v>2811</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -17873,6 +21071,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb91b0dd59094f:0x4a980e70f98df750!8m2!3d17.4840645!4d78.3890165!16s%2Fg%2F11rskcz6d0!19sChIJTwlZ3bCRyzsRUPeN-XAOmEo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G55" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H55" s="14" t="n">
+        <v>706</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -17903,6 +21107,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s+-+Gachibowli+Cloud/data=!4m7!3m6!1s0x3bcb93e8a066f96f:0xdf24b9aaf267c9cb!8m2!3d17.4396118!4d78.3630471!16s%2Fg%2F11kjk464rc!19sChIJb_lmoOiTyzsRy8ln8qq5JN8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G56" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H56" s="14" t="n">
+        <v>289</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -17933,6 +21143,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9771a71af1bd:0x2120c1b9f031a51!8m2!3d17.3544993!4d78.421283!16s%2Fg%2F11kpdgvt17!19sChIJvfEap3GXyzsRURoDnxsMEgI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G57" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H57" s="14" t="n">
+        <v>4513</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -17963,6 +21179,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb990fbe5eacb3:0xe000f43fccaa7968!8m2!3d17.4239975!4d78.4950257!16s%2Fg%2F11ryf8j305!19sChIJs6xevg-ZyzsRaHmqzD_0AOA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G58" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H58" s="14" t="n">
+        <v>456</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -17993,6 +21215,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9146f44ba4bd:0xa4cac9184debd8ad!8m2!3d17.4789078!4d78.4738022!16s%2Fg%2F11swvb46nc!19sChIJvaRL9EaRyzsRrdjrTRjJyqQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G59" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H59" s="14" t="n">
+        <v>3006</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -18023,6 +21251,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9320c77fb721:0xba3e7a353ad20f19!8m2!3d17.4344005!4d78.3823429!16s%2Fg%2F11s17v2vrz!19sChIJIbd_xyCTyzsRGQ_SOjV6Pro?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H60" s="14" t="n">
+        <v>971</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -18052,6 +21286,12 @@
         <is>
           <t>https://www.google.com/maps/place/Haldiram%27s+-+Nallagandla/data=!4m7!3m6!1s0x3bcb93827c79a5cd:0x5f3be93001f7c002!8m2!3d17.4711734!4d78.3097188!16s%2Fg%2F11y44x1nlx!19sChIJzaV5fIKTyzsRAsD3ATDpO18?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
+      </c>
+      <c r="G61" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H61" s="14" t="n">
+        <v>1074</v>
       </c>
     </row>
   </sheetData>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -659,7 +659,7 @@
         <v>4.4</v>
       </c>
       <c r="H3" s="14" t="n">
-        <v>4871</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         <v>4.3</v>
       </c>
       <c r="H4" s="14" t="n">
-        <v>15768</v>
+        <v>15765</v>
       </c>
     </row>
     <row r="5">
@@ -731,7 +731,7 @@
         <v>4.5</v>
       </c>
       <c r="H5" s="14" t="n">
-        <v>5546</v>
+        <v>5545</v>
       </c>
     </row>
     <row r="6">
@@ -767,7 +767,7 @@
         <v>4.3</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>6544</v>
+        <v>6545</v>
       </c>
     </row>
     <row r="7">
@@ -803,7 +803,7 @@
         <v>4.5</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>2414</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="8">
@@ -839,7 +839,7 @@
         <v>4.4</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>7187</v>
+        <v>7188</v>
       </c>
     </row>
     <row r="9">
@@ -875,7 +875,7 @@
         <v>4.4</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>3666</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="10">
@@ -911,7 +911,7 @@
         <v>4.4</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>2768</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="11">
@@ -1019,7 +1019,7 @@
         <v>4.7</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>2222</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="14">
@@ -1055,7 +1055,7 @@
         <v>4.4</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>2379</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="15">
@@ -1091,7 +1091,7 @@
         <v>4.4</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>2598</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="16">
@@ -1127,7 +1127,7 @@
         <v>4.5</v>
       </c>
       <c r="H16" s="14" t="n">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="17">
@@ -1235,7 +1235,7 @@
         <v>4.7</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="20">
@@ -1271,7 +1271,7 @@
         <v>4.6</v>
       </c>
       <c r="H20" s="14" t="n">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="21">
@@ -1379,7 +1379,7 @@
         <v>4.8</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="24">
@@ -1607,7 +1607,7 @@
         <v>4.8</v>
       </c>
       <c r="I3" s="14" t="n">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="4">
@@ -1812,7 +1812,7 @@
         <v>4.5</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="9">
@@ -1853,7 +1853,7 @@
         <v>4.4</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>3265</v>
+        <v>3266</v>
       </c>
     </row>
     <row r="10">
@@ -2099,7 +2099,7 @@
         <v>4.4</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>7187</v>
+        <v>7188</v>
       </c>
     </row>
     <row r="16">
@@ -2263,7 +2263,7 @@
         <v>4.3</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>6544</v>
+        <v>6545</v>
       </c>
     </row>
     <row r="20">
@@ -2304,7 +2304,7 @@
         <v>4.4</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>2768</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="21">
@@ -2345,7 +2345,7 @@
         <v>4.3</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>15768</v>
+        <v>15765</v>
       </c>
     </row>
     <row r="22">
@@ -2386,7 +2386,7 @@
         <v>4.2</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>5933</v>
+        <v>5934</v>
       </c>
     </row>
     <row r="23">
@@ -2509,7 +2509,7 @@
         <v>4.3</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>2006</v>
+        <v>19109</v>
       </c>
     </row>
     <row r="26">
@@ -2591,7 +2591,7 @@
         <v>4.4</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>3666</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="28">
@@ -2673,7 +2673,7 @@
         <v>4.4</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>4871</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="30">
@@ -2755,7 +2755,7 @@
         <v>4.7</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>2222</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="32">
@@ -2837,7 +2837,7 @@
         <v>4.5</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>5546</v>
+        <v>5545</v>
       </c>
     </row>
     <row r="34">
@@ -3001,7 +3001,7 @@
         <v>4.5</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>2414</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="38">
@@ -3083,7 +3083,7 @@
         <v>4.4</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>2598</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="40">
@@ -3247,7 +3247,7 @@
         <v>4.6</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="44">
@@ -3370,7 +3370,7 @@
         <v>4.3</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="47">
@@ -3411,7 +3411,7 @@
         <v>4.4</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>2379</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="48">
@@ -3452,7 +3452,7 @@
         <v>4.7</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="49">
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="H51" s="14" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="I51" s="14" t="n">
-        <v>1566</v>
+        <v>5934</v>
       </c>
     </row>
     <row r="52">
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="H53" s="14" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>3265</v>
+        <v>5934</v>
       </c>
     </row>
     <row r="54">
@@ -3736,10 +3736,10 @@
         </is>
       </c>
       <c r="H55" s="14" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>5547</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56">
@@ -3903,7 +3903,7 @@
         <v>4.2</v>
       </c>
       <c r="I59" s="14" t="n">
-        <v>5780</v>
+        <v>5781</v>
       </c>
     </row>
     <row r="60">
@@ -4108,7 +4108,7 @@
         <v>4.3</v>
       </c>
       <c r="I64" s="14" t="n">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="65">
@@ -4149,7 +4149,7 @@
         <v>4.2</v>
       </c>
       <c r="I65" s="14" t="n">
-        <v>28</v>
+        <v>19721</v>
       </c>
     </row>
     <row r="66">
@@ -4272,7 +4272,7 @@
         <v>4.2</v>
       </c>
       <c r="I68" s="14" t="n">
-        <v>14377</v>
+        <v>14379</v>
       </c>
     </row>
   </sheetData>
@@ -4395,7 +4395,7 @@
         <v>4.3</v>
       </c>
       <c r="I3" s="14" t="n">
-        <v>2115</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -4559,7 +4559,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>10888</v>
+        <v>10889</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -4600,7 +4600,7 @@
         <v>4.2</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>2940</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -4682,7 +4682,7 @@
         <v>4.3</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>5138</v>
+        <v>5139</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="H11" s="14" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>1</v>
+        <v>52621</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H12" s="14" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>656</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -4805,7 +4805,7 @@
         <v>4.3</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>2494</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="H15" s="14" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="H16" s="14" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>3431</v>
+        <v>449</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -4966,10 +4966,10 @@
         </is>
       </c>
       <c r="H17" s="14" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>220</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="H18" s="14" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>1865</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -5051,7 +5051,7 @@
         <v>4.3</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="H25" s="14" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>1</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -5338,7 +5338,7 @@
         <v>4.6</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -5420,7 +5420,7 @@
         <v>4.5</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>10034</v>
+        <v>10035</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -5461,7 +5461,7 @@
         <v>4.3</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>8671</v>
+        <v>8673</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -5502,7 +5502,7 @@
         <v>4.6</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>21970</v>
+        <v>22258</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -5615,7 +5615,7 @@
         <v>4.4</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>4871</v>
+        <v>4870</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -5651,7 +5651,7 @@
         <v>4.5</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="H35" s="14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -5720,10 +5720,10 @@
         </is>
       </c>
       <c r="H36" s="14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>695</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -5795,7 +5795,7 @@
         <v>4.7</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>2687</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -5831,7 +5831,7 @@
         <v>4</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>23003</v>
+        <v>23004</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -5939,7 +5939,7 @@
         <v>4.5</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>2414</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="H43" s="14" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>2222</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -6011,7 +6011,7 @@
         <v>4.3</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>1358</v>
+        <v>6545</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -6083,7 +6083,7 @@
         <v>4.4</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>7190</v>
+        <v>7188</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H47" s="14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>56</v>
+        <v>3809</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -6155,7 +6155,7 @@
         <v>4.4</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>3666</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -6191,7 +6191,7 @@
         <v>4.4</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>2379</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -6227,7 +6227,7 @@
         <v>4.4</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>5591</v>
+        <v>5593</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -6296,10 +6296,10 @@
         </is>
       </c>
       <c r="H52" s="14" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>772</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -6803,7 +6803,7 @@
         <v>3.9</v>
       </c>
       <c r="I66" s="14" t="n">
-        <v>4137</v>
+        <v>4138</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -6836,10 +6836,10 @@
         </is>
       </c>
       <c r="H67" s="14" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="I67" s="14" t="n">
-        <v>44</v>
+        <v>26858</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -6875,7 +6875,7 @@
         <v>4.5</v>
       </c>
       <c r="I68" s="14" t="n">
-        <v>4300</v>
+        <v>4301</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -6911,7 +6911,7 @@
         <v>4.7</v>
       </c>
       <c r="I69" s="14" t="n">
-        <v>2213</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -7055,7 +7055,7 @@
         <v>4.3</v>
       </c>
       <c r="I73" s="14" t="n">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -7127,7 +7127,7 @@
         <v>4.2</v>
       </c>
       <c r="I75" s="14" t="n">
-        <v>16969</v>
+        <v>16970</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -7232,10 +7232,10 @@
         </is>
       </c>
       <c r="H78" s="14" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I78" s="14" t="n">
-        <v>10943</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -7383,7 +7383,7 @@
         <v>4.4</v>
       </c>
       <c r="I82" s="14" t="n">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -7419,7 +7419,7 @@
         <v>4.2</v>
       </c>
       <c r="I83" s="14" t="n">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -7491,7 +7491,7 @@
         <v>4.6</v>
       </c>
       <c r="I85" s="14" t="n">
-        <v>3949</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -7560,10 +7560,10 @@
         </is>
       </c>
       <c r="H87" s="14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I87" s="14" t="n">
-        <v>9</v>
+        <v>4503</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -7704,10 +7704,10 @@
         </is>
       </c>
       <c r="H91" s="14" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I91" s="14" t="n">
-        <v>19</v>
+        <v>859</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="H92" s="14" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I92" s="14" t="n">
-        <v>27258</v>
+        <v>387</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="H99" s="14" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I99" s="14" t="n">
-        <v>12477</v>
+        <v>44060</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -8100,10 +8100,10 @@
         </is>
       </c>
       <c r="H102" s="14" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="I102" s="14" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="H106" s="14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I106" s="14" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="H107" s="14" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I107" s="14" t="n">
-        <v>4253</v>
+        <v>444</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -8632,7 +8632,7 @@
         <v>4.3</v>
       </c>
       <c r="I116" s="14" t="n">
-        <v>8671</v>
+        <v>8673</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -8673,7 +8673,7 @@
         <v>4.2</v>
       </c>
       <c r="I117" s="14" t="n">
-        <v>11852</v>
+        <v>11855</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -8714,7 +8714,7 @@
         <v>4.4</v>
       </c>
       <c r="I118" s="14" t="n">
-        <v>2769</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -9001,7 +9001,7 @@
         <v>4.2</v>
       </c>
       <c r="I125" s="14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -9340,7 +9340,7 @@
         <v>4.8</v>
       </c>
       <c r="I134" s="14" t="n">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -9556,7 +9556,7 @@
         <v>4.4</v>
       </c>
       <c r="I140" s="14" t="n">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -9664,7 +9664,7 @@
         <v>4.1</v>
       </c>
       <c r="I143" s="14" t="n">
-        <v>4189</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -9772,7 +9772,7 @@
         <v>4.6</v>
       </c>
       <c r="I146" s="14" t="n">
-        <v>3949</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -9916,7 +9916,7 @@
         <v>4</v>
       </c>
       <c r="I150" s="14" t="n">
-        <v>2594</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -10096,7 +10096,7 @@
         <v>4.5</v>
       </c>
       <c r="I155" s="14" t="n">
-        <v>4300</v>
+        <v>4301</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -10348,7 +10348,7 @@
         <v>4.2</v>
       </c>
       <c r="I162" s="14" t="n">
-        <v>1937</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -10384,7 +10384,7 @@
         <v>4.1</v>
       </c>
       <c r="I163" s="14" t="n">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -10564,7 +10564,7 @@
         <v>4.4</v>
       </c>
       <c r="I168" s="14" t="n">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -10600,7 +10600,7 @@
         <v>4.8</v>
       </c>
       <c r="I169" s="14" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -10744,7 +10744,7 @@
         <v>3.8</v>
       </c>
       <c r="I173" s="14" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -10924,7 +10924,7 @@
         <v>4.1</v>
       </c>
       <c r="I178" s="14" t="n">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -10960,7 +10960,7 @@
         <v>3.9</v>
       </c>
       <c r="I179" s="14" t="n">
-        <v>3196</v>
+        <v>3197</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -10996,7 +10996,7 @@
         <v>4.3</v>
       </c>
       <c r="I180" s="14" t="n">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -11068,7 +11068,7 @@
         <v>4.1</v>
       </c>
       <c r="I182" s="14" t="n">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
@@ -11176,7 +11176,7 @@
         <v>4.2</v>
       </c>
       <c r="I185" s="14" t="n">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
@@ -11356,7 +11356,7 @@
         <v>4.3</v>
       </c>
       <c r="I190" s="14" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
@@ -11428,7 +11428,7 @@
         <v>4.5</v>
       </c>
       <c r="I192" s="14" t="n">
-        <v>2939</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
@@ -11572,7 +11572,7 @@
         <v>4.7</v>
       </c>
       <c r="I196" s="14" t="n">
-        <v>2665</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -11644,7 +11644,7 @@
         <v>4.6</v>
       </c>
       <c r="I198" s="14" t="n">
-        <v>8998</v>
+        <v>8996</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -11784,12 +11784,8 @@
           <t>https://goo.gl/maps/gt6giRYsgV7Jfsmp8</t>
         </is>
       </c>
-      <c r="H202" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I202" s="14" t="n">
-        <v>2882</v>
-      </c>
+      <c r="H202" s="14" t="n"/>
+      <c r="I202" s="14" t="n"/>
     </row>
     <row r="203" ht="20" customHeight="1">
       <c r="A203" s="7" t="n">
@@ -11824,7 +11820,7 @@
         <v>4.8</v>
       </c>
       <c r="I203" s="14" t="n">
-        <v>16993</v>
+        <v>17008</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -11896,7 +11892,7 @@
         <v>4.2</v>
       </c>
       <c r="I205" s="14" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
@@ -11947,7 +11943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11970,6 +11966,12 @@
       <c r="H1" s="11" t="n">
         <v>46303</v>
       </c>
+      <c r="I1" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="J1" s="11" t="n">
+        <v>46304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -12008,6 +12010,16 @@
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -12048,6 +12060,12 @@
       <c r="H3" s="14" t="n">
         <v>6999</v>
       </c>
+      <c r="I3" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>7003</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -12084,6 +12102,12 @@
       <c r="H4" s="14" t="n">
         <v>1720</v>
       </c>
+      <c r="I4" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>1720</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -12120,6 +12144,12 @@
       <c r="H5" s="14" t="n">
         <v>3414</v>
       </c>
+      <c r="I5" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>3417</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -12156,6 +12186,12 @@
       <c r="H6" s="14" t="n">
         <v>1351</v>
       </c>
+      <c r="I6" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>1351</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -12192,6 +12228,12 @@
       <c r="H7" s="14" t="n">
         <v>1108</v>
       </c>
+      <c r="I7" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>1109</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -12228,6 +12270,12 @@
       <c r="H8" s="14" t="n">
         <v>3371</v>
       </c>
+      <c r="I8" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>3370</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -12264,6 +12312,12 @@
       <c r="H9" s="14" t="n">
         <v>1970</v>
       </c>
+      <c r="I9" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -12300,6 +12354,12 @@
       <c r="H10" s="14" t="n">
         <v>1200</v>
       </c>
+      <c r="I10" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>1201</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -12336,6 +12396,12 @@
       <c r="H11" s="14" t="n">
         <v>812</v>
       </c>
+      <c r="I11" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>812</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -12372,6 +12438,12 @@
       <c r="H12" s="14" t="n">
         <v>3414</v>
       </c>
+      <c r="I12" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>3417</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -12408,6 +12480,12 @@
       <c r="H13" s="14" t="n">
         <v>406</v>
       </c>
+      <c r="I13" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>406</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -12444,6 +12522,12 @@
       <c r="H14" s="14" t="n">
         <v>3465</v>
       </c>
+      <c r="I14" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>3466</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -12480,6 +12564,12 @@
       <c r="H15" s="14" t="n">
         <v>1986</v>
       </c>
+      <c r="I15" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>1986</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -12516,6 +12606,12 @@
       <c r="H16" s="14" t="n">
         <v>1337</v>
       </c>
+      <c r="I16" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>1337</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -12552,6 +12648,12 @@
       <c r="H17" s="14" t="n">
         <v>1337</v>
       </c>
+      <c r="I17" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>1336</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -12588,6 +12690,12 @@
       <c r="H18" s="14" t="n">
         <v>4492</v>
       </c>
+      <c r="I18" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>4492</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -12624,6 +12732,12 @@
       <c r="H19" s="14" t="n">
         <v>1672</v>
       </c>
+      <c r="I19" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>1674</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -12660,6 +12774,12 @@
       <c r="H20" s="14" t="n">
         <v>4374</v>
       </c>
+      <c r="I20" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>4379</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -12696,6 +12816,12 @@
       <c r="H21" s="14" t="n">
         <v>3854</v>
       </c>
+      <c r="I21" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>3858</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -12732,6 +12858,12 @@
       <c r="H22" s="14" t="n">
         <v>87</v>
       </c>
+      <c r="I22" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -12768,6 +12900,12 @@
       <c r="H23" s="14" t="n">
         <v>443</v>
       </c>
+      <c r="I23" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>443</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -12804,6 +12942,12 @@
       <c r="H24" s="14" t="n">
         <v>1684</v>
       </c>
+      <c r="I24" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>1684</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -12840,6 +12984,12 @@
       <c r="H25" s="14" t="n">
         <v>3364</v>
       </c>
+      <c r="I25" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>3364</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -12876,6 +13026,12 @@
       <c r="H26" s="14" t="n">
         <v>1766</v>
       </c>
+      <c r="I26" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>1765</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -12912,6 +13068,12 @@
       <c r="H27" s="14" t="n">
         <v>531</v>
       </c>
+      <c r="I27" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>532</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -12948,6 +13110,12 @@
       <c r="H28" s="14" t="n">
         <v>1325</v>
       </c>
+      <c r="I28" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>1325</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -12984,6 +13152,12 @@
       <c r="H29" s="14" t="n">
         <v>642</v>
       </c>
+      <c r="I29" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>642</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -13020,6 +13194,12 @@
       <c r="H30" s="14" t="n">
         <v>35</v>
       </c>
+      <c r="I30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -13056,6 +13236,12 @@
       <c r="H31" s="14" t="n">
         <v>1323</v>
       </c>
+      <c r="I31" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>1323</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -13092,6 +13278,12 @@
       <c r="H32" s="14" t="n">
         <v>1427</v>
       </c>
+      <c r="I32" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>1427</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -13128,6 +13320,12 @@
       <c r="H33" s="14" t="n">
         <v>1335</v>
       </c>
+      <c r="I33" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>1335</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -13164,6 +13362,12 @@
       <c r="H34" s="14" t="n">
         <v>192</v>
       </c>
+      <c r="I34" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -13200,6 +13404,12 @@
       <c r="H35" s="14" t="n">
         <v>127</v>
       </c>
+      <c r="I35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -13236,6 +13446,12 @@
       <c r="H36" s="14" t="n">
         <v>994</v>
       </c>
+      <c r="I36" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>994</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -13272,6 +13488,12 @@
       <c r="H37" s="14" t="n">
         <v>205</v>
       </c>
+      <c r="I37" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>205</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -13308,6 +13530,12 @@
       <c r="H38" s="14" t="n">
         <v>212</v>
       </c>
+      <c r="I38" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>212</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -13344,6 +13572,12 @@
       <c r="H39" s="14" t="n">
         <v>841</v>
       </c>
+      <c r="I39" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J39" s="14" t="n">
+        <v>847</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -13380,6 +13614,12 @@
       <c r="H40" s="14" t="n">
         <v>2233</v>
       </c>
+      <c r="I40" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>2234</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -13416,6 +13656,12 @@
       <c r="H41" s="14" t="n">
         <v>450</v>
       </c>
+      <c r="I41" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J41" s="14" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -13452,6 +13698,12 @@
       <c r="H42" s="14" t="n">
         <v>1586</v>
       </c>
+      <c r="I42" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J42" s="14" t="n">
+        <v>1587</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -13488,6 +13740,12 @@
       <c r="H43" s="14" t="n">
         <v>1164</v>
       </c>
+      <c r="I43" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J43" s="14" t="n">
+        <v>1165</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -13524,6 +13782,12 @@
       <c r="H44" s="14" t="n">
         <v>474</v>
       </c>
+      <c r="I44" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J44" s="14" t="n">
+        <v>474</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -13560,6 +13824,12 @@
       <c r="H45" s="14" t="n">
         <v>411</v>
       </c>
+      <c r="I45" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J45" s="14" t="n">
+        <v>410</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -13596,6 +13866,12 @@
       <c r="H46" s="14" t="n">
         <v>1045</v>
       </c>
+      <c r="I46" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J46" s="14" t="n">
+        <v>1045</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -13628,6 +13904,12 @@
       </c>
       <c r="G47" s="14" t="n"/>
       <c r="H47" s="14" t="n"/>
+      <c r="I47" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J47" s="14" t="n">
+        <v>2568</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -13664,6 +13946,12 @@
       <c r="H48" s="14" t="n">
         <v>1429</v>
       </c>
+      <c r="I48" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J48" s="14" t="n">
+        <v>1429</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -13700,6 +13988,12 @@
       <c r="H49" s="14" t="n">
         <v>1420</v>
       </c>
+      <c r="I49" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J49" s="14" t="n">
+        <v>1420</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -13736,6 +14030,12 @@
       <c r="H50" s="14" t="n">
         <v>1550</v>
       </c>
+      <c r="I50" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J50" s="14" t="n">
+        <v>1550</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -13772,6 +14072,12 @@
       <c r="H51" s="14" t="n">
         <v>2806</v>
       </c>
+      <c r="I51" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J51" s="14" t="n">
+        <v>2807</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -13808,6 +14114,12 @@
       <c r="H52" s="14" t="n">
         <v>744</v>
       </c>
+      <c r="I52" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" s="14" t="n">
+        <v>744</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -13844,6 +14156,12 @@
       <c r="H53" s="14" t="n">
         <v>1229</v>
       </c>
+      <c r="I53" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J53" s="14" t="n">
+        <v>1230</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -13880,6 +14198,12 @@
       <c r="H54" s="14" t="n">
         <v>674</v>
       </c>
+      <c r="I54" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" s="14" t="n">
+        <v>674</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -13914,6 +14238,12 @@
         <v>4.4</v>
       </c>
       <c r="H55" s="14" t="n">
+        <v>424</v>
+      </c>
+      <c r="I55" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J55" s="14" t="n">
         <v>424</v>
       </c>
     </row>
@@ -14162,7 +14492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14185,6 +14515,12 @@
       <c r="H1" s="11" t="n">
         <v>46303</v>
       </c>
+      <c r="I1" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="J1" s="11" t="n">
+        <v>46304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -14223,6 +14559,16 @@
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -14263,6 +14609,12 @@
       <c r="H3" s="14" t="n">
         <v>4571</v>
       </c>
+      <c r="I3" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>4571</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -14299,6 +14651,12 @@
       <c r="H4" s="14" t="n">
         <v>1230</v>
       </c>
+      <c r="I4" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>1230</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -14335,6 +14693,12 @@
       <c r="H5" s="14" t="n">
         <v>460</v>
       </c>
+      <c r="I5" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>460</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -14371,6 +14735,12 @@
       <c r="H6" s="14" t="n">
         <v>11587</v>
       </c>
+      <c r="I6" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>11588</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -14407,6 +14777,12 @@
       <c r="H7" s="14" t="n">
         <v>2050</v>
       </c>
+      <c r="I7" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -14443,6 +14819,12 @@
       <c r="H8" s="14" t="n">
         <v>918</v>
       </c>
+      <c r="I8" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>919</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -14479,6 +14861,12 @@
       <c r="H9" s="14" t="n">
         <v>1604</v>
       </c>
+      <c r="I9" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>1604</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -14515,6 +14903,12 @@
       <c r="H10" s="14" t="n">
         <v>2049</v>
       </c>
+      <c r="I10" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>2019</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -14551,6 +14945,12 @@
       <c r="H11" s="14" t="n">
         <v>3082</v>
       </c>
+      <c r="I11" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>3082</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -14587,6 +14987,12 @@
       <c r="H12" s="14" t="n">
         <v>3628</v>
       </c>
+      <c r="I12" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>3629</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -14623,6 +15029,12 @@
       <c r="H13" s="14" t="n">
         <v>21269</v>
       </c>
+      <c r="I13" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>21269</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -14659,6 +15071,12 @@
       <c r="H14" s="14" t="n">
         <v>2947</v>
       </c>
+      <c r="I14" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>2947</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -14695,6 +15113,12 @@
       <c r="H15" s="14" t="n">
         <v>4205</v>
       </c>
+      <c r="I15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>4205</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -14731,6 +15155,12 @@
       <c r="H16" s="14" t="n">
         <v>2389</v>
       </c>
+      <c r="I16" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>2390</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -14767,6 +15197,12 @@
       <c r="H17" s="14" t="n">
         <v>4</v>
       </c>
+      <c r="I17" s="14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -14803,6 +15239,12 @@
       <c r="H18" s="14" t="n">
         <v>12127</v>
       </c>
+      <c r="I18" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>12127</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -14839,6 +15281,12 @@
       <c r="H19" s="14" t="n">
         <v>3092</v>
       </c>
+      <c r="I19" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>3092</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -14875,6 +15323,12 @@
       <c r="H20" s="14" t="n">
         <v>9247</v>
       </c>
+      <c r="I20" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>9247</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -14911,6 +15365,12 @@
       <c r="H21" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="I21" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -14947,6 +15407,12 @@
       <c r="H22" s="14" t="n">
         <v>6137</v>
       </c>
+      <c r="I22" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>6137</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -14983,6 +15449,12 @@
       <c r="H23" s="14" t="n">
         <v>1766</v>
       </c>
+      <c r="I23" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>1769</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -15019,6 +15491,12 @@
       <c r="H24" s="14" t="n">
         <v>1060</v>
       </c>
+      <c r="I24" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>1060</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -15055,6 +15533,12 @@
       <c r="H25" s="14" t="n">
         <v>2054</v>
       </c>
+      <c r="I25" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>2054</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -15091,6 +15575,12 @@
       <c r="H26" s="14" t="n">
         <v>2780</v>
       </c>
+      <c r="I26" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>2780</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -15127,6 +15617,12 @@
       <c r="H27" s="14" t="n">
         <v>11084</v>
       </c>
+      <c r="I27" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>11084</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -15163,6 +15659,12 @@
       <c r="H28" s="14" t="n">
         <v>5490</v>
       </c>
+      <c r="I28" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>5490</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -15199,6 +15701,12 @@
       <c r="H29" s="14" t="n">
         <v>4018</v>
       </c>
+      <c r="I29" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>4018</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -15235,6 +15743,12 @@
       <c r="H30" s="14" t="n">
         <v>1579</v>
       </c>
+      <c r="I30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>1580</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -15271,6 +15785,12 @@
       <c r="H31" s="14" t="n">
         <v>1579</v>
       </c>
+      <c r="I31" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>1580</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -15307,6 +15827,12 @@
       <c r="H32" s="14" t="n">
         <v>2810</v>
       </c>
+      <c r="I32" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>2809</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -15343,6 +15869,12 @@
       <c r="H33" s="14" t="n">
         <v>18971</v>
       </c>
+      <c r="I33" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>18972</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -15379,6 +15911,12 @@
       <c r="H34" s="14" t="n">
         <v>39691</v>
       </c>
+      <c r="I34" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>39694</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -15415,6 +15953,12 @@
       <c r="H35" s="14" t="n">
         <v>5229</v>
       </c>
+      <c r="I35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>5229</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -15451,6 +15995,12 @@
       <c r="H36" s="14" t="n">
         <v>10387</v>
       </c>
+      <c r="I36" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>10387</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -15487,6 +16037,12 @@
       <c r="H37" s="14" t="n">
         <v>7404</v>
       </c>
+      <c r="I37" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>7405</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -15523,6 +16079,12 @@
       <c r="H38" s="14" t="n">
         <v>538</v>
       </c>
+      <c r="I38" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>538</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -15559,6 +16121,12 @@
       <c r="H39" s="14" t="n">
         <v>1124</v>
       </c>
+      <c r="I39" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J39" s="14" t="n">
+        <v>1124</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -15595,6 +16163,12 @@
       <c r="H40" s="14" t="n">
         <v>538</v>
       </c>
+      <c r="I40" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>538</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -15631,6 +16205,12 @@
       <c r="H41" s="14" t="n">
         <v>2621</v>
       </c>
+      <c r="I41" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J41" s="14" t="n">
+        <v>2621</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -15667,6 +16247,12 @@
       <c r="H42" s="14" t="n">
         <v>1445</v>
       </c>
+      <c r="I42" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J42" s="14" t="n">
+        <v>1445</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -15703,6 +16289,12 @@
       <c r="H43" s="14" t="n">
         <v>955</v>
       </c>
+      <c r="I43" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J43" s="14" t="n">
+        <v>955</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -15739,6 +16331,12 @@
       <c r="H44" s="14" t="n">
         <v>4181</v>
       </c>
+      <c r="I44" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J44" s="14" t="n">
+        <v>4181</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -15775,6 +16373,12 @@
       <c r="H45" s="14" t="n">
         <v>3486</v>
       </c>
+      <c r="I45" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J45" s="14" t="n">
+        <v>3486</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -15811,6 +16415,12 @@
       <c r="H46" s="14" t="n">
         <v>7886</v>
       </c>
+      <c r="I46" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J46" s="14" t="n">
+        <v>7886</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -15847,6 +16457,12 @@
       <c r="H47" s="14" t="n">
         <v>6137</v>
       </c>
+      <c r="I47" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J47" s="14" t="n">
+        <v>6137</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -15883,6 +16499,12 @@
       <c r="H48" s="14" t="n">
         <v>983</v>
       </c>
+      <c r="I48" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J48" s="14" t="n">
+        <v>983</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -15919,6 +16541,12 @@
       <c r="H49" s="14" t="n">
         <v>3645</v>
       </c>
+      <c r="I49" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J49" s="14" t="n">
+        <v>3645</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -15955,6 +16583,12 @@
       <c r="H50" s="14" t="n">
         <v>171</v>
       </c>
+      <c r="I50" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J50" s="14" t="n">
+        <v>171</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -15991,6 +16625,12 @@
       <c r="H51" s="14" t="n">
         <v>4120</v>
       </c>
+      <c r="I51" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J51" s="14" t="n">
+        <v>171</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -16027,6 +16667,12 @@
       <c r="H52" s="14" t="n">
         <v>294</v>
       </c>
+      <c r="I52" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J52" s="14" t="n">
+        <v>294</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -16063,6 +16709,12 @@
       <c r="H53" s="14" t="n">
         <v>127</v>
       </c>
+      <c r="I53" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J53" s="14" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -16099,6 +16751,12 @@
       <c r="H54" s="14" t="n">
         <v>4120</v>
       </c>
+      <c r="I54" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J54" s="14" t="n">
+        <v>4120</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -16135,6 +16793,12 @@
       <c r="H55" s="14" t="n">
         <v>56</v>
       </c>
+      <c r="I55" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J55" s="14" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -16171,6 +16835,12 @@
       <c r="H56" s="14" t="n">
         <v>493</v>
       </c>
+      <c r="I56" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J56" s="14" t="n">
+        <v>493</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -16207,6 +16877,12 @@
       <c r="H57" s="14" t="n">
         <v>7853</v>
       </c>
+      <c r="I57" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J57" s="14" t="n">
+        <v>7853</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -16243,6 +16919,12 @@
       <c r="H58" s="14" t="n">
         <v>4018</v>
       </c>
+      <c r="I58" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J58" s="14" t="n">
+        <v>4018</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -16279,6 +16961,12 @@
       <c r="H59" s="14" t="n">
         <v>2876</v>
       </c>
+      <c r="I59" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v>2882</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -16315,6 +17003,12 @@
       <c r="H60" s="14" t="n">
         <v>2251</v>
       </c>
+      <c r="I60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J60" s="14" t="n">
+        <v>2251</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -16351,6 +17045,12 @@
       <c r="H61" s="14" t="n">
         <v>7832</v>
       </c>
+      <c r="I61" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J61" s="14" t="n">
+        <v>7832</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -16387,6 +17087,12 @@
       <c r="H62" s="14" t="n">
         <v>3616</v>
       </c>
+      <c r="I62" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J62" s="14" t="n">
+        <v>3616</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -16423,6 +17129,12 @@
       <c r="H63" s="14" t="n">
         <v>4769</v>
       </c>
+      <c r="I63" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" s="14" t="n">
+        <v>4769</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -16459,6 +17171,12 @@
       <c r="H64" s="14" t="n">
         <v>2626</v>
       </c>
+      <c r="I64" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J64" s="14" t="n">
+        <v>2626</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -16495,6 +17213,12 @@
       <c r="H65" s="14" t="n">
         <v>2903</v>
       </c>
+      <c r="I65" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J65" s="14" t="n">
+        <v>2903</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -16531,6 +17255,12 @@
       <c r="H66" s="14" t="n">
         <v>6446</v>
       </c>
+      <c r="I66" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J66" s="14" t="n">
+        <v>6445</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -16567,6 +17297,12 @@
       <c r="H67" s="14" t="n">
         <v>781</v>
       </c>
+      <c r="I67" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J67" s="14" t="n">
+        <v>781</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -16603,6 +17339,12 @@
       <c r="H68" s="14" t="n">
         <v>19109</v>
       </c>
+      <c r="I68" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J68" s="14" t="n">
+        <v>19109</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -16639,6 +17381,12 @@
       <c r="H69" s="14" t="n">
         <v>2918</v>
       </c>
+      <c r="I69" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J69" s="14" t="n">
+        <v>2919</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -16675,6 +17423,12 @@
       <c r="H70" s="14" t="n">
         <v>2629</v>
       </c>
+      <c r="I70" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J70" s="14" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
@@ -16711,6 +17465,12 @@
       <c r="H71" s="14" t="n">
         <v>1193</v>
       </c>
+      <c r="I71" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J71" s="14" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -16747,6 +17507,12 @@
       <c r="H72" s="14" t="n">
         <v>4165</v>
       </c>
+      <c r="I72" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J72" s="14" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -16783,6 +17549,12 @@
       <c r="H73" s="14" t="n">
         <v>3864</v>
       </c>
+      <c r="I73" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J73" s="14" t="n">
+        <v>3864</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -16819,6 +17591,12 @@
       <c r="H74" s="14" t="n">
         <v>755</v>
       </c>
+      <c r="I74" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J74" s="14" t="n">
+        <v>755</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -16855,6 +17633,12 @@
       <c r="H75" s="14" t="n">
         <v>4658</v>
       </c>
+      <c r="I75" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J75" s="14" t="n">
+        <v>4658</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -16891,6 +17675,12 @@
       <c r="H76" s="14" t="n">
         <v>5288</v>
       </c>
+      <c r="I76" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J76" s="14" t="n">
+        <v>5288</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -16927,6 +17717,12 @@
       <c r="H77" s="14" t="n">
         <v>159</v>
       </c>
+      <c r="I77" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J77" s="14" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -16963,6 +17759,12 @@
       <c r="H78" s="14" t="n">
         <v>1131</v>
       </c>
+      <c r="I78" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J78" s="14" t="n">
+        <v>1131</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -16999,6 +17801,12 @@
       <c r="H79" s="14" t="n">
         <v>634</v>
       </c>
+      <c r="I79" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J79" s="14" t="n">
+        <v>634</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -17035,6 +17843,12 @@
       <c r="H80" s="14" t="n">
         <v>1187</v>
       </c>
+      <c r="I80" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J80" s="14" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -17071,6 +17885,12 @@
       <c r="H81" s="14" t="n">
         <v>1566</v>
       </c>
+      <c r="I81" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J81" s="14" t="n">
+        <v>1566</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -17107,6 +17927,12 @@
       <c r="H82" s="14" t="n">
         <v>11744</v>
       </c>
+      <c r="I82" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J82" s="14" t="n">
+        <v>11744</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -17143,6 +17969,12 @@
       <c r="H83" s="14" t="n">
         <v>15</v>
       </c>
+      <c r="I83" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J83" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
@@ -17179,6 +18011,12 @@
       <c r="H84" s="14" t="n">
         <v>5933</v>
       </c>
+      <c r="I84" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J84" s="14" t="n">
+        <v>5934</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -17215,6 +18053,12 @@
       <c r="H85" s="14" t="n">
         <v>3265</v>
       </c>
+      <c r="I85" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J85" s="14" t="n">
+        <v>3266</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -17251,6 +18095,12 @@
       <c r="H86" s="14" t="n">
         <v>10433</v>
       </c>
+      <c r="I86" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J86" s="14" t="n">
+        <v>10433</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
@@ -17287,6 +18137,12 @@
       <c r="H87" s="14" t="n">
         <v>4152</v>
       </c>
+      <c r="I87" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J87" s="14" t="n">
+        <v>4152</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
@@ -17323,6 +18179,12 @@
       <c r="H88" s="14" t="n">
         <v>2998</v>
       </c>
+      <c r="I88" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J88" s="14" t="n">
+        <v>2998</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
@@ -17359,6 +18221,12 @@
       <c r="H89" s="14" t="n">
         <v>1295</v>
       </c>
+      <c r="I89" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J89" s="14" t="n">
+        <v>1295</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -17395,6 +18263,12 @@
       <c r="H90" s="14" t="n">
         <v>2235</v>
       </c>
+      <c r="I90" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J90" s="14" t="n">
+        <v>2235</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
@@ -17431,6 +18305,12 @@
       <c r="H91" s="14" t="n">
         <v>7974</v>
       </c>
+      <c r="I91" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J91" s="14" t="n">
+        <v>7974</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
@@ -17467,6 +18347,12 @@
       <c r="H92" s="14" t="n">
         <v>783</v>
       </c>
+      <c r="I92" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J92" s="14" t="n">
+        <v>783</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
@@ -17503,6 +18389,12 @@
       <c r="H93" s="14" t="n">
         <v>790</v>
       </c>
+      <c r="I93" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J93" s="14" t="n">
+        <v>790</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
@@ -17539,6 +18431,12 @@
       <c r="H94" s="14" t="n">
         <v>2595</v>
       </c>
+      <c r="I94" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J94" s="14" t="n">
+        <v>2595</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
@@ -17575,6 +18473,12 @@
       <c r="H95" s="14" t="n">
         <v>1678</v>
       </c>
+      <c r="I95" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J95" s="14" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
@@ -17611,6 +18515,12 @@
       <c r="H96" s="14" t="n">
         <v>6440</v>
       </c>
+      <c r="I96" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J96" s="14" t="n">
+        <v>6440</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
@@ -17647,6 +18557,12 @@
       <c r="H97" s="14" t="n">
         <v>2315</v>
       </c>
+      <c r="I97" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J97" s="14" t="n">
+        <v>2315</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -17683,6 +18599,12 @@
       <c r="H98" s="14" t="n">
         <v>1937</v>
       </c>
+      <c r="I98" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J98" s="14" t="n">
+        <v>1937</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
@@ -17719,6 +18641,12 @@
       <c r="H99" s="14" t="n">
         <v>5580</v>
       </c>
+      <c r="I99" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J99" s="14" t="n">
+        <v>5582</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -17755,6 +18683,12 @@
       <c r="H100" s="14" t="n">
         <v>17789</v>
       </c>
+      <c r="I100" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J100" s="14" t="n">
+        <v>17789</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -17791,6 +18725,12 @@
       <c r="H101" s="14" t="n">
         <v>6173</v>
       </c>
+      <c r="I101" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J101" s="14" t="n">
+        <v>6172</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -17827,6 +18767,12 @@
       <c r="H102" s="14" t="n">
         <v>5282</v>
       </c>
+      <c r="I102" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J102" s="14" t="n">
+        <v>5282</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
@@ -17863,6 +18809,12 @@
       <c r="H103" s="14" t="n">
         <v>1176</v>
       </c>
+      <c r="I103" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J103" s="14" t="n">
+        <v>1176</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -17899,6 +18851,12 @@
       <c r="H104" s="14" t="n">
         <v>4077</v>
       </c>
+      <c r="I104" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J104" s="14" t="n">
+        <v>4077</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
@@ -17935,6 +18893,12 @@
       <c r="H105" s="14" t="n">
         <v>1176</v>
       </c>
+      <c r="I105" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J105" s="14" t="n">
+        <v>1176</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
@@ -17971,6 +18935,12 @@
       <c r="H106" s="14" t="n">
         <v>10977</v>
       </c>
+      <c r="I106" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J106" s="14" t="n">
+        <v>10977</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -18007,6 +18977,12 @@
       <c r="H107" s="14" t="n">
         <v>3159</v>
       </c>
+      <c r="I107" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J107" s="14" t="n">
+        <v>3159</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -18043,6 +19019,12 @@
       <c r="H108" s="14" t="n">
         <v>3059</v>
       </c>
+      <c r="I108" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J108" s="14" t="n">
+        <v>3059</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
@@ -18079,6 +19061,12 @@
       <c r="H109" s="14" t="n">
         <v>2622</v>
       </c>
+      <c r="I109" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J109" s="14" t="n">
+        <v>2622</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
@@ -18115,6 +19103,12 @@
       <c r="H110" s="14" t="n">
         <v>1881</v>
       </c>
+      <c r="I110" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J110" s="14" t="n">
+        <v>1881</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
@@ -18151,6 +19145,12 @@
       <c r="H111" s="14" t="n">
         <v>1196</v>
       </c>
+      <c r="I111" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J111" s="14" t="n">
+        <v>1196</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -18187,6 +19187,12 @@
       <c r="H112" s="14" t="n">
         <v>2454</v>
       </c>
+      <c r="I112" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J112" s="14" t="n">
+        <v>2454</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
@@ -18221,6 +19227,12 @@
         <v>4.6</v>
       </c>
       <c r="H113" s="14" t="n">
+        <v>2645</v>
+      </c>
+      <c r="I113" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J113" s="14" t="n">
         <v>2645</v>
       </c>
     </row>
@@ -18235,7 +19247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18258,6 +19270,12 @@
       <c r="H1" s="11" t="n">
         <v>46303</v>
       </c>
+      <c r="I1" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="J1" s="11" t="n">
+        <v>46304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -18296,6 +19314,16 @@
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -18336,6 +19364,12 @@
       <c r="H3" s="14" t="n">
         <v>14378</v>
       </c>
+      <c r="I3" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>14379</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -18372,6 +19406,12 @@
       <c r="H4" s="14" t="n">
         <v>1201</v>
       </c>
+      <c r="I4" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>1202</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -18408,6 +19448,12 @@
       <c r="H5" s="14" t="n">
         <v>15</v>
       </c>
+      <c r="I5" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -18444,6 +19490,12 @@
       <c r="H6" s="14" t="n">
         <v>62</v>
       </c>
+      <c r="I6" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -18480,6 +19532,12 @@
       <c r="H7" s="14" t="n">
         <v>4837</v>
       </c>
+      <c r="I7" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>4837</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -18516,6 +19574,12 @@
       <c r="H8" s="14" t="n">
         <v>2067</v>
       </c>
+      <c r="I8" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>2067</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -18552,6 +19616,12 @@
       <c r="H9" s="14" t="n">
         <v>5780</v>
       </c>
+      <c r="I9" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>5782</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -18588,6 +19658,12 @@
       <c r="H10" s="14" t="n">
         <v>6559</v>
       </c>
+      <c r="I10" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>6559</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -18624,6 +19700,12 @@
       <c r="H11" s="14" t="n">
         <v>10577</v>
       </c>
+      <c r="I11" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>10577</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -18660,6 +19742,12 @@
       <c r="H12" s="14" t="n">
         <v>12236</v>
       </c>
+      <c r="I12" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>12236</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -18696,6 +19784,12 @@
       <c r="H13" s="14" t="n">
         <v>10701</v>
       </c>
+      <c r="I13" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>10701</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -18732,6 +19826,12 @@
       <c r="H14" s="14" t="n">
         <v>6811</v>
       </c>
+      <c r="I14" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>6811</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -18768,6 +19868,12 @@
       <c r="H15" s="14" t="n">
         <v>3606</v>
       </c>
+      <c r="I15" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>3606</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -18804,6 +19910,12 @@
       <c r="H16" s="14" t="n">
         <v>4504</v>
       </c>
+      <c r="I16" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>4504</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -18840,6 +19952,12 @@
       <c r="H17" s="14" t="n">
         <v>878</v>
       </c>
+      <c r="I17" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>878</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -18876,6 +19994,12 @@
       <c r="H18" s="14" t="n">
         <v>19721</v>
       </c>
+      <c r="I18" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>19721</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -18912,6 +20036,12 @@
       <c r="H19" s="14" t="n">
         <v>2022</v>
       </c>
+      <c r="I19" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>2022</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -18948,6 +20078,12 @@
       <c r="H20" s="14" t="n">
         <v>2045</v>
       </c>
+      <c r="I20" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>2048</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -18984,6 +20120,12 @@
       <c r="H21" s="14" t="n">
         <v>8784</v>
       </c>
+      <c r="I21" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>8784</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -19020,6 +20162,12 @@
       <c r="H22" s="14" t="n">
         <v>1119</v>
       </c>
+      <c r="I22" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>1119</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -19056,6 +20204,12 @@
       <c r="H23" s="14" t="n">
         <v>677</v>
       </c>
+      <c r="I23" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>677</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -19090,6 +20244,12 @@
         <v>4</v>
       </c>
       <c r="H24" s="14" t="n">
+        <v>1822</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" s="14" t="n">
         <v>1822</v>
       </c>
     </row>
@@ -19104,7 +20264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -19127,6 +20287,12 @@
       <c r="H1" s="11" t="n">
         <v>46303</v>
       </c>
+      <c r="I1" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="J1" s="11" t="n">
+        <v>46304</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -19165,6 +20331,16 @@
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -19205,6 +20381,12 @@
       <c r="H3" s="14" t="n">
         <v>1595</v>
       </c>
+      <c r="I3" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -19241,6 +20423,12 @@
       <c r="H4" s="14" t="n">
         <v>1041</v>
       </c>
+      <c r="I4" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>1041</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -19277,6 +20465,12 @@
       <c r="H5" s="14" t="n">
         <v>1981</v>
       </c>
+      <c r="I5" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>1981</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -19313,6 +20507,12 @@
       <c r="H6" s="14" t="n">
         <v>1187</v>
       </c>
+      <c r="I6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -19349,6 +20549,8 @@
       <c r="H7" s="14" t="n">
         <v>1412</v>
       </c>
+      <c r="I7" s="14" t="n"/>
+      <c r="J7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -19385,6 +20587,12 @@
       <c r="H8" s="14" t="n">
         <v>24</v>
       </c>
+      <c r="I8" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>1981</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -19421,6 +20629,12 @@
       <c r="H9" s="14" t="n">
         <v>1133</v>
       </c>
+      <c r="I9" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>1133</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -19457,6 +20671,12 @@
       <c r="H10" s="14" t="n">
         <v>722</v>
       </c>
+      <c r="I10" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>722</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -19493,6 +20713,12 @@
       <c r="H11" s="14" t="n">
         <v>25</v>
       </c>
+      <c r="I11" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -19529,6 +20755,12 @@
       <c r="H12" s="14" t="n">
         <v>23</v>
       </c>
+      <c r="I12" s="14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -19565,6 +20797,12 @@
       <c r="H13" s="14" t="n">
         <v>93</v>
       </c>
+      <c r="I13" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -19601,6 +20839,12 @@
       <c r="H14" s="14" t="n">
         <v>73</v>
       </c>
+      <c r="I14" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -19637,6 +20881,12 @@
       <c r="H15" s="14" t="n">
         <v>562</v>
       </c>
+      <c r="I15" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>562</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -19673,6 +20923,12 @@
       <c r="H16" s="14" t="n">
         <v>14</v>
       </c>
+      <c r="I16" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -19709,6 +20965,12 @@
       <c r="H17" s="14" t="n">
         <v>5835</v>
       </c>
+      <c r="I17" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>5835</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -19745,6 +21007,12 @@
       <c r="H18" s="14" t="n">
         <v>1120</v>
       </c>
+      <c r="I18" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>1124</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -19781,6 +21049,12 @@
       <c r="H19" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="I19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -19817,6 +21091,12 @@
       <c r="H20" s="14" t="n">
         <v>2471</v>
       </c>
+      <c r="I20" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>2472</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -19853,6 +21133,12 @@
       <c r="H21" s="14" t="n">
         <v>341</v>
       </c>
+      <c r="I21" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>341</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -19889,6 +21175,12 @@
       <c r="H22" s="14" t="n">
         <v>4357</v>
       </c>
+      <c r="I22" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>4356</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -19925,6 +21217,12 @@
       <c r="H23" s="14" t="n">
         <v>11258</v>
       </c>
+      <c r="I23" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>11258</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -19961,6 +21259,12 @@
       <c r="H24" s="14" t="n">
         <v>13829</v>
       </c>
+      <c r="I24" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>13830</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -19997,6 +21301,8 @@
       <c r="H25" s="14" t="n">
         <v>5024</v>
       </c>
+      <c r="I25" s="14" t="n"/>
+      <c r="J25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -20033,6 +21339,12 @@
       <c r="H26" s="14" t="n">
         <v>8083</v>
       </c>
+      <c r="I26" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>8062</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -20069,6 +21381,12 @@
       <c r="H27" s="14" t="n">
         <v>7816</v>
       </c>
+      <c r="I27" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>7816</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -20105,6 +21423,12 @@
       <c r="H28" s="14" t="n">
         <v>6651</v>
       </c>
+      <c r="I28" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>6651</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -20141,6 +21465,12 @@
       <c r="H29" s="14" t="n">
         <v>1155</v>
       </c>
+      <c r="I29" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>1155</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -20177,6 +21507,12 @@
       <c r="H30" s="14" t="n">
         <v>4943</v>
       </c>
+      <c r="I30" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>8062</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -20213,6 +21549,12 @@
       <c r="H31" s="14" t="n">
         <v>8065</v>
       </c>
+      <c r="I31" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>8062</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -20249,6 +21591,8 @@
       <c r="H32" s="14" t="n">
         <v>8436</v>
       </c>
+      <c r="I32" s="14" t="n"/>
+      <c r="J32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -20285,6 +21629,12 @@
       <c r="H33" s="14" t="n">
         <v>4182</v>
       </c>
+      <c r="I33" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>4182</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -20321,6 +21671,12 @@
       <c r="H34" s="14" t="n">
         <v>22</v>
       </c>
+      <c r="I34" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -20357,6 +21713,12 @@
       <c r="H35" s="14" t="n">
         <v>4429</v>
       </c>
+      <c r="I35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>4429</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -20393,6 +21755,12 @@
       <c r="H36" s="14" t="n">
         <v>5551</v>
       </c>
+      <c r="I36" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>5551</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -20429,6 +21797,12 @@
       <c r="H37" s="14" t="n">
         <v>4185</v>
       </c>
+      <c r="I37" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>4186</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -20465,6 +21839,12 @@
       <c r="H38" s="14" t="n">
         <v>2506</v>
       </c>
+      <c r="I38" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>2506</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -20501,6 +21881,12 @@
       <c r="H39" s="14" t="n">
         <v>6421</v>
       </c>
+      <c r="I39" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J39" s="14" t="n">
+        <v>6421</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -20537,6 +21923,12 @@
       <c r="H40" s="14" t="n">
         <v>2544</v>
       </c>
+      <c r="I40" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>2544</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -20573,6 +21965,12 @@
       <c r="H41" s="14" t="n">
         <v>1059</v>
       </c>
+      <c r="I41" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J41" s="14" t="n">
+        <v>1061</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -20609,6 +22007,12 @@
       <c r="H42" s="14" t="n">
         <v>799</v>
       </c>
+      <c r="I42" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J42" s="14" t="n">
+        <v>798</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -20645,6 +22049,12 @@
       <c r="H43" s="14" t="n">
         <v>547</v>
       </c>
+      <c r="I43" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J43" s="14" t="n">
+        <v>547</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -20681,6 +22091,12 @@
       <c r="H44" s="14" t="n">
         <v>19</v>
       </c>
+      <c r="I44" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J44" s="14" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -20717,6 +22133,12 @@
       <c r="H45" s="14" t="n">
         <v>5063</v>
       </c>
+      <c r="I45" s="14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J45" s="14" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -20753,6 +22175,12 @@
       <c r="H46" s="14" t="n">
         <v>647</v>
       </c>
+      <c r="I46" s="14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J46" s="14" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -20789,6 +22217,12 @@
       <c r="H47" s="14" t="n">
         <v>2581</v>
       </c>
+      <c r="I47" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J47" s="14" t="n">
+        <v>2578</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -20825,6 +22259,12 @@
       <c r="H48" s="14" t="n">
         <v>81</v>
       </c>
+      <c r="I48" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J48" s="14" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -20861,6 +22301,12 @@
       <c r="H49" s="14" t="n">
         <v>4615</v>
       </c>
+      <c r="I49" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J49" s="14" t="n">
+        <v>4615</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -20897,6 +22343,12 @@
       <c r="H50" s="14" t="n">
         <v>3299</v>
       </c>
+      <c r="I50" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J50" s="14" t="n">
+        <v>3298</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -20933,6 +22385,12 @@
       <c r="H51" s="14" t="n">
         <v>783</v>
       </c>
+      <c r="I51" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J51" s="14" t="n">
+        <v>783</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -20969,6 +22427,12 @@
       <c r="H52" s="14" t="n">
         <v>1497</v>
       </c>
+      <c r="I52" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J52" s="14" t="n">
+        <v>1497</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -21005,6 +22469,12 @@
       <c r="H53" s="14" t="n">
         <v>92</v>
       </c>
+      <c r="I53" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J53" s="14" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -21041,6 +22511,12 @@
       <c r="H54" s="14" t="n">
         <v>2811</v>
       </c>
+      <c r="I54" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J54" s="14" t="n">
+        <v>2811</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -21077,6 +22553,12 @@
       <c r="H55" s="14" t="n">
         <v>706</v>
       </c>
+      <c r="I55" s="14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J55" s="14" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -21113,6 +22595,12 @@
       <c r="H56" s="14" t="n">
         <v>289</v>
       </c>
+      <c r="I56" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J56" s="14" t="n">
+        <v>289</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -21149,6 +22637,12 @@
       <c r="H57" s="14" t="n">
         <v>4513</v>
       </c>
+      <c r="I57" s="14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J57" s="14" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -21185,6 +22679,12 @@
       <c r="H58" s="14" t="n">
         <v>456</v>
       </c>
+      <c r="I58" s="14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J58" s="14" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -21221,6 +22721,12 @@
       <c r="H59" s="14" t="n">
         <v>3006</v>
       </c>
+      <c r="I59" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v>3006</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -21257,6 +22763,12 @@
       <c r="H60" s="14" t="n">
         <v>971</v>
       </c>
+      <c r="I60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J60" s="14" t="n">
+        <v>970</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -21292,6 +22804,12 @@
       </c>
       <c r="H61" s="14" t="n">
         <v>1074</v>
+      </c>
+      <c r="I61" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J61" s="14" t="n">
+        <v>1075</v>
       </c>
     </row>
   </sheetData>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Bikanervala GGN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Competitors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="India BV" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="International BV" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Haldiram India" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="OM Sweets India" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Other Outlets" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bikanervala GGN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="India BV" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="International BV" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haldiram India" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OM Sweets India" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Other Outlets" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,14 +52,8 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -88,12 +82,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -152,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,9 +178,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -561,7 +546,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -578,10 +563,10 @@
         </is>
       </c>
       <c r="G1" s="11" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H1" s="11" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="2">
@@ -659,7 +644,7 @@
         <v>4.4</v>
       </c>
       <c r="H3" s="14" t="n">
-        <v>4870</v>
+        <v>4872</v>
       </c>
     </row>
     <row r="4">
@@ -727,12 +712,6 @@
           <t>https://share.google/Lq1yf4rveBX5BWyts</t>
         </is>
       </c>
-      <c r="G5" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>5545</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -763,12 +742,6 @@
           <t>https://share.google/5iiO04ZTn35j8E5HB</t>
         </is>
       </c>
-      <c r="G6" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H6" s="14" t="n">
-        <v>6545</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -799,12 +772,6 @@
           <t>https://share.google/iNagaqHoCbBOIvV0x</t>
         </is>
       </c>
-      <c r="G7" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>2415</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -835,12 +802,6 @@
           <t>https://share.google/S4Kwkg9xEW0S2j7a0</t>
         </is>
       </c>
-      <c r="G8" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>7188</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -871,12 +832,6 @@
           <t>https://share.google/NS8T7gwZSlKSNr3UP</t>
         </is>
       </c>
-      <c r="G9" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>3662</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -907,12 +862,6 @@
           <t>https://share.google/Xmyef4OwQmXyWCFN0</t>
         </is>
       </c>
-      <c r="G10" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>2772</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -943,12 +892,6 @@
           <t>https://share.google/6khAtgqK72w0kjN0Q</t>
         </is>
       </c>
-      <c r="G11" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>1115</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -979,12 +922,6 @@
           <t>https://share.google/CgukSORsdWkszVRvP</t>
         </is>
       </c>
-      <c r="G12" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H12" s="14" t="n">
-        <v>1107</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -1015,12 +952,6 @@
           <t>https://share.google/BNfINmH1QbNZhf7ox</t>
         </is>
       </c>
-      <c r="G13" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>2241</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -1051,12 +982,6 @@
           <t>https://share.google/LJxUW77APw08Vr9a0</t>
         </is>
       </c>
-      <c r="G14" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H14" s="14" t="n">
-        <v>2377</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1087,12 +1012,6 @@
           <t>https://share.google/LAZMqwdryXVTeQkgt</t>
         </is>
       </c>
-      <c r="G15" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H15" s="14" t="n">
-        <v>2593</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1123,12 +1042,6 @@
           <t>https://share.google/lkP8lqhdoKZRzyal3</t>
         </is>
       </c>
-      <c r="G16" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>894</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -1159,12 +1072,6 @@
           <t>https://share.google/255ZPlPOiTGMhDzy0</t>
         </is>
       </c>
-      <c r="G17" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>1332</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -1195,12 +1102,6 @@
           <t>https://share.google/9TqthrgcK6VnEH9Kh</t>
         </is>
       </c>
-      <c r="G18" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H18" s="14" t="n">
-        <v>455</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -1231,12 +1132,6 @@
           <t>https://share.google/uqXvcL4esuwjgcsRz</t>
         </is>
       </c>
-      <c r="G19" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>915</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -1267,12 +1162,6 @@
           <t>https://share.google/E5KGOYYKX6YqD07hf</t>
         </is>
       </c>
-      <c r="G20" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H20" s="14" t="n">
-        <v>1098</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -1303,12 +1192,6 @@
           <t>https://share.google/ooNGpI4Ewi9Zt5t02</t>
         </is>
       </c>
-      <c r="G21" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <v>787</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -1339,12 +1222,6 @@
           <t>https://share.google/Z2RQtKISxQhQWQSl4</t>
         </is>
       </c>
-      <c r="G22" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H22" s="14" t="n">
-        <v>659</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -1375,12 +1252,6 @@
           <t>https://share.google/grSJuehxs8v7sVOVt</t>
         </is>
       </c>
-      <c r="G23" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H23" s="14" t="n">
-        <v>694</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -1411,12 +1282,6 @@
           <t>https://share.google/V1f6JY6CBgPW0eoIg</t>
         </is>
       </c>
-      <c r="G24" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H24" s="14" t="n">
-        <v>1424</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -1447,12 +1312,6 @@
           <t>https://share.google/r13AfGhfeAFwXti2i</t>
         </is>
       </c>
-      <c r="G25" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H25" s="14" t="n">
-        <v>706</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1478,12 +1337,6 @@
         <is>
           <t>https://share.google/e0rEvKWJDcji81RKF</t>
         </is>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H26" s="14" t="n">
-        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -1498,7 +1351,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -1516,10 +1369,10 @@
         </is>
       </c>
       <c r="H1" s="11" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="I1" s="11" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="2">
@@ -1607,7 +1460,7 @@
         <v>4.8</v>
       </c>
       <c r="I3" s="14" t="n">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="4">
@@ -1685,12 +1538,6 @@
           <t>Pair 2</t>
         </is>
       </c>
-      <c r="H5" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>787</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1726,12 +1573,6 @@
           <t>#4</t>
         </is>
       </c>
-      <c r="H6" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>3864</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1767,12 +1608,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H7" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>659</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1808,12 +1643,6 @@
           <t>Pair 3</t>
         </is>
       </c>
-      <c r="H8" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>894</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1849,12 +1678,6 @@
           <t>#7</t>
         </is>
       </c>
-      <c r="H9" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>3266</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1890,12 +1713,6 @@
           <t>#8</t>
         </is>
       </c>
-      <c r="H10" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>19721</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1931,12 +1748,6 @@
           <t>Pair 2</t>
         </is>
       </c>
-      <c r="H11" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>1424</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1972,12 +1783,6 @@
           <t>#10</t>
         </is>
       </c>
-      <c r="H12" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>1193</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -2013,12 +1818,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H13" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>755</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -2054,12 +1853,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H14" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>6811</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -2095,12 +1888,6 @@
           <t>Pair 3</t>
         </is>
       </c>
-      <c r="H15" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>7188</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -2136,12 +1923,6 @@
           <t>#14</t>
         </is>
       </c>
-      <c r="H16" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>535</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -2177,12 +1958,6 @@
           <t>#15</t>
         </is>
       </c>
-      <c r="H17" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>1822</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -2218,12 +1993,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H18" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>4504</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -2259,12 +2028,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H19" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>6545</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -2300,12 +2063,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H20" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>2772</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -2341,12 +2098,6 @@
           <t>Pair 2</t>
         </is>
       </c>
-      <c r="H21" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>15765</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2382,12 +2133,6 @@
           <t>#20</t>
         </is>
       </c>
-      <c r="H22" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>5934</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -2423,12 +2168,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H23" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>10577</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -2464,12 +2203,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H24" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <v>12236</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -2505,12 +2238,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H25" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>19109</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -2546,12 +2273,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H26" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>28</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -2587,12 +2308,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H27" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>3662</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -2628,12 +2343,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H28" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>3606</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -2669,12 +2378,6 @@
           <t>Pair 2</t>
         </is>
       </c>
-      <c r="H29" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>4870</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -2710,12 +2413,6 @@
           <t>#28</t>
         </is>
       </c>
-      <c r="H30" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I30" s="14" t="n">
-        <v>1160</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -2751,12 +2448,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H31" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>2241</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -2792,12 +2483,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H32" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I32" s="14" t="n">
-        <v>1043</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -2833,12 +2518,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H33" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>5545</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -2874,12 +2553,6 @@
           <t>Pair 2</t>
         </is>
       </c>
-      <c r="H34" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <v>1131</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -2915,12 +2588,6 @@
           <t>#33</t>
         </is>
       </c>
-      <c r="H35" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I35" s="14" t="n">
-        <v>4837</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -2956,12 +2623,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H36" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I36" s="14" t="n">
-        <v>1107</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -2997,12 +2658,6 @@
           <t>Pair 2</t>
         </is>
       </c>
-      <c r="H37" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>2415</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -3038,12 +2693,6 @@
           <t>#36</t>
         </is>
       </c>
-      <c r="H38" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I38" s="14" t="n">
-        <v>281</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -3079,12 +2728,6 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H39" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I39" s="14" t="n">
-        <v>2593</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -3112,19 +2755,13 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Bikanervala+Sector+62+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Bikanervala+Sector+62+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H40" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <v>455</v>
       </c>
     </row>
     <row r="41">
@@ -3153,19 +2790,13 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Bikanervala+CyberPark+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Bikanervala+CyberPark+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H41" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I41" s="14" t="n">
-        <v>1115</v>
       </c>
     </row>
     <row r="42">
@@ -3194,19 +2825,13 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Haldiram%27s+Sahara+Mall+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://share.google/Jlgj9CSmiwGBJzq7p</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H42" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I42" s="14" t="n">
-        <v>11744</v>
       </c>
     </row>
     <row r="43">
@@ -3235,19 +2860,13 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Bikanervala+JMD+Empire+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://share.google/E5KGOYYKX6YqD07hf</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H43" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I43" s="14" t="n">
-        <v>1098</v>
       </c>
     </row>
     <row r="44">
@@ -3276,19 +2895,13 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Bikanervala+Esplanade+Mall+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://share.google/255ZPlPOiTGMhDzy0</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
           <t>Pair 2</t>
         </is>
-      </c>
-      <c r="H44" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I44" s="14" t="n">
-        <v>1332</v>
       </c>
     </row>
     <row r="45">
@@ -3307,7 +2920,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Sector37  ,Gurgaon</t>
+          <t>Sector 37, Gurgaon</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -3317,19 +2930,13 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Om+Sweets+Sector37+++Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Om+Sweets+Sector37+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
           <t>#43</t>
         </is>
-      </c>
-      <c r="H45" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I45" s="14" t="n">
-        <v>192</v>
       </c>
     </row>
     <row r="46">
@@ -3358,19 +2965,13 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Haldiram%27s+Elan+Miracle+Mall+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://share.google/aioloSd77eFIRO9Ok</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H46" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I46" s="14" t="n">
-        <v>2007</v>
       </c>
     </row>
     <row r="47">
@@ -3389,7 +2990,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Elan Marcado,Gurgaon</t>
+          <t>Elan Mercado, Gurgaon</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -3399,19 +3000,13 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Bikanervala+Elan+Marcado+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://share.google/LJxUW77APw08Vr9a0</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H47" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I47" s="14" t="n">
-        <v>2377</v>
       </c>
     </row>
     <row r="48">
@@ -3430,7 +3025,7 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Sec 68,Gurgaon</t>
+          <t>Sector 68, Gurgaon</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -3440,19 +3035,13 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Bikanervala+Sec+68+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://share.google/uqXvcL4esuwjgcsRz</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
           <t>Pair 2</t>
         </is>
-      </c>
-      <c r="H48" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I48" s="14" t="n">
-        <v>915</v>
       </c>
     </row>
     <row r="49">
@@ -3481,19 +3070,13 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Haldiram%27s+Sector+68+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Haldiram%27s+Sector+68+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
           <t>#47</t>
         </is>
-      </c>
-      <c r="H49" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I49" s="14" t="n">
-        <v>1774</v>
       </c>
     </row>
     <row r="50">
@@ -3522,19 +3105,13 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Haldiram%27s+Vatika+City++Gurgaon+Gurgaon?hl=en</t>
+          <t>https://share.google/F88ypuX3UQ9U5lOzq</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H50" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I50" s="14" t="n">
-        <v>2629</v>
       </c>
     </row>
     <row r="51">
@@ -3563,19 +3140,13 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Haldiram%27s+Sector25+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Haldiram%27s+Sector25+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H51" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I51" s="14" t="n">
-        <v>5934</v>
       </c>
     </row>
     <row r="52">
@@ -3594,7 +3165,7 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Matropolitan Mall Gurgaon</t>
+          <t>Metropolitan Mall Gurgaon</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -3604,19 +3175,13 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Haldiram%27s+Matropolitan+Mall+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Haldiram%27s+Matropolitan+Mall+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H52" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I52" s="14" t="n">
-        <v>1566</v>
       </c>
     </row>
     <row r="53">
@@ -3645,19 +3210,13 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Haldiram%27s+Sector+2+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://share.google/tcFJSMcls3CixV91Q</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H53" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I53" s="14" t="n">
-        <v>5934</v>
       </c>
     </row>
     <row r="54">
@@ -3686,19 +3245,13 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Haldiram%27s+Element+One+Mall+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Haldiram%27s+Element+One+Mall+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H54" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I54" s="14" t="n">
-        <v>5288</v>
       </c>
     </row>
     <row r="55">
@@ -3717,7 +3270,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Ambeince Mall Gurgaon</t>
+          <t>Ambience Mall Gurgaon</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
@@ -3727,19 +3280,13 @@
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Bikanervala+Ambeince+Mall+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Bikanervala+Ambeince+Mall+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
           <t>Pair 2</t>
         </is>
-      </c>
-      <c r="H55" s="14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I55" s="14" t="n">
-        <v>170</v>
       </c>
     </row>
     <row r="56">
@@ -3758,7 +3305,7 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Ambeince Mall Gurgaon</t>
+          <t>Ambience Mall Gurgaon</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -3768,19 +3315,13 @@
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Haldiram%27s+Ambeince+Mall+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Haldiram%27s+Ambeince+Mall+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
           <t>#54</t>
         </is>
-      </c>
-      <c r="H56" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I56" s="14" t="n">
-        <v>4165</v>
       </c>
     </row>
     <row r="57">
@@ -3809,19 +3350,13 @@
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Haldiram%27s+Satya+Mall+Gurgaon?hl=en</t>
+          <t>https://share.google/1gvPrfJFsxGqq8Rva</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H57" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I57" s="14" t="n">
-        <v>1846</v>
       </c>
     </row>
     <row r="58">
@@ -3850,19 +3385,13 @@
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Haldiram%27s+Sector+1+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Haldiram%27s+Sector+1+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H58" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I58" s="14" t="n">
-        <v>4658</v>
       </c>
     </row>
     <row r="59">
@@ -3881,7 +3410,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Sector3,Gurgaon</t>
+          <t>Sector 5, Gurgaon</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
@@ -3891,19 +3420,13 @@
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Om+Sweets+Sector3+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Om+Sweets+Sector3+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H59" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I59" s="14" t="n">
-        <v>5781</v>
       </c>
     </row>
     <row r="60">
@@ -3932,19 +3455,13 @@
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Om+Sweets+Sector10++Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Om+Sweets+Sector10+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H60" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I60" s="14" t="n">
-        <v>6559</v>
       </c>
     </row>
     <row r="61">
@@ -3973,19 +3490,13 @@
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Om+Sweets+Sector4++Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Om+Sweets+Sector4+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H61" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I61" s="14" t="n">
-        <v>10701</v>
       </c>
     </row>
     <row r="62">
@@ -4014,19 +3525,13 @@
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Om+Sweets+Circular+RD+New+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Om+Sweets+Circular+RD+New+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H62" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I62" s="14" t="n">
-        <v>2067</v>
       </c>
     </row>
     <row r="63">
@@ -4055,19 +3560,13 @@
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Om+Sweets+Sector7++Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Om+Sweets+Sector7+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H63" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I63" s="14" t="n">
-        <v>878</v>
       </c>
     </row>
     <row r="64">
@@ -4096,19 +3595,13 @@
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Om+Sweets+Sector8++Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Om+Sweets+Sector8+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H64" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I64" s="14" t="n">
-        <v>1202</v>
       </c>
     </row>
     <row r="65">
@@ -4137,19 +3630,13 @@
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Om+Sweets+Sheetla+Colony+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Om+Sweets+Sheetla+Colony+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H65" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I65" s="14" t="n">
-        <v>19721</v>
       </c>
     </row>
     <row r="66">
@@ -4178,19 +3665,13 @@
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Om+Sweets+Garhi+Harsaru+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Om+Sweets+Garhi+Harsaru+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H66" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I66" s="14" t="n">
-        <v>73</v>
       </c>
     </row>
     <row r="67">
@@ -4219,19 +3700,13 @@
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/Om+Sweets+Dale+Corner+Sohna+Gurgaon+Gurgaon?hl=en</t>
+          <t>https://www.google.com/maps/search/Om+Sweets+Dale+Corner+Sohna+Gurgaon?hl=en</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H67" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I67" s="14" t="n">
-        <v>886</v>
       </c>
     </row>
     <row r="68">
@@ -4267,12 +3742,6 @@
         <is>
           <t>Pair 1</t>
         </is>
-      </c>
-      <c r="H68" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I68" s="14" t="n">
-        <v>14379</v>
       </c>
     </row>
   </sheetData>
@@ -4287,7 +3756,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I206"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -4304,10 +3773,10 @@
         </is>
       </c>
       <c r="H1" s="11" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="I1" s="11" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
@@ -4395,7 +3864,7 @@
         <v>4.3</v>
       </c>
       <c r="I3" s="14" t="n">
-        <v>2117</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -4433,10 +3902,10 @@
         </is>
       </c>
       <c r="H4" s="14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I4" s="14" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -4473,12 +3942,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Liberty+Cinema+Karol+Bagh/@28.6606284,77.1876003,17z/data=!3m1!4b1!4m6!3m5!1s0x390d03326d19a899:0xd2fef34572239279!8m2!3d28.6606284!4d77.1876003!16s%2Fg%2F11m5qhcscj?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H5" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>1555</v>
-      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="7" t="n">
@@ -4514,12 +3977,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Kalkaji+Metro/@28.5494507,77.259104,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce361d13dfecb:0x11d594dba2638f6d!8m2!3d28.5494507!4d77.259104!16s%2Fg%2F11x72l6mq2?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H6" s="14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>138</v>
-      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="n">
@@ -4555,12 +4012,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Lajpat+Nagar+Delhi/@28.5708816,77.2390955,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce252e00cf3fb:0xf48521c45d7cd156!8m2!3d28.5708816!4d77.2390955!16s%2Fg%2F1td_wzrz?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H7" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>10889</v>
-      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="7" t="n">
@@ -4596,12 +4047,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Defence+Colony+Delhi/@28.5748765,77.2381202,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce3d5f019e1e9:0xa3e490839a38e681!8m2!3d28.5748765!4d77.2381202!16s%2Fg%2F11qb4tsxc0?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H8" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>2941</v>
-      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="7" t="n">
@@ -4637,12 +4082,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+East+of+Kailash+Delhi/@28.5587762,77.246459,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce39ca675e7c3:0xbe857ad66d22f2bf!8m2!3d28.5587762!4d77.246459!16s%2Fg%2F11s1qvx_74?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H9" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>218</v>
-      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="7" t="n">
@@ -4678,12 +4117,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Preet+Vihar+Delhi/@28.6392518,77.2948339,17z/data=!3m1!4b1!4m6!3m5!1s0x390cfb510ec67a93:0xfad0c088f3f91804!8m2!3d28.6392518!4d77.2948339!16s%2Fg%2F1tgnkg53?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H10" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>5139</v>
-      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="7" t="n">
@@ -4719,12 +4152,6 @@
           <t>https://www.google.com/maps/search/BV+Connaught+Place+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H11" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>52621</v>
-      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="7" t="n">
@@ -4760,12 +4187,6 @@
           <t>https://www.google.com/maps/search/BV+RRM+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H12" s="14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>340</v>
-      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="7" t="n">
@@ -4801,12 +4222,6 @@
           <t>https://www.google.com/maps/search/BV+Mayur+Vihar+Phase+1+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H13" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>2493</v>
-      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="7" t="n">
@@ -4842,12 +4257,6 @@
           <t>https://www.google.com/maps/search/BV+Chandni+Chowk+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H14" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>108</v>
-      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="n">
@@ -4883,12 +4292,6 @@
           <t>https://www.google.com/maps/search/BV+Okhla+Industrial+Area+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H15" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="7" t="n">
@@ -4924,12 +4327,6 @@
           <t>https://www.google.com/maps/search/BV+GTK+Road+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H16" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>449</v>
-      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="n">
@@ -4965,12 +4362,6 @@
           <t>https://www.google.com/maps/search/BV+Punjabi+Bagh+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H17" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>2653</v>
-      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="7" t="n">
@@ -5006,12 +4397,6 @@
           <t>https://www.google.com/maps/search/BV+Kamla+Nagar+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H18" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>1623</v>
-      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="7" t="n">
@@ -5047,12 +4432,6 @@
           <t>https://www.google.com/maps/search/BV+Rohini+West+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H19" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>607</v>
-      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="7" t="n">
@@ -5088,12 +4467,6 @@
           <t>https://www.google.com/maps/search/BV+Kirti+Nagar+Industrial+Area+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H20" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>102</v>
-      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="7" t="n">
@@ -5129,12 +4502,6 @@
           <t>https://www.google.com/maps/search/BV+Dilshad+Garden+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H21" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="7" t="n">
@@ -5170,12 +4537,6 @@
           <t>https://www.google.com/maps/search/BV+Malviya+Nagar+Extension+Saket?hl=en</t>
         </is>
       </c>
-      <c r="H22" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>6280</v>
-      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="7" t="n">
@@ -5211,12 +4572,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Dwarka+Delhi/@28.5966087,77.0417524,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1b72556cb43b:0xdd37fb0751d2b900!8m2!3d28.5966087!4d77.0417524!16s%2Fg%2F11grt4vw5b?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H23" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>6218</v>
-      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="7" t="n">
@@ -5252,12 +4607,6 @@
           <t>https://www.google.com/maps/search/BV+Rani+Bagh+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H24" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <v>13126</v>
-      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="7" t="n">
@@ -5293,12 +4642,6 @@
           <t>https://www.google.com/maps/search/BV+Janakpuri+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H25" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>2355</v>
-      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="7" t="n">
@@ -5334,12 +4677,6 @@
           <t>https://www.google.com/maps/search/BV+Jyoti+Nagar+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H26" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>1909</v>
-      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="7" t="n">
@@ -5375,12 +4712,6 @@
           <t>https://www.google.com/maps/search/BV+Raja+Garden+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H27" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>13</v>
-      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="7" t="n">
@@ -5416,12 +4747,6 @@
           <t>https://www.google.com/maps/search/BV+Nehru+Place+Metro+Station+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H28" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>10035</v>
-      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="7" t="n">
@@ -5457,12 +4782,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Chanakyapuri+Delhi/@28.585244,77.19149,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1d7cdedc3389:0x60798b43139c76d3!8m2!3d28.585244!4d77.19149!16s%2Fg%2F1tdvhkdv?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H29" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>8673</v>
-      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="n">
@@ -5498,12 +4817,6 @@
           <t>https://www.google.com/maps/search/BV+Aerocity+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="H30" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I30" s="14" t="n">
-        <v>22258</v>
-      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="7" t="n">
@@ -5539,12 +4852,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+GK-II+Savitri+Cinema+Delhi/@28.5374253,77.2389712,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce22b17e2d781:0x40c5f102209b866c!8m2!3d28.5374253!4d77.2389712!16s%2Fg%2F11cmr0t9q8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H31" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>5576</v>
-      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="7" t="n">
@@ -5575,12 +4882,6 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+109+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="H32" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I32" s="14" t="n">
-        <v>11</v>
-      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="7" t="n">
@@ -5611,12 +4912,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+57+Gurugram/@28.4161819,77.0849591,17z/data=!3m1!4b1!4m6!3m5!1s0x390d232798684757:0xb380904dacac7eed!8m2!3d28.4161819!4d77.0849591!16s%2Fg%2F11k522rkjz?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H33" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>4870</v>
-      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="7" t="n">
@@ -5647,12 +4942,6 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+14+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="H34" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <v>894</v>
-      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="7" t="n">
@@ -5683,12 +4972,6 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+99+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="H35" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I35" s="14" t="n">
-        <v>18</v>
-      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="7" t="n">
@@ -5719,12 +5002,6 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+24+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="H36" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I36" s="14" t="n">
-        <v>68</v>
-      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="7" t="n">
@@ -5755,12 +5032,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+The+Esplanade+Mall+Sector+37+Gurugram/@28.4538074,76.9928507,17z/data=!3m1!4b1!4m6!3m5!1s0x390d171587c41467:0x4070a84c531d04ce!8m2!3d28.4538074!4d76.9928507!16s%2Fg%2F11tggmn3j8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H37" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>1332</v>
-      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="7" t="n">
@@ -5791,12 +5062,6 @@
           <t>https://www.google.com/maps/search/BV+Cyber+Park+Udhyog+Vihar+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="H38" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I38" s="14" t="n">
-        <v>2688</v>
-      </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="7" t="n">
@@ -5827,12 +5092,6 @@
           <t>https://www.google.com/maps/search/BV+Foodcourt+Opulent+Mall+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="H39" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I39" s="14" t="n">
-        <v>23004</v>
-      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="7" t="n">
@@ -5863,12 +5122,6 @@
           <t>https://www.google.com/maps/search/BV+JMD+Empire+Square+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="H40" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <v>571</v>
-      </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="7" t="n">
@@ -5899,12 +5152,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+62+Gurugram/@28.4014616,77.0852188,17z/data=!3m1!4b1!4m6!3m5!1s0x390d23dcf278418d:0x4d1e11be0af4d661!8m2!3d28.4014616!4d77.0852188!16s%2Fg%2F11h7qrpfv4?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H41" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I41" s="14" t="n">
-        <v>455</v>
-      </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="7" t="n">
@@ -5935,12 +5182,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+15+Gurugram/@28.4578375,77.0443773,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1902973194b5:0x7d02f6d383fb8a58!8m2!3d28.4578375!4d77.0443773!16s%2Fg%2F11trqkrhym?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H42" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I42" s="14" t="n">
-        <v>2415</v>
-      </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="7" t="n">
@@ -5971,12 +5212,6 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+95+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="H43" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I43" s="14" t="n">
-        <v>143</v>
-      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="7" t="n">
@@ -6007,12 +5242,6 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+54+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="H44" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I44" s="14" t="n">
-        <v>6545</v>
-      </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="7" t="n">
@@ -6043,12 +5272,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+67+Gurugram/@28.3897015,77.0674498,17z/data=!3m1!4b1!4m6!3m5!1s0x390d23d7d3976715:0xb8dc58e2f64d1b2e!8m2!3d28.3897015!4d77.0674498!16s%2Fg%2F11h7ksct1w?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H45" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I45" s="14" t="n">
-        <v>1107</v>
-      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="7" t="n">
@@ -6079,12 +5302,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sohna+Road+Gurugram/@28.4253629,77.0390099,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1875d4418c91:0x3b4b144484bee44a!8m2!3d28.4253629!4d77.0390099!16s%2Fg%2F1wj_4f0r?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H46" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I46" s="14" t="n">
-        <v>7188</v>
-      </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="7" t="n">
@@ -6115,12 +5332,6 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+29+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="H47" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I47" s="14" t="n">
-        <v>3809</v>
-      </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="7" t="n">
@@ -6151,12 +5362,6 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+86+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="H48" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I48" s="14" t="n">
-        <v>3662</v>
-      </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="7" t="n">
@@ -6187,12 +5392,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+80+Gurugram/@28.3766192,76.9593435,17z/data=!3m1!4b1!4m6!3m5!1s0x390d3da30c57ee59:0x82d80073b91470fc!8m2!3d28.3766192!4d76.9593435!16s%2Fg%2F11fhh4ykm5?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H49" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I49" s="14" t="n">
-        <v>2377</v>
-      </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="7" t="n">
@@ -6223,12 +5422,6 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+62+Noida?hl=en</t>
         </is>
       </c>
-      <c r="H50" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I50" s="14" t="n">
-        <v>5593</v>
-      </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="7" t="n">
@@ -6259,12 +5452,6 @@
           <t>https://www.google.com/maps/search/BV+Omaxe+NRI+Greater+Noida?hl=en</t>
         </is>
       </c>
-      <c r="H51" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I51" s="14" t="n">
-        <v>1007</v>
-      </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="7" t="n">
@@ -6295,12 +5482,6 @@
           <t>https://www.google.com/maps/search/BV+Knowledge+Park+3+Greater+Noida?hl=en</t>
         </is>
       </c>
-      <c r="H52" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I52" s="14" t="n">
-        <v>28</v>
-      </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="7" t="n">
@@ -6331,12 +5512,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+18+Noida/@28.5715738,77.3246799,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce44edd59cf9b:0x7abd947a6a0578bf!8m2!3d28.5715738!4d77.3246799!16s%2Fg%2F124sxkwj8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H53" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I53" s="14" t="n">
-        <v>9648</v>
-      </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="7" t="n">
@@ -6367,12 +5542,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Gaur+City+Mall+Greater+Noida?hl=en</t>
         </is>
       </c>
-      <c r="H54" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I54" s="14" t="n">
-        <v>796</v>
-      </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="7" t="n">
@@ -6403,12 +5572,6 @@
           <t>https://www.google.com/maps/search/BV+Krishna+Apsara+Plaza+Noida?hl=en</t>
         </is>
       </c>
-      <c r="H55" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I55" s="14" t="n">
-        <v>298</v>
-      </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="7" t="n">
@@ -6439,12 +5602,6 @@
           <t>https://www.google.com/maps/search/BV+URBTCH+Sec+-+153+Noida?hl=en</t>
         </is>
       </c>
-      <c r="H56" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I56" s="14" t="n">
-        <v>51</v>
-      </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="7" t="n">
@@ -6475,12 +5632,6 @@
           <t>https://share.google/ROkTSrwbJf84BzhPA</t>
         </is>
       </c>
-      <c r="H57" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I57" s="14" t="n">
-        <v>437</v>
-      </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="7" t="n">
@@ -6511,12 +5662,6 @@
           <t>https://share.google/zdFAyEbaRbQ5k484p</t>
         </is>
       </c>
-      <c r="H58" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I58" s="14" t="n">
-        <v>203</v>
-      </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="7" t="n">
@@ -6547,12 +5692,6 @@
           <t>https://share.google/Lb3nqjJMTsd4B288R</t>
         </is>
       </c>
-      <c r="H59" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I59" s="14" t="n">
-        <v>658</v>
-      </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="7" t="n">
@@ -6583,12 +5722,6 @@
           <t>https://share.google/UhwDLEldKfKeeOvuF</t>
         </is>
       </c>
-      <c r="H60" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I60" s="14" t="n">
-        <v>361</v>
-      </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="7" t="n">
@@ -6619,12 +5752,6 @@
           <t>https://share.google/y3qxY9okUtRY9qT5G</t>
         </is>
       </c>
-      <c r="H61" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I61" s="14" t="n">
-        <v>2914</v>
-      </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="7" t="n">
@@ -6655,12 +5782,6 @@
           <t>https://share.google/6IsINvdHSLIIHkIhQ</t>
         </is>
       </c>
-      <c r="H62" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I62" s="14" t="n">
-        <v>585</v>
-      </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="7" t="n">
@@ -6691,12 +5812,6 @@
           <t>https://share.google/dyEWjeSFB5bMuBtCr</t>
         </is>
       </c>
-      <c r="H63" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I63" s="14" t="n">
-        <v>9258</v>
-      </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="7" t="n">
@@ -6727,12 +5842,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Gaur+Biz+Park+Gaziabad?hl=en</t>
         </is>
       </c>
-      <c r="H64" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I64" s="14" t="n">
-        <v>1007</v>
-      </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="7" t="n">
@@ -6763,12 +5872,6 @@
           <t>https://www.google.com/maps/place/Plot+No.+12,+Bikanervala+%7C+Rajendra+Nagar,+Sahibabad,,+Rajender+Nagar,+Sector+5,+Rajendra+Nagar,+Sahibabad,+Ghaziabad,+Uttar+Pradesh+201005/@28.6780951,77.3592434,16z/data=!4m6!3m5!1s0x390cfa8b972e5a11:0x42944ce5f6223fbd!8m2!3d28.6780951!4d77.3592434!16s%2Fg%2F11b6gg2nvh?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
-      <c r="H65" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I65" s="14" t="n">
-        <v>3845</v>
-      </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="7" t="n">
@@ -6799,12 +5902,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Choudhary+More+Ghaziabad/@28.656764,77.4343384,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf1cfc180871d:0x5aa84735b213aa6a!8m2!3d28.656764!4d77.4343384!16s%2Fg%2F11clr_s4v9?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H66" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I66" s="14" t="n">
-        <v>4138</v>
-      </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="7" t="n">
@@ -6835,12 +5932,6 @@
           <t>https://www.google.com/maps/search/BV+Indirapuram+Gaziabad?hl=en</t>
         </is>
       </c>
-      <c r="H67" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I67" s="14" t="n">
-        <v>26858</v>
-      </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="7" t="n">
@@ -6871,12 +5962,6 @@
           <t>https://www.google.com/maps/search/BV+Raj+Nagar+Extension+Gaziabad?hl=en</t>
         </is>
       </c>
-      <c r="H68" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I68" s="14" t="n">
-        <v>4301</v>
-      </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="7" t="n">
@@ -6907,12 +5992,6 @@
           <t>https://www.google.com/maps/search/BV+Vasundhara+Gaziabad?hl=en</t>
         </is>
       </c>
-      <c r="H69" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I69" s="14" t="n">
-        <v>2214</v>
-      </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="7" t="n">
@@ -6943,12 +6022,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+KW+Delhi+6/@28.696452,77.4352816,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf15e12b7409f:0x21ba0dd8e12c1453!8m2!3d28.696452!4d77.4352816!16s%2Fg%2F11jzgk44vp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H70" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I70" s="14" t="n">
-        <v>280</v>
-      </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="7" t="n">
@@ -6979,12 +6052,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Modinagar/@28.8133765,77.5519765,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf5b71abce455:0xfc2ef5a0bb38f92!8m2!3d28.8133765!4d77.5519765!16s%2Fg%2F11ghftj4c1?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H71" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I71" s="14" t="n">
-        <v>6142</v>
-      </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="7" t="n">
@@ -7015,12 +6082,6 @@
           <t>https://www.google.com/maps/search/BV+Lal+Kuan+Gaziabad?hl=en</t>
         </is>
       </c>
-      <c r="H72" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I72" s="14" t="n">
-        <v>47</v>
-      </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="7" t="n">
@@ -7051,12 +6112,6 @@
           <t>https://maps.app.goo.gl/KegUZzVNtBCzn3zC9</t>
         </is>
       </c>
-      <c r="H73" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I73" s="14" t="n">
-        <v>1109</v>
-      </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="7" t="n">
@@ -7087,12 +6142,6 @@
           <t>https://goo.gl/maps/uzteMjzzkSa3PjHcA</t>
         </is>
       </c>
-      <c r="H74" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I74" s="14" t="n">
-        <v>9514</v>
-      </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="7" t="n">
@@ -7123,12 +6172,6 @@
           <t>https://goo.gl/maps/o8aMcy4bzjEiMSc88</t>
         </is>
       </c>
-      <c r="H75" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I75" s="14" t="n">
-        <v>16970</v>
-      </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="7" t="n">
@@ -7159,12 +6202,6 @@
           <t>https://goo.gl/maps/LeLGBiAqApZipLR2A</t>
         </is>
       </c>
-      <c r="H76" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I76" s="14" t="n">
-        <v>8560</v>
-      </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="7" t="n">
@@ -7195,12 +6232,6 @@
           <t>https://www.google.com/maps/place/Bikanervala/@26.7851067,80.9918353,17z/data=!3m1!4b1!4m6!3m5!1s0x399be30647fd426d:0xd01584f16db3efe3!8m2!3d26.7851067!4d80.9918353!16s%2Fg%2F11jsr96pd9?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H77" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I77" s="14" t="n">
-        <v>2468</v>
-      </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="7" t="n">
@@ -7231,12 +6262,6 @@
           <t>https://www.google.com/maps/search/BV+Fun+Republik+Lucknow?hl=en</t>
         </is>
       </c>
-      <c r="H78" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I78" s="14" t="n">
-        <v>111</v>
-      </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="7" t="n">
@@ -7267,12 +6292,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Emerald+Mall+Lucknow/@26.7879677,80.9106156,17z/data=!3m1!4b1!4m6!3m5!1s0x399bfda33d9b4ed1:0x4bc0f33320d7156b!8m2!3d26.7879677!4d80.9106156!16s%2Fg%2F11vs2f1qpf?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="H79" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I79" s="14" t="n">
-        <v>175</v>
-      </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="7" t="n">
@@ -7303,12 +6322,6 @@
           <t>https://www.google.com/maps/search/BV+Vijay+Tower+Lucknow?hl=en</t>
         </is>
       </c>
-      <c r="H80" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I80" s="14" t="n">
-        <v>148</v>
-      </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="7" t="n">
@@ -7339,16 +6352,6 @@
           <t>https://www.google.com/maps/search/BV+Indira+Nagar+Lucknow+%28Closed%29?hl=en</t>
         </is>
       </c>
-      <c r="H81" s="15" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I81" s="15" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="7" t="n">
@@ -7379,12 +6382,6 @@
           <t>https://www.google.com/maps/search/BV+Vibhuti+Khand+Gomti+Nagar+Lucknow?hl=en</t>
         </is>
       </c>
-      <c r="H82" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I82" s="14" t="n">
-        <v>1438</v>
-      </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="7" t="n">
@@ -7415,12 +6412,6 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+12+Faridabad?hl=en</t>
         </is>
       </c>
-      <c r="H83" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I83" s="14" t="n">
-        <v>1740</v>
-      </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="7" t="n">
@@ -7451,12 +6442,6 @@
           <t>https://www.google.com/maps/search/BV+Mansha+Vega+Street+Faridabad?hl=en</t>
         </is>
       </c>
-      <c r="H84" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I84" s="14" t="n">
-        <v>43</v>
-      </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="7" t="n">
@@ -7487,12 +6472,6 @@
           <t>https://www.google.com/maps/search/BV+Mandi+Dabwali+Road+Bhatinda?hl=en</t>
         </is>
       </c>
-      <c r="H85" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I85" s="14" t="n">
-        <v>3950</v>
-      </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="7" t="n">
@@ -7523,12 +6502,6 @@
           <t>https://www.google.com/maps/search/BV+Park+Penorama+Colony+Bhatinda?hl=en</t>
         </is>
       </c>
-      <c r="H86" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I86" s="14" t="n">
-        <v>45</v>
-      </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="7" t="n">
@@ -7559,12 +6532,6 @@
           <t>https://www.google.com/maps/search/BV+Nungabakkam+Chennai?hl=en</t>
         </is>
       </c>
-      <c r="H87" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I87" s="14" t="n">
-        <v>4503</v>
-      </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="7" t="n">
@@ -7595,12 +6562,6 @@
           <t>https://www.google.com/maps/search/BV+Chennai+Kilpauk?hl=en</t>
         </is>
       </c>
-      <c r="H88" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I88" s="14" t="n">
-        <v>23</v>
-      </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="7" t="n">
@@ -7631,12 +6592,6 @@
           <t>https://www.google.com/maps/search/BV+Modipuram+Meerut?hl=en</t>
         </is>
       </c>
-      <c r="H89" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I89" s="14" t="n">
-        <v>834</v>
-      </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="7" t="n">
@@ -7667,12 +6622,6 @@
           <t>https://www.google.com/maps/search/BV+Harsh+Commercial+Park+Meerut?hl=en</t>
         </is>
       </c>
-      <c r="H90" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I90" s="14" t="n">
-        <v>14</v>
-      </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="7" t="n">
@@ -7703,12 +6652,6 @@
           <t>https://www.google.com/maps/search/BV+Kundli+Sonipat?hl=en</t>
         </is>
       </c>
-      <c r="H91" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I91" s="14" t="n">
-        <v>859</v>
-      </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="7" t="n">
@@ -7739,12 +6682,6 @@
           <t>https://www.google.com/maps/search/BV+Bhelupura+Varanasi?hl=en</t>
         </is>
       </c>
-      <c r="H92" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I92" s="14" t="n">
-        <v>387</v>
-      </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="7" t="n">
@@ -7775,12 +6712,6 @@
           <t>https://www.google.com/maps/search/BV+Global+Business+Park+Zirakpur?hl=en</t>
         </is>
       </c>
-      <c r="H93" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I93" s="14" t="n">
-        <v>160</v>
-      </c>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="7" t="n">
@@ -7811,12 +6742,6 @@
           <t>https://www.google.com/maps/search/BV+Pakhowal+Road+Ludhiana?hl=en</t>
         </is>
       </c>
-      <c r="H94" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I94" s="14" t="n">
-        <v>1624</v>
-      </c>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="7" t="n">
@@ -7847,12 +6772,6 @@
           <t>https://www.google.com/maps/search/BV+Tonk+Road+Jaipur?hl=en</t>
         </is>
       </c>
-      <c r="H95" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I95" s="14" t="n">
-        <v>7498</v>
-      </c>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="7" t="n">
@@ -7883,12 +6802,6 @@
           <t>https://www.google.com/maps/search/BV+Model+Town+Jalandhar?hl=en</t>
         </is>
       </c>
-      <c r="H96" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I96" s="14" t="n">
-        <v>2835</v>
-      </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="7" t="n">
@@ -7919,12 +6832,6 @@
           <t>https://www.google.com/maps/search/BV+C+Plaza+Mohali?hl=en</t>
         </is>
       </c>
-      <c r="H97" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I97" s="14" t="n">
-        <v>43968</v>
-      </c>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="7" t="n">
@@ -7955,12 +6862,6 @@
           <t>https://www.google.com/maps/search/BV+Pacific+Mall+Rajpur+Road+Dehradun?hl=en</t>
         </is>
       </c>
-      <c r="H98" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I98" s="14" t="n">
-        <v>42232</v>
-      </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="7" t="n">
@@ -7991,12 +6892,6 @@
           <t>https://www.google.com/maps/search/BV+Lashkar+Gwalier?hl=en</t>
         </is>
       </c>
-      <c r="H99" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I99" s="14" t="n">
-        <v>44060</v>
-      </c>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="7" t="n">
@@ -8027,12 +6922,6 @@
           <t>https://www.google.com/maps/search/BV+Avenue+37+Bahadurgarh?hl=en</t>
         </is>
       </c>
-      <c r="H100" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I100" s="14" t="n">
-        <v>344</v>
-      </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="7" t="n">
@@ -8063,12 +6952,6 @@
           <t>https://www.google.com/maps/search/BV+Tehsil+Deoband+Saharanpur?hl=en</t>
         </is>
       </c>
-      <c r="H101" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I101" s="14" t="n">
-        <v>23</v>
-      </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="7" t="n">
@@ -8099,12 +6982,6 @@
           <t>https://www.google.com/maps/search/BV+Barara+Ambala?hl=en</t>
         </is>
       </c>
-      <c r="H102" s="14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I102" s="14" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="7" t="n">
@@ -8135,12 +7012,6 @@
           <t>https://www.google.com/maps/search/BV+Hanuman+Garh+Road+Sri+GnagaNagar?hl=en</t>
         </is>
       </c>
-      <c r="H103" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I103" s="14" t="n">
-        <v>857</v>
-      </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="7" t="n">
@@ -8171,12 +7042,6 @@
           <t>https://www.google.com/maps/search/BV+Nabha+Gate+Road+Sangrur?hl=en</t>
         </is>
       </c>
-      <c r="H104" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I104" s="14" t="n">
-        <v>428</v>
-      </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="7" t="n">
@@ -8207,12 +7072,6 @@
           <t>https://www.google.com/maps/search/BV+Jayanagar+Bengaluru?hl=en</t>
         </is>
       </c>
-      <c r="H105" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="I105" s="14" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="7" t="n">
@@ -8243,12 +7102,6 @@
           <t>https://www.google.com/maps/search/BV+Village+Quatabpur+Hisar?hl=en</t>
         </is>
       </c>
-      <c r="H106" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I106" s="14" t="n">
-        <v>40</v>
-      </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="7" t="n">
@@ -8279,12 +7132,6 @@
           <t>https://www.google.com/maps/search/BV+Akhnoor+Jammu?hl=en</t>
         </is>
       </c>
-      <c r="H107" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I107" s="14" t="n">
-        <v>444</v>
-      </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="7" t="n">
@@ -8315,12 +7162,6 @@
           <t>https://www.google.com/maps/search/BV+Model+Town+Rohtak?hl=en</t>
         </is>
       </c>
-      <c r="H108" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I108" s="14" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="7" t="n">
@@ -8351,12 +7192,6 @@
           <t>https://www.google.com/maps/search/BV+NH+27+Abu+Road+Rajasthan?hl=en</t>
         </is>
       </c>
-      <c r="H109" s="14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I109" s="14" t="n">
-        <v>64</v>
-      </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="7" t="n">
@@ -8387,12 +7222,6 @@
           <t>https://goo.gl/maps/X2g2z7mRg9ZU92F2A</t>
         </is>
       </c>
-      <c r="H110" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I110" s="14" t="n">
-        <v>100</v>
-      </c>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="7" t="n">
@@ -8423,12 +7252,6 @@
           <t>https://maps.app.goo.gl/37R2ESFo5oS8p2em7</t>
         </is>
       </c>
-      <c r="H111" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I111" s="14" t="n">
-        <v>866</v>
-      </c>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="7" t="n">
@@ -8464,12 +7287,6 @@
           <t>https://goo.gl/maps/iMtbXqwaWUDYu8xf6</t>
         </is>
       </c>
-      <c r="H112" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I112" s="14" t="n">
-        <v>8390</v>
-      </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="7" t="n">
@@ -8505,12 +7322,6 @@
           <t>https://goo.gl/maps/CxUCASbc6Zf2TocB8</t>
         </is>
       </c>
-      <c r="H113" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I113" s="14" t="n">
-        <v>4894</v>
-      </c>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="7" t="n">
@@ -8546,12 +7357,6 @@
           <t>https://goo.gl/maps/ATskvznck1gui7f6A</t>
         </is>
       </c>
-      <c r="H114" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I114" s="14" t="n">
-        <v>3365</v>
-      </c>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="7" t="n">
@@ -8587,12 +7392,6 @@
           <t>https://goo.gl/maps/KbVjkRcx6jMVdGQW7</t>
         </is>
       </c>
-      <c r="H115" s="14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I115" s="14" t="n">
-        <v>170</v>
-      </c>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="7" t="n">
@@ -8628,12 +7427,6 @@
           <t>https://goo.gl/maps/AmjQDTZCHpP9PfrB6</t>
         </is>
       </c>
-      <c r="H116" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I116" s="14" t="n">
-        <v>8673</v>
-      </c>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="7" t="n">
@@ -8669,12 +7462,6 @@
           <t>https://maps.app.goo.gl/zcrubnk5RZ3jKg5A8</t>
         </is>
       </c>
-      <c r="H117" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I117" s="14" t="n">
-        <v>11855</v>
-      </c>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="7" t="n">
@@ -8710,12 +7497,6 @@
           <t>https://goo.gl/maps/dqHX14AbaKcSsV5i7</t>
         </is>
       </c>
-      <c r="H118" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I118" s="14" t="n">
-        <v>2772</v>
-      </c>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="7" t="n">
@@ -8751,12 +7532,6 @@
           <t>https://maps.app.goo.gl/NbSW2GgWBiTTWokQ6</t>
         </is>
       </c>
-      <c r="H119" s="14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I119" s="14" t="n">
-        <v>89</v>
-      </c>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="7" t="n">
@@ -8792,12 +7567,6 @@
           <t>https://maps.app.goo.gl/x8i3gr7m9LKKvijw9</t>
         </is>
       </c>
-      <c r="H120" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I120" s="14" t="n">
-        <v>464</v>
-      </c>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="7" t="n">
@@ -8833,12 +7602,6 @@
           <t>https://maps.app.goo.gl/pNH5r5yxdP3DTRfj9</t>
         </is>
       </c>
-      <c r="H121" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I121" s="14" t="n">
-        <v>776</v>
-      </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="7" t="n">
@@ -8874,12 +7637,6 @@
           <t>https://maps.app.goo.gl/Lt1LVynLWcuu8eXy5</t>
         </is>
       </c>
-      <c r="H122" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I122" s="14" t="n">
-        <v>169</v>
-      </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="7" t="n">
@@ -8915,12 +7672,6 @@
           <t>https://maps.app.goo.gl/G7HFA2zCPT3Co2BU9</t>
         </is>
       </c>
-      <c r="H123" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I123" s="14" t="n">
-        <v>13</v>
-      </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="7" t="n">
@@ -8956,12 +7707,6 @@
           <t>https://maps.app.goo.gl/9LmyBZrg48UVmmmM7</t>
         </is>
       </c>
-      <c r="H124" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I124" s="14" t="n">
-        <v>41</v>
-      </c>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="7" t="n">
@@ -8997,12 +7742,6 @@
           <t>https://maps.app.goo.gl/mnuCcmi4TeeNHkNv7</t>
         </is>
       </c>
-      <c r="H125" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I125" s="14" t="n">
-        <v>48</v>
-      </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="7" t="n">
@@ -9038,12 +7777,6 @@
           <t>https://maps.app.goo.gl/hWXz3RWjo8iBq8vC6</t>
         </is>
       </c>
-      <c r="H126" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I126" s="14" t="n">
-        <v>11</v>
-      </c>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="7" t="n">
@@ -9079,12 +7812,6 @@
           <t>https://goo.gl/maps/EXwmxHqPpSwBfAn9A</t>
         </is>
       </c>
-      <c r="H127" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I127" s="14" t="n">
-        <v>4191</v>
-      </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="7" t="n">
@@ -9120,12 +7847,6 @@
           <t>https://maps.app.goo.gl/Qr7ipPaWf38VtzRZA</t>
         </is>
       </c>
-      <c r="H128" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I128" s="14" t="n">
-        <v>288</v>
-      </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="7" t="n">
@@ -9156,12 +7877,6 @@
           <t>https://goo.gl/maps/xV9F7hCGssGURhmZ9</t>
         </is>
       </c>
-      <c r="H129" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I129" s="14" t="n">
-        <v>4227</v>
-      </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="7" t="n">
@@ -9192,12 +7907,6 @@
           <t>https://maps.app.goo.gl/je2V2Z8h1Pu8a2Vz8</t>
         </is>
       </c>
-      <c r="H130" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I130" s="14" t="n">
-        <v>659</v>
-      </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="7" t="n">
@@ -9228,12 +7937,6 @@
           <t>https://maps.app.goo.gl/12vCQuxEBD9PWE8F8</t>
         </is>
       </c>
-      <c r="H131" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I131" s="14" t="n">
-        <v>787</v>
-      </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="7" t="n">
@@ -9264,12 +7967,6 @@
           <t>https://maps.app.goo.gl/ucnkKCkPLq9GUTEL8</t>
         </is>
       </c>
-      <c r="H132" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I132" s="14" t="n">
-        <v>706</v>
-      </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="7" t="n">
@@ -9300,12 +7997,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Elan+Epic+Sec-70+Gurguram+Gurugram?hl=en</t>
         </is>
       </c>
-      <c r="H133" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I133" s="14" t="n">
-        <v>1424</v>
-      </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="7" t="n">
@@ -9336,12 +8027,6 @@
           <t>https://maps.app.goo.gl/CWNkDPq7wK3DihFMA</t>
         </is>
       </c>
-      <c r="H134" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I134" s="14" t="n">
-        <v>694</v>
-      </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="7" t="n">
@@ -9372,12 +8057,6 @@
           <t>https://maps.app.goo.gl/uYECDKn6odyrrTA96</t>
         </is>
       </c>
-      <c r="H135" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I135" s="14" t="n">
-        <v>372</v>
-      </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="7" t="n">
@@ -9408,12 +8087,6 @@
           <t>https://maps.app.goo.gl/uYECDKn6odyrrTA96</t>
         </is>
       </c>
-      <c r="H136" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I136" s="14" t="n">
-        <v>372</v>
-      </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="7" t="n">
@@ -9444,12 +8117,6 @@
           <t>https://goo.gl/maps/KTGuqx8wJFbQL3V48</t>
         </is>
       </c>
-      <c r="H137" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I137" s="14" t="n">
-        <v>5273</v>
-      </c>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="7" t="n">
@@ -9480,12 +8147,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Prahalad+Nagar%2C+Ahmedabad%2C+Gujarat+380051+Ahmedabad?hl=en</t>
         </is>
       </c>
-      <c r="H138" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I138" s="14" t="n">
-        <v>2545</v>
-      </c>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="7" t="n">
@@ -9516,12 +8177,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Nehru+Nagar%2C+Ahmedabad%2C+Gujarat+380015+Ahmedabad?hl=en</t>
         </is>
       </c>
-      <c r="H139" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I139" s="14" t="n">
-        <v>3196</v>
-      </c>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="7" t="n">
@@ -9552,12 +8207,6 @@
           <t>https://goo.gl/maps/32mqLYxSNUxQfjDy5</t>
         </is>
       </c>
-      <c r="H140" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I140" s="14" t="n">
-        <v>1438</v>
-      </c>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="7" t="n">
@@ -9588,12 +8237,6 @@
           <t>https://maps.app.goo.gl/723xYbZvfAGXSj5g7</t>
         </is>
       </c>
-      <c r="H141" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I141" s="14" t="n">
-        <v>175</v>
-      </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="7" t="n">
@@ -9624,12 +8267,6 @@
           <t>https://maps.app.goo.gl/3WvgLWd5QSehGjEH6</t>
         </is>
       </c>
-      <c r="H142" s="14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I142" s="14" t="n">
-        <v>19</v>
-      </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="7" t="n">
@@ -9660,12 +8297,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Fatehabad+Rd%2C+opposite+Hotel+ITC+Mughal%2C+Tajganj%2C+Agra%2C+Uttar+Pradesh+282001+Agra?hl=en</t>
         </is>
       </c>
-      <c r="H143" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I143" s="14" t="n">
-        <v>4191</v>
-      </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="7" t="n">
@@ -9696,12 +8327,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Near+tulsi+cinema%2C+Kripal+colony%2C+Sanjay+nagar%2C+pashupati+colony%2C+khandari%2C+Agra%2C+Agra?hl=en</t>
         </is>
       </c>
-      <c r="H144" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I144" s="14" t="n">
-        <v>4586</v>
-      </c>
     </row>
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="7" t="n">
@@ -9732,12 +8357,6 @@
           <t>https://goo.gl/maps/uYKxT37zNmYp3MU78</t>
         </is>
       </c>
-      <c r="H145" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I145" s="14" t="n">
-        <v>1530</v>
-      </c>
     </row>
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="7" t="n">
@@ -9768,12 +8387,6 @@
           <t>https://maps.app.goo.gl/q1cas4PoB2wq7y218</t>
         </is>
       </c>
-      <c r="H146" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I146" s="14" t="n">
-        <v>3950</v>
-      </c>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="7" t="n">
@@ -9804,12 +8417,6 @@
           <t>https://maps.app.goo.gl/9korfoaVEuCnsttx9</t>
         </is>
       </c>
-      <c r="H147" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I147" s="14" t="n">
-        <v>2953</v>
-      </c>
     </row>
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="7" t="n">
@@ -9840,12 +8447,6 @@
           <t>https://maps.app.goo.gl/wyFeTmbGR45kCHRJ8</t>
         </is>
       </c>
-      <c r="H148" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I148" s="14" t="n">
-        <v>62</v>
-      </c>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="7" t="n">
@@ -9876,12 +8477,6 @@
           <t>https://maps.app.goo.gl/NuHBsab6Z71CqfnJ7</t>
         </is>
       </c>
-      <c r="H149" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I149" s="14" t="n">
-        <v>80</v>
-      </c>
     </row>
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="7" t="n">
@@ -9912,12 +8507,6 @@
           <t>https://maps.app.goo.gl/szumsxsq2FSh8P7h7</t>
         </is>
       </c>
-      <c r="H150" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I150" s="14" t="n">
-        <v>2595</v>
-      </c>
     </row>
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="7" t="n">
@@ -9948,12 +8537,6 @@
           <t>https://goo.gl/maps/B4CK1TxcuJf2gwGV8</t>
         </is>
       </c>
-      <c r="H151" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I151" s="14" t="n">
-        <v>3845</v>
-      </c>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="7" t="n">
@@ -9984,12 +8567,6 @@
           <t>https://goo.gl/maps/4pJwnbEcxGBVBWZi6</t>
         </is>
       </c>
-      <c r="H152" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I152" s="14" t="n">
-        <v>510</v>
-      </c>
     </row>
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="7" t="n">
@@ -10020,12 +8597,6 @@
           <t>https://goo.gl/maps/gYRQUULU5t9wi18S8</t>
         </is>
       </c>
-      <c r="H153" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I153" s="14" t="n">
-        <v>9258</v>
-      </c>
     </row>
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="7" t="n">
@@ -10056,12 +8627,6 @@
           <t>https://goo.gl/maps/arsjABkMQUNEYFgF6</t>
         </is>
       </c>
-      <c r="H154" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I154" s="14" t="n">
-        <v>9244</v>
-      </c>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="7" t="n">
@@ -10092,12 +8657,6 @@
           <t>https://goo.gl/maps/N7a66uNDkDcDgctb6</t>
         </is>
       </c>
-      <c r="H155" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I155" s="14" t="n">
-        <v>4301</v>
-      </c>
     </row>
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="7" t="n">
@@ -10128,12 +8687,6 @@
           <t>https://maps.app.goo.gl/LkRXmhWrNkmb4bfQ9</t>
         </is>
       </c>
-      <c r="H156" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I156" s="14" t="n">
-        <v>198</v>
-      </c>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="7" t="n">
@@ -10164,12 +8717,6 @@
           <t>https://maps.app.goo.gl/fdpmtgiFnnmBpBhZ6</t>
         </is>
       </c>
-      <c r="H157" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I157" s="14" t="n">
-        <v>585</v>
-      </c>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="7" t="n">
@@ -10200,12 +8747,6 @@
           <t>https://maps.app.goo.gl/LJVSZyoMxAU6wMvDA</t>
         </is>
       </c>
-      <c r="H158" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I158" s="14" t="n">
-        <v>81</v>
-      </c>
     </row>
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="7" t="n">
@@ -10236,12 +8777,6 @@
           <t>https://maps.app.goo.gl/AjzLtZx8muxVP8NEA</t>
         </is>
       </c>
-      <c r="H159" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I159" s="14" t="n">
-        <v>37</v>
-      </c>
     </row>
     <row r="160" ht="20" customHeight="1">
       <c r="A160" s="7" t="n">
@@ -10272,12 +8807,6 @@
           <t>https://maps.app.goo.gl/6HL3Gohkz7u4cYQa7</t>
         </is>
       </c>
-      <c r="H160" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I160" s="14" t="n">
-        <v>95</v>
-      </c>
     </row>
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="7" t="n">
@@ -10308,12 +8837,6 @@
           <t>https://maps.app.goo.gl/oWmDoNJLbdvENyak7</t>
         </is>
       </c>
-      <c r="H161" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I161" s="14" t="n">
-        <v>133</v>
-      </c>
     </row>
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="7" t="n">
@@ -10344,12 +8867,6 @@
           <t>https://maps.app.goo.gl/FHgqWFsLmanWmdpD7</t>
         </is>
       </c>
-      <c r="H162" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I162" s="14" t="n">
-        <v>1938</v>
-      </c>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="7" t="n">
@@ -10380,12 +8897,6 @@
           <t>https://maps.app.goo.gl/xJrmieBbKX6bUuSV7</t>
         </is>
       </c>
-      <c r="H163" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I163" s="14" t="n">
-        <v>1698</v>
-      </c>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="7" t="n">
@@ -10416,12 +8927,6 @@
           <t>https://goo.gl/maps/aNahaC7CwDFV5kyi9</t>
         </is>
       </c>
-      <c r="H164" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I164" s="14" t="n">
-        <v>9349</v>
-      </c>
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="7" t="n">
@@ -10452,12 +8957,6 @@
           <t>https://maps.app.goo.gl/jWbbnvbERR8sWwr67</t>
         </is>
       </c>
-      <c r="H165" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I165" s="14" t="n">
-        <v>1091</v>
-      </c>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="7" t="n">
@@ -10488,12 +8987,6 @@
           <t>https://goo.gl/maps/fHakJ7u4WEXt3Ck36</t>
         </is>
       </c>
-      <c r="H166" s="14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I166" s="14" t="n">
-        <v>175</v>
-      </c>
     </row>
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="7" t="n">
@@ -10524,12 +9017,6 @@
           <t>https://goo.gl/maps/apShSYj546Yn2Sb77</t>
         </is>
       </c>
-      <c r="H167" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I167" s="14" t="n">
-        <v>3360</v>
-      </c>
     </row>
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="7" t="n">
@@ -10560,12 +9047,6 @@
           <t>https://maps.app.goo.gl/V9dCfncbjgbxiVmu8</t>
         </is>
       </c>
-      <c r="H168" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I168" s="14" t="n">
-        <v>849</v>
-      </c>
     </row>
     <row r="169" ht="20" customHeight="1">
       <c r="A169" s="7" t="n">
@@ -10596,12 +9077,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+BX-143%2C+Royal+Plaza%2C+Plot+No.+224%2C+Model+House+Rd%2C+Tej+Mohan+Nagar%2C+Basti+Sheikh%2C+Dashmesh+Nagar%2C+Jalandhar%2C+Punjab+144002+Jalandhar?hl=en</t>
         </is>
       </c>
-      <c r="H169" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I169" s="14" t="n">
-        <v>110</v>
-      </c>
     </row>
     <row r="170" ht="20" customHeight="1">
       <c r="A170" s="7" t="n">
@@ -10632,12 +9107,6 @@
           <t>https://maps.app.goo.gl/HLAivSgrHkcp4qnaA</t>
         </is>
       </c>
-      <c r="H170" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I170" s="14" t="n">
-        <v>142</v>
-      </c>
     </row>
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="7" t="n">
@@ -10668,12 +9137,6 @@
           <t>https://maps.app.goo.gl/Vz5yNZTUumTKdLSd8</t>
         </is>
       </c>
-      <c r="H171" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I171" s="14" t="n">
-        <v>220</v>
-      </c>
     </row>
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="7" t="n">
@@ -10704,12 +9167,6 @@
           <t>https://maps.app.goo.gl/zYmsiM2GuUKTfVeD6</t>
         </is>
       </c>
-      <c r="H172" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I172" s="14" t="n">
-        <v>190</v>
-      </c>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="7" t="n">
@@ -10740,12 +9197,6 @@
           <t>https://maps.app.goo.gl/LBtyvdAnk8e5m1578</t>
         </is>
       </c>
-      <c r="H173" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I173" s="14" t="n">
-        <v>407</v>
-      </c>
     </row>
     <row r="174" ht="20" customHeight="1">
       <c r="A174" s="7" t="n">
@@ -10776,12 +9227,6 @@
           <t>https://maps.app.goo.gl/UStZQsyjFuie2zcQA</t>
         </is>
       </c>
-      <c r="H174" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I174" s="14" t="n">
-        <v>71</v>
-      </c>
     </row>
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="7" t="n">
@@ -10812,12 +9257,6 @@
           <t>https://maps.app.goo.gl/u7fUEMutEveKTJfaA</t>
         </is>
       </c>
-      <c r="H175" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I175" s="14" t="n">
-        <v>78</v>
-      </c>
     </row>
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="7" t="n">
@@ -10848,12 +9287,6 @@
           <t>https://goo.gl/maps/Y1coLwehTfUaHJgQ9</t>
         </is>
       </c>
-      <c r="H176" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I176" s="14" t="n">
-        <v>2052</v>
-      </c>
     </row>
     <row r="177" ht="20" customHeight="1">
       <c r="A177" s="7" t="n">
@@ -10884,12 +9317,6 @@
           <t>https://maps.app.goo.gl/nCMGxjXNMPSkpduXA</t>
         </is>
       </c>
-      <c r="H177" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I177" s="14" t="n">
-        <v>566</v>
-      </c>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="7" t="n">
@@ -10920,12 +9347,6 @@
           <t>https://goo.gl/maps/Yd2kU1mEc8tyWvnJ8</t>
         </is>
       </c>
-      <c r="H178" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I178" s="14" t="n">
-        <v>4077</v>
-      </c>
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="7" t="n">
@@ -10956,12 +9377,6 @@
           <t>https://goo.gl/maps/b1DPwmk5pLaEaMkAA</t>
         </is>
       </c>
-      <c r="H179" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I179" s="14" t="n">
-        <v>3197</v>
-      </c>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="7" t="n">
@@ -10992,12 +9407,6 @@
           <t>https://maps.app.goo.gl/9shVkw5NVcCaEc2f7</t>
         </is>
       </c>
-      <c r="H180" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I180" s="14" t="n">
-        <v>494</v>
-      </c>
     </row>
     <row r="181" ht="20" customHeight="1">
       <c r="A181" s="7" t="n">
@@ -11028,12 +9437,6 @@
           <t>https://maps.app.goo.gl/KD7iMcgQd1KqrwuX6</t>
         </is>
       </c>
-      <c r="H181" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I181" s="14" t="n">
-        <v>180</v>
-      </c>
     </row>
     <row r="182" ht="20" customHeight="1">
       <c r="A182" s="7" t="n">
@@ -11064,12 +9467,6 @@
           <t>https://goo.gl/maps/Yd2kU1mEc8tyWvnJ8</t>
         </is>
       </c>
-      <c r="H182" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I182" s="14" t="n">
-        <v>4077</v>
-      </c>
     </row>
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="7" t="n">
@@ -11100,12 +9497,6 @@
           <t>https://maps.app.goo.gl/ZCFFUjrMcfzQt27h8</t>
         </is>
       </c>
-      <c r="H183" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I183" s="14" t="n">
-        <v>219</v>
-      </c>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="7" t="n">
@@ -11136,12 +9527,6 @@
           <t>https://goo.gl/maps/wyjWtNYLyFV8wGLo6</t>
         </is>
       </c>
-      <c r="H184" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I184" s="14" t="n">
-        <v>372</v>
-      </c>
     </row>
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="7" t="n">
@@ -11172,12 +9557,6 @@
           <t>https://maps.app.goo.gl/Mdwf9WhXGqgWpP1s8</t>
         </is>
       </c>
-      <c r="H185" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I185" s="14" t="n">
-        <v>728</v>
-      </c>
     </row>
     <row r="186" ht="20" customHeight="1">
       <c r="A186" s="7" t="n">
@@ -11208,12 +9587,6 @@
           <t>https://goo.gl/maps/qYiG7AWurb3kpPT57</t>
         </is>
       </c>
-      <c r="H186" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I186" s="14" t="n">
-        <v>434</v>
-      </c>
     </row>
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="7" t="n">
@@ -11244,12 +9617,6 @@
           <t>https://maps.app.goo.gl/8CvxLW27EUBgXm287</t>
         </is>
       </c>
-      <c r="H187" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I187" s="14" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="188" ht="20" customHeight="1">
       <c r="A188" s="7" t="n">
@@ -11280,12 +9647,6 @@
           <t>https://maps.app.goo.gl/XA4qoyenHaBCULJR9</t>
         </is>
       </c>
-      <c r="H188" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I188" s="14" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="7" t="n">
@@ -11316,12 +9677,6 @@
           <t>https://maps.app.goo.gl/jF1fPUaWD5TR8wZn6</t>
         </is>
       </c>
-      <c r="H189" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I189" s="14" t="n">
-        <v>196</v>
-      </c>
     </row>
     <row r="190" ht="20" customHeight="1">
       <c r="A190" s="7" t="n">
@@ -11352,12 +9707,6 @@
           <t>https://maps.app.goo.gl/6pZshenjLsstWLWy5</t>
         </is>
       </c>
-      <c r="H190" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I190" s="14" t="n">
-        <v>67</v>
-      </c>
     </row>
     <row r="191" ht="20" customHeight="1">
       <c r="A191" s="7" t="n">
@@ -11388,12 +9737,6 @@
           <t>https://goo.gl/maps/YwNxSsrKnhA3Fzae8</t>
         </is>
       </c>
-      <c r="H191" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I191" s="14" t="n">
-        <v>7436</v>
-      </c>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="7" t="n">
@@ -11424,12 +9767,6 @@
           <t>https://maps.app.goo.gl/W21VqyaGAhgWLW1Z7</t>
         </is>
       </c>
-      <c r="H192" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I192" s="14" t="n">
-        <v>2940</v>
-      </c>
     </row>
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="7" t="n">
@@ -11460,12 +9797,6 @@
           <t>https://maps.app.goo.gl/SofrRQ31CC1sKfiq9</t>
         </is>
       </c>
-      <c r="H193" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I193" s="14" t="n">
-        <v>488</v>
-      </c>
     </row>
     <row r="194" ht="20" customHeight="1">
       <c r="A194" s="7" t="n">
@@ -11496,12 +9827,6 @@
           <t>https://maps.app.goo.gl/UnxqTGRsvK65sSta7</t>
         </is>
       </c>
-      <c r="H194" s="14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I194" s="14" t="n">
-        <v>64</v>
-      </c>
     </row>
     <row r="195" ht="20" customHeight="1">
       <c r="A195" s="7" t="n">
@@ -11532,12 +9857,6 @@
           <t>https://maps.app.goo.gl/F8jPscSQ2V93c6vi8</t>
         </is>
       </c>
-      <c r="H195" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I195" s="14" t="n">
-        <v>2228</v>
-      </c>
     </row>
     <row r="196" ht="20" customHeight="1">
       <c r="A196" s="7" t="n">
@@ -11568,12 +9887,6 @@
           <t>https://maps.app.goo.gl/Zh4ebnPqcXvPMZNG9</t>
         </is>
       </c>
-      <c r="H196" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I196" s="14" t="n">
-        <v>2670</v>
-      </c>
     </row>
     <row r="197" ht="20" customHeight="1">
       <c r="A197" s="7" t="n">
@@ -11604,12 +9917,6 @@
           <t>https://maps.app.goo.gl/kuVZMKKgf5DubNtN8</t>
         </is>
       </c>
-      <c r="H197" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I197" s="14" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="7" t="n">
@@ -11640,12 +9947,6 @@
           <t>https://goo.gl/maps/EFUzibDLaLXcxkTd8</t>
         </is>
       </c>
-      <c r="H198" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I198" s="14" t="n">
-        <v>8996</v>
-      </c>
     </row>
     <row r="199" ht="20" customHeight="1">
       <c r="A199" s="7" t="n">
@@ -11676,12 +9977,6 @@
           <t>https://maps.app.goo.gl/6W1ZNqLiW1QG7swx5</t>
         </is>
       </c>
-      <c r="H199" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I199" s="14" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="200" ht="20" customHeight="1">
       <c r="A200" s="7" t="n">
@@ -11712,12 +10007,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Sirsa%2C+Haryana%2C+Sirsa+Sirsa?hl=en</t>
         </is>
       </c>
-      <c r="H200" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I200" s="14" t="n">
-        <v>190</v>
-      </c>
     </row>
     <row r="201" ht="20" customHeight="1">
       <c r="A201" s="7" t="n">
@@ -11748,12 +10037,6 @@
           <t>https://maps.app.goo.gl/ifJQ68YEKMTaET63A</t>
         </is>
       </c>
-      <c r="H201" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I201" s="14" t="n">
-        <v>143</v>
-      </c>
     </row>
     <row r="202" ht="20" customHeight="1">
       <c r="A202" s="7" t="n">
@@ -11784,8 +10067,6 @@
           <t>https://goo.gl/maps/gt6giRYsgV7Jfsmp8</t>
         </is>
       </c>
-      <c r="H202" s="14" t="n"/>
-      <c r="I202" s="14" t="n"/>
     </row>
     <row r="203" ht="20" customHeight="1">
       <c r="A203" s="7" t="n">
@@ -11816,12 +10097,6 @@
           <t>https://maps.app.goo.gl/k8nPnXCjPNR1Fw26A</t>
         </is>
       </c>
-      <c r="H203" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I203" s="14" t="n">
-        <v>17008</v>
-      </c>
     </row>
     <row r="204" ht="20" customHeight="1">
       <c r="A204" s="7" t="n">
@@ -11852,12 +10127,6 @@
           <t>https://maps.app.goo.gl/zD7nJnVUnKHTBbTc7</t>
         </is>
       </c>
-      <c r="H204" s="14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I204" s="14" t="n">
-        <v>152</v>
-      </c>
     </row>
     <row r="205" ht="20" customHeight="1">
       <c r="A205" s="7" t="n">
@@ -11888,12 +10157,6 @@
           <t>https://maps.app.goo.gl/rTKgS8LFdLXcgLgG8</t>
         </is>
       </c>
-      <c r="H205" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I205" s="14" t="n">
-        <v>338</v>
-      </c>
     </row>
     <row r="206" ht="20" customHeight="1">
       <c r="A206" s="7" t="n">
@@ -11923,12 +10186,6 @@
         <is>
           <t>https://maps.app.goo.gl/F4A61XtKBQZhzMRC7</t>
         </is>
-      </c>
-      <c r="H206" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I206" s="14" t="n">
-        <v>161</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1"/>
@@ -11943,8 +10200,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:H68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -11961,15 +10218,9 @@
         </is>
       </c>
       <c r="G1" s="11" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H1" s="11" t="n">
-        <v>46303</v>
-      </c>
-      <c r="I1" s="11" t="n">
-        <v>46304</v>
-      </c>
-      <c r="J1" s="11" t="n">
         <v>46304</v>
       </c>
     </row>
@@ -12010,16 +10261,6 @@
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>Review Count</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -12058,13 +10299,7 @@
         <v>4.5</v>
       </c>
       <c r="H3" s="14" t="n">
-        <v>6999</v>
-      </c>
-      <c r="I3" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J3" s="14" t="n">
-        <v>7003</v>
+        <v>7006</v>
       </c>
     </row>
     <row r="4">
@@ -12102,12 +10337,6 @@
       <c r="H4" s="14" t="n">
         <v>1720</v>
       </c>
-      <c r="I4" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J4" s="14" t="n">
-        <v>1720</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -12138,18 +10367,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Barsha+1+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1159702,55.2049553,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6bc01e76ba11:0x4fd1a9f4b2e6f5e3!8m2!3d25.1159702!4d55.2049553!16s%2Fg%2F1hhn4cw5b?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G5" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>3414</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J5" s="14" t="n">
-        <v>3417</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -12180,18 +10397,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Arjan+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.0611644,55.2416108,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6f3d18bbdbdd:0xf394598ae51611cd!8m2!3d25.0611644!4d55.2416108!16s%2Fg%2F11k4t6j5kj?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G6" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H6" s="14" t="n">
-        <v>1351</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J6" s="14" t="n">
-        <v>1351</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -12222,18 +10427,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Dubai+Hills+Mall+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1000884,55.2380841,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6ffb10c94323:0xe15233cd12b4c95e!8m2!3d25.1000884!4d55.2380841!16s%2Fg%2F11srb65qdy?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G7" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>1108</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J7" s="14" t="n">
-        <v>1109</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -12264,18 +10457,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Sheikh+Zayed+Road+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2287901,55.2861116,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43aad3d78e71:0xb8b194cb916fd9b0!8m2!3d25.2287901!4d55.2861116!16s%2Fg%2F11spn08t8p?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G8" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>3371</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>3370</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -12306,18 +10487,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Gold+Souk+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2720383,55.2977013,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43768964654b:0xc11f03b76b0ba714!8m2!3d25.2720383!4d55.2977013!16s%2Fg%2F11sqkp7mp7?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G9" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>1970</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>1970</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -12348,18 +10517,6 @@
           <t>https://www.google.com/maps/place/Bikanervala/@25.1971872,55.2793099,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43291308afa5:0xe48b7db44021ad9d!8m2!3d25.1971872!4d55.2793099!16s%2Fg%2F11h_6kxb_4?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G10" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>1201</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -12390,18 +10547,6 @@
           <t>https://www.google.com/maps/place/Bikanervala/@25.0443703,55.2301107,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6fbad2abf81f:0x2b8744ab6a1bf442!8m2!3d25.0443703!4d55.2301107!16s%2Fg%2F11wqdtyl9k?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G11" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>812</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>812</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -12432,18 +10577,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Jumeirah+Village+Circle?hl=en</t>
         </is>
       </c>
-      <c r="G12" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H12" s="14" t="n">
-        <v>3414</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>3417</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -12474,18 +10607,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Jumeirah+3+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1568314,55.2048822,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6bf2c1bdccc9:0x43c26854ab27ef01!8m2!3d25.1568314!4d55.2048822!16s%2Fg%2F11s5twnr34?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G13" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>406</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>406</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -12516,18 +10637,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Furjan+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.0253394,55.1523478,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6d3bc9bcdbdb:0xe6f0ccdcb4b1e8ab!8m2!3d25.0253394!4d55.1523478!16s%2Fg%2F11g8kr7p26?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G14" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H14" s="14" t="n">
-        <v>3465</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J14" s="14" t="n">
-        <v>3466</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -12558,18 +10667,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+International+City+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1587461,55.4044494,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6152822cefa7:0x62485254b618ad37!8m2!3d25.1587461!4d55.4044494!16s%2Fg%2F11fy4nt_fh?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G15" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H15" s="14" t="n">
-        <v>1986</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J15" s="14" t="n">
-        <v>1986</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -12600,18 +10697,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Ghurair+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.268832,55.3167197,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f432a6356bd7d:0x6e8727a69863a0ea!8m2!3d25.268832!4d55.3167197!16s%2Fg%2F11gj4q5yml?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G16" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>1337</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>1337</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -12642,18 +10727,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Business+Bay+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1907081,55.2657305,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f69d43a494553:0xcae55dd8d4af25bc!8m2!3d25.1907081!4d55.2657305!16s%2Fg%2F11cnch2xjh?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G17" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>1337</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <v>1336</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -12684,18 +10757,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Abu+Dhabi+%7C+Indian+Vegetarian+Restaurant+in+Abu+Dhabi/@24.4787181,54.3632708,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5e6797000fef8b:0x252e9c63c8d0f687!8m2!3d24.4787181!4d54.3632708!16s%2Fg%2F11j3jt3jck?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G18" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H18" s="14" t="n">
-        <v>4492</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J18" s="14" t="n">
-        <v>4492</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -12726,18 +10787,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Qusais+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2779484,55.362064,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f5c5ef14f580b:0x42f37dd66cc3bd09!8m2!3d25.2779484!4d55.362064!16s%2Fg%2F11bbwn_ftp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G19" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>1672</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J19" s="14" t="n">
-        <v>1674</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -12768,18 +10817,6 @@
           <t>https://www.google.com/maps/place/Bikanervala+Hounslow/@51.4697256,-0.3575675,17z/data=!3m1!4b1!4m6!3m5!1s0x48760db0ad77af37:0x259004b7a001719e!8m2!3d51.4697256!4d-0.3575675!16s%2Fg%2F11lw2pkxzp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
-      <c r="G20" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H20" s="14" t="n">
-        <v>4374</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J20" s="14" t="n">
-        <v>4379</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -12810,18 +10847,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Doha+Qatar?hl=en</t>
         </is>
       </c>
-      <c r="G21" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <v>3854</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J21" s="14" t="n">
-        <v>3858</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -12852,18 +10877,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Investment+Park+Dubai+%28Dubai%29?hl=en</t>
         </is>
       </c>
-      <c r="G22" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H22" s="14" t="n">
-        <v>87</v>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J22" s="14" t="n">
-        <v>87</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -12894,18 +10907,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Jumeirah+%28The+Point%2C+Palm%29+Dubai+%28Dubai%29?hl=en</t>
         </is>
       </c>
-      <c r="G23" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H23" s="14" t="n">
-        <v>443</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J23" s="14" t="n">
-        <v>443</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -12936,18 +10937,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Lynx+Tower+%28Silicon+Oasis%29+Dubai+%28Dubai%29?hl=en</t>
         </is>
       </c>
-      <c r="G24" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H24" s="14" t="n">
-        <v>1684</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J24" s="14" t="n">
-        <v>1684</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -12978,18 +10967,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+JLT+Dubai+%28Dubai%29?hl=en</t>
         </is>
       </c>
-      <c r="G25" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H25" s="14" t="n">
-        <v>3364</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J25" s="14" t="n">
-        <v>3364</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -13020,18 +10997,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Al+Wahda+Street+Sharjah+%28Sharjah%29?hl=en</t>
         </is>
       </c>
-      <c r="G26" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H26" s="14" t="n">
-        <v>1766</v>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J26" s="14" t="n">
-        <v>1765</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -13062,18 +11027,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Muweillah+Sharjah+%28Sharjah%29?hl=en</t>
         </is>
       </c>
-      <c r="G27" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H27" s="14" t="n">
-        <v>531</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J27" s="14" t="n">
-        <v>532</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -13104,18 +11057,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Southall+London+%28UK%29?hl=en</t>
         </is>
       </c>
-      <c r="G28" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H28" s="14" t="n">
-        <v>1325</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J28" s="14" t="n">
-        <v>1325</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -13146,18 +11087,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Ilford+London+%28UK%29?hl=en</t>
         </is>
       </c>
-      <c r="G29" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H29" s="14" t="n">
-        <v>642</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J29" s="14" t="n">
-        <v>642</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -13188,18 +11117,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Express+City+Centre+Mall+Doha+%28Qatar%29?hl=en</t>
         </is>
       </c>
-      <c r="G30" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H30" s="14" t="n">
-        <v>35</v>
-      </c>
-      <c r="I30" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J30" s="14" t="n">
-        <v>35</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -13230,18 +11147,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Jersey+City+NJ+%28USA%29?hl=en</t>
         </is>
       </c>
-      <c r="G31" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H31" s="14" t="n">
-        <v>1323</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J31" s="14" t="n">
-        <v>1323</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -13272,18 +11177,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Iselin+NJ+%28USA%29?hl=en</t>
         </is>
       </c>
-      <c r="G32" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H32" s="14" t="n">
-        <v>1427</v>
-      </c>
-      <c r="I32" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J32" s="14" t="n">
-        <v>1427</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -13314,18 +11207,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Kendall+Park+NJ+%28USA%29?hl=en</t>
         </is>
       </c>
-      <c r="G33" s="14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H33" s="14" t="n">
-        <v>1335</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J33" s="14" t="n">
-        <v>1335</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -13356,18 +11237,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Rochelle+Park+NJ+%28USA%29?hl=en</t>
         </is>
       </c>
-      <c r="G34" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H34" s="14" t="n">
-        <v>192</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J34" s="14" t="n">
-        <v>192</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -13398,18 +11267,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Westlake+Village+CA+%28USA%29?hl=en</t>
         </is>
       </c>
-      <c r="G35" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H35" s="14" t="n">
-        <v>127</v>
-      </c>
-      <c r="I35" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J35" s="14" t="n">
-        <v>127</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -13440,18 +11297,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Fremont+CA+%28USA%29?hl=en</t>
         </is>
       </c>
-      <c r="G36" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H36" s="14" t="n">
-        <v>994</v>
-      </c>
-      <c r="I36" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J36" s="14" t="n">
-        <v>994</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -13482,18 +11327,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Diamond+Bar+CA+%28USA%29?hl=en</t>
         </is>
       </c>
-      <c r="G37" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H37" s="14" t="n">
-        <v>205</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J37" s="14" t="n">
-        <v>205</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -13524,18 +11357,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Sunnyvale+CA+%28USA%29?hl=en</t>
         </is>
       </c>
-      <c r="G38" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H38" s="14" t="n">
-        <v>212</v>
-      </c>
-      <c r="I38" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J38" s="14" t="n">
-        <v>212</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -13566,18 +11387,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Overland+Park+KS+%28USA%29?hl=en</t>
         </is>
       </c>
-      <c r="G39" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H39" s="14" t="n">
-        <v>841</v>
-      </c>
-      <c r="I39" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J39" s="14" t="n">
-        <v>847</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -13608,18 +11417,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Irving+TX+%28USA%29?hl=en</t>
         </is>
       </c>
-      <c r="G40" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H40" s="14" t="n">
-        <v>2233</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J40" s="14" t="n">
-        <v>2234</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -13650,18 +11447,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Dublin+OH+%28USA%29?hl=en</t>
         </is>
       </c>
-      <c r="G41" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H41" s="14" t="n">
-        <v>450</v>
-      </c>
-      <c r="I41" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J41" s="14" t="n">
-        <v>450</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -13692,18 +11477,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Hicksville+NY+%28USA%29?hl=en</t>
         </is>
       </c>
-      <c r="G42" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H42" s="14" t="n">
-        <v>1586</v>
-      </c>
-      <c r="I42" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J42" s="14" t="n">
-        <v>1587</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -13734,18 +11507,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Schaumburg+IL+%28USA%29?hl=en</t>
         </is>
       </c>
-      <c r="G43" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H43" s="14" t="n">
-        <v>1164</v>
-      </c>
-      <c r="I43" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J43" s="14" t="n">
-        <v>1165</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -13776,18 +11537,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Chandler+AZ+%28USA%29?hl=en</t>
         </is>
       </c>
-      <c r="G44" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H44" s="14" t="n">
-        <v>474</v>
-      </c>
-      <c r="I44" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J44" s="14" t="n">
-        <v>474</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -13818,18 +11567,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Campbelltown+Adelaide+%28Australia%29?hl=en</t>
         </is>
       </c>
-      <c r="G45" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H45" s="14" t="n">
-        <v>411</v>
-      </c>
-      <c r="I45" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J45" s="14" t="n">
-        <v>410</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -13860,18 +11597,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Rouse+Hill+Sydney+%28Australia%29?hl=en</t>
         </is>
       </c>
-      <c r="G46" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H46" s="14" t="n">
-        <v>1045</v>
-      </c>
-      <c r="I46" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J46" s="14" t="n">
-        <v>1045</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -13902,14 +11627,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Truganina+Melbourne+%28Australia%29?hl=en</t>
         </is>
       </c>
-      <c r="G47" s="14" t="n"/>
-      <c r="H47" s="14" t="n"/>
-      <c r="I47" s="14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J47" s="14" t="n">
-        <v>2568</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -13940,18 +11657,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Henderson+Auckland+%28New+Zealand%29?hl=en</t>
         </is>
       </c>
-      <c r="G48" s="14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H48" s="14" t="n">
-        <v>1429</v>
-      </c>
-      <c r="I48" s="14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J48" s="14" t="n">
-        <v>1429</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -13982,18 +11687,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Mount+Roskill+Auckland+%28New+Zealand%29?hl=en</t>
         </is>
       </c>
-      <c r="G49" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H49" s="14" t="n">
-        <v>1420</v>
-      </c>
-      <c r="I49" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J49" s="14" t="n">
-        <v>1420</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -14024,18 +11717,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Sydenham+Christchurch+%28New+Zealand%29?hl=en</t>
         </is>
       </c>
-      <c r="G50" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H50" s="14" t="n">
-        <v>1550</v>
-      </c>
-      <c r="I50" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J50" s="14" t="n">
-        <v>1550</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -14066,18 +11747,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Brampton+%28Canada%29?hl=en</t>
         </is>
       </c>
-      <c r="G51" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H51" s="14" t="n">
-        <v>2806</v>
-      </c>
-      <c r="I51" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J51" s="14" t="n">
-        <v>2807</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -14108,18 +11777,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Markham+%28Canada%29?hl=en</t>
         </is>
       </c>
-      <c r="G52" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H52" s="14" t="n">
-        <v>744</v>
-      </c>
-      <c r="I52" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J52" s="14" t="n">
-        <v>744</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -14150,18 +11807,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Changi+Airport+T3+%28Singapore%29?hl=en</t>
         </is>
       </c>
-      <c r="G53" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H53" s="14" t="n">
-        <v>1229</v>
-      </c>
-      <c r="I53" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J53" s="14" t="n">
-        <v>1230</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -14192,18 +11837,6 @@
           <t>https://www.google.com/maps/search/Bikanervala+Katong+%28Singapore%29?hl=en</t>
         </is>
       </c>
-      <c r="G54" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H54" s="14" t="n">
-        <v>674</v>
-      </c>
-      <c r="I54" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J54" s="14" t="n">
-        <v>674</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -14233,18 +11866,6 @@
         <is>
           <t>https://www.google.com/maps/search/Bikanervala+Manama+%28Bahrain%29?hl=en</t>
         </is>
-      </c>
-      <c r="G55" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H55" s="14" t="n">
-        <v>424</v>
-      </c>
-      <c r="I55" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J55" s="14" t="n">
-        <v>424</v>
       </c>
     </row>
     <row r="56">
@@ -14492,8 +12113,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:H113"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -14510,15 +12131,9 @@
         </is>
       </c>
       <c r="G1" s="11" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H1" s="11" t="n">
-        <v>46303</v>
-      </c>
-      <c r="I1" s="11" t="n">
-        <v>46304</v>
-      </c>
-      <c r="J1" s="11" t="n">
         <v>46304</v>
       </c>
     </row>
@@ -14559,16 +12174,6 @@
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>Review Count</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -14609,12 +12214,6 @@
       <c r="H3" s="14" t="n">
         <v>4571</v>
       </c>
-      <c r="I3" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J3" s="14" t="n">
-        <v>4571</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -14649,13 +12248,7 @@
         <v>4.4</v>
       </c>
       <c r="H4" s="14" t="n">
-        <v>1230</v>
-      </c>
-      <c r="I4" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J4" s="14" t="n">
-        <v>1230</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="5">
@@ -14687,18 +12280,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Vikas+Marg+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G5" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>460</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J5" s="14" t="n">
-        <v>460</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -14729,18 +12310,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Akshardham+Parsvnath+Mall+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G6" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H6" s="14" t="n">
-        <v>11587</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J6" s="14" t="n">
-        <v>11588</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -14771,18 +12340,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Dilshad+Garden+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G7" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>2050</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J7" s="14" t="n">
-        <v>2050</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -14813,18 +12370,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Krishna+Nagar+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G8" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>918</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>919</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -14855,18 +12400,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Indraprastha+Apollo+Hospital+Sarita+Vihar+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G9" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>1604</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>1604</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -14897,18 +12430,6 @@
           <t>https://www.google.com/maps/search/Haldiram+DLF+Promenade+Vasant+Kunj+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G10" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>2049</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>2019</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -14939,18 +12460,6 @@
           <t>https://www.google.com/maps/search/Haldiram+DLF+Saket+District+Centre+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G11" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>3082</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>3082</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -14981,18 +12490,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Kalkaji+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G12" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H12" s="14" t="n">
-        <v>3628</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>3629</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -15023,18 +12520,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Lajpat+Nagar+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G13" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>21269</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>21269</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -15065,18 +12550,6 @@
           <t>https://www.google.com/maps/search/Haldiram+New+Friends+Colony+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G14" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H14" s="14" t="n">
-        <v>2947</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J14" s="14" t="n">
-        <v>2947</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -15107,18 +12580,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Green+Park+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G15" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H15" s="14" t="n">
-        <v>4205</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J15" s="14" t="n">
-        <v>4205</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -15149,18 +12610,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Nehru+Place+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G16" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>2389</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>2390</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -15191,18 +12640,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Kailash+Colony+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G17" s="14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -15233,18 +12670,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Mathura+Road+Mohan+Co-operative+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G18" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H18" s="14" t="n">
-        <v>12127</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J18" s="14" t="n">
-        <v>12127</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -15275,18 +12700,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Sarojini+Nagar+DLF+South+Square+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G19" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>3092</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J19" s="14" t="n">
-        <v>3092</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -15317,18 +12730,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Malviya+Nagar+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G20" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H20" s="14" t="n">
-        <v>9247</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J20" s="14" t="n">
-        <v>9247</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -15359,18 +12760,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Lok+Vihar+Pitampura+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G21" s="14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J21" s="14" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -15401,18 +12790,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Paschim+Vihar+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G22" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H22" s="14" t="n">
-        <v>6137</v>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J22" s="14" t="n">
-        <v>6137</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -15443,18 +12820,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Katwaria+Sarai+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G23" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H23" s="14" t="n">
-        <v>1766</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J23" s="14" t="n">
-        <v>1769</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -15485,18 +12850,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Anupam+Saket+PVR+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G24" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H24" s="14" t="n">
-        <v>1060</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J24" s="14" t="n">
-        <v>1060</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -15527,18 +12880,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Jungpura+Extension+Eros+One+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G25" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H25" s="14" t="n">
-        <v>2054</v>
-      </c>
-      <c r="I25" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J25" s="14" t="n">
-        <v>2054</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -15569,18 +12910,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Jasola+DLF+Tower+A+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G26" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H26" s="14" t="n">
-        <v>2780</v>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J26" s="14" t="n">
-        <v>2780</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -15611,18 +12940,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Moti+Nagar+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G27" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H27" s="14" t="n">
-        <v>11084</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J27" s="14" t="n">
-        <v>11084</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -15653,18 +12970,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Pitampura+D+Mall+Netaji+Subhash+Place+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G28" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H28" s="14" t="n">
-        <v>5490</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J28" s="14" t="n">
-        <v>5490</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -15695,18 +13000,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Janpath+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G29" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H29" s="14" t="n">
-        <v>4018</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J29" s="14" t="n">
-        <v>4018</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -15737,18 +13030,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Netaji+Subhash+Place+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G30" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H30" s="14" t="n">
-        <v>1579</v>
-      </c>
-      <c r="I30" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J30" s="14" t="n">
-        <v>1580</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -15779,18 +13060,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Netaji+Subhash+Place+2+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G31" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H31" s="14" t="n">
-        <v>1579</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J31" s="14" t="n">
-        <v>1580</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -15821,18 +13090,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Bikaner+House+Pandara+Road+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G32" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H32" s="14" t="n">
-        <v>2810</v>
-      </c>
-      <c r="I32" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J32" s="14" t="n">
-        <v>2809</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -15863,18 +13120,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Chandni+Chowk+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G33" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H33" s="14" t="n">
-        <v>18971</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" s="14" t="n">
-        <v>18972</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -15905,18 +13150,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Connaught+Place+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G34" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H34" s="14" t="n">
-        <v>39691</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J34" s="14" t="n">
-        <v>39694</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -15947,18 +13180,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Model+Town+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G35" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H35" s="14" t="n">
-        <v>5229</v>
-      </c>
-      <c r="I35" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J35" s="14" t="n">
-        <v>5229</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -15989,18 +13210,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Pusa+Road+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G36" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H36" s="14" t="n">
-        <v>10387</v>
-      </c>
-      <c r="I36" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J36" s="14" t="n">
-        <v>10387</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -16031,18 +13240,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Dwarka+City+Centre+Sector+12+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G37" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H37" s="14" t="n">
-        <v>7404</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J37" s="14" t="n">
-        <v>7405</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -16073,18 +13270,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Vegas+Mall+Food+Court+Dwarka+Sector+14+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G38" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H38" s="14" t="n">
-        <v>538</v>
-      </c>
-      <c r="I38" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J38" s="14" t="n">
-        <v>538</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -16115,18 +13300,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Dwarka+Sector+21+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G39" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H39" s="14" t="n">
-        <v>1124</v>
-      </c>
-      <c r="I39" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J39" s="14" t="n">
-        <v>1124</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -16157,18 +13330,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Vegas+Mall+Showroom+Dwarka+Sector+14+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G40" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H40" s="14" t="n">
-        <v>538</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J40" s="14" t="n">
-        <v>538</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -16199,18 +13360,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Tilak+Nagar+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G41" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H41" s="14" t="n">
-        <v>2621</v>
-      </c>
-      <c r="I41" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J41" s="14" t="n">
-        <v>2621</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -16241,18 +13390,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Janakpuri+Unity+One+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G42" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H42" s="14" t="n">
-        <v>1445</v>
-      </c>
-      <c r="I42" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J42" s="14" t="n">
-        <v>1445</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -16283,18 +13420,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Janak+Cinema+Janakpuri+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G43" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H43" s="14" t="n">
-        <v>955</v>
-      </c>
-      <c r="I43" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J43" s="14" t="n">
-        <v>955</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -16325,18 +13450,6 @@
           <t>https://www.google.com/maps/search/Haldiram+New+Delhi+Railway+Station?hl=en</t>
         </is>
       </c>
-      <c r="G44" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H44" s="14" t="n">
-        <v>4181</v>
-      </c>
-      <c r="I44" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J44" s="14" t="n">
-        <v>4181</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -16367,18 +13480,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Rajouri+Garden+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G45" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H45" s="14" t="n">
-        <v>3486</v>
-      </c>
-      <c r="I45" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J45" s="14" t="n">
-        <v>3486</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -16409,18 +13510,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Rohini+D+Mall+Sector+10+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G46" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H46" s="14" t="n">
-        <v>7886</v>
-      </c>
-      <c r="I46" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J46" s="14" t="n">
-        <v>7886</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -16451,18 +13540,6 @@
           <t>https://www.google.com/maps/search/Haldiram+ARSS+Mall+Paschim+Vihar+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G47" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H47" s="14" t="n">
-        <v>6137</v>
-      </c>
-      <c r="I47" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J47" s="14" t="n">
-        <v>6137</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -16493,18 +13570,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Vaishali+Enclave+Pitampura+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G48" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H48" s="14" t="n">
-        <v>983</v>
-      </c>
-      <c r="I48" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J48" s="14" t="n">
-        <v>983</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -16535,18 +13600,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Dwarka+Sector+11+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G49" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H49" s="14" t="n">
-        <v>3645</v>
-      </c>
-      <c r="I49" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J49" s="14" t="n">
-        <v>3645</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -16577,18 +13630,6 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T1+Domestic+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G50" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H50" s="14" t="n">
-        <v>171</v>
-      </c>
-      <c r="I50" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J50" s="14" t="n">
-        <v>171</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -16619,18 +13660,6 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+D-04+Domestic+Departure+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G51" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H51" s="14" t="n">
-        <v>4120</v>
-      </c>
-      <c r="I51" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J51" s="14" t="n">
-        <v>171</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -16661,18 +13690,6 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T3+International+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G52" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H52" s="14" t="n">
-        <v>294</v>
-      </c>
-      <c r="I52" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J52" s="14" t="n">
-        <v>294</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -16703,18 +13720,6 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T3+International+Departure+Gate+17B+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G53" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H53" s="14" t="n">
-        <v>127</v>
-      </c>
-      <c r="I53" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J53" s="14" t="n">
-        <v>128</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -16745,18 +13750,6 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T3A+Baggage+Reclaim+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G54" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H54" s="14" t="n">
-        <v>4120</v>
-      </c>
-      <c r="I54" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J54" s="14" t="n">
-        <v>4120</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -16787,18 +13780,6 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T2+Arrival+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G55" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H55" s="14" t="n">
-        <v>56</v>
-      </c>
-      <c r="I55" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J55" s="14" t="n">
-        <v>56</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -16829,18 +13810,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Okhla+Jasola+Delhi?hl=en</t>
         </is>
       </c>
-      <c r="G56" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H56" s="14" t="n">
-        <v>493</v>
-      </c>
-      <c r="I56" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J56" s="14" t="n">
-        <v>493</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -16871,18 +13840,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Spice+Mall+Sector+25A+Noida?hl=en</t>
         </is>
       </c>
-      <c r="G57" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H57" s="14" t="n">
-        <v>7853</v>
-      </c>
-      <c r="I57" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J57" s="14" t="n">
-        <v>7853</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -16913,18 +13870,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Logix+City+Centre+Sector+32+Noida?hl=en</t>
         </is>
       </c>
-      <c r="G58" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H58" s="14" t="n">
-        <v>4018</v>
-      </c>
-      <c r="I58" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J58" s="14" t="n">
-        <v>4018</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -16955,18 +13900,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Skymark+One+Sector+98+Noida?hl=en</t>
         </is>
       </c>
-      <c r="G59" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H59" s="14" t="n">
-        <v>2876</v>
-      </c>
-      <c r="I59" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J59" s="14" t="n">
-        <v>2882</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -16997,18 +13930,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Paras+One33+Sector+133+Noida?hl=en</t>
         </is>
       </c>
-      <c r="G60" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H60" s="14" t="n">
-        <v>2251</v>
-      </c>
-      <c r="I60" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J60" s="14" t="n">
-        <v>2251</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -17039,18 +13960,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Sector+18+Noida?hl=en</t>
         </is>
       </c>
-      <c r="G61" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H61" s="14" t="n">
-        <v>7832</v>
-      </c>
-      <c r="I61" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J61" s="14" t="n">
-        <v>7832</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -17081,18 +13990,6 @@
           <t>https://www.google.com/maps/search/Haldiram+DLF+Mall+of+India+Noida?hl=en</t>
         </is>
       </c>
-      <c r="G62" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H62" s="14" t="n">
-        <v>3616</v>
-      </c>
-      <c r="I62" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J62" s="14" t="n">
-        <v>3616</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -17123,18 +14020,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Youth+Plaza+Sector+63+Noida?hl=en</t>
         </is>
       </c>
-      <c r="G63" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H63" s="14" t="n">
-        <v>4769</v>
-      </c>
-      <c r="I63" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J63" s="14" t="n">
-        <v>4769</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -17165,18 +14050,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Hush+Life+Sector+63+Noida?hl=en</t>
         </is>
       </c>
-      <c r="G64" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H64" s="14" t="n">
-        <v>2626</v>
-      </c>
-      <c r="I64" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J64" s="14" t="n">
-        <v>2626</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -17207,18 +14080,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Advant+IT+Park+Noida+Expressway?hl=en</t>
         </is>
       </c>
-      <c r="G65" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H65" s="14" t="n">
-        <v>2903</v>
-      </c>
-      <c r="I65" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J65" s="14" t="n">
-        <v>2903</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -17249,18 +14110,6 @@
           <t>https://www.google.com/maps/search/Haldiram+MSX+Mall+Greater+Noida?hl=en</t>
         </is>
       </c>
-      <c r="G66" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H66" s="14" t="n">
-        <v>6446</v>
-      </c>
-      <c r="I66" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J66" s="14" t="n">
-        <v>6445</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -17291,18 +14140,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Grand+Venice+Mall+Greater+Noida?hl=en</t>
         </is>
       </c>
-      <c r="G67" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H67" s="14" t="n">
-        <v>781</v>
-      </c>
-      <c r="I67" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J67" s="14" t="n">
-        <v>781</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -17333,18 +14170,6 @@
           <t>https://www.google.com/maps/search/Haldiram+NH8+Kherki+Daula+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G68" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H68" s="14" t="n">
-        <v>19109</v>
-      </c>
-      <c r="I68" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J68" s="14" t="n">
-        <v>19109</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -17375,18 +14200,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Iris+Broadway+Sector+85-86+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G69" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H69" s="14" t="n">
-        <v>2918</v>
-      </c>
-      <c r="I69" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J69" s="14" t="n">
-        <v>2919</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -17417,18 +14230,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Vatika+Business+Park+Sector+49+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G70" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H70" s="14" t="n">
-        <v>2629</v>
-      </c>
-      <c r="I70" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J70" s="14" t="n">
-        <v>2629</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
@@ -17459,18 +14260,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Three+Roads+Sector+70+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G71" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H71" s="14" t="n">
-        <v>1193</v>
-      </c>
-      <c r="I71" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J71" s="14" t="n">
-        <v>1193</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -17501,18 +14290,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Ambience+Mall+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G72" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H72" s="14" t="n">
-        <v>4165</v>
-      </c>
-      <c r="I72" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J72" s="14" t="n">
-        <v>4165</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -17543,18 +14320,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Cyber+Hub+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G73" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H73" s="14" t="n">
-        <v>3864</v>
-      </c>
-      <c r="I73" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J73" s="14" t="n">
-        <v>3864</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -17585,18 +14350,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Fortis+Hospital+Huda+City+Centre+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G74" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H74" s="14" t="n">
-        <v>755</v>
-      </c>
-      <c r="I74" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J74" s="14" t="n">
-        <v>755</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -17627,18 +14380,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Palam+Vihar+Global+Foyer+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G75" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H75" s="14" t="n">
-        <v>4658</v>
-      </c>
-      <c r="I75" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J75" s="14" t="n">
-        <v>4658</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -17669,18 +14410,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Element+One+Sector+47-49+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G76" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H76" s="14" t="n">
-        <v>5288</v>
-      </c>
-      <c r="I76" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J76" s="14" t="n">
-        <v>5288</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -17711,18 +14440,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Eros+City+Square+Sector+49-50+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G77" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H77" s="14" t="n">
-        <v>159</v>
-      </c>
-      <c r="I77" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J77" s="14" t="n">
-        <v>159</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -17753,18 +14470,6 @@
           <t>https://www.google.com/maps/search/Haldiram+AIPL+Joy+Street+Sector+66+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G78" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H78" s="14" t="n">
-        <v>1131</v>
-      </c>
-      <c r="I78" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J78" s="14" t="n">
-        <v>1131</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -17795,18 +14500,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Worldmark+3+Sector+65+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G79" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H79" s="14" t="n">
-        <v>634</v>
-      </c>
-      <c r="I79" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J79" s="14" t="n">
-        <v>634</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -17837,18 +14530,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Ardee+Mall+Sector+52+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G80" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H80" s="14" t="n">
-        <v>1187</v>
-      </c>
-      <c r="I80" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J80" s="14" t="n">
-        <v>1187</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -17879,18 +14560,6 @@
           <t>https://www.google.com/maps/search/Haldiram+MGF+Metropolitan+Mall+MG+Road+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G81" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H81" s="14" t="n">
-        <v>1566</v>
-      </c>
-      <c r="I81" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J81" s="14" t="n">
-        <v>1566</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -17921,18 +14590,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Sahara+Mall+MG+Road+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G82" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H82" s="14" t="n">
-        <v>11744</v>
-      </c>
-      <c r="I82" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J82" s="14" t="n">
-        <v>11744</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -17963,18 +14620,6 @@
           <t>https://www.google.com/maps/search/Haldiram+City+Centre+MG+Road+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G83" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H83" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="I83" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J83" s="14" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
@@ -18005,18 +14650,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Sector+29+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G84" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H84" s="14" t="n">
-        <v>5933</v>
-      </c>
-      <c r="I84" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J84" s="14" t="n">
-        <v>5934</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -18047,18 +14680,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Sector+14+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G85" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H85" s="14" t="n">
-        <v>3265</v>
-      </c>
-      <c r="I85" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J85" s="14" t="n">
-        <v>3266</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -18089,18 +14710,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Parsvnath+City+Mall+Sector+12+Faridabad?hl=en</t>
         </is>
       </c>
-      <c r="G86" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H86" s="14" t="n">
-        <v>10433</v>
-      </c>
-      <c r="I86" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J86" s="14" t="n">
-        <v>10433</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
@@ -18131,18 +14740,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Crown+Interiorz+Sector+35+Faridabad?hl=en</t>
         </is>
       </c>
-      <c r="G87" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H87" s="14" t="n">
-        <v>4152</v>
-      </c>
-      <c r="I87" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J87" s="14" t="n">
-        <v>4152</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
@@ -18173,18 +14770,6 @@
           <t>https://www.google.com/maps/search/Haldiram+NIT+Metropolis+Mall+Faridabad?hl=en</t>
         </is>
       </c>
-      <c r="G88" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H88" s="14" t="n">
-        <v>2998</v>
-      </c>
-      <c r="I88" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J88" s="14" t="n">
-        <v>2998</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
@@ -18215,18 +14800,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Sector+15+Faridabad?hl=en</t>
         </is>
       </c>
-      <c r="G89" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H89" s="14" t="n">
-        <v>1295</v>
-      </c>
-      <c r="I89" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J89" s="14" t="n">
-        <v>1295</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -18257,18 +14830,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Angel+Mega+Mall+Kaushambi+Ghaziabad?hl=en</t>
         </is>
       </c>
-      <c r="G90" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H90" s="14" t="n">
-        <v>2235</v>
-      </c>
-      <c r="I90" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J90" s="14" t="n">
-        <v>2235</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
@@ -18299,18 +14860,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Ajnara+Orbit+Plaza+Crossing+Republic+Ghaziabad?hl=en</t>
         </is>
       </c>
-      <c r="G91" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H91" s="14" t="n">
-        <v>7974</v>
-      </c>
-      <c r="I91" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J91" s="14" t="n">
-        <v>7974</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
@@ -18341,18 +14890,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Sahibabad+Ghaziabad?hl=en</t>
         </is>
       </c>
-      <c r="G92" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H92" s="14" t="n">
-        <v>783</v>
-      </c>
-      <c r="I92" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J92" s="14" t="n">
-        <v>783</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
@@ -18383,18 +14920,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Signature+Global+Mall+Vaishali+Ghaziabad?hl=en</t>
         </is>
       </c>
-      <c r="G93" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H93" s="14" t="n">
-        <v>790</v>
-      </c>
-      <c r="I93" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J93" s="14" t="n">
-        <v>790</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
@@ -18425,18 +14950,6 @@
           <t>https://www.google.com/maps/search/Haldiram+RDC+Raj+Nagar+Ghaziabad?hl=en</t>
         </is>
       </c>
-      <c r="G94" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H94" s="14" t="n">
-        <v>2595</v>
-      </c>
-      <c r="I94" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J94" s="14" t="n">
-        <v>2595</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
@@ -18467,18 +14980,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Nehru+Nagar+Ghaziabad?hl=en</t>
         </is>
       </c>
-      <c r="G95" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H95" s="14" t="n">
-        <v>1678</v>
-      </c>
-      <c r="I95" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J95" s="14" t="n">
-        <v>1679</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
@@ -18509,18 +15010,6 @@
           <t>https://www.google.com/maps/search/Haldiram+World+Square+Mall+Ghaziabad?hl=en</t>
         </is>
       </c>
-      <c r="G96" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H96" s="14" t="n">
-        <v>6440</v>
-      </c>
-      <c r="I96" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J96" s="14" t="n">
-        <v>6440</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
@@ -18551,18 +15040,6 @@
           <t>https://www.google.com/maps/search/Haldiram+East+Delhi+Mall+Kaushambi+Ghaziabad?hl=en</t>
         </is>
       </c>
-      <c r="G97" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H97" s="14" t="n">
-        <v>2315</v>
-      </c>
-      <c r="I97" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J97" s="14" t="n">
-        <v>2315</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -18593,18 +15070,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Vasundhara+Sector+11+Ghaziabad?hl=en</t>
         </is>
       </c>
-      <c r="G98" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H98" s="14" t="n">
-        <v>1937</v>
-      </c>
-      <c r="I98" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J98" s="14" t="n">
-        <v>1937</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
@@ -18635,18 +15100,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Gajraula+NH-24?hl=en</t>
         </is>
       </c>
-      <c r="G99" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H99" s="14" t="n">
-        <v>5580</v>
-      </c>
-      <c r="I99" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J99" s="14" t="n">
-        <v>5582</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -18677,18 +15130,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Khatauli?hl=en</t>
         </is>
       </c>
-      <c r="G100" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H100" s="14" t="n">
-        <v>17789</v>
-      </c>
-      <c r="I100" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J100" s="14" t="n">
-        <v>17789</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -18719,18 +15160,6 @@
           <t>https://www.google.com/maps/search/Haldiram+SRK+Mall+Agra?hl=en</t>
         </is>
       </c>
-      <c r="G101" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H101" s="14" t="n">
-        <v>6173</v>
-      </c>
-      <c r="I101" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J101" s="14" t="n">
-        <v>6172</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -18761,18 +15190,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Rewari?hl=en</t>
         </is>
       </c>
-      <c r="G102" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H102" s="14" t="n">
-        <v>5282</v>
-      </c>
-      <c r="I102" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J102" s="14" t="n">
-        <v>5282</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
@@ -18803,18 +15220,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Jaipur+135+NH-8+Behror?hl=en</t>
         </is>
       </c>
-      <c r="G103" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H103" s="14" t="n">
-        <v>1176</v>
-      </c>
-      <c r="I103" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J103" s="14" t="n">
-        <v>1176</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -18845,18 +15250,6 @@
           <t>https://www.google.com/maps/search/Haldiram+V+Square+Mall+Bhiwadi?hl=en</t>
         </is>
       </c>
-      <c r="G104" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H104" s="14" t="n">
-        <v>4077</v>
-      </c>
-      <c r="I104" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J104" s="14" t="n">
-        <v>4077</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
@@ -18887,18 +15280,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Delhi+135+NH-8+Behror?hl=en</t>
         </is>
       </c>
-      <c r="G105" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H105" s="14" t="n">
-        <v>1176</v>
-      </c>
-      <c r="I105" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J105" s="14" t="n">
-        <v>1176</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
@@ -18929,18 +15310,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Zirakpur?hl=en</t>
         </is>
       </c>
-      <c r="G106" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H106" s="14" t="n">
-        <v>10977</v>
-      </c>
-      <c r="I106" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J106" s="14" t="n">
-        <v>10977</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -18971,18 +15340,6 @@
           <t>https://www.google.com/maps/search/Haldiram+VR+Punjab+Mall+Mohali?hl=en</t>
         </is>
       </c>
-      <c r="G107" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H107" s="14" t="n">
-        <v>3159</v>
-      </c>
-      <c r="I107" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J107" s="14" t="n">
-        <v>3159</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -19013,18 +15370,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Ambala?hl=en</t>
         </is>
       </c>
-      <c r="G108" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H108" s="14" t="n">
-        <v>3059</v>
-      </c>
-      <c r="I108" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J108" s="14" t="n">
-        <v>3059</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
@@ -19055,18 +15400,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Amritsar?hl=en</t>
         </is>
       </c>
-      <c r="G109" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H109" s="14" t="n">
-        <v>2622</v>
-      </c>
-      <c r="I109" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J109" s="14" t="n">
-        <v>2622</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
@@ -19097,18 +15430,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Barnala?hl=en</t>
         </is>
       </c>
-      <c r="G110" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H110" s="14" t="n">
-        <v>1881</v>
-      </c>
-      <c r="I110" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J110" s="14" t="n">
-        <v>1881</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
@@ -19139,18 +15460,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Sonipat?hl=en</t>
         </is>
       </c>
-      <c r="G111" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H111" s="14" t="n">
-        <v>1196</v>
-      </c>
-      <c r="I111" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J111" s="14" t="n">
-        <v>1196</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -19181,18 +15490,6 @@
           <t>https://www.google.com/maps/search/Haldiram+Pathankot?hl=en</t>
         </is>
       </c>
-      <c r="G112" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H112" s="14" t="n">
-        <v>2454</v>
-      </c>
-      <c r="I112" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J112" s="14" t="n">
-        <v>2454</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
@@ -19222,18 +15519,6 @@
         <is>
           <t>https://www.google.com/maps/search/Haldiram+Kosi+Kalan?hl=en</t>
         </is>
-      </c>
-      <c r="G113" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H113" s="14" t="n">
-        <v>2645</v>
-      </c>
-      <c r="I113" s="14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J113" s="14" t="n">
-        <v>2645</v>
       </c>
     </row>
   </sheetData>
@@ -19247,8 +15532,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -19265,15 +15550,9 @@
         </is>
       </c>
       <c r="G1" s="11" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H1" s="11" t="n">
-        <v>46303</v>
-      </c>
-      <c r="I1" s="11" t="n">
-        <v>46304</v>
-      </c>
-      <c r="J1" s="11" t="n">
         <v>46304</v>
       </c>
     </row>
@@ -19314,16 +15593,6 @@
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>Review Count</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -19364,12 +15633,6 @@
       <c r="H3" s="14" t="n">
         <v>14378</v>
       </c>
-      <c r="I3" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J3" s="14" t="n">
-        <v>14379</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -19404,12 +15667,6 @@
         <v>4.3</v>
       </c>
       <c r="H4" s="14" t="n">
-        <v>1201</v>
-      </c>
-      <c r="I4" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J4" s="14" t="n">
         <v>1202</v>
       </c>
     </row>
@@ -19442,18 +15699,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Elan+Town+Centre+Sector+67+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G5" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J5" s="14" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -19484,18 +15729,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Huda+Market+Sector+57+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G6" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H6" s="14" t="n">
-        <v>62</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J6" s="14" t="n">
-        <v>62</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -19526,18 +15759,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+M3M+Cosmopolitan+Sector+66+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G7" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>4837</v>
-      </c>
-      <c r="I7" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J7" s="14" t="n">
-        <v>4837</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -19568,18 +15789,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+New+Colony+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G8" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>2067</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>2067</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -19610,18 +15819,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Palam+Vihar+Road+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G9" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>5780</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>5782</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -19652,18 +15849,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+10A+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G10" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>6559</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>6559</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -19694,18 +15879,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+23+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G11" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>10577</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>10577</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -19736,18 +15909,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+31+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G12" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H12" s="14" t="n">
-        <v>12236</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>12236</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -19778,18 +15939,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+4+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G13" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>10701</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>10701</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -19820,18 +15969,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+46+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G14" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H14" s="14" t="n">
-        <v>6811</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J14" s="14" t="n">
-        <v>6811</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -19862,18 +15999,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+50+Good+Earth+City+Centre+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G15" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H15" s="14" t="n">
-        <v>3606</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J15" s="14" t="n">
-        <v>3606</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -19904,18 +16029,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+57+Hong+Kong+Bazaar+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G16" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>4504</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>4504</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -19946,18 +16059,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+7+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G17" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>878</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <v>878</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -19988,18 +16089,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+14+Gurgaon?hl=en</t>
         </is>
       </c>
-      <c r="G18" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H18" s="14" t="n">
-        <v>19721</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J18" s="14" t="n">
-        <v>19721</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -20030,18 +16119,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+NIT+Faridabad?hl=en</t>
         </is>
       </c>
-      <c r="G19" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>2022</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J19" s="14" t="n">
-        <v>2022</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -20072,18 +16149,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Omaxe+World+Street+Sector+79+Faridabad?hl=en</t>
         </is>
       </c>
-      <c r="G20" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H20" s="14" t="n">
-        <v>2045</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J20" s="14" t="n">
-        <v>2048</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -20114,18 +16179,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+16+Faridabad?hl=en</t>
         </is>
       </c>
-      <c r="G21" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <v>8784</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J21" s="14" t="n">
-        <v>8784</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -20156,18 +16209,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+31+Faridabad?hl=en</t>
         </is>
       </c>
-      <c r="G22" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H22" s="14" t="n">
-        <v>1119</v>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J22" s="14" t="n">
-        <v>1119</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -20198,18 +16239,6 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Palwal?hl=en</t>
         </is>
       </c>
-      <c r="G23" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H23" s="14" t="n">
-        <v>677</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J23" s="14" t="n">
-        <v>677</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -20239,18 +16268,6 @@
         <is>
           <t>https://www.google.com/maps/search/Om+Sweets+Sohna?hl=en</t>
         </is>
-      </c>
-      <c r="G24" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" s="14" t="n">
-        <v>1822</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="14" t="n">
-        <v>1822</v>
       </c>
     </row>
   </sheetData>
@@ -20264,8 +16281,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:H61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -20282,15 +16299,9 @@
         </is>
       </c>
       <c r="G1" s="11" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H1" s="11" t="n">
-        <v>46303</v>
-      </c>
-      <c r="I1" s="11" t="n">
-        <v>46304</v>
-      </c>
-      <c r="J1" s="11" t="n">
         <v>46304</v>
       </c>
     </row>
@@ -20331,16 +16342,6 @@
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>Review Count</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>GMB Live Rating</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -20381,12 +16382,6 @@
       <c r="H3" s="14" t="n">
         <v>1595</v>
       </c>
-      <c r="I3" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" s="14" t="n">
-        <v>1595</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -20423,12 +16418,6 @@
       <c r="H4" s="14" t="n">
         <v>1041</v>
       </c>
-      <c r="I4" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J4" s="14" t="n">
-        <v>1041</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -20459,18 +16448,6 @@
           <t>https://www.google.com/maps/place/Puranmal+Sweets+and+Restaurant/data=!4m7!3m6!1s0x3e5f42d80a18fbdb:0x9f86aefc091ecb9!8m2!3d25.2486238!4d55.3024612!16s%2Fg%2F11bbwx1fbb!19sChIJ2_sYCthCXz4RueyRwO9q-Ak?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G5" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>1981</v>
-      </c>
-      <c r="I5" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J5" s="14" t="n">
-        <v>1981</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -20501,18 +16478,6 @@
           <t>https://www.google.com/maps/place/Puranmal+Restaurant/data=!4m7!3m6!1s0x3e5f729cb45eefab:0xac26aaf47bcb314!8m2!3d24.9992282!4d55.170383!16s%2Fg%2F11f3hf2kqp!19sChIJq-9etJxyXz4RFLO8R69qwgo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G6" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" s="14" t="n">
-        <v>1187</v>
-      </c>
-      <c r="I6" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" s="14" t="n">
-        <v>1187</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -20543,14 +16508,6 @@
           <t>https://www.google.com/maps/place/Puranmal/data=!4m7!3m6!1s0x3e5f133176ad688d:0x3383f49dba4666ef!8m2!3d25.0476057!4d55.1311601!16s%2Fg%2F1hhgjxrxn!19sChIJjWitdjETXz4R72ZGup30gzM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G7" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H7" s="14" t="n">
-        <v>1412</v>
-      </c>
-      <c r="I7" s="14" t="n"/>
-      <c r="J7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -20581,18 +16538,6 @@
           <t>https://www.google.com/maps/place/Puranmal+sweets+and+restaurant/data=!4m7!3m6!1s0x3e5f6fca777c80b7:0xd9fcbfdd4343072d!8m2!3d25.0590927!4d55.2412228!16s%2Fg%2F11y_gyll3p!19sChIJt4B8d8pvXz4RLQdDQ92__Nk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G8" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>1981</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -20623,18 +16568,6 @@
           <t>https://www.google.com/maps/place/Puranmal+Sweets+%26+Restaurant/data=!4m7!3m6!1s0x3e5f646e13b36049:0xb69ac7e875aba115!8m2!3d25.1180318!4d55.3910236!16s%2Fg%2F11bbwqz2c0!19sChIJSWCzE25kXz4RFaGrdejHmrY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G9" s="14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>1133</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>1133</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -20665,18 +16598,6 @@
           <t>https://www.google.com/maps/place/Vega+by+Puranmal/data=!4m7!3m6!1s0x3e5f4251eda72f51:0x1b6293d48301a31c!8m2!3d25.2284641!4d55.2604103!16s%2Fg%2F11bc7tvmsh!19sChIJUS-n7VFCXz4RHKMBg9STYhs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G10" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>722</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>722</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -20707,18 +16628,6 @@
           <t>https://www.google.com/maps/place/Puranmal+Restaurants+DMCC/data=!4m7!3m6!1s0x3e5f6d48eaaed9f7:0x791c0ba6c372ae26!8m2!3d25.0690597!4d55.138396!16s%2Fg%2F11ms89fkjx!19sChIJ99mu6khtXz4RJq5yw6YLHHk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G11" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -20749,18 +16658,6 @@
           <t>https://www.google.com/maps/place/Puranmal+Authentic+Indian+Delicacies/data=!4m7!3m6!1s0x3e5f436690ce24a1:0x7980cd991fdc9e15!8m2!3d25.2218502!4d55.2814127!16s%2Fg%2F11s_fz4c8s!19sChIJoSTOkGZDXz4RFZ7cH5nNgHk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G12" s="14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H12" s="14" t="n">
-        <v>23</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>23</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -20791,18 +16688,6 @@
           <t>https://www.google.com/maps/place/Puranmal+Meadows+%28Enoc%29/data=!4m7!3m6!1s0x3e5f6d258d8a3247:0x6cbc17e16920e393!8m2!3d25.0642063!4d55.1549915!16s%2Fg%2F11j3phbw8b!19sChIJRzKKjSVtXz4Rk-MgaeEXvGw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G13" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>93</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>93</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -20833,18 +16718,6 @@
           <t>https://www.google.com/maps/place/Puranmal+Greens/data=!4m7!3m6!1s0x3e5f6b50f32318cf:0xc102df0e0c359348!8m2!3d25.094062!4d55.1678865!16s%2Fg%2F11hjkgs3kq!19sChIJzxgj81BrXz4RSJM1DA7fAsE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G14" s="14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H14" s="14" t="n">
-        <v>73</v>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J14" s="14" t="n">
-        <v>73</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -20875,18 +16748,6 @@
           <t>https://www.google.com/maps/place/Puranmal+Resturant/data=!4m7!3m6!1s0x3e5f5c77eab52041:0x9bf086c3c54484d0!8m2!3d25.303719!4d55.3708944!16s%2Fg%2F11c1ptxkdb!19sChIJQSC16ndcXz4R0IRExcOG8Js?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G15" s="14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H15" s="14" t="n">
-        <v>562</v>
-      </c>
-      <c r="I15" s="14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J15" s="14" t="n">
-        <v>562</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -20917,18 +16778,6 @@
           <t>https://www.google.com/maps/place/Puranmal+Warehouse/data=!4m7!3m6!1s0x3e5f7268095ac931:0x1bebae7a986abcaf!8m2!3d24.9894399!4d55.192723!16s%2Fg%2F11bx1gykmp!19sChIJMclaCWhyXz4Rr7xqmHqu6xs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G16" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>14</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>14</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -20959,18 +16808,6 @@
           <t>https://www.google.com/maps/place/Haldiram%E2%80%99s+Al+Mankhool-+Vegetarian+Restaurant+in+Dubai/data=!4m7!3m6!1s0x3e5f43ffefd64bdf:0xd55fd4634f47f83f!8m2!3d25.2550953!4d55.2935363!16s%2Fg%2F11yc82939p!19sChIJ30vW7_9DXz4RP_hHT2PUX9U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G17" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>5835</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <v>5835</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -21001,18 +16838,6 @@
           <t>https://www.google.com/maps/place/Haldiram%27s-+Sheikh+Zayed+Road/data=!4m7!3m6!1s0x3e5f430026f8137d:0xbc533bf410617740!8m2!3d25.2226875!4d55.2820625!16s%2Fg%2F11z3v_0z7p!19sChIJfRP4JgBDXz4RQHdhEPQ7U7w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G18" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H18" s="14" t="n">
-        <v>1120</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J18" s="14" t="n">
-        <v>1124</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -21043,18 +16868,6 @@
           <t>https://www.google.com/maps/place/Shree+Haldiram+restaurant/data=!4m7!3m6!1s0x3e5f43208d06a43d:0xa95a2f625d380979!8m2!3d25.2370936!4d55.3075144!16s%2Fg%2F11rvdtdbqf!19sChIJPaQGjSBDXz4ReQk4XWIvWqk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G19" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J19" s="14" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -21085,18 +16898,6 @@
           <t>https://www.google.com/maps/place/Kailash+Parbat/data=!4m7!3m6!1s0x3e5f4339607918bb:0xb6fb2afaf133c371!8m2!3d25.25816!4d55.3108109!16s%2Fg%2F11gtb6v4m3!19sChIJuxh5YDlDXz4RccMz8foq-7Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G20" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H20" s="14" t="n">
-        <v>2471</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J20" s="14" t="n">
-        <v>2472</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -21127,18 +16928,6 @@
           <t>https://www.google.com/maps/place/Kailash+Parbat,+Pure+Veg+Restaurant+Oud+Metha,+Dubai/data=!4m7!3m6!1s0x3e5f4354d534364f:0x7e15b26dd9861a0b!8m2!3d25.236946!4d55.3066909!16s%2Fg%2F11rjttcfky!19sChIJTzY01VRDXz4RCxqG2W2yFX4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G21" s="14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <v>341</v>
-      </c>
-      <c r="I21" s="14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J21" s="14" t="n">
-        <v>341</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -21156,7 +16945,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Almond House - Almond House</t>
+          <t>Road No. 36, Jubilee Hills</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -21168,18 +16957,6 @@
         <is>
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb913407f2d1b5:0x3249a9e465711151!8m2!3d17.429486!4d78.4098711!16s%2Fg%2F12629gjp0!19sChIJtdHyBzSRyzsRURFxZeSpSTI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
-      </c>
-      <c r="G22" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H22" s="14" t="n">
-        <v>4357</v>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J22" s="14" t="n">
-        <v>4356</v>
       </c>
     </row>
     <row r="23">
@@ -21198,7 +16975,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Almond House - Almond House</t>
+          <t>Himayat Nagar</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -21210,18 +16987,6 @@
         <is>
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb99dd2703988d:0xef045befa5f3726e!8m2!3d17.4011091!4d78.4858873!16s%2Fg%2F1tj48yhg!19sChIJjZgDJ92ZyzsRbnLzpe9bBO8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
-      </c>
-      <c r="G23" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H23" s="14" t="n">
-        <v>11258</v>
-      </c>
-      <c r="I23" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J23" s="14" t="n">
-        <v>11258</v>
       </c>
     </row>
     <row r="24">
@@ -21240,7 +17005,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Almond House - Almond House</t>
+          <t>KPHB Phase 3, Kukatpally</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -21252,18 +17017,6 @@
         <is>
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb918eafb67403:0x509ba3d059027dd0!8m2!3d17.4859258!4d78.3903757!16s%2Fg%2F11fy9ssrk3!19sChIJA3S2r46RyzsR0H0CWdCjm1A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
-      </c>
-      <c r="G24" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H24" s="14" t="n">
-        <v>13829</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J24" s="14" t="n">
-        <v>13830</v>
       </c>
     </row>
     <row r="25">
@@ -21282,7 +17035,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Almond House - Almond House</t>
+          <t>Sindhi Colony, Begumpet</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
@@ -21295,14 +17048,6 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9b23a1136449:0xeaa3a261dda1ba18!8m2!3d17.4432886!4d78.4781068!16s%2Fg%2F11h_11dbss!19sChIJSWQToSObyzsRGLqh3WGio-o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G25" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H25" s="14" t="n">
-        <v>5024</v>
-      </c>
-      <c r="I25" s="14" t="n"/>
-      <c r="J25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -21320,7 +17065,7 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Almond House - Almond House</t>
+          <t>Road No. 3, Banjara Hills</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -21332,18 +17077,6 @@
         <is>
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb972c621e321f:0x39d6c04e3a800c16!8m2!3d17.4269497!4d78.4433936!16s%2Fg%2F1w110n5q!19sChIJHzIeYiyXyzsRFgyAOk7A1jk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="H26" s="14" t="n">
-        <v>8083</v>
-      </c>
-      <c r="I26" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J26" s="14" t="n">
-        <v>8062</v>
       </c>
     </row>
     <row r="27">
@@ -21362,7 +17095,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>Almond House - Almond House</t>
+          <t>Regimental Bazaar, Secunderabad</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -21374,18 +17107,6 @@
         <is>
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9bdb0fd94b33:0x2cf8f2cc691ea5b4!8m2!3d17.4408497!4d78.5032582!16s%2Fg%2F11h4tnmqw2!19sChIJM0vZD9ubyzsRtKUeaczy-Cw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
-      </c>
-      <c r="G27" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H27" s="14" t="n">
-        <v>7816</v>
-      </c>
-      <c r="I27" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J27" s="14" t="n">
-        <v>7816</v>
       </c>
     </row>
     <row r="28">
@@ -21404,7 +17125,7 @@
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Almond House - Almond House</t>
+          <t>Le Meredian, Gachibowli</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
@@ -21416,18 +17137,6 @@
         <is>
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb93a010c47de3:0x2a6d183afbe9aea9!8m2!3d17.4495681!4d78.3634623!16s%2Fg%2F11fqqbr4t3!19sChIJ433EEKCTyzsRqa7p-zoYbSo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
-      </c>
-      <c r="G28" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H28" s="14" t="n">
-        <v>6651</v>
-      </c>
-      <c r="I28" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J28" s="14" t="n">
-        <v>6651</v>
       </c>
     </row>
     <row r="29">
@@ -21446,7 +17155,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Almond House - Almond House</t>
+          <t>Kokapet One, Gandipet</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -21458,18 +17167,6 @@
         <is>
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb95404cdeed5f:0x368b5c59f9072840!8m2!3d17.3855295!4d78.3303451!16s%2Fg%2F11xt9dz54t!19sChIJX-3eTECVyzsRQCgH-VlcizY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
-      </c>
-      <c r="G29" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H29" s="14" t="n">
-        <v>1155</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J29" s="14" t="n">
-        <v>1155</v>
       </c>
     </row>
     <row r="30">
@@ -21488,7 +17185,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Almond House - Almond House</t>
+          <t>Road No. 12, Banjara Hills</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -21500,18 +17197,6 @@
         <is>
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9727c96cf2cb:0xed10d003e11e198d!8m2!3d17.4126667!4d78.4303883!16s%2Fg%2F1ptxy0rc8!19sChIJy_JsySeXyzsRjRke4QPQEO0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
-      </c>
-      <c r="G30" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H30" s="14" t="n">
-        <v>4943</v>
-      </c>
-      <c r="I30" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J30" s="14" t="n">
-        <v>8062</v>
       </c>
     </row>
     <row r="31">
@@ -21530,7 +17215,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Almond House - Almond House</t>
+          <t>Puli KR Square, Kompally</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
@@ -21542,18 +17227,6 @@
         <is>
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9b76029a6381:0xfbe255b51a1975d8!8m2!3d17.5137477!4d78.479297!16s%2Fg%2F11svfkn0lv!19sChIJgWOaAnabyzsR2HUZGrVV4vs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
-      </c>
-      <c r="G31" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H31" s="14" t="n">
-        <v>8065</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J31" s="14" t="n">
-        <v>8062</v>
       </c>
     </row>
     <row r="32">
@@ -21572,7 +17245,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Almond House - Almond House</t>
+          <t>Shamshabad Airport</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
@@ -21585,14 +17258,6 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcbbb81d4c3e721:0x6cfdcb31d373fc39!8m2!3d17.2352717!4d78.4306917!16s%2Fg%2F11c5t04l3c!19sChIJIefD1IG7yzsROfxz0zHL_Ww?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G32" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H32" s="14" t="n">
-        <v>8436</v>
-      </c>
-      <c r="I32" s="14" t="n"/>
-      <c r="J32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -21610,7 +17275,7 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>Almond House - Almond House</t>
+          <t>Vayupuri, Sainikpuri</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
@@ -21622,18 +17287,6 @@
         <is>
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9b1732f66e7b:0xf311299cd0febcba!8m2!3d17.4837097!4d78.5426156!16s%2Fg%2F11y3npb6zt!19sChIJe272MhebyzsRurz-0JwpEfM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
-      </c>
-      <c r="G33" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H33" s="14" t="n">
-        <v>4182</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J33" s="14" t="n">
-        <v>4182</v>
       </c>
     </row>
     <row r="34">
@@ -21652,7 +17305,7 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Almond House - Almond House</t>
+          <t>Raidurg, Serilingampally</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -21664,18 +17317,6 @@
         <is>
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb95633e613e13:0x5de8794d037bb3ee!8m2!3d17.4203322!4d78.3797772!16s%2Fg%2F11ntl7h69x!19sChIJEz5hPmOVyzsR7rN7A0156F0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
-      </c>
-      <c r="G34" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H34" s="14" t="n">
-        <v>22</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J34" s="14" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="35">
@@ -21707,18 +17348,6 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Jubilee+Hills/data=!4m7!3m6!1s0x3bcb9136402aa371:0xf6b91a349382b790!8m2!3d17.4313965!4d78.407714!16s%2Fg%2F1pp2x6w4s!19sChIJcaMqQDaRyzsRkLeCkzQaufY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G35" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H35" s="14" t="n">
-        <v>4429</v>
-      </c>
-      <c r="I35" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J35" s="14" t="n">
-        <v>4429</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -21749,18 +17378,6 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Himayathnagar/data=!4m7!3m6!1s0x3bcb99e0f3ba40ad:0x95ec754fd3ed92!8m2!3d17.4056989!4d78.4791329!16s%2Fg%2F1hc5k1hm9!19sChIJrUC68-CZyzsRku3TT3XslQA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G36" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H36" s="14" t="n">
-        <v>5551</v>
-      </c>
-      <c r="I36" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J36" s="14" t="n">
-        <v>5551</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -21791,18 +17408,6 @@
           <t>https://www.google.com/maps/place/Dadu%E2%80%99s+Gachibowli/data=!4m7!3m6!1s0x3bcb93c86eaff663:0xe881fab9e954d25b!8m2!3d17.446841!4d78.3639362!16s%2Fg%2F11fn5sfyl9!19sChIJY_avbsiTyzsRW9JU6bn6geg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G37" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H37" s="14" t="n">
-        <v>4185</v>
-      </c>
-      <c r="I37" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J37" s="14" t="n">
-        <v>4186</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -21833,18 +17438,6 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Banjara+Hills/data=!4m7!3m6!1s0x3bcb973c9c5873a1:0x2940a491f0de08bf!8m2!3d17.4134194!4d78.4276568!16s%2Fg%2F11by_dbs5h!19sChIJoXNYnDyXyzsRvwje8JGkQCk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G38" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H38" s="14" t="n">
-        <v>2506</v>
-      </c>
-      <c r="I38" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J38" s="14" t="n">
-        <v>2506</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -21875,18 +17468,6 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Secunderabad/data=!4m7!3m6!1s0x3bcb9a101536a157:0x4fbfcbf25b9c1602!8m2!3d17.4414333!4d78.4880539!16s%2Fg%2F1td46f3y!19sChIJV6E2FRCayzsRAhacW_LLv08?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G39" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H39" s="14" t="n">
-        <v>6421</v>
-      </c>
-      <c r="I39" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J39" s="14" t="n">
-        <v>6421</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -21917,18 +17498,6 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Kukatpally/data=!4m7!3m6!1s0x3bcb91f9fa95f95d:0xf3471b49fd532f93!8m2!3d17.495512!4d78.3994334!16s%2Fg%2F11h6m7_vqw!19sChIJXfmV-vmRyzsRky9T_UkbR_M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G40" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H40" s="14" t="n">
-        <v>2544</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J40" s="14" t="n">
-        <v>2544</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -21959,18 +17528,6 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Chaitanyapuri/data=!4m7!3m6!1s0x3bcb99a4d81ed5f7:0xc4937f510b885941!8m2!3d17.3687084!4d78.5325781!16s%2Fg%2F11kbl95gd1!19sChIJ99Ue2KSZyzsRQVmIC1F_k8Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G41" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H41" s="14" t="n">
-        <v>1059</v>
-      </c>
-      <c r="I41" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J41" s="14" t="n">
-        <v>1061</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -22001,18 +17558,6 @@
           <t>https://www.google.com/maps/place/Dadu%27s+A.s+Rao+Nagar/data=!4m7!3m6!1s0x3bcb9b47f0228861:0x9970f2f0f46294c9!8m2!3d17.4767773!4d78.5647402!16s%2Fg%2F11l1fnp8hs!19sChIJYYgi8EebyzsRyZRi9PDycJk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G42" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H42" s="14" t="n">
-        <v>799</v>
-      </c>
-      <c r="I42" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J42" s="14" t="n">
-        <v>798</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -22043,18 +17588,6 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Kompally/data=!4m7!3m6!1s0x3bcb8547f232405d:0xe1b5a93b4c962020!8m2!3d17.5239986!4d78.4830535!16s%2Fg%2F11vzgjlgsk!19sChIJXUAy8keFyzsRICCWTDupteE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G43" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="H43" s="14" t="n">
-        <v>547</v>
-      </c>
-      <c r="I43" s="14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J43" s="14" t="n">
-        <v>547</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -22072,7 +17605,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Dadu's</t>
+          <t>Shamshabad Airport</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -22085,16 +17618,10 @@
           <t>https://www.google.com/maps/place/Dadu%27s/data=!4m7!3m6!1s0x3bcbbb64da0fd53d:0xd3947265d1327d51!8m2!3d17.2351596!4d78.4313221!16s%2Fg%2F11rx1gt4d5!19sChIJPdUP2mS7yzsRUX0y0WVylNM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G44" s="14" t="n">
+      <c r="G44" t="n">
         <v>3.9</v>
       </c>
-      <c r="H44" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="I44" s="14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J44" s="14" t="n">
+      <c r="H44" t="n">
         <v>19</v>
       </c>
     </row>
@@ -22114,7 +17641,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>Haldiram's</t>
+          <t>SBR Gateway, HITEC City</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -22127,17 +17654,11 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9344d3dd34e5:0x701ec19a3d8373e1!8m2!3d17.4472944!4d78.3784477!16s%2Fg%2F11ng76x8kt!19sChIJ5TTd00STyzsR4XODPZrBHnA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G45" s="14" t="n">
+      <c r="G45" t="n">
         <v>4.3</v>
       </c>
-      <c r="H45" s="14" t="n">
-        <v>5063</v>
-      </c>
-      <c r="I45" s="14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J45" s="14" t="n">
-        <v>7</v>
+      <c r="H45" t="n">
+        <v>5064</v>
       </c>
     </row>
     <row r="46">
@@ -22156,7 +17677,7 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Haldiram's</t>
+          <t>GVK One Mall, Banjara Hills</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -22169,17 +17690,11 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb97a0091cc689:0x5f7ee7f4961d390c!8m2!3d17.4191704!4d78.4486398!16s%2Fg%2F11n5wdprb_!19sChIJicYcCaCXyzsRDDkdlvTnfl8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G46" s="14" t="n">
+      <c r="G46" t="n">
         <v>4.6</v>
       </c>
-      <c r="H46" s="14" t="n">
+      <c r="H46" t="n">
         <v>647</v>
-      </c>
-      <c r="I46" s="14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J46" s="14" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -22198,7 +17713,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>Aero Plaza, Hyderabad</t>
+          <t>Aero Plaza, Hyderabad Airport</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -22211,17 +17726,11 @@
           <t>https://www.google.com/maps/place/Haldiram%27s+-+Aero+Plaza,+Hyderabad/data=!4m7!3m6!1s0x3bcbbbff55e0cb19:0x4268c454a214c7a3!8m2!3d17.237544!4d78.4295774!16s%2Fg%2F11ptph2_n0!19sChIJGcvgVf-7yzsRo8cUolTEaEI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G47" s="14" t="n">
+      <c r="G47" t="n">
         <v>4.8</v>
       </c>
-      <c r="H47" s="14" t="n">
-        <v>2581</v>
-      </c>
-      <c r="I47" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J47" s="14" t="n">
-        <v>2578</v>
+      <c r="H47" t="n">
+        <v>2577</v>
       </c>
     </row>
     <row r="48">
@@ -22253,16 +17762,10 @@
           <t>https://www.google.com/maps/place/Haldirams+-+International+Airport,+Hyderabad/data=!4m7!3m6!1s0x3bcbbbc5450a64d5:0x66e9f016f5a1788a!8m2!3d17.2356242!4d78.4297872!16s%2Fg%2F11y37rf_81!19sChIJ1WQKRcW7yzsRinih9Rbw6WY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G48" s="14" t="n">
+      <c r="G48" t="n">
         <v>4.8</v>
       </c>
-      <c r="H48" s="14" t="n">
-        <v>81</v>
-      </c>
-      <c r="I48" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J48" s="14" t="n">
+      <c r="H48" t="n">
         <v>81</v>
       </c>
     </row>
@@ -22282,7 +17785,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>Haldiram's</t>
+          <t>Malakpet Metro Station</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
@@ -22295,16 +17798,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb99d3156ad8a7:0x1f634101e38f8bf1!8m2!3d17.3719005!4d78.5112991!16s%2Fg%2F11sbh9wfj7!19sChIJp9hqFdOZyzsR8YuP4wFBYx8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G49" s="14" t="n">
+      <c r="G49" t="n">
         <v>4.7</v>
       </c>
-      <c r="H49" s="14" t="n">
-        <v>4615</v>
-      </c>
-      <c r="I49" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J49" s="14" t="n">
+      <c r="H49" t="n">
         <v>4615</v>
       </c>
     </row>
@@ -22324,7 +17821,7 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Begumpet</t>
+          <t>Sindhi Colony, Begumpet</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
@@ -22337,17 +17834,11 @@
           <t>https://www.google.com/maps/place/Haldiram%27s+-+Begumpet/data=!4m7!3m6!1s0x3bcb9b2fb6226879:0x792f95f1fa86db53!8m2!3d17.4433059!4d78.4779833!16s%2Fg%2F11y1vfjg9x!19sChIJeWgiti-byzsRU9uG-vGVL3k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G50" s="14" t="n">
+      <c r="G50" t="n">
         <v>4.7</v>
       </c>
-      <c r="H50" s="14" t="n">
-        <v>3299</v>
-      </c>
-      <c r="I50" s="14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J50" s="14" t="n">
-        <v>3298</v>
+      <c r="H50" t="n">
+        <v>3300</v>
       </c>
     </row>
     <row r="51">
@@ -22366,7 +17857,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Haldiram's</t>
+          <t>Inorbit Mall, Madhapur</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -22379,16 +17870,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9193207c307b:0x21e95c3d44bbc116!8m2!3d17.434484!4d78.386676!16s%2Fg%2F11mngj1_p3!19sChIJezB8IJORyzsRFsG7RD1c6SE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G51" s="14" t="n">
+      <c r="G51" t="n">
         <v>4.4</v>
       </c>
-      <c r="H51" s="14" t="n">
-        <v>783</v>
-      </c>
-      <c r="I51" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J51" s="14" t="n">
+      <c r="H51" t="n">
         <v>783</v>
       </c>
     </row>
@@ -22408,7 +17893,7 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Haldiram's</t>
+          <t>Sarath City Capital Mall, Kondapur</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -22421,16 +17906,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb93ac007ef313:0x5752fbf292af5ebc!8m2!3d17.457948!4d78.3636007!16s%2Fg%2F11h8y9pk4d!19sChIJE_N-AKyTyzsRvF6vkvL7Ulc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G52" s="14" t="n">
+      <c r="G52" t="n">
         <v>4.2</v>
       </c>
-      <c r="H52" s="14" t="n">
-        <v>1497</v>
-      </c>
-      <c r="I52" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J52" s="14" t="n">
+      <c r="H52" t="n">
         <v>1497</v>
       </c>
     </row>
@@ -22450,7 +17929,7 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>Haldiram's</t>
+          <t>Aero Plaza Food Court, Shamshabad</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
@@ -22463,16 +17942,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcbbb42526f5f6f:0xc737ba21de493937!8m2!3d17.2365531!4d78.4294807!16s%2Fg%2F11rv6lmby8!19sChIJb19vUkK7yzsRNzlJ3iG6N8c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G53" s="14" t="n">
+      <c r="G53" t="n">
         <v>4.8</v>
       </c>
-      <c r="H53" s="14" t="n">
-        <v>92</v>
-      </c>
-      <c r="I53" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J53" s="14" t="n">
+      <c r="H53" t="n">
         <v>92</v>
       </c>
     </row>
@@ -22492,7 +17965,7 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Haldiram's</t>
+          <t>DSL Virtue Mall, Uppal</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
@@ -22505,16 +17978,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb992d5300c2dd:0x78bb7b7bb178e2a5!8m2!3d17.4004116!4d78.5549239!16s%2Fg%2F11sk8g8pt2!19sChIJ3cIAUy2ZyzsRpeJ4sXt7u3g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G54" s="14" t="n">
+      <c r="G54" t="n">
         <v>4.8</v>
       </c>
-      <c r="H54" s="14" t="n">
-        <v>2811</v>
-      </c>
-      <c r="I54" s="14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J54" s="14" t="n">
+      <c r="H54" t="n">
         <v>2811</v>
       </c>
     </row>
@@ -22534,7 +18001,7 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>Haldiram's</t>
+          <t>KPHB Phase 9, Kukatpally</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
@@ -22547,17 +18014,11 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb91b0dd59094f:0x4a980e70f98df750!8m2!3d17.4840645!4d78.3890165!16s%2Fg%2F11rskcz6d0!19sChIJTwlZ3bCRyzsRUPeN-XAOmEo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G55" s="14" t="n">
+      <c r="G55" t="n">
         <v>4.3</v>
       </c>
-      <c r="H55" s="14" t="n">
-        <v>706</v>
-      </c>
-      <c r="I55" s="14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J55" s="14" t="n">
-        <v>7</v>
+      <c r="H55" t="n">
+        <v>709</v>
       </c>
     </row>
     <row r="56">
@@ -22589,16 +18050,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s+-+Gachibowli+Cloud/data=!4m7!3m6!1s0x3bcb93e8a066f96f:0xdf24b9aaf267c9cb!8m2!3d17.4396118!4d78.3630471!16s%2Fg%2F11kjk464rc!19sChIJb_lmoOiTyzsRy8ln8qq5JN8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G56" s="14" t="n">
+      <c r="G56" t="n">
         <v>4.5</v>
       </c>
-      <c r="H56" s="14" t="n">
-        <v>289</v>
-      </c>
-      <c r="I56" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J56" s="14" t="n">
+      <c r="H56" t="n">
         <v>289</v>
       </c>
     </row>
@@ -22618,7 +18073,7 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>Haldiram's</t>
+          <t>Naredi Square, Attapur</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
@@ -22631,17 +18086,11 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9771a71af1bd:0x2120c1b9f031a51!8m2!3d17.3544993!4d78.421283!16s%2Fg%2F11kpdgvt17!19sChIJvfEap3GXyzsRURoDnxsMEgI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G57" s="14" t="n">
+      <c r="G57" t="n">
         <v>4.6</v>
       </c>
-      <c r="H57" s="14" t="n">
-        <v>4513</v>
-      </c>
-      <c r="I57" s="14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J57" s="14" t="n">
-        <v>7</v>
+      <c r="H57" t="n">
+        <v>4514</v>
       </c>
     </row>
     <row r="58">
@@ -22660,7 +18109,7 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Haldiram's</t>
+          <t>Sattva NecLick Mall, Kavadiguda</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -22673,17 +18122,11 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb990fbe5eacb3:0xe000f43fccaa7968!8m2!3d17.4239975!4d78.4950257!16s%2Fg%2F11ryf8j305!19sChIJs6xevg-ZyzsRaHmqzD_0AOA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G58" s="14" t="n">
+      <c r="G58" t="n">
         <v>4.5</v>
       </c>
-      <c r="H58" s="14" t="n">
+      <c r="H58" t="n">
         <v>456</v>
-      </c>
-      <c r="I58" s="14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J58" s="14" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -22702,7 +18145,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>Haldiram's</t>
+          <t>Vinayak Towers, Bowenpally</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
@@ -22715,17 +18158,11 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9146f44ba4bd:0xa4cac9184debd8ad!8m2!3d17.4789078!4d78.4738022!16s%2Fg%2F11swvb46nc!19sChIJvaRL9EaRyzsRrdjrTRjJyqQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G59" s="14" t="n">
+      <c r="G59" t="n">
         <v>4.4</v>
       </c>
-      <c r="H59" s="14" t="n">
-        <v>3006</v>
-      </c>
-      <c r="I59" s="14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J59" s="14" t="n">
-        <v>3006</v>
+      <c r="H59" t="n">
+        <v>3008</v>
       </c>
     </row>
     <row r="60">
@@ -22744,7 +18181,7 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Haldiram's</t>
+          <t>Knowledge City, Madhapur</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
@@ -22757,17 +18194,11 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9320c77fb721:0xba3e7a353ad20f19!8m2!3d17.4344005!4d78.3823429!16s%2Fg%2F11s17v2vrz!19sChIJIbd_xyCTyzsRGQ_SOjV6Pro?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G60" s="14" t="n">
+      <c r="G60" t="n">
         <v>4.2</v>
       </c>
-      <c r="H60" s="14" t="n">
-        <v>971</v>
-      </c>
-      <c r="I60" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J60" s="14" t="n">
-        <v>970</v>
+      <c r="H60" t="n">
+        <v>969</v>
       </c>
     </row>
     <row r="61">
@@ -22799,16 +18230,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s+-+Nallagandla/data=!4m7!3m6!1s0x3bcb93827c79a5cd:0x5f3be93001f7c002!8m2!3d17.4711734!4d78.3097188!16s%2Fg%2F11y44x1nlx!19sChIJzaV5fIKTyzsRAsD3ATDpO18?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G61" s="14" t="n">
+      <c r="G61" t="n">
         <v>4.2</v>
       </c>
-      <c r="H61" s="14" t="n">
-        <v>1074</v>
-      </c>
-      <c r="I61" s="14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J61" s="14" t="n">
+      <c r="H61" t="n">
         <v>1075</v>
       </c>
     </row>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bikanervala GGN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="India BV" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="International BV" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Haldiram India" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OM Sweets India" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Other Outlets" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Bikanervala GGN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Competitors" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="India BV" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="International BV" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Haldiram India" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="OM Sweets India" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Other Outlets" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +52,14 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -82,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -140,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -178,6 +190,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -546,7 +561,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -712,6 +727,12 @@
           <t>https://share.google/Lq1yf4rveBX5BWyts</t>
         </is>
       </c>
+      <c r="G5" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>5552</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -742,6 +763,12 @@
           <t>https://share.google/5iiO04ZTn35j8E5HB</t>
         </is>
       </c>
+      <c r="G6" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>6547</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -772,6 +799,12 @@
           <t>https://share.google/iNagaqHoCbBOIvV0x</t>
         </is>
       </c>
+      <c r="G7" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>2418</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -802,6 +835,12 @@
           <t>https://share.google/S4Kwkg9xEW0S2j7a0</t>
         </is>
       </c>
+      <c r="G8" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>7195</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -832,6 +871,12 @@
           <t>https://share.google/NS8T7gwZSlKSNr3UP</t>
         </is>
       </c>
+      <c r="G9" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>3647</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -862,6 +907,12 @@
           <t>https://share.google/Xmyef4OwQmXyWCFN0</t>
         </is>
       </c>
+      <c r="G10" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>2780</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -892,6 +943,12 @@
           <t>https://share.google/6khAtgqK72w0kjN0Q</t>
         </is>
       </c>
+      <c r="G11" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>1116</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -922,6 +979,12 @@
           <t>https://share.google/CgukSORsdWkszVRvP</t>
         </is>
       </c>
+      <c r="G12" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>1107</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -952,6 +1015,12 @@
           <t>https://share.google/BNfINmH1QbNZhf7ox</t>
         </is>
       </c>
+      <c r="G13" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>2245</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -982,6 +1051,12 @@
           <t>https://share.google/LJxUW77APw08Vr9a0</t>
         </is>
       </c>
+      <c r="G14" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>2378</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1012,6 +1087,12 @@
           <t>https://share.google/LAZMqwdryXVTeQkgt</t>
         </is>
       </c>
+      <c r="G15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>2592</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1042,6 +1123,12 @@
           <t>https://share.google/lkP8lqhdoKZRzyal3</t>
         </is>
       </c>
+      <c r="G16" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>893</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -1072,6 +1159,12 @@
           <t>https://share.google/255ZPlPOiTGMhDzy0</t>
         </is>
       </c>
+      <c r="G17" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>1332</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -1102,6 +1195,12 @@
           <t>https://share.google/9TqthrgcK6VnEH9Kh</t>
         </is>
       </c>
+      <c r="G18" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>455</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -1132,6 +1231,12 @@
           <t>https://share.google/uqXvcL4esuwjgcsRz</t>
         </is>
       </c>
+      <c r="G19" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>916</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -1162,6 +1267,12 @@
           <t>https://share.google/E5KGOYYKX6YqD07hf</t>
         </is>
       </c>
+      <c r="G20" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>1098</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -1192,6 +1303,12 @@
           <t>https://share.google/ooNGpI4Ewi9Zt5t02</t>
         </is>
       </c>
+      <c r="G21" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>789</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -1222,6 +1339,12 @@
           <t>https://share.google/Z2RQtKISxQhQWQSl4</t>
         </is>
       </c>
+      <c r="G22" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>660</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -1252,6 +1375,12 @@
           <t>https://share.google/grSJuehxs8v7sVOVt</t>
         </is>
       </c>
+      <c r="G23" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>694</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -1282,6 +1411,12 @@
           <t>https://share.google/V1f6JY6CBgPW0eoIg</t>
         </is>
       </c>
+      <c r="G24" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>1425</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -1312,6 +1447,12 @@
           <t>https://share.google/r13AfGhfeAFwXti2i</t>
         </is>
       </c>
+      <c r="G25" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>706</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1337,6 +1478,12 @@
         <is>
           <t>https://share.google/e0rEvKWJDcji81RKF</t>
         </is>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -1351,7 +1498,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -1460,7 +1607,7 @@
         <v>4.8</v>
       </c>
       <c r="I3" s="14" t="n">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="4">
@@ -1538,6 +1685,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H5" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>789</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1573,6 +1726,12 @@
           <t>#4</t>
         </is>
       </c>
+      <c r="H6" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>789</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1608,6 +1767,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H7" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>660</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1643,6 +1808,12 @@
           <t>Pair 3</t>
         </is>
       </c>
+      <c r="H8" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>893</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1678,6 +1849,12 @@
           <t>#7</t>
         </is>
       </c>
+      <c r="H9" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>3266</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1713,6 +1890,12 @@
           <t>#8</t>
         </is>
       </c>
+      <c r="H10" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>3266</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1748,6 +1931,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H11" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>1425</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1783,6 +1972,12 @@
           <t>#10</t>
         </is>
       </c>
+      <c r="H12" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>1192</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -1818,6 +2013,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H13" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>755</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -1853,6 +2054,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H14" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>6811</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1888,6 +2095,12 @@
           <t>Pair 3</t>
         </is>
       </c>
+      <c r="H15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>7198</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1923,6 +2136,12 @@
           <t>#14</t>
         </is>
       </c>
+      <c r="H16" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -1958,6 +2177,12 @@
           <t>#15</t>
         </is>
       </c>
+      <c r="H17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>1823</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -1993,6 +2218,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H18" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>4504</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -2028,6 +2259,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>6547</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -2063,6 +2300,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H20" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>2780</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -2098,6 +2341,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H21" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>15765</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2133,6 +2382,12 @@
           <t>#20</t>
         </is>
       </c>
+      <c r="H22" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>15765</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -2168,6 +2423,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H23" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>10577</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -2203,6 +2464,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H24" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>12237</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -2238,6 +2505,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H25" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>2008</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -2273,6 +2546,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H26" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>848</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -2308,6 +2587,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H27" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>3647</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -2343,6 +2628,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H28" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>3606</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -2378,6 +2669,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H29" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>4872</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -2413,6 +2710,12 @@
           <t>#28</t>
         </is>
       </c>
+      <c r="H30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>1161</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -2448,6 +2751,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H31" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>2245</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -2483,6 +2792,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H32" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>1043</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -2518,6 +2833,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H33" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>5552</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -2553,6 +2874,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H34" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>1131</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -2588,6 +2915,12 @@
           <t>#33</t>
         </is>
       </c>
+      <c r="H35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>4838</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -2623,6 +2956,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H36" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>1107</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -2658,6 +2997,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H37" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>2418</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -2693,6 +3038,12 @@
           <t>#36</t>
         </is>
       </c>
+      <c r="H38" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>2418</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -2728,6 +3079,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H39" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>2592</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -2763,6 +3120,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H40" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>455</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -2798,6 +3161,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H41" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>1116</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -2833,6 +3202,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H42" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I42" s="14" t="n">
+        <v>11746</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -2868,6 +3243,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H43" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>1098</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -2903,6 +3284,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H44" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>1332</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -2938,6 +3325,12 @@
           <t>#43</t>
         </is>
       </c>
+      <c r="H45" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -2973,6 +3366,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H46" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I46" s="14" t="n">
+        <v>2008</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -3008,6 +3407,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H47" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>2378</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -3043,6 +3448,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H48" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I48" s="14" t="n">
+        <v>916</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -3078,6 +3489,12 @@
           <t>#47</t>
         </is>
       </c>
+      <c r="H49" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>1775</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -3113,6 +3530,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H50" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I50" s="14" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -3148,6 +3571,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H51" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I51" s="14" t="n">
+        <v>5934</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -3183,6 +3612,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H52" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I52" s="14" t="n">
+        <v>1566</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -3218,6 +3653,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H53" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I53" s="14" t="n">
+        <v>4658</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -3253,6 +3694,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H54" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I54" s="14" t="n">
+        <v>5290</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -3288,6 +3735,12 @@
           <t>Pair 2</t>
         </is>
       </c>
+      <c r="H55" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I55" s="14" t="n">
+        <v>706</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -3323,6 +3776,12 @@
           <t>#54</t>
         </is>
       </c>
+      <c r="H56" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I56" s="14" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -3358,6 +3817,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H57" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I57" s="14" t="n">
+        <v>1847</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -3393,6 +3858,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H58" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I58" s="14" t="n">
+        <v>4658</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -3428,6 +3899,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H59" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I59" s="14" t="n">
+        <v>264</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -3463,6 +3940,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I60" s="14" t="n">
+        <v>6559</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -3498,6 +3981,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H61" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I61" s="14" t="n">
+        <v>10702</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -3533,6 +4022,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H62" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I62" s="14" t="n">
+        <v>2067</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -3568,6 +4063,8 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H63" s="14" t="n"/>
+      <c r="I63" s="14" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -3603,6 +4100,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H64" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I64" s="14" t="n">
+        <v>1202</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -3638,6 +4141,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H65" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I65" s="14" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -3673,6 +4182,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H66" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I66" s="14" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -3708,6 +4223,12 @@
           <t>Pair 1</t>
         </is>
       </c>
+      <c r="H67" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I67" s="14" t="n">
+        <v>886</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -3742,6 +4263,12 @@
         <is>
           <t>Pair 1</t>
         </is>
+      </c>
+      <c r="H68" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I68" s="14" t="n">
+        <v>14378</v>
       </c>
     </row>
   </sheetData>
@@ -3756,7 +4283,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I206"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -3864,7 +4391,7 @@
         <v>4.3</v>
       </c>
       <c r="I3" s="14" t="n">
-        <v>2121</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -3942,6 +4469,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Liberty+Cinema+Karol+Bagh/@28.6606284,77.1876003,17z/data=!3m1!4b1!4m6!3m5!1s0x390d03326d19a899:0xd2fef34572239279!8m2!3d28.6606284!4d77.1876003!16s%2Fg%2F11m5qhcscj?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H5" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>1555</v>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="7" t="n">
@@ -3977,6 +4510,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Kalkaji+Metro/@28.5494507,77.259104,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce361d13dfecb:0x11d594dba2638f6d!8m2!3d28.5494507!4d77.259104!16s%2Fg%2F11x72l6mq2?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H6" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="n">
@@ -4012,6 +4551,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Lajpat+Nagar+Delhi/@28.5708816,77.2390955,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce252e00cf3fb:0xf48521c45d7cd156!8m2!3d28.5708816!4d77.2390955!16s%2Fg%2F1td_wzrz?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>10890</v>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="7" t="n">
@@ -4047,6 +4592,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Defence+Colony+Delhi/@28.5748765,77.2381202,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce3d5f019e1e9:0xa3e490839a38e681!8m2!3d28.5748765!4d77.2381202!16s%2Fg%2F11qb4tsxc0?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H8" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>2941</v>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="7" t="n">
@@ -4082,6 +4633,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+East+of+Kailash+Delhi/@28.5587762,77.246459,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce39ca675e7c3:0xbe857ad66d22f2bf!8m2!3d28.5587762!4d77.246459!16s%2Fg%2F11s1qvx_74?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>218</v>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="7" t="n">
@@ -4117,6 +4674,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Preet+Vihar+Delhi/@28.6392518,77.2948339,17z/data=!3m1!4b1!4m6!3m5!1s0x390cfb510ec67a93:0xfad0c088f3f91804!8m2!3d28.6392518!4d77.2948339!16s%2Fg%2F1tgnkg53?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H10" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>5139</v>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="7" t="n">
@@ -4152,6 +4715,12 @@
           <t>https://www.google.com/maps/search/BV+Connaught+Place+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H11" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="7" t="n">
@@ -4187,6 +4756,12 @@
           <t>https://www.google.com/maps/search/BV+RRM+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H12" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>340</v>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="7" t="n">
@@ -4222,6 +4797,12 @@
           <t>https://www.google.com/maps/search/BV+Mayur+Vihar+Phase+1+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H13" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>2496</v>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="7" t="n">
@@ -4257,6 +4838,12 @@
           <t>https://www.google.com/maps/search/BV+Chandni+Chowk+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H14" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="n">
@@ -4292,6 +4879,12 @@
           <t>https://www.google.com/maps/search/BV+Okhla+Industrial+Area+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H15" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="7" t="n">
@@ -4327,6 +4920,12 @@
           <t>https://www.google.com/maps/search/BV+GTK+Road+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H16" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>5554</v>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="n">
@@ -4362,6 +4961,12 @@
           <t>https://www.google.com/maps/search/BV+Punjabi+Bagh+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H17" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="7" t="n">
@@ -4397,6 +5002,12 @@
           <t>https://www.google.com/maps/search/BV+Kamla+Nagar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H18" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>1623</v>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="7" t="n">
@@ -4432,6 +5043,12 @@
           <t>https://www.google.com/maps/search/BV+Rohini+West+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>607</v>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="7" t="n">
@@ -4467,6 +5084,12 @@
           <t>https://www.google.com/maps/search/BV+Kirti+Nagar+Industrial+Area+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H20" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="7" t="n">
@@ -4502,6 +5125,12 @@
           <t>https://www.google.com/maps/search/BV+Dilshad+Garden+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H21" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="7" t="n">
@@ -4537,6 +5166,12 @@
           <t>https://www.google.com/maps/search/BV+Malviya+Nagar+Extension+Saket?hl=en</t>
         </is>
       </c>
+      <c r="H22" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I22" s="14" t="n">
+        <v>6287</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="7" t="n">
@@ -4572,6 +5207,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Dwarka+Delhi/@28.5966087,77.0417524,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1b72556cb43b:0xdd37fb0751d2b900!8m2!3d28.5966087!4d77.0417524!16s%2Fg%2F11grt4vw5b?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H23" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>6218</v>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="7" t="n">
@@ -4607,6 +5248,12 @@
           <t>https://www.google.com/maps/search/BV+Rani+Bagh+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H24" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>13126</v>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="7" t="n">
@@ -4642,6 +5289,12 @@
           <t>https://www.google.com/maps/search/BV+Janakpuri+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H25" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="7" t="n">
@@ -4677,6 +5330,12 @@
           <t>https://www.google.com/maps/search/BV+Jyoti+Nagar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H26" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>1909</v>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="7" t="n">
@@ -4712,6 +5371,12 @@
           <t>https://www.google.com/maps/search/BV+Raja+Garden+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H27" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="7" t="n">
@@ -4747,6 +5412,12 @@
           <t>https://www.google.com/maps/search/BV+Nehru+Place+Metro+Station+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H28" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>10035</v>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="7" t="n">
@@ -4782,6 +5453,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Chanakyapuri+Delhi/@28.585244,77.19149,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1d7cdedc3389:0x60798b43139c76d3!8m2!3d28.585244!4d77.19149!16s%2Fg%2F1tdvhkdv?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H29" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>8673</v>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="n">
@@ -4817,6 +5494,12 @@
           <t>https://www.google.com/maps/search/BV+Aerocity+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="H30" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>29500</v>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="7" t="n">
@@ -4852,6 +5535,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+GK-II+Savitri+Cinema+Delhi/@28.5374253,77.2389712,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce22b17e2d781:0x40c5f102209b866c!8m2!3d28.5374253!4d77.2389712!16s%2Fg%2F11cmr0t9q8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H31" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>5576</v>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="7" t="n">
@@ -4882,6 +5571,12 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+109+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="H32" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="7" t="n">
@@ -4912,6 +5607,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+57+Gurugram/@28.4161819,77.0849591,17z/data=!3m1!4b1!4m6!3m5!1s0x390d232798684757:0xb380904dacac7eed!8m2!3d28.4161819!4d77.0849591!16s%2Fg%2F11k522rkjz?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H33" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>4872</v>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="7" t="n">
@@ -4942,6 +5643,12 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+14+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="H34" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I34" s="14" t="n">
+        <v>893</v>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="7" t="n">
@@ -4972,6 +5679,12 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+99+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="H35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="7" t="n">
@@ -5002,6 +5715,12 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+24+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="H36" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="7" t="n">
@@ -5032,6 +5751,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+The+Esplanade+Mall+Sector+37+Gurugram/@28.4538074,76.9928507,17z/data=!3m1!4b1!4m6!3m5!1s0x390d171587c41467:0x4070a84c531d04ce!8m2!3d28.4538074!4d76.9928507!16s%2Fg%2F11tggmn3j8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H37" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>1332</v>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="7" t="n">
@@ -5062,6 +5787,12 @@
           <t>https://www.google.com/maps/search/BV+Cyber+Park+Udhyog+Vihar+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="H38" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <v>2688</v>
+      </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="7" t="n">
@@ -5092,6 +5823,12 @@
           <t>https://www.google.com/maps/search/BV+Foodcourt+Opulent+Mall+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="H39" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>23004</v>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="7" t="n">
@@ -5122,6 +5859,12 @@
           <t>https://www.google.com/maps/search/BV+JMD+Empire+Square+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="H40" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>571</v>
+      </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="7" t="n">
@@ -5152,6 +5895,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+62+Gurugram/@28.4014616,77.0852188,17z/data=!3m1!4b1!4m6!3m5!1s0x390d23dcf278418d:0x4d1e11be0af4d661!8m2!3d28.4014616!4d77.0852188!16s%2Fg%2F11h7qrpfv4?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H41" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>455</v>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="7" t="n">
@@ -5182,6 +5931,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+15+Gurugram/@28.4578375,77.0443773,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1902973194b5:0x7d02f6d383fb8a58!8m2!3d28.4578375!4d77.0443773!16s%2Fg%2F11trqkrhym?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H42" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I42" s="14" t="n">
+        <v>2418</v>
+      </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="7" t="n">
@@ -5212,6 +5967,12 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+95+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="H43" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="7" t="n">
@@ -5242,6 +6003,12 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+54+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="H44" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <v>292</v>
+      </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="7" t="n">
@@ -5272,6 +6039,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+67+Gurugram/@28.3897015,77.0674498,17z/data=!3m1!4b1!4m6!3m5!1s0x390d23d7d3976715:0xb8dc58e2f64d1b2e!8m2!3d28.3897015!4d77.0674498!16s%2Fg%2F11h7ksct1w?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H45" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>1107</v>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="7" t="n">
@@ -5302,6 +6075,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sohna+Road+Gurugram/@28.4253629,77.0390099,17z/data=!3m1!4b1!4m6!3m5!1s0x390d1875d4418c91:0x3b4b144484bee44a!8m2!3d28.4253629!4d77.0390099!16s%2Fg%2F1wj_4f0r?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H46" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I46" s="14" t="n">
+        <v>7200</v>
+      </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="7" t="n">
@@ -5332,6 +6111,12 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+29+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="H47" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>3369</v>
+      </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="7" t="n">
@@ -5362,6 +6147,12 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+86+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="H48" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I48" s="14" t="n">
+        <v>3647</v>
+      </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="7" t="n">
@@ -5392,6 +6183,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+80+Gurugram/@28.3766192,76.9593435,17z/data=!3m1!4b1!4m6!3m5!1s0x390d3da30c57ee59:0x82d80073b91470fc!8m2!3d28.3766192!4d76.9593435!16s%2Fg%2F11fhh4ykm5?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H49" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>2378</v>
+      </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="7" t="n">
@@ -5422,6 +6219,12 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+62+Noida?hl=en</t>
         </is>
       </c>
+      <c r="H50" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I50" s="14" t="n">
+        <v>5595</v>
+      </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="7" t="n">
@@ -5452,6 +6255,12 @@
           <t>https://www.google.com/maps/search/BV+Omaxe+NRI+Greater+Noida?hl=en</t>
         </is>
       </c>
+      <c r="H51" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I51" s="14" t="n">
+        <v>1007</v>
+      </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="7" t="n">
@@ -5482,6 +6291,12 @@
           <t>https://www.google.com/maps/search/BV+Knowledge+Park+3+Greater+Noida?hl=en</t>
         </is>
       </c>
+      <c r="H52" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I52" s="14" t="n">
+        <v>1012</v>
+      </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="7" t="n">
@@ -5512,6 +6327,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Sector+18+Noida/@28.5715738,77.3246799,17z/data=!3m1!4b1!4m6!3m5!1s0x390ce44edd59cf9b:0x7abd947a6a0578bf!8m2!3d28.5715738!4d77.3246799!16s%2Fg%2F124sxkwj8?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H53" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I53" s="14" t="n">
+        <v>9649</v>
+      </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="7" t="n">
@@ -5542,6 +6363,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Gaur+City+Mall+Greater+Noida?hl=en</t>
         </is>
       </c>
+      <c r="H54" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I54" s="14" t="n">
+        <v>796</v>
+      </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="7" t="n">
@@ -5572,6 +6399,12 @@
           <t>https://www.google.com/maps/search/BV+Krishna+Apsara+Plaza+Noida?hl=en</t>
         </is>
       </c>
+      <c r="H55" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I55" s="14" t="n">
+        <v>298</v>
+      </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="7" t="n">
@@ -5602,6 +6435,12 @@
           <t>https://www.google.com/maps/search/BV+URBTCH+Sec+-+153+Noida?hl=en</t>
         </is>
       </c>
+      <c r="H56" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I56" s="14" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="7" t="n">
@@ -5632,6 +6471,12 @@
           <t>https://share.google/ROkTSrwbJf84BzhPA</t>
         </is>
       </c>
+      <c r="H57" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I57" s="14" t="n">
+        <v>439</v>
+      </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="7" t="n">
@@ -5662,6 +6507,12 @@
           <t>https://share.google/zdFAyEbaRbQ5k484p</t>
         </is>
       </c>
+      <c r="H58" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I58" s="14" t="n">
+        <v>203</v>
+      </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="7" t="n">
@@ -5692,6 +6543,12 @@
           <t>https://share.google/Lb3nqjJMTsd4B288R</t>
         </is>
       </c>
+      <c r="H59" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I59" s="14" t="n">
+        <v>658</v>
+      </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="7" t="n">
@@ -5722,6 +6579,12 @@
           <t>https://share.google/UhwDLEldKfKeeOvuF</t>
         </is>
       </c>
+      <c r="H60" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I60" s="14" t="n">
+        <v>361</v>
+      </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="7" t="n">
@@ -5752,6 +6615,12 @@
           <t>https://share.google/y3qxY9okUtRY9qT5G</t>
         </is>
       </c>
+      <c r="H61" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I61" s="14" t="n">
+        <v>2922</v>
+      </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="7" t="n">
@@ -5782,6 +6651,12 @@
           <t>https://share.google/6IsINvdHSLIIHkIhQ</t>
         </is>
       </c>
+      <c r="H62" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I62" s="14" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="7" t="n">
@@ -5812,6 +6687,12 @@
           <t>https://share.google/dyEWjeSFB5bMuBtCr</t>
         </is>
       </c>
+      <c r="H63" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I63" s="14" t="n">
+        <v>9259</v>
+      </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="7" t="n">
@@ -5842,6 +6723,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Gaur+Biz+Park+Gaziabad?hl=en</t>
         </is>
       </c>
+      <c r="H64" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I64" s="14" t="n">
+        <v>1007</v>
+      </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="7" t="n">
@@ -5872,6 +6759,12 @@
           <t>https://www.google.com/maps/place/Plot+No.+12,+Bikanervala+%7C+Rajendra+Nagar,+Sahibabad,,+Rajender+Nagar,+Sector+5,+Rajendra+Nagar,+Sahibabad,+Ghaziabad,+Uttar+Pradesh+201005/@28.6780951,77.3592434,16z/data=!4m6!3m5!1s0x390cfa8b972e5a11:0x42944ce5f6223fbd!8m2!3d28.6780951!4d77.3592434!16s%2Fg%2F11b6gg2nvh?hl=en&amp;g_ep=Eg1tbF8yMDI2MDkyMl8wIJvbDyoASAJQAg%3D%3D</t>
         </is>
       </c>
+      <c r="H65" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I65" s="14" t="n">
+        <v>3845</v>
+      </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="7" t="n">
@@ -5902,6 +6795,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Choudhary+More+Ghaziabad/@28.656764,77.4343384,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf1cfc180871d:0x5aa84735b213aa6a!8m2!3d28.656764!4d77.4343384!16s%2Fg%2F11clr_s4v9?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H66" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I66" s="14" t="n">
+        <v>4138</v>
+      </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="7" t="n">
@@ -5932,6 +6831,12 @@
           <t>https://www.google.com/maps/search/BV+Indirapuram+Gaziabad?hl=en</t>
         </is>
       </c>
+      <c r="H67" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I67" s="14" t="n">
+        <v>10369</v>
+      </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="7" t="n">
@@ -5962,6 +6867,12 @@
           <t>https://www.google.com/maps/search/BV+Raj+Nagar+Extension+Gaziabad?hl=en</t>
         </is>
       </c>
+      <c r="H68" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I68" s="14" t="n">
+        <v>4304</v>
+      </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="7" t="n">
@@ -5992,6 +6903,12 @@
           <t>https://www.google.com/maps/search/BV+Vasundhara+Gaziabad?hl=en</t>
         </is>
       </c>
+      <c r="H69" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I69" s="14" t="n">
+        <v>2214</v>
+      </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="7" t="n">
@@ -6022,6 +6939,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+KW+Delhi+6/@28.696452,77.4352816,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf15e12b7409f:0x21ba0dd8e12c1453!8m2!3d28.696452!4d77.4352816!16s%2Fg%2F11jzgk44vp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H70" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I70" s="14" t="n">
+        <v>280</v>
+      </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="7" t="n">
@@ -6052,6 +6975,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Modinagar/@28.8133765,77.5519765,17z/data=!3m1!4b1!4m6!3m5!1s0x390cf5b71abce455:0xfc2ef5a0bb38f92!8m2!3d28.8133765!4d77.5519765!16s%2Fg%2F11ghftj4c1?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H71" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I71" s="14" t="n">
+        <v>6142</v>
+      </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="7" t="n">
@@ -6082,6 +7011,12 @@
           <t>https://www.google.com/maps/search/BV+Lal+Kuan+Gaziabad?hl=en</t>
         </is>
       </c>
+      <c r="H72" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I72" s="14" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="7" t="n">
@@ -6112,6 +7047,12 @@
           <t>https://maps.app.goo.gl/KegUZzVNtBCzn3zC9</t>
         </is>
       </c>
+      <c r="H73" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I73" s="14" t="n">
+        <v>1109</v>
+      </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="7" t="n">
@@ -6142,6 +7083,12 @@
           <t>https://goo.gl/maps/uzteMjzzkSa3PjHcA</t>
         </is>
       </c>
+      <c r="H74" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I74" s="14" t="n">
+        <v>9514</v>
+      </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="7" t="n">
@@ -6172,6 +7119,12 @@
           <t>https://goo.gl/maps/o8aMcy4bzjEiMSc88</t>
         </is>
       </c>
+      <c r="H75" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I75" s="14" t="n">
+        <v>16972</v>
+      </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="7" t="n">
@@ -6202,6 +7155,12 @@
           <t>https://goo.gl/maps/LeLGBiAqApZipLR2A</t>
         </is>
       </c>
+      <c r="H76" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I76" s="14" t="n">
+        <v>8561</v>
+      </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="7" t="n">
@@ -6232,6 +7191,12 @@
           <t>https://www.google.com/maps/place/Bikanervala/@26.7851067,80.9918353,17z/data=!3m1!4b1!4m6!3m5!1s0x399be30647fd426d:0xd01584f16db3efe3!8m2!3d26.7851067!4d80.9918353!16s%2Fg%2F11jsr96pd9?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H77" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I77" s="14" t="n">
+        <v>2473</v>
+      </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="7" t="n">
@@ -6262,6 +7227,12 @@
           <t>https://www.google.com/maps/search/BV+Fun+Republik+Lucknow?hl=en</t>
         </is>
       </c>
+      <c r="H78" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I78" s="14" t="n">
+        <v>10943</v>
+      </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="7" t="n">
@@ -6292,6 +7263,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+%7C+Emerald+Mall+Lucknow/@26.7879677,80.9106156,17z/data=!3m1!4b1!4m6!3m5!1s0x399bfda33d9b4ed1:0x4bc0f33320d7156b!8m2!3d26.7879677!4d80.9106156!16s%2Fg%2F11vs2f1qpf?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="H79" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I79" s="14" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="7" t="n">
@@ -6322,6 +7299,12 @@
           <t>https://www.google.com/maps/search/BV+Vijay+Tower+Lucknow?hl=en</t>
         </is>
       </c>
+      <c r="H80" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I80" s="14" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="7" t="n">
@@ -6352,6 +7335,16 @@
           <t>https://www.google.com/maps/search/BV+Indira+Nagar+Lucknow+%28Closed%29?hl=en</t>
         </is>
       </c>
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="7" t="n">
@@ -6382,6 +7375,12 @@
           <t>https://www.google.com/maps/search/BV+Vibhuti+Khand+Gomti+Nagar+Lucknow?hl=en</t>
         </is>
       </c>
+      <c r="H82" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I82" s="14" t="n">
+        <v>1445</v>
+      </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="7" t="n">
@@ -6412,6 +7411,12 @@
           <t>https://www.google.com/maps/search/BV+Sec+-+12+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="H83" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I83" s="14" t="n">
+        <v>1741</v>
+      </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="7" t="n">
@@ -6442,6 +7447,12 @@
           <t>https://www.google.com/maps/search/BV+Mansha+Vega+Street+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="H84" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I84" s="14" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="7" t="n">
@@ -6472,6 +7483,12 @@
           <t>https://www.google.com/maps/search/BV+Mandi+Dabwali+Road+Bhatinda?hl=en</t>
         </is>
       </c>
+      <c r="H85" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I85" s="14" t="n">
+        <v>3952</v>
+      </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="7" t="n">
@@ -6502,6 +7519,12 @@
           <t>https://www.google.com/maps/search/BV+Park+Penorama+Colony+Bhatinda?hl=en</t>
         </is>
       </c>
+      <c r="H86" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I86" s="14" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="7" t="n">
@@ -6532,6 +7555,12 @@
           <t>https://www.google.com/maps/search/BV+Nungabakkam+Chennai?hl=en</t>
         </is>
       </c>
+      <c r="H87" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I87" s="14" t="n">
+        <v>4507</v>
+      </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="7" t="n">
@@ -6562,6 +7591,12 @@
           <t>https://www.google.com/maps/search/BV+Chennai+Kilpauk?hl=en</t>
         </is>
       </c>
+      <c r="H88" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I88" s="14" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="7" t="n">
@@ -6592,6 +7627,12 @@
           <t>https://www.google.com/maps/search/BV+Modipuram+Meerut?hl=en</t>
         </is>
       </c>
+      <c r="H89" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I89" s="14" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="7" t="n">
@@ -6622,6 +7663,12 @@
           <t>https://www.google.com/maps/search/BV+Harsh+Commercial+Park+Meerut?hl=en</t>
         </is>
       </c>
+      <c r="H90" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I90" s="14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="7" t="n">
@@ -6652,6 +7699,12 @@
           <t>https://www.google.com/maps/search/BV+Kundli+Sonipat?hl=en</t>
         </is>
       </c>
+      <c r="H91" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I91" s="14" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="7" t="n">
@@ -6682,6 +7735,12 @@
           <t>https://www.google.com/maps/search/BV+Bhelupura+Varanasi?hl=en</t>
         </is>
       </c>
+      <c r="H92" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I92" s="14" t="n">
+        <v>388</v>
+      </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="7" t="n">
@@ -6712,6 +7771,12 @@
           <t>https://www.google.com/maps/search/BV+Global+Business+Park+Zirakpur?hl=en</t>
         </is>
       </c>
+      <c r="H93" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I93" s="14" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="7" t="n">
@@ -6742,6 +7807,12 @@
           <t>https://www.google.com/maps/search/BV+Pakhowal+Road+Ludhiana?hl=en</t>
         </is>
       </c>
+      <c r="H94" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I94" s="14" t="n">
+        <v>7200</v>
+      </c>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="7" t="n">
@@ -6772,6 +7843,12 @@
           <t>https://www.google.com/maps/search/BV+Tonk+Road+Jaipur?hl=en</t>
         </is>
       </c>
+      <c r="H95" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I95" s="14" t="n">
+        <v>7498</v>
+      </c>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="7" t="n">
@@ -6802,6 +7879,12 @@
           <t>https://www.google.com/maps/search/BV+Model+Town+Jalandhar?hl=en</t>
         </is>
       </c>
+      <c r="H96" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I96" s="14" t="n">
+        <v>2838</v>
+      </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="7" t="n">
@@ -6832,6 +7915,12 @@
           <t>https://www.google.com/maps/search/BV+C+Plaza+Mohali?hl=en</t>
         </is>
       </c>
+      <c r="H97" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I97" s="14" t="n">
+        <v>359</v>
+      </c>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="7" t="n">
@@ -6862,6 +7951,12 @@
           <t>https://www.google.com/maps/search/BV+Pacific+Mall+Rajpur+Road+Dehradun?hl=en</t>
         </is>
       </c>
+      <c r="H98" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I98" s="14" t="n">
+        <v>42235</v>
+      </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="7" t="n">
@@ -6892,6 +7987,12 @@
           <t>https://www.google.com/maps/search/BV+Lashkar+Gwalier?hl=en</t>
         </is>
       </c>
+      <c r="H99" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I99" s="14" t="n">
+        <v>310</v>
+      </c>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="7" t="n">
@@ -6922,6 +8023,12 @@
           <t>https://www.google.com/maps/search/BV+Avenue+37+Bahadurgarh?hl=en</t>
         </is>
       </c>
+      <c r="H100" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I100" s="14" t="n">
+        <v>344</v>
+      </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="7" t="n">
@@ -6952,6 +8059,12 @@
           <t>https://www.google.com/maps/search/BV+Tehsil+Deoband+Saharanpur?hl=en</t>
         </is>
       </c>
+      <c r="H101" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I101" s="14" t="n">
+        <v>289</v>
+      </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="7" t="n">
@@ -6982,6 +8095,12 @@
           <t>https://www.google.com/maps/search/BV+Barara+Ambala?hl=en</t>
         </is>
       </c>
+      <c r="H102" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I102" s="14" t="n">
+        <v>7201</v>
+      </c>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="7" t="n">
@@ -7012,6 +8131,12 @@
           <t>https://www.google.com/maps/search/BV+Hanuman+Garh+Road+Sri+GnagaNagar?hl=en</t>
         </is>
       </c>
+      <c r="H103" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I103" s="14" t="n">
+        <v>861</v>
+      </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="7" t="n">
@@ -7042,6 +8167,12 @@
           <t>https://www.google.com/maps/search/BV+Nabha+Gate+Road+Sangrur?hl=en</t>
         </is>
       </c>
+      <c r="H104" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I104" s="14" t="n">
+        <v>428</v>
+      </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="7" t="n">
@@ -7072,6 +8203,12 @@
           <t>https://www.google.com/maps/search/BV+Jayanagar+Bengaluru?hl=en</t>
         </is>
       </c>
+      <c r="H105" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I105" s="14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="7" t="n">
@@ -7102,6 +8239,12 @@
           <t>https://www.google.com/maps/search/BV+Village+Quatabpur+Hisar?hl=en</t>
         </is>
       </c>
+      <c r="H106" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I106" s="14" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="7" t="n">
@@ -7132,6 +8275,12 @@
           <t>https://www.google.com/maps/search/BV+Akhnoor+Jammu?hl=en</t>
         </is>
       </c>
+      <c r="H107" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I107" s="14" t="n">
+        <v>4255</v>
+      </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="7" t="n">
@@ -7162,6 +8311,12 @@
           <t>https://www.google.com/maps/search/BV+Model+Town+Rohtak?hl=en</t>
         </is>
       </c>
+      <c r="H108" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I108" s="14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="7" t="n">
@@ -7192,6 +8347,12 @@
           <t>https://www.google.com/maps/search/BV+NH+27+Abu+Road+Rajasthan?hl=en</t>
         </is>
       </c>
+      <c r="H109" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I109" s="14" t="n">
+        <v>1425</v>
+      </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="7" t="n">
@@ -7222,6 +8383,12 @@
           <t>https://goo.gl/maps/X2g2z7mRg9ZU92F2A</t>
         </is>
       </c>
+      <c r="H110" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I110" s="14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="7" t="n">
@@ -7252,6 +8419,12 @@
           <t>https://maps.app.goo.gl/37R2ESFo5oS8p2em7</t>
         </is>
       </c>
+      <c r="H111" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I111" s="14" t="n">
+        <v>866</v>
+      </c>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="7" t="n">
@@ -7287,6 +8460,12 @@
           <t>https://goo.gl/maps/iMtbXqwaWUDYu8xf6</t>
         </is>
       </c>
+      <c r="H112" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I112" s="14" t="n">
+        <v>8411</v>
+      </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="7" t="n">
@@ -7322,6 +8501,12 @@
           <t>https://goo.gl/maps/CxUCASbc6Zf2TocB8</t>
         </is>
       </c>
+      <c r="H113" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I113" s="14" t="n">
+        <v>4900</v>
+      </c>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="7" t="n">
@@ -7357,6 +8542,12 @@
           <t>https://goo.gl/maps/ATskvznck1gui7f6A</t>
         </is>
       </c>
+      <c r="H114" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I114" s="14" t="n">
+        <v>3365</v>
+      </c>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="7" t="n">
@@ -7392,6 +8583,12 @@
           <t>https://goo.gl/maps/KbVjkRcx6jMVdGQW7</t>
         </is>
       </c>
+      <c r="H115" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I115" s="14" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="7" t="n">
@@ -7427,6 +8624,12 @@
           <t>https://goo.gl/maps/AmjQDTZCHpP9PfrB6</t>
         </is>
       </c>
+      <c r="H116" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I116" s="14" t="n">
+        <v>8673</v>
+      </c>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="7" t="n">
@@ -7462,6 +8665,12 @@
           <t>https://maps.app.goo.gl/zcrubnk5RZ3jKg5A8</t>
         </is>
       </c>
+      <c r="H117" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I117" s="14" t="n">
+        <v>11856</v>
+      </c>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="7" t="n">
@@ -7497,6 +8706,12 @@
           <t>https://goo.gl/maps/dqHX14AbaKcSsV5i7</t>
         </is>
       </c>
+      <c r="H118" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I118" s="14" t="n">
+        <v>2780</v>
+      </c>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="7" t="n">
@@ -7532,6 +8747,12 @@
           <t>https://maps.app.goo.gl/NbSW2GgWBiTTWokQ6</t>
         </is>
       </c>
+      <c r="H119" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I119" s="14" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="7" t="n">
@@ -7567,6 +8788,12 @@
           <t>https://maps.app.goo.gl/x8i3gr7m9LKKvijw9</t>
         </is>
       </c>
+      <c r="H120" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I120" s="14" t="n">
+        <v>464</v>
+      </c>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="7" t="n">
@@ -7602,6 +8829,12 @@
           <t>https://maps.app.goo.gl/pNH5r5yxdP3DTRfj9</t>
         </is>
       </c>
+      <c r="H121" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I121" s="14" t="n">
+        <v>776</v>
+      </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="7" t="n">
@@ -7637,6 +8870,12 @@
           <t>https://maps.app.goo.gl/Lt1LVynLWcuu8eXy5</t>
         </is>
       </c>
+      <c r="H122" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I122" s="14" t="n">
+        <v>169</v>
+      </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="7" t="n">
@@ -7672,6 +8911,12 @@
           <t>https://maps.app.goo.gl/G7HFA2zCPT3Co2BU9</t>
         </is>
       </c>
+      <c r="H123" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I123" s="14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="7" t="n">
@@ -7707,6 +8952,12 @@
           <t>https://maps.app.goo.gl/9LmyBZrg48UVmmmM7</t>
         </is>
       </c>
+      <c r="H124" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I124" s="14" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="7" t="n">
@@ -7742,6 +8993,12 @@
           <t>https://maps.app.goo.gl/mnuCcmi4TeeNHkNv7</t>
         </is>
       </c>
+      <c r="H125" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I125" s="14" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="7" t="n">
@@ -7777,6 +9034,12 @@
           <t>https://maps.app.goo.gl/hWXz3RWjo8iBq8vC6</t>
         </is>
       </c>
+      <c r="H126" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I126" s="14" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="7" t="n">
@@ -7812,6 +9075,12 @@
           <t>https://goo.gl/maps/EXwmxHqPpSwBfAn9A</t>
         </is>
       </c>
+      <c r="H127" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I127" s="14" t="n">
+        <v>4191</v>
+      </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="7" t="n">
@@ -7847,6 +9116,12 @@
           <t>https://maps.app.goo.gl/Qr7ipPaWf38VtzRZA</t>
         </is>
       </c>
+      <c r="H128" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I128" s="14" t="n">
+        <v>289</v>
+      </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="7" t="n">
@@ -7877,6 +9152,12 @@
           <t>https://goo.gl/maps/xV9F7hCGssGURhmZ9</t>
         </is>
       </c>
+      <c r="H129" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I129" s="14" t="n">
+        <v>4228</v>
+      </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="7" t="n">
@@ -7907,6 +9188,12 @@
           <t>https://maps.app.goo.gl/je2V2Z8h1Pu8a2Vz8</t>
         </is>
       </c>
+      <c r="H130" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I130" s="14" t="n">
+        <v>660</v>
+      </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="7" t="n">
@@ -7937,6 +9224,12 @@
           <t>https://maps.app.goo.gl/12vCQuxEBD9PWE8F8</t>
         </is>
       </c>
+      <c r="H131" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I131" s="14" t="n">
+        <v>789</v>
+      </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="7" t="n">
@@ -7967,6 +9260,12 @@
           <t>https://maps.app.goo.gl/ucnkKCkPLq9GUTEL8</t>
         </is>
       </c>
+      <c r="H132" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I132" s="14" t="n">
+        <v>706</v>
+      </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="7" t="n">
@@ -7997,6 +9296,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Elan+Epic+Sec-70+Gurguram+Gurugram?hl=en</t>
         </is>
       </c>
+      <c r="H133" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I133" s="14" t="n">
+        <v>1425</v>
+      </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="7" t="n">
@@ -8027,6 +9332,12 @@
           <t>https://maps.app.goo.gl/CWNkDPq7wK3DihFMA</t>
         </is>
       </c>
+      <c r="H134" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I134" s="14" t="n">
+        <v>694</v>
+      </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="7" t="n">
@@ -8057,6 +9368,12 @@
           <t>https://maps.app.goo.gl/uYECDKn6odyrrTA96</t>
         </is>
       </c>
+      <c r="H135" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I135" s="14" t="n">
+        <v>377</v>
+      </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="7" t="n">
@@ -8087,6 +9404,12 @@
           <t>https://maps.app.goo.gl/uYECDKn6odyrrTA96</t>
         </is>
       </c>
+      <c r="H136" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I136" s="14" t="n">
+        <v>377</v>
+      </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="7" t="n">
@@ -8117,6 +9440,12 @@
           <t>https://goo.gl/maps/KTGuqx8wJFbQL3V48</t>
         </is>
       </c>
+      <c r="H137" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I137" s="14" t="n">
+        <v>5277</v>
+      </c>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="7" t="n">
@@ -8147,6 +9476,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Prahalad+Nagar%2C+Ahmedabad%2C+Gujarat+380051+Ahmedabad?hl=en</t>
         </is>
       </c>
+      <c r="H138" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I138" s="14" t="n">
+        <v>2545</v>
+      </c>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="7" t="n">
@@ -8177,6 +9512,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Nehru+Nagar%2C+Ahmedabad%2C+Gujarat+380015+Ahmedabad?hl=en</t>
         </is>
       </c>
+      <c r="H139" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I139" s="14" t="n">
+        <v>3197</v>
+      </c>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="7" t="n">
@@ -8207,6 +9548,12 @@
           <t>https://goo.gl/maps/32mqLYxSNUxQfjDy5</t>
         </is>
       </c>
+      <c r="H140" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I140" s="14" t="n">
+        <v>1445</v>
+      </c>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="7" t="n">
@@ -8237,6 +9584,12 @@
           <t>https://maps.app.goo.gl/723xYbZvfAGXSj5g7</t>
         </is>
       </c>
+      <c r="H141" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I141" s="14" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="7" t="n">
@@ -8267,6 +9620,12 @@
           <t>https://maps.app.goo.gl/3WvgLWd5QSehGjEH6</t>
         </is>
       </c>
+      <c r="H142" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I142" s="14" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="7" t="n">
@@ -8297,6 +9656,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Fatehabad+Rd%2C+opposite+Hotel+ITC+Mughal%2C+Tajganj%2C+Agra%2C+Uttar+Pradesh+282001+Agra?hl=en</t>
         </is>
       </c>
+      <c r="H143" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I143" s="14" t="n">
+        <v>4194</v>
+      </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="7" t="n">
@@ -8327,6 +9692,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Near+tulsi+cinema%2C+Kripal+colony%2C+Sanjay+nagar%2C+pashupati+colony%2C+khandari%2C+Agra%2C+Agra?hl=en</t>
         </is>
       </c>
+      <c r="H144" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I144" s="14" t="n">
+        <v>4587</v>
+      </c>
     </row>
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="7" t="n">
@@ -8357,6 +9728,12 @@
           <t>https://goo.gl/maps/uYKxT37zNmYp3MU78</t>
         </is>
       </c>
+      <c r="H145" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I145" s="14" t="n">
+        <v>1530</v>
+      </c>
     </row>
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="7" t="n">
@@ -8387,6 +9764,12 @@
           <t>https://maps.app.goo.gl/q1cas4PoB2wq7y218</t>
         </is>
       </c>
+      <c r="H146" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I146" s="14" t="n">
+        <v>3952</v>
+      </c>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="7" t="n">
@@ -8417,6 +9800,12 @@
           <t>https://maps.app.goo.gl/9korfoaVEuCnsttx9</t>
         </is>
       </c>
+      <c r="H147" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I147" s="14" t="n">
+        <v>2953</v>
+      </c>
     </row>
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="7" t="n">
@@ -8447,6 +9836,12 @@
           <t>https://maps.app.goo.gl/wyFeTmbGR45kCHRJ8</t>
         </is>
       </c>
+      <c r="H148" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I148" s="14" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="7" t="n">
@@ -8477,6 +9872,12 @@
           <t>https://maps.app.goo.gl/NuHBsab6Z71CqfnJ7</t>
         </is>
       </c>
+      <c r="H149" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I149" s="14" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="7" t="n">
@@ -8507,6 +9908,12 @@
           <t>https://maps.app.goo.gl/szumsxsq2FSh8P7h7</t>
         </is>
       </c>
+      <c r="H150" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I150" s="14" t="n">
+        <v>2595</v>
+      </c>
     </row>
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="7" t="n">
@@ -8537,6 +9944,12 @@
           <t>https://goo.gl/maps/B4CK1TxcuJf2gwGV8</t>
         </is>
       </c>
+      <c r="H151" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I151" s="14" t="n">
+        <v>3845</v>
+      </c>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="7" t="n">
@@ -8567,6 +9980,12 @@
           <t>https://goo.gl/maps/4pJwnbEcxGBVBWZi6</t>
         </is>
       </c>
+      <c r="H152" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I152" s="14" t="n">
+        <v>510</v>
+      </c>
     </row>
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="7" t="n">
@@ -8597,6 +10016,12 @@
           <t>https://goo.gl/maps/gYRQUULU5t9wi18S8</t>
         </is>
       </c>
+      <c r="H153" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I153" s="14" t="n">
+        <v>9259</v>
+      </c>
     </row>
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="7" t="n">
@@ -8627,6 +10052,12 @@
           <t>https://goo.gl/maps/arsjABkMQUNEYFgF6</t>
         </is>
       </c>
+      <c r="H154" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I154" s="14" t="n">
+        <v>9246</v>
+      </c>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="7" t="n">
@@ -8657,6 +10088,12 @@
           <t>https://goo.gl/maps/N7a66uNDkDcDgctb6</t>
         </is>
       </c>
+      <c r="H155" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I155" s="14" t="n">
+        <v>4304</v>
+      </c>
     </row>
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="7" t="n">
@@ -8687,6 +10124,12 @@
           <t>https://maps.app.goo.gl/LkRXmhWrNkmb4bfQ9</t>
         </is>
       </c>
+      <c r="H156" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I156" s="14" t="n">
+        <v>198</v>
+      </c>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="7" t="n">
@@ -8717,6 +10160,12 @@
           <t>https://maps.app.goo.gl/fdpmtgiFnnmBpBhZ6</t>
         </is>
       </c>
+      <c r="H157" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I157" s="14" t="n">
+        <v>585</v>
+      </c>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="7" t="n">
@@ -8747,6 +10196,12 @@
           <t>https://maps.app.goo.gl/LJVSZyoMxAU6wMvDA</t>
         </is>
       </c>
+      <c r="H158" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I158" s="14" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="7" t="n">
@@ -8777,6 +10232,12 @@
           <t>https://maps.app.goo.gl/AjzLtZx8muxVP8NEA</t>
         </is>
       </c>
+      <c r="H159" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I159" s="14" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="160" ht="20" customHeight="1">
       <c r="A160" s="7" t="n">
@@ -8807,6 +10268,12 @@
           <t>https://maps.app.goo.gl/6HL3Gohkz7u4cYQa7</t>
         </is>
       </c>
+      <c r="H160" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I160" s="14" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="7" t="n">
@@ -8837,6 +10304,12 @@
           <t>https://maps.app.goo.gl/oWmDoNJLbdvENyak7</t>
         </is>
       </c>
+      <c r="H161" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I161" s="14" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="7" t="n">
@@ -8867,6 +10340,12 @@
           <t>https://maps.app.goo.gl/FHgqWFsLmanWmdpD7</t>
         </is>
       </c>
+      <c r="H162" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I162" s="14" t="n">
+        <v>1944</v>
+      </c>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="7" t="n">
@@ -8897,6 +10376,12 @@
           <t>https://maps.app.goo.gl/xJrmieBbKX6bUuSV7</t>
         </is>
       </c>
+      <c r="H163" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I163" s="14" t="n">
+        <v>1698</v>
+      </c>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="7" t="n">
@@ -8927,6 +10412,12 @@
           <t>https://goo.gl/maps/aNahaC7CwDFV5kyi9</t>
         </is>
       </c>
+      <c r="H164" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I164" s="14" t="n">
+        <v>9349</v>
+      </c>
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="7" t="n">
@@ -8957,6 +10448,12 @@
           <t>https://maps.app.goo.gl/jWbbnvbERR8sWwr67</t>
         </is>
       </c>
+      <c r="H165" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I165" s="14" t="n">
+        <v>1092</v>
+      </c>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="7" t="n">
@@ -8987,6 +10484,12 @@
           <t>https://goo.gl/maps/fHakJ7u4WEXt3Ck36</t>
         </is>
       </c>
+      <c r="H166" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I166" s="14" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="7" t="n">
@@ -9017,6 +10520,12 @@
           <t>https://goo.gl/maps/apShSYj546Yn2Sb77</t>
         </is>
       </c>
+      <c r="H167" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I167" s="14" t="n">
+        <v>3361</v>
+      </c>
     </row>
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="7" t="n">
@@ -9047,6 +10556,12 @@
           <t>https://maps.app.goo.gl/V9dCfncbjgbxiVmu8</t>
         </is>
       </c>
+      <c r="H168" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I168" s="14" t="n">
+        <v>849</v>
+      </c>
     </row>
     <row r="169" ht="20" customHeight="1">
       <c r="A169" s="7" t="n">
@@ -9077,6 +10592,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+BX-143%2C+Royal+Plaza%2C+Plot+No.+224%2C+Model+House+Rd%2C+Tej+Mohan+Nagar%2C+Basti+Sheikh%2C+Dashmesh+Nagar%2C+Jalandhar%2C+Punjab+144002+Jalandhar?hl=en</t>
         </is>
       </c>
+      <c r="H169" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I169" s="14" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="170" ht="20" customHeight="1">
       <c r="A170" s="7" t="n">
@@ -9107,6 +10628,12 @@
           <t>https://maps.app.goo.gl/HLAivSgrHkcp4qnaA</t>
         </is>
       </c>
+      <c r="H170" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I170" s="14" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="7" t="n">
@@ -9137,6 +10664,12 @@
           <t>https://maps.app.goo.gl/Vz5yNZTUumTKdLSd8</t>
         </is>
       </c>
+      <c r="H171" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I171" s="14" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="7" t="n">
@@ -9167,6 +10700,12 @@
           <t>https://maps.app.goo.gl/zYmsiM2GuUKTfVeD6</t>
         </is>
       </c>
+      <c r="H172" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I172" s="14" t="n">
+        <v>190</v>
+      </c>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="7" t="n">
@@ -9197,6 +10736,12 @@
           <t>https://maps.app.goo.gl/LBtyvdAnk8e5m1578</t>
         </is>
       </c>
+      <c r="H173" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I173" s="14" t="n">
+        <v>407</v>
+      </c>
     </row>
     <row r="174" ht="20" customHeight="1">
       <c r="A174" s="7" t="n">
@@ -9227,6 +10772,12 @@
           <t>https://maps.app.goo.gl/UStZQsyjFuie2zcQA</t>
         </is>
       </c>
+      <c r="H174" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I174" s="14" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="7" t="n">
@@ -9257,6 +10808,12 @@
           <t>https://maps.app.goo.gl/u7fUEMutEveKTJfaA</t>
         </is>
       </c>
+      <c r="H175" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I175" s="14" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="7" t="n">
@@ -9287,6 +10844,12 @@
           <t>https://goo.gl/maps/Y1coLwehTfUaHJgQ9</t>
         </is>
       </c>
+      <c r="H176" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I176" s="14" t="n">
+        <v>2053</v>
+      </c>
     </row>
     <row r="177" ht="20" customHeight="1">
       <c r="A177" s="7" t="n">
@@ -9317,6 +10880,12 @@
           <t>https://maps.app.goo.gl/nCMGxjXNMPSkpduXA</t>
         </is>
       </c>
+      <c r="H177" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I177" s="14" t="n">
+        <v>566</v>
+      </c>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="7" t="n">
@@ -9347,6 +10916,12 @@
           <t>https://goo.gl/maps/Yd2kU1mEc8tyWvnJ8</t>
         </is>
       </c>
+      <c r="H178" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I178" s="14" t="n">
+        <v>4077</v>
+      </c>
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="7" t="n">
@@ -9377,6 +10952,12 @@
           <t>https://goo.gl/maps/b1DPwmk5pLaEaMkAA</t>
         </is>
       </c>
+      <c r="H179" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I179" s="14" t="n">
+        <v>3197</v>
+      </c>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="7" t="n">
@@ -9407,6 +10988,12 @@
           <t>https://maps.app.goo.gl/9shVkw5NVcCaEc2f7</t>
         </is>
       </c>
+      <c r="H180" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I180" s="14" t="n">
+        <v>494</v>
+      </c>
     </row>
     <row r="181" ht="20" customHeight="1">
       <c r="A181" s="7" t="n">
@@ -9437,6 +11024,12 @@
           <t>https://maps.app.goo.gl/KD7iMcgQd1KqrwuX6</t>
         </is>
       </c>
+      <c r="H181" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I181" s="14" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="182" ht="20" customHeight="1">
       <c r="A182" s="7" t="n">
@@ -9467,6 +11060,12 @@
           <t>https://goo.gl/maps/Yd2kU1mEc8tyWvnJ8</t>
         </is>
       </c>
+      <c r="H182" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I182" s="14" t="n">
+        <v>4077</v>
+      </c>
     </row>
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="7" t="n">
@@ -9497,6 +11096,12 @@
           <t>https://maps.app.goo.gl/ZCFFUjrMcfzQt27h8</t>
         </is>
       </c>
+      <c r="H183" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I183" s="14" t="n">
+        <v>219</v>
+      </c>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="7" t="n">
@@ -9527,6 +11132,12 @@
           <t>https://goo.gl/maps/wyjWtNYLyFV8wGLo6</t>
         </is>
       </c>
+      <c r="H184" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I184" s="14" t="n">
+        <v>372</v>
+      </c>
     </row>
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="7" t="n">
@@ -9557,6 +11168,12 @@
           <t>https://maps.app.goo.gl/Mdwf9WhXGqgWpP1s8</t>
         </is>
       </c>
+      <c r="H185" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I185" s="14" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="186" ht="20" customHeight="1">
       <c r="A186" s="7" t="n">
@@ -9587,6 +11204,12 @@
           <t>https://goo.gl/maps/qYiG7AWurb3kpPT57</t>
         </is>
       </c>
+      <c r="H186" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I186" s="14" t="n">
+        <v>434</v>
+      </c>
     </row>
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="7" t="n">
@@ -9617,6 +11240,12 @@
           <t>https://maps.app.goo.gl/8CvxLW27EUBgXm287</t>
         </is>
       </c>
+      <c r="H187" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I187" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="188" ht="20" customHeight="1">
       <c r="A188" s="7" t="n">
@@ -9647,6 +11276,12 @@
           <t>https://maps.app.goo.gl/XA4qoyenHaBCULJR9</t>
         </is>
       </c>
+      <c r="H188" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I188" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="7" t="n">
@@ -9677,6 +11312,12 @@
           <t>https://maps.app.goo.gl/jF1fPUaWD5TR8wZn6</t>
         </is>
       </c>
+      <c r="H189" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I189" s="14" t="n">
+        <v>196</v>
+      </c>
     </row>
     <row r="190" ht="20" customHeight="1">
       <c r="A190" s="7" t="n">
@@ -9707,6 +11348,12 @@
           <t>https://maps.app.goo.gl/6pZshenjLsstWLWy5</t>
         </is>
       </c>
+      <c r="H190" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I190" s="14" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="191" ht="20" customHeight="1">
       <c r="A191" s="7" t="n">
@@ -9737,6 +11384,12 @@
           <t>https://goo.gl/maps/YwNxSsrKnhA3Fzae8</t>
         </is>
       </c>
+      <c r="H191" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I191" s="14" t="n">
+        <v>7436</v>
+      </c>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="7" t="n">
@@ -9767,6 +11420,12 @@
           <t>https://maps.app.goo.gl/W21VqyaGAhgWLW1Z7</t>
         </is>
       </c>
+      <c r="H192" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I192" s="14" t="n">
+        <v>2941</v>
+      </c>
     </row>
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="7" t="n">
@@ -9797,6 +11456,12 @@
           <t>https://maps.app.goo.gl/SofrRQ31CC1sKfiq9</t>
         </is>
       </c>
+      <c r="H193" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I193" s="14" t="n">
+        <v>488</v>
+      </c>
     </row>
     <row r="194" ht="20" customHeight="1">
       <c r="A194" s="7" t="n">
@@ -9827,6 +11492,12 @@
           <t>https://maps.app.goo.gl/UnxqTGRsvK65sSta7</t>
         </is>
       </c>
+      <c r="H194" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I194" s="14" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="195" ht="20" customHeight="1">
       <c r="A195" s="7" t="n">
@@ -9857,6 +11528,12 @@
           <t>https://maps.app.goo.gl/F8jPscSQ2V93c6vi8</t>
         </is>
       </c>
+      <c r="H195" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I195" s="14" t="n">
+        <v>2229</v>
+      </c>
     </row>
     <row r="196" ht="20" customHeight="1">
       <c r="A196" s="7" t="n">
@@ -9887,6 +11564,12 @@
           <t>https://maps.app.goo.gl/Zh4ebnPqcXvPMZNG9</t>
         </is>
       </c>
+      <c r="H196" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I196" s="14" t="n">
+        <v>2669</v>
+      </c>
     </row>
     <row r="197" ht="20" customHeight="1">
       <c r="A197" s="7" t="n">
@@ -9917,6 +11600,12 @@
           <t>https://maps.app.goo.gl/kuVZMKKgf5DubNtN8</t>
         </is>
       </c>
+      <c r="H197" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" s="14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="7" t="n">
@@ -9947,6 +11636,12 @@
           <t>https://goo.gl/maps/EFUzibDLaLXcxkTd8</t>
         </is>
       </c>
+      <c r="H198" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I198" s="14" t="n">
+        <v>8994</v>
+      </c>
     </row>
     <row r="199" ht="20" customHeight="1">
       <c r="A199" s="7" t="n">
@@ -9977,6 +11672,12 @@
           <t>https://maps.app.goo.gl/6W1ZNqLiW1QG7swx5</t>
         </is>
       </c>
+      <c r="H199" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I199" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="200" ht="20" customHeight="1">
       <c r="A200" s="7" t="n">
@@ -10007,6 +11708,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Sirsa%2C+Haryana%2C+Sirsa+Sirsa?hl=en</t>
         </is>
       </c>
+      <c r="H200" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I200" s="14" t="n">
+        <v>190</v>
+      </c>
     </row>
     <row r="201" ht="20" customHeight="1">
       <c r="A201" s="7" t="n">
@@ -10037,6 +11744,12 @@
           <t>https://maps.app.goo.gl/ifJQ68YEKMTaET63A</t>
         </is>
       </c>
+      <c r="H201" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I201" s="14" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="202" ht="20" customHeight="1">
       <c r="A202" s="7" t="n">
@@ -10067,6 +11780,12 @@
           <t>https://goo.gl/maps/gt6giRYsgV7Jfsmp8</t>
         </is>
       </c>
+      <c r="H202" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I202" s="14" t="n">
+        <v>2883</v>
+      </c>
     </row>
     <row r="203" ht="20" customHeight="1">
       <c r="A203" s="7" t="n">
@@ -10097,6 +11816,12 @@
           <t>https://maps.app.goo.gl/k8nPnXCjPNR1Fw26A</t>
         </is>
       </c>
+      <c r="H203" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I203" s="14" t="n">
+        <v>17008</v>
+      </c>
     </row>
     <row r="204" ht="20" customHeight="1">
       <c r="A204" s="7" t="n">
@@ -10127,6 +11852,12 @@
           <t>https://maps.app.goo.gl/zD7nJnVUnKHTBbTc7</t>
         </is>
       </c>
+      <c r="H204" s="14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I204" s="14" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="205" ht="20" customHeight="1">
       <c r="A205" s="7" t="n">
@@ -10157,6 +11888,12 @@
           <t>https://maps.app.goo.gl/rTKgS8LFdLXcgLgG8</t>
         </is>
       </c>
+      <c r="H205" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I205" s="14" t="n">
+        <v>338</v>
+      </c>
     </row>
     <row r="206" ht="20" customHeight="1">
       <c r="A206" s="7" t="n">
@@ -10186,6 +11923,12 @@
         <is>
           <t>https://maps.app.goo.gl/F4A61XtKBQZhzMRC7</t>
         </is>
+      </c>
+      <c r="H206" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I206" s="14" t="n">
+        <v>161</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1"/>
@@ -10201,7 +11944,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -10299,7 +12042,7 @@
         <v>4.5</v>
       </c>
       <c r="H3" s="14" t="n">
-        <v>7006</v>
+        <v>7008</v>
       </c>
     </row>
     <row r="4">
@@ -10367,6 +12110,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Barsha+1+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1159702,55.2049553,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6bc01e76ba11:0x4fd1a9f4b2e6f5e3!8m2!3d25.1159702!4d55.2049553!16s%2Fg%2F1hhn4cw5b?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G5" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>3417</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -10397,6 +12146,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Arjan+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.0611644,55.2416108,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6f3d18bbdbdd:0xf394598ae51611cd!8m2!3d25.0611644!4d55.2416108!16s%2Fg%2F11k4t6j5kj?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G6" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>1351</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -10427,6 +12182,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Dubai+Hills+Mall+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1000884,55.2380841,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6ffb10c94323:0xe15233cd12b4c95e!8m2!3d25.1000884!4d55.2380841!16s%2Fg%2F11srb65qdy?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G7" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>1110</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -10457,6 +12218,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Sheikh+Zayed+Road+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2287901,55.2861116,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43aad3d78e71:0xb8b194cb916fd9b0!8m2!3d25.2287901!4d55.2861116!16s%2Fg%2F11spn08t8p?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G8" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>3370</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -10487,6 +12254,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Gold+Souk+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2720383,55.2977013,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43768964654b:0xc11f03b76b0ba714!8m2!3d25.2720383!4d55.2977013!16s%2Fg%2F11sqkp7mp7?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G9" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -10517,6 +12290,12 @@
           <t>https://www.google.com/maps/place/Bikanervala/@25.1971872,55.2793099,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f43291308afa5:0xe48b7db44021ad9d!8m2!3d25.1971872!4d55.2793099!16s%2Fg%2F11h_6kxb_4?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G10" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>1201</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -10547,6 +12326,12 @@
           <t>https://www.google.com/maps/place/Bikanervala/@25.0443703,55.2301107,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6fbad2abf81f:0x2b8744ab6a1bf442!8m2!3d25.0443703!4d55.2301107!16s%2Fg%2F11wqdtyl9k?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G11" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>812</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -10577,6 +12362,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Jumeirah+Village+Circle?hl=en</t>
         </is>
       </c>
+      <c r="G12" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>812</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -10607,6 +12398,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Jumeirah+3+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1568314,55.2048822,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6bf2c1bdccc9:0x43c26854ab27ef01!8m2!3d25.1568314!4d55.2048822!16s%2Fg%2F11s5twnr34?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G13" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>406</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -10637,6 +12434,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Furjan+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.0253394,55.1523478,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6d3bc9bcdbdb:0xe6f0ccdcb4b1e8ab!8m2!3d25.0253394!4d55.1523478!16s%2Fg%2F11g8kr7p26?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G14" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>3469</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -10667,6 +12470,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+International+City+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1587461,55.4044494,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f6152822cefa7:0x62485254b618ad37!8m2!3d25.1587461!4d55.4044494!16s%2Fg%2F11fy4nt_fh?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G15" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>1986</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -10697,6 +12506,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Ghurair+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.268832,55.3167197,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f432a6356bd7d:0x6e8727a69863a0ea!8m2!3d25.268832!4d55.3167197!16s%2Fg%2F11gj4q5yml?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G16" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>1337</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -10727,6 +12542,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Business+Bay+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.1907081,55.2657305,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f69d43a494553:0xcae55dd8d4af25bc!8m2!3d25.1907081!4d55.2657305!16s%2Fg%2F11cnch2xjh?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G17" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>1336</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -10757,6 +12578,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Abu+Dhabi+%7C+Indian+Vegetarian+Restaurant+in+Abu+Dhabi/@24.4787181,54.3632708,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5e6797000fef8b:0x252e9c63c8d0f687!8m2!3d24.4787181!4d54.3632708!16s%2Fg%2F11j3jt3jck?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G18" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>4496</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -10787,6 +12614,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Al+Qusais+%7C+Indian+Vegetarian+Restaurant+in+Dubai/@25.2779484,55.362064,17z/data=!3m1!4b1!4m6!3m5!1s0x3e5f5c5ef14f580b:0x42f37dd66cc3bd09!8m2!3d25.2779484!4d55.362064!16s%2Fg%2F11bbwn_ftp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G19" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>1675</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -10817,6 +12650,12 @@
           <t>https://www.google.com/maps/place/Bikanervala+Hounslow/@51.4697256,-0.3575675,17z/data=!3m1!4b1!4m6!3m5!1s0x48760db0ad77af37:0x259004b7a001719e!8m2!3d51.4697256!4d-0.3575675!16s%2Fg%2F11lw2pkxzp?hl=en&amp;entry=ttu&amp;g_ep=EgoyMDI2MDkyMy4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
+      <c r="G20" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>4379</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -10847,6 +12686,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Doha+Qatar?hl=en</t>
         </is>
       </c>
+      <c r="G21" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>3859</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -10877,6 +12722,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Investment+Park+Dubai+%28Dubai%29?hl=en</t>
         </is>
       </c>
+      <c r="G22" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -10907,6 +12758,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Jumeirah+%28The+Point%2C+Palm%29+Dubai+%28Dubai%29?hl=en</t>
         </is>
       </c>
+      <c r="G23" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>443</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -10937,6 +12794,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Lynx+Tower+%28Silicon+Oasis%29+Dubai+%28Dubai%29?hl=en</t>
         </is>
       </c>
+      <c r="G24" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>1684</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -10967,6 +12830,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+JLT+Dubai+%28Dubai%29?hl=en</t>
         </is>
       </c>
+      <c r="G25" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>3365</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -10997,6 +12866,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Al+Wahda+Street+Sharjah+%28Sharjah%29?hl=en</t>
         </is>
       </c>
+      <c r="G26" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>1765</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -11027,6 +12902,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Muweillah+Sharjah+%28Sharjah%29?hl=en</t>
         </is>
       </c>
+      <c r="G27" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>532</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -11057,6 +12938,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Southall+London+%28UK%29?hl=en</t>
         </is>
       </c>
+      <c r="G28" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>1324</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -11087,6 +12974,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Ilford+London+%28UK%29?hl=en</t>
         </is>
       </c>
+      <c r="G29" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>642</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -11117,6 +13010,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Express+City+Centre+Mall+Doha+%28Qatar%29?hl=en</t>
         </is>
       </c>
+      <c r="G30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -11147,6 +13046,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Jersey+City+NJ+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G31" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>1323</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -11177,6 +13082,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Iselin+NJ+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G32" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>1427</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -11207,6 +13118,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Kendall+Park+NJ+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G33" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>1335</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -11237,6 +13154,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Rochelle+Park+NJ+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G34" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>193</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -11267,6 +13190,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Westlake+Village+CA+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -11297,6 +13226,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Fremont+CA+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G36" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>994</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -11327,6 +13262,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Diamond+Bar+CA+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G37" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>205</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -11357,6 +13298,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Sunnyvale+CA+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G38" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>213</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -11387,6 +13334,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Overland+Park+KS+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G39" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>851</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -11417,6 +13370,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Irving+TX+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G40" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>2236</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -11447,6 +13406,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Dublin+OH+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G41" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -11477,6 +13442,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Hicksville+NY+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G42" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>1587</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -11507,6 +13478,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Schaumburg+IL+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G43" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>1165</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -11537,6 +13514,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Chandler+AZ+%28USA%29?hl=en</t>
         </is>
       </c>
+      <c r="G44" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>474</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -11567,6 +13550,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Campbelltown+Adelaide+%28Australia%29?hl=en</t>
         </is>
       </c>
+      <c r="G45" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>433</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -11597,6 +13586,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Rouse+Hill+Sydney+%28Australia%29?hl=en</t>
         </is>
       </c>
+      <c r="G46" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>937</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -11627,6 +13622,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Truganina+Melbourne+%28Australia%29?hl=en</t>
         </is>
       </c>
+      <c r="G47" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>2569</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -11657,6 +13658,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Henderson+Auckland+%28New+Zealand%29?hl=en</t>
         </is>
       </c>
+      <c r="G48" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>1429</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -11687,6 +13694,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Mount+Roskill+Auckland+%28New+Zealand%29?hl=en</t>
         </is>
       </c>
+      <c r="G49" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>1420</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -11717,6 +13730,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Sydenham+Christchurch+%28New+Zealand%29?hl=en</t>
         </is>
       </c>
+      <c r="G50" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H50" s="14" t="n">
+        <v>1553</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -11747,6 +13766,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Brampton+%28Canada%29?hl=en</t>
         </is>
       </c>
+      <c r="G51" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H51" s="14" t="n">
+        <v>2808</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -11777,6 +13802,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Markham+%28Canada%29?hl=en</t>
         </is>
       </c>
+      <c r="G52" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" s="14" t="n">
+        <v>744</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -11807,6 +13838,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Changi+Airport+T3+%28Singapore%29?hl=en</t>
         </is>
       </c>
+      <c r="G53" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H53" s="14" t="n">
+        <v>1230</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -11837,6 +13874,12 @@
           <t>https://www.google.com/maps/search/Bikanervala+Katong+%28Singapore%29?hl=en</t>
         </is>
       </c>
+      <c r="G54" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" s="14" t="n">
+        <v>674</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -11866,6 +13909,12 @@
         <is>
           <t>https://www.google.com/maps/search/Bikanervala+Manama+%28Bahrain%29?hl=en</t>
         </is>
+      </c>
+      <c r="G55" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H55" s="14" t="n">
+        <v>424</v>
       </c>
     </row>
     <row r="56">
@@ -12114,7 +14163,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H113"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -12280,6 +14329,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Vikas+Marg+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G5" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>460</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -12310,6 +14365,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Akshardham+Parsvnath+Mall+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G6" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>11588</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -12340,6 +14401,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Dilshad+Garden+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G7" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>2050</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -12370,6 +14437,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Krishna+Nagar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G8" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>919</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -12400,6 +14473,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Indraprastha+Apollo+Hospital+Sarita+Vihar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G9" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>1605</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -12430,6 +14509,12 @@
           <t>https://www.google.com/maps/search/Haldiram+DLF+Promenade+Vasant+Kunj+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G10" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>2024</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -12460,6 +14545,12 @@
           <t>https://www.google.com/maps/search/Haldiram+DLF+Saket+District+Centre+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G11" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>3082</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -12490,6 +14581,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Kalkaji+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G12" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>3628</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -12520,6 +14617,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Lajpat+Nagar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G13" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>21269</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -12550,6 +14653,12 @@
           <t>https://www.google.com/maps/search/Haldiram+New+Friends+Colony+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G14" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>2948</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -12580,6 +14689,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Green+Park+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>4205</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -12610,6 +14725,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Nehru+Place+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G16" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>2393</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -12640,6 +14761,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Kailash+Colony+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G17" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>415</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -12670,6 +14797,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Mathura+Road+Mohan+Co-operative+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G18" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>12127</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -12700,6 +14833,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Sarojini+Nagar+DLF+South+Square+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G19" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>3093</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -12730,6 +14869,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Malviya+Nagar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G20" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>9247</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -12760,6 +14905,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Lok+Vihar+Pitampura+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G21" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -12790,6 +14941,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Paschim+Vihar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G22" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>6138</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -12820,6 +14977,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Katwaria+Sarai+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G23" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>1755</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -12850,6 +15013,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Anupam+Saket+PVR+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G24" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>1060</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -12880,6 +15049,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Jungpura+Extension+Eros+One+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G25" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>2056</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -12910,6 +15085,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Jasola+DLF+Tower+A+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G26" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>2780</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -12940,6 +15121,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Moti+Nagar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G27" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>11091</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -12970,6 +15157,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pitampura+D+Mall+Netaji+Subhash+Place+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G28" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>5490</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -13000,6 +15193,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Janpath+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G29" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>4019</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -13030,6 +15229,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Netaji+Subhash+Place+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>1580</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -13060,6 +15265,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Netaji+Subhash+Place+2+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G31" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>1580</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -13090,6 +15301,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Bikaner+House+Pandara+Road+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G32" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>2811</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -13120,6 +15337,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Chandni+Chowk+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G33" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>18972</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -13150,6 +15373,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Connaught+Place+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G34" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>39702</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -13180,6 +15409,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Model+Town+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>5229</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -13210,6 +15445,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pusa+Road+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G36" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>10387</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -13240,6 +15481,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Dwarka+City+Centre+Sector+12+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G37" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>7406</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -13270,6 +15517,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Vegas+Mall+Food+Court+Dwarka+Sector+14+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G38" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>539</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -13300,6 +15553,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Dwarka+Sector+21+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G39" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>1124</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -13330,6 +15589,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Vegas+Mall+Showroom+Dwarka+Sector+14+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G40" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>539</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -13360,6 +15625,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Tilak+Nagar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G41" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>2626</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -13390,6 +15661,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Janakpuri+Unity+One+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G42" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>1445</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -13420,6 +15697,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Janak+Cinema+Janakpuri+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G43" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>955</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -13450,6 +15733,12 @@
           <t>https://www.google.com/maps/search/Haldiram+New+Delhi+Railway+Station?hl=en</t>
         </is>
       </c>
+      <c r="G44" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <v>4187</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -13480,6 +15769,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Rajouri+Garden+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G45" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <v>3486</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -13510,6 +15805,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Rohini+D+Mall+Sector+10+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G46" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>7887</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -13540,6 +15841,12 @@
           <t>https://www.google.com/maps/search/Haldiram+ARSS+Mall+Paschim+Vihar+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G47" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H47" s="14" t="n">
+        <v>6138</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -13570,6 +15877,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Vaishali+Enclave+Pitampura+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G48" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H48" s="14" t="n">
+        <v>983</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -13600,6 +15913,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Dwarka+Sector+11+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G49" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <v>3651</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -13630,6 +15949,12 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T1+Domestic+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G50" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H50" s="14" t="n">
+        <v>171</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -13660,6 +15985,12 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+D-04+Domestic+Departure+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G51" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H51" s="14" t="n">
+        <v>4120</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -13690,6 +16021,12 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T3+International+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G52" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H52" s="14" t="n">
+        <v>294</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -13720,6 +16057,12 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T3+International+Departure+Gate+17B+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G53" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H53" s="14" t="n">
+        <v>4120</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -13750,6 +16093,12 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T3A+Baggage+Reclaim+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G54" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H54" s="14" t="n">
+        <v>4120</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -13780,6 +16129,12 @@
           <t>https://www.google.com/maps/search/Haldiram+IGI+Airport+T2+Arrival+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G55" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H55" s="14" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -13810,6 +16165,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Okhla+Jasola+Delhi?hl=en</t>
         </is>
       </c>
+      <c r="G56" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H56" s="14" t="n">
+        <v>493</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -13840,6 +16201,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Spice+Mall+Sector+25A+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G57" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H57" s="14" t="n">
+        <v>7853</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -13870,6 +16237,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Logix+City+Centre+Sector+32+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G58" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H58" s="14" t="n">
+        <v>4018</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -13900,6 +16273,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Skymark+One+Sector+98+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G59" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H59" s="14" t="n">
+        <v>2882</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -13930,6 +16309,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Paras+One33+Sector+133+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H60" s="14" t="n">
+        <v>2252</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -13960,6 +16345,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Sector+18+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G61" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H61" s="14" t="n">
+        <v>7836</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -13990,6 +16381,12 @@
           <t>https://www.google.com/maps/search/Haldiram+DLF+Mall+of+India+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G62" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H62" s="14" t="n">
+        <v>3616</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -14020,6 +16417,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Youth+Plaza+Sector+63+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G63" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H63" s="14" t="n">
+        <v>4769</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -14050,6 +16453,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Hush+Life+Sector+63+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G64" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H64" s="14" t="n">
+        <v>2626</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -14080,6 +16489,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Advant+IT+Park+Noida+Expressway?hl=en</t>
         </is>
       </c>
+      <c r="G65" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H65" s="14" t="n">
+        <v>2903</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -14110,6 +16525,12 @@
           <t>https://www.google.com/maps/search/Haldiram+MSX+Mall+Greater+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G66" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H66" s="14" t="n">
+        <v>6445</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -14140,6 +16561,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Grand+Venice+Mall+Greater+Noida?hl=en</t>
         </is>
       </c>
+      <c r="G67" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H67" s="14" t="n">
+        <v>781</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -14170,6 +16597,12 @@
           <t>https://www.google.com/maps/search/Haldiram+NH8+Kherki+Daula+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G68" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H68" s="14" t="n">
+        <v>19110</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -14200,6 +16633,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Iris+Broadway+Sector+85-86+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G69" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H69" s="14" t="n">
+        <v>2918</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -14230,6 +16669,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Vatika+Business+Park+Sector+49+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G70" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H70" s="14" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
@@ -14260,6 +16705,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Three+Roads+Sector+70+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G71" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H71" s="14" t="n">
+        <v>1192</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -14290,6 +16741,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Ambience+Mall+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G72" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H72" s="14" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -14320,6 +16777,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Cyber+Hub+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G73" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H73" s="14" t="n">
+        <v>3864</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -14350,6 +16813,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Fortis+Hospital+Huda+City+Centre+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G74" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H74" s="14" t="n">
+        <v>755</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -14380,6 +16849,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Palam+Vihar+Global+Foyer+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G75" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H75" s="14" t="n">
+        <v>4658</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -14410,6 +16885,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Element+One+Sector+47-49+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G76" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H76" s="14" t="n">
+        <v>5290</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -14440,6 +16921,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Eros+City+Square+Sector+49-50+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G77" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H77" s="14" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -14470,6 +16957,12 @@
           <t>https://www.google.com/maps/search/Haldiram+AIPL+Joy+Street+Sector+66+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G78" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H78" s="14" t="n">
+        <v>1131</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -14500,6 +16993,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Worldmark+3+Sector+65+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G79" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H79" s="14" t="n">
+        <v>634</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -14530,6 +17029,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Ardee+Mall+Sector+52+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G80" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H80" s="14" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -14560,6 +17065,12 @@
           <t>https://www.google.com/maps/search/Haldiram+MGF+Metropolitan+Mall+MG+Road+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G81" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H81" s="14" t="n">
+        <v>1566</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -14590,6 +17101,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Sahara+Mall+MG+Road+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G82" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H82" s="14" t="n">
+        <v>11746</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -14620,6 +17137,12 @@
           <t>https://www.google.com/maps/search/Haldiram+City+Centre+MG+Road+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G83" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H83" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
@@ -14650,6 +17173,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Sector+29+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G84" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H84" s="14" t="n">
+        <v>5934</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -14680,6 +17209,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Sector+14+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G85" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H85" s="14" t="n">
+        <v>3266</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -14710,6 +17245,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Parsvnath+City+Mall+Sector+12+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G86" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H86" s="14" t="n">
+        <v>10433</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
@@ -14740,6 +17281,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Crown+Interiorz+Sector+35+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G87" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H87" s="14" t="n">
+        <v>4152</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
@@ -14770,6 +17317,12 @@
           <t>https://www.google.com/maps/search/Haldiram+NIT+Metropolis+Mall+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G88" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H88" s="14" t="n">
+        <v>2998</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
@@ -14800,6 +17353,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Sector+15+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G89" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H89" s="14" t="n">
+        <v>1295</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -14830,6 +17389,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Angel+Mega+Mall+Kaushambi+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G90" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H90" s="14" t="n">
+        <v>2236</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
@@ -14860,6 +17425,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Ajnara+Orbit+Plaza+Crossing+Republic+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G91" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H91" s="14" t="n">
+        <v>7973</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
@@ -14890,6 +17461,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pacific+Mall+Sahibabad+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G92" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H92" s="14" t="n">
+        <v>783</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
@@ -14920,6 +17497,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Signature+Global+Mall+Vaishali+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G93" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H93" s="14" t="n">
+        <v>790</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
@@ -14950,6 +17533,12 @@
           <t>https://www.google.com/maps/search/Haldiram+RDC+Raj+Nagar+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G94" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H94" s="14" t="n">
+        <v>2595</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
@@ -14980,6 +17569,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Nehru+Nagar+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G95" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H95" s="14" t="n">
+        <v>1679</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
@@ -15010,6 +17605,12 @@
           <t>https://www.google.com/maps/search/Haldiram+World+Square+Mall+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G96" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H96" s="14" t="n">
+        <v>6440</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
@@ -15040,6 +17641,12 @@
           <t>https://www.google.com/maps/search/Haldiram+East+Delhi+Mall+Kaushambi+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G97" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H97" s="14" t="n">
+        <v>2315</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -15070,6 +17677,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Vasundhara+Sector+11+Ghaziabad?hl=en</t>
         </is>
       </c>
+      <c r="G98" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H98" s="14" t="n">
+        <v>1937</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
@@ -15100,6 +17713,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Gajraula+NH-24?hl=en</t>
         </is>
       </c>
+      <c r="G99" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H99" s="14" t="n">
+        <v>5583</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -15130,6 +17749,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Khatauli?hl=en</t>
         </is>
       </c>
+      <c r="G100" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H100" s="14" t="n">
+        <v>17792</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -15160,6 +17785,12 @@
           <t>https://www.google.com/maps/search/Haldiram+SRK+Mall+Agra?hl=en</t>
         </is>
       </c>
+      <c r="G101" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H101" s="14" t="n">
+        <v>6181</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -15190,6 +17821,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Rewari?hl=en</t>
         </is>
       </c>
+      <c r="G102" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H102" s="14" t="n">
+        <v>5282</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
@@ -15220,6 +17857,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Jaipur+135+NH-8+Behror?hl=en</t>
         </is>
       </c>
+      <c r="G103" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H103" s="14" t="n">
+        <v>1176</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -15250,6 +17893,12 @@
           <t>https://www.google.com/maps/search/Haldiram+V+Square+Mall+Bhiwadi?hl=en</t>
         </is>
       </c>
+      <c r="G104" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H104" s="14" t="n">
+        <v>4077</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
@@ -15280,6 +17929,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Delhi+135+NH-8+Behror?hl=en</t>
         </is>
       </c>
+      <c r="G105" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H105" s="14" t="n">
+        <v>1176</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
@@ -15310,6 +17965,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Zirakpur?hl=en</t>
         </is>
       </c>
+      <c r="G106" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H106" s="14" t="n">
+        <v>10979</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -15340,6 +18001,12 @@
           <t>https://www.google.com/maps/search/Haldiram+VR+Punjab+Mall+Mohali?hl=en</t>
         </is>
       </c>
+      <c r="G107" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H107" s="14" t="n">
+        <v>3159</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -15370,6 +18037,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Ambala?hl=en</t>
         </is>
       </c>
+      <c r="G108" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H108" s="14" t="n">
+        <v>3059</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
@@ -15400,6 +18073,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Amritsar?hl=en</t>
         </is>
       </c>
+      <c r="G109" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H109" s="14" t="n">
+        <v>2635</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
@@ -15430,6 +18109,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Barnala?hl=en</t>
         </is>
       </c>
+      <c r="G110" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H110" s="14" t="n">
+        <v>1882</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
@@ -15460,6 +18145,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Sonipat?hl=en</t>
         </is>
       </c>
+      <c r="G111" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H111" s="14" t="n">
+        <v>4616</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -15490,6 +18181,12 @@
           <t>https://www.google.com/maps/search/Haldiram+Pathankot?hl=en</t>
         </is>
       </c>
+      <c r="G112" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H112" s="14" t="n">
+        <v>2456</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
@@ -15519,6 +18216,12 @@
         <is>
           <t>https://www.google.com/maps/search/Haldiram+Kosi+Kalan?hl=en</t>
         </is>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H113" s="14" t="n">
+        <v>2652</v>
       </c>
     </row>
   </sheetData>
@@ -15533,7 +18236,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -15699,6 +18402,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Elan+Town+Centre+Sector+67+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G5" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -15729,6 +18438,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Huda+Market+Sector+57+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G6" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -15759,6 +18474,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+M3M+Cosmopolitan+Sector+66+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G7" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>4838</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -15789,6 +18510,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+New+Colony+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G8" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>2067</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -15819,6 +18546,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Palam+Vihar+Road+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G9" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>5782</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -15849,6 +18582,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+10A+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G10" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>6559</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -15879,6 +18618,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+23+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G11" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>10577</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -15909,6 +18654,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+31+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G12" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>12237</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -15939,6 +18690,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+4+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G13" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>10702</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -15969,6 +18726,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+46+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G14" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>6811</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -15999,6 +18762,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+50+Good+Earth+City+Centre+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G15" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>3606</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -16029,6 +18798,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+57+Hong+Kong+Bazaar+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G16" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>4505</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -16059,6 +18834,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+7+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G17" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>878</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -16089,6 +18870,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+14+Gurgaon?hl=en</t>
         </is>
       </c>
+      <c r="G18" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>19721</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -16119,6 +18906,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+NIT+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G19" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>2022</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -16149,6 +18942,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Omaxe+World+Street+Sector+79+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G20" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>2056</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -16179,6 +18978,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+16+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G21" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>8785</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -16209,6 +19014,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Sector+31+Faridabad?hl=en</t>
         </is>
       </c>
+      <c r="G22" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>1120</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -16239,6 +19050,12 @@
           <t>https://www.google.com/maps/search/Om+Sweets+Palwal?hl=en</t>
         </is>
       </c>
+      <c r="G23" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>676</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -16268,6 +19085,12 @@
         <is>
           <t>https://www.google.com/maps/search/Om+Sweets+Sohna?hl=en</t>
         </is>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>1823</v>
       </c>
     </row>
   </sheetData>
@@ -16282,7 +19105,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H61"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -16448,6 +19271,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Sweets+and+Restaurant/data=!4m7!3m6!1s0x3e5f42d80a18fbdb:0x9f86aefc091ecb9!8m2!3d25.2486238!4d55.3024612!16s%2Fg%2F11bbwx1fbb!19sChIJ2_sYCthCXz4RueyRwO9q-Ak?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G5" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>1981</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -16478,6 +19307,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Restaurant/data=!4m7!3m6!1s0x3e5f729cb45eefab:0xac26aaf47bcb314!8m2!3d24.9992282!4d55.170383!16s%2Fg%2F11f3hf2kqp!19sChIJq-9etJxyXz4RFLO8R69qwgo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -16508,6 +19343,12 @@
           <t>https://www.google.com/maps/place/Puranmal/data=!4m7!3m6!1s0x3e5f133176ad688d:0x3383f49dba4666ef!8m2!3d25.0476057!4d55.1311601!16s%2Fg%2F1hhgjxrxn!19sChIJjWitdjETXz4R72ZGup30gzM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G7" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>1412</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -16538,6 +19379,12 @@
           <t>https://www.google.com/maps/place/Puranmal+sweets+and+restaurant/data=!4m7!3m6!1s0x3e5f6fca777c80b7:0xd9fcbfdd4343072d!8m2!3d25.0590927!4d55.2412228!16s%2Fg%2F11y_gyll3p!19sChIJt4B8d8pvXz4RLQdDQ92__Nk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G8" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -16568,6 +19415,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Sweets+%26+Restaurant/data=!4m7!3m6!1s0x3e5f646e13b36049:0xb69ac7e875aba115!8m2!3d25.1180318!4d55.3910236!16s%2Fg%2F11bbwqz2c0!19sChIJSWCzE25kXz4RFaGrdejHmrY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G9" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>1133</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -16598,6 +19451,12 @@
           <t>https://www.google.com/maps/place/Vega+by+Puranmal/data=!4m7!3m6!1s0x3e5f4251eda72f51:0x1b6293d48301a31c!8m2!3d25.2284641!4d55.2604103!16s%2Fg%2F11bc7tvmsh!19sChIJUS-n7VFCXz4RHKMBg9STYhs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G10" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>722</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -16628,6 +19487,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Restaurants+DMCC/data=!4m7!3m6!1s0x3e5f6d48eaaed9f7:0x791c0ba6c372ae26!8m2!3d25.0690597!4d55.138396!16s%2Fg%2F11ms89fkjx!19sChIJ99mu6khtXz4RJq5yw6YLHHk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G11" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -16658,6 +19523,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Authentic+Indian+Delicacies/data=!4m7!3m6!1s0x3e5f436690ce24a1:0x7980cd991fdc9e15!8m2!3d25.2218502!4d55.2814127!16s%2Fg%2F11s_fz4c8s!19sChIJoSTOkGZDXz4RFZ7cH5nNgHk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G12" s="14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -16688,6 +19559,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Meadows+%28Enoc%29/data=!4m7!3m6!1s0x3e5f6d258d8a3247:0x6cbc17e16920e393!8m2!3d25.0642063!4d55.1549915!16s%2Fg%2F11j3phbw8b!19sChIJRzKKjSVtXz4Rk-MgaeEXvGw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G13" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -16718,6 +19595,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Greens/data=!4m7!3m6!1s0x3e5f6b50f32318cf:0xc102df0e0c359348!8m2!3d25.094062!4d55.1678865!16s%2Fg%2F11hjkgs3kq!19sChIJzxgj81BrXz4RSJM1DA7fAsE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G14" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -16748,6 +19631,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Resturant/data=!4m7!3m6!1s0x3e5f5c77eab52041:0x9bf086c3c54484d0!8m2!3d25.303719!4d55.3708944!16s%2Fg%2F11c1ptxkdb!19sChIJQSC16ndcXz4R0IRExcOG8Js?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G15" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>562</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -16778,6 +19667,12 @@
           <t>https://www.google.com/maps/place/Puranmal+Warehouse/data=!4m7!3m6!1s0x3e5f7268095ac931:0x1bebae7a986abcaf!8m2!3d24.9894399!4d55.192723!16s%2Fg%2F11bx1gykmp!19sChIJMclaCWhyXz4Rr7xqmHqu6xs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G16" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -16808,6 +19703,12 @@
           <t>https://www.google.com/maps/place/Haldiram%E2%80%99s+Al+Mankhool-+Vegetarian+Restaurant+in+Dubai/data=!4m7!3m6!1s0x3e5f43ffefd64bdf:0xd55fd4634f47f83f!8m2!3d25.2550953!4d55.2935363!16s%2Fg%2F11yc82939p!19sChIJ30vW7_9DXz4RP_hHT2PUX9U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G17" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>5840</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -16838,6 +19739,12 @@
           <t>https://www.google.com/maps/place/Haldiram%27s-+Sheikh+Zayed+Road/data=!4m7!3m6!1s0x3e5f430026f8137d:0xbc533bf410617740!8m2!3d25.2226875!4d55.2820625!16s%2Fg%2F11z3v_0z7p!19sChIJfRP4JgBDXz4RQHdhEPQ7U7w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G18" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>1127</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -16868,6 +19775,12 @@
           <t>https://www.google.com/maps/place/Shree+Haldiram+restaurant/data=!4m7!3m6!1s0x3e5f43208d06a43d:0xa95a2f625d380979!8m2!3d25.2370936!4d55.3075144!16s%2Fg%2F11rvdtdbqf!19sChIJPaQGjSBDXz4ReQk4XWIvWqk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -16898,6 +19811,12 @@
           <t>https://www.google.com/maps/place/Kailash+Parbat/data=!4m7!3m6!1s0x3e5f4339607918bb:0xb6fb2afaf133c371!8m2!3d25.25816!4d55.3108109!16s%2Fg%2F11gtb6v4m3!19sChIJuxh5YDlDXz4RccMz8foq-7Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G20" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>2472</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -16928,6 +19847,12 @@
           <t>https://www.google.com/maps/place/Kailash+Parbat,+Pure+Veg+Restaurant+Oud+Metha,+Dubai/data=!4m7!3m6!1s0x3e5f4354d534364f:0x7e15b26dd9861a0b!8m2!3d25.236946!4d55.3066909!16s%2Fg%2F11rjttcfky!19sChIJTzY01VRDXz4RCxqG2W2yFX4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G21" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>341</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -16958,6 +19883,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb913407f2d1b5:0x3249a9e465711151!8m2!3d17.429486!4d78.4098711!16s%2Fg%2F12629gjp0!19sChIJtdHyBzSRyzsRURFxZeSpSTI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G22" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>4357</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -16988,6 +19919,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb99dd2703988d:0xef045befa5f3726e!8m2!3d17.4011091!4d78.4858873!16s%2Fg%2F1tj48yhg!19sChIJjZgDJ92ZyzsRbnLzpe9bBO8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G23" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>11258</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -17018,6 +19955,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb918eafb67403:0x509ba3d059027dd0!8m2!3d17.4859258!4d78.3903757!16s%2Fg%2F11fy9ssrk3!19sChIJA3S2r46RyzsR0H0CWdCjm1A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G24" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>13831</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -17048,6 +19991,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9b23a1136449:0xeaa3a261dda1ba18!8m2!3d17.4432886!4d78.4781068!16s%2Fg%2F11h_11dbss!19sChIJSWQToSObyzsRGLqh3WGio-o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G25" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>5024</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -17078,6 +20027,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb972c621e321f:0x39d6c04e3a800c16!8m2!3d17.4269497!4d78.4433936!16s%2Fg%2F1w110n5q!19sChIJHzIeYiyXyzsRFgyAOk7A1jk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G26" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>8084</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -17108,6 +20063,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9bdb0fd94b33:0x2cf8f2cc691ea5b4!8m2!3d17.4408497!4d78.5032582!16s%2Fg%2F11h4tnmqw2!19sChIJM0vZD9ubyzsRtKUeaczy-Cw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G27" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>7820</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -17138,6 +20099,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb93a010c47de3:0x2a6d183afbe9aea9!8m2!3d17.4495681!4d78.3634623!16s%2Fg%2F11fqqbr4t3!19sChIJ433EEKCTyzsRqa7p-zoYbSo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G28" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>6652</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -17168,6 +20135,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb95404cdeed5f:0x368b5c59f9072840!8m2!3d17.3855295!4d78.3303451!16s%2Fg%2F11xt9dz54t!19sChIJX-3eTECVyzsRQCgH-VlcizY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G29" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>1155</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -17198,6 +20171,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9727c96cf2cb:0xed10d003e11e198d!8m2!3d17.4126667!4d78.4303883!16s%2Fg%2F1ptxy0rc8!19sChIJy_JsySeXyzsRjRke4QPQEO0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G30" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>4943</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -17228,6 +20207,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9b76029a6381:0xfbe255b51a1975d8!8m2!3d17.5137477!4d78.479297!16s%2Fg%2F11svfkn0lv!19sChIJgWOaAnabyzsR2HUZGrVV4vs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G31" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>8066</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -17258,6 +20243,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcbbb81d4c3e721:0x6cfdcb31d373fc39!8m2!3d17.2352717!4d78.4306917!16s%2Fg%2F11c5t04l3c!19sChIJIefD1IG7yzsROfxz0zHL_Ww?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G32" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>8451</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -17288,6 +20279,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb9b1732f66e7b:0xf311299cd0febcba!8m2!3d17.4837097!4d78.5426156!16s%2Fg%2F11y3npb6zt!19sChIJe272MhebyzsRurz-0JwpEfM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G33" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H33" s="14" t="n">
+        <v>4182</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -17318,6 +20315,12 @@
           <t>https://www.google.com/maps/place/Almond+House/data=!4m7!3m6!1s0x3bcb95633e613e13:0x5de8794d037bb3ee!8m2!3d17.4203322!4d78.3797772!16s%2Fg%2F11ntl7h69x!19sChIJEz5hPmOVyzsR7rN7A0156F0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G34" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H34" s="14" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -17348,6 +20351,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Jubilee+Hills/data=!4m7!3m6!1s0x3bcb9136402aa371:0xf6b91a349382b790!8m2!3d17.4313965!4d78.407714!16s%2Fg%2F1pp2x6w4s!19sChIJcaMqQDaRyzsRkLeCkzQaufY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>4429</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -17378,6 +20387,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Himayathnagar/data=!4m7!3m6!1s0x3bcb99e0f3ba40ad:0x95ec754fd3ed92!8m2!3d17.4056989!4d78.4791329!16s%2Fg%2F1hc5k1hm9!19sChIJrUC68-CZyzsRku3TT3XslQA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G36" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <v>5551</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -17408,6 +20423,12 @@
           <t>https://www.google.com/maps/place/Dadu%E2%80%99s+Gachibowli/data=!4m7!3m6!1s0x3bcb93c86eaff663:0xe881fab9e954d25b!8m2!3d17.446841!4d78.3639362!16s%2Fg%2F11fn5sfyl9!19sChIJY_avbsiTyzsRW9JU6bn6geg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G37" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <v>4188</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -17438,6 +20459,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Banjara+Hills/data=!4m7!3m6!1s0x3bcb973c9c5873a1:0x2940a491f0de08bf!8m2!3d17.4134194!4d78.4276568!16s%2Fg%2F11by_dbs5h!19sChIJoXNYnDyXyzsRvwje8JGkQCk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G38" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>2507</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -17468,6 +20495,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Secunderabad/data=!4m7!3m6!1s0x3bcb9a101536a157:0x4fbfcbf25b9c1602!8m2!3d17.4414333!4d78.4880539!16s%2Fg%2F1td46f3y!19sChIJV6E2FRCayzsRAhacW_LLv08?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G39" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H39" s="14" t="n">
+        <v>6421</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -17498,6 +20531,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Kukatpally/data=!4m7!3m6!1s0x3bcb91f9fa95f95d:0xf3471b49fd532f93!8m2!3d17.495512!4d78.3994334!16s%2Fg%2F11h6m7_vqw!19sChIJXfmV-vmRyzsRky9T_UkbR_M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G40" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>2545</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -17528,6 +20567,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Chaitanyapuri/data=!4m7!3m6!1s0x3bcb99a4d81ed5f7:0xc4937f510b885941!8m2!3d17.3687084!4d78.5325781!16s%2Fg%2F11kbl95gd1!19sChIJ99Ue2KSZyzsRQVmIC1F_k8Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G41" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H41" s="14" t="n">
+        <v>1067</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -17558,6 +20603,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+A.s+Rao+Nagar/data=!4m7!3m6!1s0x3bcb9b47f0228861:0x9970f2f0f46294c9!8m2!3d17.4767773!4d78.5647402!16s%2Fg%2F11l1fnp8hs!19sChIJYYgi8EebyzsRyZRi9PDycJk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G42" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H42" s="14" t="n">
+        <v>800</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -17588,6 +20639,12 @@
           <t>https://www.google.com/maps/place/Dadu%27s+Kompally/data=!4m7!3m6!1s0x3bcb8547f232405d:0xe1b5a93b4c962020!8m2!3d17.5239986!4d78.4830535!16s%2Fg%2F11vzgjlgsk!19sChIJXUAy8keFyzsRICCWTDupteE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
+      <c r="G43" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>549</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -17618,10 +20675,10 @@
           <t>https://www.google.com/maps/place/Dadu%27s/data=!4m7!3m6!1s0x3bcbbb64da0fd53d:0xd3947265d1327d51!8m2!3d17.2351596!4d78.4313221!16s%2Fg%2F11rx1gt4d5!19sChIJPdUP2mS7yzsRUX0y0WVylNM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" s="14" t="n">
         <v>3.9</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="14" t="n">
         <v>19</v>
       </c>
     </row>
@@ -17654,10 +20711,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9344d3dd34e5:0x701ec19a3d8373e1!8m2!3d17.4472944!4d78.3784477!16s%2Fg%2F11ng76x8kt!19sChIJ5TTd00STyzsR4XODPZrBHnA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="G45" s="14" t="n">
         <v>4.3</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="14" t="n">
         <v>5064</v>
       </c>
     </row>
@@ -17690,10 +20747,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb97a0091cc689:0x5f7ee7f4961d390c!8m2!3d17.4191704!4d78.4486398!16s%2Fg%2F11n5wdprb_!19sChIJicYcCaCXyzsRDDkdlvTnfl8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="G46" s="14" t="n">
         <v>4.6</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="14" t="n">
         <v>647</v>
       </c>
     </row>
@@ -17726,10 +20783,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s+-+Aero+Plaza,+Hyderabad/data=!4m7!3m6!1s0x3bcbbbff55e0cb19:0x4268c454a214c7a3!8m2!3d17.237544!4d78.4295774!16s%2Fg%2F11ptph2_n0!19sChIJGcvgVf-7yzsRo8cUolTEaEI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G47" t="n">
+      <c r="G47" s="14" t="n">
         <v>4.8</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="14" t="n">
         <v>2577</v>
       </c>
     </row>
@@ -17762,10 +20819,10 @@
           <t>https://www.google.com/maps/place/Haldirams+-+International+Airport,+Hyderabad/data=!4m7!3m6!1s0x3bcbbbc5450a64d5:0x66e9f016f5a1788a!8m2!3d17.2356242!4d78.4297872!16s%2Fg%2F11y37rf_81!19sChIJ1WQKRcW7yzsRinih9Rbw6WY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G48" t="n">
+      <c r="G48" s="14" t="n">
         <v>4.8</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="14" t="n">
         <v>81</v>
       </c>
     </row>
@@ -17798,10 +20855,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb99d3156ad8a7:0x1f634101e38f8bf1!8m2!3d17.3719005!4d78.5112991!16s%2Fg%2F11sbh9wfj7!19sChIJp9hqFdOZyzsR8YuP4wFBYx8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G49" t="n">
+      <c r="G49" s="14" t="n">
         <v>4.7</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" s="14" t="n">
         <v>4615</v>
       </c>
     </row>
@@ -17834,11 +20891,11 @@
           <t>https://www.google.com/maps/place/Haldiram%27s+-+Begumpet/data=!4m7!3m6!1s0x3bcb9b2fb6226879:0x792f95f1fa86db53!8m2!3d17.4433059!4d78.4779833!16s%2Fg%2F11y1vfjg9x!19sChIJeWgiti-byzsRU9uG-vGVL3k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G50" t="n">
+      <c r="G50" s="14" t="n">
         <v>4.7</v>
       </c>
-      <c r="H50" t="n">
-        <v>3300</v>
+      <c r="H50" s="14" t="n">
+        <v>3301</v>
       </c>
     </row>
     <row r="51">
@@ -17870,10 +20927,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9193207c307b:0x21e95c3d44bbc116!8m2!3d17.434484!4d78.386676!16s%2Fg%2F11mngj1_p3!19sChIJezB8IJORyzsRFsG7RD1c6SE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G51" t="n">
+      <c r="G51" s="14" t="n">
         <v>4.4</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="14" t="n">
         <v>783</v>
       </c>
     </row>
@@ -17906,10 +20963,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb93ac007ef313:0x5752fbf292af5ebc!8m2!3d17.457948!4d78.3636007!16s%2Fg%2F11h8y9pk4d!19sChIJE_N-AKyTyzsRvF6vkvL7Ulc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G52" t="n">
+      <c r="G52" s="14" t="n">
         <v>4.2</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" s="14" t="n">
         <v>1497</v>
       </c>
     </row>
@@ -17942,10 +20999,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcbbb42526f5f6f:0xc737ba21de493937!8m2!3d17.2365531!4d78.4294807!16s%2Fg%2F11rv6lmby8!19sChIJb19vUkK7yzsRNzlJ3iG6N8c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="G53" s="14" t="n">
         <v>4.8</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="14" t="n">
         <v>92</v>
       </c>
     </row>
@@ -17978,10 +21035,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb992d5300c2dd:0x78bb7b7bb178e2a5!8m2!3d17.4004116!4d78.5549239!16s%2Fg%2F11sk8g8pt2!19sChIJ3cIAUy2ZyzsRpeJ4sXt7u3g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="G54" s="14" t="n">
         <v>4.8</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54" s="14" t="n">
         <v>2811</v>
       </c>
     </row>
@@ -18014,10 +21071,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb91b0dd59094f:0x4a980e70f98df750!8m2!3d17.4840645!4d78.3890165!16s%2Fg%2F11rskcz6d0!19sChIJTwlZ3bCRyzsRUPeN-XAOmEo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="G55" s="14" t="n">
         <v>4.3</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="14" t="n">
         <v>709</v>
       </c>
     </row>
@@ -18050,10 +21107,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s+-+Gachibowli+Cloud/data=!4m7!3m6!1s0x3bcb93e8a066f96f:0xdf24b9aaf267c9cb!8m2!3d17.4396118!4d78.3630471!16s%2Fg%2F11kjk464rc!19sChIJb_lmoOiTyzsRy8ln8qq5JN8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G56" t="n">
+      <c r="G56" s="14" t="n">
         <v>4.5</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H56" s="14" t="n">
         <v>289</v>
       </c>
     </row>
@@ -18086,10 +21143,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9771a71af1bd:0x2120c1b9f031a51!8m2!3d17.3544993!4d78.421283!16s%2Fg%2F11kpdgvt17!19sChIJvfEap3GXyzsRURoDnxsMEgI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G57" t="n">
+      <c r="G57" s="14" t="n">
         <v>4.6</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H57" s="14" t="n">
         <v>4514</v>
       </c>
     </row>
@@ -18122,10 +21179,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb990fbe5eacb3:0xe000f43fccaa7968!8m2!3d17.4239975!4d78.4950257!16s%2Fg%2F11ryf8j305!19sChIJs6xevg-ZyzsRaHmqzD_0AOA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G58" t="n">
+      <c r="G58" s="14" t="n">
         <v>4.5</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58" s="14" t="n">
         <v>456</v>
       </c>
     </row>
@@ -18158,10 +21215,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9146f44ba4bd:0xa4cac9184debd8ad!8m2!3d17.4789078!4d78.4738022!16s%2Fg%2F11swvb46nc!19sChIJvaRL9EaRyzsRrdjrTRjJyqQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G59" t="n">
+      <c r="G59" s="14" t="n">
         <v>4.4</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H59" s="14" t="n">
         <v>3008</v>
       </c>
     </row>
@@ -18194,10 +21251,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s/data=!4m7!3m6!1s0x3bcb9320c77fb721:0xba3e7a353ad20f19!8m2!3d17.4344005!4d78.3823429!16s%2Fg%2F11s17v2vrz!19sChIJIbd_xyCTyzsRGQ_SOjV6Pro?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G60" t="n">
+      <c r="G60" s="14" t="n">
         <v>4.2</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H60" s="14" t="n">
         <v>969</v>
       </c>
     </row>
@@ -18230,10 +21287,10 @@
           <t>https://www.google.com/maps/place/Haldiram%27s+-+Nallagandla/data=!4m7!3m6!1s0x3bcb93827c79a5cd:0x5f3be93001f7c002!8m2!3d17.4711734!4d78.3097188!16s%2Fg%2F11y44x1nlx!19sChIJzaV5fIKTyzsRAsD3ATDpO18?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAwNS4wIJJjKgBIAVAD&amp;rclk=1</t>
         </is>
       </c>
-      <c r="G61" t="n">
+      <c r="G61" s="14" t="n">
         <v>4.2</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61" s="14" t="n">
         <v>1075</v>
       </c>
     </row>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -659,7 +659,7 @@
         <v>4.4</v>
       </c>
       <c r="H3" s="14" t="n">
-        <v>4872</v>
+        <v>4873</v>
       </c>
     </row>
     <row r="4">
@@ -731,7 +731,7 @@
         <v>4.5</v>
       </c>
       <c r="H5" s="14" t="n">
-        <v>5552</v>
+        <v>5555</v>
       </c>
     </row>
     <row r="6">
@@ -767,7 +767,7 @@
         <v>4.3</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
     </row>
     <row r="7">
@@ -803,7 +803,7 @@
         <v>4.5</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>2418</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="8">
@@ -839,7 +839,7 @@
         <v>4.4</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>7195</v>
+        <v>7210</v>
       </c>
     </row>
     <row r="9">
@@ -875,7 +875,7 @@
         <v>4.4</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>3647</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="10">
@@ -911,7 +911,7 @@
         <v>4.4</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>2780</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="11">
@@ -1019,7 +1019,7 @@
         <v>4.7</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>2245</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="14">
@@ -1091,7 +1091,7 @@
         <v>4.4</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>2592</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="16">
@@ -1127,7 +1127,7 @@
         <v>4.5</v>
       </c>
       <c r="H16" s="14" t="n">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="17">
@@ -1199,7 +1199,7 @@
         <v>4.5</v>
       </c>
       <c r="H18" s="14" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19">
@@ -1235,7 +1235,7 @@
         <v>4.7</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="20">
@@ -1271,7 +1271,7 @@
         <v>4.6</v>
       </c>
       <c r="H20" s="14" t="n">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="21">
@@ -1307,7 +1307,7 @@
         <v>4.6</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="22">
@@ -1451,7 +1451,7 @@
         <v>4.8</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>706</v>
+        <v>712</v>
       </c>
     </row>
     <row r="26">
@@ -1483,7 +1483,7 @@
         <v>4.9</v>
       </c>
       <c r="H26" s="14" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -1689,7 +1689,7 @@
         <v>4.6</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="6">
@@ -1730,7 +1730,7 @@
         <v>4.6</v>
       </c>
       <c r="I6" s="14" t="n">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7">
@@ -1812,7 +1812,7 @@
         <v>4.5</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="9">
@@ -2017,7 +2017,7 @@
         <v>4.9</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="14">
@@ -2099,7 +2099,7 @@
         <v>4.4</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>7198</v>
+        <v>7210</v>
       </c>
     </row>
     <row r="16">
@@ -2263,7 +2263,7 @@
         <v>4.3</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
     </row>
     <row r="20">
@@ -2304,7 +2304,7 @@
         <v>4.4</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>2780</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="21">
@@ -2468,7 +2468,7 @@
         <v>4.2</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>12237</v>
+        <v>12238</v>
       </c>
     </row>
     <row r="25">
@@ -2509,7 +2509,7 @@
         <v>4.3</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="26">
@@ -2550,7 +2550,7 @@
         <v>4.6</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="27">
@@ -2591,7 +2591,7 @@
         <v>4.4</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>3647</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="28">
@@ -2673,7 +2673,7 @@
         <v>4.4</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>4872</v>
+        <v>4873</v>
       </c>
     </row>
     <row r="30">
@@ -2714,7 +2714,7 @@
         <v>4.5</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>1161</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="31">
@@ -2755,7 +2755,7 @@
         <v>4.7</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>2245</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="32">
@@ -2837,7 +2837,7 @@
         <v>4.5</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>5552</v>
+        <v>5555</v>
       </c>
     </row>
     <row r="34">
@@ -3001,7 +3001,7 @@
         <v>4.5</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>2418</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="38">
@@ -3042,7 +3042,7 @@
         <v>4.5</v>
       </c>
       <c r="I38" s="14" t="n">
-        <v>2418</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="39">
@@ -3083,7 +3083,7 @@
         <v>4.4</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>2592</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="40">
@@ -3124,7 +3124,7 @@
         <v>4.5</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="41">
@@ -3206,7 +3206,7 @@
         <v>4.3</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>11746</v>
+        <v>11747</v>
       </c>
     </row>
     <row r="43">
@@ -3247,7 +3247,7 @@
         <v>4.6</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="44">
@@ -3370,7 +3370,7 @@
         <v>4.3</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="47">
@@ -3452,7 +3452,7 @@
         <v>4.7</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="49">
@@ -3736,10 +3736,10 @@
         </is>
       </c>
       <c r="H55" s="14" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>706</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56">
@@ -3821,7 +3821,7 @@
         <v>4.6</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>1847</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="58">
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="H59" s="14" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I59" s="14" t="n">
-        <v>264</v>
+        <v>5783</v>
       </c>
     </row>
     <row r="60">
@@ -3944,7 +3944,7 @@
         <v>4.2</v>
       </c>
       <c r="I60" s="14" t="n">
-        <v>6559</v>
+        <v>6560</v>
       </c>
     </row>
     <row r="61">
@@ -4026,7 +4026,7 @@
         <v>4.2</v>
       </c>
       <c r="I62" s="14" t="n">
-        <v>2067</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="63">
@@ -4063,8 +4063,12 @@
           <t>Pair 1</t>
         </is>
       </c>
-      <c r="H63" s="14" t="n"/>
-      <c r="I63" s="14" t="n"/>
+      <c r="H63" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I63" s="14" t="n">
+        <v>878</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -4104,7 +4108,7 @@
         <v>4.3</v>
       </c>
       <c r="I64" s="14" t="n">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="65">
@@ -4145,7 +4149,7 @@
         <v>4.2</v>
       </c>
       <c r="I65" s="14" t="n">
-        <v>28</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="66">
@@ -4268,7 +4272,7 @@
         <v>4.2</v>
       </c>
       <c r="I68" s="14" t="n">
-        <v>14378</v>
+        <v>14379</v>
       </c>
     </row>
   </sheetData>
@@ -4555,7 +4559,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>10890</v>
+        <v>10892</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -4596,7 +4600,7 @@
         <v>4.2</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>2941</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -4716,10 +4720,10 @@
         </is>
       </c>
       <c r="H11" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>144</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -4757,10 +4761,10 @@
         </is>
       </c>
       <c r="H12" s="14" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>340</v>
+        <v>656</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -4801,7 +4805,7 @@
         <v>4.3</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>2496</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -4839,10 +4843,10 @@
         </is>
       </c>
       <c r="H14" s="14" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>108</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -4880,10 +4884,10 @@
         </is>
       </c>
       <c r="H15" s="14" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -4921,10 +4925,10 @@
         </is>
       </c>
       <c r="H16" s="14" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>5554</v>
+        <v>15765</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -4962,10 +4966,10 @@
         </is>
       </c>
       <c r="H17" s="14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>66</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -5003,10 +5007,10 @@
         </is>
       </c>
       <c r="H18" s="14" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>1623</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -5085,10 +5089,10 @@
         </is>
       </c>
       <c r="H20" s="14" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>102</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -5211,7 +5215,7 @@
         <v>4.3</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>6218</v>
+        <v>6219</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -5290,10 +5294,10 @@
         </is>
       </c>
       <c r="H25" s="14" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>1</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -5334,7 +5338,7 @@
         <v>4.6</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>1909</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -5375,7 +5379,7 @@
         <v>4.2</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>13</v>
+        <v>8411</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -5416,7 +5420,7 @@
         <v>4.5</v>
       </c>
       <c r="I28" s="14" t="n">
-        <v>10035</v>
+        <v>10036</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -5495,10 +5499,10 @@
         </is>
       </c>
       <c r="H30" s="14" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I30" s="14" t="n">
-        <v>29500</v>
+        <v>21971</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -5611,7 +5615,7 @@
         <v>4.4</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>4872</v>
+        <v>4873</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -5647,7 +5651,7 @@
         <v>4.5</v>
       </c>
       <c r="I34" s="14" t="n">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -5680,10 +5684,10 @@
         </is>
       </c>
       <c r="H35" s="14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>18</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -5716,10 +5720,10 @@
         </is>
       </c>
       <c r="H36" s="14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I36" s="14" t="n">
-        <v>69</v>
+        <v>694</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -5827,7 +5831,7 @@
         <v>4</v>
       </c>
       <c r="I39" s="14" t="n">
-        <v>23004</v>
+        <v>23006</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -5863,7 +5867,7 @@
         <v>4.3</v>
       </c>
       <c r="I40" s="14" t="n">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -5899,7 +5903,7 @@
         <v>4.5</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -5935,7 +5939,7 @@
         <v>4.5</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>2418</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -5968,10 +5972,10 @@
         </is>
       </c>
       <c r="H43" s="14" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>143</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -6004,10 +6008,10 @@
         </is>
       </c>
       <c r="H44" s="14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>292</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -6079,7 +6083,7 @@
         <v>4.4</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>7200</v>
+        <v>7210</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -6112,10 +6116,10 @@
         </is>
       </c>
       <c r="H47" s="14" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I47" s="14" t="n">
-        <v>3369</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -6151,7 +6155,7 @@
         <v>4.4</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>3647</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -6223,7 +6227,7 @@
         <v>4.4</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>5595</v>
+        <v>5599</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -6292,10 +6296,10 @@
         </is>
       </c>
       <c r="H52" s="14" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>1012</v>
+        <v>790</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -6331,7 +6335,7 @@
         <v>4</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>9649</v>
+        <v>9651</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -6547,7 +6551,7 @@
         <v>4.5</v>
       </c>
       <c r="I59" s="14" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -6619,7 +6623,7 @@
         <v>4.4</v>
       </c>
       <c r="I61" s="14" t="n">
-        <v>2922</v>
+        <v>2921</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -6727,7 +6731,7 @@
         <v>3.9</v>
       </c>
       <c r="I64" s="14" t="n">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -6832,10 +6836,10 @@
         </is>
       </c>
       <c r="H67" s="14" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="I67" s="14" t="n">
-        <v>10369</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -6871,7 +6875,7 @@
         <v>4.5</v>
       </c>
       <c r="I68" s="14" t="n">
-        <v>4304</v>
+        <v>4306</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -6907,7 +6911,7 @@
         <v>4.7</v>
       </c>
       <c r="I69" s="14" t="n">
-        <v>2214</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -6979,7 +6983,7 @@
         <v>4.3</v>
       </c>
       <c r="I71" s="14" t="n">
-        <v>6142</v>
+        <v>6144</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -7051,7 +7055,7 @@
         <v>4.3</v>
       </c>
       <c r="I73" s="14" t="n">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -7123,7 +7127,7 @@
         <v>4.2</v>
       </c>
       <c r="I75" s="14" t="n">
-        <v>16972</v>
+        <v>16973</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -7159,7 +7163,7 @@
         <v>4</v>
       </c>
       <c r="I76" s="14" t="n">
-        <v>8561</v>
+        <v>8562</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -7195,7 +7199,7 @@
         <v>4.7</v>
       </c>
       <c r="I77" s="14" t="n">
-        <v>2473</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -7379,7 +7383,7 @@
         <v>4.4</v>
       </c>
       <c r="I82" s="14" t="n">
-        <v>1445</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -7412,10 +7416,10 @@
         </is>
       </c>
       <c r="H83" s="14" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I83" s="14" t="n">
-        <v>1741</v>
+        <v>22671</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -7484,10 +7488,10 @@
         </is>
       </c>
       <c r="H85" s="14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I85" s="14" t="n">
-        <v>3952</v>
+        <v>456</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -7556,10 +7560,10 @@
         </is>
       </c>
       <c r="H87" s="14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I87" s="14" t="n">
-        <v>4507</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -7628,10 +7632,10 @@
         </is>
       </c>
       <c r="H89" s="14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I89" s="14" t="n">
-        <v>118</v>
+        <v>8389</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -7700,10 +7704,10 @@
         </is>
       </c>
       <c r="H91" s="14" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I91" s="14" t="n">
-        <v>119</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -7736,10 +7740,10 @@
         </is>
       </c>
       <c r="H92" s="14" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I92" s="14" t="n">
-        <v>388</v>
+        <v>27283</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -7808,10 +7812,10 @@
         </is>
       </c>
       <c r="H94" s="14" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I94" s="14" t="n">
-        <v>7200</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -7916,10 +7920,10 @@
         </is>
       </c>
       <c r="H97" s="14" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I97" s="14" t="n">
-        <v>359</v>
+        <v>43969</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -7955,7 +7959,7 @@
         <v>4.4</v>
       </c>
       <c r="I98" s="14" t="n">
-        <v>42235</v>
+        <v>42236</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -7988,10 +7992,10 @@
         </is>
       </c>
       <c r="H99" s="14" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I99" s="14" t="n">
-        <v>310</v>
+        <v>12477</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -8060,10 +8064,10 @@
         </is>
       </c>
       <c r="H101" s="14" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I101" s="14" t="n">
-        <v>289</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -8096,10 +8100,10 @@
         </is>
       </c>
       <c r="H102" s="14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I102" s="14" t="n">
-        <v>7201</v>
+        <v>49</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
@@ -8135,7 +8139,7 @@
         <v>4.4</v>
       </c>
       <c r="I103" s="14" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -8240,10 +8244,10 @@
         </is>
       </c>
       <c r="H106" s="14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I106" s="14" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -8348,10 +8352,10 @@
         </is>
       </c>
       <c r="H109" s="14" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="I109" s="14" t="n">
-        <v>1425</v>
+        <v>64</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -8710,7 +8714,7 @@
         <v>4.4</v>
       </c>
       <c r="I118" s="14" t="n">
-        <v>2780</v>
+        <v>2782</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -9079,7 +9083,7 @@
         <v>4.2</v>
       </c>
       <c r="I127" s="14" t="n">
-        <v>4191</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -9228,7 +9232,7 @@
         <v>4.6</v>
       </c>
       <c r="I131" s="14" t="n">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -9264,7 +9268,7 @@
         <v>4.8</v>
       </c>
       <c r="I132" s="14" t="n">
-        <v>706</v>
+        <v>712</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -9372,7 +9376,7 @@
         <v>4.9</v>
       </c>
       <c r="I135" s="14" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -9408,7 +9412,7 @@
         <v>4.9</v>
       </c>
       <c r="I136" s="14" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -9444,7 +9448,7 @@
         <v>4.2</v>
       </c>
       <c r="I137" s="14" t="n">
-        <v>5277</v>
+        <v>5282</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -9516,7 +9520,7 @@
         <v>4</v>
       </c>
       <c r="I139" s="14" t="n">
-        <v>3197</v>
+        <v>3198</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -9552,7 +9556,7 @@
         <v>4.4</v>
       </c>
       <c r="I140" s="14" t="n">
-        <v>1445</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -9660,7 +9664,7 @@
         <v>4.1</v>
       </c>
       <c r="I143" s="14" t="n">
-        <v>4194</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -9732,7 +9736,7 @@
         <v>3.8</v>
       </c>
       <c r="I145" s="14" t="n">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -10056,7 +10060,7 @@
         <v>4</v>
       </c>
       <c r="I154" s="14" t="n">
-        <v>9246</v>
+        <v>9245</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -10092,7 +10096,7 @@
         <v>4.5</v>
       </c>
       <c r="I155" s="14" t="n">
-        <v>4304</v>
+        <v>4306</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -10305,10 +10309,10 @@
         </is>
       </c>
       <c r="H161" s="14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I161" s="14" t="n">
-        <v>137</v>
+        <v>114</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -10344,7 +10348,7 @@
         <v>4.2</v>
       </c>
       <c r="I162" s="14" t="n">
-        <v>1944</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -10596,7 +10600,7 @@
         <v>4.8</v>
       </c>
       <c r="I169" s="14" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -11568,7 +11572,7 @@
         <v>4.7</v>
       </c>
       <c r="I196" s="14" t="n">
-        <v>2669</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
@@ -11640,7 +11644,7 @@
         <v>4.6</v>
       </c>
       <c r="I198" s="14" t="n">
-        <v>8994</v>
+        <v>8991</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
@@ -11784,7 +11788,7 @@
         <v>4</v>
       </c>
       <c r="I202" s="14" t="n">
-        <v>2883</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
@@ -11820,7 +11824,7 @@
         <v>4.8</v>
       </c>
       <c r="I203" s="14" t="n">
-        <v>17008</v>
+        <v>17010</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
@@ -12042,7 +12046,7 @@
         <v>4.5</v>
       </c>
       <c r="H3" s="14" t="n">
-        <v>7008</v>
+        <v>7013</v>
       </c>
     </row>
     <row r="4">
@@ -12078,7 +12082,7 @@
         <v>4.6</v>
       </c>
       <c r="H4" s="14" t="n">
-        <v>1720</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="5">
@@ -12186,7 +12190,7 @@
         <v>4.7</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>1110</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="8">
@@ -12258,7 +12262,7 @@
         <v>4.7</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>1970</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="10">
@@ -12294,7 +12298,7 @@
         <v>4.6</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="11">
@@ -12363,10 +12367,10 @@
         </is>
       </c>
       <c r="G12" s="14" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>812</v>
+        <v>3417</v>
       </c>
     </row>
     <row r="13">
@@ -12402,7 +12406,7 @@
         <v>4.6</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>406</v>
+        <v>415</v>
       </c>
     </row>
     <row r="14">
@@ -12438,7 +12442,7 @@
         <v>4.7</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>3469</v>
+        <v>3471</v>
       </c>
     </row>
     <row r="15">
@@ -12510,7 +12514,7 @@
         <v>4.6</v>
       </c>
       <c r="H16" s="14" t="n">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="17">
@@ -12582,7 +12586,7 @@
         <v>4.5</v>
       </c>
       <c r="H18" s="14" t="n">
-        <v>4496</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="19">
@@ -12654,7 +12658,7 @@
         <v>4.6</v>
       </c>
       <c r="H20" s="14" t="n">
-        <v>4379</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="21">
@@ -12690,7 +12694,7 @@
         <v>4.4</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>3859</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="22">
@@ -12834,7 +12838,7 @@
         <v>4.6</v>
       </c>
       <c r="H25" s="14" t="n">
-        <v>3365</v>
+        <v>3368</v>
       </c>
     </row>
     <row r="26">
@@ -12906,7 +12910,7 @@
         <v>4.6</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="28">
@@ -12978,7 +12982,7 @@
         <v>4.6</v>
       </c>
       <c r="H29" s="14" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="30">
@@ -13338,7 +13342,7 @@
         <v>4.2</v>
       </c>
       <c r="H39" s="14" t="n">
-        <v>851</v>
+        <v>857</v>
       </c>
     </row>
     <row r="40">
@@ -13374,7 +13378,7 @@
         <v>4.3</v>
       </c>
       <c r="H40" s="14" t="n">
-        <v>2236</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="41">
@@ -13554,7 +13558,7 @@
         <v>4.3</v>
       </c>
       <c r="H45" s="14" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="46">
@@ -13587,10 +13591,10 @@
         </is>
       </c>
       <c r="G46" s="14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H46" s="14" t="n">
-        <v>937</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="47">
@@ -13623,10 +13627,10 @@
         </is>
       </c>
       <c r="G47" s="14" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="H47" s="14" t="n">
-        <v>2569</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="48">
@@ -13770,7 +13774,7 @@
         <v>4.1</v>
       </c>
       <c r="H51" s="14" t="n">
-        <v>2808</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="52">
@@ -13842,7 +13846,7 @@
         <v>4.1</v>
       </c>
       <c r="H53" s="14" t="n">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="54">
@@ -13914,7 +13918,7 @@
         <v>4.4</v>
       </c>
       <c r="H55" s="14" t="n">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="56">
@@ -14513,7 +14517,7 @@
         <v>4.3</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="11">
@@ -14621,7 +14625,7 @@
         <v>4.2</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>21269</v>
+        <v>21270</v>
       </c>
     </row>
     <row r="14">
@@ -14657,7 +14661,7 @@
         <v>4.6</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>2948</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="15">
@@ -14693,7 +14697,7 @@
         <v>4.4</v>
       </c>
       <c r="H15" s="14" t="n">
-        <v>4205</v>
+        <v>4206</v>
       </c>
     </row>
     <row r="16">
@@ -14762,10 +14766,10 @@
         </is>
       </c>
       <c r="G17" s="14" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>415</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -14873,7 +14877,7 @@
         <v>4.3</v>
       </c>
       <c r="H20" s="14" t="n">
-        <v>9247</v>
+        <v>9248</v>
       </c>
     </row>
     <row r="21">
@@ -14981,7 +14985,7 @@
         <v>4.5</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>1755</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="24">
@@ -15125,7 +15129,7 @@
         <v>4.2</v>
       </c>
       <c r="H27" s="14" t="n">
-        <v>11091</v>
+        <v>11092</v>
       </c>
     </row>
     <row r="28">
@@ -15233,7 +15237,7 @@
         <v>4.5</v>
       </c>
       <c r="H30" s="14" t="n">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="31">
@@ -15269,7 +15273,7 @@
         <v>4.5</v>
       </c>
       <c r="H31" s="14" t="n">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="32">
@@ -15305,7 +15309,7 @@
         <v>4.4</v>
       </c>
       <c r="H32" s="14" t="n">
-        <v>2811</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="33">
@@ -15377,7 +15381,7 @@
         <v>4.1</v>
       </c>
       <c r="H34" s="14" t="n">
-        <v>39702</v>
+        <v>39704</v>
       </c>
     </row>
     <row r="35">
@@ -15665,7 +15669,7 @@
         <v>4.1</v>
       </c>
       <c r="H42" s="14" t="n">
-        <v>1445</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="43">
@@ -15953,7 +15957,7 @@
         <v>4.9</v>
       </c>
       <c r="H50" s="14" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51">
@@ -15989,7 +15993,7 @@
         <v>4.2</v>
       </c>
       <c r="H51" s="14" t="n">
-        <v>4120</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="52">
@@ -16025,7 +16029,7 @@
         <v>4.6</v>
       </c>
       <c r="H52" s="14" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53">
@@ -16058,10 +16062,10 @@
         </is>
       </c>
       <c r="G53" s="14" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="H53" s="14" t="n">
-        <v>4120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54">
@@ -16097,7 +16101,7 @@
         <v>4.2</v>
       </c>
       <c r="H54" s="14" t="n">
-        <v>4120</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="55">
@@ -16277,7 +16281,7 @@
         <v>4.5</v>
       </c>
       <c r="H59" s="14" t="n">
-        <v>2882</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="60">
@@ -16349,7 +16353,7 @@
         <v>4.2</v>
       </c>
       <c r="H61" s="14" t="n">
-        <v>7836</v>
+        <v>7838</v>
       </c>
     </row>
     <row r="62">
@@ -16529,7 +16533,7 @@
         <v>4.1</v>
       </c>
       <c r="H66" s="14" t="n">
-        <v>6445</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="67">
@@ -16601,7 +16605,7 @@
         <v>4.3</v>
       </c>
       <c r="H68" s="14" t="n">
-        <v>19110</v>
+        <v>19111</v>
       </c>
     </row>
     <row r="69">
@@ -16817,7 +16821,7 @@
         <v>4.9</v>
       </c>
       <c r="H74" s="14" t="n">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="75">
@@ -17105,7 +17109,7 @@
         <v>4.3</v>
       </c>
       <c r="H82" s="14" t="n">
-        <v>11746</v>
+        <v>11747</v>
       </c>
     </row>
     <row r="83">
@@ -17537,7 +17541,7 @@
         <v>4.2</v>
       </c>
       <c r="H94" s="14" t="n">
-        <v>2595</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="95">
@@ -17573,7 +17577,7 @@
         <v>4.3</v>
       </c>
       <c r="H95" s="14" t="n">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="96">
@@ -17717,7 +17721,7 @@
         <v>4.5</v>
       </c>
       <c r="H99" s="14" t="n">
-        <v>5583</v>
+        <v>5584</v>
       </c>
     </row>
     <row r="100">
@@ -17753,7 +17757,7 @@
         <v>4.4</v>
       </c>
       <c r="H100" s="14" t="n">
-        <v>17792</v>
+        <v>17798</v>
       </c>
     </row>
     <row r="101">
@@ -17789,7 +17793,7 @@
         <v>4.5</v>
       </c>
       <c r="H101" s="14" t="n">
-        <v>6181</v>
+        <v>6180</v>
       </c>
     </row>
     <row r="102">
@@ -17969,7 +17973,7 @@
         <v>4.1</v>
       </c>
       <c r="H106" s="14" t="n">
-        <v>10979</v>
+        <v>10980</v>
       </c>
     </row>
     <row r="107">
@@ -18113,7 +18117,7 @@
         <v>4.4</v>
       </c>
       <c r="H110" s="14" t="n">
-        <v>1882</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="111">
@@ -18146,10 +18150,10 @@
         </is>
       </c>
       <c r="G111" s="14" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="H111" s="14" t="n">
-        <v>4616</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="112">
@@ -18185,7 +18189,7 @@
         <v>4.4</v>
       </c>
       <c r="H112" s="14" t="n">
-        <v>2456</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="113">
@@ -18235,7 +18239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18258,6 +18262,12 @@
       <c r="H1" s="11" t="n">
         <v>46304</v>
       </c>
+      <c r="I1" s="11" t="n">
+        <v>46305</v>
+      </c>
+      <c r="J1" s="11" t="n">
+        <v>46305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -18296,6 +18306,16 @@
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -18336,6 +18356,12 @@
       <c r="H3" s="14" t="n">
         <v>14378</v>
       </c>
+      <c r="I3" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>14379</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -18372,6 +18398,12 @@
       <c r="H4" s="14" t="n">
         <v>1202</v>
       </c>
+      <c r="I4" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>1203</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -18408,6 +18440,12 @@
       <c r="H5" s="14" t="n">
         <v>15</v>
       </c>
+      <c r="I5" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -18444,6 +18482,12 @@
       <c r="H6" s="14" t="n">
         <v>62</v>
       </c>
+      <c r="I6" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -18480,6 +18524,12 @@
       <c r="H7" s="14" t="n">
         <v>4838</v>
       </c>
+      <c r="I7" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>4838</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -18516,6 +18566,12 @@
       <c r="H8" s="14" t="n">
         <v>2067</v>
       </c>
+      <c r="I8" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>2068</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -18552,6 +18608,12 @@
       <c r="H9" s="14" t="n">
         <v>5782</v>
       </c>
+      <c r="I9" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>5783</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -18588,6 +18650,12 @@
       <c r="H10" s="14" t="n">
         <v>6559</v>
       </c>
+      <c r="I10" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>6560</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -18624,6 +18692,12 @@
       <c r="H11" s="14" t="n">
         <v>10577</v>
       </c>
+      <c r="I11" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>10577</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -18660,6 +18734,12 @@
       <c r="H12" s="14" t="n">
         <v>12237</v>
       </c>
+      <c r="I12" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>12238</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -18696,6 +18776,12 @@
       <c r="H13" s="14" t="n">
         <v>10702</v>
       </c>
+      <c r="I13" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>10702</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -18732,6 +18818,12 @@
       <c r="H14" s="14" t="n">
         <v>6811</v>
       </c>
+      <c r="I14" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>6811</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -18768,6 +18860,12 @@
       <c r="H15" s="14" t="n">
         <v>3606</v>
       </c>
+      <c r="I15" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>3606</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -18804,6 +18902,12 @@
       <c r="H16" s="14" t="n">
         <v>4505</v>
       </c>
+      <c r="I16" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>4504</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -18840,6 +18944,12 @@
       <c r="H17" s="14" t="n">
         <v>878</v>
       </c>
+      <c r="I17" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>878</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -18876,6 +18986,12 @@
       <c r="H18" s="14" t="n">
         <v>19721</v>
       </c>
+      <c r="I18" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>19722</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -18912,6 +19028,12 @@
       <c r="H19" s="14" t="n">
         <v>2022</v>
       </c>
+      <c r="I19" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>2022</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -18948,6 +19070,12 @@
       <c r="H20" s="14" t="n">
         <v>2056</v>
       </c>
+      <c r="I20" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>2058</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -18984,6 +19112,12 @@
       <c r="H21" s="14" t="n">
         <v>8785</v>
       </c>
+      <c r="I21" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>8787</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -19020,6 +19154,12 @@
       <c r="H22" s="14" t="n">
         <v>1120</v>
       </c>
+      <c r="I22" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>1120</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -19056,6 +19196,12 @@
       <c r="H23" s="14" t="n">
         <v>676</v>
       </c>
+      <c r="I23" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>676</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -19090,6 +19236,12 @@
         <v>4</v>
       </c>
       <c r="H24" s="14" t="n">
+        <v>1823</v>
+      </c>
+      <c r="I24" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" s="14" t="n">
         <v>1823</v>
       </c>
     </row>
@@ -19104,7 +19256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -19127,6 +19279,12 @@
       <c r="H1" s="11" t="n">
         <v>46304</v>
       </c>
+      <c r="I1" s="11" t="n">
+        <v>46305</v>
+      </c>
+      <c r="J1" s="11" t="n">
+        <v>46305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -19165,6 +19323,16 @@
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -19205,6 +19373,12 @@
       <c r="H3" s="14" t="n">
         <v>1595</v>
       </c>
+      <c r="I3" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -19241,6 +19415,12 @@
       <c r="H4" s="14" t="n">
         <v>1041</v>
       </c>
+      <c r="I4" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>1041</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -19277,6 +19457,12 @@
       <c r="H5" s="14" t="n">
         <v>1981</v>
       </c>
+      <c r="I5" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>1981</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -19313,6 +19499,12 @@
       <c r="H6" s="14" t="n">
         <v>1187</v>
       </c>
+      <c r="I6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -19349,6 +19541,12 @@
       <c r="H7" s="14" t="n">
         <v>1412</v>
       </c>
+      <c r="I7" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>1412</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -19385,6 +19583,12 @@
       <c r="H8" s="14" t="n">
         <v>24</v>
       </c>
+      <c r="I8" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -19421,6 +19625,12 @@
       <c r="H9" s="14" t="n">
         <v>1133</v>
       </c>
+      <c r="I9" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>1133</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -19457,6 +19667,12 @@
       <c r="H10" s="14" t="n">
         <v>722</v>
       </c>
+      <c r="I10" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>722</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -19493,6 +19709,12 @@
       <c r="H11" s="14" t="n">
         <v>25</v>
       </c>
+      <c r="I11" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -19529,6 +19751,12 @@
       <c r="H12" s="14" t="n">
         <v>23</v>
       </c>
+      <c r="I12" s="14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -19565,6 +19793,12 @@
       <c r="H13" s="14" t="n">
         <v>93</v>
       </c>
+      <c r="I13" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -19601,6 +19835,12 @@
       <c r="H14" s="14" t="n">
         <v>73</v>
       </c>
+      <c r="I14" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -19637,6 +19877,12 @@
       <c r="H15" s="14" t="n">
         <v>562</v>
       </c>
+      <c r="I15" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>562</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -19673,6 +19919,12 @@
       <c r="H16" s="14" t="n">
         <v>14</v>
       </c>
+      <c r="I16" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -19709,6 +19961,12 @@
       <c r="H17" s="14" t="n">
         <v>5840</v>
       </c>
+      <c r="I17" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>5845</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -19745,6 +20003,12 @@
       <c r="H18" s="14" t="n">
         <v>1127</v>
       </c>
+      <c r="I18" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>1129</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -19781,6 +20045,12 @@
       <c r="H19" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="I19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -19817,6 +20087,12 @@
       <c r="H20" s="14" t="n">
         <v>2472</v>
       </c>
+      <c r="I20" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>2472</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -19853,6 +20129,12 @@
       <c r="H21" s="14" t="n">
         <v>341</v>
       </c>
+      <c r="I21" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>341</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -19889,6 +20171,12 @@
       <c r="H22" s="14" t="n">
         <v>4357</v>
       </c>
+      <c r="I22" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>4357</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -19925,6 +20213,12 @@
       <c r="H23" s="14" t="n">
         <v>11258</v>
       </c>
+      <c r="I23" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>11258</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -19961,6 +20255,12 @@
       <c r="H24" s="14" t="n">
         <v>13831</v>
       </c>
+      <c r="I24" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>13832</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -19997,6 +20297,12 @@
       <c r="H25" s="14" t="n">
         <v>5024</v>
       </c>
+      <c r="I25" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>5024</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -20033,6 +20339,12 @@
       <c r="H26" s="14" t="n">
         <v>8084</v>
       </c>
+      <c r="I26" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>8085</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -20069,6 +20381,12 @@
       <c r="H27" s="14" t="n">
         <v>7820</v>
       </c>
+      <c r="I27" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>7822</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -20105,6 +20423,12 @@
       <c r="H28" s="14" t="n">
         <v>6652</v>
       </c>
+      <c r="I28" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>6652</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -20141,6 +20465,12 @@
       <c r="H29" s="14" t="n">
         <v>1155</v>
       </c>
+      <c r="I29" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>1155</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -20177,6 +20507,12 @@
       <c r="H30" s="14" t="n">
         <v>4943</v>
       </c>
+      <c r="I30" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>4943</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -20213,6 +20549,12 @@
       <c r="H31" s="14" t="n">
         <v>8066</v>
       </c>
+      <c r="I31" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>8066</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -20249,6 +20591,12 @@
       <c r="H32" s="14" t="n">
         <v>8451</v>
       </c>
+      <c r="I32" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>8451</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -20285,6 +20633,12 @@
       <c r="H33" s="14" t="n">
         <v>4182</v>
       </c>
+      <c r="I33" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>4182</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -20321,6 +20675,12 @@
       <c r="H34" s="14" t="n">
         <v>22</v>
       </c>
+      <c r="I34" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -20357,6 +20717,12 @@
       <c r="H35" s="14" t="n">
         <v>4429</v>
       </c>
+      <c r="I35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>4429</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -20393,6 +20759,12 @@
       <c r="H36" s="14" t="n">
         <v>5551</v>
       </c>
+      <c r="I36" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>5551</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -20429,6 +20801,12 @@
       <c r="H37" s="14" t="n">
         <v>4188</v>
       </c>
+      <c r="I37" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>4188</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -20465,6 +20843,12 @@
       <c r="H38" s="14" t="n">
         <v>2507</v>
       </c>
+      <c r="I38" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>2513</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -20501,6 +20885,12 @@
       <c r="H39" s="14" t="n">
         <v>6421</v>
       </c>
+      <c r="I39" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J39" s="14" t="n">
+        <v>6421</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -20537,6 +20927,12 @@
       <c r="H40" s="14" t="n">
         <v>2545</v>
       </c>
+      <c r="I40" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>2545</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -20573,6 +20969,12 @@
       <c r="H41" s="14" t="n">
         <v>1067</v>
       </c>
+      <c r="I41" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J41" s="14" t="n">
+        <v>1070</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -20609,6 +21011,12 @@
       <c r="H42" s="14" t="n">
         <v>800</v>
       </c>
+      <c r="I42" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J42" s="14" t="n">
+        <v>801</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -20645,6 +21053,12 @@
       <c r="H43" s="14" t="n">
         <v>549</v>
       </c>
+      <c r="I43" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J43" s="14" t="n">
+        <v>548</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -20681,6 +21095,12 @@
       <c r="H44" s="14" t="n">
         <v>19</v>
       </c>
+      <c r="I44" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J44" s="14" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -20717,6 +21137,12 @@
       <c r="H45" s="14" t="n">
         <v>5064</v>
       </c>
+      <c r="I45" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J45" s="14" t="n">
+        <v>5066</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -20753,6 +21179,12 @@
       <c r="H46" s="14" t="n">
         <v>647</v>
       </c>
+      <c r="I46" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J46" s="14" t="n">
+        <v>647</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -20789,6 +21221,12 @@
       <c r="H47" s="14" t="n">
         <v>2577</v>
       </c>
+      <c r="I47" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J47" s="14" t="n">
+        <v>2577</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -20825,6 +21263,12 @@
       <c r="H48" s="14" t="n">
         <v>81</v>
       </c>
+      <c r="I48" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J48" s="14" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -20861,6 +21305,12 @@
       <c r="H49" s="14" t="n">
         <v>4615</v>
       </c>
+      <c r="I49" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J49" s="14" t="n">
+        <v>4621</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -20897,6 +21347,12 @@
       <c r="H50" s="14" t="n">
         <v>3301</v>
       </c>
+      <c r="I50" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J50" s="14" t="n">
+        <v>3301</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -20933,6 +21389,12 @@
       <c r="H51" s="14" t="n">
         <v>783</v>
       </c>
+      <c r="I51" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J51" s="14" t="n">
+        <v>783</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -20969,6 +21431,12 @@
       <c r="H52" s="14" t="n">
         <v>1497</v>
       </c>
+      <c r="I52" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J52" s="14" t="n">
+        <v>1497</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -21005,6 +21473,12 @@
       <c r="H53" s="14" t="n">
         <v>92</v>
       </c>
+      <c r="I53" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J53" s="14" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -21041,6 +21515,12 @@
       <c r="H54" s="14" t="n">
         <v>2811</v>
       </c>
+      <c r="I54" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J54" s="14" t="n">
+        <v>2811</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -21077,6 +21557,12 @@
       <c r="H55" s="14" t="n">
         <v>709</v>
       </c>
+      <c r="I55" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J55" s="14" t="n">
+        <v>709</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -21113,6 +21599,12 @@
       <c r="H56" s="14" t="n">
         <v>289</v>
       </c>
+      <c r="I56" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J56" s="14" t="n">
+        <v>288</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -21149,6 +21641,12 @@
       <c r="H57" s="14" t="n">
         <v>4514</v>
       </c>
+      <c r="I57" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J57" s="14" t="n">
+        <v>4516</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -21185,6 +21683,12 @@
       <c r="H58" s="14" t="n">
         <v>456</v>
       </c>
+      <c r="I58" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J58" s="14" t="n">
+        <v>456</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -21221,6 +21725,12 @@
       <c r="H59" s="14" t="n">
         <v>3008</v>
       </c>
+      <c r="I59" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v>3008</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -21257,6 +21767,12 @@
       <c r="H60" s="14" t="n">
         <v>969</v>
       </c>
+      <c r="I60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J60" s="14" t="n">
+        <v>968</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -21292,6 +21808,12 @@
       </c>
       <c r="H61" s="14" t="n">
         <v>1075</v>
+      </c>
+      <c r="I61" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J61" s="14" t="n">
+        <v>1076</v>
       </c>
     </row>
   </sheetData>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -583,6 +583,12 @@
       <c r="H1" s="11" t="n">
         <v>46304</v>
       </c>
+      <c r="I1" s="11" t="n">
+        <v>46305</v>
+      </c>
+      <c r="J1" s="11" t="n">
+        <v>46305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -621,6 +627,16 @@
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -661,6 +677,12 @@
       <c r="H3" s="14" t="n">
         <v>4873</v>
       </c>
+      <c r="I3" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>4875</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -697,6 +719,12 @@
       <c r="H4" s="14" t="n">
         <v>15765</v>
       </c>
+      <c r="I4" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>15765</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -733,6 +761,12 @@
       <c r="H5" s="14" t="n">
         <v>5555</v>
       </c>
+      <c r="I5" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>5558</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -769,6 +803,12 @@
       <c r="H6" s="14" t="n">
         <v>6549</v>
       </c>
+      <c r="I6" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>6557</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -805,6 +845,12 @@
       <c r="H7" s="14" t="n">
         <v>2412</v>
       </c>
+      <c r="I7" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>2426</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -841,6 +887,12 @@
       <c r="H8" s="14" t="n">
         <v>7210</v>
       </c>
+      <c r="I8" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>7192</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -877,6 +929,12 @@
       <c r="H9" s="14" t="n">
         <v>3645</v>
       </c>
+      <c r="I9" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>3648</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -913,6 +971,12 @@
       <c r="H10" s="14" t="n">
         <v>2782</v>
       </c>
+      <c r="I10" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>2792</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -949,6 +1013,12 @@
       <c r="H11" s="14" t="n">
         <v>1116</v>
       </c>
+      <c r="I11" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>1120</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -985,6 +1055,12 @@
       <c r="H12" s="14" t="n">
         <v>1107</v>
       </c>
+      <c r="I12" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>1109</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -1021,6 +1097,12 @@
       <c r="H13" s="14" t="n">
         <v>2255</v>
       </c>
+      <c r="I13" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>2279</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -1057,6 +1139,12 @@
       <c r="H14" s="14" t="n">
         <v>2378</v>
       </c>
+      <c r="I14" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>2384</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1093,6 +1181,12 @@
       <c r="H15" s="14" t="n">
         <v>2598</v>
       </c>
+      <c r="I15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>2604</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1129,6 +1223,12 @@
       <c r="H16" s="14" t="n">
         <v>894</v>
       </c>
+      <c r="I16" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>895</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -1165,6 +1265,12 @@
       <c r="H17" s="14" t="n">
         <v>1332</v>
       </c>
+      <c r="I17" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>1333</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -1201,6 +1307,12 @@
       <c r="H18" s="14" t="n">
         <v>456</v>
       </c>
+      <c r="I18" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>461</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -1237,6 +1349,12 @@
       <c r="H19" s="14" t="n">
         <v>918</v>
       </c>
+      <c r="I19" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>919</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -1273,6 +1391,12 @@
       <c r="H20" s="14" t="n">
         <v>1099</v>
       </c>
+      <c r="I20" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>1098</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -1309,6 +1433,12 @@
       <c r="H21" s="14" t="n">
         <v>788</v>
       </c>
+      <c r="I21" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>789</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -1345,6 +1475,12 @@
       <c r="H22" s="14" t="n">
         <v>660</v>
       </c>
+      <c r="I22" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>660</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -1381,6 +1517,12 @@
       <c r="H23" s="14" t="n">
         <v>694</v>
       </c>
+      <c r="I23" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>698</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -1417,6 +1559,12 @@
       <c r="H24" s="14" t="n">
         <v>1425</v>
       </c>
+      <c r="I24" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>1424</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -1453,6 +1601,12 @@
       <c r="H25" s="14" t="n">
         <v>712</v>
       </c>
+      <c r="I25" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>720</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1484,6 +1638,12 @@
       </c>
       <c r="H26" s="14" t="n">
         <v>376</v>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -1497,7 +1657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1521,6 +1681,12 @@
       <c r="I1" s="11" t="n">
         <v>46304</v>
       </c>
+      <c r="J1" s="11" t="n">
+        <v>46305</v>
+      </c>
+      <c r="K1" s="11" t="n">
+        <v>46305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -1564,6 +1730,16 @@
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="K2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1609,6 +1785,12 @@
       <c r="I3" s="14" t="n">
         <v>694</v>
       </c>
+      <c r="J3" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>698</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -1650,6 +1832,12 @@
       <c r="I4" s="14" t="n">
         <v>81</v>
       </c>
+      <c r="J4" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -1691,6 +1879,12 @@
       <c r="I5" s="14" t="n">
         <v>788</v>
       </c>
+      <c r="J5" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>789</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1732,6 +1926,12 @@
       <c r="I6" s="14" t="n">
         <v>788</v>
       </c>
+      <c r="J6" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>789</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1773,6 +1973,12 @@
       <c r="I7" s="14" t="n">
         <v>660</v>
       </c>
+      <c r="J7" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>660</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1814,6 +2020,12 @@
       <c r="I8" s="14" t="n">
         <v>894</v>
       </c>
+      <c r="J8" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>895</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1855,6 +2067,12 @@
       <c r="I9" s="14" t="n">
         <v>3266</v>
       </c>
+      <c r="J9" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>3269</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1896,6 +2114,12 @@
       <c r="I10" s="14" t="n">
         <v>3266</v>
       </c>
+      <c r="J10" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>3269</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1937,6 +2161,12 @@
       <c r="I11" s="14" t="n">
         <v>1425</v>
       </c>
+      <c r="J11" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>1424</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1978,6 +2208,12 @@
       <c r="I12" s="14" t="n">
         <v>1192</v>
       </c>
+      <c r="J12" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -2019,6 +2255,12 @@
       <c r="I13" s="14" t="n">
         <v>756</v>
       </c>
+      <c r="J13" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>756</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -2060,6 +2302,12 @@
       <c r="I14" s="14" t="n">
         <v>6811</v>
       </c>
+      <c r="J14" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K14" s="14" t="n">
+        <v>6813</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -2101,6 +2349,12 @@
       <c r="I15" s="14" t="n">
         <v>7210</v>
       </c>
+      <c r="J15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K15" s="14" t="n">
+        <v>7192</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -2142,6 +2396,12 @@
       <c r="I16" s="14" t="n">
         <v>2629</v>
       </c>
+      <c r="J16" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -2183,6 +2443,12 @@
       <c r="I17" s="14" t="n">
         <v>1823</v>
       </c>
+      <c r="J17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>1824</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -2224,6 +2490,12 @@
       <c r="I18" s="14" t="n">
         <v>4504</v>
       </c>
+      <c r="J18" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>4504</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -2265,6 +2537,12 @@
       <c r="I19" s="14" t="n">
         <v>6549</v>
       </c>
+      <c r="J19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>6557</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -2306,6 +2584,12 @@
       <c r="I20" s="14" t="n">
         <v>2782</v>
       </c>
+      <c r="J20" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>2792</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -2347,6 +2631,12 @@
       <c r="I21" s="14" t="n">
         <v>15765</v>
       </c>
+      <c r="J21" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <v>15765</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2388,6 +2678,12 @@
       <c r="I22" s="14" t="n">
         <v>15765</v>
       </c>
+      <c r="J22" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K22" s="14" t="n">
+        <v>15765</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -2429,6 +2725,12 @@
       <c r="I23" s="14" t="n">
         <v>10577</v>
       </c>
+      <c r="J23" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>10578</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -2470,6 +2772,12 @@
       <c r="I24" s="14" t="n">
         <v>12238</v>
       </c>
+      <c r="J24" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>12239</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -2511,6 +2819,12 @@
       <c r="I25" s="14" t="n">
         <v>2010</v>
       </c>
+      <c r="J25" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>2016</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -2552,6 +2866,12 @@
       <c r="I26" s="14" t="n">
         <v>847</v>
       </c>
+      <c r="J26" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>850</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -2593,6 +2913,12 @@
       <c r="I27" s="14" t="n">
         <v>3645</v>
       </c>
+      <c r="J27" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K27" s="14" t="n">
+        <v>3648</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -2634,6 +2960,12 @@
       <c r="I28" s="14" t="n">
         <v>3606</v>
       </c>
+      <c r="J28" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K28" s="14" t="n">
+        <v>3606</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -2675,6 +3007,12 @@
       <c r="I29" s="14" t="n">
         <v>4873</v>
       </c>
+      <c r="J29" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>4875</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -2716,6 +3054,12 @@
       <c r="I30" s="14" t="n">
         <v>1163</v>
       </c>
+      <c r="J30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>1164</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -2757,6 +3101,12 @@
       <c r="I31" s="14" t="n">
         <v>2255</v>
       </c>
+      <c r="J31" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>2279</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -2798,6 +3148,12 @@
       <c r="I32" s="14" t="n">
         <v>1043</v>
       </c>
+      <c r="J32" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" s="14" t="n">
+        <v>1044</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -2839,6 +3195,12 @@
       <c r="I33" s="14" t="n">
         <v>5555</v>
       </c>
+      <c r="J33" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K33" s="14" t="n">
+        <v>5558</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -2880,6 +3242,12 @@
       <c r="I34" s="14" t="n">
         <v>1131</v>
       </c>
+      <c r="J34" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K34" s="14" t="n">
+        <v>1132</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -2921,6 +3289,12 @@
       <c r="I35" s="14" t="n">
         <v>4838</v>
       </c>
+      <c r="J35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>4839</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -2962,6 +3336,12 @@
       <c r="I36" s="14" t="n">
         <v>1107</v>
       </c>
+      <c r="J36" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K36" s="14" t="n">
+        <v>1109</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -3003,6 +3383,12 @@
       <c r="I37" s="14" t="n">
         <v>2412</v>
       </c>
+      <c r="J37" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K37" s="14" t="n">
+        <v>2426</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -3044,6 +3430,12 @@
       <c r="I38" s="14" t="n">
         <v>2412</v>
       </c>
+      <c r="J38" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K38" s="14" t="n">
+        <v>2426</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -3085,6 +3477,12 @@
       <c r="I39" s="14" t="n">
         <v>2598</v>
       </c>
+      <c r="J39" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K39" s="14" t="n">
+        <v>2604</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -3126,6 +3524,12 @@
       <c r="I40" s="14" t="n">
         <v>456</v>
       </c>
+      <c r="J40" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K40" s="14" t="n">
+        <v>461</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -3167,6 +3571,12 @@
       <c r="I41" s="14" t="n">
         <v>1116</v>
       </c>
+      <c r="J41" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K41" s="14" t="n">
+        <v>1120</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -3208,6 +3618,12 @@
       <c r="I42" s="14" t="n">
         <v>11747</v>
       </c>
+      <c r="J42" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K42" s="14" t="n">
+        <v>11751</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -3249,6 +3665,12 @@
       <c r="I43" s="14" t="n">
         <v>1099</v>
       </c>
+      <c r="J43" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K43" s="14" t="n">
+        <v>1098</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -3290,6 +3712,12 @@
       <c r="I44" s="14" t="n">
         <v>1332</v>
       </c>
+      <c r="J44" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K44" s="14" t="n">
+        <v>1333</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -3331,6 +3759,12 @@
       <c r="I45" s="14" t="n">
         <v>192</v>
       </c>
+      <c r="J45" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K45" s="14" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -3372,6 +3806,12 @@
       <c r="I46" s="14" t="n">
         <v>2010</v>
       </c>
+      <c r="J46" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K46" s="14" t="n">
+        <v>2016</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -3413,6 +3853,12 @@
       <c r="I47" s="14" t="n">
         <v>2378</v>
       </c>
+      <c r="J47" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K47" s="14" t="n">
+        <v>2384</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -3454,6 +3900,12 @@
       <c r="I48" s="14" t="n">
         <v>918</v>
       </c>
+      <c r="J48" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K48" s="14" t="n">
+        <v>919</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -3495,6 +3947,12 @@
       <c r="I49" s="14" t="n">
         <v>1775</v>
       </c>
+      <c r="J49" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K49" s="14" t="n">
+        <v>1775</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -3536,6 +3994,12 @@
       <c r="I50" s="14" t="n">
         <v>2629</v>
       </c>
+      <c r="J50" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K50" s="14" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -3577,6 +4041,12 @@
       <c r="I51" s="14" t="n">
         <v>5934</v>
       </c>
+      <c r="J51" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K51" s="14" t="n">
+        <v>5937</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -3618,6 +4088,12 @@
       <c r="I52" s="14" t="n">
         <v>1566</v>
       </c>
+      <c r="J52" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K52" s="14" t="n">
+        <v>1566</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -3659,6 +4135,12 @@
       <c r="I53" s="14" t="n">
         <v>4658</v>
       </c>
+      <c r="J53" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K53" s="14" t="n">
+        <v>4660</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -3700,6 +4182,12 @@
       <c r="I54" s="14" t="n">
         <v>5290</v>
       </c>
+      <c r="J54" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K54" s="14" t="n">
+        <v>5290</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -3741,6 +4229,12 @@
       <c r="I55" s="14" t="n">
         <v>170</v>
       </c>
+      <c r="J55" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K55" s="14" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -3782,6 +4276,12 @@
       <c r="I56" s="14" t="n">
         <v>4165</v>
       </c>
+      <c r="J56" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K56" s="14" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -3823,6 +4323,12 @@
       <c r="I57" s="14" t="n">
         <v>1848</v>
       </c>
+      <c r="J57" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K57" s="14" t="n">
+        <v>1851</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -3864,6 +4370,12 @@
       <c r="I58" s="14" t="n">
         <v>4658</v>
       </c>
+      <c r="J58" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K58" s="14" t="n">
+        <v>4660</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -3905,6 +4417,12 @@
       <c r="I59" s="14" t="n">
         <v>5783</v>
       </c>
+      <c r="J59" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v>5783</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -3946,6 +4464,12 @@
       <c r="I60" s="14" t="n">
         <v>6560</v>
       </c>
+      <c r="J60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K60" s="14" t="n">
+        <v>6560</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -3987,6 +4511,12 @@
       <c r="I61" s="14" t="n">
         <v>10702</v>
       </c>
+      <c r="J61" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K61" s="14" t="n">
+        <v>10708</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -4028,6 +4558,12 @@
       <c r="I62" s="14" t="n">
         <v>2068</v>
       </c>
+      <c r="J62" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K62" s="14" t="n">
+        <v>2069</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -4069,6 +4605,12 @@
       <c r="I63" s="14" t="n">
         <v>878</v>
       </c>
+      <c r="J63" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K63" s="14" t="n">
+        <v>878</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -4110,6 +4652,12 @@
       <c r="I64" s="14" t="n">
         <v>1203</v>
       </c>
+      <c r="J64" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v>1204</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -4151,6 +4699,12 @@
       <c r="I65" s="14" t="n">
         <v>2068</v>
       </c>
+      <c r="J65" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K65" s="14" t="n">
+        <v>2069</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -4192,6 +4746,12 @@
       <c r="I66" s="14" t="n">
         <v>73</v>
       </c>
+      <c r="J66" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K66" s="14" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -4233,6 +4793,12 @@
       <c r="I67" s="14" t="n">
         <v>886</v>
       </c>
+      <c r="J67" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K67" s="14" t="n">
+        <v>886</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -4273,6 +4839,12 @@
       </c>
       <c r="I68" s="14" t="n">
         <v>14379</v>
+      </c>
+      <c r="J68" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K68" s="14" t="n">
+        <v>14381</v>
       </c>
     </row>
   </sheetData>
@@ -4286,7 +4858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I206"/>
+  <dimension ref="A1:K206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4309,6 +4881,12 @@
       <c r="I1" s="11" t="n">
         <v>46304</v>
       </c>
+      <c r="J1" s="11" t="n">
+        <v>46305</v>
+      </c>
+      <c r="K1" s="11" t="n">
+        <v>46305</v>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
@@ -4352,6 +4930,16 @@
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="K2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -4397,6 +4985,12 @@
       <c r="I3" s="14" t="n">
         <v>2124</v>
       </c>
+      <c r="J3" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>2128</v>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="7" t="n">
@@ -4438,6 +5032,12 @@
       <c r="I4" s="14" t="n">
         <v>634</v>
       </c>
+      <c r="J4" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>634</v>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="7" t="n">
@@ -4479,6 +5079,12 @@
       <c r="I5" s="14" t="n">
         <v>1555</v>
       </c>
+      <c r="J5" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>1556</v>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="7" t="n">
@@ -4520,6 +5126,12 @@
       <c r="I6" s="14" t="n">
         <v>138</v>
       </c>
+      <c r="J6" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="n">
@@ -4561,6 +5173,12 @@
       <c r="I7" s="14" t="n">
         <v>10892</v>
       </c>
+      <c r="J7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>10894</v>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="7" t="n">
@@ -4602,6 +5220,12 @@
       <c r="I8" s="14" t="n">
         <v>2943</v>
       </c>
+      <c r="J8" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>2945</v>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="7" t="n">
@@ -4643,6 +5267,12 @@
       <c r="I9" s="14" t="n">
         <v>218</v>
       </c>
+      <c r="J9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>221</v>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="7" t="n">
@@ -4684,6 +5314,12 @@
       <c r="I10" s="14" t="n">
         <v>5139</v>
       </c>
+      <c r="J10" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>5139</v>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="7" t="n">
@@ -4725,6 +5361,12 @@
       <c r="I11" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="J11" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>52638</v>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="7" t="n">
@@ -4766,6 +5408,12 @@
       <c r="I12" s="14" t="n">
         <v>656</v>
       </c>
+      <c r="J12" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>340</v>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="7" t="n">
@@ -4807,6 +5455,12 @@
       <c r="I13" s="14" t="n">
         <v>2501</v>
       </c>
+      <c r="J13" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>2508</v>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="7" t="n">
@@ -4848,6 +5502,12 @@
       <c r="I14" s="14" t="n">
         <v>245</v>
       </c>
+      <c r="J14" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K14" s="14" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="n">
@@ -4889,6 +5549,12 @@
       <c r="I15" s="14" t="n">
         <v>14</v>
       </c>
+      <c r="J15" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K15" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="7" t="n">
@@ -4930,6 +5596,12 @@
       <c r="I16" s="14" t="n">
         <v>15765</v>
       </c>
+      <c r="J16" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>452</v>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="n">
@@ -4971,6 +5643,12 @@
       <c r="I17" s="14" t="n">
         <v>220</v>
       </c>
+      <c r="J17" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>2656</v>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="7" t="n">
@@ -5012,6 +5690,12 @@
       <c r="I18" s="14" t="n">
         <v>1866</v>
       </c>
+      <c r="J18" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <v>1624</v>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="7" t="n">
@@ -5053,6 +5737,12 @@
       <c r="I19" s="14" t="n">
         <v>607</v>
       </c>
+      <c r="J19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>607</v>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="7" t="n">
@@ -5094,6 +5784,12 @@
       <c r="I20" s="14" t="n">
         <v>40</v>
       </c>
+      <c r="J20" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="7" t="n">
@@ -5135,6 +5831,12 @@
       <c r="I21" s="14" t="n">
         <v>15</v>
       </c>
+      <c r="J21" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="7" t="n">
@@ -5176,6 +5878,12 @@
       <c r="I22" s="14" t="n">
         <v>6287</v>
       </c>
+      <c r="J22" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K22" s="14" t="n">
+        <v>6297</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="7" t="n">
@@ -5217,6 +5925,12 @@
       <c r="I23" s="14" t="n">
         <v>6219</v>
       </c>
+      <c r="J23" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K23" s="14" t="n">
+        <v>6223</v>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="7" t="n">
@@ -5258,6 +5972,12 @@
       <c r="I24" s="14" t="n">
         <v>13126</v>
       </c>
+      <c r="J24" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>13126</v>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="7" t="n">
@@ -5299,6 +6019,12 @@
       <c r="I25" s="14" t="n">
         <v>173</v>
       </c>
+      <c r="J25" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>2365</v>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="7" t="n">
@@ -5340,6 +6066,12 @@
       <c r="I26" s="14" t="n">
         <v>1913</v>
       </c>
+      <c r="J26" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>1919</v>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="7" t="n">
@@ -5381,6 +6113,12 @@
       <c r="I27" s="14" t="n">
         <v>8411</v>
       </c>
+      <c r="J27" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K27" s="14" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="7" t="n">
@@ -5422,6 +6160,12 @@
       <c r="I28" s="14" t="n">
         <v>10036</v>
       </c>
+      <c r="J28" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K28" s="14" t="n">
+        <v>10038</v>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="7" t="n">
@@ -5463,6 +6207,12 @@
       <c r="I29" s="14" t="n">
         <v>8673</v>
       </c>
+      <c r="J29" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>8674</v>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="n">
@@ -5504,6 +6254,12 @@
       <c r="I30" s="14" t="n">
         <v>21971</v>
       </c>
+      <c r="J30" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K30" s="14" t="n">
+        <v>22267</v>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="7" t="n">
@@ -5545,6 +6301,12 @@
       <c r="I31" s="14" t="n">
         <v>5576</v>
       </c>
+      <c r="J31" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>5576</v>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="7" t="n">
@@ -5581,6 +6343,12 @@
       <c r="I32" s="14" t="n">
         <v>11</v>
       </c>
+      <c r="J32" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K32" s="14" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="7" t="n">
@@ -5617,6 +6385,12 @@
       <c r="I33" s="14" t="n">
         <v>4873</v>
       </c>
+      <c r="J33" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K33" s="14" t="n">
+        <v>4875</v>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="7" t="n">
@@ -5653,6 +6427,12 @@
       <c r="I34" s="14" t="n">
         <v>894</v>
       </c>
+      <c r="J34" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K34" s="14" t="n">
+        <v>895</v>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="7" t="n">
@@ -5689,6 +6469,12 @@
       <c r="I35" s="14" t="n">
         <v>63</v>
       </c>
+      <c r="J35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="7" t="n">
@@ -5725,6 +6511,12 @@
       <c r="I36" s="14" t="n">
         <v>694</v>
       </c>
+      <c r="J36" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K36" s="14" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="7" t="n">
@@ -5761,6 +6553,12 @@
       <c r="I37" s="14" t="n">
         <v>1332</v>
       </c>
+      <c r="J37" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K37" s="14" t="n">
+        <v>1333</v>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="7" t="n">
@@ -5797,6 +6595,12 @@
       <c r="I38" s="14" t="n">
         <v>2688</v>
       </c>
+      <c r="J38" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K38" s="14" t="n">
+        <v>2688</v>
+      </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="7" t="n">
@@ -5833,6 +6637,12 @@
       <c r="I39" s="14" t="n">
         <v>23006</v>
       </c>
+      <c r="J39" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="14" t="n">
+        <v>23007</v>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="7" t="n">
@@ -5869,6 +6679,12 @@
       <c r="I40" s="14" t="n">
         <v>572</v>
       </c>
+      <c r="J40" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K40" s="14" t="n">
+        <v>572</v>
+      </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="7" t="n">
@@ -5905,6 +6721,12 @@
       <c r="I41" s="14" t="n">
         <v>456</v>
       </c>
+      <c r="J41" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K41" s="14" t="n">
+        <v>461</v>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="7" t="n">
@@ -5941,6 +6763,12 @@
       <c r="I42" s="14" t="n">
         <v>2412</v>
       </c>
+      <c r="J42" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K42" s="14" t="n">
+        <v>2426</v>
+      </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="7" t="n">
@@ -5977,6 +6805,12 @@
       <c r="I43" s="14" t="n">
         <v>2255</v>
       </c>
+      <c r="J43" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K43" s="14" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="7" t="n">
@@ -6013,6 +6847,12 @@
       <c r="I44" s="14" t="n">
         <v>1358</v>
       </c>
+      <c r="J44" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K44" s="14" t="n">
+        <v>6557</v>
+      </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="7" t="n">
@@ -6049,6 +6889,12 @@
       <c r="I45" s="14" t="n">
         <v>1107</v>
       </c>
+      <c r="J45" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K45" s="14" t="n">
+        <v>1109</v>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="7" t="n">
@@ -6085,6 +6931,12 @@
       <c r="I46" s="14" t="n">
         <v>7210</v>
       </c>
+      <c r="J46" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K46" s="14" t="n">
+        <v>7192</v>
+      </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="7" t="n">
@@ -6121,6 +6973,12 @@
       <c r="I47" s="14" t="n">
         <v>56</v>
       </c>
+      <c r="J47" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K47" s="14" t="n">
+        <v>3820</v>
+      </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="7" t="n">
@@ -6157,6 +7015,12 @@
       <c r="I48" s="14" t="n">
         <v>3645</v>
       </c>
+      <c r="J48" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K48" s="14" t="n">
+        <v>3648</v>
+      </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="7" t="n">
@@ -6193,6 +7057,12 @@
       <c r="I49" s="14" t="n">
         <v>2378</v>
       </c>
+      <c r="J49" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K49" s="14" t="n">
+        <v>2384</v>
+      </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="7" t="n">
@@ -6229,6 +7099,12 @@
       <c r="I50" s="14" t="n">
         <v>5599</v>
       </c>
+      <c r="J50" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K50" s="14" t="n">
+        <v>5606</v>
+      </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="7" t="n">
@@ -6265,6 +7141,12 @@
       <c r="I51" s="14" t="n">
         <v>1007</v>
       </c>
+      <c r="J51" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K51" s="14" t="n">
+        <v>1007</v>
+      </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="7" t="n">
@@ -6301,6 +7183,12 @@
       <c r="I52" s="14" t="n">
         <v>790</v>
       </c>
+      <c r="J52" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K52" s="14" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="7" t="n">
@@ -6337,6 +7225,12 @@
       <c r="I53" s="14" t="n">
         <v>9651</v>
       </c>
+      <c r="J53" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" s="14" t="n">
+        <v>9652</v>
+      </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="7" t="n">
@@ -6373,6 +7267,12 @@
       <c r="I54" s="14" t="n">
         <v>796</v>
       </c>
+      <c r="J54" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K54" s="14" t="n">
+        <v>796</v>
+      </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="7" t="n">
@@ -6409,6 +7309,12 @@
       <c r="I55" s="14" t="n">
         <v>298</v>
       </c>
+      <c r="J55" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K55" s="14" t="n">
+        <v>298</v>
+      </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="7" t="n">
@@ -6445,6 +7351,12 @@
       <c r="I56" s="14" t="n">
         <v>51</v>
       </c>
+      <c r="J56" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K56" s="14" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="7" t="n">
@@ -6481,6 +7393,12 @@
       <c r="I57" s="14" t="n">
         <v>439</v>
       </c>
+      <c r="J57" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K57" s="14" t="n">
+        <v>441</v>
+      </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="7" t="n">
@@ -6517,6 +7435,12 @@
       <c r="I58" s="14" t="n">
         <v>203</v>
       </c>
+      <c r="J58" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K58" s="14" t="n">
+        <v>203</v>
+      </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="7" t="n">
@@ -6553,6 +7477,12 @@
       <c r="I59" s="14" t="n">
         <v>659</v>
       </c>
+      <c r="J59" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v>659</v>
+      </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="7" t="n">
@@ -6589,6 +7519,12 @@
       <c r="I60" s="14" t="n">
         <v>361</v>
       </c>
+      <c r="J60" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K60" s="14" t="n">
+        <v>361</v>
+      </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="7" t="n">
@@ -6625,6 +7561,12 @@
       <c r="I61" s="14" t="n">
         <v>2921</v>
       </c>
+      <c r="J61" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K61" s="14" t="n">
+        <v>2921</v>
+      </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="7" t="n">
@@ -6661,6 +7603,12 @@
       <c r="I62" s="14" t="n">
         <v>585</v>
       </c>
+      <c r="J62" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K62" s="14" t="n">
+        <v>587</v>
+      </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="7" t="n">
@@ -6697,6 +7645,12 @@
       <c r="I63" s="14" t="n">
         <v>9259</v>
       </c>
+      <c r="J63" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K63" s="14" t="n">
+        <v>9258</v>
+      </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="7" t="n">
@@ -6733,6 +7687,12 @@
       <c r="I64" s="14" t="n">
         <v>1008</v>
       </c>
+      <c r="J64" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v>1008</v>
+      </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="7" t="n">
@@ -6769,6 +7729,12 @@
       <c r="I65" s="14" t="n">
         <v>3845</v>
       </c>
+      <c r="J65" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K65" s="14" t="n">
+        <v>3845</v>
+      </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="7" t="n">
@@ -6805,6 +7771,12 @@
       <c r="I66" s="14" t="n">
         <v>4138</v>
       </c>
+      <c r="J66" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K66" s="14" t="n">
+        <v>4139</v>
+      </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="7" t="n">
@@ -6841,6 +7813,12 @@
       <c r="I67" s="14" t="n">
         <v>44</v>
       </c>
+      <c r="J67" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K67" s="14" t="n">
+        <v>26860</v>
+      </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="7" t="n">
@@ -6877,6 +7855,12 @@
       <c r="I68" s="14" t="n">
         <v>4306</v>
       </c>
+      <c r="J68" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K68" s="14" t="n">
+        <v>4321</v>
+      </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="7" t="n">
@@ -6913,6 +7897,12 @@
       <c r="I69" s="14" t="n">
         <v>2255</v>
       </c>
+      <c r="J69" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K69" s="14" t="n">
+        <v>2279</v>
+      </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="7" t="n">
@@ -6949,6 +7939,12 @@
       <c r="I70" s="14" t="n">
         <v>280</v>
       </c>
+      <c r="J70" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K70" s="14" t="n">
+        <v>280</v>
+      </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="7" t="n">
@@ -6985,6 +7981,12 @@
       <c r="I71" s="14" t="n">
         <v>6144</v>
       </c>
+      <c r="J71" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K71" s="14" t="n">
+        <v>6145</v>
+      </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="7" t="n">
@@ -7021,6 +8023,12 @@
       <c r="I72" s="14" t="n">
         <v>47</v>
       </c>
+      <c r="J72" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K72" s="14" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="7" t="n">
@@ -7057,6 +8065,12 @@
       <c r="I73" s="14" t="n">
         <v>1110</v>
       </c>
+      <c r="J73" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K73" s="14" t="n">
+        <v>1111</v>
+      </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="7" t="n">
@@ -7093,6 +8107,12 @@
       <c r="I74" s="14" t="n">
         <v>9514</v>
       </c>
+      <c r="J74" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K74" s="14" t="n">
+        <v>9514</v>
+      </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="7" t="n">
@@ -7129,6 +8149,12 @@
       <c r="I75" s="14" t="n">
         <v>16973</v>
       </c>
+      <c r="J75" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K75" s="14" t="n">
+        <v>16974</v>
+      </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="7" t="n">
@@ -7165,6 +8191,12 @@
       <c r="I76" s="14" t="n">
         <v>8562</v>
       </c>
+      <c r="J76" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" s="14" t="n">
+        <v>8565</v>
+      </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="7" t="n">
@@ -7201,6 +8233,12 @@
       <c r="I77" s="14" t="n">
         <v>2481</v>
       </c>
+      <c r="J77" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K77" s="14" t="n">
+        <v>2487</v>
+      </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="7" t="n">
@@ -7237,6 +8275,12 @@
       <c r="I78" s="14" t="n">
         <v>10943</v>
       </c>
+      <c r="J78" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K78" s="14" t="n">
+        <v>10945</v>
+      </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="7" t="n">
@@ -7273,6 +8317,12 @@
       <c r="I79" s="14" t="n">
         <v>175</v>
       </c>
+      <c r="J79" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K79" s="14" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="7" t="n">
@@ -7309,6 +8359,12 @@
       <c r="I80" s="14" t="n">
         <v>148</v>
       </c>
+      <c r="J80" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K80" s="14" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="7" t="n">
@@ -7349,6 +8405,16 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="J81" s="15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K81" s="15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="7" t="n">
@@ -7385,6 +8451,12 @@
       <c r="I82" s="14" t="n">
         <v>1447</v>
       </c>
+      <c r="J82" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K82" s="14" t="n">
+        <v>1452</v>
+      </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="7" t="n">
@@ -7421,6 +8493,12 @@
       <c r="I83" s="14" t="n">
         <v>22671</v>
       </c>
+      <c r="J83" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K83" s="14" t="n">
+        <v>1741</v>
+      </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="7" t="n">
@@ -7457,6 +8535,12 @@
       <c r="I84" s="14" t="n">
         <v>43</v>
       </c>
+      <c r="J84" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K84" s="14" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="7" t="n">
@@ -7493,6 +8577,12 @@
       <c r="I85" s="14" t="n">
         <v>456</v>
       </c>
+      <c r="J85" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K85" s="14" t="n">
+        <v>461</v>
+      </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="7" t="n">
@@ -7529,6 +8619,12 @@
       <c r="I86" s="14" t="n">
         <v>45</v>
       </c>
+      <c r="J86" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K86" s="14" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="7" t="n">
@@ -7565,6 +8661,12 @@
       <c r="I87" s="14" t="n">
         <v>9</v>
       </c>
+      <c r="J87" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K87" s="14" t="n">
+        <v>4508</v>
+      </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="7" t="n">
@@ -7601,6 +8703,12 @@
       <c r="I88" s="14" t="n">
         <v>23</v>
       </c>
+      <c r="J88" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K88" s="14" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="7" t="n">
@@ -7637,6 +8745,12 @@
       <c r="I89" s="14" t="n">
         <v>8389</v>
       </c>
+      <c r="J89" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K89" s="14" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="7" t="n">
@@ -7673,6 +8787,12 @@
       <c r="I90" s="14" t="n">
         <v>14</v>
       </c>
+      <c r="J90" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K90" s="14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="7" t="n">
@@ -7709,6 +8829,12 @@
       <c r="I91" s="14" t="n">
         <v>19</v>
       </c>
+      <c r="J91" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K91" s="14" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="7" t="n">
@@ -7745,6 +8871,12 @@
       <c r="I92" s="14" t="n">
         <v>27283</v>
       </c>
+      <c r="J92" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K92" s="14" t="n">
+        <v>391</v>
+      </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="7" t="n">
@@ -7781,6 +8913,12 @@
       <c r="I93" s="14" t="n">
         <v>160</v>
       </c>
+      <c r="J93" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K93" s="14" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="7" t="n">
@@ -7817,6 +8955,12 @@
       <c r="I94" s="14" t="n">
         <v>1624</v>
       </c>
+      <c r="J94" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K94" s="14" t="n">
+        <v>1624</v>
+      </c>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="7" t="n">
@@ -7853,6 +8997,12 @@
       <c r="I95" s="14" t="n">
         <v>7498</v>
       </c>
+      <c r="J95" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K95" s="14" t="n">
+        <v>7500</v>
+      </c>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="7" t="n">
@@ -7889,6 +9039,12 @@
       <c r="I96" s="14" t="n">
         <v>2838</v>
       </c>
+      <c r="J96" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K96" s="14" t="n">
+        <v>2838</v>
+      </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="7" t="n">
@@ -7925,6 +9081,12 @@
       <c r="I97" s="14" t="n">
         <v>43969</v>
       </c>
+      <c r="J97" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K97" s="14" t="n">
+        <v>359</v>
+      </c>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="7" t="n">
@@ -7961,6 +9123,12 @@
       <c r="I98" s="14" t="n">
         <v>42236</v>
       </c>
+      <c r="J98" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K98" s="14" t="n">
+        <v>42241</v>
+      </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="7" t="n">
@@ -7997,6 +9165,12 @@
       <c r="I99" s="14" t="n">
         <v>12477</v>
       </c>
+      <c r="J99" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K99" s="14" t="n">
+        <v>44063</v>
+      </c>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="7" t="n">
@@ -8033,6 +9207,12 @@
       <c r="I100" s="14" t="n">
         <v>344</v>
       </c>
+      <c r="J100" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K100" s="14" t="n">
+        <v>344</v>
+      </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="7" t="n">
@@ -8069,6 +9249,12 @@
       <c r="I101" s="14" t="n">
         <v>23</v>
       </c>
+      <c r="J101" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K101" s="14" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="7" t="n">
@@ -8105,6 +9291,12 @@
       <c r="I102" s="14" t="n">
         <v>49</v>
       </c>
+      <c r="J102" s="14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K102" s="14" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="7" t="n">
@@ -8141,6 +9333,12 @@
       <c r="I103" s="14" t="n">
         <v>862</v>
       </c>
+      <c r="J103" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K103" s="14" t="n">
+        <v>865</v>
+      </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="7" t="n">
@@ -8177,6 +9375,12 @@
       <c r="I104" s="14" t="n">
         <v>428</v>
       </c>
+      <c r="J104" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K104" s="14" t="n">
+        <v>429</v>
+      </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="7" t="n">
@@ -8213,6 +9417,12 @@
       <c r="I105" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="J105" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K105" s="14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="7" t="n">
@@ -8249,6 +9459,12 @@
       <c r="I106" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="J106" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K106" s="14" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="7" t="n">
@@ -8285,6 +9501,12 @@
       <c r="I107" s="14" t="n">
         <v>4255</v>
       </c>
+      <c r="J107" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K107" s="14" t="n">
+        <v>4256</v>
+      </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="7" t="n">
@@ -8321,6 +9543,12 @@
       <c r="I108" s="14" t="n">
         <v>3</v>
       </c>
+      <c r="J108" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K108" s="14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="7" t="n">
@@ -8357,6 +9585,12 @@
       <c r="I109" s="14" t="n">
         <v>64</v>
       </c>
+      <c r="J109" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K109" s="14" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="7" t="n">
@@ -8393,6 +9627,12 @@
       <c r="I110" s="14" t="n">
         <v>100</v>
       </c>
+      <c r="J110" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K110" s="14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="7" t="n">
@@ -8429,6 +9669,12 @@
       <c r="I111" s="14" t="n">
         <v>866</v>
       </c>
+      <c r="J111" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K111" s="14" t="n">
+        <v>866</v>
+      </c>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="7" t="n">
@@ -8470,6 +9716,12 @@
       <c r="I112" s="14" t="n">
         <v>8411</v>
       </c>
+      <c r="J112" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K112" s="14" t="n">
+        <v>8426</v>
+      </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="7" t="n">
@@ -8511,6 +9763,12 @@
       <c r="I113" s="14" t="n">
         <v>4900</v>
       </c>
+      <c r="J113" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K113" s="14" t="n">
+        <v>4895</v>
+      </c>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="7" t="n">
@@ -8552,6 +9810,12 @@
       <c r="I114" s="14" t="n">
         <v>3365</v>
       </c>
+      <c r="J114" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K114" s="14" t="n">
+        <v>3365</v>
+      </c>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="7" t="n">
@@ -8593,6 +9857,12 @@
       <c r="I115" s="14" t="n">
         <v>170</v>
       </c>
+      <c r="J115" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K115" s="14" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="7" t="n">
@@ -8634,6 +9904,12 @@
       <c r="I116" s="14" t="n">
         <v>8673</v>
       </c>
+      <c r="J116" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K116" s="14" t="n">
+        <v>8674</v>
+      </c>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="7" t="n">
@@ -8675,6 +9951,12 @@
       <c r="I117" s="14" t="n">
         <v>11856</v>
       </c>
+      <c r="J117" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K117" s="14" t="n">
+        <v>11858</v>
+      </c>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="7" t="n">
@@ -8716,6 +9998,12 @@
       <c r="I118" s="14" t="n">
         <v>2782</v>
       </c>
+      <c r="J118" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K118" s="14" t="n">
+        <v>2792</v>
+      </c>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="7" t="n">
@@ -8757,6 +10045,12 @@
       <c r="I119" s="14" t="n">
         <v>89</v>
       </c>
+      <c r="J119" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K119" s="14" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="7" t="n">
@@ -8798,6 +10092,12 @@
       <c r="I120" s="14" t="n">
         <v>464</v>
       </c>
+      <c r="J120" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K120" s="14" t="n">
+        <v>464</v>
+      </c>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="7" t="n">
@@ -8839,6 +10139,12 @@
       <c r="I121" s="14" t="n">
         <v>776</v>
       </c>
+      <c r="J121" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K121" s="14" t="n">
+        <v>776</v>
+      </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="7" t="n">
@@ -8880,6 +10186,12 @@
       <c r="I122" s="14" t="n">
         <v>169</v>
       </c>
+      <c r="J122" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K122" s="14" t="n">
+        <v>169</v>
+      </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="7" t="n">
@@ -8921,6 +10233,12 @@
       <c r="I123" s="14" t="n">
         <v>14</v>
       </c>
+      <c r="J123" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K123" s="14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="7" t="n">
@@ -8962,6 +10280,12 @@
       <c r="I124" s="14" t="n">
         <v>41</v>
       </c>
+      <c r="J124" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K124" s="14" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="7" t="n">
@@ -9003,6 +10327,12 @@
       <c r="I125" s="14" t="n">
         <v>48</v>
       </c>
+      <c r="J125" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K125" s="14" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="7" t="n">
@@ -9044,6 +10374,12 @@
       <c r="I126" s="14" t="n">
         <v>11</v>
       </c>
+      <c r="J126" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K126" s="14" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="7" t="n">
@@ -9085,6 +10421,12 @@
       <c r="I127" s="14" t="n">
         <v>4192</v>
       </c>
+      <c r="J127" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K127" s="14" t="n">
+        <v>4192</v>
+      </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="7" t="n">
@@ -9126,6 +10468,12 @@
       <c r="I128" s="14" t="n">
         <v>289</v>
       </c>
+      <c r="J128" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K128" s="14" t="n">
+        <v>291</v>
+      </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="7" t="n">
@@ -9162,6 +10510,12 @@
       <c r="I129" s="14" t="n">
         <v>4228</v>
       </c>
+      <c r="J129" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K129" s="14" t="n">
+        <v>4228</v>
+      </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="7" t="n">
@@ -9198,6 +10552,12 @@
       <c r="I130" s="14" t="n">
         <v>660</v>
       </c>
+      <c r="J130" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K130" s="14" t="n">
+        <v>660</v>
+      </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="7" t="n">
@@ -9234,6 +10594,12 @@
       <c r="I131" s="14" t="n">
         <v>788</v>
       </c>
+      <c r="J131" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K131" s="14" t="n">
+        <v>789</v>
+      </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="7" t="n">
@@ -9270,6 +10636,12 @@
       <c r="I132" s="14" t="n">
         <v>712</v>
       </c>
+      <c r="J132" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K132" s="14" t="n">
+        <v>720</v>
+      </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="7" t="n">
@@ -9306,6 +10678,12 @@
       <c r="I133" s="14" t="n">
         <v>1425</v>
       </c>
+      <c r="J133" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K133" s="14" t="n">
+        <v>1424</v>
+      </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="7" t="n">
@@ -9342,6 +10720,12 @@
       <c r="I134" s="14" t="n">
         <v>694</v>
       </c>
+      <c r="J134" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K134" s="14" t="n">
+        <v>698</v>
+      </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="7" t="n">
@@ -9378,6 +10762,12 @@
       <c r="I135" s="14" t="n">
         <v>376</v>
       </c>
+      <c r="J135" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K135" s="14" t="n">
+        <v>384</v>
+      </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="7" t="n">
@@ -9414,6 +10804,12 @@
       <c r="I136" s="14" t="n">
         <v>376</v>
       </c>
+      <c r="J136" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K136" s="14" t="n">
+        <v>384</v>
+      </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="7" t="n">
@@ -9450,6 +10846,12 @@
       <c r="I137" s="14" t="n">
         <v>5282</v>
       </c>
+      <c r="J137" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K137" s="14" t="n">
+        <v>5284</v>
+      </c>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="7" t="n">
@@ -9486,6 +10888,12 @@
       <c r="I138" s="14" t="n">
         <v>2545</v>
       </c>
+      <c r="J138" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K138" s="14" t="n">
+        <v>2545</v>
+      </c>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="7" t="n">
@@ -9522,6 +10930,12 @@
       <c r="I139" s="14" t="n">
         <v>3198</v>
       </c>
+      <c r="J139" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K139" s="14" t="n">
+        <v>3199</v>
+      </c>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="7" t="n">
@@ -9558,6 +10972,12 @@
       <c r="I140" s="14" t="n">
         <v>1447</v>
       </c>
+      <c r="J140" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K140" s="14" t="n">
+        <v>1452</v>
+      </c>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="7" t="n">
@@ -9594,6 +11014,12 @@
       <c r="I141" s="14" t="n">
         <v>175</v>
       </c>
+      <c r="J141" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K141" s="14" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="7" t="n">
@@ -9630,6 +11056,12 @@
       <c r="I142" s="14" t="n">
         <v>19</v>
       </c>
+      <c r="J142" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K142" s="14" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="7" t="n">
@@ -9666,6 +11098,12 @@
       <c r="I143" s="14" t="n">
         <v>4196</v>
       </c>
+      <c r="J143" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K143" s="14" t="n">
+        <v>4204</v>
+      </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="7" t="n">
@@ -9702,6 +11140,12 @@
       <c r="I144" s="14" t="n">
         <v>4587</v>
       </c>
+      <c r="J144" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K144" s="14" t="n">
+        <v>4587</v>
+      </c>
     </row>
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="7" t="n">
@@ -9738,6 +11182,12 @@
       <c r="I145" s="14" t="n">
         <v>1531</v>
       </c>
+      <c r="J145" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K145" s="14" t="n">
+        <v>1533</v>
+      </c>
     </row>
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="7" t="n">
@@ -9774,6 +11224,12 @@
       <c r="I146" s="14" t="n">
         <v>3952</v>
       </c>
+      <c r="J146" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K146" s="14" t="n">
+        <v>3952</v>
+      </c>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="7" t="n">
@@ -9810,6 +11266,12 @@
       <c r="I147" s="14" t="n">
         <v>2953</v>
       </c>
+      <c r="J147" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K147" s="14" t="n">
+        <v>2953</v>
+      </c>
     </row>
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="7" t="n">
@@ -9846,6 +11308,12 @@
       <c r="I148" s="14" t="n">
         <v>63</v>
       </c>
+      <c r="J148" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K148" s="14" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="7" t="n">
@@ -9882,6 +11350,12 @@
       <c r="I149" s="14" t="n">
         <v>80</v>
       </c>
+      <c r="J149" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K149" s="14" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="7" t="n">
@@ -9918,6 +11392,12 @@
       <c r="I150" s="14" t="n">
         <v>2595</v>
       </c>
+      <c r="J150" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K150" s="14" t="n">
+        <v>2596</v>
+      </c>
     </row>
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="7" t="n">
@@ -9954,6 +11434,12 @@
       <c r="I151" s="14" t="n">
         <v>3845</v>
       </c>
+      <c r="J151" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K151" s="14" t="n">
+        <v>3845</v>
+      </c>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="7" t="n">
@@ -9990,6 +11476,12 @@
       <c r="I152" s="14" t="n">
         <v>510</v>
       </c>
+      <c r="J152" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K152" s="14" t="n">
+        <v>510</v>
+      </c>
     </row>
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="7" t="n">
@@ -10026,6 +11518,12 @@
       <c r="I153" s="14" t="n">
         <v>9259</v>
       </c>
+      <c r="J153" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K153" s="14" t="n">
+        <v>9258</v>
+      </c>
     </row>
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="7" t="n">
@@ -10062,6 +11560,12 @@
       <c r="I154" s="14" t="n">
         <v>9245</v>
       </c>
+      <c r="J154" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K154" s="14" t="n">
+        <v>9245</v>
+      </c>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="7" t="n">
@@ -10098,6 +11602,12 @@
       <c r="I155" s="14" t="n">
         <v>4306</v>
       </c>
+      <c r="J155" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K155" s="14" t="n">
+        <v>4321</v>
+      </c>
     </row>
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="7" t="n">
@@ -10134,6 +11644,12 @@
       <c r="I156" s="14" t="n">
         <v>198</v>
       </c>
+      <c r="J156" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K156" s="14" t="n">
+        <v>199</v>
+      </c>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="7" t="n">
@@ -10170,6 +11686,12 @@
       <c r="I157" s="14" t="n">
         <v>585</v>
       </c>
+      <c r="J157" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K157" s="14" t="n">
+        <v>587</v>
+      </c>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="7" t="n">
@@ -10206,6 +11728,12 @@
       <c r="I158" s="14" t="n">
         <v>80</v>
       </c>
+      <c r="J158" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K158" s="14" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="7" t="n">
@@ -10242,6 +11770,12 @@
       <c r="I159" s="14" t="n">
         <v>38</v>
       </c>
+      <c r="J159" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K159" s="14" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="160" ht="20" customHeight="1">
       <c r="A160" s="7" t="n">
@@ -10278,6 +11812,12 @@
       <c r="I160" s="14" t="n">
         <v>96</v>
       </c>
+      <c r="J160" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K160" s="14" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="7" t="n">
@@ -10314,6 +11854,12 @@
       <c r="I161" s="14" t="n">
         <v>114</v>
       </c>
+      <c r="J161" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K161" s="14" t="n">
+        <v>117</v>
+      </c>
     </row>
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="7" t="n">
@@ -10350,6 +11896,12 @@
       <c r="I162" s="14" t="n">
         <v>1951</v>
       </c>
+      <c r="J162" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K162" s="14" t="n">
+        <v>1954</v>
+      </c>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="7" t="n">
@@ -10386,6 +11938,12 @@
       <c r="I163" s="14" t="n">
         <v>1698</v>
       </c>
+      <c r="J163" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K163" s="14" t="n">
+        <v>1699</v>
+      </c>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="7" t="n">
@@ -10422,6 +11980,12 @@
       <c r="I164" s="14" t="n">
         <v>9349</v>
       </c>
+      <c r="J164" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K164" s="14" t="n">
+        <v>9352</v>
+      </c>
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="7" t="n">
@@ -10458,6 +12022,12 @@
       <c r="I165" s="14" t="n">
         <v>1092</v>
       </c>
+      <c r="J165" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K165" s="14" t="n">
+        <v>1092</v>
+      </c>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="7" t="n">
@@ -10494,6 +12064,12 @@
       <c r="I166" s="14" t="n">
         <v>175</v>
       </c>
+      <c r="J166" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K166" s="14" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="7" t="n">
@@ -10530,6 +12106,12 @@
       <c r="I167" s="14" t="n">
         <v>3361</v>
       </c>
+      <c r="J167" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K167" s="14" t="n">
+        <v>3362</v>
+      </c>
     </row>
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="7" t="n">
@@ -10566,6 +12148,12 @@
       <c r="I168" s="14" t="n">
         <v>849</v>
       </c>
+      <c r="J168" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K168" s="14" t="n">
+        <v>850</v>
+      </c>
     </row>
     <row r="169" ht="20" customHeight="1">
       <c r="A169" s="7" t="n">
@@ -10602,6 +12190,12 @@
       <c r="I169" s="14" t="n">
         <v>119</v>
       </c>
+      <c r="J169" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K169" s="14" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="170" ht="20" customHeight="1">
       <c r="A170" s="7" t="n">
@@ -10638,6 +12232,12 @@
       <c r="I170" s="14" t="n">
         <v>142</v>
       </c>
+      <c r="J170" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K170" s="14" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="7" t="n">
@@ -10674,6 +12274,12 @@
       <c r="I171" s="14" t="n">
         <v>220</v>
       </c>
+      <c r="J171" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K171" s="14" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="7" t="n">
@@ -10710,6 +12316,12 @@
       <c r="I172" s="14" t="n">
         <v>190</v>
       </c>
+      <c r="J172" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K172" s="14" t="n">
+        <v>190</v>
+      </c>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="7" t="n">
@@ -10746,6 +12358,12 @@
       <c r="I173" s="14" t="n">
         <v>407</v>
       </c>
+      <c r="J173" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K173" s="14" t="n">
+        <v>407</v>
+      </c>
     </row>
     <row r="174" ht="20" customHeight="1">
       <c r="A174" s="7" t="n">
@@ -10782,6 +12400,12 @@
       <c r="I174" s="14" t="n">
         <v>71</v>
       </c>
+      <c r="J174" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K174" s="14" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="7" t="n">
@@ -10818,6 +12442,12 @@
       <c r="I175" s="14" t="n">
         <v>78</v>
       </c>
+      <c r="J175" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K175" s="14" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="7" t="n">
@@ -10854,6 +12484,12 @@
       <c r="I176" s="14" t="n">
         <v>2053</v>
       </c>
+      <c r="J176" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K176" s="14" t="n">
+        <v>2053</v>
+      </c>
     </row>
     <row r="177" ht="20" customHeight="1">
       <c r="A177" s="7" t="n">
@@ -10890,6 +12526,12 @@
       <c r="I177" s="14" t="n">
         <v>566</v>
       </c>
+      <c r="J177" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K177" s="14" t="n">
+        <v>566</v>
+      </c>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="7" t="n">
@@ -10926,6 +12568,12 @@
       <c r="I178" s="14" t="n">
         <v>4077</v>
       </c>
+      <c r="J178" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K178" s="14" t="n">
+        <v>4077</v>
+      </c>
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="7" t="n">
@@ -10962,6 +12610,12 @@
       <c r="I179" s="14" t="n">
         <v>3197</v>
       </c>
+      <c r="J179" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K179" s="14" t="n">
+        <v>3197</v>
+      </c>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="7" t="n">
@@ -10998,6 +12652,12 @@
       <c r="I180" s="14" t="n">
         <v>494</v>
       </c>
+      <c r="J180" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K180" s="14" t="n">
+        <v>494</v>
+      </c>
     </row>
     <row r="181" ht="20" customHeight="1">
       <c r="A181" s="7" t="n">
@@ -11034,6 +12694,12 @@
       <c r="I181" s="14" t="n">
         <v>180</v>
       </c>
+      <c r="J181" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K181" s="14" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="182" ht="20" customHeight="1">
       <c r="A182" s="7" t="n">
@@ -11070,6 +12736,12 @@
       <c r="I182" s="14" t="n">
         <v>4077</v>
       </c>
+      <c r="J182" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K182" s="14" t="n">
+        <v>4077</v>
+      </c>
     </row>
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="7" t="n">
@@ -11106,6 +12778,12 @@
       <c r="I183" s="14" t="n">
         <v>219</v>
       </c>
+      <c r="J183" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K183" s="14" t="n">
+        <v>219</v>
+      </c>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="7" t="n">
@@ -11142,6 +12820,12 @@
       <c r="I184" s="14" t="n">
         <v>372</v>
       </c>
+      <c r="J184" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K184" s="14" t="n">
+        <v>372</v>
+      </c>
     </row>
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="7" t="n">
@@ -11178,6 +12862,12 @@
       <c r="I185" s="14" t="n">
         <v>728</v>
       </c>
+      <c r="J185" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K185" s="14" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="186" ht="20" customHeight="1">
       <c r="A186" s="7" t="n">
@@ -11214,6 +12904,12 @@
       <c r="I186" s="14" t="n">
         <v>434</v>
       </c>
+      <c r="J186" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K186" s="14" t="n">
+        <v>436</v>
+      </c>
     </row>
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="7" t="n">
@@ -11250,6 +12946,12 @@
       <c r="I187" s="14" t="n">
         <v>15</v>
       </c>
+      <c r="J187" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K187" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="188" ht="20" customHeight="1">
       <c r="A188" s="7" t="n">
@@ -11286,6 +12988,12 @@
       <c r="I188" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="J188" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K188" s="14" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="7" t="n">
@@ -11322,6 +13030,12 @@
       <c r="I189" s="14" t="n">
         <v>196</v>
       </c>
+      <c r="J189" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K189" s="14" t="n">
+        <v>196</v>
+      </c>
     </row>
     <row r="190" ht="20" customHeight="1">
       <c r="A190" s="7" t="n">
@@ -11358,6 +13072,12 @@
       <c r="I190" s="14" t="n">
         <v>64</v>
       </c>
+      <c r="J190" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K190" s="14" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="191" ht="20" customHeight="1">
       <c r="A191" s="7" t="n">
@@ -11394,6 +13114,12 @@
       <c r="I191" s="14" t="n">
         <v>7436</v>
       </c>
+      <c r="J191" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K191" s="14" t="n">
+        <v>7437</v>
+      </c>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="7" t="n">
@@ -11430,6 +13156,12 @@
       <c r="I192" s="14" t="n">
         <v>2941</v>
       </c>
+      <c r="J192" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K192" s="14" t="n">
+        <v>2942</v>
+      </c>
     </row>
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="7" t="n">
@@ -11466,6 +13198,12 @@
       <c r="I193" s="14" t="n">
         <v>488</v>
       </c>
+      <c r="J193" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K193" s="14" t="n">
+        <v>491</v>
+      </c>
     </row>
     <row r="194" ht="20" customHeight="1">
       <c r="A194" s="7" t="n">
@@ -11502,6 +13240,12 @@
       <c r="I194" s="14" t="n">
         <v>64</v>
       </c>
+      <c r="J194" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K194" s="14" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="195" ht="20" customHeight="1">
       <c r="A195" s="7" t="n">
@@ -11538,6 +13282,12 @@
       <c r="I195" s="14" t="n">
         <v>2229</v>
       </c>
+      <c r="J195" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K195" s="14" t="n">
+        <v>2230</v>
+      </c>
     </row>
     <row r="196" ht="20" customHeight="1">
       <c r="A196" s="7" t="n">
@@ -11574,6 +13324,12 @@
       <c r="I196" s="14" t="n">
         <v>2673</v>
       </c>
+      <c r="J196" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K196" s="14" t="n">
+        <v>2677</v>
+      </c>
     </row>
     <row r="197" ht="20" customHeight="1">
       <c r="A197" s="7" t="n">
@@ -11610,6 +13366,12 @@
       <c r="I197" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="J197" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K197" s="14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="7" t="n">
@@ -11646,6 +13408,12 @@
       <c r="I198" s="14" t="n">
         <v>8991</v>
       </c>
+      <c r="J198" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K198" s="14" t="n">
+        <v>8993</v>
+      </c>
     </row>
     <row r="199" ht="20" customHeight="1">
       <c r="A199" s="7" t="n">
@@ -11682,6 +13450,12 @@
       <c r="I199" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="J199" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K199" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="200" ht="20" customHeight="1">
       <c r="A200" s="7" t="n">
@@ -11718,6 +13492,12 @@
       <c r="I200" s="14" t="n">
         <v>190</v>
       </c>
+      <c r="J200" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K200" s="14" t="n">
+        <v>190</v>
+      </c>
     </row>
     <row r="201" ht="20" customHeight="1">
       <c r="A201" s="7" t="n">
@@ -11754,6 +13534,12 @@
       <c r="I201" s="14" t="n">
         <v>143</v>
       </c>
+      <c r="J201" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K201" s="14" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="202" ht="20" customHeight="1">
       <c r="A202" s="7" t="n">
@@ -11790,6 +13576,12 @@
       <c r="I202" s="14" t="n">
         <v>2884</v>
       </c>
+      <c r="J202" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K202" s="14" t="n">
+        <v>2884</v>
+      </c>
     </row>
     <row r="203" ht="20" customHeight="1">
       <c r="A203" s="7" t="n">
@@ -11826,6 +13618,12 @@
       <c r="I203" s="14" t="n">
         <v>17010</v>
       </c>
+      <c r="J203" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K203" s="14" t="n">
+        <v>17019</v>
+      </c>
     </row>
     <row r="204" ht="20" customHeight="1">
       <c r="A204" s="7" t="n">
@@ -11862,6 +13660,12 @@
       <c r="I204" s="14" t="n">
         <v>152</v>
       </c>
+      <c r="J204" s="14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K204" s="14" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="205" ht="20" customHeight="1">
       <c r="A205" s="7" t="n">
@@ -11898,6 +13702,12 @@
       <c r="I205" s="14" t="n">
         <v>338</v>
       </c>
+      <c r="J205" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K205" s="14" t="n">
+        <v>338</v>
+      </c>
     </row>
     <row r="206" ht="20" customHeight="1">
       <c r="A206" s="7" t="n">
@@ -11932,6 +13742,12 @@
         <v>4.5</v>
       </c>
       <c r="I206" s="14" t="n">
+        <v>161</v>
+      </c>
+      <c r="J206" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K206" s="14" t="n">
         <v>161</v>
       </c>
     </row>
@@ -11947,7 +13763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11970,6 +13786,12 @@
       <c r="H1" s="11" t="n">
         <v>46304</v>
       </c>
+      <c r="I1" s="11" t="n">
+        <v>46305</v>
+      </c>
+      <c r="J1" s="11" t="n">
+        <v>46305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -12008,6 +13830,16 @@
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -12048,6 +13880,12 @@
       <c r="H3" s="14" t="n">
         <v>7013</v>
       </c>
+      <c r="I3" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>7020</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -12084,6 +13922,12 @@
       <c r="H4" s="14" t="n">
         <v>1722</v>
       </c>
+      <c r="I4" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>1724</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -12120,6 +13964,12 @@
       <c r="H5" s="14" t="n">
         <v>3417</v>
       </c>
+      <c r="I5" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>3417</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -12156,6 +14006,12 @@
       <c r="H6" s="14" t="n">
         <v>1351</v>
       </c>
+      <c r="I6" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>1351</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -12192,6 +14048,12 @@
       <c r="H7" s="14" t="n">
         <v>1112</v>
       </c>
+      <c r="I7" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>1112</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -12228,6 +14090,12 @@
       <c r="H8" s="14" t="n">
         <v>3370</v>
       </c>
+      <c r="I8" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>3371</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -12264,6 +14132,12 @@
       <c r="H9" s="14" t="n">
         <v>1972</v>
       </c>
+      <c r="I9" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>1973</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -12300,6 +14174,12 @@
       <c r="H10" s="14" t="n">
         <v>1202</v>
       </c>
+      <c r="I10" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>1204</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -12336,6 +14216,12 @@
       <c r="H11" s="14" t="n">
         <v>812</v>
       </c>
+      <c r="I11" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>813</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -12372,6 +14258,12 @@
       <c r="H12" s="14" t="n">
         <v>3417</v>
       </c>
+      <c r="I12" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>3417</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -12408,6 +14300,12 @@
       <c r="H13" s="14" t="n">
         <v>415</v>
       </c>
+      <c r="I13" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>415</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -12444,6 +14342,12 @@
       <c r="H14" s="14" t="n">
         <v>3471</v>
       </c>
+      <c r="I14" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>3478</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -12480,6 +14384,12 @@
       <c r="H15" s="14" t="n">
         <v>1986</v>
       </c>
+      <c r="I15" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>1986</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -12516,6 +14426,12 @@
       <c r="H16" s="14" t="n">
         <v>1336</v>
       </c>
+      <c r="I16" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>1336</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -12552,6 +14468,12 @@
       <c r="H17" s="14" t="n">
         <v>1336</v>
       </c>
+      <c r="I17" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -12588,6 +14510,12 @@
       <c r="H18" s="14" t="n">
         <v>4501</v>
       </c>
+      <c r="I18" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>4505</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -12624,6 +14552,12 @@
       <c r="H19" s="14" t="n">
         <v>1675</v>
       </c>
+      <c r="I19" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>1677</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -12660,6 +14594,12 @@
       <c r="H20" s="14" t="n">
         <v>4380</v>
       </c>
+      <c r="I20" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>4385</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -12696,6 +14636,12 @@
       <c r="H21" s="14" t="n">
         <v>3872</v>
       </c>
+      <c r="I21" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>3878</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -12732,6 +14678,12 @@
       <c r="H22" s="14" t="n">
         <v>87</v>
       </c>
+      <c r="I22" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -12768,6 +14720,12 @@
       <c r="H23" s="14" t="n">
         <v>443</v>
       </c>
+      <c r="I23" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>443</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -12804,6 +14762,12 @@
       <c r="H24" s="14" t="n">
         <v>1684</v>
       </c>
+      <c r="I24" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>1684</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -12840,6 +14804,12 @@
       <c r="H25" s="14" t="n">
         <v>3368</v>
       </c>
+      <c r="I25" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>3369</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -12876,6 +14846,12 @@
       <c r="H26" s="14" t="n">
         <v>1765</v>
       </c>
+      <c r="I26" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>1765</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -12912,6 +14888,12 @@
       <c r="H27" s="14" t="n">
         <v>534</v>
       </c>
+      <c r="I27" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>537</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -12948,6 +14930,12 @@
       <c r="H28" s="14" t="n">
         <v>1324</v>
       </c>
+      <c r="I28" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>1324</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -12984,6 +14972,12 @@
       <c r="H29" s="14" t="n">
         <v>643</v>
       </c>
+      <c r="I29" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>646</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -13020,6 +15014,12 @@
       <c r="H30" s="14" t="n">
         <v>35</v>
       </c>
+      <c r="I30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -13056,6 +15056,12 @@
       <c r="H31" s="14" t="n">
         <v>1323</v>
       </c>
+      <c r="I31" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>1323</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -13092,6 +15098,12 @@
       <c r="H32" s="14" t="n">
         <v>1427</v>
       </c>
+      <c r="I32" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>1428</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -13128,6 +15140,12 @@
       <c r="H33" s="14" t="n">
         <v>1335</v>
       </c>
+      <c r="I33" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>1335</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -13164,6 +15182,12 @@
       <c r="H34" s="14" t="n">
         <v>193</v>
       </c>
+      <c r="I34" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>193</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -13200,6 +15224,12 @@
       <c r="H35" s="14" t="n">
         <v>126</v>
       </c>
+      <c r="I35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -13236,6 +15266,12 @@
       <c r="H36" s="14" t="n">
         <v>994</v>
       </c>
+      <c r="I36" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>995</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -13272,6 +15308,12 @@
       <c r="H37" s="14" t="n">
         <v>205</v>
       </c>
+      <c r="I37" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>205</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -13308,6 +15350,12 @@
       <c r="H38" s="14" t="n">
         <v>213</v>
       </c>
+      <c r="I38" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>213</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -13344,6 +15392,12 @@
       <c r="H39" s="14" t="n">
         <v>857</v>
       </c>
+      <c r="I39" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J39" s="14" t="n">
+        <v>863</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -13380,6 +15434,12 @@
       <c r="H40" s="14" t="n">
         <v>2238</v>
       </c>
+      <c r="I40" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>2245</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -13416,6 +15476,12 @@
       <c r="H41" s="14" t="n">
         <v>450</v>
       </c>
+      <c r="I41" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J41" s="14" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -13452,6 +15518,12 @@
       <c r="H42" s="14" t="n">
         <v>1587</v>
       </c>
+      <c r="I42" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J42" s="14" t="n">
+        <v>1589</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -13488,6 +15560,12 @@
       <c r="H43" s="14" t="n">
         <v>1165</v>
       </c>
+      <c r="I43" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J43" s="14" t="n">
+        <v>1167</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -13524,6 +15602,12 @@
       <c r="H44" s="14" t="n">
         <v>474</v>
       </c>
+      <c r="I44" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J44" s="14" t="n">
+        <v>475</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -13560,6 +15644,12 @@
       <c r="H45" s="14" t="n">
         <v>435</v>
       </c>
+      <c r="I45" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J45" s="14" t="n">
+        <v>449</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -13596,6 +15686,12 @@
       <c r="H46" s="14" t="n">
         <v>1049</v>
       </c>
+      <c r="I46" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J46" s="14" t="n">
+        <v>1051</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -13632,6 +15728,12 @@
       <c r="H47" s="14" t="n">
         <v>2598</v>
       </c>
+      <c r="I47" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J47" s="14" t="n">
+        <v>2572</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -13668,6 +15770,12 @@
       <c r="H48" s="14" t="n">
         <v>1429</v>
       </c>
+      <c r="I48" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J48" s="14" t="n">
+        <v>1429</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -13704,6 +15812,12 @@
       <c r="H49" s="14" t="n">
         <v>1420</v>
       </c>
+      <c r="I49" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J49" s="14" t="n">
+        <v>1421</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -13740,6 +15854,12 @@
       <c r="H50" s="14" t="n">
         <v>1553</v>
       </c>
+      <c r="I50" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J50" s="14" t="n">
+        <v>1553</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -13776,6 +15896,12 @@
       <c r="H51" s="14" t="n">
         <v>2810</v>
       </c>
+      <c r="I51" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J51" s="14" t="n">
+        <v>2810</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -13812,6 +15938,12 @@
       <c r="H52" s="14" t="n">
         <v>744</v>
       </c>
+      <c r="I52" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" s="14" t="n">
+        <v>745</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -13848,6 +15980,12 @@
       <c r="H53" s="14" t="n">
         <v>1229</v>
       </c>
+      <c r="I53" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J53" s="14" t="n">
+        <v>1229</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -13884,6 +16022,12 @@
       <c r="H54" s="14" t="n">
         <v>674</v>
       </c>
+      <c r="I54" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" s="14" t="n">
+        <v>674</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -13918,6 +16062,12 @@
         <v>4.4</v>
       </c>
       <c r="H55" s="14" t="n">
+        <v>426</v>
+      </c>
+      <c r="I55" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J55" s="14" t="n">
         <v>426</v>
       </c>
     </row>
@@ -14166,7 +16316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14189,6 +16339,12 @@
       <c r="H1" s="11" t="n">
         <v>46304</v>
       </c>
+      <c r="I1" s="11" t="n">
+        <v>46305</v>
+      </c>
+      <c r="J1" s="11" t="n">
+        <v>46305</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -14227,6 +16383,16 @@
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -14267,6 +16433,12 @@
       <c r="H3" s="14" t="n">
         <v>4571</v>
       </c>
+      <c r="I3" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>4571</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -14303,6 +16475,12 @@
       <c r="H4" s="14" t="n">
         <v>1234</v>
       </c>
+      <c r="I4" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>1234</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -14339,6 +16517,12 @@
       <c r="H5" s="14" t="n">
         <v>460</v>
       </c>
+      <c r="I5" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>460</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -14375,6 +16559,12 @@
       <c r="H6" s="14" t="n">
         <v>11588</v>
       </c>
+      <c r="I6" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>11589</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -14411,6 +16601,12 @@
       <c r="H7" s="14" t="n">
         <v>2050</v>
       </c>
+      <c r="I7" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>2051</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -14447,6 +16643,12 @@
       <c r="H8" s="14" t="n">
         <v>919</v>
       </c>
+      <c r="I8" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>919</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -14483,6 +16685,12 @@
       <c r="H9" s="14" t="n">
         <v>1605</v>
       </c>
+      <c r="I9" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>1605</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -14519,6 +16727,12 @@
       <c r="H10" s="14" t="n">
         <v>2023</v>
       </c>
+      <c r="I10" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>2026</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -14555,6 +16769,12 @@
       <c r="H11" s="14" t="n">
         <v>3082</v>
       </c>
+      <c r="I11" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>3082</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -14591,6 +16811,12 @@
       <c r="H12" s="14" t="n">
         <v>3628</v>
       </c>
+      <c r="I12" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>3630</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -14627,6 +16853,12 @@
       <c r="H13" s="14" t="n">
         <v>21270</v>
       </c>
+      <c r="I13" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>21272</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -14663,6 +16895,12 @@
       <c r="H14" s="14" t="n">
         <v>2949</v>
       </c>
+      <c r="I14" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>2949</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -14699,6 +16937,12 @@
       <c r="H15" s="14" t="n">
         <v>4206</v>
       </c>
+      <c r="I15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>4207</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -14735,6 +16979,12 @@
       <c r="H16" s="14" t="n">
         <v>2393</v>
       </c>
+      <c r="I16" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>2394</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -14771,6 +17021,12 @@
       <c r="H17" s="14" t="n">
         <v>4</v>
       </c>
+      <c r="I17" s="14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -14807,6 +17063,12 @@
       <c r="H18" s="14" t="n">
         <v>12127</v>
       </c>
+      <c r="I18" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>12126</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -14843,6 +17105,12 @@
       <c r="H19" s="14" t="n">
         <v>3093</v>
       </c>
+      <c r="I19" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>3107</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -14879,6 +17147,12 @@
       <c r="H20" s="14" t="n">
         <v>9248</v>
       </c>
+      <c r="I20" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>9249</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -14915,6 +17189,12 @@
       <c r="H21" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="I21" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -14951,6 +17231,12 @@
       <c r="H22" s="14" t="n">
         <v>6138</v>
       </c>
+      <c r="I22" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>6139</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -14987,6 +17273,12 @@
       <c r="H23" s="14" t="n">
         <v>1744</v>
       </c>
+      <c r="I23" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>1753</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -15023,6 +17315,12 @@
       <c r="H24" s="14" t="n">
         <v>1060</v>
       </c>
+      <c r="I24" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>1060</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -15059,6 +17357,12 @@
       <c r="H25" s="14" t="n">
         <v>2056</v>
       </c>
+      <c r="I25" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>2056</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -15095,6 +17399,12 @@
       <c r="H26" s="14" t="n">
         <v>2780</v>
       </c>
+      <c r="I26" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>2780</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -15131,6 +17441,12 @@
       <c r="H27" s="14" t="n">
         <v>11092</v>
       </c>
+      <c r="I27" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>11105</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -15167,6 +17483,12 @@
       <c r="H28" s="14" t="n">
         <v>5490</v>
       </c>
+      <c r="I28" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>5490</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -15203,6 +17525,12 @@
       <c r="H29" s="14" t="n">
         <v>4019</v>
       </c>
+      <c r="I29" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J29" s="14" t="n">
+        <v>4019</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -15239,6 +17567,12 @@
       <c r="H30" s="14" t="n">
         <v>1581</v>
       </c>
+      <c r="I30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>1581</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -15275,6 +17609,12 @@
       <c r="H31" s="14" t="n">
         <v>1581</v>
       </c>
+      <c r="I31" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>1581</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -15311,6 +17651,12 @@
       <c r="H32" s="14" t="n">
         <v>2813</v>
       </c>
+      <c r="I32" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>2813</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -15347,6 +17693,12 @@
       <c r="H33" s="14" t="n">
         <v>18972</v>
       </c>
+      <c r="I33" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>18972</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -15383,6 +17735,12 @@
       <c r="H34" s="14" t="n">
         <v>39704</v>
       </c>
+      <c r="I34" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>39706</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -15419,6 +17777,12 @@
       <c r="H35" s="14" t="n">
         <v>5229</v>
       </c>
+      <c r="I35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>5229</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -15455,6 +17819,12 @@
       <c r="H36" s="14" t="n">
         <v>10387</v>
       </c>
+      <c r="I36" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>10388</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -15491,6 +17861,12 @@
       <c r="H37" s="14" t="n">
         <v>7406</v>
       </c>
+      <c r="I37" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>7410</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -15527,6 +17903,12 @@
       <c r="H38" s="14" t="n">
         <v>539</v>
       </c>
+      <c r="I38" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>539</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -15563,6 +17945,12 @@
       <c r="H39" s="14" t="n">
         <v>1124</v>
       </c>
+      <c r="I39" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J39" s="14" t="n">
+        <v>1124</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -15599,6 +17987,12 @@
       <c r="H40" s="14" t="n">
         <v>539</v>
       </c>
+      <c r="I40" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>539</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -15635,6 +18029,12 @@
       <c r="H41" s="14" t="n">
         <v>2626</v>
       </c>
+      <c r="I41" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J41" s="14" t="n">
+        <v>2627</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -15671,6 +18071,12 @@
       <c r="H42" s="14" t="n">
         <v>1447</v>
       </c>
+      <c r="I42" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J42" s="14" t="n">
+        <v>1447</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -15707,6 +18113,12 @@
       <c r="H43" s="14" t="n">
         <v>955</v>
       </c>
+      <c r="I43" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J43" s="14" t="n">
+        <v>955</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -15743,6 +18155,12 @@
       <c r="H44" s="14" t="n">
         <v>4187</v>
       </c>
+      <c r="I44" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J44" s="14" t="n">
+        <v>4188</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -15779,6 +18197,12 @@
       <c r="H45" s="14" t="n">
         <v>3486</v>
       </c>
+      <c r="I45" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J45" s="14" t="n">
+        <v>3488</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -15815,6 +18239,12 @@
       <c r="H46" s="14" t="n">
         <v>7887</v>
       </c>
+      <c r="I46" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J46" s="14" t="n">
+        <v>7887</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -15851,6 +18281,12 @@
       <c r="H47" s="14" t="n">
         <v>6138</v>
       </c>
+      <c r="I47" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J47" s="14" t="n">
+        <v>6139</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -15887,6 +18323,12 @@
       <c r="H48" s="14" t="n">
         <v>983</v>
       </c>
+      <c r="I48" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J48" s="14" t="n">
+        <v>983</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -15923,6 +18365,12 @@
       <c r="H49" s="14" t="n">
         <v>3651</v>
       </c>
+      <c r="I49" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J49" s="14" t="n">
+        <v>3654</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -15959,6 +18407,12 @@
       <c r="H50" s="14" t="n">
         <v>180</v>
       </c>
+      <c r="I50" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J50" s="14" t="n">
+        <v>182</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -15995,6 +18449,12 @@
       <c r="H51" s="14" t="n">
         <v>4121</v>
       </c>
+      <c r="I51" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J51" s="14" t="n">
+        <v>4122</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -16031,6 +18491,12 @@
       <c r="H52" s="14" t="n">
         <v>296</v>
       </c>
+      <c r="I52" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J52" s="14" t="n">
+        <v>296</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -16067,6 +18533,12 @@
       <c r="H53" s="14" t="n">
         <v>124</v>
       </c>
+      <c r="I53" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J53" s="14" t="n">
+        <v>339</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -16103,6 +18575,12 @@
       <c r="H54" s="14" t="n">
         <v>4121</v>
       </c>
+      <c r="I54" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J54" s="14" t="n">
+        <v>4122</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -16139,6 +18617,12 @@
       <c r="H55" s="14" t="n">
         <v>56</v>
       </c>
+      <c r="I55" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J55" s="14" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -16175,6 +18659,12 @@
       <c r="H56" s="14" t="n">
         <v>493</v>
       </c>
+      <c r="I56" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J56" s="14" t="n">
+        <v>493</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -16211,6 +18701,12 @@
       <c r="H57" s="14" t="n">
         <v>7853</v>
       </c>
+      <c r="I57" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J57" s="14" t="n">
+        <v>7853</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -16247,6 +18743,12 @@
       <c r="H58" s="14" t="n">
         <v>4018</v>
       </c>
+      <c r="I58" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J58" s="14" t="n">
+        <v>4018</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -16283,6 +18785,12 @@
       <c r="H59" s="14" t="n">
         <v>2899</v>
       </c>
+      <c r="I59" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v>2916</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -16319,6 +18827,12 @@
       <c r="H60" s="14" t="n">
         <v>2252</v>
       </c>
+      <c r="I60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J60" s="14" t="n">
+        <v>2252</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -16355,6 +18869,12 @@
       <c r="H61" s="14" t="n">
         <v>7838</v>
       </c>
+      <c r="I61" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J61" s="14" t="n">
+        <v>7843</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -16391,6 +18911,12 @@
       <c r="H62" s="14" t="n">
         <v>3616</v>
       </c>
+      <c r="I62" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J62" s="14" t="n">
+        <v>3617</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -16427,6 +18953,12 @@
       <c r="H63" s="14" t="n">
         <v>4769</v>
       </c>
+      <c r="I63" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" s="14" t="n">
+        <v>4769</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -16463,6 +18995,12 @@
       <c r="H64" s="14" t="n">
         <v>2626</v>
       </c>
+      <c r="I64" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J64" s="14" t="n">
+        <v>2626</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -16499,6 +19037,12 @@
       <c r="H65" s="14" t="n">
         <v>2903</v>
       </c>
+      <c r="I65" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J65" s="14" t="n">
+        <v>2903</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -16535,6 +19079,12 @@
       <c r="H66" s="14" t="n">
         <v>6444</v>
       </c>
+      <c r="I66" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J66" s="14" t="n">
+        <v>6445</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -16571,6 +19121,12 @@
       <c r="H67" s="14" t="n">
         <v>781</v>
       </c>
+      <c r="I67" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J67" s="14" t="n">
+        <v>781</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -16607,6 +19163,12 @@
       <c r="H68" s="14" t="n">
         <v>19111</v>
       </c>
+      <c r="I68" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J68" s="14" t="n">
+        <v>19113</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -16643,6 +19205,12 @@
       <c r="H69" s="14" t="n">
         <v>2918</v>
       </c>
+      <c r="I69" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J69" s="14" t="n">
+        <v>2919</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -16679,6 +19247,12 @@
       <c r="H70" s="14" t="n">
         <v>2629</v>
       </c>
+      <c r="I70" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J70" s="14" t="n">
+        <v>2629</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
@@ -16715,6 +19289,12 @@
       <c r="H71" s="14" t="n">
         <v>1192</v>
       </c>
+      <c r="I71" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J71" s="14" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -16751,6 +19331,12 @@
       <c r="H72" s="14" t="n">
         <v>4165</v>
       </c>
+      <c r="I72" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J72" s="14" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -16787,6 +19373,12 @@
       <c r="H73" s="14" t="n">
         <v>3864</v>
       </c>
+      <c r="I73" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J73" s="14" t="n">
+        <v>3866</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -16823,6 +19415,12 @@
       <c r="H74" s="14" t="n">
         <v>756</v>
       </c>
+      <c r="I74" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J74" s="14" t="n">
+        <v>756</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -16859,6 +19457,12 @@
       <c r="H75" s="14" t="n">
         <v>4658</v>
       </c>
+      <c r="I75" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J75" s="14" t="n">
+        <v>4660</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -16895,6 +19499,12 @@
       <c r="H76" s="14" t="n">
         <v>5290</v>
       </c>
+      <c r="I76" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J76" s="14" t="n">
+        <v>5290</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -16931,6 +19541,12 @@
       <c r="H77" s="14" t="n">
         <v>159</v>
       </c>
+      <c r="I77" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J77" s="14" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -16967,6 +19583,12 @@
       <c r="H78" s="14" t="n">
         <v>1131</v>
       </c>
+      <c r="I78" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J78" s="14" t="n">
+        <v>1132</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -17003,6 +19625,12 @@
       <c r="H79" s="14" t="n">
         <v>634</v>
       </c>
+      <c r="I79" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J79" s="14" t="n">
+        <v>634</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -17039,6 +19667,12 @@
       <c r="H80" s="14" t="n">
         <v>1187</v>
       </c>
+      <c r="I80" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J80" s="14" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -17075,6 +19709,12 @@
       <c r="H81" s="14" t="n">
         <v>1566</v>
       </c>
+      <c r="I81" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J81" s="14" t="n">
+        <v>1566</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -17111,6 +19751,12 @@
       <c r="H82" s="14" t="n">
         <v>11747</v>
       </c>
+      <c r="I82" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J82" s="14" t="n">
+        <v>11751</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -17147,6 +19793,12 @@
       <c r="H83" s="14" t="n">
         <v>15</v>
       </c>
+      <c r="I83" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J83" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
@@ -17183,6 +19835,12 @@
       <c r="H84" s="14" t="n">
         <v>5934</v>
       </c>
+      <c r="I84" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J84" s="14" t="n">
+        <v>5937</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -17219,6 +19877,12 @@
       <c r="H85" s="14" t="n">
         <v>3266</v>
       </c>
+      <c r="I85" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J85" s="14" t="n">
+        <v>3269</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -17255,6 +19919,12 @@
       <c r="H86" s="14" t="n">
         <v>10433</v>
       </c>
+      <c r="I86" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J86" s="14" t="n">
+        <v>10433</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
@@ -17291,6 +19961,12 @@
       <c r="H87" s="14" t="n">
         <v>4152</v>
       </c>
+      <c r="I87" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J87" s="14" t="n">
+        <v>4152</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
@@ -17327,6 +20003,12 @@
       <c r="H88" s="14" t="n">
         <v>2998</v>
       </c>
+      <c r="I88" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J88" s="14" t="n">
+        <v>2998</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
@@ -17363,6 +20045,12 @@
       <c r="H89" s="14" t="n">
         <v>1295</v>
       </c>
+      <c r="I89" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J89" s="14" t="n">
+        <v>1295</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -17399,6 +20087,12 @@
       <c r="H90" s="14" t="n">
         <v>2236</v>
       </c>
+      <c r="I90" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J90" s="14" t="n">
+        <v>2238</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
@@ -17435,6 +20129,12 @@
       <c r="H91" s="14" t="n">
         <v>7973</v>
       </c>
+      <c r="I91" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J91" s="14" t="n">
+        <v>7972</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
@@ -17471,6 +20171,12 @@
       <c r="H92" s="14" t="n">
         <v>783</v>
       </c>
+      <c r="I92" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J92" s="14" t="n">
+        <v>783</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
@@ -17507,6 +20213,12 @@
       <c r="H93" s="14" t="n">
         <v>790</v>
       </c>
+      <c r="I93" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J93" s="14" t="n">
+        <v>790</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
@@ -17543,6 +20255,12 @@
       <c r="H94" s="14" t="n">
         <v>2596</v>
       </c>
+      <c r="I94" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J94" s="14" t="n">
+        <v>2596</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
@@ -17579,6 +20297,12 @@
       <c r="H95" s="14" t="n">
         <v>1680</v>
       </c>
+      <c r="I95" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J95" s="14" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
@@ -17615,6 +20339,12 @@
       <c r="H96" s="14" t="n">
         <v>6440</v>
       </c>
+      <c r="I96" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J96" s="14" t="n">
+        <v>6440</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
@@ -17651,6 +20381,12 @@
       <c r="H97" s="14" t="n">
         <v>2315</v>
       </c>
+      <c r="I97" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J97" s="14" t="n">
+        <v>2315</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -17687,6 +20423,12 @@
       <c r="H98" s="14" t="n">
         <v>1937</v>
       </c>
+      <c r="I98" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J98" s="14" t="n">
+        <v>1937</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
@@ -17723,6 +20465,12 @@
       <c r="H99" s="14" t="n">
         <v>5584</v>
       </c>
+      <c r="I99" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J99" s="14" t="n">
+        <v>5585</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -17759,6 +20507,12 @@
       <c r="H100" s="14" t="n">
         <v>17798</v>
       </c>
+      <c r="I100" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J100" s="14" t="n">
+        <v>17800</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -17795,6 +20549,12 @@
       <c r="H101" s="14" t="n">
         <v>6180</v>
       </c>
+      <c r="I101" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J101" s="14" t="n">
+        <v>6184</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -17831,6 +20591,12 @@
       <c r="H102" s="14" t="n">
         <v>5282</v>
       </c>
+      <c r="I102" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J102" s="14" t="n">
+        <v>5283</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
@@ -17867,6 +20633,12 @@
       <c r="H103" s="14" t="n">
         <v>1176</v>
       </c>
+      <c r="I103" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J103" s="14" t="n">
+        <v>1177</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -17903,6 +20675,12 @@
       <c r="H104" s="14" t="n">
         <v>4077</v>
       </c>
+      <c r="I104" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J104" s="14" t="n">
+        <v>4077</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
@@ -17939,6 +20717,12 @@
       <c r="H105" s="14" t="n">
         <v>1176</v>
       </c>
+      <c r="I105" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J105" s="14" t="n">
+        <v>1177</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
@@ -17975,6 +20759,12 @@
       <c r="H106" s="14" t="n">
         <v>10980</v>
       </c>
+      <c r="I106" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J106" s="14" t="n">
+        <v>10980</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -18011,6 +20801,12 @@
       <c r="H107" s="14" t="n">
         <v>3159</v>
       </c>
+      <c r="I107" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J107" s="14" t="n">
+        <v>3159</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -18047,6 +20843,12 @@
       <c r="H108" s="14" t="n">
         <v>3059</v>
       </c>
+      <c r="I108" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J108" s="14" t="n">
+        <v>3062</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
@@ -18083,6 +20885,12 @@
       <c r="H109" s="14" t="n">
         <v>2635</v>
       </c>
+      <c r="I109" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J109" s="14" t="n">
+        <v>2637</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
@@ -18119,6 +20927,12 @@
       <c r="H110" s="14" t="n">
         <v>1883</v>
       </c>
+      <c r="I110" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J110" s="14" t="n">
+        <v>1886</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
@@ -18155,6 +20969,12 @@
       <c r="H111" s="14" t="n">
         <v>1196</v>
       </c>
+      <c r="I111" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J111" s="14" t="n">
+        <v>1196</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -18191,6 +21011,12 @@
       <c r="H112" s="14" t="n">
         <v>2457</v>
       </c>
+      <c r="I112" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J112" s="14" t="n">
+        <v>2460</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
@@ -18226,6 +21052,12 @@
       </c>
       <c r="H113" s="14" t="n">
         <v>2652</v>
+      </c>
+      <c r="I113" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J113" s="14" t="n">
+        <v>2658</v>
       </c>
     </row>
   </sheetData>
@@ -18360,7 +21192,7 @@
         <v>4.2</v>
       </c>
       <c r="J3" s="14" t="n">
-        <v>14379</v>
+        <v>14381</v>
       </c>
     </row>
     <row r="4">
@@ -18402,7 +21234,7 @@
         <v>4.3</v>
       </c>
       <c r="J4" s="14" t="n">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="5">
@@ -18486,7 +21318,7 @@
         <v>4.3</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -18528,7 +21360,7 @@
         <v>4.2</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>4838</v>
+        <v>4839</v>
       </c>
     </row>
     <row r="8">
@@ -18570,7 +21402,7 @@
         <v>4.2</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>2068</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="9">
@@ -18696,7 +21528,7 @@
         <v>4.2</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>10577</v>
+        <v>10578</v>
       </c>
     </row>
     <row r="12">
@@ -18738,7 +21570,7 @@
         <v>4.2</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>12238</v>
+        <v>12239</v>
       </c>
     </row>
     <row r="13">
@@ -18780,7 +21612,7 @@
         <v>4.1</v>
       </c>
       <c r="J13" s="14" t="n">
-        <v>10702</v>
+        <v>10708</v>
       </c>
     </row>
     <row r="14">
@@ -18822,7 +21654,7 @@
         <v>4.2</v>
       </c>
       <c r="J14" s="14" t="n">
-        <v>6811</v>
+        <v>6813</v>
       </c>
     </row>
     <row r="15">
@@ -18990,7 +21822,7 @@
         <v>4.2</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>19722</v>
+        <v>19724</v>
       </c>
     </row>
     <row r="19">
@@ -19074,7 +21906,7 @@
         <v>4.1</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>2058</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="21">
@@ -19242,7 +22074,7 @@
         <v>4</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
   </sheetData>
@@ -19545,7 +22377,7 @@
         <v>3.8</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="8">
@@ -19965,7 +22797,7 @@
         <v>4.8</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>5845</v>
+        <v>5855</v>
       </c>
     </row>
     <row r="18">
@@ -20007,7 +22839,7 @@
         <v>4.8</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>1129</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="19">
@@ -20091,7 +22923,7 @@
         <v>4.3</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>2472</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="21">
@@ -20175,7 +23007,7 @@
         <v>4.8</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>4357</v>
+        <v>4358</v>
       </c>
     </row>
     <row r="23">
@@ -20259,7 +23091,7 @@
         <v>4.7</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>13832</v>
+        <v>13841</v>
       </c>
     </row>
     <row r="25">
@@ -20301,7 +23133,7 @@
         <v>4.8</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>5024</v>
+        <v>5033</v>
       </c>
     </row>
     <row r="26">
@@ -20343,7 +23175,7 @@
         <v>4.7</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>8085</v>
+        <v>8086</v>
       </c>
     </row>
     <row r="27">
@@ -20385,7 +23217,7 @@
         <v>4.8</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>7822</v>
+        <v>7826</v>
       </c>
     </row>
     <row r="28">
@@ -20427,7 +23259,7 @@
         <v>4.8</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>6652</v>
+        <v>6654</v>
       </c>
     </row>
     <row r="29">
@@ -20553,7 +23385,7 @@
         <v>4.9</v>
       </c>
       <c r="J31" s="14" t="n">
-        <v>8066</v>
+        <v>8076</v>
       </c>
     </row>
     <row r="32">
@@ -20595,7 +23427,7 @@
         <v>4.9</v>
       </c>
       <c r="J32" s="14" t="n">
-        <v>8451</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="33">
@@ -20721,7 +23553,7 @@
         <v>4.2</v>
       </c>
       <c r="J35" s="14" t="n">
-        <v>4429</v>
+        <v>4431</v>
       </c>
     </row>
     <row r="36">
@@ -20763,7 +23595,7 @@
         <v>4.2</v>
       </c>
       <c r="J36" s="14" t="n">
-        <v>5551</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="37">
@@ -20847,7 +23679,7 @@
         <v>4.2</v>
       </c>
       <c r="J38" s="14" t="n">
-        <v>2513</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="39">
@@ -20889,7 +23721,7 @@
         <v>4.2</v>
       </c>
       <c r="J39" s="14" t="n">
-        <v>6421</v>
+        <v>6423</v>
       </c>
     </row>
     <row r="40">
@@ -20931,7 +23763,7 @@
         <v>4.1</v>
       </c>
       <c r="J40" s="14" t="n">
-        <v>2545</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="41">
@@ -20973,7 +23805,7 @@
         <v>4.4</v>
       </c>
       <c r="J41" s="14" t="n">
-        <v>1070</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="42">
@@ -21015,7 +23847,7 @@
         <v>4.5</v>
       </c>
       <c r="J42" s="14" t="n">
-        <v>801</v>
+        <v>808</v>
       </c>
     </row>
     <row r="43">
@@ -21057,7 +23889,7 @@
         <v>4.3</v>
       </c>
       <c r="J43" s="14" t="n">
-        <v>548</v>
+        <v>555</v>
       </c>
     </row>
     <row r="44">
@@ -21141,7 +23973,7 @@
         <v>4.3</v>
       </c>
       <c r="J45" s="14" t="n">
-        <v>5066</v>
+        <v>5069</v>
       </c>
     </row>
     <row r="46">
@@ -21183,7 +24015,7 @@
         <v>4.6</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="47">
@@ -21225,7 +24057,7 @@
         <v>4.8</v>
       </c>
       <c r="J47" s="14" t="n">
-        <v>2577</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="48">
@@ -21309,7 +24141,7 @@
         <v>4.7</v>
       </c>
       <c r="J49" s="14" t="n">
-        <v>4621</v>
+        <v>4632</v>
       </c>
     </row>
     <row r="50">
@@ -21351,7 +24183,7 @@
         <v>4.7</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>3301</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="51">
@@ -21477,7 +24309,7 @@
         <v>4.8</v>
       </c>
       <c r="J53" s="14" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54">
@@ -21645,7 +24477,7 @@
         <v>4.6</v>
       </c>
       <c r="J57" s="14" t="n">
-        <v>4516</v>
+        <v>4518</v>
       </c>
     </row>
     <row r="58">
@@ -21729,7 +24561,7 @@
         <v>4.4</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>3008</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="60">
@@ -21771,7 +24603,7 @@
         <v>4.2</v>
       </c>
       <c r="J60" s="14" t="n">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="61">

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -589,6 +589,12 @@
       <c r="J1" s="11" t="n">
         <v>46305</v>
       </c>
+      <c r="K1" s="11" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L1" s="11" t="n">
+        <v>46306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -637,6 +643,16 @@
         </is>
       </c>
       <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -683,6 +699,12 @@
       <c r="J3" s="14" t="n">
         <v>4875</v>
       </c>
+      <c r="K3" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>4875</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -725,6 +747,12 @@
       <c r="J4" s="14" t="n">
         <v>15765</v>
       </c>
+      <c r="K4" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L4" s="14" t="n">
+        <v>15767</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -767,6 +795,12 @@
       <c r="J5" s="14" t="n">
         <v>5558</v>
       </c>
+      <c r="K5" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>5560</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -809,6 +843,12 @@
       <c r="J6" s="14" t="n">
         <v>6557</v>
       </c>
+      <c r="K6" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L6" s="14" t="n">
+        <v>6563</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -851,6 +891,12 @@
       <c r="J7" s="14" t="n">
         <v>2426</v>
       </c>
+      <c r="K7" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>2428</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -893,6 +939,12 @@
       <c r="J8" s="14" t="n">
         <v>7192</v>
       </c>
+      <c r="K8" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L8" s="14" t="n">
+        <v>7177</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -935,6 +987,12 @@
       <c r="J9" s="14" t="n">
         <v>3648</v>
       </c>
+      <c r="K9" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>3657</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -977,6 +1035,12 @@
       <c r="J10" s="14" t="n">
         <v>2792</v>
       </c>
+      <c r="K10" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L10" s="14" t="n">
+        <v>2794</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1019,6 +1083,12 @@
       <c r="J11" s="14" t="n">
         <v>1120</v>
       </c>
+      <c r="K11" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>1122</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1061,6 +1131,12 @@
       <c r="J12" s="14" t="n">
         <v>1109</v>
       </c>
+      <c r="K12" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>1110</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -1103,6 +1179,12 @@
       <c r="J13" s="14" t="n">
         <v>2279</v>
       </c>
+      <c r="K13" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>2278</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -1145,6 +1227,12 @@
       <c r="J14" s="14" t="n">
         <v>2384</v>
       </c>
+      <c r="K14" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>2391</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1187,6 +1275,12 @@
       <c r="J15" s="14" t="n">
         <v>2604</v>
       </c>
+      <c r="K15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>2613</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1229,6 +1323,12 @@
       <c r="J16" s="14" t="n">
         <v>895</v>
       </c>
+      <c r="K16" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>895</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -1271,6 +1371,12 @@
       <c r="J17" s="14" t="n">
         <v>1333</v>
       </c>
+      <c r="K17" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>1337</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -1313,6 +1419,12 @@
       <c r="J18" s="14" t="n">
         <v>461</v>
       </c>
+      <c r="K18" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>470</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -1355,6 +1467,12 @@
       <c r="J19" s="14" t="n">
         <v>919</v>
       </c>
+      <c r="K19" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>920</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -1397,6 +1515,12 @@
       <c r="J20" s="14" t="n">
         <v>1098</v>
       </c>
+      <c r="K20" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>1097</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -1439,6 +1563,12 @@
       <c r="J21" s="14" t="n">
         <v>789</v>
       </c>
+      <c r="K21" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>790</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -1481,6 +1611,12 @@
       <c r="J22" s="14" t="n">
         <v>660</v>
       </c>
+      <c r="K22" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>667</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -1523,6 +1659,12 @@
       <c r="J23" s="14" t="n">
         <v>698</v>
       </c>
+      <c r="K23" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>702</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -1565,6 +1707,12 @@
       <c r="J24" s="14" t="n">
         <v>1424</v>
       </c>
+      <c r="K24" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>1424</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -1607,6 +1755,12 @@
       <c r="J25" s="14" t="n">
         <v>720</v>
       </c>
+      <c r="K25" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>720</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1643,6 +1797,12 @@
         <v>4.9</v>
       </c>
       <c r="J26" s="14" t="n">
+        <v>384</v>
+      </c>
+      <c r="K26" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L26" s="14" t="n">
         <v>384</v>
       </c>
     </row>
@@ -1657,7 +1817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1687,6 +1847,12 @@
       <c r="K1" s="11" t="n">
         <v>46305</v>
       </c>
+      <c r="L1" s="11" t="n">
+        <v>46306</v>
+      </c>
+      <c r="M1" s="11" t="n">
+        <v>46306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -1740,6 +1906,16 @@
         </is>
       </c>
       <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="L2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="M2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1791,6 +1967,12 @@
       <c r="K3" s="14" t="n">
         <v>698</v>
       </c>
+      <c r="L3" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M3" s="14" t="n">
+        <v>702</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -1838,6 +2020,12 @@
       <c r="K4" s="14" t="n">
         <v>81</v>
       </c>
+      <c r="L4" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M4" s="14" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -1885,6 +2073,12 @@
       <c r="K5" s="14" t="n">
         <v>789</v>
       </c>
+      <c r="L5" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>790</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1932,6 +2126,12 @@
       <c r="K6" s="14" t="n">
         <v>789</v>
       </c>
+      <c r="L6" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M6" s="14" t="n">
+        <v>790</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1979,6 +2179,12 @@
       <c r="K7" s="14" t="n">
         <v>660</v>
       </c>
+      <c r="L7" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M7" s="14" t="n">
+        <v>667</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -2026,6 +2232,12 @@
       <c r="K8" s="14" t="n">
         <v>895</v>
       </c>
+      <c r="L8" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>895</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -2073,6 +2285,12 @@
       <c r="K9" s="14" t="n">
         <v>3269</v>
       </c>
+      <c r="L9" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>3271</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -2120,6 +2338,12 @@
       <c r="K10" s="14" t="n">
         <v>3269</v>
       </c>
+      <c r="L10" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M10" s="14" t="n">
+        <v>3271</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -2167,6 +2391,12 @@
       <c r="K11" s="14" t="n">
         <v>1424</v>
       </c>
+      <c r="L11" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>1424</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -2214,6 +2444,12 @@
       <c r="K12" s="14" t="n">
         <v>1193</v>
       </c>
+      <c r="L12" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -2261,6 +2497,12 @@
       <c r="K13" s="14" t="n">
         <v>756</v>
       </c>
+      <c r="L13" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>756</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -2308,6 +2550,12 @@
       <c r="K14" s="14" t="n">
         <v>6813</v>
       </c>
+      <c r="L14" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>6816</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -2355,6 +2603,12 @@
       <c r="K15" s="14" t="n">
         <v>7192</v>
       </c>
+      <c r="L15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>7177</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -2402,6 +2656,12 @@
       <c r="K16" s="14" t="n">
         <v>2629</v>
       </c>
+      <c r="L16" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>2630</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -2449,6 +2709,12 @@
       <c r="K17" s="14" t="n">
         <v>1824</v>
       </c>
+      <c r="L17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>1825</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -2496,6 +2762,12 @@
       <c r="K18" s="14" t="n">
         <v>4504</v>
       </c>
+      <c r="L18" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>4505</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -2543,6 +2815,12 @@
       <c r="K19" s="14" t="n">
         <v>6557</v>
       </c>
+      <c r="L19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M19" s="14" t="n">
+        <v>6563</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -2590,6 +2868,12 @@
       <c r="K20" s="14" t="n">
         <v>2792</v>
       </c>
+      <c r="L20" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M20" s="14" t="n">
+        <v>2794</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -2637,6 +2921,12 @@
       <c r="K21" s="14" t="n">
         <v>15765</v>
       </c>
+      <c r="L21" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>15767</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2684,6 +2974,12 @@
       <c r="K22" s="14" t="n">
         <v>15765</v>
       </c>
+      <c r="L22" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M22" s="14" t="n">
+        <v>15767</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -2731,6 +3027,12 @@
       <c r="K23" s="14" t="n">
         <v>10578</v>
       </c>
+      <c r="L23" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>10581</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -2778,6 +3080,12 @@
       <c r="K24" s="14" t="n">
         <v>12239</v>
       </c>
+      <c r="L24" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>12241</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -2825,6 +3133,12 @@
       <c r="K25" s="14" t="n">
         <v>2016</v>
       </c>
+      <c r="L25" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>2019</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -2872,6 +3186,12 @@
       <c r="K26" s="14" t="n">
         <v>850</v>
       </c>
+      <c r="L26" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M26" s="14" t="n">
+        <v>853</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -2919,6 +3239,12 @@
       <c r="K27" s="14" t="n">
         <v>3648</v>
       </c>
+      <c r="L27" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>3657</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -2966,6 +3292,12 @@
       <c r="K28" s="14" t="n">
         <v>3606</v>
       </c>
+      <c r="L28" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M28" s="14" t="n">
+        <v>3607</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -3013,6 +3345,12 @@
       <c r="K29" s="14" t="n">
         <v>4875</v>
       </c>
+      <c r="L29" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>4875</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -3060,6 +3398,12 @@
       <c r="K30" s="14" t="n">
         <v>1164</v>
       </c>
+      <c r="L30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M30" s="14" t="n">
+        <v>1172</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -3107,6 +3451,12 @@
       <c r="K31" s="14" t="n">
         <v>2279</v>
       </c>
+      <c r="L31" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M31" s="14" t="n">
+        <v>2278</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -3154,6 +3504,12 @@
       <c r="K32" s="14" t="n">
         <v>1044</v>
       </c>
+      <c r="L32" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M32" s="14" t="n">
+        <v>1044</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -3201,6 +3557,12 @@
       <c r="K33" s="14" t="n">
         <v>5558</v>
       </c>
+      <c r="L33" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M33" s="14" t="n">
+        <v>5560</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -3248,6 +3610,12 @@
       <c r="K34" s="14" t="n">
         <v>1132</v>
       </c>
+      <c r="L34" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M34" s="14" t="n">
+        <v>1132</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -3295,6 +3663,12 @@
       <c r="K35" s="14" t="n">
         <v>4839</v>
       </c>
+      <c r="L35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M35" s="14" t="n">
+        <v>4840</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -3342,6 +3716,12 @@
       <c r="K36" s="14" t="n">
         <v>1109</v>
       </c>
+      <c r="L36" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M36" s="14" t="n">
+        <v>1110</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -3389,6 +3769,12 @@
       <c r="K37" s="14" t="n">
         <v>2426</v>
       </c>
+      <c r="L37" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M37" s="14" t="n">
+        <v>2428</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -3436,6 +3822,12 @@
       <c r="K38" s="14" t="n">
         <v>2426</v>
       </c>
+      <c r="L38" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M38" s="14" t="n">
+        <v>2428</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -3483,6 +3875,12 @@
       <c r="K39" s="14" t="n">
         <v>2604</v>
       </c>
+      <c r="L39" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M39" s="14" t="n">
+        <v>2613</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -3530,6 +3928,12 @@
       <c r="K40" s="14" t="n">
         <v>461</v>
       </c>
+      <c r="L40" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M40" s="14" t="n">
+        <v>470</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -3577,6 +3981,12 @@
       <c r="K41" s="14" t="n">
         <v>1120</v>
       </c>
+      <c r="L41" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M41" s="14" t="n">
+        <v>1122</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -3624,6 +4034,12 @@
       <c r="K42" s="14" t="n">
         <v>11751</v>
       </c>
+      <c r="L42" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M42" s="14" t="n">
+        <v>11754</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -3671,6 +4087,12 @@
       <c r="K43" s="14" t="n">
         <v>1098</v>
       </c>
+      <c r="L43" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M43" s="14" t="n">
+        <v>1097</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -3718,6 +4140,12 @@
       <c r="K44" s="14" t="n">
         <v>1333</v>
       </c>
+      <c r="L44" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M44" s="14" t="n">
+        <v>1337</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -3765,6 +4193,12 @@
       <c r="K45" s="14" t="n">
         <v>192</v>
       </c>
+      <c r="L45" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M45" s="14" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -3812,6 +4246,12 @@
       <c r="K46" s="14" t="n">
         <v>2016</v>
       </c>
+      <c r="L46" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M46" s="14" t="n">
+        <v>2019</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -3859,6 +4299,12 @@
       <c r="K47" s="14" t="n">
         <v>2384</v>
       </c>
+      <c r="L47" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M47" s="14" t="n">
+        <v>2391</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -3906,6 +4352,12 @@
       <c r="K48" s="14" t="n">
         <v>919</v>
       </c>
+      <c r="L48" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M48" s="14" t="n">
+        <v>920</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -3953,6 +4405,12 @@
       <c r="K49" s="14" t="n">
         <v>1775</v>
       </c>
+      <c r="L49" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M49" s="14" t="n">
+        <v>1776</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -4000,6 +4458,12 @@
       <c r="K50" s="14" t="n">
         <v>2629</v>
       </c>
+      <c r="L50" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M50" s="14" t="n">
+        <v>2630</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -4047,6 +4511,12 @@
       <c r="K51" s="14" t="n">
         <v>5937</v>
       </c>
+      <c r="L51" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M51" s="14" t="n">
+        <v>5940</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -4094,6 +4564,12 @@
       <c r="K52" s="14" t="n">
         <v>1566</v>
       </c>
+      <c r="L52" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M52" s="14" t="n">
+        <v>1566</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -4141,6 +4617,12 @@
       <c r="K53" s="14" t="n">
         <v>4660</v>
       </c>
+      <c r="L53" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M53" s="14" t="n">
+        <v>4661</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -4188,6 +4670,12 @@
       <c r="K54" s="14" t="n">
         <v>5290</v>
       </c>
+      <c r="L54" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M54" s="14" t="n">
+        <v>5291</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -4235,6 +4723,12 @@
       <c r="K55" s="14" t="n">
         <v>170</v>
       </c>
+      <c r="L55" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M55" s="14" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -4282,6 +4776,12 @@
       <c r="K56" s="14" t="n">
         <v>4165</v>
       </c>
+      <c r="L56" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M56" s="14" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -4329,6 +4829,12 @@
       <c r="K57" s="14" t="n">
         <v>1851</v>
       </c>
+      <c r="L57" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M57" s="14" t="n">
+        <v>1852</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -4376,6 +4882,12 @@
       <c r="K58" s="14" t="n">
         <v>4660</v>
       </c>
+      <c r="L58" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M58" s="14" t="n">
+        <v>4661</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -4423,6 +4935,12 @@
       <c r="K59" s="14" t="n">
         <v>5783</v>
       </c>
+      <c r="L59" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v>5785</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -4470,6 +4988,12 @@
       <c r="K60" s="14" t="n">
         <v>6560</v>
       </c>
+      <c r="L60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M60" s="14" t="n">
+        <v>6562</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -4517,6 +5041,12 @@
       <c r="K61" s="14" t="n">
         <v>10708</v>
       </c>
+      <c r="L61" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M61" s="14" t="n">
+        <v>10710</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -4564,6 +5094,12 @@
       <c r="K62" s="14" t="n">
         <v>2069</v>
       </c>
+      <c r="L62" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M62" s="14" t="n">
+        <v>2069</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -4611,6 +5147,12 @@
       <c r="K63" s="14" t="n">
         <v>878</v>
       </c>
+      <c r="L63" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M63" s="14" t="n">
+        <v>878</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -4658,6 +5200,12 @@
       <c r="K64" s="14" t="n">
         <v>1204</v>
       </c>
+      <c r="L64" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M64" s="14" t="n">
+        <v>1205</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -4705,6 +5253,12 @@
       <c r="K65" s="14" t="n">
         <v>2069</v>
       </c>
+      <c r="L65" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M65" s="14" t="n">
+        <v>2069</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -4752,6 +5306,12 @@
       <c r="K66" s="14" t="n">
         <v>73</v>
       </c>
+      <c r="L66" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M66" s="14" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -4799,6 +5359,12 @@
       <c r="K67" s="14" t="n">
         <v>886</v>
       </c>
+      <c r="L67" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M67" s="14" t="n">
+        <v>886</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -4845,6 +5411,12 @@
       </c>
       <c r="K68" s="14" t="n">
         <v>14381</v>
+      </c>
+      <c r="L68" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M68" s="14" t="n">
+        <v>14386</v>
       </c>
     </row>
   </sheetData>
@@ -4858,7 +5430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K206"/>
+  <dimension ref="A1:M206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4887,6 +5459,12 @@
       <c r="K1" s="11" t="n">
         <v>46305</v>
       </c>
+      <c r="L1" s="11" t="n">
+        <v>46306</v>
+      </c>
+      <c r="M1" s="11" t="n">
+        <v>46306</v>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
@@ -4940,6 +5518,16 @@
         </is>
       </c>
       <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="L2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="M2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -4991,6 +5579,12 @@
       <c r="K3" s="14" t="n">
         <v>2128</v>
       </c>
+      <c r="L3" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M3" s="14" t="n">
+        <v>2142</v>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="7" t="n">
@@ -5038,6 +5632,12 @@
       <c r="K4" s="14" t="n">
         <v>634</v>
       </c>
+      <c r="L4" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M4" s="14" t="n">
+        <v>637</v>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="7" t="n">
@@ -5085,6 +5685,12 @@
       <c r="K5" s="14" t="n">
         <v>1556</v>
       </c>
+      <c r="L5" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>1556</v>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="7" t="n">
@@ -5132,6 +5738,12 @@
       <c r="K6" s="14" t="n">
         <v>147</v>
       </c>
+      <c r="L6" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M6" s="14" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="n">
@@ -5179,6 +5791,12 @@
       <c r="K7" s="14" t="n">
         <v>10894</v>
       </c>
+      <c r="L7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" s="14" t="n">
+        <v>10895</v>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="7" t="n">
@@ -5226,6 +5844,12 @@
       <c r="K8" s="14" t="n">
         <v>2945</v>
       </c>
+      <c r="L8" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>2947</v>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="7" t="n">
@@ -5273,6 +5897,12 @@
       <c r="K9" s="14" t="n">
         <v>221</v>
       </c>
+      <c r="L9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>221</v>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="7" t="n">
@@ -5320,6 +5950,12 @@
       <c r="K10" s="14" t="n">
         <v>5139</v>
       </c>
+      <c r="L10" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M10" s="14" t="n">
+        <v>5139</v>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="7" t="n">
@@ -5367,6 +6003,12 @@
       <c r="K11" s="14" t="n">
         <v>52638</v>
       </c>
+      <c r="L11" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>52651</v>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="7" t="n">
@@ -5414,6 +6056,12 @@
       <c r="K12" s="14" t="n">
         <v>340</v>
       </c>
+      <c r="L12" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>340</v>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="7" t="n">
@@ -5461,6 +6109,12 @@
       <c r="K13" s="14" t="n">
         <v>2508</v>
       </c>
+      <c r="L13" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>2513</v>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="7" t="n">
@@ -5508,6 +6162,12 @@
       <c r="K14" s="14" t="n">
         <v>108</v>
       </c>
+      <c r="L14" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="n">
@@ -5555,6 +6215,12 @@
       <c r="K15" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="L15" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="7" t="n">
@@ -5602,6 +6268,12 @@
       <c r="K16" s="14" t="n">
         <v>452</v>
       </c>
+      <c r="L16" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>452</v>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="n">
@@ -5649,6 +6321,12 @@
       <c r="K17" s="14" t="n">
         <v>2656</v>
       </c>
+      <c r="L17" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M17" s="14" t="n">
+        <v>2658</v>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="7" t="n">
@@ -5696,6 +6374,12 @@
       <c r="K18" s="14" t="n">
         <v>1624</v>
       </c>
+      <c r="L18" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" s="14" t="n">
+        <v>1624</v>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="7" t="n">
@@ -5743,6 +6427,12 @@
       <c r="K19" s="14" t="n">
         <v>607</v>
       </c>
+      <c r="L19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M19" s="14" t="n">
+        <v>610</v>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="7" t="n">
@@ -5790,6 +6480,12 @@
       <c r="K20" s="14" t="n">
         <v>102</v>
       </c>
+      <c r="L20" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M20" s="14" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="7" t="n">
@@ -5837,6 +6533,12 @@
       <c r="K21" s="14" t="n">
         <v>15</v>
       </c>
+      <c r="L21" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="7" t="n">
@@ -5884,6 +6586,12 @@
       <c r="K22" s="14" t="n">
         <v>6297</v>
       </c>
+      <c r="L22" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M22" s="14" t="n">
+        <v>6310</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="7" t="n">
@@ -5931,6 +6639,12 @@
       <c r="K23" s="14" t="n">
         <v>6223</v>
       </c>
+      <c r="L23" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M23" s="14" t="n">
+        <v>6217</v>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="7" t="n">
@@ -5978,6 +6692,12 @@
       <c r="K24" s="14" t="n">
         <v>13126</v>
       </c>
+      <c r="L24" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>13126</v>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="7" t="n">
@@ -6025,6 +6745,12 @@
       <c r="K25" s="14" t="n">
         <v>2365</v>
       </c>
+      <c r="L25" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>2374</v>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="7" t="n">
@@ -6072,6 +6798,12 @@
       <c r="K26" s="14" t="n">
         <v>1919</v>
       </c>
+      <c r="L26" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M26" s="14" t="n">
+        <v>1919</v>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="7" t="n">
@@ -6119,6 +6851,12 @@
       <c r="K27" s="14" t="n">
         <v>13</v>
       </c>
+      <c r="L27" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M27" s="14" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="7" t="n">
@@ -6166,6 +6904,12 @@
       <c r="K28" s="14" t="n">
         <v>10038</v>
       </c>
+      <c r="L28" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M28" s="14" t="n">
+        <v>10040</v>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="7" t="n">
@@ -6213,6 +6957,12 @@
       <c r="K29" s="14" t="n">
         <v>8674</v>
       </c>
+      <c r="L29" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M29" s="14" t="n">
+        <v>8674</v>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="n">
@@ -6260,6 +7010,12 @@
       <c r="K30" s="14" t="n">
         <v>22267</v>
       </c>
+      <c r="L30" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M30" s="14" t="n">
+        <v>22271</v>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="7" t="n">
@@ -6307,6 +7063,12 @@
       <c r="K31" s="14" t="n">
         <v>5576</v>
       </c>
+      <c r="L31" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M31" s="14" t="n">
+        <v>5578</v>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="7" t="n">
@@ -6349,6 +7111,12 @@
       <c r="K32" s="14" t="n">
         <v>12</v>
       </c>
+      <c r="L32" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M32" s="14" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="7" t="n">
@@ -6391,6 +7159,12 @@
       <c r="K33" s="14" t="n">
         <v>4875</v>
       </c>
+      <c r="L33" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M33" s="14" t="n">
+        <v>4875</v>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="7" t="n">
@@ -6433,6 +7207,12 @@
       <c r="K34" s="14" t="n">
         <v>895</v>
       </c>
+      <c r="L34" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M34" s="14" t="n">
+        <v>895</v>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="7" t="n">
@@ -6475,6 +7255,12 @@
       <c r="K35" s="14" t="n">
         <v>18</v>
       </c>
+      <c r="L35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M35" s="14" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="7" t="n">
@@ -6517,6 +7303,12 @@
       <c r="K36" s="14" t="n">
         <v>69</v>
       </c>
+      <c r="L36" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M36" s="14" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="7" t="n">
@@ -6559,6 +7351,12 @@
       <c r="K37" s="14" t="n">
         <v>1333</v>
       </c>
+      <c r="L37" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M37" s="14" t="n">
+        <v>1337</v>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="7" t="n">
@@ -6601,6 +7399,12 @@
       <c r="K38" s="14" t="n">
         <v>2688</v>
       </c>
+      <c r="L38" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M38" s="14" t="n">
+        <v>2694</v>
+      </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="7" t="n">
@@ -6643,6 +7447,12 @@
       <c r="K39" s="14" t="n">
         <v>23007</v>
       </c>
+      <c r="L39" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M39" s="14" t="n">
+        <v>23008</v>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="7" t="n">
@@ -6685,6 +7495,12 @@
       <c r="K40" s="14" t="n">
         <v>572</v>
       </c>
+      <c r="L40" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M40" s="14" t="n">
+        <v>572</v>
+      </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="7" t="n">
@@ -6727,6 +7543,12 @@
       <c r="K41" s="14" t="n">
         <v>461</v>
       </c>
+      <c r="L41" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M41" s="14" t="n">
+        <v>470</v>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="7" t="n">
@@ -6769,6 +7591,12 @@
       <c r="K42" s="14" t="n">
         <v>2426</v>
       </c>
+      <c r="L42" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M42" s="14" t="n">
+        <v>2428</v>
+      </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="7" t="n">
@@ -6811,6 +7639,12 @@
       <c r="K43" s="14" t="n">
         <v>143</v>
       </c>
+      <c r="L43" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M43" s="14" t="n">
+        <v>714</v>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="7" t="n">
@@ -6853,6 +7687,12 @@
       <c r="K44" s="14" t="n">
         <v>6557</v>
       </c>
+      <c r="L44" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M44" s="14" t="n">
+        <v>6563</v>
+      </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="7" t="n">
@@ -6895,6 +7735,12 @@
       <c r="K45" s="14" t="n">
         <v>1109</v>
       </c>
+      <c r="L45" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M45" s="14" t="n">
+        <v>1110</v>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="7" t="n">
@@ -6937,6 +7783,12 @@
       <c r="K46" s="14" t="n">
         <v>7192</v>
       </c>
+      <c r="L46" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M46" s="14" t="n">
+        <v>7177</v>
+      </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="7" t="n">
@@ -6979,6 +7831,12 @@
       <c r="K47" s="14" t="n">
         <v>3820</v>
       </c>
+      <c r="L47" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M47" s="14" t="n">
+        <v>3835</v>
+      </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="7" t="n">
@@ -7021,6 +7879,12 @@
       <c r="K48" s="14" t="n">
         <v>3648</v>
       </c>
+      <c r="L48" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M48" s="14" t="n">
+        <v>781</v>
+      </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="7" t="n">
@@ -7063,6 +7927,12 @@
       <c r="K49" s="14" t="n">
         <v>2384</v>
       </c>
+      <c r="L49" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M49" s="14" t="n">
+        <v>2391</v>
+      </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="7" t="n">
@@ -7105,6 +7975,12 @@
       <c r="K50" s="14" t="n">
         <v>5606</v>
       </c>
+      <c r="L50" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M50" s="14" t="n">
+        <v>5616</v>
+      </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="7" t="n">
@@ -7147,6 +8023,12 @@
       <c r="K51" s="14" t="n">
         <v>1007</v>
       </c>
+      <c r="L51" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M51" s="14" t="n">
+        <v>1007</v>
+      </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="7" t="n">
@@ -7189,6 +8071,12 @@
       <c r="K52" s="14" t="n">
         <v>28</v>
       </c>
+      <c r="L52" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M52" s="14" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="7" t="n">
@@ -7231,6 +8119,12 @@
       <c r="K53" s="14" t="n">
         <v>9652</v>
       </c>
+      <c r="L53" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M53" s="14" t="n">
+        <v>9654</v>
+      </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="7" t="n">
@@ -7273,6 +8167,12 @@
       <c r="K54" s="14" t="n">
         <v>796</v>
       </c>
+      <c r="L54" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M54" s="14" t="n">
+        <v>797</v>
+      </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="7" t="n">
@@ -7315,6 +8215,12 @@
       <c r="K55" s="14" t="n">
         <v>298</v>
       </c>
+      <c r="L55" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M55" s="14" t="n">
+        <v>298</v>
+      </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="7" t="n">
@@ -7357,6 +8263,12 @@
       <c r="K56" s="14" t="n">
         <v>51</v>
       </c>
+      <c r="L56" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M56" s="14" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="7" t="n">
@@ -7399,6 +8311,12 @@
       <c r="K57" s="14" t="n">
         <v>441</v>
       </c>
+      <c r="L57" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M57" s="14" t="n">
+        <v>444</v>
+      </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="7" t="n">
@@ -7441,6 +8359,12 @@
       <c r="K58" s="14" t="n">
         <v>203</v>
       </c>
+      <c r="L58" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M58" s="14" t="n">
+        <v>203</v>
+      </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="7" t="n">
@@ -7483,6 +8407,12 @@
       <c r="K59" s="14" t="n">
         <v>659</v>
       </c>
+      <c r="L59" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v>659</v>
+      </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="7" t="n">
@@ -7525,6 +8455,12 @@
       <c r="K60" s="14" t="n">
         <v>361</v>
       </c>
+      <c r="L60" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M60" s="14" t="n">
+        <v>362</v>
+      </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="7" t="n">
@@ -7567,6 +8503,12 @@
       <c r="K61" s="14" t="n">
         <v>2921</v>
       </c>
+      <c r="L61" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M61" s="14" t="n">
+        <v>2919</v>
+      </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="7" t="n">
@@ -7609,6 +8551,12 @@
       <c r="K62" s="14" t="n">
         <v>587</v>
       </c>
+      <c r="L62" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M62" s="14" t="n">
+        <v>587</v>
+      </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="7" t="n">
@@ -7651,6 +8599,12 @@
       <c r="K63" s="14" t="n">
         <v>9258</v>
       </c>
+      <c r="L63" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M63" s="14" t="n">
+        <v>9261</v>
+      </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="7" t="n">
@@ -7693,6 +8647,12 @@
       <c r="K64" s="14" t="n">
         <v>1008</v>
       </c>
+      <c r="L64" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M64" s="14" t="n">
+        <v>1008</v>
+      </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="7" t="n">
@@ -7735,6 +8695,12 @@
       <c r="K65" s="14" t="n">
         <v>3845</v>
       </c>
+      <c r="L65" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M65" s="14" t="n">
+        <v>3845</v>
+      </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="7" t="n">
@@ -7777,6 +8743,12 @@
       <c r="K66" s="14" t="n">
         <v>4139</v>
       </c>
+      <c r="L66" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M66" s="14" t="n">
+        <v>4139</v>
+      </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="7" t="n">
@@ -7819,6 +8791,12 @@
       <c r="K67" s="14" t="n">
         <v>26860</v>
       </c>
+      <c r="L67" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M67" s="14" t="n">
+        <v>26860</v>
+      </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="7" t="n">
@@ -7861,6 +8839,12 @@
       <c r="K68" s="14" t="n">
         <v>4321</v>
       </c>
+      <c r="L68" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M68" s="14" t="n">
+        <v>4321</v>
+      </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="7" t="n">
@@ -7903,6 +8887,12 @@
       <c r="K69" s="14" t="n">
         <v>2279</v>
       </c>
+      <c r="L69" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M69" s="14" t="n">
+        <v>2278</v>
+      </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="7" t="n">
@@ -7945,6 +8935,12 @@
       <c r="K70" s="14" t="n">
         <v>280</v>
       </c>
+      <c r="L70" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M70" s="14" t="n">
+        <v>281</v>
+      </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="7" t="n">
@@ -7987,6 +8983,12 @@
       <c r="K71" s="14" t="n">
         <v>6145</v>
       </c>
+      <c r="L71" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M71" s="14" t="n">
+        <v>6144</v>
+      </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="7" t="n">
@@ -8029,6 +9031,12 @@
       <c r="K72" s="14" t="n">
         <v>47</v>
       </c>
+      <c r="L72" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M72" s="14" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="7" t="n">
@@ -8071,6 +9079,12 @@
       <c r="K73" s="14" t="n">
         <v>1111</v>
       </c>
+      <c r="L73" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M73" s="14" t="n">
+        <v>1112</v>
+      </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="7" t="n">
@@ -8113,6 +9127,12 @@
       <c r="K74" s="14" t="n">
         <v>9514</v>
       </c>
+      <c r="L74" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M74" s="14" t="n">
+        <v>9514</v>
+      </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="7" t="n">
@@ -8155,6 +9175,12 @@
       <c r="K75" s="14" t="n">
         <v>16974</v>
       </c>
+      <c r="L75" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M75" s="14" t="n">
+        <v>16975</v>
+      </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="7" t="n">
@@ -8197,6 +9223,12 @@
       <c r="K76" s="14" t="n">
         <v>8565</v>
       </c>
+      <c r="L76" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M76" s="14" t="n">
+        <v>8567</v>
+      </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="7" t="n">
@@ -8239,6 +9271,12 @@
       <c r="K77" s="14" t="n">
         <v>2487</v>
       </c>
+      <c r="L77" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M77" s="14" t="n">
+        <v>2491</v>
+      </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="7" t="n">
@@ -8281,6 +9319,12 @@
       <c r="K78" s="14" t="n">
         <v>10945</v>
       </c>
+      <c r="L78" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M78" s="14" t="n">
+        <v>10950</v>
+      </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="7" t="n">
@@ -8323,6 +9367,12 @@
       <c r="K79" s="14" t="n">
         <v>175</v>
       </c>
+      <c r="L79" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M79" s="14" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="7" t="n">
@@ -8365,6 +9415,12 @@
       <c r="K80" s="14" t="n">
         <v>148</v>
       </c>
+      <c r="L80" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M80" s="14" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="7" t="n">
@@ -8415,6 +9471,16 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="L81" s="15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M81" s="15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="7" t="n">
@@ -8457,6 +9523,12 @@
       <c r="K82" s="14" t="n">
         <v>1452</v>
       </c>
+      <c r="L82" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M82" s="14" t="n">
+        <v>1459</v>
+      </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="7" t="n">
@@ -8499,6 +9571,12 @@
       <c r="K83" s="14" t="n">
         <v>1741</v>
       </c>
+      <c r="L83" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M83" s="14" t="n">
+        <v>1743</v>
+      </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="7" t="n">
@@ -8541,6 +9619,12 @@
       <c r="K84" s="14" t="n">
         <v>43</v>
       </c>
+      <c r="L84" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M84" s="14" t="n">
+        <v>43</v>
+      </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="7" t="n">
@@ -8583,6 +9667,12 @@
       <c r="K85" s="14" t="n">
         <v>461</v>
       </c>
+      <c r="L85" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M85" s="14" t="n">
+        <v>470</v>
+      </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="7" t="n">
@@ -8625,6 +9715,12 @@
       <c r="K86" s="14" t="n">
         <v>45</v>
       </c>
+      <c r="L86" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M86" s="14" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="7" t="n">
@@ -8667,6 +9763,12 @@
       <c r="K87" s="14" t="n">
         <v>4508</v>
       </c>
+      <c r="L87" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M87" s="14" t="n">
+        <v>4508</v>
+      </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="7" t="n">
@@ -8709,6 +9811,12 @@
       <c r="K88" s="14" t="n">
         <v>23</v>
       </c>
+      <c r="L88" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M88" s="14" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="7" t="n">
@@ -8751,6 +9859,12 @@
       <c r="K89" s="14" t="n">
         <v>118</v>
       </c>
+      <c r="L89" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M89" s="14" t="n">
+        <v>837</v>
+      </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="7" t="n">
@@ -8793,6 +9907,12 @@
       <c r="K90" s="14" t="n">
         <v>14</v>
       </c>
+      <c r="L90" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M90" s="14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="7" t="n">
@@ -8835,6 +9955,12 @@
       <c r="K91" s="14" t="n">
         <v>52</v>
       </c>
+      <c r="L91" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M91" s="14" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="7" t="n">
@@ -8877,6 +10003,12 @@
       <c r="K92" s="14" t="n">
         <v>391</v>
       </c>
+      <c r="L92" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M92" s="14" t="n">
+        <v>391</v>
+      </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="7" t="n">
@@ -8919,6 +10051,12 @@
       <c r="K93" s="14" t="n">
         <v>160</v>
       </c>
+      <c r="L93" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M93" s="14" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="7" t="n">
@@ -8961,6 +10099,12 @@
       <c r="K94" s="14" t="n">
         <v>1624</v>
       </c>
+      <c r="L94" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M94" s="14" t="n">
+        <v>1624</v>
+      </c>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="7" t="n">
@@ -9003,6 +10147,12 @@
       <c r="K95" s="14" t="n">
         <v>7500</v>
       </c>
+      <c r="L95" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M95" s="14" t="n">
+        <v>7503</v>
+      </c>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="7" t="n">
@@ -9045,6 +10195,12 @@
       <c r="K96" s="14" t="n">
         <v>2838</v>
       </c>
+      <c r="L96" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M96" s="14" t="n">
+        <v>2835</v>
+      </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="7" t="n">
@@ -9087,6 +10243,12 @@
       <c r="K97" s="14" t="n">
         <v>359</v>
       </c>
+      <c r="L97" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M97" s="14" t="n">
+        <v>359</v>
+      </c>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="7" t="n">
@@ -9129,6 +10291,12 @@
       <c r="K98" s="14" t="n">
         <v>42241</v>
       </c>
+      <c r="L98" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M98" s="14" t="n">
+        <v>42244</v>
+      </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="7" t="n">
@@ -9171,6 +10339,12 @@
       <c r="K99" s="14" t="n">
         <v>44063</v>
       </c>
+      <c r="L99" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M99" s="14" t="n">
+        <v>310</v>
+      </c>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="7" t="n">
@@ -9213,6 +10387,12 @@
       <c r="K100" s="14" t="n">
         <v>344</v>
       </c>
+      <c r="L100" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M100" s="14" t="n">
+        <v>346</v>
+      </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="7" t="n">
@@ -9255,6 +10435,12 @@
       <c r="K101" s="14" t="n">
         <v>24</v>
       </c>
+      <c r="L101" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M101" s="14" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="7" t="n">
@@ -9297,6 +10483,12 @@
       <c r="K102" s="14" t="n">
         <v>9</v>
       </c>
+      <c r="L102" s="14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M102" s="14" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="7" t="n">
@@ -9339,6 +10531,12 @@
       <c r="K103" s="14" t="n">
         <v>865</v>
       </c>
+      <c r="L103" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M103" s="14" t="n">
+        <v>867</v>
+      </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="7" t="n">
@@ -9381,6 +10579,12 @@
       <c r="K104" s="14" t="n">
         <v>429</v>
       </c>
+      <c r="L104" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M104" s="14" t="n">
+        <v>430</v>
+      </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="7" t="n">
@@ -9423,6 +10627,12 @@
       <c r="K105" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="L105" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M105" s="14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="7" t="n">
@@ -9465,6 +10675,12 @@
       <c r="K106" s="14" t="n">
         <v>40</v>
       </c>
+      <c r="L106" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M106" s="14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="7" t="n">
@@ -9507,6 +10723,12 @@
       <c r="K107" s="14" t="n">
         <v>4256</v>
       </c>
+      <c r="L107" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M107" s="14" t="n">
+        <v>4256</v>
+      </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="7" t="n">
@@ -9549,6 +10771,12 @@
       <c r="K108" s="14" t="n">
         <v>3</v>
       </c>
+      <c r="L108" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M108" s="14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="7" t="n">
@@ -9591,6 +10819,12 @@
       <c r="K109" s="14" t="n">
         <v>64</v>
       </c>
+      <c r="L109" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M109" s="14" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="7" t="n">
@@ -9633,6 +10867,12 @@
       <c r="K110" s="14" t="n">
         <v>100</v>
       </c>
+      <c r="L110" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M110" s="14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="7" t="n">
@@ -9675,6 +10915,12 @@
       <c r="K111" s="14" t="n">
         <v>866</v>
       </c>
+      <c r="L111" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M111" s="14" t="n">
+        <v>866</v>
+      </c>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="7" t="n">
@@ -9722,6 +10968,12 @@
       <c r="K112" s="14" t="n">
         <v>8426</v>
       </c>
+      <c r="L112" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M112" s="14" t="n">
+        <v>8408</v>
+      </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="7" t="n">
@@ -9769,6 +11021,12 @@
       <c r="K113" s="14" t="n">
         <v>4895</v>
       </c>
+      <c r="L113" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M113" s="14" t="n">
+        <v>4906</v>
+      </c>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="7" t="n">
@@ -9816,6 +11074,12 @@
       <c r="K114" s="14" t="n">
         <v>3365</v>
       </c>
+      <c r="L114" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M114" s="14" t="n">
+        <v>3368</v>
+      </c>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="7" t="n">
@@ -9863,6 +11127,12 @@
       <c r="K115" s="14" t="n">
         <v>170</v>
       </c>
+      <c r="L115" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M115" s="14" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="7" t="n">
@@ -9910,6 +11180,12 @@
       <c r="K116" s="14" t="n">
         <v>8674</v>
       </c>
+      <c r="L116" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M116" s="14" t="n">
+        <v>8674</v>
+      </c>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="7" t="n">
@@ -9957,6 +11233,12 @@
       <c r="K117" s="14" t="n">
         <v>11858</v>
       </c>
+      <c r="L117" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M117" s="14" t="n">
+        <v>11860</v>
+      </c>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="7" t="n">
@@ -10004,6 +11286,12 @@
       <c r="K118" s="14" t="n">
         <v>2792</v>
       </c>
+      <c r="L118" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M118" s="14" t="n">
+        <v>2794</v>
+      </c>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="7" t="n">
@@ -10051,6 +11339,12 @@
       <c r="K119" s="14" t="n">
         <v>89</v>
       </c>
+      <c r="L119" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M119" s="14" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="7" t="n">
@@ -10098,6 +11392,12 @@
       <c r="K120" s="14" t="n">
         <v>464</v>
       </c>
+      <c r="L120" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M120" s="14" t="n">
+        <v>465</v>
+      </c>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="7" t="n">
@@ -10145,6 +11445,12 @@
       <c r="K121" s="14" t="n">
         <v>776</v>
       </c>
+      <c r="L121" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M121" s="14" t="n">
+        <v>776</v>
+      </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="7" t="n">
@@ -10192,6 +11498,12 @@
       <c r="K122" s="14" t="n">
         <v>169</v>
       </c>
+      <c r="L122" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M122" s="14" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="7" t="n">
@@ -10239,6 +11551,12 @@
       <c r="K123" s="14" t="n">
         <v>14</v>
       </c>
+      <c r="L123" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M123" s="14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="7" t="n">
@@ -10286,6 +11604,12 @@
       <c r="K124" s="14" t="n">
         <v>41</v>
       </c>
+      <c r="L124" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M124" s="14" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="7" t="n">
@@ -10333,6 +11657,12 @@
       <c r="K125" s="14" t="n">
         <v>48</v>
       </c>
+      <c r="L125" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M125" s="14" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="7" t="n">
@@ -10380,6 +11710,12 @@
       <c r="K126" s="14" t="n">
         <v>11</v>
       </c>
+      <c r="L126" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M126" s="14" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="7" t="n">
@@ -10427,6 +11763,12 @@
       <c r="K127" s="14" t="n">
         <v>4192</v>
       </c>
+      <c r="L127" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M127" s="14" t="n">
+        <v>4192</v>
+      </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="7" t="n">
@@ -10474,6 +11816,12 @@
       <c r="K128" s="14" t="n">
         <v>291</v>
       </c>
+      <c r="L128" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M128" s="14" t="n">
+        <v>294</v>
+      </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="7" t="n">
@@ -10516,6 +11864,12 @@
       <c r="K129" s="14" t="n">
         <v>4228</v>
       </c>
+      <c r="L129" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M129" s="14" t="n">
+        <v>4228</v>
+      </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="7" t="n">
@@ -10558,6 +11912,12 @@
       <c r="K130" s="14" t="n">
         <v>660</v>
       </c>
+      <c r="L130" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M130" s="14" t="n">
+        <v>667</v>
+      </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="7" t="n">
@@ -10600,6 +11960,12 @@
       <c r="K131" s="14" t="n">
         <v>789</v>
       </c>
+      <c r="L131" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M131" s="14" t="n">
+        <v>790</v>
+      </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="7" t="n">
@@ -10642,6 +12008,12 @@
       <c r="K132" s="14" t="n">
         <v>720</v>
       </c>
+      <c r="L132" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M132" s="14" t="n">
+        <v>720</v>
+      </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="7" t="n">
@@ -10684,6 +12056,12 @@
       <c r="K133" s="14" t="n">
         <v>1424</v>
       </c>
+      <c r="L133" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M133" s="14" t="n">
+        <v>1424</v>
+      </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="7" t="n">
@@ -10726,6 +12104,12 @@
       <c r="K134" s="14" t="n">
         <v>698</v>
       </c>
+      <c r="L134" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M134" s="14" t="n">
+        <v>702</v>
+      </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="7" t="n">
@@ -10768,6 +12152,12 @@
       <c r="K135" s="14" t="n">
         <v>384</v>
       </c>
+      <c r="L135" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M135" s="14" t="n">
+        <v>384</v>
+      </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="7" t="n">
@@ -10810,6 +12200,12 @@
       <c r="K136" s="14" t="n">
         <v>384</v>
       </c>
+      <c r="L136" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M136" s="14" t="n">
+        <v>384</v>
+      </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="7" t="n">
@@ -10852,6 +12248,12 @@
       <c r="K137" s="14" t="n">
         <v>5284</v>
       </c>
+      <c r="L137" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M137" s="14" t="n">
+        <v>5288</v>
+      </c>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="7" t="n">
@@ -10894,6 +12296,12 @@
       <c r="K138" s="14" t="n">
         <v>2545</v>
       </c>
+      <c r="L138" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M138" s="14" t="n">
+        <v>2546</v>
+      </c>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="7" t="n">
@@ -10936,6 +12344,12 @@
       <c r="K139" s="14" t="n">
         <v>3199</v>
       </c>
+      <c r="L139" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M139" s="14" t="n">
+        <v>3198</v>
+      </c>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="7" t="n">
@@ -10978,6 +12392,12 @@
       <c r="K140" s="14" t="n">
         <v>1452</v>
       </c>
+      <c r="L140" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M140" s="14" t="n">
+        <v>1459</v>
+      </c>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="7" t="n">
@@ -11020,6 +12440,12 @@
       <c r="K141" s="14" t="n">
         <v>175</v>
       </c>
+      <c r="L141" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M141" s="14" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="7" t="n">
@@ -11062,6 +12488,12 @@
       <c r="K142" s="14" t="n">
         <v>19</v>
       </c>
+      <c r="L142" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M142" s="14" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="7" t="n">
@@ -11104,6 +12536,12 @@
       <c r="K143" s="14" t="n">
         <v>4204</v>
       </c>
+      <c r="L143" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M143" s="14" t="n">
+        <v>4214</v>
+      </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="7" t="n">
@@ -11146,6 +12584,12 @@
       <c r="K144" s="14" t="n">
         <v>4587</v>
       </c>
+      <c r="L144" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M144" s="14" t="n">
+        <v>4589</v>
+      </c>
     </row>
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="7" t="n">
@@ -11188,6 +12632,12 @@
       <c r="K145" s="14" t="n">
         <v>1533</v>
       </c>
+      <c r="L145" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M145" s="14" t="n">
+        <v>1533</v>
+      </c>
     </row>
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="7" t="n">
@@ -11230,6 +12680,12 @@
       <c r="K146" s="14" t="n">
         <v>3952</v>
       </c>
+      <c r="L146" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M146" s="14" t="n">
+        <v>3952</v>
+      </c>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="7" t="n">
@@ -11272,6 +12728,12 @@
       <c r="K147" s="14" t="n">
         <v>2953</v>
       </c>
+      <c r="L147" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M147" s="14" t="n">
+        <v>2953</v>
+      </c>
     </row>
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="7" t="n">
@@ -11314,6 +12776,12 @@
       <c r="K148" s="14" t="n">
         <v>63</v>
       </c>
+      <c r="L148" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M148" s="14" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="7" t="n">
@@ -11356,6 +12824,12 @@
       <c r="K149" s="14" t="n">
         <v>80</v>
       </c>
+      <c r="L149" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M149" s="14" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="7" t="n">
@@ -11398,6 +12872,12 @@
       <c r="K150" s="14" t="n">
         <v>2596</v>
       </c>
+      <c r="L150" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M150" s="14" t="n">
+        <v>2598</v>
+      </c>
     </row>
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="7" t="n">
@@ -11440,6 +12920,12 @@
       <c r="K151" s="14" t="n">
         <v>3845</v>
       </c>
+      <c r="L151" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M151" s="14" t="n">
+        <v>3845</v>
+      </c>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="7" t="n">
@@ -11482,6 +12968,12 @@
       <c r="K152" s="14" t="n">
         <v>510</v>
       </c>
+      <c r="L152" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M152" s="14" t="n">
+        <v>511</v>
+      </c>
     </row>
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="7" t="n">
@@ -11524,6 +13016,12 @@
       <c r="K153" s="14" t="n">
         <v>9258</v>
       </c>
+      <c r="L153" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M153" s="14" t="n">
+        <v>9261</v>
+      </c>
     </row>
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="7" t="n">
@@ -11566,6 +13064,12 @@
       <c r="K154" s="14" t="n">
         <v>9245</v>
       </c>
+      <c r="L154" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M154" s="14" t="n">
+        <v>9245</v>
+      </c>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="7" t="n">
@@ -11608,6 +13112,12 @@
       <c r="K155" s="14" t="n">
         <v>4321</v>
       </c>
+      <c r="L155" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M155" s="14" t="n">
+        <v>4321</v>
+      </c>
     </row>
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="7" t="n">
@@ -11650,6 +13160,12 @@
       <c r="K156" s="14" t="n">
         <v>199</v>
       </c>
+      <c r="L156" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M156" s="14" t="n">
+        <v>199</v>
+      </c>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="7" t="n">
@@ -11692,6 +13208,12 @@
       <c r="K157" s="14" t="n">
         <v>587</v>
       </c>
+      <c r="L157" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M157" s="14" t="n">
+        <v>587</v>
+      </c>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="7" t="n">
@@ -11734,6 +13256,12 @@
       <c r="K158" s="14" t="n">
         <v>81</v>
       </c>
+      <c r="L158" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M158" s="14" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="7" t="n">
@@ -11776,6 +13304,12 @@
       <c r="K159" s="14" t="n">
         <v>38</v>
       </c>
+      <c r="L159" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M159" s="14" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="160" ht="20" customHeight="1">
       <c r="A160" s="7" t="n">
@@ -11818,6 +13352,12 @@
       <c r="K160" s="14" t="n">
         <v>98</v>
       </c>
+      <c r="L160" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M160" s="14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="7" t="n">
@@ -11860,6 +13400,12 @@
       <c r="K161" s="14" t="n">
         <v>117</v>
       </c>
+      <c r="L161" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M161" s="14" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="7" t="n">
@@ -11902,6 +13448,12 @@
       <c r="K162" s="14" t="n">
         <v>1954</v>
       </c>
+      <c r="L162" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M162" s="14" t="n">
+        <v>1955</v>
+      </c>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="7" t="n">
@@ -11944,6 +13496,12 @@
       <c r="K163" s="14" t="n">
         <v>1699</v>
       </c>
+      <c r="L163" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M163" s="14" t="n">
+        <v>1700</v>
+      </c>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="7" t="n">
@@ -11986,6 +13544,12 @@
       <c r="K164" s="14" t="n">
         <v>9352</v>
       </c>
+      <c r="L164" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M164" s="14" t="n">
+        <v>9353</v>
+      </c>
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="7" t="n">
@@ -12028,6 +13592,12 @@
       <c r="K165" s="14" t="n">
         <v>1092</v>
       </c>
+      <c r="L165" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M165" s="14" t="n">
+        <v>1092</v>
+      </c>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="7" t="n">
@@ -12070,6 +13640,12 @@
       <c r="K166" s="14" t="n">
         <v>175</v>
       </c>
+      <c r="L166" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M166" s="14" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="7" t="n">
@@ -12112,6 +13688,12 @@
       <c r="K167" s="14" t="n">
         <v>3362</v>
       </c>
+      <c r="L167" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M167" s="14" t="n">
+        <v>3363</v>
+      </c>
     </row>
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="7" t="n">
@@ -12154,6 +13736,12 @@
       <c r="K168" s="14" t="n">
         <v>850</v>
       </c>
+      <c r="L168" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M168" s="14" t="n">
+        <v>851</v>
+      </c>
     </row>
     <row r="169" ht="20" customHeight="1">
       <c r="A169" s="7" t="n">
@@ -12196,6 +13784,12 @@
       <c r="K169" s="14" t="n">
         <v>121</v>
       </c>
+      <c r="L169" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M169" s="14" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="170" ht="20" customHeight="1">
       <c r="A170" s="7" t="n">
@@ -12238,6 +13832,12 @@
       <c r="K170" s="14" t="n">
         <v>142</v>
       </c>
+      <c r="L170" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M170" s="14" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="7" t="n">
@@ -12280,6 +13880,12 @@
       <c r="K171" s="14" t="n">
         <v>220</v>
       </c>
+      <c r="L171" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M171" s="14" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="7" t="n">
@@ -12322,6 +13928,12 @@
       <c r="K172" s="14" t="n">
         <v>190</v>
       </c>
+      <c r="L172" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M172" s="14" t="n">
+        <v>190</v>
+      </c>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="7" t="n">
@@ -12364,6 +13976,12 @@
       <c r="K173" s="14" t="n">
         <v>407</v>
       </c>
+      <c r="L173" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M173" s="14" t="n">
+        <v>408</v>
+      </c>
     </row>
     <row r="174" ht="20" customHeight="1">
       <c r="A174" s="7" t="n">
@@ -12406,6 +14024,12 @@
       <c r="K174" s="14" t="n">
         <v>71</v>
       </c>
+      <c r="L174" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M174" s="14" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="7" t="n">
@@ -12448,6 +14072,12 @@
       <c r="K175" s="14" t="n">
         <v>78</v>
       </c>
+      <c r="L175" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M175" s="14" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="7" t="n">
@@ -12490,6 +14120,12 @@
       <c r="K176" s="14" t="n">
         <v>2053</v>
       </c>
+      <c r="L176" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M176" s="14" t="n">
+        <v>2054</v>
+      </c>
     </row>
     <row r="177" ht="20" customHeight="1">
       <c r="A177" s="7" t="n">
@@ -12532,6 +14168,12 @@
       <c r="K177" s="14" t="n">
         <v>566</v>
       </c>
+      <c r="L177" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M177" s="14" t="n">
+        <v>567</v>
+      </c>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="7" t="n">
@@ -12574,6 +14216,12 @@
       <c r="K178" s="14" t="n">
         <v>4077</v>
       </c>
+      <c r="L178" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M178" s="14" t="n">
+        <v>4077</v>
+      </c>
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="7" t="n">
@@ -12616,6 +14264,12 @@
       <c r="K179" s="14" t="n">
         <v>3197</v>
       </c>
+      <c r="L179" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M179" s="14" t="n">
+        <v>3197</v>
+      </c>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="7" t="n">
@@ -12658,6 +14312,12 @@
       <c r="K180" s="14" t="n">
         <v>494</v>
       </c>
+      <c r="L180" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M180" s="14" t="n">
+        <v>494</v>
+      </c>
     </row>
     <row r="181" ht="20" customHeight="1">
       <c r="A181" s="7" t="n">
@@ -12700,6 +14360,12 @@
       <c r="K181" s="14" t="n">
         <v>180</v>
       </c>
+      <c r="L181" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M181" s="14" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="182" ht="20" customHeight="1">
       <c r="A182" s="7" t="n">
@@ -12742,6 +14408,12 @@
       <c r="K182" s="14" t="n">
         <v>4077</v>
       </c>
+      <c r="L182" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M182" s="14" t="n">
+        <v>4077</v>
+      </c>
     </row>
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="7" t="n">
@@ -12784,6 +14456,12 @@
       <c r="K183" s="14" t="n">
         <v>219</v>
       </c>
+      <c r="L183" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M183" s="14" t="n">
+        <v>219</v>
+      </c>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="7" t="n">
@@ -12826,6 +14504,12 @@
       <c r="K184" s="14" t="n">
         <v>372</v>
       </c>
+      <c r="L184" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M184" s="14" t="n">
+        <v>372</v>
+      </c>
     </row>
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="7" t="n">
@@ -12868,6 +14552,12 @@
       <c r="K185" s="14" t="n">
         <v>728</v>
       </c>
+      <c r="L185" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M185" s="14" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="186" ht="20" customHeight="1">
       <c r="A186" s="7" t="n">
@@ -12910,6 +14600,12 @@
       <c r="K186" s="14" t="n">
         <v>436</v>
       </c>
+      <c r="L186" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M186" s="14" t="n">
+        <v>436</v>
+      </c>
     </row>
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="7" t="n">
@@ -12952,6 +14648,12 @@
       <c r="K187" s="14" t="n">
         <v>15</v>
       </c>
+      <c r="L187" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M187" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="188" ht="20" customHeight="1">
       <c r="A188" s="7" t="n">
@@ -12994,6 +14696,12 @@
       <c r="K188" s="14" t="n">
         <v>9</v>
       </c>
+      <c r="L188" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M188" s="14" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="7" t="n">
@@ -13036,6 +14744,12 @@
       <c r="K189" s="14" t="n">
         <v>196</v>
       </c>
+      <c r="L189" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M189" s="14" t="n">
+        <v>196</v>
+      </c>
     </row>
     <row r="190" ht="20" customHeight="1">
       <c r="A190" s="7" t="n">
@@ -13078,6 +14792,12 @@
       <c r="K190" s="14" t="n">
         <v>64</v>
       </c>
+      <c r="L190" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M190" s="14" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="191" ht="20" customHeight="1">
       <c r="A191" s="7" t="n">
@@ -13120,6 +14840,12 @@
       <c r="K191" s="14" t="n">
         <v>7437</v>
       </c>
+      <c r="L191" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M191" s="14" t="n">
+        <v>7443</v>
+      </c>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="7" t="n">
@@ -13162,6 +14888,12 @@
       <c r="K192" s="14" t="n">
         <v>2942</v>
       </c>
+      <c r="L192" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M192" s="14" t="n">
+        <v>2944</v>
+      </c>
     </row>
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="7" t="n">
@@ -13204,6 +14936,12 @@
       <c r="K193" s="14" t="n">
         <v>491</v>
       </c>
+      <c r="L193" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M193" s="14" t="n">
+        <v>493</v>
+      </c>
     </row>
     <row r="194" ht="20" customHeight="1">
       <c r="A194" s="7" t="n">
@@ -13246,6 +14984,12 @@
       <c r="K194" s="14" t="n">
         <v>64</v>
       </c>
+      <c r="L194" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M194" s="14" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="195" ht="20" customHeight="1">
       <c r="A195" s="7" t="n">
@@ -13288,6 +15032,12 @@
       <c r="K195" s="14" t="n">
         <v>2230</v>
       </c>
+      <c r="L195" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M195" s="14" t="n">
+        <v>2230</v>
+      </c>
     </row>
     <row r="196" ht="20" customHeight="1">
       <c r="A196" s="7" t="n">
@@ -13330,6 +15080,12 @@
       <c r="K196" s="14" t="n">
         <v>2677</v>
       </c>
+      <c r="L196" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M196" s="14" t="n">
+        <v>2680</v>
+      </c>
     </row>
     <row r="197" ht="20" customHeight="1">
       <c r="A197" s="7" t="n">
@@ -13372,6 +15128,12 @@
       <c r="K197" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="L197" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" s="14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="7" t="n">
@@ -13414,6 +15176,12 @@
       <c r="K198" s="14" t="n">
         <v>8993</v>
       </c>
+      <c r="L198" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M198" s="14" t="n">
+        <v>8993</v>
+      </c>
     </row>
     <row r="199" ht="20" customHeight="1">
       <c r="A199" s="7" t="n">
@@ -13456,6 +15224,12 @@
       <c r="K199" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="L199" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M199" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="200" ht="20" customHeight="1">
       <c r="A200" s="7" t="n">
@@ -13498,6 +15272,12 @@
       <c r="K200" s="14" t="n">
         <v>190</v>
       </c>
+      <c r="L200" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M200" s="14" t="n">
+        <v>191</v>
+      </c>
     </row>
     <row r="201" ht="20" customHeight="1">
       <c r="A201" s="7" t="n">
@@ -13540,6 +15320,12 @@
       <c r="K201" s="14" t="n">
         <v>143</v>
       </c>
+      <c r="L201" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M201" s="14" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="202" ht="20" customHeight="1">
       <c r="A202" s="7" t="n">
@@ -13582,6 +15368,12 @@
       <c r="K202" s="14" t="n">
         <v>2884</v>
       </c>
+      <c r="L202" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M202" s="14" t="n">
+        <v>2886</v>
+      </c>
     </row>
     <row r="203" ht="20" customHeight="1">
       <c r="A203" s="7" t="n">
@@ -13624,6 +15416,12 @@
       <c r="K203" s="14" t="n">
         <v>17019</v>
       </c>
+      <c r="L203" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M203" s="14" t="n">
+        <v>17057</v>
+      </c>
     </row>
     <row r="204" ht="20" customHeight="1">
       <c r="A204" s="7" t="n">
@@ -13666,6 +15464,12 @@
       <c r="K204" s="14" t="n">
         <v>153</v>
       </c>
+      <c r="L204" s="14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M204" s="14" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="205" ht="20" customHeight="1">
       <c r="A205" s="7" t="n">
@@ -13708,6 +15512,12 @@
       <c r="K205" s="14" t="n">
         <v>338</v>
       </c>
+      <c r="L205" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M205" s="14" t="n">
+        <v>338</v>
+      </c>
     </row>
     <row r="206" ht="20" customHeight="1">
       <c r="A206" s="7" t="n">
@@ -13748,6 +15558,12 @@
         <v>4.5</v>
       </c>
       <c r="K206" s="14" t="n">
+        <v>161</v>
+      </c>
+      <c r="L206" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M206" s="14" t="n">
         <v>161</v>
       </c>
     </row>
@@ -13763,7 +15579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13792,6 +15608,12 @@
       <c r="J1" s="11" t="n">
         <v>46305</v>
       </c>
+      <c r="K1" s="11" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L1" s="11" t="n">
+        <v>46306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -13840,6 +15662,16 @@
         </is>
       </c>
       <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -13886,6 +15718,12 @@
       <c r="J3" s="14" t="n">
         <v>7020</v>
       </c>
+      <c r="K3" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>7029</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -13928,6 +15766,12 @@
       <c r="J4" s="14" t="n">
         <v>1724</v>
       </c>
+      <c r="K4" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L4" s="14" t="n">
+        <v>1723</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -13970,6 +15814,12 @@
       <c r="J5" s="14" t="n">
         <v>3417</v>
       </c>
+      <c r="K5" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>3418</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -14012,6 +15862,12 @@
       <c r="J6" s="14" t="n">
         <v>1351</v>
       </c>
+      <c r="K6" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L6" s="14" t="n">
+        <v>1351</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -14054,6 +15910,12 @@
       <c r="J7" s="14" t="n">
         <v>1112</v>
       </c>
+      <c r="K7" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>1114</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -14096,6 +15958,12 @@
       <c r="J8" s="14" t="n">
         <v>3371</v>
       </c>
+      <c r="K8" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L8" s="14" t="n">
+        <v>3374</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -14138,6 +16006,12 @@
       <c r="J9" s="14" t="n">
         <v>1973</v>
       </c>
+      <c r="K9" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>1975</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -14180,6 +16054,12 @@
       <c r="J10" s="14" t="n">
         <v>1204</v>
       </c>
+      <c r="K10" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L10" s="14" t="n">
+        <v>1207</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -14222,6 +16102,12 @@
       <c r="J11" s="14" t="n">
         <v>813</v>
       </c>
+      <c r="K11" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>813</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -14264,6 +16150,12 @@
       <c r="J12" s="14" t="n">
         <v>3417</v>
       </c>
+      <c r="K12" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>3418</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -14306,6 +16198,12 @@
       <c r="J13" s="14" t="n">
         <v>415</v>
       </c>
+      <c r="K13" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>409</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -14348,6 +16246,12 @@
       <c r="J14" s="14" t="n">
         <v>3478</v>
       </c>
+      <c r="K14" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>3484</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -14390,6 +16294,12 @@
       <c r="J15" s="14" t="n">
         <v>1986</v>
       </c>
+      <c r="K15" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>1986</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -14432,6 +16342,12 @@
       <c r="J16" s="14" t="n">
         <v>1336</v>
       </c>
+      <c r="K16" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>1336</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -14474,6 +16390,12 @@
       <c r="J17" s="14" t="n">
         <v>1338</v>
       </c>
+      <c r="K17" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>1338</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -14516,6 +16438,12 @@
       <c r="J18" s="14" t="n">
         <v>4505</v>
       </c>
+      <c r="K18" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>4505</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -14558,6 +16486,12 @@
       <c r="J19" s="14" t="n">
         <v>1677</v>
       </c>
+      <c r="K19" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>1677</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -14600,6 +16534,12 @@
       <c r="J20" s="14" t="n">
         <v>4385</v>
       </c>
+      <c r="K20" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>4387</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -14642,6 +16582,12 @@
       <c r="J21" s="14" t="n">
         <v>3878</v>
       </c>
+      <c r="K21" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>3885</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -14684,6 +16630,12 @@
       <c r="J22" s="14" t="n">
         <v>87</v>
       </c>
+      <c r="K22" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -14726,6 +16678,12 @@
       <c r="J23" s="14" t="n">
         <v>443</v>
       </c>
+      <c r="K23" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>443</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -14768,6 +16726,12 @@
       <c r="J24" s="14" t="n">
         <v>1684</v>
       </c>
+      <c r="K24" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>1684</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -14810,6 +16774,12 @@
       <c r="J25" s="14" t="n">
         <v>3369</v>
       </c>
+      <c r="K25" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>3378</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -14852,6 +16822,12 @@
       <c r="J26" s="14" t="n">
         <v>1765</v>
       </c>
+      <c r="K26" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L26" s="14" t="n">
+        <v>1765</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -14894,6 +16870,12 @@
       <c r="J27" s="14" t="n">
         <v>537</v>
       </c>
+      <c r="K27" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L27" s="14" t="n">
+        <v>538</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -14936,6 +16918,12 @@
       <c r="J28" s="14" t="n">
         <v>1324</v>
       </c>
+      <c r="K28" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L28" s="14" t="n">
+        <v>1327</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -14978,6 +16966,12 @@
       <c r="J29" s="14" t="n">
         <v>646</v>
       </c>
+      <c r="K29" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>652</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -15020,6 +17014,12 @@
       <c r="J30" s="14" t="n">
         <v>35</v>
       </c>
+      <c r="K30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L30" s="14" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -15062,6 +17062,12 @@
       <c r="J31" s="14" t="n">
         <v>1323</v>
       </c>
+      <c r="K31" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L31" s="14" t="n">
+        <v>1325</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -15104,6 +17110,12 @@
       <c r="J32" s="14" t="n">
         <v>1428</v>
       </c>
+      <c r="K32" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L32" s="14" t="n">
+        <v>1428</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -15146,6 +17158,12 @@
       <c r="J33" s="14" t="n">
         <v>1335</v>
       </c>
+      <c r="K33" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L33" s="14" t="n">
+        <v>1335</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -15188,6 +17206,12 @@
       <c r="J34" s="14" t="n">
         <v>193</v>
       </c>
+      <c r="K34" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" s="14" t="n">
+        <v>198</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -15230,6 +17254,12 @@
       <c r="J35" s="14" t="n">
         <v>126</v>
       </c>
+      <c r="K35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L35" s="14" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -15272,6 +17302,12 @@
       <c r="J36" s="14" t="n">
         <v>995</v>
       </c>
+      <c r="K36" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L36" s="14" t="n">
+        <v>995</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -15314,6 +17350,12 @@
       <c r="J37" s="14" t="n">
         <v>205</v>
       </c>
+      <c r="K37" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L37" s="14" t="n">
+        <v>205</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -15356,6 +17398,12 @@
       <c r="J38" s="14" t="n">
         <v>213</v>
       </c>
+      <c r="K38" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L38" s="14" t="n">
+        <v>219</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -15398,6 +17446,12 @@
       <c r="J39" s="14" t="n">
         <v>863</v>
       </c>
+      <c r="K39" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L39" s="14" t="n">
+        <v>863</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -15440,6 +17494,12 @@
       <c r="J40" s="14" t="n">
         <v>2245</v>
       </c>
+      <c r="K40" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L40" s="14" t="n">
+        <v>2250</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -15482,6 +17542,12 @@
       <c r="J41" s="14" t="n">
         <v>450</v>
       </c>
+      <c r="K41" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L41" s="14" t="n">
+        <v>452</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -15524,6 +17590,12 @@
       <c r="J42" s="14" t="n">
         <v>1589</v>
       </c>
+      <c r="K42" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L42" s="14" t="n">
+        <v>1594</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -15566,6 +17638,12 @@
       <c r="J43" s="14" t="n">
         <v>1167</v>
       </c>
+      <c r="K43" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L43" s="14" t="n">
+        <v>1168</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -15608,6 +17686,12 @@
       <c r="J44" s="14" t="n">
         <v>475</v>
       </c>
+      <c r="K44" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L44" s="14" t="n">
+        <v>475</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -15650,6 +17734,12 @@
       <c r="J45" s="14" t="n">
         <v>449</v>
       </c>
+      <c r="K45" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L45" s="14" t="n">
+        <v>460</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -15692,6 +17782,12 @@
       <c r="J46" s="14" t="n">
         <v>1051</v>
       </c>
+      <c r="K46" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L46" s="14" t="n">
+        <v>1055</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -15734,6 +17830,12 @@
       <c r="J47" s="14" t="n">
         <v>2572</v>
       </c>
+      <c r="K47" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L47" s="14" t="n">
+        <v>2572</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -15776,6 +17878,12 @@
       <c r="J48" s="14" t="n">
         <v>1429</v>
       </c>
+      <c r="K48" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L48" s="14" t="n">
+        <v>1429</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -15818,6 +17926,12 @@
       <c r="J49" s="14" t="n">
         <v>1421</v>
       </c>
+      <c r="K49" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L49" s="14" t="n">
+        <v>1422</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -15860,6 +17974,12 @@
       <c r="J50" s="14" t="n">
         <v>1553</v>
       </c>
+      <c r="K50" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L50" s="14" t="n">
+        <v>1553</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -15902,6 +18022,12 @@
       <c r="J51" s="14" t="n">
         <v>2810</v>
       </c>
+      <c r="K51" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L51" s="14" t="n">
+        <v>2810</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -15944,6 +18070,12 @@
       <c r="J52" s="14" t="n">
         <v>745</v>
       </c>
+      <c r="K52" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L52" s="14" t="n">
+        <v>745</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -15986,6 +18118,12 @@
       <c r="J53" s="14" t="n">
         <v>1229</v>
       </c>
+      <c r="K53" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L53" s="14" t="n">
+        <v>1230</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -16028,6 +18166,12 @@
       <c r="J54" s="14" t="n">
         <v>674</v>
       </c>
+      <c r="K54" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L54" s="14" t="n">
+        <v>675</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -16069,6 +18213,12 @@
       </c>
       <c r="J55" s="14" t="n">
         <v>426</v>
+      </c>
+      <c r="K55" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L55" s="14" t="n">
+        <v>427</v>
       </c>
     </row>
     <row r="56">
@@ -16316,7 +18466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -16345,6 +18495,12 @@
       <c r="J1" s="11" t="n">
         <v>46305</v>
       </c>
+      <c r="K1" s="11" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L1" s="11" t="n">
+        <v>46306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -16393,6 +18549,16 @@
         </is>
       </c>
       <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -16439,6 +18605,12 @@
       <c r="J3" s="14" t="n">
         <v>4571</v>
       </c>
+      <c r="K3" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>4572</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -16481,6 +18653,12 @@
       <c r="J4" s="14" t="n">
         <v>1234</v>
       </c>
+      <c r="K4" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L4" s="14" t="n">
+        <v>1234</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -16523,6 +18701,12 @@
       <c r="J5" s="14" t="n">
         <v>460</v>
       </c>
+      <c r="K5" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>460</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -16565,6 +18749,12 @@
       <c r="J6" s="14" t="n">
         <v>11589</v>
       </c>
+      <c r="K6" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L6" s="14" t="n">
+        <v>11590</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -16607,6 +18797,12 @@
       <c r="J7" s="14" t="n">
         <v>2051</v>
       </c>
+      <c r="K7" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>2051</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -16649,6 +18845,12 @@
       <c r="J8" s="14" t="n">
         <v>919</v>
       </c>
+      <c r="K8" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L8" s="14" t="n">
+        <v>919</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -16691,6 +18893,12 @@
       <c r="J9" s="14" t="n">
         <v>1605</v>
       </c>
+      <c r="K9" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>1605</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -16733,6 +18941,12 @@
       <c r="J10" s="14" t="n">
         <v>2026</v>
       </c>
+      <c r="K10" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L10" s="14" t="n">
+        <v>2026</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -16775,6 +18989,12 @@
       <c r="J11" s="14" t="n">
         <v>3082</v>
       </c>
+      <c r="K11" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>3081</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -16817,6 +19037,12 @@
       <c r="J12" s="14" t="n">
         <v>3630</v>
       </c>
+      <c r="K12" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>3631</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -16859,6 +19085,12 @@
       <c r="J13" s="14" t="n">
         <v>21272</v>
       </c>
+      <c r="K13" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>21275</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -16901,6 +19133,12 @@
       <c r="J14" s="14" t="n">
         <v>2949</v>
       </c>
+      <c r="K14" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>2949</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -16943,6 +19181,12 @@
       <c r="J15" s="14" t="n">
         <v>4207</v>
       </c>
+      <c r="K15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>4211</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -16985,6 +19229,12 @@
       <c r="J16" s="14" t="n">
         <v>2394</v>
       </c>
+      <c r="K16" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>2394</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -17027,6 +19277,12 @@
       <c r="J17" s="14" t="n">
         <v>4</v>
       </c>
+      <c r="K17" s="14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -17069,6 +19325,12 @@
       <c r="J18" s="14" t="n">
         <v>12126</v>
       </c>
+      <c r="K18" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>12126</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -17111,6 +19373,12 @@
       <c r="J19" s="14" t="n">
         <v>3107</v>
       </c>
+      <c r="K19" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>3109</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -17153,6 +19421,12 @@
       <c r="J20" s="14" t="n">
         <v>9249</v>
       </c>
+      <c r="K20" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>9250</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -17195,6 +19469,12 @@
       <c r="J21" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="K21" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -17237,6 +19517,12 @@
       <c r="J22" s="14" t="n">
         <v>6139</v>
       </c>
+      <c r="K22" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>6135</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -17279,6 +19565,12 @@
       <c r="J23" s="14" t="n">
         <v>1753</v>
       </c>
+      <c r="K23" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>1746</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -17321,6 +19613,12 @@
       <c r="J24" s="14" t="n">
         <v>1060</v>
       </c>
+      <c r="K24" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>1063</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -17363,6 +19661,12 @@
       <c r="J25" s="14" t="n">
         <v>2056</v>
       </c>
+      <c r="K25" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>2057</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -17405,6 +19709,12 @@
       <c r="J26" s="14" t="n">
         <v>2780</v>
       </c>
+      <c r="K26" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L26" s="14" t="n">
+        <v>2780</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -17447,6 +19757,12 @@
       <c r="J27" s="14" t="n">
         <v>11105</v>
       </c>
+      <c r="K27" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L27" s="14" t="n">
+        <v>11108</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -17489,6 +19805,12 @@
       <c r="J28" s="14" t="n">
         <v>5490</v>
       </c>
+      <c r="K28" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L28" s="14" t="n">
+        <v>5492</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -17531,6 +19853,12 @@
       <c r="J29" s="14" t="n">
         <v>4019</v>
       </c>
+      <c r="K29" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>4020</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -17573,6 +19901,12 @@
       <c r="J30" s="14" t="n">
         <v>1581</v>
       </c>
+      <c r="K30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L30" s="14" t="n">
+        <v>1582</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -17615,6 +19949,12 @@
       <c r="J31" s="14" t="n">
         <v>1581</v>
       </c>
+      <c r="K31" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L31" s="14" t="n">
+        <v>1582</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -17657,6 +19997,12 @@
       <c r="J32" s="14" t="n">
         <v>2813</v>
       </c>
+      <c r="K32" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L32" s="14" t="n">
+        <v>2814</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -17699,6 +20045,12 @@
       <c r="J33" s="14" t="n">
         <v>18972</v>
       </c>
+      <c r="K33" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="14" t="n">
+        <v>18975</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -17741,6 +20093,12 @@
       <c r="J34" s="14" t="n">
         <v>39706</v>
       </c>
+      <c r="K34" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L34" s="14" t="n">
+        <v>39715</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -17783,6 +20141,12 @@
       <c r="J35" s="14" t="n">
         <v>5229</v>
       </c>
+      <c r="K35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L35" s="14" t="n">
+        <v>5228</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -17825,6 +20189,12 @@
       <c r="J36" s="14" t="n">
         <v>10388</v>
       </c>
+      <c r="K36" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L36" s="14" t="n">
+        <v>10391</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -17867,6 +20237,12 @@
       <c r="J37" s="14" t="n">
         <v>7410</v>
       </c>
+      <c r="K37" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L37" s="14" t="n">
+        <v>7410</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -17909,6 +20285,12 @@
       <c r="J38" s="14" t="n">
         <v>539</v>
       </c>
+      <c r="K38" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L38" s="14" t="n">
+        <v>540</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -17951,6 +20333,12 @@
       <c r="J39" s="14" t="n">
         <v>1124</v>
       </c>
+      <c r="K39" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L39" s="14" t="n">
+        <v>1124</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -17993,6 +20381,12 @@
       <c r="J40" s="14" t="n">
         <v>539</v>
       </c>
+      <c r="K40" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L40" s="14" t="n">
+        <v>540</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -18035,6 +20429,12 @@
       <c r="J41" s="14" t="n">
         <v>2627</v>
       </c>
+      <c r="K41" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L41" s="14" t="n">
+        <v>2628</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -18077,6 +20477,12 @@
       <c r="J42" s="14" t="n">
         <v>1447</v>
       </c>
+      <c r="K42" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L42" s="14" t="n">
+        <v>1447</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -18119,6 +20525,12 @@
       <c r="J43" s="14" t="n">
         <v>955</v>
       </c>
+      <c r="K43" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L43" s="14" t="n">
+        <v>955</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -18161,6 +20573,12 @@
       <c r="J44" s="14" t="n">
         <v>4188</v>
       </c>
+      <c r="K44" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L44" s="14" t="n">
+        <v>4200</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -18203,6 +20621,12 @@
       <c r="J45" s="14" t="n">
         <v>3488</v>
       </c>
+      <c r="K45" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L45" s="14" t="n">
+        <v>3491</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -18245,6 +20669,12 @@
       <c r="J46" s="14" t="n">
         <v>7887</v>
       </c>
+      <c r="K46" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L46" s="14" t="n">
+        <v>7888</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -18287,6 +20717,12 @@
       <c r="J47" s="14" t="n">
         <v>6139</v>
       </c>
+      <c r="K47" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L47" s="14" t="n">
+        <v>6135</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -18329,6 +20765,12 @@
       <c r="J48" s="14" t="n">
         <v>983</v>
       </c>
+      <c r="K48" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L48" s="14" t="n">
+        <v>983</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -18371,6 +20813,12 @@
       <c r="J49" s="14" t="n">
         <v>3654</v>
       </c>
+      <c r="K49" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L49" s="14" t="n">
+        <v>3658</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -18413,6 +20861,12 @@
       <c r="J50" s="14" t="n">
         <v>182</v>
       </c>
+      <c r="K50" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L50" s="14" t="n">
+        <v>182</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -18455,6 +20909,12 @@
       <c r="J51" s="14" t="n">
         <v>4122</v>
       </c>
+      <c r="K51" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L51" s="14" t="n">
+        <v>182</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -18497,6 +20957,12 @@
       <c r="J52" s="14" t="n">
         <v>296</v>
       </c>
+      <c r="K52" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L52" s="14" t="n">
+        <v>296</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -18539,6 +21005,12 @@
       <c r="J53" s="14" t="n">
         <v>339</v>
       </c>
+      <c r="K53" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L53" s="14" t="n">
+        <v>339</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -18581,6 +21053,12 @@
       <c r="J54" s="14" t="n">
         <v>4122</v>
       </c>
+      <c r="K54" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L54" s="14" t="n">
+        <v>4122</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -18623,6 +21101,12 @@
       <c r="J55" s="14" t="n">
         <v>56</v>
       </c>
+      <c r="K55" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L55" s="14" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -18665,6 +21149,12 @@
       <c r="J56" s="14" t="n">
         <v>493</v>
       </c>
+      <c r="K56" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L56" s="14" t="n">
+        <v>493</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -18707,6 +21197,12 @@
       <c r="J57" s="14" t="n">
         <v>7853</v>
       </c>
+      <c r="K57" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L57" s="14" t="n">
+        <v>7852</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -18749,6 +21245,12 @@
       <c r="J58" s="14" t="n">
         <v>4018</v>
       </c>
+      <c r="K58" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L58" s="14" t="n">
+        <v>4019</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -18791,6 +21293,12 @@
       <c r="J59" s="14" t="n">
         <v>2916</v>
       </c>
+      <c r="K59" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v>2920</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -18833,6 +21341,12 @@
       <c r="J60" s="14" t="n">
         <v>2252</v>
       </c>
+      <c r="K60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L60" s="14" t="n">
+        <v>2252</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -18875,6 +21389,12 @@
       <c r="J61" s="14" t="n">
         <v>7843</v>
       </c>
+      <c r="K61" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L61" s="14" t="n">
+        <v>7856</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -18917,6 +21437,12 @@
       <c r="J62" s="14" t="n">
         <v>3617</v>
       </c>
+      <c r="K62" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L62" s="14" t="n">
+        <v>3618</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -18959,6 +21485,12 @@
       <c r="J63" s="14" t="n">
         <v>4769</v>
       </c>
+      <c r="K63" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L63" s="14" t="n">
+        <v>4769</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -19001,6 +21533,12 @@
       <c r="J64" s="14" t="n">
         <v>2626</v>
       </c>
+      <c r="K64" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L64" s="14" t="n">
+        <v>2626</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -19043,6 +21581,12 @@
       <c r="J65" s="14" t="n">
         <v>2903</v>
       </c>
+      <c r="K65" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L65" s="14" t="n">
+        <v>2903</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -19085,6 +21629,12 @@
       <c r="J66" s="14" t="n">
         <v>6445</v>
       </c>
+      <c r="K66" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L66" s="14" t="n">
+        <v>6446</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -19127,6 +21677,12 @@
       <c r="J67" s="14" t="n">
         <v>781</v>
       </c>
+      <c r="K67" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L67" s="14" t="n">
+        <v>781</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -19169,6 +21725,12 @@
       <c r="J68" s="14" t="n">
         <v>19113</v>
       </c>
+      <c r="K68" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L68" s="14" t="n">
+        <v>19116</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -19211,6 +21773,12 @@
       <c r="J69" s="14" t="n">
         <v>2919</v>
       </c>
+      <c r="K69" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L69" s="14" t="n">
+        <v>2922</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -19253,6 +21821,12 @@
       <c r="J70" s="14" t="n">
         <v>2629</v>
       </c>
+      <c r="K70" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L70" s="14" t="n">
+        <v>2630</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
@@ -19295,6 +21869,12 @@
       <c r="J71" s="14" t="n">
         <v>1193</v>
       </c>
+      <c r="K71" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L71" s="14" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -19337,6 +21917,12 @@
       <c r="J72" s="14" t="n">
         <v>4165</v>
       </c>
+      <c r="K72" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L72" s="14" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -19379,6 +21965,12 @@
       <c r="J73" s="14" t="n">
         <v>3866</v>
       </c>
+      <c r="K73" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L73" s="14" t="n">
+        <v>3870</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -19421,6 +22013,12 @@
       <c r="J74" s="14" t="n">
         <v>756</v>
       </c>
+      <c r="K74" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L74" s="14" t="n">
+        <v>756</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -19463,6 +22061,12 @@
       <c r="J75" s="14" t="n">
         <v>4660</v>
       </c>
+      <c r="K75" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L75" s="14" t="n">
+        <v>4661</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -19505,6 +22109,12 @@
       <c r="J76" s="14" t="n">
         <v>5290</v>
       </c>
+      <c r="K76" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L76" s="14" t="n">
+        <v>5291</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -19547,6 +22157,12 @@
       <c r="J77" s="14" t="n">
         <v>159</v>
       </c>
+      <c r="K77" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L77" s="14" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -19589,6 +22205,12 @@
       <c r="J78" s="14" t="n">
         <v>1132</v>
       </c>
+      <c r="K78" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L78" s="14" t="n">
+        <v>1132</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -19631,6 +22253,12 @@
       <c r="J79" s="14" t="n">
         <v>634</v>
       </c>
+      <c r="K79" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L79" s="14" t="n">
+        <v>634</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -19673,6 +22301,12 @@
       <c r="J80" s="14" t="n">
         <v>1187</v>
       </c>
+      <c r="K80" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L80" s="14" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -19715,6 +22349,12 @@
       <c r="J81" s="14" t="n">
         <v>1566</v>
       </c>
+      <c r="K81" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L81" s="14" t="n">
+        <v>1566</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -19757,6 +22397,12 @@
       <c r="J82" s="14" t="n">
         <v>11751</v>
       </c>
+      <c r="K82" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L82" s="14" t="n">
+        <v>11754</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -19799,6 +22445,12 @@
       <c r="J83" s="14" t="n">
         <v>15</v>
       </c>
+      <c r="K83" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L83" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
@@ -19841,6 +22493,12 @@
       <c r="J84" s="14" t="n">
         <v>5937</v>
       </c>
+      <c r="K84" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L84" s="14" t="n">
+        <v>5940</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -19883,6 +22541,12 @@
       <c r="J85" s="14" t="n">
         <v>3269</v>
       </c>
+      <c r="K85" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L85" s="14" t="n">
+        <v>3271</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -19925,6 +22589,12 @@
       <c r="J86" s="14" t="n">
         <v>10433</v>
       </c>
+      <c r="K86" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L86" s="14" t="n">
+        <v>10433</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
@@ -19967,6 +22637,12 @@
       <c r="J87" s="14" t="n">
         <v>4152</v>
       </c>
+      <c r="K87" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L87" s="14" t="n">
+        <v>4152</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
@@ -20009,6 +22685,12 @@
       <c r="J88" s="14" t="n">
         <v>2998</v>
       </c>
+      <c r="K88" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L88" s="14" t="n">
+        <v>2998</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
@@ -20051,6 +22733,12 @@
       <c r="J89" s="14" t="n">
         <v>1295</v>
       </c>
+      <c r="K89" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L89" s="14" t="n">
+        <v>1295</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -20093,6 +22781,12 @@
       <c r="J90" s="14" t="n">
         <v>2238</v>
       </c>
+      <c r="K90" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L90" s="14" t="n">
+        <v>2241</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
@@ -20135,6 +22829,12 @@
       <c r="J91" s="14" t="n">
         <v>7972</v>
       </c>
+      <c r="K91" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L91" s="14" t="n">
+        <v>7973</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
@@ -20177,6 +22877,12 @@
       <c r="J92" s="14" t="n">
         <v>783</v>
       </c>
+      <c r="K92" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L92" s="14" t="n">
+        <v>783</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
@@ -20219,6 +22925,12 @@
       <c r="J93" s="14" t="n">
         <v>790</v>
       </c>
+      <c r="K93" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L93" s="14" t="n">
+        <v>791</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
@@ -20261,6 +22973,12 @@
       <c r="J94" s="14" t="n">
         <v>2596</v>
       </c>
+      <c r="K94" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L94" s="14" t="n">
+        <v>2597</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
@@ -20303,6 +23021,12 @@
       <c r="J95" s="14" t="n">
         <v>1680</v>
       </c>
+      <c r="K95" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L95" s="14" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
@@ -20345,6 +23069,12 @@
       <c r="J96" s="14" t="n">
         <v>6440</v>
       </c>
+      <c r="K96" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L96" s="14" t="n">
+        <v>6440</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
@@ -20387,6 +23117,12 @@
       <c r="J97" s="14" t="n">
         <v>2315</v>
       </c>
+      <c r="K97" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L97" s="14" t="n">
+        <v>2315</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -20429,6 +23165,12 @@
       <c r="J98" s="14" t="n">
         <v>1937</v>
       </c>
+      <c r="K98" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L98" s="14" t="n">
+        <v>1937</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
@@ -20471,6 +23213,12 @@
       <c r="J99" s="14" t="n">
         <v>5585</v>
       </c>
+      <c r="K99" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L99" s="14" t="n">
+        <v>5587</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -20513,6 +23261,12 @@
       <c r="J100" s="14" t="n">
         <v>17800</v>
       </c>
+      <c r="K100" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L100" s="14" t="n">
+        <v>17808</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -20555,6 +23309,12 @@
       <c r="J101" s="14" t="n">
         <v>6184</v>
       </c>
+      <c r="K101" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L101" s="14" t="n">
+        <v>6187</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -20597,6 +23357,12 @@
       <c r="J102" s="14" t="n">
         <v>5283</v>
       </c>
+      <c r="K102" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L102" s="14" t="n">
+        <v>5284</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
@@ -20639,6 +23405,12 @@
       <c r="J103" s="14" t="n">
         <v>1177</v>
       </c>
+      <c r="K103" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L103" s="14" t="n">
+        <v>1177</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -20681,6 +23453,12 @@
       <c r="J104" s="14" t="n">
         <v>4077</v>
       </c>
+      <c r="K104" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L104" s="14" t="n">
+        <v>4077</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
@@ -20723,6 +23501,12 @@
       <c r="J105" s="14" t="n">
         <v>1177</v>
       </c>
+      <c r="K105" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L105" s="14" t="n">
+        <v>1177</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
@@ -20765,6 +23549,12 @@
       <c r="J106" s="14" t="n">
         <v>10980</v>
       </c>
+      <c r="K106" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L106" s="14" t="n">
+        <v>10982</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -20807,6 +23597,12 @@
       <c r="J107" s="14" t="n">
         <v>3159</v>
       </c>
+      <c r="K107" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L107" s="14" t="n">
+        <v>3158</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -20849,6 +23645,12 @@
       <c r="J108" s="14" t="n">
         <v>3062</v>
       </c>
+      <c r="K108" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L108" s="14" t="n">
+        <v>3066</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
@@ -20891,6 +23693,12 @@
       <c r="J109" s="14" t="n">
         <v>2637</v>
       </c>
+      <c r="K109" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L109" s="14" t="n">
+        <v>2643</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
@@ -20933,6 +23741,12 @@
       <c r="J110" s="14" t="n">
         <v>1886</v>
       </c>
+      <c r="K110" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L110" s="14" t="n">
+        <v>1886</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
@@ -20975,6 +23789,12 @@
       <c r="J111" s="14" t="n">
         <v>1196</v>
       </c>
+      <c r="K111" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L111" s="14" t="n">
+        <v>1196</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -21017,6 +23837,12 @@
       <c r="J112" s="14" t="n">
         <v>2460</v>
       </c>
+      <c r="K112" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L112" s="14" t="n">
+        <v>2462</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
@@ -21057,6 +23883,12 @@
         <v>4.6</v>
       </c>
       <c r="J113" s="14" t="n">
+        <v>2658</v>
+      </c>
+      <c r="K113" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L113" s="14" t="n">
         <v>2658</v>
       </c>
     </row>
@@ -21071,7 +23903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -21100,6 +23932,12 @@
       <c r="J1" s="11" t="n">
         <v>46305</v>
       </c>
+      <c r="K1" s="11" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L1" s="11" t="n">
+        <v>46306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -21148,6 +23986,16 @@
         </is>
       </c>
       <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -21194,6 +24042,12 @@
       <c r="J3" s="14" t="n">
         <v>14381</v>
       </c>
+      <c r="K3" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>14386</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -21236,6 +24090,12 @@
       <c r="J4" s="14" t="n">
         <v>1204</v>
       </c>
+      <c r="K4" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L4" s="14" t="n">
+        <v>1205</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -21278,6 +24138,12 @@
       <c r="J5" s="14" t="n">
         <v>15</v>
       </c>
+      <c r="K5" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -21320,6 +24186,12 @@
       <c r="J6" s="14" t="n">
         <v>63</v>
       </c>
+      <c r="K6" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L6" s="14" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -21362,6 +24234,12 @@
       <c r="J7" s="14" t="n">
         <v>4839</v>
       </c>
+      <c r="K7" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>4840</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -21404,6 +24282,12 @@
       <c r="J8" s="14" t="n">
         <v>2069</v>
       </c>
+      <c r="K8" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L8" s="14" t="n">
+        <v>2069</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -21446,6 +24330,12 @@
       <c r="J9" s="14" t="n">
         <v>5783</v>
       </c>
+      <c r="K9" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>5786</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -21488,6 +24378,12 @@
       <c r="J10" s="14" t="n">
         <v>6560</v>
       </c>
+      <c r="K10" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L10" s="14" t="n">
+        <v>6562</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -21530,6 +24426,12 @@
       <c r="J11" s="14" t="n">
         <v>10578</v>
       </c>
+      <c r="K11" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>10581</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -21572,6 +24474,12 @@
       <c r="J12" s="14" t="n">
         <v>12239</v>
       </c>
+      <c r="K12" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>12241</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -21614,6 +24522,12 @@
       <c r="J13" s="14" t="n">
         <v>10708</v>
       </c>
+      <c r="K13" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>10710</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -21656,6 +24570,12 @@
       <c r="J14" s="14" t="n">
         <v>6813</v>
       </c>
+      <c r="K14" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>6816</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -21698,6 +24618,12 @@
       <c r="J15" s="14" t="n">
         <v>3606</v>
       </c>
+      <c r="K15" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>3607</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -21740,6 +24666,12 @@
       <c r="J16" s="14" t="n">
         <v>4504</v>
       </c>
+      <c r="K16" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>4505</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -21782,6 +24714,12 @@
       <c r="J17" s="14" t="n">
         <v>878</v>
       </c>
+      <c r="K17" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>878</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -21824,6 +24762,12 @@
       <c r="J18" s="14" t="n">
         <v>19724</v>
       </c>
+      <c r="K18" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>19724</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -21866,6 +24810,12 @@
       <c r="J19" s="14" t="n">
         <v>2022</v>
       </c>
+      <c r="K19" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>2022</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -21908,6 +24858,12 @@
       <c r="J20" s="14" t="n">
         <v>2049</v>
       </c>
+      <c r="K20" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>2047</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -21950,6 +24906,12 @@
       <c r="J21" s="14" t="n">
         <v>8787</v>
       </c>
+      <c r="K21" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>8786</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -21992,6 +24954,12 @@
       <c r="J22" s="14" t="n">
         <v>1120</v>
       </c>
+      <c r="K22" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>1120</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -22034,6 +25002,12 @@
       <c r="J23" s="14" t="n">
         <v>676</v>
       </c>
+      <c r="K23" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>676</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -22075,6 +25049,12 @@
       </c>
       <c r="J24" s="14" t="n">
         <v>1824</v>
+      </c>
+      <c r="K24" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>1825</v>
       </c>
     </row>
   </sheetData>
@@ -22088,7 +25068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -22117,6 +25097,12 @@
       <c r="J1" s="11" t="n">
         <v>46305</v>
       </c>
+      <c r="K1" s="11" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L1" s="11" t="n">
+        <v>46306</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -22165,6 +25151,16 @@
         </is>
       </c>
       <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="L2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -22211,6 +25207,12 @@
       <c r="J3" s="14" t="n">
         <v>1595</v>
       </c>
+      <c r="K3" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -22253,6 +25255,12 @@
       <c r="J4" s="14" t="n">
         <v>1041</v>
       </c>
+      <c r="K4" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L4" s="14" t="n">
+        <v>1042</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -22295,6 +25303,12 @@
       <c r="J5" s="14" t="n">
         <v>1981</v>
       </c>
+      <c r="K5" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>1982</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -22337,6 +25351,12 @@
       <c r="J6" s="14" t="n">
         <v>1187</v>
       </c>
+      <c r="K6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="14" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -22379,6 +25399,12 @@
       <c r="J7" s="14" t="n">
         <v>1413</v>
       </c>
+      <c r="K7" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>1414</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -22421,6 +25447,12 @@
       <c r="J8" s="14" t="n">
         <v>24</v>
       </c>
+      <c r="K8" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L8" s="14" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -22463,6 +25495,12 @@
       <c r="J9" s="14" t="n">
         <v>1133</v>
       </c>
+      <c r="K9" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>1134</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -22505,6 +25543,12 @@
       <c r="J10" s="14" t="n">
         <v>722</v>
       </c>
+      <c r="K10" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L10" s="14" t="n">
+        <v>722</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -22547,6 +25591,12 @@
       <c r="J11" s="14" t="n">
         <v>25</v>
       </c>
+      <c r="K11" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -22589,6 +25639,12 @@
       <c r="J12" s="14" t="n">
         <v>23</v>
       </c>
+      <c r="K12" s="14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -22631,6 +25687,12 @@
       <c r="J13" s="14" t="n">
         <v>93</v>
       </c>
+      <c r="K13" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -22673,6 +25735,12 @@
       <c r="J14" s="14" t="n">
         <v>73</v>
       </c>
+      <c r="K14" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -22715,6 +25783,12 @@
       <c r="J15" s="14" t="n">
         <v>562</v>
       </c>
+      <c r="K15" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>562</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -22757,6 +25831,12 @@
       <c r="J16" s="14" t="n">
         <v>14</v>
       </c>
+      <c r="K16" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -22799,6 +25879,12 @@
       <c r="J17" s="14" t="n">
         <v>5855</v>
       </c>
+      <c r="K17" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L17" s="14" t="n">
+        <v>5862</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -22841,6 +25927,12 @@
       <c r="J18" s="14" t="n">
         <v>1145</v>
       </c>
+      <c r="K18" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>1148</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -22883,6 +25975,12 @@
       <c r="J19" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="K19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -22925,6 +26023,12 @@
       <c r="J20" s="14" t="n">
         <v>2473</v>
       </c>
+      <c r="K20" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>2473</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -22967,6 +26071,12 @@
       <c r="J21" s="14" t="n">
         <v>341</v>
       </c>
+      <c r="K21" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>341</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -23009,6 +26119,12 @@
       <c r="J22" s="14" t="n">
         <v>4358</v>
       </c>
+      <c r="K22" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>4358</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -23051,6 +26167,12 @@
       <c r="J23" s="14" t="n">
         <v>11258</v>
       </c>
+      <c r="K23" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>11258</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -23093,6 +26215,12 @@
       <c r="J24" s="14" t="n">
         <v>13841</v>
       </c>
+      <c r="K24" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>13843</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -23135,6 +26263,12 @@
       <c r="J25" s="14" t="n">
         <v>5033</v>
       </c>
+      <c r="K25" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>5037</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -23177,6 +26311,12 @@
       <c r="J26" s="14" t="n">
         <v>8086</v>
       </c>
+      <c r="K26" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L26" s="14" t="n">
+        <v>8086</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -23219,6 +26359,12 @@
       <c r="J27" s="14" t="n">
         <v>7826</v>
       </c>
+      <c r="K27" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L27" s="14" t="n">
+        <v>7833</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -23261,6 +26407,12 @@
       <c r="J28" s="14" t="n">
         <v>6654</v>
       </c>
+      <c r="K28" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L28" s="14" t="n">
+        <v>6655</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -23303,6 +26455,12 @@
       <c r="J29" s="14" t="n">
         <v>1155</v>
       </c>
+      <c r="K29" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L29" s="14" t="n">
+        <v>1157</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -23345,6 +26503,12 @@
       <c r="J30" s="14" t="n">
         <v>4943</v>
       </c>
+      <c r="K30" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L30" s="14" t="n">
+        <v>4947</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -23387,6 +26551,12 @@
       <c r="J31" s="14" t="n">
         <v>8076</v>
       </c>
+      <c r="K31" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L31" s="14" t="n">
+        <v>8085</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -23429,6 +26599,12 @@
       <c r="J32" s="14" t="n">
         <v>8463</v>
       </c>
+      <c r="K32" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L32" s="14" t="n">
+        <v>8471</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -23471,6 +26647,12 @@
       <c r="J33" s="14" t="n">
         <v>4182</v>
       </c>
+      <c r="K33" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L33" s="14" t="n">
+        <v>4182</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -23513,6 +26695,12 @@
       <c r="J34" s="14" t="n">
         <v>22</v>
       </c>
+      <c r="K34" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L34" s="14" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -23555,6 +26743,12 @@
       <c r="J35" s="14" t="n">
         <v>4431</v>
       </c>
+      <c r="K35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L35" s="14" t="n">
+        <v>4432</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -23597,6 +26791,12 @@
       <c r="J36" s="14" t="n">
         <v>5550</v>
       </c>
+      <c r="K36" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L36" s="14" t="n">
+        <v>5550</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -23639,6 +26839,12 @@
       <c r="J37" s="14" t="n">
         <v>4188</v>
       </c>
+      <c r="K37" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L37" s="14" t="n">
+        <v>4188</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -23681,6 +26887,12 @@
       <c r="J38" s="14" t="n">
         <v>2512</v>
       </c>
+      <c r="K38" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L38" s="14" t="n">
+        <v>2512</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -23723,6 +26935,12 @@
       <c r="J39" s="14" t="n">
         <v>6423</v>
       </c>
+      <c r="K39" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L39" s="14" t="n">
+        <v>6423</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -23765,6 +26983,12 @@
       <c r="J40" s="14" t="n">
         <v>2547</v>
       </c>
+      <c r="K40" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L40" s="14" t="n">
+        <v>2547</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -23807,6 +27031,12 @@
       <c r="J41" s="14" t="n">
         <v>1080</v>
       </c>
+      <c r="K41" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L41" s="14" t="n">
+        <v>1089</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -23849,6 +27079,12 @@
       <c r="J42" s="14" t="n">
         <v>808</v>
       </c>
+      <c r="K42" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L42" s="14" t="n">
+        <v>812</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -23891,6 +27127,12 @@
       <c r="J43" s="14" t="n">
         <v>555</v>
       </c>
+      <c r="K43" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L43" s="14" t="n">
+        <v>555</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -23933,6 +27175,12 @@
       <c r="J44" s="14" t="n">
         <v>19</v>
       </c>
+      <c r="K44" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L44" s="14" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -23975,6 +27223,12 @@
       <c r="J45" s="14" t="n">
         <v>5069</v>
       </c>
+      <c r="K45" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L45" s="14" t="n">
+        <v>5074</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -24017,6 +27271,12 @@
       <c r="J46" s="14" t="n">
         <v>649</v>
       </c>
+      <c r="K46" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L46" s="14" t="n">
+        <v>649</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -24059,6 +27319,12 @@
       <c r="J47" s="14" t="n">
         <v>2575</v>
       </c>
+      <c r="K47" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L47" s="14" t="n">
+        <v>2575</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -24101,6 +27367,12 @@
       <c r="J48" s="14" t="n">
         <v>81</v>
       </c>
+      <c r="K48" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L48" s="14" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -24143,6 +27415,12 @@
       <c r="J49" s="14" t="n">
         <v>4632</v>
       </c>
+      <c r="K49" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L49" s="14" t="n">
+        <v>4633</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -24185,6 +27463,12 @@
       <c r="J50" s="14" t="n">
         <v>3302</v>
       </c>
+      <c r="K50" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L50" s="14" t="n">
+        <v>3304</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -24227,6 +27511,12 @@
       <c r="J51" s="14" t="n">
         <v>783</v>
       </c>
+      <c r="K51" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L51" s="14" t="n">
+        <v>783</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -24269,6 +27559,12 @@
       <c r="J52" s="14" t="n">
         <v>1497</v>
       </c>
+      <c r="K52" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L52" s="14" t="n">
+        <v>1498</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -24311,6 +27607,12 @@
       <c r="J53" s="14" t="n">
         <v>91</v>
       </c>
+      <c r="K53" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L53" s="14" t="n">
+        <v>91</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -24353,6 +27655,12 @@
       <c r="J54" s="14" t="n">
         <v>2811</v>
       </c>
+      <c r="K54" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L54" s="14" t="n">
+        <v>2811</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -24395,6 +27703,12 @@
       <c r="J55" s="14" t="n">
         <v>709</v>
       </c>
+      <c r="K55" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L55" s="14" t="n">
+        <v>709</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -24437,6 +27751,12 @@
       <c r="J56" s="14" t="n">
         <v>288</v>
       </c>
+      <c r="K56" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L56" s="14" t="n">
+        <v>288</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -24479,6 +27799,12 @@
       <c r="J57" s="14" t="n">
         <v>4518</v>
       </c>
+      <c r="K57" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L57" s="14" t="n">
+        <v>4520</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -24521,6 +27847,12 @@
       <c r="J58" s="14" t="n">
         <v>456</v>
       </c>
+      <c r="K58" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L58" s="14" t="n">
+        <v>456</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -24563,6 +27895,12 @@
       <c r="J59" s="14" t="n">
         <v>3011</v>
       </c>
+      <c r="K59" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v>3011</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -24605,6 +27943,12 @@
       <c r="J60" s="14" t="n">
         <v>969</v>
       </c>
+      <c r="K60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L60" s="14" t="n">
+        <v>969</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -24646,6 +27990,12 @@
       </c>
       <c r="J61" s="14" t="n">
         <v>1076</v>
+      </c>
+      <c r="K61" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L61" s="14" t="n">
+        <v>1079</v>
       </c>
     </row>
   </sheetData>

--- a/Outlet name and Link.xlsx
+++ b/Outlet name and Link.xlsx
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -595,6 +595,12 @@
       <c r="L1" s="11" t="n">
         <v>46306</v>
       </c>
+      <c r="M1" s="11" t="n">
+        <v>46308</v>
+      </c>
+      <c r="N1" s="11" t="n">
+        <v>46308</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -653,6 +659,16 @@
         </is>
       </c>
       <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -705,6 +721,12 @@
       <c r="L3" s="14" t="n">
         <v>4875</v>
       </c>
+      <c r="M3" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>4884</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -753,6 +775,12 @@
       <c r="L4" s="14" t="n">
         <v>15767</v>
       </c>
+      <c r="M4" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N4" s="14" t="n">
+        <v>15774</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -801,6 +829,12 @@
       <c r="L5" s="14" t="n">
         <v>5560</v>
       </c>
+      <c r="M5" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>5569</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -849,6 +883,12 @@
       <c r="L6" s="14" t="n">
         <v>6563</v>
       </c>
+      <c r="M6" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>6578</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -897,6 +937,12 @@
       <c r="L7" s="14" t="n">
         <v>2428</v>
       </c>
+      <c r="M7" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>2433</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -945,6 +991,12 @@
       <c r="L8" s="14" t="n">
         <v>7177</v>
       </c>
+      <c r="M8" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N8" s="14" t="n">
+        <v>7175</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -993,6 +1045,12 @@
       <c r="L9" s="14" t="n">
         <v>3657</v>
       </c>
+      <c r="M9" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N9" s="14" t="n">
+        <v>3658</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1041,6 +1099,12 @@
       <c r="L10" s="14" t="n">
         <v>2794</v>
       </c>
+      <c r="M10" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N10" s="14" t="n">
+        <v>2796</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1089,6 +1153,12 @@
       <c r="L11" s="14" t="n">
         <v>1122</v>
       </c>
+      <c r="M11" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N11" s="14" t="n">
+        <v>1124</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1137,6 +1207,12 @@
       <c r="L12" s="14" t="n">
         <v>1110</v>
       </c>
+      <c r="M12" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N12" s="14" t="n">
+        <v>1110</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -1185,6 +1261,12 @@
       <c r="L13" s="14" t="n">
         <v>2278</v>
       </c>
+      <c r="M13" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N13" s="14" t="n">
+        <v>2271</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -1233,6 +1315,12 @@
       <c r="L14" s="14" t="n">
         <v>2391</v>
       </c>
+      <c r="M14" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N14" s="14" t="n">
+        <v>2389</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1281,6 +1369,12 @@
       <c r="L15" s="14" t="n">
         <v>2613</v>
       </c>
+      <c r="M15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N15" s="14" t="n">
+        <v>2618</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1329,6 +1423,12 @@
       <c r="L16" s="14" t="n">
         <v>895</v>
       </c>
+      <c r="M16" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N16" s="14" t="n">
+        <v>896</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -1377,6 +1477,12 @@
       <c r="L17" s="14" t="n">
         <v>1337</v>
       </c>
+      <c r="M17" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N17" s="14" t="n">
+        <v>1339</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -1425,6 +1531,12 @@
       <c r="L18" s="14" t="n">
         <v>470</v>
       </c>
+      <c r="M18" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N18" s="14" t="n">
+        <v>477</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -1473,6 +1585,12 @@
       <c r="L19" s="14" t="n">
         <v>920</v>
       </c>
+      <c r="M19" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N19" s="14" t="n">
+        <v>922</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -1521,6 +1639,12 @@
       <c r="L20" s="14" t="n">
         <v>1097</v>
       </c>
+      <c r="M20" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N20" s="14" t="n">
+        <v>1098</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -1569,6 +1693,12 @@
       <c r="L21" s="14" t="n">
         <v>790</v>
       </c>
+      <c r="M21" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>793</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -1617,6 +1747,12 @@
       <c r="L22" s="14" t="n">
         <v>667</v>
       </c>
+      <c r="M22" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>669</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -1665,6 +1801,12 @@
       <c r="L23" s="14" t="n">
         <v>702</v>
       </c>
+      <c r="M23" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N23" s="14" t="n">
+        <v>708</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -1713,6 +1855,12 @@
       <c r="L24" s="14" t="n">
         <v>1424</v>
       </c>
+      <c r="M24" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N24" s="14" t="n">
+        <v>1424</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -1761,6 +1909,12 @@
       <c r="L25" s="14" t="n">
         <v>720</v>
       </c>
+      <c r="M25" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N25" s="14" t="n">
+        <v>727</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1804,6 +1958,12 @@
       </c>
       <c r="L26" s="14" t="n">
         <v>384</v>
+      </c>
+      <c r="M26" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N26" s="14" t="n">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1853,6 +2013,12 @@
       <c r="M1" s="11" t="n">
         <v>46306</v>
       </c>
+      <c r="N1" s="11" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O1" s="11" t="n">
+        <v>46308</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -1916,6 +2082,16 @@
         </is>
       </c>
       <c r="M2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="N2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="O2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -1973,6 +2149,12 @@
       <c r="M3" s="14" t="n">
         <v>702</v>
       </c>
+      <c r="N3" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O3" s="14" t="n">
+        <v>708</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -2026,6 +2208,12 @@
       <c r="M4" s="14" t="n">
         <v>81</v>
       </c>
+      <c r="N4" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O4" s="14" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -2079,6 +2267,12 @@
       <c r="M5" s="14" t="n">
         <v>790</v>
       </c>
+      <c r="N5" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O5" s="14" t="n">
+        <v>793</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2132,6 +2326,12 @@
       <c r="M6" s="14" t="n">
         <v>790</v>
       </c>
+      <c r="N6" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O6" s="14" t="n">
+        <v>793</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -2185,6 +2385,12 @@
       <c r="M7" s="14" t="n">
         <v>667</v>
       </c>
+      <c r="N7" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O7" s="14" t="n">
+        <v>669</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -2238,6 +2444,12 @@
       <c r="M8" s="14" t="n">
         <v>895</v>
       </c>
+      <c r="N8" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O8" s="14" t="n">
+        <v>896</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -2291,6 +2503,12 @@
       <c r="M9" s="14" t="n">
         <v>3271</v>
       </c>
+      <c r="N9" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O9" s="14" t="n">
+        <v>3273</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -2344,6 +2562,12 @@
       <c r="M10" s="14" t="n">
         <v>3271</v>
       </c>
+      <c r="N10" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O10" s="14" t="n">
+        <v>3273</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -2397,6 +2621,12 @@
       <c r="M11" s="14" t="n">
         <v>1424</v>
       </c>
+      <c r="N11" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O11" s="14" t="n">
+        <v>1424</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -2450,6 +2680,12 @@
       <c r="M12" s="14" t="n">
         <v>1193</v>
       </c>
+      <c r="N12" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O12" s="14" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -2503,6 +2739,12 @@
       <c r="M13" s="14" t="n">
         <v>756</v>
       </c>
+      <c r="N13" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O13" s="14" t="n">
+        <v>756</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -2556,6 +2798,12 @@
       <c r="M14" s="14" t="n">
         <v>6816</v>
       </c>
+      <c r="N14" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O14" s="14" t="n">
+        <v>6818</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -2609,6 +2857,12 @@
       <c r="M15" s="14" t="n">
         <v>7177</v>
       </c>
+      <c r="N15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O15" s="14" t="n">
+        <v>7175</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -2662,6 +2916,12 @@
       <c r="M16" s="14" t="n">
         <v>2630</v>
       </c>
+      <c r="N16" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O16" s="14" t="n">
+        <v>2630</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -2715,6 +2975,12 @@
       <c r="M17" s="14" t="n">
         <v>1825</v>
       </c>
+      <c r="N17" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" s="14" t="n">
+        <v>1825</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -2768,6 +3034,12 @@
       <c r="M18" s="14" t="n">
         <v>4505</v>
       </c>
+      <c r="N18" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O18" s="14" t="n">
+        <v>4505</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -2821,6 +3093,12 @@
       <c r="M19" s="14" t="n">
         <v>6563</v>
       </c>
+      <c r="N19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O19" s="14" t="n">
+        <v>6578</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -2874,6 +3152,12 @@
       <c r="M20" s="14" t="n">
         <v>2794</v>
       </c>
+      <c r="N20" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O20" s="14" t="n">
+        <v>2796</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -2927,6 +3211,12 @@
       <c r="M21" s="14" t="n">
         <v>15767</v>
       </c>
+      <c r="N21" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O21" s="14" t="n">
+        <v>15774</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2980,6 +3270,12 @@
       <c r="M22" s="14" t="n">
         <v>15767</v>
       </c>
+      <c r="N22" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O22" s="14" t="n">
+        <v>15774</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -3033,6 +3329,12 @@
       <c r="M23" s="14" t="n">
         <v>10581</v>
       </c>
+      <c r="N23" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O23" s="14" t="n">
+        <v>10580</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -3086,6 +3388,12 @@
       <c r="M24" s="14" t="n">
         <v>12241</v>
       </c>
+      <c r="N24" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O24" s="14" t="n">
+        <v>12241</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -3139,6 +3447,12 @@
       <c r="M25" s="14" t="n">
         <v>2019</v>
       </c>
+      <c r="N25" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O25" s="14" t="n">
+        <v>2026</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -3192,6 +3506,12 @@
       <c r="M26" s="14" t="n">
         <v>853</v>
       </c>
+      <c r="N26" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O26" s="14" t="n">
+        <v>853</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -3245,6 +3565,12 @@
       <c r="M27" s="14" t="n">
         <v>3657</v>
       </c>
+      <c r="N27" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O27" s="14" t="n">
+        <v>3658</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -3298,6 +3624,12 @@
       <c r="M28" s="14" t="n">
         <v>3607</v>
       </c>
+      <c r="N28" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O28" s="14" t="n">
+        <v>3608</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -3351,6 +3683,12 @@
       <c r="M29" s="14" t="n">
         <v>4875</v>
       </c>
+      <c r="N29" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O29" s="14" t="n">
+        <v>4884</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -3404,6 +3742,12 @@
       <c r="M30" s="14" t="n">
         <v>1172</v>
       </c>
+      <c r="N30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O30" s="14" t="n">
+        <v>1173</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -3457,6 +3801,12 @@
       <c r="M31" s="14" t="n">
         <v>2278</v>
       </c>
+      <c r="N31" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O31" s="14" t="n">
+        <v>2271</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -3510,6 +3860,12 @@
       <c r="M32" s="14" t="n">
         <v>1044</v>
       </c>
+      <c r="N32" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O32" s="14" t="n">
+        <v>1044</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -3563,6 +3919,12 @@
       <c r="M33" s="14" t="n">
         <v>5560</v>
       </c>
+      <c r="N33" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O33" s="14" t="n">
+        <v>5569</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -3616,6 +3978,12 @@
       <c r="M34" s="14" t="n">
         <v>1132</v>
       </c>
+      <c r="N34" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O34" s="14" t="n">
+        <v>1132</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -3669,6 +4037,12 @@
       <c r="M35" s="14" t="n">
         <v>4840</v>
       </c>
+      <c r="N35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O35" s="14" t="n">
+        <v>4839</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -3722,6 +4096,12 @@
       <c r="M36" s="14" t="n">
         <v>1110</v>
       </c>
+      <c r="N36" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O36" s="14" t="n">
+        <v>1110</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -3775,6 +4155,12 @@
       <c r="M37" s="14" t="n">
         <v>2428</v>
       </c>
+      <c r="N37" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O37" s="14" t="n">
+        <v>2433</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -3828,6 +4214,12 @@
       <c r="M38" s="14" t="n">
         <v>2428</v>
       </c>
+      <c r="N38" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O38" s="14" t="n">
+        <v>2433</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -3881,6 +4273,12 @@
       <c r="M39" s="14" t="n">
         <v>2613</v>
       </c>
+      <c r="N39" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O39" s="14" t="n">
+        <v>2618</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -3934,6 +4332,12 @@
       <c r="M40" s="14" t="n">
         <v>470</v>
       </c>
+      <c r="N40" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O40" s="14" t="n">
+        <v>477</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -3987,6 +4391,12 @@
       <c r="M41" s="14" t="n">
         <v>1122</v>
       </c>
+      <c r="N41" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O41" s="14" t="n">
+        <v>1124</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -4040,6 +4450,12 @@
       <c r="M42" s="14" t="n">
         <v>11754</v>
       </c>
+      <c r="N42" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O42" s="14" t="n">
+        <v>11761</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -4093,6 +4509,12 @@
       <c r="M43" s="14" t="n">
         <v>1097</v>
       </c>
+      <c r="N43" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O43" s="14" t="n">
+        <v>1098</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -4146,6 +4568,12 @@
       <c r="M44" s="14" t="n">
         <v>1337</v>
       </c>
+      <c r="N44" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O44" s="14" t="n">
+        <v>1339</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -4199,6 +4627,12 @@
       <c r="M45" s="14" t="n">
         <v>192</v>
       </c>
+      <c r="N45" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O45" s="14" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -4252,6 +4686,12 @@
       <c r="M46" s="14" t="n">
         <v>2019</v>
       </c>
+      <c r="N46" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O46" s="14" t="n">
+        <v>2026</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -4305,6 +4745,12 @@
       <c r="M47" s="14" t="n">
         <v>2391</v>
       </c>
+      <c r="N47" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O47" s="14" t="n">
+        <v>2389</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -4358,6 +4804,12 @@
       <c r="M48" s="14" t="n">
         <v>920</v>
       </c>
+      <c r="N48" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O48" s="14" t="n">
+        <v>922</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -4411,6 +4863,12 @@
       <c r="M49" s="14" t="n">
         <v>1776</v>
       </c>
+      <c r="N49" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O49" s="14" t="n">
+        <v>1776</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -4464,6 +4922,12 @@
       <c r="M50" s="14" t="n">
         <v>2630</v>
       </c>
+      <c r="N50" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O50" s="14" t="n">
+        <v>2630</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -4517,6 +4981,12 @@
       <c r="M51" s="14" t="n">
         <v>5940</v>
       </c>
+      <c r="N51" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O51" s="14" t="n">
+        <v>5941</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -4570,6 +5040,12 @@
       <c r="M52" s="14" t="n">
         <v>1566</v>
       </c>
+      <c r="N52" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O52" s="14" t="n">
+        <v>1566</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -4623,6 +5099,12 @@
       <c r="M53" s="14" t="n">
         <v>4661</v>
       </c>
+      <c r="N53" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O53" s="14" t="n">
+        <v>4666</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -4676,6 +5158,12 @@
       <c r="M54" s="14" t="n">
         <v>5291</v>
       </c>
+      <c r="N54" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O54" s="14" t="n">
+        <v>5293</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -4729,6 +5217,12 @@
       <c r="M55" s="14" t="n">
         <v>170</v>
       </c>
+      <c r="N55" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O55" s="14" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -4782,6 +5276,12 @@
       <c r="M56" s="14" t="n">
         <v>4165</v>
       </c>
+      <c r="N56" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O56" s="14" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -4835,6 +5335,12 @@
       <c r="M57" s="14" t="n">
         <v>1852</v>
       </c>
+      <c r="N57" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O57" s="14" t="n">
+        <v>1854</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -4888,6 +5394,12 @@
       <c r="M58" s="14" t="n">
         <v>4661</v>
       </c>
+      <c r="N58" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O58" s="14" t="n">
+        <v>4666</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -4941,6 +5453,12 @@
       <c r="M59" s="14" t="n">
         <v>5785</v>
       </c>
+      <c r="N59" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>5790</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -4994,6 +5512,12 @@
       <c r="M60" s="14" t="n">
         <v>6562</v>
       </c>
+      <c r="N60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O60" s="14" t="n">
+        <v>6565</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -5047,6 +5571,12 @@
       <c r="M61" s="14" t="n">
         <v>10710</v>
       </c>
+      <c r="N61" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O61" s="14" t="n">
+        <v>10711</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -5100,6 +5630,12 @@
       <c r="M62" s="14" t="n">
         <v>2069</v>
       </c>
+      <c r="N62" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O62" s="14" t="n">
+        <v>2069</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -5153,6 +5689,12 @@
       <c r="M63" s="14" t="n">
         <v>878</v>
       </c>
+      <c r="N63" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O63" s="14" t="n">
+        <v>879</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -5206,6 +5748,12 @@
       <c r="M64" s="14" t="n">
         <v>1205</v>
       </c>
+      <c r="N64" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O64" s="14" t="n">
+        <v>1207</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -5259,6 +5807,12 @@
       <c r="M65" s="14" t="n">
         <v>2069</v>
       </c>
+      <c r="N65" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O65" s="14" t="n">
+        <v>2069</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -5312,6 +5866,12 @@
       <c r="M66" s="14" t="n">
         <v>73</v>
       </c>
+      <c r="N66" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O66" s="14" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -5365,6 +5925,12 @@
       <c r="M67" s="14" t="n">
         <v>886</v>
       </c>
+      <c r="N67" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O67" s="14" t="n">
+        <v>886</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -5417,6 +5983,12 @@
       </c>
       <c r="M68" s="14" t="n">
         <v>14386</v>
+      </c>
+      <c r="N68" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O68" s="14" t="n">
+        <v>14385</v>
       </c>
     </row>
   </sheetData>
@@ -5430,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M206"/>
+  <dimension ref="A1:O206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5465,6 +6037,12 @@
       <c r="M1" s="11" t="n">
         <v>46306</v>
       </c>
+      <c r="N1" s="11" t="n">
+        <v>46308</v>
+      </c>
+      <c r="O1" s="11" t="n">
+        <v>46308</v>
+      </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
@@ -5528,6 +6106,16 @@
         </is>
       </c>
       <c r="M2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="N2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="O2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -5585,6 +6173,12 @@
       <c r="M3" s="14" t="n">
         <v>2142</v>
       </c>
+      <c r="N3" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O3" s="14" t="n">
+        <v>2152</v>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="7" t="n">
@@ -5638,6 +6232,12 @@
       <c r="M4" s="14" t="n">
         <v>637</v>
       </c>
+      <c r="N4" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O4" s="14" t="n">
+        <v>639</v>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="7" t="n">
@@ -5691,6 +6291,12 @@
       <c r="M5" s="14" t="n">
         <v>1556</v>
       </c>
+      <c r="N5" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O5" s="14" t="n">
+        <v>1559</v>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="7" t="n">
@@ -5744,6 +6350,12 @@
       <c r="M6" s="14" t="n">
         <v>147</v>
       </c>
+      <c r="N6" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O6" s="14" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="n">
@@ -5797,6 +6409,12 @@
       <c r="M7" s="14" t="n">
         <v>10895</v>
       </c>
+      <c r="N7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" s="14" t="n">
+        <v>10896</v>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="7" t="n">
@@ -5850,6 +6468,12 @@
       <c r="M8" s="14" t="n">
         <v>2947</v>
       </c>
+      <c r="N8" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O8" s="14" t="n">
+        <v>2948</v>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="7" t="n">
@@ -5903,6 +6527,12 @@
       <c r="M9" s="14" t="n">
         <v>221</v>
       </c>
+      <c r="N9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" s="14" t="n">
+        <v>221</v>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="7" t="n">
@@ -5956,6 +6586,12 @@
       <c r="M10" s="14" t="n">
         <v>5139</v>
       </c>
+      <c r="N10" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O10" s="14" t="n">
+        <v>5141</v>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="7" t="n">
@@ -6009,6 +6645,12 @@
       <c r="M11" s="14" t="n">
         <v>52651</v>
       </c>
+      <c r="N11" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O11" s="14" t="n">
+        <v>52656</v>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="7" t="n">
@@ -6062,6 +6704,12 @@
       <c r="M12" s="14" t="n">
         <v>340</v>
       </c>
+      <c r="N12" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O12" s="14" t="n">
+        <v>340</v>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="7" t="n">
@@ -6115,6 +6763,12 @@
       <c r="M13" s="14" t="n">
         <v>2513</v>
       </c>
+      <c r="N13" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O13" s="14" t="n">
+        <v>2509</v>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="7" t="n">
@@ -6168,6 +6822,12 @@
       <c r="M14" s="14" t="n">
         <v>108</v>
       </c>
+      <c r="N14" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O14" s="14" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="7" t="n">
@@ -6221,6 +6881,12 @@
       <c r="M15" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="N15" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O15" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="7" t="n">
@@ -6274,6 +6940,12 @@
       <c r="M16" s="14" t="n">
         <v>452</v>
       </c>
+      <c r="N16" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O16" s="14" t="n">
+        <v>452</v>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="7" t="n">
@@ -6327,6 +6999,12 @@
       <c r="M17" s="14" t="n">
         <v>2658</v>
       </c>
+      <c r="N17" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O17" s="14" t="n">
+        <v>2659</v>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="7" t="n">
@@ -6380,6 +7058,12 @@
       <c r="M18" s="14" t="n">
         <v>1624</v>
       </c>
+      <c r="N18" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O18" s="14" t="n">
+        <v>1623</v>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="7" t="n">
@@ -6433,6 +7117,12 @@
       <c r="M19" s="14" t="n">
         <v>610</v>
       </c>
+      <c r="N19" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O19" s="14" t="n">
+        <v>610</v>
+      </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="7" t="n">
@@ -6486,6 +7176,12 @@
       <c r="M20" s="14" t="n">
         <v>102</v>
       </c>
+      <c r="N20" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O20" s="14" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="7" t="n">
@@ -6539,6 +7235,12 @@
       <c r="M21" s="14" t="n">
         <v>15</v>
       </c>
+      <c r="N21" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O21" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="7" t="n">
@@ -6592,6 +7294,12 @@
       <c r="M22" s="14" t="n">
         <v>6310</v>
       </c>
+      <c r="N22" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O22" s="14" t="n">
+        <v>6316</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="7" t="n">
@@ -6645,6 +7353,12 @@
       <c r="M23" s="14" t="n">
         <v>6217</v>
       </c>
+      <c r="N23" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O23" s="14" t="n">
+        <v>6225</v>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="7" t="n">
@@ -6698,6 +7412,12 @@
       <c r="M24" s="14" t="n">
         <v>13126</v>
       </c>
+      <c r="N24" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O24" s="14" t="n">
+        <v>13127</v>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="7" t="n">
@@ -6751,6 +7471,12 @@
       <c r="M25" s="14" t="n">
         <v>2374</v>
       </c>
+      <c r="N25" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O25" s="14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="7" t="n">
@@ -6804,6 +7530,12 @@
       <c r="M26" s="14" t="n">
         <v>1919</v>
       </c>
+      <c r="N26" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O26" s="14" t="n">
+        <v>1922</v>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="7" t="n">
@@ -6857,6 +7589,12 @@
       <c r="M27" s="14" t="n">
         <v>13</v>
       </c>
+      <c r="N27" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O27" s="14" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="7" t="n">
@@ -6910,6 +7648,12 @@
       <c r="M28" s="14" t="n">
         <v>10040</v>
       </c>
+      <c r="N28" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O28" s="14" t="n">
+        <v>10044</v>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="7" t="n">
@@ -6963,6 +7707,12 @@
       <c r="M29" s="14" t="n">
         <v>8674</v>
       </c>
+      <c r="N29" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O29" s="14" t="n">
+        <v>8675</v>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="n">
@@ -7016,6 +7766,12 @@
       <c r="M30" s="14" t="n">
         <v>22271</v>
       </c>
+      <c r="N30" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O30" s="14" t="n">
+        <v>22273</v>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="7" t="n">
@@ -7069,6 +7825,12 @@
       <c r="M31" s="14" t="n">
         <v>5578</v>
       </c>
+      <c r="N31" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O31" s="14" t="n">
+        <v>5579</v>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="7" t="n">
@@ -7117,6 +7879,12 @@
       <c r="M32" s="14" t="n">
         <v>12</v>
       </c>
+      <c r="N32" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O32" s="14" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="7" t="n">
@@ -7165,6 +7933,12 @@
       <c r="M33" s="14" t="n">
         <v>4875</v>
       </c>
+      <c r="N33" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O33" s="14" t="n">
+        <v>4884</v>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="7" t="n">
@@ -7213,6 +7987,12 @@
       <c r="M34" s="14" t="n">
         <v>895</v>
       </c>
+      <c r="N34" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O34" s="14" t="n">
+        <v>896</v>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="7" t="n">
@@ -7261,6 +8041,12 @@
       <c r="M35" s="14" t="n">
         <v>18</v>
       </c>
+      <c r="N35" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O35" s="14" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="7" t="n">
@@ -7309,6 +8095,12 @@
       <c r="M36" s="14" t="n">
         <v>70</v>
       </c>
+      <c r="N36" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O36" s="14" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="7" t="n">
@@ -7357,6 +8149,12 @@
       <c r="M37" s="14" t="n">
         <v>1337</v>
       </c>
+      <c r="N37" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O37" s="14" t="n">
+        <v>1339</v>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="7" t="n">
@@ -7405,6 +8203,12 @@
       <c r="M38" s="14" t="n">
         <v>2694</v>
       </c>
+      <c r="N38" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O38" s="14" t="n">
+        <v>2694</v>
+      </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="7" t="n">
@@ -7453,6 +8257,12 @@
       <c r="M39" s="14" t="n">
         <v>23008</v>
       </c>
+      <c r="N39" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O39" s="14" t="n">
+        <v>23007</v>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="7" t="n">
@@ -7501,6 +8311,12 @@
       <c r="M40" s="14" t="n">
         <v>572</v>
       </c>
+      <c r="N40" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O40" s="14" t="n">
+        <v>572</v>
+      </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="7" t="n">
@@ -7549,6 +8365,12 @@
       <c r="M41" s="14" t="n">
         <v>470</v>
       </c>
+      <c r="N41" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O41" s="14" t="n">
+        <v>477</v>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="7" t="n">
@@ -7597,6 +8419,12 @@
       <c r="M42" s="14" t="n">
         <v>2428</v>
       </c>
+      <c r="N42" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O42" s="14" t="n">
+        <v>2433</v>
+      </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="7" t="n">
@@ -7645,6 +8473,12 @@
       <c r="M43" s="14" t="n">
         <v>714</v>
       </c>
+      <c r="N43" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O43" s="14" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="7" t="n">
@@ -7693,6 +8527,12 @@
       <c r="M44" s="14" t="n">
         <v>6563</v>
       </c>
+      <c r="N44" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O44" s="14" t="n">
+        <v>6578</v>
+      </c>
     </row>
     <row r="45" ht="20" customHeight="1">
       <c r="A45" s="7" t="n">
@@ -7741,6 +8581,12 @@
       <c r="M45" s="14" t="n">
         <v>1110</v>
       </c>
+      <c r="N45" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O45" s="14" t="n">
+        <v>1110</v>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="7" t="n">
@@ -7789,6 +8635,12 @@
       <c r="M46" s="14" t="n">
         <v>7177</v>
       </c>
+      <c r="N46" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O46" s="14" t="n">
+        <v>7175</v>
+      </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="7" t="n">
@@ -7837,6 +8689,12 @@
       <c r="M47" s="14" t="n">
         <v>3835</v>
       </c>
+      <c r="N47" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O47" s="14" t="n">
+        <v>3839</v>
+      </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="7" t="n">
@@ -7885,6 +8743,12 @@
       <c r="M48" s="14" t="n">
         <v>781</v>
       </c>
+      <c r="N48" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O48" s="14" t="n">
+        <v>3658</v>
+      </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="7" t="n">
@@ -7933,6 +8797,12 @@
       <c r="M49" s="14" t="n">
         <v>2391</v>
       </c>
+      <c r="N49" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O49" s="14" t="n">
+        <v>2389</v>
+      </c>
     </row>
     <row r="50" ht="20" customHeight="1">
       <c r="A50" s="7" t="n">
@@ -7981,6 +8851,12 @@
       <c r="M50" s="14" t="n">
         <v>5616</v>
       </c>
+      <c r="N50" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O50" s="14" t="n">
+        <v>5628</v>
+      </c>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="A51" s="7" t="n">
@@ -8029,6 +8905,12 @@
       <c r="M51" s="14" t="n">
         <v>1007</v>
       </c>
+      <c r="N51" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O51" s="14" t="n">
+        <v>1007</v>
+      </c>
     </row>
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="7" t="n">
@@ -8077,6 +8959,12 @@
       <c r="M52" s="14" t="n">
         <v>28</v>
       </c>
+      <c r="N52" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O52" s="14" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="7" t="n">
@@ -8125,6 +9013,12 @@
       <c r="M53" s="14" t="n">
         <v>9654</v>
       </c>
+      <c r="N53" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O53" s="14" t="n">
+        <v>9656</v>
+      </c>
     </row>
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="7" t="n">
@@ -8173,6 +9067,12 @@
       <c r="M54" s="14" t="n">
         <v>797</v>
       </c>
+      <c r="N54" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O54" s="14" t="n">
+        <v>797</v>
+      </c>
     </row>
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="7" t="n">
@@ -8221,6 +9121,12 @@
       <c r="M55" s="14" t="n">
         <v>298</v>
       </c>
+      <c r="N55" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O55" s="14" t="n">
+        <v>298</v>
+      </c>
     </row>
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="7" t="n">
@@ -8269,6 +9175,12 @@
       <c r="M56" s="14" t="n">
         <v>51</v>
       </c>
+      <c r="N56" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O56" s="14" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="7" t="n">
@@ -8317,6 +9229,12 @@
       <c r="M57" s="14" t="n">
         <v>444</v>
       </c>
+      <c r="N57" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O57" s="14" t="n">
+        <v>444</v>
+      </c>
     </row>
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="7" t="n">
@@ -8365,6 +9283,12 @@
       <c r="M58" s="14" t="n">
         <v>203</v>
       </c>
+      <c r="N58" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O58" s="14" t="n">
+        <v>203</v>
+      </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="7" t="n">
@@ -8413,6 +9337,12 @@
       <c r="M59" s="14" t="n">
         <v>659</v>
       </c>
+      <c r="N59" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>658</v>
+      </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="7" t="n">
@@ -8461,6 +9391,12 @@
       <c r="M60" s="14" t="n">
         <v>362</v>
       </c>
+      <c r="N60" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O60" s="14" t="n">
+        <v>363</v>
+      </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="7" t="n">
@@ -8509,6 +9445,12 @@
       <c r="M61" s="14" t="n">
         <v>2919</v>
       </c>
+      <c r="N61" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O61" s="14" t="n">
+        <v>2917</v>
+      </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="7" t="n">
@@ -8557,6 +9499,12 @@
       <c r="M62" s="14" t="n">
         <v>587</v>
       </c>
+      <c r="N62" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O62" s="14" t="n">
+        <v>588</v>
+      </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="7" t="n">
@@ -8605,6 +9553,12 @@
       <c r="M63" s="14" t="n">
         <v>9261</v>
       </c>
+      <c r="N63" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O63" s="14" t="n">
+        <v>9260</v>
+      </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="7" t="n">
@@ -8653,6 +9607,12 @@
       <c r="M64" s="14" t="n">
         <v>1008</v>
       </c>
+      <c r="N64" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O64" s="14" t="n">
+        <v>1009</v>
+      </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="7" t="n">
@@ -8701,6 +9661,12 @@
       <c r="M65" s="14" t="n">
         <v>3845</v>
       </c>
+      <c r="N65" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O65" s="14" t="n">
+        <v>3850</v>
+      </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="7" t="n">
@@ -8749,6 +9715,12 @@
       <c r="M66" s="14" t="n">
         <v>4139</v>
       </c>
+      <c r="N66" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O66" s="14" t="n">
+        <v>4139</v>
+      </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="7" t="n">
@@ -8797,6 +9769,12 @@
       <c r="M67" s="14" t="n">
         <v>26860</v>
       </c>
+      <c r="N67" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O67" s="14" t="n">
+        <v>26860</v>
+      </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="7" t="n">
@@ -8845,6 +9823,12 @@
       <c r="M68" s="14" t="n">
         <v>4321</v>
       </c>
+      <c r="N68" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O68" s="14" t="n">
+        <v>4321</v>
+      </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="7" t="n">
@@ -8893,6 +9877,12 @@
       <c r="M69" s="14" t="n">
         <v>2278</v>
       </c>
+      <c r="N69" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O69" s="14" t="n">
+        <v>2271</v>
+      </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="7" t="n">
@@ -8941,6 +9931,12 @@
       <c r="M70" s="14" t="n">
         <v>281</v>
       </c>
+      <c r="N70" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O70" s="14" t="n">
+        <v>281</v>
+      </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="7" t="n">
@@ -8989,6 +9985,12 @@
       <c r="M71" s="14" t="n">
         <v>6144</v>
       </c>
+      <c r="N71" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O71" s="14" t="n">
+        <v>6144</v>
+      </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="7" t="n">
@@ -9037,6 +10039,12 @@
       <c r="M72" s="14" t="n">
         <v>47</v>
       </c>
+      <c r="N72" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O72" s="14" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="7" t="n">
@@ -9085,6 +10093,12 @@
       <c r="M73" s="14" t="n">
         <v>1112</v>
       </c>
+      <c r="N73" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O73" s="14" t="n">
+        <v>1116</v>
+      </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="7" t="n">
@@ -9133,6 +10147,12 @@
       <c r="M74" s="14" t="n">
         <v>9514</v>
       </c>
+      <c r="N74" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O74" s="14" t="n">
+        <v>9515</v>
+      </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="7" t="n">
@@ -9181,6 +10201,12 @@
       <c r="M75" s="14" t="n">
         <v>16975</v>
       </c>
+      <c r="N75" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O75" s="14" t="n">
+        <v>16976</v>
+      </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="7" t="n">
@@ -9229,6 +10255,12 @@
       <c r="M76" s="14" t="n">
         <v>8567</v>
       </c>
+      <c r="N76" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O76" s="14" t="n">
+        <v>8567</v>
+      </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="7" t="n">
@@ -9277,6 +10309,12 @@
       <c r="M77" s="14" t="n">
         <v>2491</v>
       </c>
+      <c r="N77" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O77" s="14" t="n">
+        <v>2500</v>
+      </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="7" t="n">
@@ -9325,6 +10363,12 @@
       <c r="M78" s="14" t="n">
         <v>10950</v>
       </c>
+      <c r="N78" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O78" s="14" t="n">
+        <v>10951</v>
+      </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="7" t="n">
@@ -9373,6 +10417,12 @@
       <c r="M79" s="14" t="n">
         <v>175</v>
       </c>
+      <c r="N79" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O79" s="14" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="7" t="n">
@@ -9421,6 +10471,12 @@
       <c r="M80" s="14" t="n">
         <v>148</v>
       </c>
+      <c r="N80" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O80" s="14" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="7" t="n">
@@ -9481,6 +10537,16 @@
           <t>Closed</t>
         </is>
       </c>
+      <c r="N81" s="15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="O81" s="15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="7" t="n">
@@ -9529,6 +10595,12 @@
       <c r="M82" s="14" t="n">
         <v>1459</v>
       </c>
+      <c r="N82" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O82" s="14" t="n">
+        <v>1464</v>
+      </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="7" t="n">
@@ -9577,6 +10649,12 @@
       <c r="M83" s="14" t="n">
         <v>1743</v>
       </c>
+      <c r="N83" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O83" s="14" t="n">
+        <v>1748</v>
+      </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="7" t="n">
@@ -9625,6 +10703,12 @@
       <c r="M84" s="14" t="n">
         <v>43</v>
       </c>
+      <c r="N84" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O84" s="14" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="7" t="n">
@@ -9673,6 +10757,12 @@
       <c r="M85" s="14" t="n">
         <v>470</v>
       </c>
+      <c r="N85" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O85" s="14" t="n">
+        <v>7175</v>
+      </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="7" t="n">
@@ -9721,6 +10811,12 @@
       <c r="M86" s="14" t="n">
         <v>45</v>
       </c>
+      <c r="N86" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O86" s="14" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="7" t="n">
@@ -9769,6 +10865,12 @@
       <c r="M87" s="14" t="n">
         <v>4508</v>
       </c>
+      <c r="N87" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O87" s="14" t="n">
+        <v>4508</v>
+      </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="7" t="n">
@@ -9817,6 +10919,12 @@
       <c r="M88" s="14" t="n">
         <v>23</v>
       </c>
+      <c r="N88" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O88" s="14" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="7" t="n">
@@ -9865,6 +10973,12 @@
       <c r="M89" s="14" t="n">
         <v>837</v>
       </c>
+      <c r="N89" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O89" s="14" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="7" t="n">
@@ -9913,6 +11027,12 @@
       <c r="M90" s="14" t="n">
         <v>14</v>
       </c>
+      <c r="N90" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O90" s="14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="7" t="n">
@@ -9961,6 +11081,12 @@
       <c r="M91" s="14" t="n">
         <v>52</v>
       </c>
+      <c r="N91" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O91" s="14" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="7" t="n">
@@ -10009,6 +11135,12 @@
       <c r="M92" s="14" t="n">
         <v>391</v>
       </c>
+      <c r="N92" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O92" s="14" t="n">
+        <v>394</v>
+      </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="7" t="n">
@@ -10057,6 +11189,12 @@
       <c r="M93" s="14" t="n">
         <v>160</v>
       </c>
+      <c r="N93" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O93" s="14" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="7" t="n">
@@ -10105,6 +11243,12 @@
       <c r="M94" s="14" t="n">
         <v>1624</v>
       </c>
+      <c r="N94" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O94" s="14" t="n">
+        <v>1624</v>
+      </c>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="7" t="n">
@@ -10153,6 +11297,12 @@
       <c r="M95" s="14" t="n">
         <v>7503</v>
       </c>
+      <c r="N95" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O95" s="14" t="n">
+        <v>7504</v>
+      </c>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="7" t="n">
@@ -10201,6 +11351,12 @@
       <c r="M96" s="14" t="n">
         <v>2835</v>
       </c>
+      <c r="N96" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O96" s="14" t="n">
+        <v>2835</v>
+      </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="7" t="n">
@@ -10249,6 +11405,12 @@
       <c r="M97" s="14" t="n">
         <v>359</v>
       </c>
+      <c r="N97" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O97" s="14" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="7" t="n">
@@ -10297,6 +11459,12 @@
       <c r="M98" s="14" t="n">
         <v>42244</v>
       </c>
+      <c r="N98" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O98" s="14" t="n">
+        <v>42245</v>
+      </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="7" t="n">
@@ -10345,6 +11513,12 @@
       <c r="M99" s="14" t="n">
         <v>310</v>
       </c>
+      <c r="N99" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O99" s="14" t="n">
+        <v>310</v>
+      </c>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="7" t="n">
@@ -10393,6 +11567,12 @@
       <c r="M100" s="14" t="n">
         <v>346</v>
       </c>
+      <c r="N100" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O100" s="14" t="n">
+        <v>347</v>
+      </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="7" t="n">
@@ -10441,6 +11621,12 @@
       <c r="M101" s="14" t="n">
         <v>25</v>
       </c>
+      <c r="N101" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O101" s="14" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="7" t="n">
@@ -10489,6 +11675,12 @@
       <c r="M102" s="14" t="n">
         <v>9</v>
       </c>
+      <c r="N102" s="14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O102" s="14" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="7" t="n">
@@ -10537,6 +11729,12 @@
       <c r="M103" s="14" t="n">
         <v>867</v>
       </c>
+      <c r="N103" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O103" s="14" t="n">
+        <v>870</v>
+      </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="7" t="n">
@@ -10585,6 +11783,12 @@
       <c r="M104" s="14" t="n">
         <v>430</v>
       </c>
+      <c r="N104" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O104" s="14" t="n">
+        <v>430</v>
+      </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="7" t="n">
@@ -10633,6 +11837,12 @@
       <c r="M105" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="N105" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="O105" s="14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="7" t="n">
@@ -10681,6 +11891,12 @@
       <c r="M106" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="N106" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O106" s="14" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="7" t="n">
@@ -10729,6 +11945,12 @@
       <c r="M107" s="14" t="n">
         <v>4256</v>
       </c>
+      <c r="N107" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O107" s="14" t="n">
+        <v>444</v>
+      </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="7" t="n">
@@ -10777,6 +11999,12 @@
       <c r="M108" s="14" t="n">
         <v>3</v>
       </c>
+      <c r="N108" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O108" s="14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="7" t="n">
@@ -10825,6 +12053,12 @@
       <c r="M109" s="14" t="n">
         <v>64</v>
       </c>
+      <c r="N109" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O109" s="14" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="7" t="n">
@@ -10873,6 +12107,12 @@
       <c r="M110" s="14" t="n">
         <v>100</v>
       </c>
+      <c r="N110" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O110" s="14" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="7" t="n">
@@ -10921,6 +12161,12 @@
       <c r="M111" s="14" t="n">
         <v>866</v>
       </c>
+      <c r="N111" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O111" s="14" t="n">
+        <v>866</v>
+      </c>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="7" t="n">
@@ -10974,6 +12220,12 @@
       <c r="M112" s="14" t="n">
         <v>8408</v>
       </c>
+      <c r="N112" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O112" s="14" t="n">
+        <v>8399</v>
+      </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="7" t="n">
@@ -11027,6 +12279,12 @@
       <c r="M113" s="14" t="n">
         <v>4906</v>
       </c>
+      <c r="N113" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O113" s="14" t="n">
+        <v>4907</v>
+      </c>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="7" t="n">
@@ -11080,6 +12338,12 @@
       <c r="M114" s="14" t="n">
         <v>3368</v>
       </c>
+      <c r="N114" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O114" s="14" t="n">
+        <v>3368</v>
+      </c>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="7" t="n">
@@ -11133,6 +12397,12 @@
       <c r="M115" s="14" t="n">
         <v>170</v>
       </c>
+      <c r="N115" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O115" s="14" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="7" t="n">
@@ -11186,6 +12456,12 @@
       <c r="M116" s="14" t="n">
         <v>8674</v>
       </c>
+      <c r="N116" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O116" s="14" t="n">
+        <v>8675</v>
+      </c>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="7" t="n">
@@ -11239,6 +12515,12 @@
       <c r="M117" s="14" t="n">
         <v>11860</v>
       </c>
+      <c r="N117" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O117" s="14" t="n">
+        <v>11865</v>
+      </c>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="7" t="n">
@@ -11292,6 +12574,12 @@
       <c r="M118" s="14" t="n">
         <v>2794</v>
       </c>
+      <c r="N118" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O118" s="14" t="n">
+        <v>2796</v>
+      </c>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="7" t="n">
@@ -11345,6 +12633,12 @@
       <c r="M119" s="14" t="n">
         <v>89</v>
       </c>
+      <c r="N119" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O119" s="14" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="7" t="n">
@@ -11398,6 +12692,12 @@
       <c r="M120" s="14" t="n">
         <v>465</v>
       </c>
+      <c r="N120" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O120" s="14" t="n">
+        <v>465</v>
+      </c>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="7" t="n">
@@ -11451,6 +12751,12 @@
       <c r="M121" s="14" t="n">
         <v>776</v>
       </c>
+      <c r="N121" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O121" s="14" t="n">
+        <v>776</v>
+      </c>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122" s="7" t="n">
@@ -11504,6 +12810,12 @@
       <c r="M122" s="14" t="n">
         <v>170</v>
       </c>
+      <c r="N122" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O122" s="14" t="n">
+        <v>171</v>
+      </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="7" t="n">
@@ -11557,6 +12869,12 @@
       <c r="M123" s="14" t="n">
         <v>14</v>
       </c>
+      <c r="N123" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O123" s="14" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="7" t="n">
@@ -11610,6 +12928,12 @@
       <c r="M124" s="14" t="n">
         <v>41</v>
       </c>
+      <c r="N124" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O124" s="14" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125" s="7" t="n">
@@ -11663,6 +12987,12 @@
       <c r="M125" s="14" t="n">
         <v>48</v>
       </c>
+      <c r="N125" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O125" s="14" t="n">
+        <v>49</v>
+      </c>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126" s="7" t="n">
@@ -11716,6 +13046,12 @@
       <c r="M126" s="14" t="n">
         <v>11</v>
       </c>
+      <c r="N126" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O126" s="14" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127" s="7" t="n">
@@ -11769,6 +13105,12 @@
       <c r="M127" s="14" t="n">
         <v>4192</v>
       </c>
+      <c r="N127" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O127" s="14" t="n">
+        <v>4191</v>
+      </c>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128" s="7" t="n">
@@ -11822,6 +13164,12 @@
       <c r="M128" s="14" t="n">
         <v>294</v>
       </c>
+      <c r="N128" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O128" s="14" t="n">
+        <v>298</v>
+      </c>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129" s="7" t="n">
@@ -11870,6 +13218,12 @@
       <c r="M129" s="14" t="n">
         <v>4228</v>
       </c>
+      <c r="N129" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O129" s="14" t="n">
+        <v>4228</v>
+      </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="7" t="n">
@@ -11918,6 +13272,12 @@
       <c r="M130" s="14" t="n">
         <v>667</v>
       </c>
+      <c r="N130" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O130" s="14" t="n">
+        <v>669</v>
+      </c>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131" s="7" t="n">
@@ -11966,6 +13326,12 @@
       <c r="M131" s="14" t="n">
         <v>790</v>
       </c>
+      <c r="N131" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O131" s="14" t="n">
+        <v>793</v>
+      </c>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132" s="7" t="n">
@@ -12014,6 +13380,12 @@
       <c r="M132" s="14" t="n">
         <v>720</v>
       </c>
+      <c r="N132" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O132" s="14" t="n">
+        <v>727</v>
+      </c>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133" s="7" t="n">
@@ -12062,6 +13434,12 @@
       <c r="M133" s="14" t="n">
         <v>1424</v>
       </c>
+      <c r="N133" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O133" s="14" t="n">
+        <v>1424</v>
+      </c>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134" s="7" t="n">
@@ -12110,6 +13488,12 @@
       <c r="M134" s="14" t="n">
         <v>702</v>
       </c>
+      <c r="N134" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O134" s="14" t="n">
+        <v>708</v>
+      </c>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="7" t="n">
@@ -12158,6 +13542,12 @@
       <c r="M135" s="14" t="n">
         <v>384</v>
       </c>
+      <c r="N135" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O135" s="14" t="n">
+        <v>387</v>
+      </c>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136" s="7" t="n">
@@ -12206,6 +13596,12 @@
       <c r="M136" s="14" t="n">
         <v>384</v>
       </c>
+      <c r="N136" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O136" s="14" t="n">
+        <v>387</v>
+      </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="7" t="n">
@@ -12254,6 +13650,12 @@
       <c r="M137" s="14" t="n">
         <v>5288</v>
       </c>
+      <c r="N137" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O137" s="14" t="n">
+        <v>5294</v>
+      </c>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138" s="7" t="n">
@@ -12302,6 +13704,12 @@
       <c r="M138" s="14" t="n">
         <v>2546</v>
       </c>
+      <c r="N138" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O138" s="14" t="n">
+        <v>2546</v>
+      </c>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139" s="7" t="n">
@@ -12350,6 +13758,12 @@
       <c r="M139" s="14" t="n">
         <v>3198</v>
       </c>
+      <c r="N139" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O139" s="14" t="n">
+        <v>3200</v>
+      </c>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140" s="7" t="n">
@@ -12398,6 +13812,12 @@
       <c r="M140" s="14" t="n">
         <v>1459</v>
       </c>
+      <c r="N140" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O140" s="14" t="n">
+        <v>1464</v>
+      </c>
     </row>
     <row r="141" ht="20" customHeight="1">
       <c r="A141" s="7" t="n">
@@ -12446,6 +13866,12 @@
       <c r="M141" s="14" t="n">
         <v>175</v>
       </c>
+      <c r="N141" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O141" s="14" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="7" t="n">
@@ -12494,6 +13920,12 @@
       <c r="M142" s="14" t="n">
         <v>19</v>
       </c>
+      <c r="N142" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O142" s="14" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="7" t="n">
@@ -12542,6 +13974,12 @@
       <c r="M143" s="14" t="n">
         <v>4214</v>
       </c>
+      <c r="N143" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O143" s="14" t="n">
+        <v>4223</v>
+      </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="7" t="n">
@@ -12590,6 +14028,12 @@
       <c r="M144" s="14" t="n">
         <v>4589</v>
       </c>
+      <c r="N144" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O144" s="14" t="n">
+        <v>4589</v>
+      </c>
     </row>
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="7" t="n">
@@ -12638,6 +14082,12 @@
       <c r="M145" s="14" t="n">
         <v>1533</v>
       </c>
+      <c r="N145" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O145" s="14" t="n">
+        <v>1533</v>
+      </c>
     </row>
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="7" t="n">
@@ -12686,6 +14136,12 @@
       <c r="M146" s="14" t="n">
         <v>3952</v>
       </c>
+      <c r="N146" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O146" s="14" t="n">
+        <v>3957</v>
+      </c>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="7" t="n">
@@ -12734,6 +14190,12 @@
       <c r="M147" s="14" t="n">
         <v>2953</v>
       </c>
+      <c r="N147" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O147" s="14" t="n">
+        <v>2953</v>
+      </c>
     </row>
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="7" t="n">
@@ -12782,6 +14244,12 @@
       <c r="M148" s="14" t="n">
         <v>63</v>
       </c>
+      <c r="N148" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O148" s="14" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="7" t="n">
@@ -12830,6 +14298,12 @@
       <c r="M149" s="14" t="n">
         <v>80</v>
       </c>
+      <c r="N149" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O149" s="14" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="7" t="n">
@@ -12878,6 +14352,12 @@
       <c r="M150" s="14" t="n">
         <v>2598</v>
       </c>
+      <c r="N150" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O150" s="14" t="n">
+        <v>2599</v>
+      </c>
     </row>
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="7" t="n">
@@ -12926,6 +14406,12 @@
       <c r="M151" s="14" t="n">
         <v>3845</v>
       </c>
+      <c r="N151" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O151" s="14" t="n">
+        <v>3850</v>
+      </c>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="7" t="n">
@@ -12974,6 +14460,12 @@
       <c r="M152" s="14" t="n">
         <v>511</v>
       </c>
+      <c r="N152" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O152" s="14" t="n">
+        <v>511</v>
+      </c>
     </row>
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="7" t="n">
@@ -13022,6 +14514,12 @@
       <c r="M153" s="14" t="n">
         <v>9261</v>
       </c>
+      <c r="N153" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O153" s="14" t="n">
+        <v>9260</v>
+      </c>
     </row>
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="7" t="n">
@@ -13070,6 +14568,12 @@
       <c r="M154" s="14" t="n">
         <v>9245</v>
       </c>
+      <c r="N154" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O154" s="14" t="n">
+        <v>9247</v>
+      </c>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="7" t="n">
@@ -13118,6 +14622,12 @@
       <c r="M155" s="14" t="n">
         <v>4321</v>
       </c>
+      <c r="N155" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O155" s="14" t="n">
+        <v>4321</v>
+      </c>
     </row>
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="7" t="n">
@@ -13166,6 +14676,12 @@
       <c r="M156" s="14" t="n">
         <v>199</v>
       </c>
+      <c r="N156" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O156" s="14" t="n">
+        <v>199</v>
+      </c>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="7" t="n">
@@ -13214,6 +14730,12 @@
       <c r="M157" s="14" t="n">
         <v>587</v>
       </c>
+      <c r="N157" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O157" s="14" t="n">
+        <v>588</v>
+      </c>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="7" t="n">
@@ -13262,6 +14784,12 @@
       <c r="M158" s="14" t="n">
         <v>81</v>
       </c>
+      <c r="N158" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O158" s="14" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="7" t="n">
@@ -13310,6 +14838,12 @@
       <c r="M159" s="14" t="n">
         <v>38</v>
       </c>
+      <c r="N159" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O159" s="14" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="160" ht="20" customHeight="1">
       <c r="A160" s="7" t="n">
@@ -13358,6 +14892,12 @@
       <c r="M160" s="14" t="n">
         <v>100</v>
       </c>
+      <c r="N160" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O160" s="14" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="7" t="n">
@@ -13406,6 +14946,12 @@
       <c r="M161" s="14" t="n">
         <v>121</v>
       </c>
+      <c r="N161" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O161" s="14" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="7" t="n">
@@ -13454,6 +15000,12 @@
       <c r="M162" s="14" t="n">
         <v>1955</v>
       </c>
+      <c r="N162" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O162" s="14" t="n">
+        <v>1957</v>
+      </c>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="7" t="n">
@@ -13502,6 +15054,12 @@
       <c r="M163" s="14" t="n">
         <v>1700</v>
       </c>
+      <c r="N163" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O163" s="14" t="n">
+        <v>1701</v>
+      </c>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="7" t="n">
@@ -13550,6 +15108,12 @@
       <c r="M164" s="14" t="n">
         <v>9353</v>
       </c>
+      <c r="N164" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O164" s="14" t="n">
+        <v>9356</v>
+      </c>
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="7" t="n">
@@ -13598,6 +15162,12 @@
       <c r="M165" s="14" t="n">
         <v>1092</v>
       </c>
+      <c r="N165" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O165" s="14" t="n">
+        <v>1092</v>
+      </c>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="7" t="n">
@@ -13646,6 +15216,12 @@
       <c r="M166" s="14" t="n">
         <v>175</v>
       </c>
+      <c r="N166" s="14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O166" s="14" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="7" t="n">
@@ -13694,6 +15270,12 @@
       <c r="M167" s="14" t="n">
         <v>3363</v>
       </c>
+      <c r="N167" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O167" s="14" t="n">
+        <v>3364</v>
+      </c>
     </row>
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="7" t="n">
@@ -13742,6 +15324,12 @@
       <c r="M168" s="14" t="n">
         <v>851</v>
       </c>
+      <c r="N168" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O168" s="14" t="n">
+        <v>851</v>
+      </c>
     </row>
     <row r="169" ht="20" customHeight="1">
       <c r="A169" s="7" t="n">
@@ -13790,6 +15378,12 @@
       <c r="M169" s="14" t="n">
         <v>121</v>
       </c>
+      <c r="N169" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O169" s="14" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="170" ht="20" customHeight="1">
       <c r="A170" s="7" t="n">
@@ -13838,6 +15432,12 @@
       <c r="M170" s="14" t="n">
         <v>142</v>
       </c>
+      <c r="N170" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O170" s="14" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="7" t="n">
@@ -13886,6 +15486,12 @@
       <c r="M171" s="14" t="n">
         <v>220</v>
       </c>
+      <c r="N171" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O171" s="14" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="7" t="n">
@@ -13934,6 +15540,12 @@
       <c r="M172" s="14" t="n">
         <v>190</v>
       </c>
+      <c r="N172" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O172" s="14" t="n">
+        <v>190</v>
+      </c>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="7" t="n">
@@ -13982,6 +15594,12 @@
       <c r="M173" s="14" t="n">
         <v>408</v>
       </c>
+      <c r="N173" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O173" s="14" t="n">
+        <v>408</v>
+      </c>
     </row>
     <row r="174" ht="20" customHeight="1">
       <c r="A174" s="7" t="n">
@@ -14030,6 +15648,12 @@
       <c r="M174" s="14" t="n">
         <v>71</v>
       </c>
+      <c r="N174" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O174" s="14" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="7" t="n">
@@ -14078,6 +15702,12 @@
       <c r="M175" s="14" t="n">
         <v>78</v>
       </c>
+      <c r="N175" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O175" s="14" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="7" t="n">
@@ -14126,6 +15756,12 @@
       <c r="M176" s="14" t="n">
         <v>2054</v>
       </c>
+      <c r="N176" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O176" s="14" t="n">
+        <v>2055</v>
+      </c>
     </row>
     <row r="177" ht="20" customHeight="1">
       <c r="A177" s="7" t="n">
@@ -14174,6 +15810,12 @@
       <c r="M177" s="14" t="n">
         <v>567</v>
       </c>
+      <c r="N177" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O177" s="14" t="n">
+        <v>567</v>
+      </c>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="7" t="n">
@@ -14222,6 +15864,12 @@
       <c r="M178" s="14" t="n">
         <v>4077</v>
       </c>
+      <c r="N178" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O178" s="14" t="n">
+        <v>4077</v>
+      </c>
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="7" t="n">
@@ -14270,6 +15918,12 @@
       <c r="M179" s="14" t="n">
         <v>3197</v>
       </c>
+      <c r="N179" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O179" s="14" t="n">
+        <v>3197</v>
+      </c>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="7" t="n">
@@ -14318,6 +15972,12 @@
       <c r="M180" s="14" t="n">
         <v>494</v>
       </c>
+      <c r="N180" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O180" s="14" t="n">
+        <v>494</v>
+      </c>
     </row>
     <row r="181" ht="20" customHeight="1">
       <c r="A181" s="7" t="n">
@@ -14366,6 +16026,12 @@
       <c r="M181" s="14" t="n">
         <v>180</v>
       </c>
+      <c r="N181" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O181" s="14" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="182" ht="20" customHeight="1">
       <c r="A182" s="7" t="n">
@@ -14414,6 +16080,12 @@
       <c r="M182" s="14" t="n">
         <v>4077</v>
       </c>
+      <c r="N182" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O182" s="14" t="n">
+        <v>4077</v>
+      </c>
     </row>
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="7" t="n">
@@ -14462,6 +16134,12 @@
       <c r="M183" s="14" t="n">
         <v>219</v>
       </c>
+      <c r="N183" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O183" s="14" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="7" t="n">
@@ -14510,6 +16188,12 @@
       <c r="M184" s="14" t="n">
         <v>372</v>
       </c>
+      <c r="N184" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O184" s="14" t="n">
+        <v>372</v>
+      </c>
     </row>
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="7" t="n">
@@ -14558,6 +16242,12 @@
       <c r="M185" s="14" t="n">
         <v>728</v>
       </c>
+      <c r="N185" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O185" s="14" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="186" ht="20" customHeight="1">
       <c r="A186" s="7" t="n">
@@ -14606,6 +16296,12 @@
       <c r="M186" s="14" t="n">
         <v>436</v>
       </c>
+      <c r="N186" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O186" s="14" t="n">
+        <v>436</v>
+      </c>
     </row>
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="7" t="n">
@@ -14654,6 +16350,12 @@
       <c r="M187" s="14" t="n">
         <v>15</v>
       </c>
+      <c r="N187" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O187" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="188" ht="20" customHeight="1">
       <c r="A188" s="7" t="n">
@@ -14702,6 +16404,12 @@
       <c r="M188" s="14" t="n">
         <v>9</v>
       </c>
+      <c r="N188" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O188" s="14" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="7" t="n">
@@ -14750,6 +16458,12 @@
       <c r="M189" s="14" t="n">
         <v>196</v>
       </c>
+      <c r="N189" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O189" s="14" t="n">
+        <v>196</v>
+      </c>
     </row>
     <row r="190" ht="20" customHeight="1">
       <c r="A190" s="7" t="n">
@@ -14798,6 +16512,12 @@
       <c r="M190" s="14" t="n">
         <v>64</v>
       </c>
+      <c r="N190" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O190" s="14" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="191" ht="20" customHeight="1">
       <c r="A191" s="7" t="n">
@@ -14846,6 +16566,12 @@
       <c r="M191" s="14" t="n">
         <v>7443</v>
       </c>
+      <c r="N191" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O191" s="14" t="n">
+        <v>7453</v>
+      </c>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="7" t="n">
@@ -14894,6 +16620,12 @@
       <c r="M192" s="14" t="n">
         <v>2944</v>
       </c>
+      <c r="N192" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O192" s="14" t="n">
+        <v>2946</v>
+      </c>
     </row>
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="7" t="n">
@@ -14942,6 +16674,12 @@
       <c r="M193" s="14" t="n">
         <v>493</v>
       </c>
+      <c r="N193" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O193" s="14" t="n">
+        <v>493</v>
+      </c>
     </row>
     <row r="194" ht="20" customHeight="1">
       <c r="A194" s="7" t="n">
@@ -14990,6 +16728,12 @@
       <c r="M194" s="14" t="n">
         <v>64</v>
       </c>
+      <c r="N194" s="14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O194" s="14" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="195" ht="20" customHeight="1">
       <c r="A195" s="7" t="n">
@@ -15038,6 +16782,12 @@
       <c r="M195" s="14" t="n">
         <v>2230</v>
       </c>
+      <c r="N195" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O195" s="14" t="n">
+        <v>2230</v>
+      </c>
     </row>
     <row r="196" ht="20" customHeight="1">
       <c r="A196" s="7" t="n">
@@ -15086,6 +16836,12 @@
       <c r="M196" s="14" t="n">
         <v>2680</v>
       </c>
+      <c r="N196" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O196" s="14" t="n">
+        <v>2681</v>
+      </c>
     </row>
     <row r="197" ht="20" customHeight="1">
       <c r="A197" s="7" t="n">
@@ -15134,6 +16890,12 @@
       <c r="M197" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="N197" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O197" s="14" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="7" t="n">
@@ -15182,6 +16944,12 @@
       <c r="M198" s="14" t="n">
         <v>8993</v>
       </c>
+      <c r="N198" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O198" s="14" t="n">
+        <v>9010</v>
+      </c>
     </row>
     <row r="199" ht="20" customHeight="1">
       <c r="A199" s="7" t="n">
@@ -15230,6 +16998,12 @@
       <c r="M199" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="N199" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O199" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="200" ht="20" customHeight="1">
       <c r="A200" s="7" t="n">
@@ -15278,6 +17052,12 @@
       <c r="M200" s="14" t="n">
         <v>191</v>
       </c>
+      <c r="N200" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O200" s="14" t="n">
+        <v>191</v>
+      </c>
     </row>
     <row r="201" ht="20" customHeight="1">
       <c r="A201" s="7" t="n">
@@ -15326,6 +17106,12 @@
       <c r="M201" s="14" t="n">
         <v>143</v>
       </c>
+      <c r="N201" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O201" s="14" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="202" ht="20" customHeight="1">
       <c r="A202" s="7" t="n">
@@ -15374,6 +17160,12 @@
       <c r="M202" s="14" t="n">
         <v>2886</v>
       </c>
+      <c r="N202" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O202" s="14" t="n">
+        <v>2888</v>
+      </c>
     </row>
     <row r="203" ht="20" customHeight="1">
       <c r="A203" s="7" t="n">
@@ -15422,6 +17214,12 @@
       <c r="M203" s="14" t="n">
         <v>17057</v>
       </c>
+      <c r="N203" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O203" s="14" t="n">
+        <v>17081</v>
+      </c>
     </row>
     <row r="204" ht="20" customHeight="1">
       <c r="A204" s="7" t="n">
@@ -15470,6 +17268,12 @@
       <c r="M204" s="14" t="n">
         <v>152</v>
       </c>
+      <c r="N204" s="14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O204" s="14" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="205" ht="20" customHeight="1">
       <c r="A205" s="7" t="n">
@@ -15518,6 +17322,12 @@
       <c r="M205" s="14" t="n">
         <v>338</v>
       </c>
+      <c r="N205" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O205" s="14" t="n">
+        <v>339</v>
+      </c>
     </row>
     <row r="206" ht="20" customHeight="1">
       <c r="A206" s="7" t="n">
@@ -15564,6 +17374,12 @@
         <v>4.5</v>
       </c>
       <c r="M206" s="14" t="n">
+        <v>161</v>
+      </c>
+      <c r="N206" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O206" s="14" t="n">
         <v>161</v>
       </c>
     </row>
@@ -15579,7 +17395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:N68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15614,6 +17430,12 @@
       <c r="L1" s="11" t="n">
         <v>46306</v>
       </c>
+      <c r="M1" s="11" t="n">
+        <v>46308</v>
+      </c>
+      <c r="N1" s="11" t="n">
+        <v>46308</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -15672,6 +17494,16 @@
         </is>
       </c>
       <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -15724,6 +17556,12 @@
       <c r="L3" s="14" t="n">
         <v>7029</v>
       </c>
+      <c r="M3" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>7030</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -15772,6 +17610,12 @@
       <c r="L4" s="14" t="n">
         <v>1723</v>
       </c>
+      <c r="M4" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N4" s="14" t="n">
+        <v>1724</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -15820,6 +17664,12 @@
       <c r="L5" s="14" t="n">
         <v>3418</v>
       </c>
+      <c r="M5" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>3418</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -15868,6 +17718,12 @@
       <c r="L6" s="14" t="n">
         <v>1351</v>
       </c>
+      <c r="M6" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>1351</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -15916,6 +17772,12 @@
       <c r="L7" s="14" t="n">
         <v>1114</v>
       </c>
+      <c r="M7" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>1114</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -15964,6 +17826,12 @@
       <c r="L8" s="14" t="n">
         <v>3374</v>
       </c>
+      <c r="M8" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N8" s="14" t="n">
+        <v>3375</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -16012,6 +17880,12 @@
       <c r="L9" s="14" t="n">
         <v>1975</v>
       </c>
+      <c r="M9" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N9" s="14" t="n">
+        <v>1976</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -16060,6 +17934,12 @@
       <c r="L10" s="14" t="n">
         <v>1207</v>
       </c>
+      <c r="M10" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N10" s="14" t="n">
+        <v>1211</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -16108,6 +17988,12 @@
       <c r="L11" s="14" t="n">
         <v>813</v>
       </c>
+      <c r="M11" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N11" s="14" t="n">
+        <v>813</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -16156,6 +18042,12 @@
       <c r="L12" s="14" t="n">
         <v>3418</v>
       </c>
+      <c r="M12" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N12" s="14" t="n">
+        <v>3418</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -16204,6 +18096,12 @@
       <c r="L13" s="14" t="n">
         <v>409</v>
       </c>
+      <c r="M13" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N13" s="14" t="n">
+        <v>406</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -16252,6 +18150,12 @@
       <c r="L14" s="14" t="n">
         <v>3484</v>
       </c>
+      <c r="M14" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N14" s="14" t="n">
+        <v>3486</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -16300,6 +18204,12 @@
       <c r="L15" s="14" t="n">
         <v>1986</v>
       </c>
+      <c r="M15" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N15" s="14" t="n">
+        <v>1987</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -16348,6 +18258,12 @@
       <c r="L16" s="14" t="n">
         <v>1336</v>
       </c>
+      <c r="M16" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N16" s="14" t="n">
+        <v>1336</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -16396,6 +18312,12 @@
       <c r="L17" s="14" t="n">
         <v>1338</v>
       </c>
+      <c r="M17" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N17" s="14" t="n">
+        <v>1340</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -16444,6 +18366,12 @@
       <c r="L18" s="14" t="n">
         <v>4505</v>
       </c>
+      <c r="M18" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N18" s="14" t="n">
+        <v>4510</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -16492,6 +18420,12 @@
       <c r="L19" s="14" t="n">
         <v>1677</v>
       </c>
+      <c r="M19" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N19" s="14" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -16540,6 +18474,12 @@
       <c r="L20" s="14" t="n">
         <v>4387</v>
       </c>
+      <c r="M20" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N20" s="14" t="n">
+        <v>4392</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -16588,6 +18528,12 @@
       <c r="L21" s="14" t="n">
         <v>3885</v>
       </c>
+      <c r="M21" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>3886</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -16636,6 +18582,12 @@
       <c r="L22" s="14" t="n">
         <v>87</v>
       </c>
+      <c r="M22" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>87</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -16684,6 +18636,12 @@
       <c r="L23" s="14" t="n">
         <v>443</v>
       </c>
+      <c r="M23" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N23" s="14" t="n">
+        <v>443</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -16732,6 +18690,12 @@
       <c r="L24" s="14" t="n">
         <v>1684</v>
       </c>
+      <c r="M24" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N24" s="14" t="n">
+        <v>1686</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -16780,6 +18744,12 @@
       <c r="L25" s="14" t="n">
         <v>3378</v>
       </c>
+      <c r="M25" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N25" s="14" t="n">
+        <v>3381</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -16828,6 +18798,12 @@
       <c r="L26" s="14" t="n">
         <v>1765</v>
       </c>
+      <c r="M26" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N26" s="14" t="n">
+        <v>1765</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -16876,6 +18852,12 @@
       <c r="L27" s="14" t="n">
         <v>538</v>
       </c>
+      <c r="M27" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N27" s="14" t="n">
+        <v>538</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -16924,6 +18906,12 @@
       <c r="L28" s="14" t="n">
         <v>1327</v>
       </c>
+      <c r="M28" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N28" s="14" t="n">
+        <v>1330</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -16972,6 +18960,12 @@
       <c r="L29" s="14" t="n">
         <v>652</v>
       </c>
+      <c r="M29" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N29" s="14" t="n">
+        <v>655</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -17020,6 +19014,12 @@
       <c r="L30" s="14" t="n">
         <v>36</v>
       </c>
+      <c r="M30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N30" s="14" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -17068,6 +19068,12 @@
       <c r="L31" s="14" t="n">
         <v>1325</v>
       </c>
+      <c r="M31" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N31" s="14" t="n">
+        <v>1325</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -17116,6 +19122,12 @@
       <c r="L32" s="14" t="n">
         <v>1428</v>
       </c>
+      <c r="M32" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N32" s="14" t="n">
+        <v>1428</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -17164,6 +19176,12 @@
       <c r="L33" s="14" t="n">
         <v>1335</v>
       </c>
+      <c r="M33" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N33" s="14" t="n">
+        <v>1335</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -17212,6 +19230,12 @@
       <c r="L34" s="14" t="n">
         <v>198</v>
       </c>
+      <c r="M34" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N34" s="14" t="n">
+        <v>199</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -17260,6 +19284,12 @@
       <c r="L35" s="14" t="n">
         <v>126</v>
       </c>
+      <c r="M35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N35" s="14" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -17308,6 +19338,12 @@
       <c r="L36" s="14" t="n">
         <v>995</v>
       </c>
+      <c r="M36" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N36" s="14" t="n">
+        <v>998</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -17356,6 +19392,12 @@
       <c r="L37" s="14" t="n">
         <v>205</v>
       </c>
+      <c r="M37" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N37" s="14" t="n">
+        <v>204</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -17404,6 +19446,12 @@
       <c r="L38" s="14" t="n">
         <v>219</v>
       </c>
+      <c r="M38" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N38" s="14" t="n">
+        <v>1330</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -17452,6 +19500,12 @@
       <c r="L39" s="14" t="n">
         <v>863</v>
       </c>
+      <c r="M39" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N39" s="14" t="n">
+        <v>865</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -17500,6 +19554,12 @@
       <c r="L40" s="14" t="n">
         <v>2250</v>
       </c>
+      <c r="M40" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N40" s="14" t="n">
+        <v>2254</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -17548,6 +19608,12 @@
       <c r="L41" s="14" t="n">
         <v>452</v>
       </c>
+      <c r="M41" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N41" s="14" t="n">
+        <v>453</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -17596,6 +19662,12 @@
       <c r="L42" s="14" t="n">
         <v>1594</v>
       </c>
+      <c r="M42" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N42" s="14" t="n">
+        <v>1595</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -17644,6 +19716,12 @@
       <c r="L43" s="14" t="n">
         <v>1168</v>
       </c>
+      <c r="M43" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N43" s="14" t="n">
+        <v>1169</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -17692,6 +19770,12 @@
       <c r="L44" s="14" t="n">
         <v>475</v>
       </c>
+      <c r="M44" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N44" s="14" t="n">
+        <v>477</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -17740,6 +19824,12 @@
       <c r="L45" s="14" t="n">
         <v>460</v>
       </c>
+      <c r="M45" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N45" s="14" t="n">
+        <v>464</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -17788,6 +19878,12 @@
       <c r="L46" s="14" t="n">
         <v>1055</v>
       </c>
+      <c r="M46" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N46" s="14" t="n">
+        <v>1056</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -17836,6 +19932,12 @@
       <c r="L47" s="14" t="n">
         <v>2572</v>
       </c>
+      <c r="M47" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N47" s="14" t="n">
+        <v>2572</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -17884,6 +19986,12 @@
       <c r="L48" s="14" t="n">
         <v>1429</v>
       </c>
+      <c r="M48" s="14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N48" s="14" t="n">
+        <v>1430</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -17932,6 +20040,12 @@
       <c r="L49" s="14" t="n">
         <v>1422</v>
       </c>
+      <c r="M49" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N49" s="14" t="n">
+        <v>1423</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -17980,6 +20094,12 @@
       <c r="L50" s="14" t="n">
         <v>1553</v>
       </c>
+      <c r="M50" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N50" s="14" t="n">
+        <v>1553</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -18028,6 +20148,12 @@
       <c r="L51" s="14" t="n">
         <v>2810</v>
       </c>
+      <c r="M51" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N51" s="14" t="n">
+        <v>2811</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -18076,6 +20202,12 @@
       <c r="L52" s="14" t="n">
         <v>745</v>
       </c>
+      <c r="M52" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N52" s="14" t="n">
+        <v>744</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -18124,6 +20256,12 @@
       <c r="L53" s="14" t="n">
         <v>1230</v>
       </c>
+      <c r="M53" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N53" s="14" t="n">
+        <v>1230</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -18172,6 +20310,12 @@
       <c r="L54" s="14" t="n">
         <v>675</v>
       </c>
+      <c r="M54" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N54" s="14" t="n">
+        <v>675</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -18218,6 +20362,12 @@
         <v>4.4</v>
       </c>
       <c r="L55" s="14" t="n">
+        <v>427</v>
+      </c>
+      <c r="M55" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N55" s="14" t="n">
         <v>427</v>
       </c>
     </row>
@@ -18466,7 +20616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:N113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -18501,6 +20651,12 @@
       <c r="L1" s="11" t="n">
         <v>46306</v>
       </c>
+      <c r="M1" s="11" t="n">
+        <v>46308</v>
+      </c>
+      <c r="N1" s="11" t="n">
+        <v>46308</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -18559,6 +20715,16 @@
         </is>
       </c>
       <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -18611,6 +20777,12 @@
       <c r="L3" s="14" t="n">
         <v>4572</v>
       </c>
+      <c r="M3" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>4572</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -18659,6 +20831,12 @@
       <c r="L4" s="14" t="n">
         <v>1234</v>
       </c>
+      <c r="M4" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N4" s="14" t="n">
+        <v>1234</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -18707,6 +20885,12 @@
       <c r="L5" s="14" t="n">
         <v>460</v>
       </c>
+      <c r="M5" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>460</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -18755,6 +20939,12 @@
       <c r="L6" s="14" t="n">
         <v>11590</v>
       </c>
+      <c r="M6" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>11591</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -18803,6 +20993,12 @@
       <c r="L7" s="14" t="n">
         <v>2051</v>
       </c>
+      <c r="M7" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>2052</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -18851,6 +21047,12 @@
       <c r="L8" s="14" t="n">
         <v>919</v>
       </c>
+      <c r="M8" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N8" s="14" t="n">
+        <v>919</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -18899,6 +21101,12 @@
       <c r="L9" s="14" t="n">
         <v>1605</v>
       </c>
+      <c r="M9" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N9" s="14" t="n">
+        <v>1605</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -18947,6 +21155,12 @@
       <c r="L10" s="14" t="n">
         <v>2026</v>
       </c>
+      <c r="M10" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N10" s="14" t="n">
+        <v>2024</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -18995,6 +21209,12 @@
       <c r="L11" s="14" t="n">
         <v>3081</v>
       </c>
+      <c r="M11" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N11" s="14" t="n">
+        <v>3081</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -19043,6 +21263,12 @@
       <c r="L12" s="14" t="n">
         <v>3631</v>
       </c>
+      <c r="M12" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N12" s="14" t="n">
+        <v>3631</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -19091,6 +21317,12 @@
       <c r="L13" s="14" t="n">
         <v>21275</v>
       </c>
+      <c r="M13" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N13" s="14" t="n">
+        <v>21275</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -19139,6 +21371,12 @@
       <c r="L14" s="14" t="n">
         <v>2949</v>
       </c>
+      <c r="M14" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N14" s="14" t="n">
+        <v>2952</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -19187,6 +21425,12 @@
       <c r="L15" s="14" t="n">
         <v>4211</v>
       </c>
+      <c r="M15" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N15" s="14" t="n">
+        <v>4216</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -19235,6 +21479,12 @@
       <c r="L16" s="14" t="n">
         <v>2394</v>
       </c>
+      <c r="M16" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N16" s="14" t="n">
+        <v>2394</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -19283,6 +21533,12 @@
       <c r="L17" s="14" t="n">
         <v>4</v>
       </c>
+      <c r="M17" s="14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N17" s="14" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -19331,6 +21587,12 @@
       <c r="L18" s="14" t="n">
         <v>12126</v>
       </c>
+      <c r="M18" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N18" s="14" t="n">
+        <v>12129</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -19379,6 +21641,12 @@
       <c r="L19" s="14" t="n">
         <v>3109</v>
       </c>
+      <c r="M19" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N19" s="14" t="n">
+        <v>3112</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -19427,6 +21695,12 @@
       <c r="L20" s="14" t="n">
         <v>9250</v>
       </c>
+      <c r="M20" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N20" s="14" t="n">
+        <v>9251</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -19475,6 +21749,12 @@
       <c r="L21" s="14" t="n">
         <v>8</v>
       </c>
+      <c r="M21" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -19523,6 +21803,12 @@
       <c r="L22" s="14" t="n">
         <v>6135</v>
       </c>
+      <c r="M22" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>6134</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -19571,6 +21857,12 @@
       <c r="L23" s="14" t="n">
         <v>1746</v>
       </c>
+      <c r="M23" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N23" s="14" t="n">
+        <v>1759</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -19619,6 +21911,12 @@
       <c r="L24" s="14" t="n">
         <v>1063</v>
       </c>
+      <c r="M24" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N24" s="14" t="n">
+        <v>1063</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -19667,6 +21965,12 @@
       <c r="L25" s="14" t="n">
         <v>2057</v>
       </c>
+      <c r="M25" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N25" s="14" t="n">
+        <v>2056</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -19715,6 +22019,12 @@
       <c r="L26" s="14" t="n">
         <v>2780</v>
       </c>
+      <c r="M26" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N26" s="14" t="n">
+        <v>2782</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -19763,6 +22073,12 @@
       <c r="L27" s="14" t="n">
         <v>11108</v>
       </c>
+      <c r="M27" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N27" s="14" t="n">
+        <v>11117</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -19811,6 +22127,12 @@
       <c r="L28" s="14" t="n">
         <v>5492</v>
       </c>
+      <c r="M28" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N28" s="14" t="n">
+        <v>5494</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -19859,6 +22181,12 @@
       <c r="L29" s="14" t="n">
         <v>4020</v>
       </c>
+      <c r="M29" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N29" s="14" t="n">
+        <v>4030</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -19907,6 +22235,12 @@
       <c r="L30" s="14" t="n">
         <v>1582</v>
       </c>
+      <c r="M30" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N30" s="14" t="n">
+        <v>1590</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -19955,6 +22289,12 @@
       <c r="L31" s="14" t="n">
         <v>1582</v>
       </c>
+      <c r="M31" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N31" s="14" t="n">
+        <v>1590</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -20003,6 +22343,12 @@
       <c r="L32" s="14" t="n">
         <v>2814</v>
       </c>
+      <c r="M32" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N32" s="14" t="n">
+        <v>2818</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -20051,6 +22397,12 @@
       <c r="L33" s="14" t="n">
         <v>18975</v>
       </c>
+      <c r="M33" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N33" s="14" t="n">
+        <v>18974</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -20099,6 +22451,12 @@
       <c r="L34" s="14" t="n">
         <v>39715</v>
       </c>
+      <c r="M34" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N34" s="14" t="n">
+        <v>39719</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -20147,6 +22505,12 @@
       <c r="L35" s="14" t="n">
         <v>5228</v>
       </c>
+      <c r="M35" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N35" s="14" t="n">
+        <v>5228</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -20195,6 +22559,12 @@
       <c r="L36" s="14" t="n">
         <v>10391</v>
       </c>
+      <c r="M36" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N36" s="14" t="n">
+        <v>10391</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -20243,6 +22613,12 @@
       <c r="L37" s="14" t="n">
         <v>7410</v>
       </c>
+      <c r="M37" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N37" s="14" t="n">
+        <v>7408</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -20291,6 +22667,12 @@
       <c r="L38" s="14" t="n">
         <v>540</v>
       </c>
+      <c r="M38" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N38" s="14" t="n">
+        <v>540</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -20339,6 +22721,12 @@
       <c r="L39" s="14" t="n">
         <v>1124</v>
       </c>
+      <c r="M39" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N39" s="14" t="n">
+        <v>1123</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -20387,6 +22775,12 @@
       <c r="L40" s="14" t="n">
         <v>540</v>
       </c>
+      <c r="M40" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N40" s="14" t="n">
+        <v>540</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -20435,6 +22829,12 @@
       <c r="L41" s="14" t="n">
         <v>2628</v>
       </c>
+      <c r="M41" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N41" s="14" t="n">
+        <v>2628</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -20483,6 +22883,12 @@
       <c r="L42" s="14" t="n">
         <v>1447</v>
       </c>
+      <c r="M42" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N42" s="14" t="n">
+        <v>1447</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -20531,6 +22937,12 @@
       <c r="L43" s="14" t="n">
         <v>955</v>
       </c>
+      <c r="M43" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N43" s="14" t="n">
+        <v>957</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -20579,6 +22991,12 @@
       <c r="L44" s="14" t="n">
         <v>4200</v>
       </c>
+      <c r="M44" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N44" s="14" t="n">
+        <v>4208</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -20627,6 +23045,12 @@
       <c r="L45" s="14" t="n">
         <v>3491</v>
       </c>
+      <c r="M45" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N45" s="14" t="n">
+        <v>3496</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -20675,6 +23099,12 @@
       <c r="L46" s="14" t="n">
         <v>7888</v>
       </c>
+      <c r="M46" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N46" s="14" t="n">
+        <v>7898</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -20723,6 +23153,12 @@
       <c r="L47" s="14" t="n">
         <v>6135</v>
       </c>
+      <c r="M47" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N47" s="14" t="n">
+        <v>6134</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -20771,6 +23207,12 @@
       <c r="L48" s="14" t="n">
         <v>983</v>
       </c>
+      <c r="M48" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N48" s="14" t="n">
+        <v>983</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -20819,6 +23261,12 @@
       <c r="L49" s="14" t="n">
         <v>3658</v>
       </c>
+      <c r="M49" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N49" s="14" t="n">
+        <v>3663</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -20867,6 +23315,12 @@
       <c r="L50" s="14" t="n">
         <v>182</v>
       </c>
+      <c r="M50" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N50" s="14" t="n">
+        <v>182</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -20915,6 +23369,12 @@
       <c r="L51" s="14" t="n">
         <v>182</v>
       </c>
+      <c r="M51" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N51" s="14" t="n">
+        <v>339</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -20963,6 +23423,12 @@
       <c r="L52" s="14" t="n">
         <v>296</v>
       </c>
+      <c r="M52" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N52" s="14" t="n">
+        <v>296</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -21011,6 +23477,12 @@
       <c r="L53" s="14" t="n">
         <v>339</v>
       </c>
+      <c r="M53" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N53" s="14" t="n">
+        <v>339</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -21059,6 +23531,12 @@
       <c r="L54" s="14" t="n">
         <v>4122</v>
       </c>
+      <c r="M54" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N54" s="14" t="n">
+        <v>339</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -21107,6 +23585,12 @@
       <c r="L55" s="14" t="n">
         <v>56</v>
       </c>
+      <c r="M55" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N55" s="14" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -21155,6 +23639,12 @@
       <c r="L56" s="14" t="n">
         <v>493</v>
       </c>
+      <c r="M56" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N56" s="14" t="n">
+        <v>493</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -21203,6 +23693,12 @@
       <c r="L57" s="14" t="n">
         <v>7852</v>
       </c>
+      <c r="M57" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N57" s="14" t="n">
+        <v>7852</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -21251,6 +23747,12 @@
       <c r="L58" s="14" t="n">
         <v>4019</v>
       </c>
+      <c r="M58" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N58" s="14" t="n">
+        <v>4019</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -21299,6 +23801,12 @@
       <c r="L59" s="14" t="n">
         <v>2920</v>
       </c>
+      <c r="M59" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v>2930</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -21347,6 +23855,12 @@
       <c r="L60" s="14" t="n">
         <v>2252</v>
       </c>
+      <c r="M60" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N60" s="14" t="n">
+        <v>2252</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n">
@@ -21395,6 +23909,12 @@
       <c r="L61" s="14" t="n">
         <v>7856</v>
       </c>
+      <c r="M61" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N61" s="14" t="n">
+        <v>7870</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -21443,6 +23963,12 @@
       <c r="L62" s="14" t="n">
         <v>3618</v>
       </c>
+      <c r="M62" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N62" s="14" t="n">
+        <v>3618</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -21491,6 +24017,12 @@
       <c r="L63" s="14" t="n">
         <v>4769</v>
       </c>
+      <c r="M63" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N63" s="14" t="n">
+        <v>4769</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -21539,6 +24071,12 @@
       <c r="L64" s="14" t="n">
         <v>2626</v>
       </c>
+      <c r="M64" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N64" s="14" t="n">
+        <v>2626</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -21587,6 +24125,12 @@
       <c r="L65" s="14" t="n">
         <v>2903</v>
       </c>
+      <c r="M65" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N65" s="14" t="n">
+        <v>2903</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -21635,6 +24179,12 @@
       <c r="L66" s="14" t="n">
         <v>6446</v>
       </c>
+      <c r="M66" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N66" s="14" t="n">
+        <v>6446</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -21683,6 +24233,12 @@
       <c r="L67" s="14" t="n">
         <v>781</v>
       </c>
+      <c r="M67" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N67" s="14" t="n">
+        <v>781</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -21731,6 +24287,12 @@
       <c r="L68" s="14" t="n">
         <v>19116</v>
       </c>
+      <c r="M68" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N68" s="14" t="n">
+        <v>19118</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -21779,6 +24341,12 @@
       <c r="L69" s="14" t="n">
         <v>2922</v>
       </c>
+      <c r="M69" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N69" s="14" t="n">
+        <v>2923</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -21827,6 +24395,12 @@
       <c r="L70" s="14" t="n">
         <v>2630</v>
       </c>
+      <c r="M70" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N70" s="14" t="n">
+        <v>2630</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
@@ -21875,6 +24449,12 @@
       <c r="L71" s="14" t="n">
         <v>1193</v>
       </c>
+      <c r="M71" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N71" s="14" t="n">
+        <v>1193</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n">
@@ -21923,6 +24503,12 @@
       <c r="L72" s="14" t="n">
         <v>4165</v>
       </c>
+      <c r="M72" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N72" s="14" t="n">
+        <v>4165</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n">
@@ -21971,6 +24557,12 @@
       <c r="L73" s="14" t="n">
         <v>3870</v>
       </c>
+      <c r="M73" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N73" s="14" t="n">
+        <v>3872</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -22019,6 +24611,12 @@
       <c r="L74" s="14" t="n">
         <v>756</v>
       </c>
+      <c r="M74" s="14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N74" s="14" t="n">
+        <v>756</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n">
@@ -22067,6 +24665,12 @@
       <c r="L75" s="14" t="n">
         <v>4661</v>
       </c>
+      <c r="M75" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N75" s="14" t="n">
+        <v>4666</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -22115,6 +24719,12 @@
       <c r="L76" s="14" t="n">
         <v>5291</v>
       </c>
+      <c r="M76" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N76" s="14" t="n">
+        <v>5293</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -22163,6 +24773,12 @@
       <c r="L77" s="14" t="n">
         <v>159</v>
       </c>
+      <c r="M77" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N77" s="14" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -22211,6 +24827,12 @@
       <c r="L78" s="14" t="n">
         <v>1132</v>
       </c>
+      <c r="M78" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N78" s="14" t="n">
+        <v>1132</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -22259,6 +24881,12 @@
       <c r="L79" s="14" t="n">
         <v>634</v>
       </c>
+      <c r="M79" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N79" s="14" t="n">
+        <v>634</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -22307,6 +24935,12 @@
       <c r="L80" s="14" t="n">
         <v>1187</v>
       </c>
+      <c r="M80" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N80" s="14" t="n">
+        <v>1187</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -22355,6 +24989,12 @@
       <c r="L81" s="14" t="n">
         <v>1566</v>
       </c>
+      <c r="M81" s="14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N81" s="14" t="n">
+        <v>1566</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -22403,6 +25043,12 @@
       <c r="L82" s="14" t="n">
         <v>11754</v>
       </c>
+      <c r="M82" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N82" s="14" t="n">
+        <v>11761</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -22451,6 +25097,12 @@
       <c r="L83" s="14" t="n">
         <v>15</v>
       </c>
+      <c r="M83" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N83" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n">
@@ -22499,6 +25151,12 @@
       <c r="L84" s="14" t="n">
         <v>5940</v>
       </c>
+      <c r="M84" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N84" s="14" t="n">
+        <v>5941</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n">
@@ -22547,6 +25205,12 @@
       <c r="L85" s="14" t="n">
         <v>3271</v>
       </c>
+      <c r="M85" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N85" s="14" t="n">
+        <v>3273</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -22595,6 +25259,12 @@
       <c r="L86" s="14" t="n">
         <v>10433</v>
       </c>
+      <c r="M86" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N86" s="14" t="n">
+        <v>10435</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
@@ -22643,6 +25313,12 @@
       <c r="L87" s="14" t="n">
         <v>4152</v>
       </c>
+      <c r="M87" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N87" s="14" t="n">
+        <v>4152</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
@@ -22691,6 +25367,12 @@
       <c r="L88" s="14" t="n">
         <v>2998</v>
       </c>
+      <c r="M88" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N88" s="14" t="n">
+        <v>2998</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
@@ -22739,6 +25421,12 @@
       <c r="L89" s="14" t="n">
         <v>1295</v>
       </c>
+      <c r="M89" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N89" s="14" t="n">
+        <v>1295</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -22787,6 +25475,12 @@
       <c r="L90" s="14" t="n">
         <v>2241</v>
       </c>
+      <c r="M90" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N90" s="14" t="n">
+        <v>2241</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
@@ -22835,6 +25529,12 @@
       <c r="L91" s="14" t="n">
         <v>7973</v>
       </c>
+      <c r="M91" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N91" s="14" t="n">
+        <v>7975</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
@@ -22883,6 +25583,12 @@
       <c r="L92" s="14" t="n">
         <v>783</v>
       </c>
+      <c r="M92" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N92" s="14" t="n">
+        <v>783</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
@@ -22931,6 +25637,12 @@
       <c r="L93" s="14" t="n">
         <v>791</v>
       </c>
+      <c r="M93" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N93" s="14" t="n">
+        <v>793</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n">
@@ -22979,6 +25691,12 @@
       <c r="L94" s="14" t="n">
         <v>2597</v>
       </c>
+      <c r="M94" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N94" s="14" t="n">
+        <v>2597</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
@@ -23027,6 +25745,12 @@
       <c r="L95" s="14" t="n">
         <v>1680</v>
       </c>
+      <c r="M95" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N95" s="14" t="n">
+        <v>1680</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
@@ -23075,6 +25799,12 @@
       <c r="L96" s="14" t="n">
         <v>6440</v>
       </c>
+      <c r="M96" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N96" s="14" t="n">
+        <v>6441</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
@@ -23123,6 +25853,12 @@
       <c r="L97" s="14" t="n">
         <v>2315</v>
       </c>
+      <c r="M97" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N97" s="14" t="n">
+        <v>2315</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -23171,6 +25907,12 @@
       <c r="L98" s="14" t="n">
         <v>1937</v>
       </c>
+      <c r="M98" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N98" s="14" t="n">
+        <v>1938</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
@@ -23219,6 +25961,12 @@
       <c r="L99" s="14" t="n">
         <v>5587</v>
       </c>
+      <c r="M99" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N99" s="14" t="n">
+        <v>5587</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -23267,6 +26015,12 @@
       <c r="L100" s="14" t="n">
         <v>17808</v>
       </c>
+      <c r="M100" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N100" s="14" t="n">
+        <v>17811</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -23315,6 +26069,12 @@
       <c r="L101" s="14" t="n">
         <v>6187</v>
       </c>
+      <c r="M101" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N101" s="14" t="n">
+        <v>6189</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -23363,6 +26123,12 @@
       <c r="L102" s="14" t="n">
         <v>5284</v>
       </c>
+      <c r="M102" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N102" s="14" t="n">
+        <v>5284</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
@@ -23411,6 +26177,12 @@
       <c r="L103" s="14" t="n">
         <v>1177</v>
       </c>
+      <c r="M103" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N103" s="14" t="n">
+        <v>1178</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -23459,6 +26231,12 @@
       <c r="L104" s="14" t="n">
         <v>4077</v>
       </c>
+      <c r="M104" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N104" s="14" t="n">
+        <v>4078</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
@@ -23507,6 +26285,12 @@
       <c r="L105" s="14" t="n">
         <v>1177</v>
       </c>
+      <c r="M105" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N105" s="14" t="n">
+        <v>1178</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
@@ -23555,6 +26339,12 @@
       <c r="L106" s="14" t="n">
         <v>10982</v>
       </c>
+      <c r="M106" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N106" s="14" t="n">
+        <v>10984</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -23603,6 +26393,12 @@
       <c r="L107" s="14" t="n">
         <v>3158</v>
       </c>
+      <c r="M107" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N107" s="14" t="n">
+        <v>3158</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -23651,6 +26447,12 @@
       <c r="L108" s="14" t="n">
         <v>3066</v>
       </c>
+      <c r="M108" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N108" s="14" t="n">
+        <v>3067</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
@@ -23699,6 +26501,12 @@
       <c r="L109" s="14" t="n">
         <v>2643</v>
       </c>
+      <c r="M109" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N109" s="14" t="n">
+        <v>2644</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
@@ -23747,6 +26555,12 @@
       <c r="L110" s="14" t="n">
         <v>1886</v>
       </c>
+      <c r="M110" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N110" s="14" t="n">
+        <v>1886</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
@@ -23795,6 +26609,12 @@
       <c r="L111" s="14" t="n">
         <v>1196</v>
       </c>
+      <c r="M111" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N111" s="14" t="n">
+        <v>1196</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -23843,6 +26663,12 @@
       <c r="L112" s="14" t="n">
         <v>2462</v>
       </c>
+      <c r="M112" s="14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N112" s="14" t="n">
+        <v>2464</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
@@ -23890,6 +26716,12 @@
       </c>
       <c r="L113" s="14" t="n">
         <v>2658</v>
+      </c>
+      <c r="M113" s="14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N113" s="14" t="n">
+        <v>2664</v>
       </c>
     </row>
   </sheetData>
@@ -23903,7 +26735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23938,6 +26770,12 @@
       <c r="L1" s="11" t="n">
         <v>46306</v>
       </c>
+      <c r="M1" s="11" t="n">
+        <v>46308</v>
+      </c>
+      <c r="N1" s="11" t="n">
+        <v>46308</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -23996,6 +26834,16 @@
         </is>
       </c>
       <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -24048,6 +26896,12 @@
       <c r="L3" s="14" t="n">
         <v>14386</v>
       </c>
+      <c r="M3" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>14385</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -24096,6 +26950,12 @@
       <c r="L4" s="14" t="n">
         <v>1205</v>
       </c>
+      <c r="M4" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N4" s="14" t="n">
+        <v>1207</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -24144,6 +27004,12 @@
       <c r="L5" s="14" t="n">
         <v>15</v>
       </c>
+      <c r="M5" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -24192,6 +27058,12 @@
       <c r="L6" s="14" t="n">
         <v>64</v>
       </c>
+      <c r="M6" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -24240,6 +27112,12 @@
       <c r="L7" s="14" t="n">
         <v>4840</v>
       </c>
+      <c r="M7" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>4839</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -24288,6 +27166,12 @@
       <c r="L8" s="14" t="n">
         <v>2069</v>
       </c>
+      <c r="M8" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N8" s="14" t="n">
+        <v>2069</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -24336,6 +27220,12 @@
       <c r="L9" s="14" t="n">
         <v>5786</v>
       </c>
+      <c r="M9" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N9" s="14" t="n">
+        <v>5790</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -24384,6 +27274,12 @@
       <c r="L10" s="14" t="n">
         <v>6562</v>
       </c>
+      <c r="M10" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N10" s="14" t="n">
+        <v>6565</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -24432,6 +27328,12 @@
       <c r="L11" s="14" t="n">
         <v>10581</v>
       </c>
+      <c r="M11" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N11" s="14" t="n">
+        <v>10580</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -24480,6 +27382,12 @@
       <c r="L12" s="14" t="n">
         <v>12241</v>
       </c>
+      <c r="M12" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N12" s="14" t="n">
+        <v>12241</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -24528,6 +27436,12 @@
       <c r="L13" s="14" t="n">
         <v>10710</v>
       </c>
+      <c r="M13" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N13" s="14" t="n">
+        <v>10711</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -24576,6 +27490,12 @@
       <c r="L14" s="14" t="n">
         <v>6816</v>
       </c>
+      <c r="M14" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N14" s="14" t="n">
+        <v>6818</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -24624,6 +27544,12 @@
       <c r="L15" s="14" t="n">
         <v>3607</v>
       </c>
+      <c r="M15" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N15" s="14" t="n">
+        <v>3608</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -24672,6 +27598,12 @@
       <c r="L16" s="14" t="n">
         <v>4505</v>
       </c>
+      <c r="M16" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N16" s="14" t="n">
+        <v>4505</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -24720,6 +27652,12 @@
       <c r="L17" s="14" t="n">
         <v>878</v>
       </c>
+      <c r="M17" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N17" s="14" t="n">
+        <v>879</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -24768,6 +27706,12 @@
       <c r="L18" s="14" t="n">
         <v>19724</v>
       </c>
+      <c r="M18" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N18" s="14" t="n">
+        <v>19723</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -24816,6 +27760,12 @@
       <c r="L19" s="14" t="n">
         <v>2022</v>
       </c>
+      <c r="M19" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N19" s="14" t="n">
+        <v>2023</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -24864,6 +27814,12 @@
       <c r="L20" s="14" t="n">
         <v>2047</v>
       </c>
+      <c r="M20" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N20" s="14" t="n">
+        <v>2060</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -24912,6 +27868,12 @@
       <c r="L21" s="14" t="n">
         <v>8786</v>
       </c>
+      <c r="M21" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>8787</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -24960,6 +27922,12 @@
       <c r="L22" s="14" t="n">
         <v>1120</v>
       </c>
+      <c r="M22" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N22" s="14" t="n">
+        <v>1121</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -25008,6 +27976,12 @@
       <c r="L23" s="14" t="n">
         <v>676</v>
       </c>
+      <c r="M23" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N23" s="14" t="n">
+        <v>676</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -25054,6 +28028,12 @@
         <v>4</v>
       </c>
       <c r="L24" s="14" t="n">
+        <v>1825</v>
+      </c>
+      <c r="M24" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N24" s="14" t="n">
         <v>1825</v>
       </c>
     </row>
@@ -25068,7 +28048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -25103,6 +28083,12 @@
       <c r="L1" s="11" t="n">
         <v>46306</v>
       </c>
+      <c r="M1" s="11" t="n">
+        <v>46308</v>
+      </c>
+      <c r="N1" s="11" t="n">
+        <v>46308</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -25161,6 +28147,16 @@
         </is>
       </c>
       <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>Review Count</t>
+        </is>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>GMB Live Rating</t>
+        </is>
+      </c>
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>Review Count</t>
         </is>
@@ -25213,6 +28209,12 @@
       <c r="L3" s="14" t="n">
         <v>1595</v>
       </c>
+      <c r="M3" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>1596</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
@@ -25261,6 +28263,12 @@
       <c r="L4" s="14" t="n">
         <v>1042</v>
       </c>
+      <c r="M4" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N4" s="14" t="n">
+        <v>1042</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -25309,6 +28317,12 @@
       <c r="L5" s="14" t="n">
         <v>1982</v>
       </c>
+      <c r="M5" s="14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>1982</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -25357,6 +28371,12 @@
       <c r="L6" s="14" t="n">
         <v>1187</v>
       </c>
+      <c r="M6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>1186</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -25405,6 +28425,12 @@
       <c r="L7" s="14" t="n">
         <v>1414</v>
       </c>
+      <c r="M7" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>1414</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -25453,6 +28479,12 @@
       <c r="L8" s="14" t="n">
         <v>24</v>
       </c>
+      <c r="M8" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N8" s="14" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="9">
      